--- a/data/germany/p6_deployment/data_preparation/df_filled.xlsx
+++ b/data/germany/p6_deployment/data_preparation/df_filled.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO42"/>
+  <dimension ref="A1:AO33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -786,45 +786,45 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>YZZcMwBs</t>
+          <t>pWQQJq6l</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45528.4375</v>
+        <v>45520.54166666666</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">petersen m 
+          <t xml:space="preserve">aytekin d 
   ger </t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">wwk arena
-  augsburg </t>
+          <t xml:space="preserve">leuna chemie stadion
+  halle </t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>30660</v>
+        <v>15057</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>fTVNku3I</t>
+          <t>boX3cIQa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Ig1f1fy3</t>
+          <t>ILyJuN3g</t>
         </is>
       </c>
       <c r="H3" t="n">
         <v>59</v>
       </c>
       <c r="I3" t="n">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K3" t="n">
         <v>20242025</v>
@@ -836,7 +836,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>bundesliga</t>
+          <t>dfb pokal</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -845,131 +845,103 @@
           <t>v9k3aY5F</t>
         </is>
       </c>
-      <c r="P3" t="n">
-        <v>25.41333333333333</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>186.0030303030303</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1.462323232323232</v>
-      </c>
-      <c r="S3" t="n">
-        <v>74.33111111111111</v>
-      </c>
-      <c r="T3" t="n">
-        <v>6657146.464646464</v>
-      </c>
-      <c r="U3" t="n">
-        <v>77.32606060606061</v>
-      </c>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>26.18181818181818</v>
+        <v>25.83181818181818</v>
       </c>
       <c r="W3" t="n">
-        <v>183.1272727272727</v>
+        <v>185.1212121212121</v>
       </c>
       <c r="X3" t="n">
-        <v>1.181818181818182</v>
+        <v>1</v>
       </c>
       <c r="Y3" t="n">
-        <v>73.16363636363636</v>
+        <v>70.01363636363637</v>
       </c>
       <c r="Z3" t="n">
-        <v>4815909.090909092</v>
+        <v>2280151.515151515</v>
       </c>
       <c r="AA3" t="n">
-        <v>75.94545454545455</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>23.899139420521</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>184.2982721956406</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>1.139229228373965</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>71.05004414445204</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>3913032.094915318</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>76.51723674717095</v>
-      </c>
+        <v>72.97727272727273</v>
+      </c>
+      <c r="AB3" t="inlineStr"/>
+      <c r="AC3" t="inlineStr"/>
+      <c r="AD3" t="inlineStr"/>
+      <c r="AE3" t="inlineStr"/>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="inlineStr"/>
       <c r="AH3" t="n">
-        <v>24.86158126293996</v>
+        <v>25.85441729323308</v>
       </c>
       <c r="AI3" t="n">
-        <v>184.8690601049726</v>
+        <v>185.9193609022556</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1.111249364352911</v>
+        <v>1</v>
       </c>
       <c r="AK3" t="n">
-        <v>68.34426964149505</v>
+        <v>66.75798872180451</v>
       </c>
       <c r="AL3" t="n">
-        <v>2456707.041607642</v>
+        <v>1303942.669172932</v>
       </c>
       <c r="AM3" t="n">
-        <v>73.74422787040064</v>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>hAcTWKKN</t>
-        </is>
-      </c>
+        <v>71.29758771929825</v>
+      </c>
+      <c r="AN3" t="inlineStr"/>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>xzRzG0VI</t>
+          <t>QHesBmSQ</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>GbeXvnR8</t>
+          <t>hIsO3XFj</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45528.4375</v>
+        <v>45520.54166666666</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">schlager d 
+          <t xml:space="preserve">willenborg f 
   ger </t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">europa park stadion
-  freiburg </t>
+          <t xml:space="preserve">brita arena
+  wiesbaden </t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>34700</v>
+        <v>12566</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>fiEQZ7C7</t>
+          <t>ObxFt3lm</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>nJQmYp1B</t>
+          <t>EuakNmc1</t>
         </is>
       </c>
       <c r="H4" t="n">
         <v>59</v>
       </c>
       <c r="I4" t="n">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K4" t="n">
         <v>20242025</v>
@@ -981,144 +953,144 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>bundesliga</t>
+          <t>dfb pokal</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>nJQmYp1B</t>
+          <t>EuakNmc1</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>fiEQZ7C7</t>
+          <t>8vndvXTk</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>27.4</v>
+        <v>26.10227272727273</v>
       </c>
       <c r="Q4" t="n">
-        <v>183.3909090909091</v>
+        <v>185.875</v>
       </c>
       <c r="R4" t="n">
-        <v>1.709090909090909</v>
+        <v>1</v>
       </c>
       <c r="S4" t="n">
-        <v>75.58181818181818</v>
+        <v>67.18181818181819</v>
       </c>
       <c r="T4" t="n">
-        <v>9104545.454545453</v>
+        <v>1195738.636363636</v>
       </c>
       <c r="U4" t="n">
-        <v>77.26363636363635</v>
+        <v>69.51136363636363</v>
       </c>
       <c r="V4" t="n">
-        <v>24.40909090909091</v>
+        <v>25.64545454545454</v>
       </c>
       <c r="W4" t="n">
-        <v>184.6454545454546</v>
+        <v>183.1363636363637</v>
       </c>
       <c r="X4" t="n">
-        <v>1.490909090909091</v>
+        <v>1.572727272727272</v>
       </c>
       <c r="Y4" t="n">
-        <v>76</v>
+        <v>74.40909090909091</v>
       </c>
       <c r="Z4" t="n">
-        <v>11738181.81818181</v>
+        <v>6797272.727272728</v>
       </c>
       <c r="AA4" t="n">
-        <v>79.16363636363636</v>
+        <v>78.53636363636363</v>
       </c>
       <c r="AB4" t="n">
-        <v>24.61444862155389</v>
+        <v>24.38020833333334</v>
       </c>
       <c r="AC4" t="n">
-        <v>184.9235651629072</v>
+        <v>183.2413194444445</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.411942355889725</v>
+        <v>1</v>
       </c>
       <c r="AE4" t="n">
-        <v>72.99003132832081</v>
+        <v>64.93229166666666</v>
       </c>
       <c r="AF4" t="n">
-        <v>5321504.072681705</v>
+        <v>1005946.180555556</v>
       </c>
       <c r="AG4" t="n">
-        <v>76.56177631578949</v>
+        <v>69.11458333333334</v>
       </c>
       <c r="AH4" t="n">
-        <v>24.40472222222222</v>
+        <v>26.37440476190476</v>
       </c>
       <c r="AI4" t="n">
-        <v>182.5288888888889</v>
+        <v>185.5630952380952</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1.280753968253968</v>
+        <v>1.522420634920635</v>
       </c>
       <c r="AK4" t="n">
-        <v>71.27392857142857</v>
+        <v>72.53829365079365</v>
       </c>
       <c r="AL4" t="n">
-        <v>5835730.158730159</v>
+        <v>4587232.142857144</v>
       </c>
       <c r="AM4" t="n">
-        <v>75.7297619047619</v>
+        <v>76.54583333333332</v>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>v9WoiHGP</t>
+          <t>QTAUlvUP</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>M5BRZDsC</t>
+          <t>vZA6VYpf</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>O48oHrZ1</t>
+          <t>EF8gXauC</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45528.4375</v>
+        <v>45520.54166666666</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">sather a 
+          <t xml:space="preserve">fritz m 
   ger </t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">prezero arena
-  sinsheim </t>
+          <t xml:space="preserve">flyeralarm arena
+  wurzburger </t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>30150</v>
+        <v>13090</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
+          <t>nVM1YUFj</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
           <t>hQAtP9Sl</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>63WsD2ei</t>
         </is>
       </c>
       <c r="H5" t="n">
         <v>59</v>
       </c>
       <c r="I5" t="n">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K5" t="n">
         <v>20242025</v>
@@ -1130,144 +1102,112 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>bundesliga</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
+          <t>dfb pokal</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr">
         <is>
           <t>nJQmYp1B</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>ILyJuN3g</t>
-        </is>
-      </c>
-      <c r="P5" t="n">
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="n">
         <v>26.76363636363636</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="W5" t="n">
         <v>185.5272727272727</v>
       </c>
-      <c r="R5" t="n">
+      <c r="X5" t="n">
         <v>1.818181818181818</v>
       </c>
-      <c r="S5" t="n">
+      <c r="Y5" t="n">
         <v>75.38181818181819</v>
       </c>
-      <c r="T5" t="n">
+      <c r="Z5" t="n">
         <v>8930000</v>
       </c>
-      <c r="U5" t="n">
+      <c r="AA5" t="n">
         <v>78.72727272727272</v>
       </c>
-      <c r="V5" t="n">
-        <v>25.25757575757576</v>
-      </c>
-      <c r="W5" t="n">
-        <v>186.5454545454545</v>
-      </c>
-      <c r="X5" t="n">
-        <v>1.075757575757576</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>68.48484848484848</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>1749242.424242425</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>72.46969696969698</v>
-      </c>
-      <c r="AB5" t="n">
+      <c r="AB5" t="inlineStr"/>
+      <c r="AC5" t="inlineStr"/>
+      <c r="AD5" t="inlineStr"/>
+      <c r="AE5" t="inlineStr"/>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="inlineStr"/>
+      <c r="AH5" t="n">
         <v>24.22996031746032</v>
       </c>
-      <c r="AC5" t="n">
+      <c r="AI5" t="n">
         <v>185.4827380952381</v>
       </c>
-      <c r="AD5" t="n">
+      <c r="AJ5" t="n">
         <v>1.367063492063492</v>
       </c>
-      <c r="AE5" t="n">
+      <c r="AK5" t="n">
         <v>71.57718253968254</v>
       </c>
-      <c r="AF5" t="n">
+      <c r="AL5" t="n">
         <v>5224836.30952381</v>
       </c>
-      <c r="AG5" t="n">
+      <c r="AM5" t="n">
         <v>77.88630952380952</v>
       </c>
-      <c r="AH5" t="n">
-        <v>25.07421785139177</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>185.8624194847021</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>1.015182884748102</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>66.6799373130895</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>1411003.637566138</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>71.2854267310789</v>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>KUx4Q7x1</t>
-        </is>
-      </c>
+      <c r="AN5" t="inlineStr"/>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>A15eUM4C</t>
+          <t>CQTUFgPk</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>2FREIeA6</t>
+          <t>lONsG15D</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45528.4375</v>
+        <v>45520.65625</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">dingert c 
+          <t xml:space="preserve">fritz m 
   ger </t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">mewa arena
-  mainz </t>
+          <t xml:space="preserve">donaustadion
+  ulm </t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>34000</v>
+        <v>19500</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>EuakNmc1</t>
+          <t>tbC3EcQn</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>pzHW4oaE</t>
+          <t>nVp0wiqd</t>
         </is>
       </c>
       <c r="H6" t="n">
         <v>59</v>
       </c>
       <c r="I6" t="n">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K6" t="n">
         <v>20242025</v>
@@ -1279,140 +1219,112 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>bundesliga</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>8vndvXTk</t>
-        </is>
-      </c>
+          <t>dfb pokal</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
-      <c r="P6" t="n">
-        <v>25.64545454545454</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>183.1363636363637</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1.572727272727272</v>
-      </c>
-      <c r="S6" t="n">
-        <v>74.40909090909091</v>
-      </c>
-      <c r="T6" t="n">
-        <v>6797272.727272728</v>
-      </c>
-      <c r="U6" t="n">
-        <v>78.53636363636363</v>
-      </c>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>26.90909090909091</v>
+        <v>27.20909090909091</v>
       </c>
       <c r="W6" t="n">
-        <v>184.6090909090909</v>
+        <v>184.9909090909091</v>
       </c>
       <c r="X6" t="n">
-        <v>1.6</v>
+        <v>2.963636363636364</v>
       </c>
       <c r="Y6" t="n">
-        <v>75.7909090909091</v>
+        <v>81.31818181818183</v>
       </c>
       <c r="Z6" t="n">
-        <v>8480000</v>
+        <v>35758636.36363636</v>
       </c>
       <c r="AA6" t="n">
-        <v>78.2</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>26.37440476190476</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>185.5630952380952</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>1.522420634920635</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>72.53829365079365</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>4587232.142857144</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>76.54583333333332</v>
-      </c>
+        <v>84.24545454545454</v>
+      </c>
+      <c r="AB6" t="inlineStr"/>
+      <c r="AC6" t="inlineStr"/>
+      <c r="AD6" t="inlineStr"/>
+      <c r="AE6" t="inlineStr"/>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="inlineStr"/>
       <c r="AH6" t="n">
-        <v>27.1820039228506</v>
+        <v>24.26583850931677</v>
       </c>
       <c r="AI6" t="n">
-        <v>184.5026783444118</v>
+        <v>182.2987005144614</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1.500474919182013</v>
+        <v>2.199501223414267</v>
       </c>
       <c r="AK6" t="n">
-        <v>73.97275298754133</v>
+        <v>77.93849559257168</v>
       </c>
       <c r="AL6" t="n">
-        <v>5185029.398677854</v>
+        <v>28680910.13982998</v>
       </c>
       <c r="AM6" t="n">
-        <v>76.06249772983183</v>
+        <v>83.33003089905263</v>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>f3ddUIXs</t>
+          <t>QevvB2nf</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>l0fHXMdE</t>
+          <t>CQTUFgPk</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>dfO6OQtS</t>
+          <t>0K2qBFNG</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45528.4375</v>
+        <v>45521.33333333334</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">aytekin d 
+          <t xml:space="preserve">schlager d 
   ger </t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">red bull arena
-  leipzig </t>
+          <t xml:space="preserve">erzgebirgsstadion
+  aue </t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>47069</v>
+        <v>16485</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>KbS1suSm</t>
+          <t>vsXIDreP</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>8Y2m6ADe</t>
+          <t>88HSzjDr</t>
         </is>
       </c>
       <c r="H7" t="n">
         <v>59</v>
       </c>
       <c r="I7" t="n">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K7" t="n">
         <v>20242025</v>
@@ -1424,144 +1336,112 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>bundesliga</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>nP1i5US1</t>
-        </is>
-      </c>
+          <t>dfb pokal</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr">
         <is>
-          <t>0Ija0Ej9</t>
-        </is>
-      </c>
-      <c r="P7" t="n">
-        <v>24.65090909090909</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>182.9127272727273</v>
-      </c>
-      <c r="R7" t="n">
-        <v>2.070909090909091</v>
-      </c>
-      <c r="S7" t="n">
-        <v>80.25818181818182</v>
-      </c>
-      <c r="T7" t="n">
-        <v>29164545.45454546</v>
-      </c>
-      <c r="U7" t="n">
-        <v>83.88727272727273</v>
-      </c>
+          <t>WG9pOTse</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>27.97222222222222</v>
+        <v>25.19424242424243</v>
       </c>
       <c r="W7" t="n">
-        <v>182.4222222222222</v>
+        <v>184.7147474747474</v>
       </c>
       <c r="X7" t="n">
-        <v>1.258333333333333</v>
+        <v>1.488282828282828</v>
       </c>
       <c r="Y7" t="n">
-        <v>73.24259259259259</v>
+        <v>74.99838383838383</v>
       </c>
       <c r="Z7" t="n">
-        <v>3645069.444444445</v>
+        <v>7986070.707070706</v>
       </c>
       <c r="AA7" t="n">
-        <v>75.01111111111112</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>25.05359730848862</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>184.9349206349206</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>1.724672187715666</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>76.71725327812285</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>17387078.1573499</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>81.29726535541754</v>
-      </c>
+        <v>78.09373737373737</v>
+      </c>
+      <c r="AB7" t="inlineStr"/>
+      <c r="AC7" t="inlineStr"/>
+      <c r="AD7" t="inlineStr"/>
+      <c r="AE7" t="inlineStr"/>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="inlineStr"/>
       <c r="AH7" t="n">
-        <v>26.61693121693122</v>
+        <v>22.90164596273292</v>
       </c>
       <c r="AI7" t="n">
-        <v>182.9073032961191</v>
+        <v>183.8122360248447</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1.064170843776107</v>
+        <v>1.30304347826087</v>
       </c>
       <c r="AK7" t="n">
-        <v>70.50391509075719</v>
+        <v>72.49769409937889</v>
       </c>
       <c r="AL7" t="n">
-        <v>2404898.16713501</v>
+        <v>6790663.043478261</v>
       </c>
       <c r="AM7" t="n">
-        <v>73.59740054049264</v>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>UgdQz0fK</t>
-        </is>
-      </c>
+        <v>78.79253105590062</v>
+      </c>
+      <c r="AN7" t="inlineStr"/>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>xzRzG0VI</t>
+          <t>M5BRZDsC</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>SxFxJ44k</t>
+          <t>Kj4sifWp</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45528.5625</v>
+        <v>45521.33333333334</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">zwayer f 
+          <t xml:space="preserve">hempel r 
   ger </t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">signal iduna park
-  dortmund </t>
+          <t xml:space="preserve">bruchwegstadion
+  mainz </t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>81365</v>
+        <v>7134</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>nP1i5US1</t>
+          <t>WzEYqEyg</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>8vndvXTk</t>
+          <t>CCQGbik8</t>
         </is>
       </c>
       <c r="H8" t="n">
         <v>59</v>
       </c>
       <c r="I8" t="n">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K8" t="n">
         <v>20242025</v>
@@ -1573,144 +1453,112 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>bundesliga</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>0Ija0Ej9</t>
-        </is>
-      </c>
+          <t>dfb pokal</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr">
         <is>
-          <t>EuakNmc1</t>
-        </is>
-      </c>
-      <c r="P8" t="n">
-        <v>25.14545454545455</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>184.7454545454545</v>
-      </c>
-      <c r="R8" t="n">
-        <v>2.245454545454546</v>
-      </c>
-      <c r="S8" t="n">
-        <v>79.55454545454546</v>
-      </c>
-      <c r="T8" t="n">
-        <v>28540909.09090909</v>
-      </c>
-      <c r="U8" t="n">
-        <v>83.10909090909091</v>
-      </c>
+          <t>6FDqshzF</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>24.25222222222222</v>
+        <v>24.03636363636363</v>
       </c>
       <c r="W8" t="n">
-        <v>183.0955555555556</v>
+        <v>183.0597402597403</v>
       </c>
       <c r="X8" t="n">
-        <v>1.63</v>
+        <v>1</v>
       </c>
       <c r="Y8" t="n">
-        <v>76.98111111111112</v>
+        <v>68.67402597402598</v>
       </c>
       <c r="Z8" t="n">
-        <v>15614611.11111111</v>
+        <v>2157987.012987013</v>
       </c>
       <c r="AA8" t="n">
-        <v>81.18111111111111</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>25.06309523809524</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>183.609126984127</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>2.011706349206349</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>77.71388888888889</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>20714563.49206349</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>82.11527777777778</v>
-      </c>
+        <v>74.4974025974026</v>
+      </c>
+      <c r="AB8" t="inlineStr"/>
+      <c r="AC8" t="inlineStr"/>
+      <c r="AD8" t="inlineStr"/>
+      <c r="AE8" t="inlineStr"/>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="inlineStr"/>
       <c r="AH8" t="n">
-        <v>24.30286226930964</v>
+        <v>22.55202535559679</v>
       </c>
       <c r="AI8" t="n">
-        <v>183.7797641831852</v>
+        <v>183.5796227581941</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1.421828434723172</v>
+        <v>1</v>
       </c>
       <c r="AK8" t="n">
-        <v>71.9276110731374</v>
+        <v>63.46678519892806</v>
       </c>
       <c r="AL8" t="n">
-        <v>5697609.791524266</v>
+        <v>1206222.299525871</v>
       </c>
       <c r="AM8" t="n">
-        <v>78.33495215311004</v>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>Q1njn0Vm</t>
-        </is>
-      </c>
+        <v>72.42241290455577</v>
+      </c>
+      <c r="AN8" t="inlineStr"/>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>pfoInmcq</t>
+          <t>pdPRS0me</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>t0w6KHuf</t>
+          <t>bF2q76Mr</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45529.4375</v>
+        <v>45521.4375</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">fritz m 
+          <t xml:space="preserve">stieler t 
   ger </t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">volkswagen arena
-  wolfsburg </t>
+          <t xml:space="preserve">ostalb arena
+  aalen </t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>28917</v>
+        <v>14500</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>nwkTahLL</t>
+          <t>Oh2C15j0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>nVp0wiqd</t>
+          <t>0Ija0Ej9</t>
         </is>
       </c>
       <c r="H9" t="n">
         <v>59</v>
       </c>
       <c r="I9" t="n">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K9" t="n">
         <v>20242025</v>
@@ -1722,140 +1570,112 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>bundesliga</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>dfNCCCzS</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="n">
-        <v>25.22</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>186.74</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="S9" t="n">
-        <v>75.81</v>
-      </c>
-      <c r="T9" t="n">
-        <v>10860000</v>
-      </c>
-      <c r="U9" t="n">
-        <v>79.66</v>
-      </c>
+          <t>dfb pokal</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>nP1i5US1</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>27.20909090909091</v>
+        <v>25.75</v>
       </c>
       <c r="W9" t="n">
-        <v>184.9909090909091</v>
+        <v>186.5178571428571</v>
       </c>
       <c r="X9" t="n">
-        <v>2.963636363636364</v>
+        <v>1</v>
       </c>
       <c r="Y9" t="n">
-        <v>81.31818181818183</v>
+        <v>68.88571428571429</v>
       </c>
       <c r="Z9" t="n">
-        <v>35758636.36363636</v>
+        <v>1755446.428571429</v>
       </c>
       <c r="AA9" t="n">
-        <v>84.24545454545454</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>24.49049516908213</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>183.5287318840579</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>1.273164251207729</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>73.89692028985507</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>8517461.956521738</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>78.55956521739131</v>
-      </c>
+        <v>73.44285714285715</v>
+      </c>
+      <c r="AB9" t="inlineStr"/>
+      <c r="AC9" t="inlineStr"/>
+      <c r="AD9" t="inlineStr"/>
+      <c r="AE9" t="inlineStr"/>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="inlineStr"/>
       <c r="AH9" t="n">
-        <v>24.26583850931677</v>
+        <v>25.18543956043956</v>
       </c>
       <c r="AI9" t="n">
-        <v>182.2987005144614</v>
+        <v>185.6027167277167</v>
       </c>
       <c r="AJ9" t="n">
-        <v>2.199501223414267</v>
+        <v>1.015873015873016</v>
       </c>
       <c r="AK9" t="n">
-        <v>77.93849559257168</v>
+        <v>66.876221001221</v>
       </c>
       <c r="AL9" t="n">
-        <v>28680910.13982998</v>
+        <v>1400815.018315018</v>
       </c>
       <c r="AM9" t="n">
-        <v>83.33003089905263</v>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>f3ddUIXs</t>
-        </is>
-      </c>
+        <v>72.19536019536019</v>
+      </c>
+      <c r="AN9" t="inlineStr"/>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>CQTUFgPk</t>
+          <t>SQrxFAMl</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>AuVMGZvJ</t>
+          <t>vyk5gjdE</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45529.52083333334</v>
+        <v>45521.4375</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">welz t 
+          <t xml:space="preserve">dingert c 
   ger </t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">millerntor stadion
-  hamburg </t>
+          <t xml:space="preserve">volksstadion greifswald
+  greifswald </t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>29546</v>
+        <v>4990</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>ILyJuN3g</t>
+          <t>Q1yNyI5t</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>KWixEVWi</t>
+          <t>pzHW4oaE</t>
         </is>
       </c>
       <c r="H10" t="n">
         <v>59</v>
       </c>
       <c r="I10" t="n">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K10" t="n">
         <v>20242025</v>
@@ -1867,130 +1687,98 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>bundesliga</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>v9k3aY5F</t>
-        </is>
-      </c>
+          <t>dfb pokal</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
-      <c r="P10" t="n">
-        <v>25.83181818181818</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>185.1212121212121</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1</v>
-      </c>
-      <c r="S10" t="n">
-        <v>70.01363636363637</v>
-      </c>
-      <c r="T10" t="n">
-        <v>2280151.515151515</v>
-      </c>
-      <c r="U10" t="n">
-        <v>72.97727272727273</v>
-      </c>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>25.62727272727273</v>
+        <v>26.90909090909091</v>
       </c>
       <c r="W10" t="n">
-        <v>186.5272727272727</v>
+        <v>184.6090909090909</v>
       </c>
       <c r="X10" t="n">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="Y10" t="n">
-        <v>72.90000000000001</v>
+        <v>75.7909090909091</v>
       </c>
       <c r="Z10" t="n">
-        <v>4462954.545454545</v>
+        <v>8480000</v>
       </c>
       <c r="AA10" t="n">
-        <v>75.34545454545454</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>25.85441729323308</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>185.9193609022556</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>66.75798872180451</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>1303942.669172932</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>71.29758771929825</v>
-      </c>
+        <v>78.2</v>
+      </c>
+      <c r="AB10" t="inlineStr"/>
+      <c r="AC10" t="inlineStr"/>
+      <c r="AD10" t="inlineStr"/>
+      <c r="AE10" t="inlineStr"/>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="inlineStr"/>
       <c r="AH10" t="n">
-        <v>27.39107142857143</v>
+        <v>27.1820039228506</v>
       </c>
       <c r="AI10" t="n">
-        <v>183.0269841269841</v>
+        <v>184.5026783444118</v>
       </c>
       <c r="AJ10" t="n">
-        <v>1</v>
+        <v>1.500474919182013</v>
       </c>
       <c r="AK10" t="n">
-        <v>69.03234126984127</v>
+        <v>73.97275298754133</v>
       </c>
       <c r="AL10" t="n">
-        <v>1845550.595238096</v>
+        <v>5185029.398677854</v>
       </c>
       <c r="AM10" t="n">
-        <v>70.72083333333333</v>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>QTAUlvUP</t>
-        </is>
-      </c>
+        <v>76.06249772983183</v>
+      </c>
+      <c r="AN10" t="inlineStr"/>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>lGJdeemM</t>
+          <t>l0fHXMdE</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>pWQQJq6l</t>
+          <t>tbKZHNz1</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>45520.54166666666</v>
+        <v>45521.4375</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve">aytekin d 
+          <t xml:space="preserve">schroder r 
   ger </t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">leuna chemie stadion
-  halle </t>
+          <t xml:space="preserve">audi sportpark
+  ingolstadt </t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>15057</v>
+        <v>15800</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>boX3cIQa</t>
+          <t>ne5QkLtB</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>ILyJuN3g</t>
+          <t>naWckLmC</t>
         </is>
       </c>
       <c r="H11" t="n">
@@ -2016,11 +1804,7 @@
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>v9k3aY5F</t>
-        </is>
-      </c>
+      <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr"/>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr"/>
@@ -2028,22 +1812,22 @@
       <c r="T11" t="inlineStr"/>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>25.83181818181818</v>
+        <v>25.39886363636364</v>
       </c>
       <c r="W11" t="n">
-        <v>185.1212121212121</v>
+        <v>183.6647727272727</v>
       </c>
       <c r="X11" t="n">
         <v>1</v>
       </c>
       <c r="Y11" t="n">
-        <v>70.01363636363637</v>
+        <v>68.24431818181819</v>
       </c>
       <c r="Z11" t="n">
-        <v>2280151.515151515</v>
+        <v>1643323.863636364</v>
       </c>
       <c r="AA11" t="n">
-        <v>72.97727272727273</v>
+        <v>71.28181818181818</v>
       </c>
       <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="inlineStr"/>
@@ -2052,62 +1836,62 @@
       <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="inlineStr"/>
       <c r="AH11" t="n">
-        <v>25.85441729323308</v>
+        <v>26.36618725874304</v>
       </c>
       <c r="AI11" t="n">
-        <v>185.9193609022556</v>
+        <v>181.0833405565957</v>
       </c>
       <c r="AJ11" t="n">
         <v>1</v>
       </c>
       <c r="AK11" t="n">
-        <v>66.75798872180451</v>
+        <v>67.65210565321406</v>
       </c>
       <c r="AL11" t="n">
-        <v>1303942.669172932</v>
+        <v>1409553.920208955</v>
       </c>
       <c r="AM11" t="n">
-        <v>71.29758771929825</v>
+        <v>70.42419222256893</v>
       </c>
       <c r="AN11" t="inlineStr"/>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>QHesBmSQ</t>
+          <t>4bJLk19p</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>hIsO3XFj</t>
+          <t>MZjh9ghT</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>45520.54166666666</v>
+        <v>45521.4375</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t xml:space="preserve">willenborg f 
+          <t xml:space="preserve">zwayer f 
   ger </t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">brita arena
-  wiesbaden </t>
+          <t xml:space="preserve">stadion an der hafenstrasse
+  essen </t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>12566</v>
+        <v>20352</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>ObxFt3lm</t>
+          <t>EB0xsr77</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>EuakNmc1</t>
+          <t>KbS1suSm</t>
         </is>
       </c>
       <c r="H12" t="n">
@@ -2132,131 +1916,99 @@
           <t>dfb pokal</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>EuakNmc1</t>
-        </is>
-      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr">
         <is>
-          <t>8vndvXTk</t>
-        </is>
-      </c>
-      <c r="P12" t="n">
-        <v>26.10227272727273</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>185.875</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1</v>
-      </c>
-      <c r="S12" t="n">
-        <v>67.18181818181819</v>
-      </c>
-      <c r="T12" t="n">
-        <v>1195738.636363636</v>
-      </c>
-      <c r="U12" t="n">
-        <v>69.51136363636363</v>
-      </c>
+          <t>nP1i5US1</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr"/>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>25.64545454545454</v>
+        <v>24.65090909090909</v>
       </c>
       <c r="W12" t="n">
-        <v>183.1363636363637</v>
+        <v>182.9127272727273</v>
       </c>
       <c r="X12" t="n">
-        <v>1.572727272727272</v>
+        <v>2.070909090909091</v>
       </c>
       <c r="Y12" t="n">
-        <v>74.40909090909091</v>
+        <v>80.25818181818182</v>
       </c>
       <c r="Z12" t="n">
-        <v>6797272.727272728</v>
+        <v>29164545.45454546</v>
       </c>
       <c r="AA12" t="n">
-        <v>78.53636363636363</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>24.38020833333334</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>183.2413194444445</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>64.93229166666666</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>1005946.180555556</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>69.11458333333334</v>
-      </c>
+        <v>83.88727272727273</v>
+      </c>
+      <c r="AB12" t="inlineStr"/>
+      <c r="AC12" t="inlineStr"/>
+      <c r="AD12" t="inlineStr"/>
+      <c r="AE12" t="inlineStr"/>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="inlineStr"/>
       <c r="AH12" t="n">
-        <v>26.37440476190476</v>
+        <v>25.05359730848862</v>
       </c>
       <c r="AI12" t="n">
-        <v>185.5630952380952</v>
+        <v>184.9349206349206</v>
       </c>
       <c r="AJ12" t="n">
-        <v>1.522420634920635</v>
+        <v>1.724672187715666</v>
       </c>
       <c r="AK12" t="n">
-        <v>72.53829365079365</v>
+        <v>76.71725327812285</v>
       </c>
       <c r="AL12" t="n">
-        <v>4587232.142857144</v>
+        <v>17387078.1573499</v>
       </c>
       <c r="AM12" t="n">
-        <v>76.54583333333332</v>
-      </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>QTAUlvUP</t>
-        </is>
-      </c>
+        <v>81.29726535541754</v>
+      </c>
+      <c r="AN12" t="inlineStr"/>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>vZA6VYpf</t>
+          <t>pfoInmcq</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>EF8gXauC</t>
+          <t>f1nnRRDE</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>45520.54166666666</v>
+        <v>45521.4375</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t xml:space="preserve">fritz m 
+          <t xml:space="preserve">dingert c 
   ger </t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">flyeralarm arena
-  wurzburger </t>
+          <t xml:space="preserve">stadion an der bremer bruck
+  osnabruck </t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>13090</v>
+        <v>16667</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>nVM1YUFj</t>
+          <t>88Xgj1Y5</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>hQAtP9Sl</t>
+          <t>fiEQZ7C7</t>
         </is>
       </c>
       <c r="H13" t="n">
@@ -2287,93 +2039,121 @@
           <t>nJQmYp1B</t>
         </is>
       </c>
-      <c r="P13" t="inlineStr"/>
-      <c r="Q13" t="inlineStr"/>
-      <c r="R13" t="inlineStr"/>
-      <c r="S13" t="inlineStr"/>
-      <c r="T13" t="inlineStr"/>
-      <c r="U13" t="inlineStr"/>
+      <c r="P13" t="n">
+        <v>25.64848484848485</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>183.1606060606061</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1</v>
+      </c>
+      <c r="S13" t="n">
+        <v>67.04545454545455</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1385075.757575758</v>
+      </c>
+      <c r="U13" t="n">
+        <v>70.99242424242424</v>
+      </c>
       <c r="V13" t="n">
-        <v>26.76363636363636</v>
+        <v>27.4</v>
       </c>
       <c r="W13" t="n">
-        <v>185.5272727272727</v>
+        <v>183.3909090909091</v>
       </c>
       <c r="X13" t="n">
-        <v>1.818181818181818</v>
+        <v>1.709090909090909</v>
       </c>
       <c r="Y13" t="n">
-        <v>75.38181818181819</v>
+        <v>75.58181818181818</v>
       </c>
       <c r="Z13" t="n">
-        <v>8930000</v>
+        <v>9104545.454545453</v>
       </c>
       <c r="AA13" t="n">
-        <v>78.72727272727272</v>
-      </c>
-      <c r="AB13" t="inlineStr"/>
-      <c r="AC13" t="inlineStr"/>
-      <c r="AD13" t="inlineStr"/>
-      <c r="AE13" t="inlineStr"/>
-      <c r="AF13" t="inlineStr"/>
-      <c r="AG13" t="inlineStr"/>
+        <v>77.26363636363635</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>25.70271164021164</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>184.5059523809524</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>66.62632275132275</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>1261367.394179894</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>69.8366402116402</v>
+      </c>
       <c r="AH13" t="n">
-        <v>24.22996031746032</v>
+        <v>24.61444862155389</v>
       </c>
       <c r="AI13" t="n">
-        <v>185.4827380952381</v>
+        <v>184.9235651629072</v>
       </c>
       <c r="AJ13" t="n">
-        <v>1.367063492063492</v>
+        <v>1.411942355889725</v>
       </c>
       <c r="AK13" t="n">
-        <v>71.57718253968254</v>
+        <v>72.99003132832081</v>
       </c>
       <c r="AL13" t="n">
-        <v>5224836.30952381</v>
+        <v>5321504.072681705</v>
       </c>
       <c r="AM13" t="n">
-        <v>77.88630952380952</v>
-      </c>
-      <c r="AN13" t="inlineStr"/>
+        <v>76.56177631578949</v>
+      </c>
+      <c r="AN13" t="inlineStr">
+        <is>
+          <t>lxrr7DgN</t>
+        </is>
+      </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>CQTUFgPk</t>
+          <t>l0fHXMdE</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>lONsG15D</t>
+          <t>8QPARz8c</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>45520.65625</v>
+        <v>45521.4375</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t xml:space="preserve">fritz m 
+          <t xml:space="preserve">welz t 
   ger </t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">donaustadion
-  ulm </t>
+          <t xml:space="preserve">ms technologie arena
+  villingen schwenningen </t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>19500</v>
+        <v>8000</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>tbC3EcQn</t>
+          <t>lKLJUxeT</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>nVp0wiqd</t>
+          <t>KWixEVWi</t>
         </is>
       </c>
       <c r="H14" t="n">
@@ -2407,22 +2187,22 @@
       <c r="T14" t="inlineStr"/>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>27.20909090909091</v>
+        <v>25.62727272727273</v>
       </c>
       <c r="W14" t="n">
-        <v>184.9909090909091</v>
+        <v>186.5272727272727</v>
       </c>
       <c r="X14" t="n">
-        <v>2.963636363636364</v>
+        <v>1</v>
       </c>
       <c r="Y14" t="n">
-        <v>81.31818181818183</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="Z14" t="n">
-        <v>35758636.36363636</v>
+        <v>4462954.545454545</v>
       </c>
       <c r="AA14" t="n">
-        <v>84.24545454545454</v>
+        <v>75.34545454545454</v>
       </c>
       <c r="AB14" t="inlineStr"/>
       <c r="AC14" t="inlineStr"/>
@@ -2431,66 +2211,62 @@
       <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="inlineStr"/>
       <c r="AH14" t="n">
-        <v>24.26583850931677</v>
+        <v>27.39107142857143</v>
       </c>
       <c r="AI14" t="n">
-        <v>182.2987005144614</v>
+        <v>183.0269841269841</v>
       </c>
       <c r="AJ14" t="n">
-        <v>2.199501223414267</v>
+        <v>1</v>
       </c>
       <c r="AK14" t="n">
-        <v>77.93849559257168</v>
+        <v>69.03234126984127</v>
       </c>
       <c r="AL14" t="n">
-        <v>28680910.13982998</v>
+        <v>1845550.595238096</v>
       </c>
       <c r="AM14" t="n">
-        <v>83.33003089905263</v>
-      </c>
-      <c r="AN14" t="inlineStr">
-        <is>
-          <t>QevvB2nf</t>
-        </is>
-      </c>
+        <v>70.72083333333333</v>
+      </c>
+      <c r="AN14" t="inlineStr"/>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>CQTUFgPk</t>
+          <t>lGJdeemM</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>0K2qBFNG</t>
+          <t>hzyf0b9b</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>45521.33333333334</v>
+        <v>45521.54166666666</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t xml:space="preserve">schlager d 
+          <t xml:space="preserve">sather a 
   ger </t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">erzgebirgsstadion
-  aue </t>
+          <t xml:space="preserve">new tivoli
+  aachen </t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>16485</v>
+        <v>31026</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>vsXIDreP</t>
+          <t>j3PKcB4E</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>88HSzjDr</t>
+          <t>63WsD2ei</t>
         </is>
       </c>
       <c r="H15" t="n">
@@ -2518,7 +2294,7 @@
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr">
         <is>
-          <t>WG9pOTse</t>
+          <t>ILyJuN3g</t>
         </is>
       </c>
       <c r="P15" t="inlineStr"/>
@@ -2528,22 +2304,22 @@
       <c r="T15" t="inlineStr"/>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>25.19424242424243</v>
+        <v>25.25757575757576</v>
       </c>
       <c r="W15" t="n">
-        <v>184.7147474747474</v>
+        <v>186.5454545454545</v>
       </c>
       <c r="X15" t="n">
-        <v>1.488282828282828</v>
+        <v>1.075757575757576</v>
       </c>
       <c r="Y15" t="n">
-        <v>74.99838383838383</v>
+        <v>68.48484848484848</v>
       </c>
       <c r="Z15" t="n">
-        <v>7986070.707070706</v>
+        <v>1749242.424242425</v>
       </c>
       <c r="AA15" t="n">
-        <v>78.09373737373737</v>
+        <v>72.46969696969698</v>
       </c>
       <c r="AB15" t="inlineStr"/>
       <c r="AC15" t="inlineStr"/>
@@ -2552,62 +2328,62 @@
       <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="inlineStr"/>
       <c r="AH15" t="n">
-        <v>22.90164596273292</v>
+        <v>25.07421785139177</v>
       </c>
       <c r="AI15" t="n">
-        <v>183.8122360248447</v>
+        <v>185.8624194847021</v>
       </c>
       <c r="AJ15" t="n">
-        <v>1.30304347826087</v>
+        <v>1.015182884748102</v>
       </c>
       <c r="AK15" t="n">
-        <v>72.49769409937889</v>
+        <v>66.6799373130895</v>
       </c>
       <c r="AL15" t="n">
-        <v>6790663.043478261</v>
+        <v>1411003.637566138</v>
       </c>
       <c r="AM15" t="n">
-        <v>78.79253105590062</v>
+        <v>71.2854267310789</v>
       </c>
       <c r="AN15" t="inlineStr"/>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>M5BRZDsC</t>
+          <t>A15eUM4C</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Kj4sifWp</t>
+          <t>CpiTEcOi</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>45521.33333333334</v>
+        <v>45521.54166666666</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t xml:space="preserve">hempel r 
+          <t xml:space="preserve">bacher m 
   ger </t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">bruchwegstadion
-  mainz </t>
+          <t xml:space="preserve">schuco arena
+  bielefeld </t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>7134</v>
+        <v>27332</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>WzEYqEyg</t>
+          <t>pp38UXK8</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>CCQGbik8</t>
+          <t>dfNCCCzS</t>
         </is>
       </c>
       <c r="H16" t="n">
@@ -2635,7 +2411,7 @@
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr">
         <is>
-          <t>6FDqshzF</t>
+          <t>QqLCC3il</t>
         </is>
       </c>
       <c r="P16" t="inlineStr"/>
@@ -2645,22 +2421,22 @@
       <c r="T16" t="inlineStr"/>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>24.03636363636363</v>
+        <v>25.69350649350649</v>
       </c>
       <c r="W16" t="n">
-        <v>183.0597402597403</v>
+        <v>183.7831168831169</v>
       </c>
       <c r="X16" t="n">
-        <v>1</v>
+        <v>1.184415584415585</v>
       </c>
       <c r="Y16" t="n">
-        <v>68.67402597402598</v>
+        <v>69.68051948051948</v>
       </c>
       <c r="Z16" t="n">
-        <v>2157987.012987013</v>
+        <v>2022500</v>
       </c>
       <c r="AA16" t="n">
-        <v>74.4974025974026</v>
+        <v>73.85194805194806</v>
       </c>
       <c r="AB16" t="inlineStr"/>
       <c r="AC16" t="inlineStr"/>
@@ -2669,62 +2445,62 @@
       <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="inlineStr"/>
       <c r="AH16" t="n">
-        <v>22.55202535559679</v>
+        <v>24.29795403009689</v>
       </c>
       <c r="AI16" t="n">
-        <v>183.5796227581941</v>
+        <v>183.7678829107401</v>
       </c>
       <c r="AJ16" t="n">
         <v>1</v>
       </c>
       <c r="AK16" t="n">
-        <v>63.46678519892806</v>
+        <v>66.42261904761905</v>
       </c>
       <c r="AL16" t="n">
-        <v>1206222.299525871</v>
+        <v>1384835.600907029</v>
       </c>
       <c r="AM16" t="n">
-        <v>72.42241290455577</v>
+        <v>71.45305091733663</v>
       </c>
       <c r="AN16" t="inlineStr"/>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>pdPRS0me</t>
+          <t>zyLSrbZQ</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>bF2q76Mr</t>
+          <t>8CpxDyg4</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>45521.4375</v>
+        <v>45521.54166666666</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t xml:space="preserve">stieler t 
+          <t xml:space="preserve">siebert d 
   ger </t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">ostalb arena
-  aalen </t>
+          <t xml:space="preserve">stadion lohmuhle
+  lubeck </t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>14500</v>
+        <v>17849</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Oh2C15j0</t>
+          <t>I1Vk6k3R</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>0Ija0Ej9</t>
+          <t>nP1i5US1</t>
         </is>
       </c>
       <c r="H17" t="n">
@@ -2752,7 +2528,7 @@
       <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr">
         <is>
-          <t>nP1i5US1</t>
+          <t>0Ija0Ej9</t>
         </is>
       </c>
       <c r="P17" t="inlineStr"/>
@@ -2762,22 +2538,22 @@
       <c r="T17" t="inlineStr"/>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>25.75</v>
+        <v>25.14545454545455</v>
       </c>
       <c r="W17" t="n">
-        <v>186.5178571428571</v>
+        <v>184.7454545454545</v>
       </c>
       <c r="X17" t="n">
-        <v>1</v>
+        <v>2.245454545454546</v>
       </c>
       <c r="Y17" t="n">
-        <v>68.88571428571429</v>
+        <v>79.55454545454546</v>
       </c>
       <c r="Z17" t="n">
-        <v>1755446.428571429</v>
+        <v>28540909.09090909</v>
       </c>
       <c r="AA17" t="n">
-        <v>73.44285714285715</v>
+        <v>83.10909090909091</v>
       </c>
       <c r="AB17" t="inlineStr"/>
       <c r="AC17" t="inlineStr"/>
@@ -2786,62 +2562,62 @@
       <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="inlineStr"/>
       <c r="AH17" t="n">
-        <v>25.18543956043956</v>
+        <v>25.06309523809524</v>
       </c>
       <c r="AI17" t="n">
-        <v>185.6027167277167</v>
+        <v>183.609126984127</v>
       </c>
       <c r="AJ17" t="n">
-        <v>1.015873015873016</v>
+        <v>2.011706349206349</v>
       </c>
       <c r="AK17" t="n">
-        <v>66.876221001221</v>
+        <v>77.71388888888889</v>
       </c>
       <c r="AL17" t="n">
-        <v>1400815.018315018</v>
+        <v>20714563.49206349</v>
       </c>
       <c r="AM17" t="n">
-        <v>72.19536019536019</v>
+        <v>82.11527777777778</v>
       </c>
       <c r="AN17" t="inlineStr"/>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>SQrxFAMl</t>
+          <t>MDhPV0RQ</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>vyk5gjdE</t>
+          <t>6q2yrHgU</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
-        <v>45521.4375</v>
+        <v>45522.33333333334</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t xml:space="preserve">dingert c 
+          <t xml:space="preserve">braun r 
   ger </t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">volksstadion greifswald
-  greifswald </t>
+          <t xml:space="preserve">ludwigspark stadion
+  saarbrucken </t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4990</v>
+        <v>16003</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Q1yNyI5t</t>
+          <t>fLbhmJ5l</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>pzHW4oaE</t>
+          <t>6FDqshzF</t>
         </is>
       </c>
       <c r="H18" t="n">
@@ -2867,7 +2643,11 @@
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
-      <c r="O18" t="inlineStr"/>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>CCQGbik8</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr"/>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr"/>
@@ -2875,22 +2655,22 @@
       <c r="T18" t="inlineStr"/>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>26.90909090909091</v>
+        <v>23.44877344877344</v>
       </c>
       <c r="W18" t="n">
-        <v>184.6090909090909</v>
+        <v>183.3506493506493</v>
       </c>
       <c r="X18" t="n">
-        <v>1.6</v>
+        <v>1.015873015873016</v>
       </c>
       <c r="Y18" t="n">
-        <v>75.7909090909091</v>
+        <v>66.96103896103897</v>
       </c>
       <c r="Z18" t="n">
-        <v>8480000</v>
+        <v>1622655.122655123</v>
       </c>
       <c r="AA18" t="n">
-        <v>78.2</v>
+        <v>72.92352092352093</v>
       </c>
       <c r="AB18" t="inlineStr"/>
       <c r="AC18" t="inlineStr"/>
@@ -2899,62 +2679,62 @@
       <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="inlineStr"/>
       <c r="AH18" t="n">
-        <v>27.1820039228506</v>
+        <v>27.19029581529582</v>
       </c>
       <c r="AI18" t="n">
-        <v>184.5026783444118</v>
+        <v>182.2007575757576</v>
       </c>
       <c r="AJ18" t="n">
-        <v>1.500474919182013</v>
+        <v>1.015873015873016</v>
       </c>
       <c r="AK18" t="n">
-        <v>73.97275298754133</v>
+        <v>67.24098124098124</v>
       </c>
       <c r="AL18" t="n">
-        <v>5185029.398677854</v>
+        <v>1184510.281385281</v>
       </c>
       <c r="AM18" t="n">
-        <v>76.06249772983183</v>
+        <v>69.51893939393939</v>
       </c>
       <c r="AN18" t="inlineStr"/>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>l0fHXMdE</t>
+          <t>tO31cZrF</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>tbKZHNz1</t>
+          <t>AiJ3kset</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
-        <v>45521.4375</v>
+        <v>45522.33333333334</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t xml:space="preserve">schroder r 
+          <t xml:space="preserve">jollenbeck m 
   ger </t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve">audi sportpark
-  ingolstadt </t>
+          <t xml:space="preserve">friedrich ludwig jahn sportpark
+  berlin </t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>15800</v>
+        <v>19708</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>ne5QkLtB</t>
+          <t>UNr2EUfd</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>naWckLmC</t>
+          <t>fTVNku3I</t>
         </is>
       </c>
       <c r="H19" t="n">
@@ -2988,22 +2768,22 @@
       <c r="T19" t="inlineStr"/>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>25.39886363636364</v>
+        <v>25.41333333333333</v>
       </c>
       <c r="W19" t="n">
-        <v>183.6647727272727</v>
+        <v>186.0030303030303</v>
       </c>
       <c r="X19" t="n">
-        <v>1</v>
+        <v>1.462323232323232</v>
       </c>
       <c r="Y19" t="n">
-        <v>68.24431818181819</v>
+        <v>74.33111111111111</v>
       </c>
       <c r="Z19" t="n">
-        <v>1643323.863636364</v>
+        <v>6657146.464646464</v>
       </c>
       <c r="AA19" t="n">
-        <v>71.28181818181818</v>
+        <v>77.32606060606061</v>
       </c>
       <c r="AB19" t="inlineStr"/>
       <c r="AC19" t="inlineStr"/>
@@ -3012,62 +2792,62 @@
       <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="inlineStr"/>
       <c r="AH19" t="n">
-        <v>26.36618725874304</v>
+        <v>23.899139420521</v>
       </c>
       <c r="AI19" t="n">
-        <v>181.0833405565957</v>
+        <v>184.2982721956406</v>
       </c>
       <c r="AJ19" t="n">
-        <v>1</v>
+        <v>1.139229228373965</v>
       </c>
       <c r="AK19" t="n">
-        <v>67.65210565321406</v>
+        <v>71.05004414445204</v>
       </c>
       <c r="AL19" t="n">
-        <v>1409553.920208955</v>
+        <v>3913032.094915318</v>
       </c>
       <c r="AM19" t="n">
-        <v>70.42419222256893</v>
+        <v>76.51723674717095</v>
       </c>
       <c r="AN19" t="inlineStr"/>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>4bJLk19p</t>
+          <t>2VSFgl3c</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>MZjh9ghT</t>
+          <t>YV3TqwPH</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
-        <v>45521.4375</v>
+        <v>45522.4375</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t xml:space="preserve">zwayer f 
+          <t xml:space="preserve">haslberger w 
   ger </t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadion an der hafenstrasse
-  essen </t>
+          <t xml:space="preserve">stadion am panzenberg
+  bremen </t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>20352</v>
+        <v>5000</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>EB0xsr77</t>
+          <t>tW75B1ei</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>KbS1suSm</t>
+          <t>G2Op923t</t>
         </is>
       </c>
       <c r="H20" t="n">
@@ -3093,11 +2873,7 @@
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>nP1i5US1</t>
-        </is>
-      </c>
+      <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr"/>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr"/>
@@ -3105,22 +2881,22 @@
       <c r="T20" t="inlineStr"/>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="n">
-        <v>24.65090909090909</v>
+        <v>24.10616883116883</v>
       </c>
       <c r="W20" t="n">
-        <v>182.9127272727273</v>
+        <v>185.4892857142857</v>
       </c>
       <c r="X20" t="n">
-        <v>2.070909090909091</v>
+        <v>1</v>
       </c>
       <c r="Y20" t="n">
-        <v>80.25818181818182</v>
+        <v>66.52467532467533</v>
       </c>
       <c r="Z20" t="n">
-        <v>29164545.45454546</v>
+        <v>1420081.168831169</v>
       </c>
       <c r="AA20" t="n">
-        <v>83.88727272727273</v>
+        <v>72.47792207792207</v>
       </c>
       <c r="AB20" t="inlineStr"/>
       <c r="AC20" t="inlineStr"/>
@@ -3129,62 +2905,62 @@
       <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="inlineStr"/>
       <c r="AH20" t="n">
-        <v>25.05359730848862</v>
+        <v>25.24755485198031</v>
       </c>
       <c r="AI20" t="n">
-        <v>184.9349206349206</v>
+        <v>186.3757108574655</v>
       </c>
       <c r="AJ20" t="n">
-        <v>1.724672187715666</v>
+        <v>1</v>
       </c>
       <c r="AK20" t="n">
-        <v>76.71725327812285</v>
+        <v>67.15276377349359</v>
       </c>
       <c r="AL20" t="n">
-        <v>17387078.1573499</v>
+        <v>1396154.689642655</v>
       </c>
       <c r="AM20" t="n">
-        <v>81.29726535541754</v>
+        <v>71.317123094297</v>
       </c>
       <c r="AN20" t="inlineStr"/>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>pfoInmcq</t>
+          <t>0AI1QUJH</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>f1nnRRDE</t>
+          <t>l0ueP5rR</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
-        <v>45521.4375</v>
+        <v>45522.4375</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t xml:space="preserve">dingert c 
+          <t xml:space="preserve">haslberger w 
   ger </t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadion an der bremer bruck
-  osnabruck </t>
+          <t xml:space="preserve">ostseestadion
+  rostock </t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>16667</v>
+        <v>29000</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>88Xgj1Y5</t>
+          <t>KIHmtCkL</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>fiEQZ7C7</t>
+          <t>2y0u8Wrq</t>
         </is>
       </c>
       <c r="H21" t="n">
@@ -3209,127 +2985,127 @@
           <t>dfb pokal</t>
         </is>
       </c>
-      <c r="N21" t="inlineStr"/>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>nJQmYp1B</t>
-        </is>
-      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>ILyJuN3g</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr"/>
       <c r="P21" t="n">
-        <v>25.64848484848485</v>
+        <v>26.5</v>
       </c>
       <c r="Q21" t="n">
-        <v>183.1606060606061</v>
+        <v>183.8030303030303</v>
       </c>
       <c r="R21" t="n">
         <v>1</v>
       </c>
       <c r="S21" t="n">
-        <v>67.04545454545455</v>
+        <v>67.83333333333333</v>
       </c>
       <c r="T21" t="n">
-        <v>1385075.757575758</v>
+        <v>1329545.454545455</v>
       </c>
       <c r="U21" t="n">
-        <v>70.99242424242424</v>
+        <v>70.51515151515152</v>
       </c>
       <c r="V21" t="n">
-        <v>27.4</v>
+        <v>23.96031746031746</v>
       </c>
       <c r="W21" t="n">
-        <v>183.3909090909091</v>
+        <v>184.3968253968254</v>
       </c>
       <c r="X21" t="n">
-        <v>1.709090909090909</v>
+        <v>1.073015873015873</v>
       </c>
       <c r="Y21" t="n">
-        <v>75.58181818181818</v>
+        <v>70.34920634920634</v>
       </c>
       <c r="Z21" t="n">
-        <v>9104545.454545453</v>
+        <v>2767460.317460318</v>
       </c>
       <c r="AA21" t="n">
-        <v>77.26363636363635</v>
+        <v>75.57301587301588</v>
       </c>
       <c r="AB21" t="n">
-        <v>25.70271164021164</v>
+        <v>25.27825224292616</v>
       </c>
       <c r="AC21" t="n">
-        <v>184.5059523809524</v>
+        <v>183.7509489302967</v>
       </c>
       <c r="AD21" t="n">
         <v>1</v>
       </c>
       <c r="AE21" t="n">
-        <v>66.62632275132275</v>
+        <v>66.6229583620888</v>
       </c>
       <c r="AF21" t="n">
-        <v>1261367.394179894</v>
+        <v>1184743.069933287</v>
       </c>
       <c r="AG21" t="n">
-        <v>69.8366402116402</v>
+        <v>70.17309351276742</v>
       </c>
       <c r="AH21" t="n">
-        <v>24.61444862155389</v>
+        <v>25.61522361805134</v>
       </c>
       <c r="AI21" t="n">
-        <v>184.9235651629072</v>
+        <v>183.4127876627386</v>
       </c>
       <c r="AJ21" t="n">
-        <v>1.411942355889725</v>
+        <v>1.22867780216587</v>
       </c>
       <c r="AK21" t="n">
-        <v>72.99003132832081</v>
+        <v>68.87196121774416</v>
       </c>
       <c r="AL21" t="n">
-        <v>5321504.072681705</v>
+        <v>1815575.481145929</v>
       </c>
       <c r="AM21" t="n">
-        <v>76.56177631578949</v>
+        <v>73.76358209187563</v>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>lxrr7DgN</t>
+          <t>UyNNTYWE</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>l0fHXMdE</t>
+          <t>0AI1QUJH</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>8QPARz8c</t>
+          <t>t2AoZLAa</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
-        <v>45521.4375</v>
+        <v>45522.4375</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t xml:space="preserve">welz t 
+          <t xml:space="preserve">heft f 
   ger </t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t xml:space="preserve">ms technologie arena
-  villingen schwenningen </t>
+          <t xml:space="preserve">friedrich ebert stadium
+  hildesheim </t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>8000</v>
+        <v>10000</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>lKLJUxeT</t>
+          <t>E3xs5mIe</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>KWixEVWi</t>
+          <t>6in2Eknb</t>
         </is>
       </c>
       <c r="H22" t="n">
@@ -3363,22 +3139,22 @@
       <c r="T22" t="inlineStr"/>
       <c r="U22" t="inlineStr"/>
       <c r="V22" t="n">
-        <v>25.62727272727273</v>
+        <v>25.27142857142857</v>
       </c>
       <c r="W22" t="n">
-        <v>186.5272727272727</v>
+        <v>182.0168831168831</v>
       </c>
       <c r="X22" t="n">
         <v>1</v>
       </c>
       <c r="Y22" t="n">
-        <v>72.90000000000001</v>
+        <v>67.14155844155843</v>
       </c>
       <c r="Z22" t="n">
-        <v>4462954.545454545</v>
+        <v>1294935.064935065</v>
       </c>
       <c r="AA22" t="n">
-        <v>75.34545454545454</v>
+        <v>70.81168831168831</v>
       </c>
       <c r="AB22" t="inlineStr"/>
       <c r="AC22" t="inlineStr"/>
@@ -3387,62 +3163,62 @@
       <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="inlineStr"/>
       <c r="AH22" t="n">
-        <v>27.39107142857143</v>
+        <v>27.46887755102041</v>
       </c>
       <c r="AI22" t="n">
-        <v>183.0269841269841</v>
+        <v>180.9216702470462</v>
       </c>
       <c r="AJ22" t="n">
         <v>1</v>
       </c>
       <c r="AK22" t="n">
-        <v>69.03234126984127</v>
+        <v>64.69414607948443</v>
       </c>
       <c r="AL22" t="n">
-        <v>1845550.595238096</v>
+        <v>798772.8696741855</v>
       </c>
       <c r="AM22" t="n">
-        <v>70.72083333333333</v>
+        <v>66.57149122807017</v>
       </c>
       <c r="AN22" t="inlineStr"/>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>lGJdeemM</t>
+          <t>8E8qmw3d</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>hzyf0b9b</t>
+          <t>jFMCm08e</t>
         </is>
       </c>
       <c r="B23" s="2" t="n">
-        <v>45521.54166666666</v>
+        <v>45522.4375</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t xml:space="preserve">sather a 
+          <t xml:space="preserve">aytekin d 
   ger </t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t xml:space="preserve">new tivoli
-  aachen </t>
+          <t xml:space="preserve">jahnstadion regensburg
+  regensburg </t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>31026</v>
+        <v>15210</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>j3PKcB4E</t>
+          <t>UiCmEP56</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>63WsD2ei</t>
+          <t>8Y2m6ADe</t>
         </is>
       </c>
       <c r="H23" t="n">
@@ -3470,7 +3246,7 @@
       <c r="N23" t="inlineStr"/>
       <c r="O23" t="inlineStr">
         <is>
-          <t>ILyJuN3g</t>
+          <t>0Ija0Ej9</t>
         </is>
       </c>
       <c r="P23" t="inlineStr"/>
@@ -3480,22 +3256,22 @@
       <c r="T23" t="inlineStr"/>
       <c r="U23" t="inlineStr"/>
       <c r="V23" t="n">
-        <v>25.25757575757576</v>
+        <v>27.97222222222222</v>
       </c>
       <c r="W23" t="n">
-        <v>186.5454545454545</v>
+        <v>182.4222222222222</v>
       </c>
       <c r="X23" t="n">
-        <v>1.075757575757576</v>
+        <v>1.258333333333333</v>
       </c>
       <c r="Y23" t="n">
-        <v>68.48484848484848</v>
+        <v>73.24259259259259</v>
       </c>
       <c r="Z23" t="n">
-        <v>1749242.424242425</v>
+        <v>3645069.444444445</v>
       </c>
       <c r="AA23" t="n">
-        <v>72.46969696969698</v>
+        <v>75.01111111111112</v>
       </c>
       <c r="AB23" t="inlineStr"/>
       <c r="AC23" t="inlineStr"/>
@@ -3504,62 +3280,66 @@
       <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="inlineStr"/>
       <c r="AH23" t="n">
-        <v>25.07421785139177</v>
+        <v>26.61693121693122</v>
       </c>
       <c r="AI23" t="n">
-        <v>185.8624194847021</v>
+        <v>182.9073032961191</v>
       </c>
       <c r="AJ23" t="n">
-        <v>1.015182884748102</v>
+        <v>1.064170843776107</v>
       </c>
       <c r="AK23" t="n">
-        <v>66.6799373130895</v>
+        <v>70.50391509075719</v>
       </c>
       <c r="AL23" t="n">
-        <v>1411003.637566138</v>
+        <v>2404898.16713501</v>
       </c>
       <c r="AM23" t="n">
-        <v>71.2854267310789</v>
-      </c>
-      <c r="AN23" t="inlineStr"/>
+        <v>73.59740054049264</v>
+      </c>
+      <c r="AN23" t="inlineStr">
+        <is>
+          <t>t0ZPdkUl</t>
+        </is>
+      </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>A15eUM4C</t>
+          <t>xzRzG0VI</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>CpiTEcOi</t>
+          <t>tvOIPExA</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
-        <v>45521.54166666666</v>
+        <v>45522.4375</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t xml:space="preserve">bacher m 
+          <t xml:space="preserve">burda m 
   ger </t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t xml:space="preserve">schuco arena
-  bielefeld </t>
+          <t xml:space="preserve">hardtwaldstadion
+  sandhausen </t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>27332</v>
+        <v>15414</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>pp38UXK8</t>
+          <t>UZxEj1R4</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>dfNCCCzS</t>
+          <t>WG9pOTse</t>
         </is>
       </c>
       <c r="H24" t="n">
@@ -3587,7 +3367,7 @@
       <c r="N24" t="inlineStr"/>
       <c r="O24" t="inlineStr">
         <is>
-          <t>QqLCC3il</t>
+          <t>88HSzjDr</t>
         </is>
       </c>
       <c r="P24" t="inlineStr"/>
@@ -3597,22 +3377,22 @@
       <c r="T24" t="inlineStr"/>
       <c r="U24" t="inlineStr"/>
       <c r="V24" t="n">
-        <v>25.69350649350649</v>
+        <v>24.17933884297521</v>
       </c>
       <c r="W24" t="n">
-        <v>183.7831168831169</v>
+        <v>185.0165289256199</v>
       </c>
       <c r="X24" t="n">
-        <v>1.184415584415585</v>
+        <v>1.340495867768595</v>
       </c>
       <c r="Y24" t="n">
-        <v>69.68051948051948</v>
+        <v>72.4404958677686</v>
       </c>
       <c r="Z24" t="n">
-        <v>2022500</v>
+        <v>5833719.008264463</v>
       </c>
       <c r="AA24" t="n">
-        <v>73.85194805194806</v>
+        <v>78.02479338842976</v>
       </c>
       <c r="AB24" t="inlineStr"/>
       <c r="AC24" t="inlineStr"/>
@@ -3621,62 +3401,62 @@
       <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="inlineStr"/>
       <c r="AH24" t="n">
-        <v>24.29795403009689</v>
+        <v>25.85333599149389</v>
       </c>
       <c r="AI24" t="n">
-        <v>183.7678829107401</v>
+        <v>184.8356592238171</v>
       </c>
       <c r="AJ24" t="n">
-        <v>1</v>
+        <v>1.308280170122275</v>
       </c>
       <c r="AK24" t="n">
-        <v>66.42261904761905</v>
+        <v>69.39958798511429</v>
       </c>
       <c r="AL24" t="n">
-        <v>1384835.600907029</v>
+        <v>2902165.071770335</v>
       </c>
       <c r="AM24" t="n">
-        <v>71.45305091733663</v>
+        <v>74.532562466773</v>
       </c>
       <c r="AN24" t="inlineStr"/>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>zyLSrbZQ</t>
+          <t>EDRZkDzS</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>8CpxDyg4</t>
+          <t>KSwfVwAO</t>
         </is>
       </c>
       <c r="B25" s="2" t="n">
-        <v>45521.54166666666</v>
+        <v>45522.4375</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t xml:space="preserve">siebert d 
+          <t xml:space="preserve">kampka r 
   ger </t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadion lohmuhle
-  lubeck </t>
+          <t xml:space="preserve">millerntor stadion
+  hamburg </t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>17849</v>
+        <v>29546</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>I1Vk6k3R</t>
+          <t>WrbkcjCd</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>nP1i5US1</t>
+          <t>S0hPB9rA</t>
         </is>
       </c>
       <c r="H25" t="n">
@@ -3704,7 +3484,7 @@
       <c r="N25" t="inlineStr"/>
       <c r="O25" t="inlineStr">
         <is>
-          <t>0Ija0Ej9</t>
+          <t>8vndvXTk</t>
         </is>
       </c>
       <c r="P25" t="inlineStr"/>
@@ -3714,22 +3494,22 @@
       <c r="T25" t="inlineStr"/>
       <c r="U25" t="inlineStr"/>
       <c r="V25" t="n">
-        <v>25.14545454545455</v>
+        <v>25.86363636363636</v>
       </c>
       <c r="W25" t="n">
-        <v>184.7454545454545</v>
+        <v>187.1436363636363</v>
       </c>
       <c r="X25" t="n">
-        <v>2.245454545454546</v>
+        <v>1</v>
       </c>
       <c r="Y25" t="n">
-        <v>79.55454545454546</v>
+        <v>70.55818181818181</v>
       </c>
       <c r="Z25" t="n">
-        <v>28540909.09090909</v>
+        <v>2390886.363636363</v>
       </c>
       <c r="AA25" t="n">
-        <v>83.10909090909091</v>
+        <v>74.07090909090908</v>
       </c>
       <c r="AB25" t="inlineStr"/>
       <c r="AC25" t="inlineStr"/>
@@ -3738,38 +3518,38 @@
       <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="inlineStr"/>
       <c r="AH25" t="n">
-        <v>25.06309523809524</v>
+        <v>26.05142422581681</v>
       </c>
       <c r="AI25" t="n">
-        <v>183.609126984127</v>
+        <v>186.2869533847795</v>
       </c>
       <c r="AJ25" t="n">
-        <v>2.011706349206349</v>
+        <v>1</v>
       </c>
       <c r="AK25" t="n">
-        <v>77.71388888888889</v>
+        <v>68.57811629263036</v>
       </c>
       <c r="AL25" t="n">
-        <v>20714563.49206349</v>
+        <v>1624988.634287707</v>
       </c>
       <c r="AM25" t="n">
-        <v>82.11527777777778</v>
+        <v>71.48562788092839</v>
       </c>
       <c r="AN25" t="inlineStr"/>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>MDhPV0RQ</t>
+          <t>AoL97rX8</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>6q2yrHgU</t>
+          <t>pzHxyrtm</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
-        <v>45522.33333333334</v>
+        <v>45522.54166666666</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3779,21 +3559,21 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t xml:space="preserve">ludwigspark stadion
-  saarbrucken </t>
+          <t xml:space="preserve">stadion am lotter kreuz
+  lotte </t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>16003</v>
+        <v>10059</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>fLbhmJ5l</t>
+          <t>hjNlCFPB</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>6FDqshzF</t>
+          <t>EB3q7jbk</t>
         </is>
       </c>
       <c r="H26" t="n">
@@ -3821,7 +3601,7 @@
       <c r="N26" t="inlineStr"/>
       <c r="O26" t="inlineStr">
         <is>
-          <t>CCQGbik8</t>
+          <t>naWckLmC</t>
         </is>
       </c>
       <c r="P26" t="inlineStr"/>
@@ -3831,22 +3611,22 @@
       <c r="T26" t="inlineStr"/>
       <c r="U26" t="inlineStr"/>
       <c r="V26" t="n">
-        <v>23.44877344877344</v>
+        <v>26.61038961038961</v>
       </c>
       <c r="W26" t="n">
-        <v>183.3506493506493</v>
+        <v>183.6103896103896</v>
       </c>
       <c r="X26" t="n">
-        <v>1.015873015873016</v>
+        <v>1.025974025974026</v>
       </c>
       <c r="Y26" t="n">
-        <v>66.96103896103897</v>
+        <v>68.55844155844156</v>
       </c>
       <c r="Z26" t="n">
-        <v>1622655.122655123</v>
+        <v>1629545.454545455</v>
       </c>
       <c r="AA26" t="n">
-        <v>72.92352092352093</v>
+        <v>72.8051948051948</v>
       </c>
       <c r="AB26" t="inlineStr"/>
       <c r="AC26" t="inlineStr"/>
@@ -3855,22 +3635,22 @@
       <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="inlineStr"/>
       <c r="AH26" t="n">
-        <v>27.19029581529582</v>
+        <v>26.45972073039743</v>
       </c>
       <c r="AI26" t="n">
-        <v>182.2007575757576</v>
+        <v>182.2928153717627</v>
       </c>
       <c r="AJ26" t="n">
-        <v>1.015873015873016</v>
+        <v>1.187641723356009</v>
       </c>
       <c r="AK26" t="n">
-        <v>67.24098124098124</v>
+        <v>66.75550483351235</v>
       </c>
       <c r="AL26" t="n">
-        <v>1184510.281385281</v>
+        <v>1201480.710705335</v>
       </c>
       <c r="AM26" t="n">
-        <v>69.51893939393939</v>
+        <v>71.62398555913595</v>
       </c>
       <c r="AN26" t="inlineStr"/>
       <c r="AO26" t="inlineStr">
@@ -3882,35 +3662,35 @@
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>AiJ3kset</t>
+          <t>dCPKovw8</t>
         </is>
       </c>
       <c r="B27" s="2" t="n">
-        <v>45522.33333333334</v>
+        <v>45522.54166666666</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t xml:space="preserve">jollenbeck m 
+          <t xml:space="preserve">burda m 
   ger </t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t xml:space="preserve">friedrich ludwig jahn sportpark
-  berlin </t>
+          <t xml:space="preserve">hansch arena
+  meppen </t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>19708</v>
+        <v>13696</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>UNr2EUfd</t>
+          <t>rXqBh2xP</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>fTVNku3I</t>
+          <t>v9k3aY5F</t>
         </is>
       </c>
       <c r="H27" t="n">
@@ -3936,7 +3716,11 @@
         </is>
       </c>
       <c r="N27" t="inlineStr"/>
-      <c r="O27" t="inlineStr"/>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>ILyJuN3g</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr"/>
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr"/>
@@ -3944,22 +3728,22 @@
       <c r="T27" t="inlineStr"/>
       <c r="U27" t="inlineStr"/>
       <c r="V27" t="n">
-        <v>25.41333333333333</v>
+        <v>24.9012987012987</v>
       </c>
       <c r="W27" t="n">
-        <v>186.0030303030303</v>
+        <v>183.1883116883117</v>
       </c>
       <c r="X27" t="n">
-        <v>1.462323232323232</v>
+        <v>1</v>
       </c>
       <c r="Y27" t="n">
-        <v>74.33111111111111</v>
+        <v>70.84155844155843</v>
       </c>
       <c r="Z27" t="n">
-        <v>6657146.464646464</v>
+        <v>2692337.662337662</v>
       </c>
       <c r="AA27" t="n">
-        <v>77.32606060606061</v>
+        <v>74.22597402597403</v>
       </c>
       <c r="AB27" t="inlineStr"/>
       <c r="AC27" t="inlineStr"/>
@@ -3968,62 +3752,62 @@
       <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="inlineStr"/>
       <c r="AH27" t="n">
-        <v>23.899139420521</v>
+        <v>25.11075036075036</v>
       </c>
       <c r="AI27" t="n">
-        <v>184.2982721956406</v>
+        <v>181.7821067821068</v>
       </c>
       <c r="AJ27" t="n">
-        <v>1.139229228373965</v>
+        <v>1</v>
       </c>
       <c r="AK27" t="n">
-        <v>71.05004414445204</v>
+        <v>69.8781746031746</v>
       </c>
       <c r="AL27" t="n">
-        <v>3913032.094915318</v>
+        <v>2400109.668109668</v>
       </c>
       <c r="AM27" t="n">
-        <v>76.51723674717095</v>
+        <v>73.3320707070707</v>
       </c>
       <c r="AN27" t="inlineStr"/>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>2VSFgl3c</t>
+          <t>EDRZkDzS</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>YV3TqwPH</t>
+          <t>vXAKoaf5</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
-        <v>45522.4375</v>
+        <v>45522.54166666666</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t xml:space="preserve">haslberger w 
+          <t xml:space="preserve">kampka r 
   ger </t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadion am panzenberg
-  bremen </t>
+          <t xml:space="preserve">rudolf harbig stadion
+  dresden </t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5000</v>
+        <v>32249</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>tW75B1ei</t>
+          <t>zL1YsOi1</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>G2Op923t</t>
+          <t>ne1oL3y7</t>
         </is>
       </c>
       <c r="H28" t="n">
@@ -4049,7 +3833,11 @@
         </is>
       </c>
       <c r="N28" t="inlineStr"/>
-      <c r="O28" t="inlineStr"/>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>WG9pOTse</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr"/>
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr"/>
@@ -4057,22 +3845,22 @@
       <c r="T28" t="inlineStr"/>
       <c r="U28" t="inlineStr"/>
       <c r="V28" t="n">
-        <v>24.10616883116883</v>
+        <v>25.48787878787878</v>
       </c>
       <c r="W28" t="n">
-        <v>185.4892857142857</v>
+        <v>184.5181818181818</v>
       </c>
       <c r="X28" t="n">
         <v>1</v>
       </c>
       <c r="Y28" t="n">
-        <v>66.52467532467533</v>
+        <v>70.55454545454546</v>
       </c>
       <c r="Z28" t="n">
-        <v>1420081.168831169</v>
+        <v>2605202.02020202</v>
       </c>
       <c r="AA28" t="n">
-        <v>72.47792207792207</v>
+        <v>73.95959595959596</v>
       </c>
       <c r="AB28" t="inlineStr"/>
       <c r="AC28" t="inlineStr"/>
@@ -4081,62 +3869,62 @@
       <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="inlineStr"/>
       <c r="AH28" t="n">
-        <v>25.24755485198031</v>
+        <v>23.88383838383838</v>
       </c>
       <c r="AI28" t="n">
-        <v>186.3757108574655</v>
+        <v>185.8560606060606</v>
       </c>
       <c r="AJ28" t="n">
         <v>1</v>
       </c>
       <c r="AK28" t="n">
-        <v>67.15276377349359</v>
+        <v>66.90628507295173</v>
       </c>
       <c r="AL28" t="n">
-        <v>1396154.689642655</v>
+        <v>1690971.520763187</v>
       </c>
       <c r="AM28" t="n">
-        <v>71.317123094297</v>
+        <v>72.77427048260382</v>
       </c>
       <c r="AN28" t="inlineStr"/>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>0AI1QUJH</t>
+          <t>AoL97rX8</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>l0ueP5rR</t>
+          <t>06NAdG8N</t>
         </is>
       </c>
       <c r="B29" s="2" t="n">
-        <v>45522.4375</v>
+        <v>45523.54166666666</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t xml:space="preserve">haslberger w 
+          <t xml:space="preserve">petersen m 
   ger </t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t xml:space="preserve">ostseestadion
-  rostock </t>
+          <t xml:space="preserve">stadion der freundschaft
+  cottbus </t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>29000</v>
+        <v>22450</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>KIHmtCkL</t>
+          <t>6g44VD52</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2y0u8Wrq</t>
+          <t>Ig1f1fy3</t>
         </is>
       </c>
       <c r="H29" t="n">
@@ -4161,103 +3949,75 @@
           <t>dfb pokal</t>
         </is>
       </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>ILyJuN3g</t>
-        </is>
-      </c>
-      <c r="O29" t="inlineStr"/>
-      <c r="P29" t="n">
-        <v>26.5</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>183.8030303030303</v>
-      </c>
-      <c r="R29" t="n">
-        <v>1</v>
-      </c>
-      <c r="S29" t="n">
-        <v>67.83333333333333</v>
-      </c>
-      <c r="T29" t="n">
-        <v>1329545.454545455</v>
-      </c>
-      <c r="U29" t="n">
-        <v>70.51515151515152</v>
-      </c>
+      <c r="N29" t="inlineStr"/>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>v9k3aY5F</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr"/>
+      <c r="Q29" t="inlineStr"/>
+      <c r="R29" t="inlineStr"/>
+      <c r="S29" t="inlineStr"/>
+      <c r="T29" t="inlineStr"/>
+      <c r="U29" t="inlineStr"/>
       <c r="V29" t="n">
-        <v>23.96031746031746</v>
+        <v>26.18181818181818</v>
       </c>
       <c r="W29" t="n">
-        <v>184.3968253968254</v>
+        <v>183.1272727272727</v>
       </c>
       <c r="X29" t="n">
-        <v>1.073015873015873</v>
+        <v>1.181818181818182</v>
       </c>
       <c r="Y29" t="n">
-        <v>70.34920634920634</v>
+        <v>73.16363636363636</v>
       </c>
       <c r="Z29" t="n">
-        <v>2767460.317460318</v>
+        <v>4815909.090909092</v>
       </c>
       <c r="AA29" t="n">
-        <v>75.57301587301588</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>25.27825224292616</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>183.7509489302967</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE29" t="n">
-        <v>66.6229583620888</v>
-      </c>
-      <c r="AF29" t="n">
-        <v>1184743.069933287</v>
-      </c>
-      <c r="AG29" t="n">
-        <v>70.17309351276742</v>
-      </c>
+        <v>75.94545454545455</v>
+      </c>
+      <c r="AB29" t="inlineStr"/>
+      <c r="AC29" t="inlineStr"/>
+      <c r="AD29" t="inlineStr"/>
+      <c r="AE29" t="inlineStr"/>
+      <c r="AF29" t="inlineStr"/>
+      <c r="AG29" t="inlineStr"/>
       <c r="AH29" t="n">
-        <v>25.61522361805134</v>
+        <v>24.86158126293996</v>
       </c>
       <c r="AI29" t="n">
-        <v>183.4127876627386</v>
+        <v>184.8690601049726</v>
       </c>
       <c r="AJ29" t="n">
-        <v>1.22867780216587</v>
+        <v>1.111249364352911</v>
       </c>
       <c r="AK29" t="n">
-        <v>68.87196121774416</v>
+        <v>68.34426964149505</v>
       </c>
       <c r="AL29" t="n">
-        <v>1815575.481145929</v>
+        <v>2456707.041607642</v>
       </c>
       <c r="AM29" t="n">
-        <v>73.76358209187563</v>
-      </c>
-      <c r="AN29" t="inlineStr">
-        <is>
-          <t>UyNNTYWE</t>
-        </is>
-      </c>
+        <v>73.74422787040064</v>
+      </c>
+      <c r="AN29" t="inlineStr"/>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>0AI1QUJH</t>
+          <t>xzRzG0VI</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>t2AoZLAa</t>
+          <t>Sff03OL7</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
-        <v>45522.4375</v>
+        <v>45523.54166666666</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4267,21 +4027,21 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t xml:space="preserve">friedrich ebert stadium
-  hildesheim </t>
+          <t xml:space="preserve">bieberer berg stadion
+  offenbach am main </t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>10000</v>
+        <v>20500</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>E3xs5mIe</t>
+          <t>YJURlaIO</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>6in2Eknb</t>
+          <t>YFuz2RLm</t>
         </is>
       </c>
       <c r="H30" t="n">
@@ -4315,22 +4075,22 @@
       <c r="T30" t="inlineStr"/>
       <c r="U30" t="inlineStr"/>
       <c r="V30" t="n">
-        <v>25.27142857142857</v>
+        <v>25.46666666666667</v>
       </c>
       <c r="W30" t="n">
-        <v>182.0168831168831</v>
+        <v>180.9833333333333</v>
       </c>
       <c r="X30" t="n">
         <v>1</v>
       </c>
       <c r="Y30" t="n">
-        <v>67.14155844155843</v>
+        <v>68.28333333333332</v>
       </c>
       <c r="Z30" t="n">
-        <v>1294935.064935065</v>
+        <v>1470833.333333333</v>
       </c>
       <c r="AA30" t="n">
-        <v>70.81168831168831</v>
+        <v>70.73333333333333</v>
       </c>
       <c r="AB30" t="inlineStr"/>
       <c r="AC30" t="inlineStr"/>
@@ -4339,22 +4099,22 @@
       <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="inlineStr"/>
       <c r="AH30" t="n">
-        <v>27.46887755102041</v>
+        <v>23.22341269841269</v>
       </c>
       <c r="AI30" t="n">
-        <v>180.9216702470462</v>
+        <v>179.9242063492063</v>
       </c>
       <c r="AJ30" t="n">
         <v>1</v>
       </c>
       <c r="AK30" t="n">
-        <v>64.69414607948443</v>
+        <v>65.57063492063493</v>
       </c>
       <c r="AL30" t="n">
-        <v>798772.8696741855</v>
+        <v>1241240.07936508</v>
       </c>
       <c r="AM30" t="n">
-        <v>66.57149122807017</v>
+        <v>70.34960317460317</v>
       </c>
       <c r="AN30" t="inlineStr"/>
       <c r="AO30" t="inlineStr">
@@ -4366,35 +4126,35 @@
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>jFMCm08e</t>
+          <t>EkP2bxvB</t>
         </is>
       </c>
       <c r="B31" s="2" t="n">
-        <v>45522.4375</v>
+        <v>45523.54166666666</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t xml:space="preserve">aytekin d 
+          <t xml:space="preserve">willenborg f 
   ger </t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t xml:space="preserve">jahnstadion regensburg
-  regensburg </t>
+          <t xml:space="preserve">stadion oberwerth
+  koblenz </t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>15210</v>
+        <v>9500</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>UiCmEP56</t>
+          <t>p8wBsqZt</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>8Y2m6ADe</t>
+          <t>nwkTahLL</t>
         </is>
       </c>
       <c r="H31" t="n">
@@ -4422,7 +4182,7 @@
       <c r="N31" t="inlineStr"/>
       <c r="O31" t="inlineStr">
         <is>
-          <t>0Ija0Ej9</t>
+          <t>dfNCCCzS</t>
         </is>
       </c>
       <c r="P31" t="inlineStr"/>
@@ -4432,22 +4192,22 @@
       <c r="T31" t="inlineStr"/>
       <c r="U31" t="inlineStr"/>
       <c r="V31" t="n">
-        <v>27.97222222222222</v>
+        <v>25.22</v>
       </c>
       <c r="W31" t="n">
-        <v>182.4222222222222</v>
+        <v>186.74</v>
       </c>
       <c r="X31" t="n">
-        <v>1.258333333333333</v>
+        <v>1.56</v>
       </c>
       <c r="Y31" t="n">
-        <v>73.24259259259259</v>
+        <v>75.81</v>
       </c>
       <c r="Z31" t="n">
-        <v>3645069.444444445</v>
+        <v>10860000</v>
       </c>
       <c r="AA31" t="n">
-        <v>75.01111111111112</v>
+        <v>79.66</v>
       </c>
       <c r="AB31" t="inlineStr"/>
       <c r="AC31" t="inlineStr"/>
@@ -4456,66 +4216,62 @@
       <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="inlineStr"/>
       <c r="AH31" t="n">
-        <v>26.61693121693122</v>
+        <v>24.49049516908213</v>
       </c>
       <c r="AI31" t="n">
-        <v>182.9073032961191</v>
+        <v>183.5287318840579</v>
       </c>
       <c r="AJ31" t="n">
-        <v>1.064170843776107</v>
+        <v>1.273164251207729</v>
       </c>
       <c r="AK31" t="n">
-        <v>70.50391509075719</v>
+        <v>73.89692028985507</v>
       </c>
       <c r="AL31" t="n">
-        <v>2404898.16713501</v>
+        <v>8517461.956521738</v>
       </c>
       <c r="AM31" t="n">
-        <v>73.59740054049264</v>
-      </c>
-      <c r="AN31" t="inlineStr">
-        <is>
-          <t>t0ZPdkUl</t>
-        </is>
-      </c>
+        <v>78.55956521739131</v>
+      </c>
+      <c r="AN31" t="inlineStr"/>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>xzRzG0VI</t>
+          <t>vZA6VYpf</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>tvOIPExA</t>
+          <t>pAXo2Kvn</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
-        <v>45522.4375</v>
+        <v>45523.65625</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t xml:space="preserve">burda m 
+          <t xml:space="preserve">zwayer f 
   ger </t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t xml:space="preserve">hardtwaldstadion
-  sandhausen </t>
+          <t xml:space="preserve">eintracht stadion
+  braunschweig </t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>15414</v>
+        <v>23325</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>UZxEj1R4</t>
+          <t>QqLCC3il</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>WG9pOTse</t>
+          <t>8vndvXTk</t>
         </is>
       </c>
       <c r="H32" t="n">
@@ -4540,112 +4296,144 @@
           <t>dfb pokal</t>
         </is>
       </c>
-      <c r="N32" t="inlineStr"/>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>dfNCCCzS</t>
+        </is>
+      </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>88HSzjDr</t>
-        </is>
-      </c>
-      <c r="P32" t="inlineStr"/>
-      <c r="Q32" t="inlineStr"/>
-      <c r="R32" t="inlineStr"/>
-      <c r="S32" t="inlineStr"/>
-      <c r="T32" t="inlineStr"/>
-      <c r="U32" t="inlineStr"/>
+          <t>EuakNmc1</t>
+        </is>
+      </c>
+      <c r="P32" t="n">
+        <v>25.41720779220779</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>184.2175324675325</v>
+      </c>
+      <c r="R32" t="n">
+        <v>1.082792207792208</v>
+      </c>
+      <c r="S32" t="n">
+        <v>67.33279220779221</v>
+      </c>
+      <c r="T32" t="n">
+        <v>1406980.519480519</v>
+      </c>
+      <c r="U32" t="n">
+        <v>71.29383116883118</v>
+      </c>
       <c r="V32" t="n">
-        <v>24.17933884297521</v>
+        <v>24.25222222222222</v>
       </c>
       <c r="W32" t="n">
-        <v>185.0165289256199</v>
+        <v>183.0955555555556</v>
       </c>
       <c r="X32" t="n">
-        <v>1.340495867768595</v>
+        <v>1.63</v>
       </c>
       <c r="Y32" t="n">
-        <v>72.4404958677686</v>
+        <v>76.98111111111112</v>
       </c>
       <c r="Z32" t="n">
-        <v>5833719.008264463</v>
+        <v>15614611.11111111</v>
       </c>
       <c r="AA32" t="n">
-        <v>78.02479338842976</v>
-      </c>
-      <c r="AB32" t="inlineStr"/>
-      <c r="AC32" t="inlineStr"/>
-      <c r="AD32" t="inlineStr"/>
-      <c r="AE32" t="inlineStr"/>
-      <c r="AF32" t="inlineStr"/>
-      <c r="AG32" t="inlineStr"/>
+        <v>81.18111111111111</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>26.05385487528344</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>182.6663832199546</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>66.68679138321995</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>1263927.154195011</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>70.07199546485261</v>
+      </c>
       <c r="AH32" t="n">
-        <v>25.85333599149389</v>
+        <v>24.30286226930964</v>
       </c>
       <c r="AI32" t="n">
-        <v>184.8356592238171</v>
+        <v>183.7797641831852</v>
       </c>
       <c r="AJ32" t="n">
-        <v>1.308280170122275</v>
+        <v>1.421828434723172</v>
       </c>
       <c r="AK32" t="n">
-        <v>69.39958798511429</v>
+        <v>71.9276110731374</v>
       </c>
       <c r="AL32" t="n">
-        <v>2902165.071770335</v>
+        <v>5697609.791524266</v>
       </c>
       <c r="AM32" t="n">
-        <v>74.532562466773</v>
-      </c>
-      <c r="AN32" t="inlineStr"/>
+        <v>78.33495215311004</v>
+      </c>
+      <c r="AN32" t="inlineStr">
+        <is>
+          <t>txZLBQVC</t>
+        </is>
+      </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>EDRZkDzS</t>
+          <t>pfoInmcq</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>KSwfVwAO</t>
+          <t>fcxqFy2l</t>
         </is>
       </c>
       <c r="B33" s="2" t="n">
-        <v>45522.4375</v>
+        <v>45521.64583333334</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t xml:space="preserve">kampka r 
+          <t xml:space="preserve">schlager d 
   ger </t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t xml:space="preserve">millerntor stadion
-  hamburg </t>
+          <t xml:space="preserve">bayarena
+  leverkusen </t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>29546</v>
+        <v>30210</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>WrbkcjCd</t>
+          <t>4jcj2zMd</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>S0hPB9rA</t>
+          <t>nJQmYp1B</t>
         </is>
       </c>
       <c r="H33" t="n">
         <v>59</v>
       </c>
       <c r="I33" t="n">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="J33" t="n">
         <v>1</v>
       </c>
       <c r="K33" t="n">
-        <v>20242025</v>
+        <v>2024</v>
       </c>
       <c r="L33" t="inlineStr">
         <is>
@@ -4654,1194 +4442,97 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>dfb pokal</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr"/>
+          <t>super cup</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>WG9pOTse</t>
+        </is>
+      </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>8vndvXTk</t>
-        </is>
-      </c>
-      <c r="P33" t="inlineStr"/>
-      <c r="Q33" t="inlineStr"/>
-      <c r="R33" t="inlineStr"/>
-      <c r="S33" t="inlineStr"/>
-      <c r="T33" t="inlineStr"/>
-      <c r="U33" t="inlineStr"/>
+          <t>fiEQZ7C7</t>
+        </is>
+      </c>
+      <c r="P33" t="n">
+        <v>25.63939393939394</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>185.3989898989899</v>
+      </c>
+      <c r="R33" t="n">
+        <v>2.018181818181818</v>
+      </c>
+      <c r="S33" t="n">
+        <v>81.13333333333334</v>
+      </c>
+      <c r="T33" t="n">
+        <v>31332828.28282828</v>
+      </c>
+      <c r="U33" t="n">
+        <v>84.04242424242423</v>
+      </c>
       <c r="V33" t="n">
-        <v>25.86363636363636</v>
+        <v>24.40909090909091</v>
       </c>
       <c r="W33" t="n">
-        <v>187.1436363636363</v>
+        <v>184.6454545454546</v>
       </c>
       <c r="X33" t="n">
-        <v>1</v>
+        <v>1.490909090909091</v>
       </c>
       <c r="Y33" t="n">
-        <v>70.55818181818181</v>
+        <v>76</v>
       </c>
       <c r="Z33" t="n">
-        <v>2390886.363636363</v>
+        <v>11738181.81818181</v>
       </c>
       <c r="AA33" t="n">
-        <v>74.07090909090908</v>
-      </c>
-      <c r="AB33" t="inlineStr"/>
-      <c r="AC33" t="inlineStr"/>
-      <c r="AD33" t="inlineStr"/>
-      <c r="AE33" t="inlineStr"/>
-      <c r="AF33" t="inlineStr"/>
-      <c r="AG33" t="inlineStr"/>
+        <v>79.16363636363636</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>22.87297666102014</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>181.3535983779067</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>1.797712300874356</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>78.8402785620177</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>36662927.46778912</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>84.46393237855688</v>
+      </c>
       <c r="AH33" t="n">
-        <v>26.05142422581681</v>
+        <v>24.40472222222222</v>
       </c>
       <c r="AI33" t="n">
-        <v>186.2869533847795</v>
+        <v>182.5288888888889</v>
       </c>
       <c r="AJ33" t="n">
-        <v>1</v>
+        <v>1.280753968253968</v>
       </c>
       <c r="AK33" t="n">
-        <v>68.57811629263036</v>
+        <v>71.27392857142857</v>
       </c>
       <c r="AL33" t="n">
-        <v>1624988.634287707</v>
+        <v>5835730.158730159</v>
       </c>
       <c r="AM33" t="n">
-        <v>71.48562788092839</v>
-      </c>
-      <c r="AN33" t="inlineStr"/>
+        <v>75.7297619047619</v>
+      </c>
+      <c r="AN33" t="inlineStr">
+        <is>
+          <t>2BYSk4KO</t>
+        </is>
+      </c>
       <c r="AO33" t="inlineStr">
-        <is>
-          <t>AoL97rX8</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="1" t="inlineStr">
-        <is>
-          <t>pzHxyrtm</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="n">
-        <v>45522.54166666666</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">braun r 
-  ger </t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stadion am lotter kreuz
-  lotte </t>
-        </is>
-      </c>
-      <c r="E34" t="n">
-        <v>10059</v>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>hjNlCFPB</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>EB3q7jbk</t>
-        </is>
-      </c>
-      <c r="H34" t="n">
-        <v>59</v>
-      </c>
-      <c r="I34" t="n">
-        <v>593</v>
-      </c>
-      <c r="J34" t="n">
-        <v>1</v>
-      </c>
-      <c r="K34" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>dfb pokal</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr"/>
-      <c r="O34" t="inlineStr">
-        <is>
-          <t>naWckLmC</t>
-        </is>
-      </c>
-      <c r="P34" t="inlineStr"/>
-      <c r="Q34" t="inlineStr"/>
-      <c r="R34" t="inlineStr"/>
-      <c r="S34" t="inlineStr"/>
-      <c r="T34" t="inlineStr"/>
-      <c r="U34" t="inlineStr"/>
-      <c r="V34" t="n">
-        <v>26.61038961038961</v>
-      </c>
-      <c r="W34" t="n">
-        <v>183.6103896103896</v>
-      </c>
-      <c r="X34" t="n">
-        <v>1.025974025974026</v>
-      </c>
-      <c r="Y34" t="n">
-        <v>68.55844155844156</v>
-      </c>
-      <c r="Z34" t="n">
-        <v>1629545.454545455</v>
-      </c>
-      <c r="AA34" t="n">
-        <v>72.8051948051948</v>
-      </c>
-      <c r="AB34" t="inlineStr"/>
-      <c r="AC34" t="inlineStr"/>
-      <c r="AD34" t="inlineStr"/>
-      <c r="AE34" t="inlineStr"/>
-      <c r="AF34" t="inlineStr"/>
-      <c r="AG34" t="inlineStr"/>
-      <c r="AH34" t="n">
-        <v>26.45972073039743</v>
-      </c>
-      <c r="AI34" t="n">
-        <v>182.2928153717627</v>
-      </c>
-      <c r="AJ34" t="n">
-        <v>1.187641723356009</v>
-      </c>
-      <c r="AK34" t="n">
-        <v>66.75550483351235</v>
-      </c>
-      <c r="AL34" t="n">
-        <v>1201480.710705335</v>
-      </c>
-      <c r="AM34" t="n">
-        <v>71.62398555913595</v>
-      </c>
-      <c r="AN34" t="inlineStr"/>
-      <c r="AO34" t="inlineStr">
-        <is>
-          <t>tO31cZrF</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="1" t="inlineStr">
-        <is>
-          <t>dCPKovw8</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="n">
-        <v>45522.54166666666</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">burda m 
-  ger </t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t xml:space="preserve">hansch arena
-  meppen </t>
-        </is>
-      </c>
-      <c r="E35" t="n">
-        <v>13696</v>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>rXqBh2xP</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>v9k3aY5F</t>
-        </is>
-      </c>
-      <c r="H35" t="n">
-        <v>59</v>
-      </c>
-      <c r="I35" t="n">
-        <v>593</v>
-      </c>
-      <c r="J35" t="n">
-        <v>1</v>
-      </c>
-      <c r="K35" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>dfb pokal</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr"/>
-      <c r="O35" t="inlineStr">
-        <is>
-          <t>ILyJuN3g</t>
-        </is>
-      </c>
-      <c r="P35" t="inlineStr"/>
-      <c r="Q35" t="inlineStr"/>
-      <c r="R35" t="inlineStr"/>
-      <c r="S35" t="inlineStr"/>
-      <c r="T35" t="inlineStr"/>
-      <c r="U35" t="inlineStr"/>
-      <c r="V35" t="n">
-        <v>24.9012987012987</v>
-      </c>
-      <c r="W35" t="n">
-        <v>183.1883116883117</v>
-      </c>
-      <c r="X35" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y35" t="n">
-        <v>70.84155844155843</v>
-      </c>
-      <c r="Z35" t="n">
-        <v>2692337.662337662</v>
-      </c>
-      <c r="AA35" t="n">
-        <v>74.22597402597403</v>
-      </c>
-      <c r="AB35" t="inlineStr"/>
-      <c r="AC35" t="inlineStr"/>
-      <c r="AD35" t="inlineStr"/>
-      <c r="AE35" t="inlineStr"/>
-      <c r="AF35" t="inlineStr"/>
-      <c r="AG35" t="inlineStr"/>
-      <c r="AH35" t="n">
-        <v>25.11075036075036</v>
-      </c>
-      <c r="AI35" t="n">
-        <v>181.7821067821068</v>
-      </c>
-      <c r="AJ35" t="n">
-        <v>1</v>
-      </c>
-      <c r="AK35" t="n">
-        <v>69.8781746031746</v>
-      </c>
-      <c r="AL35" t="n">
-        <v>2400109.668109668</v>
-      </c>
-      <c r="AM35" t="n">
-        <v>73.3320707070707</v>
-      </c>
-      <c r="AN35" t="inlineStr"/>
-      <c r="AO35" t="inlineStr">
-        <is>
-          <t>EDRZkDzS</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="1" t="inlineStr">
-        <is>
-          <t>vXAKoaf5</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="n">
-        <v>45522.54166666666</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">kampka r 
-  ger </t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">rudolf harbig stadion
-  dresden </t>
-        </is>
-      </c>
-      <c r="E36" t="n">
-        <v>32249</v>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>zL1YsOi1</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>ne1oL3y7</t>
-        </is>
-      </c>
-      <c r="H36" t="n">
-        <v>59</v>
-      </c>
-      <c r="I36" t="n">
-        <v>593</v>
-      </c>
-      <c r="J36" t="n">
-        <v>1</v>
-      </c>
-      <c r="K36" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>dfb pokal</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr"/>
-      <c r="O36" t="inlineStr">
-        <is>
-          <t>WG9pOTse</t>
-        </is>
-      </c>
-      <c r="P36" t="inlineStr"/>
-      <c r="Q36" t="inlineStr"/>
-      <c r="R36" t="inlineStr"/>
-      <c r="S36" t="inlineStr"/>
-      <c r="T36" t="inlineStr"/>
-      <c r="U36" t="inlineStr"/>
-      <c r="V36" t="n">
-        <v>25.48787878787878</v>
-      </c>
-      <c r="W36" t="n">
-        <v>184.5181818181818</v>
-      </c>
-      <c r="X36" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y36" t="n">
-        <v>70.55454545454546</v>
-      </c>
-      <c r="Z36" t="n">
-        <v>2605202.02020202</v>
-      </c>
-      <c r="AA36" t="n">
-        <v>73.95959595959596</v>
-      </c>
-      <c r="AB36" t="inlineStr"/>
-      <c r="AC36" t="inlineStr"/>
-      <c r="AD36" t="inlineStr"/>
-      <c r="AE36" t="inlineStr"/>
-      <c r="AF36" t="inlineStr"/>
-      <c r="AG36" t="inlineStr"/>
-      <c r="AH36" t="n">
-        <v>23.88383838383838</v>
-      </c>
-      <c r="AI36" t="n">
-        <v>185.8560606060606</v>
-      </c>
-      <c r="AJ36" t="n">
-        <v>1</v>
-      </c>
-      <c r="AK36" t="n">
-        <v>66.90628507295173</v>
-      </c>
-      <c r="AL36" t="n">
-        <v>1690971.520763187</v>
-      </c>
-      <c r="AM36" t="n">
-        <v>72.77427048260382</v>
-      </c>
-      <c r="AN36" t="inlineStr"/>
-      <c r="AO36" t="inlineStr">
-        <is>
-          <t>AoL97rX8</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="1" t="inlineStr">
-        <is>
-          <t>06NAdG8N</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="n">
-        <v>45523.54166666666</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t xml:space="preserve">petersen m 
-  ger </t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stadion der freundschaft
-  cottbus </t>
-        </is>
-      </c>
-      <c r="E37" t="n">
-        <v>22450</v>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>6g44VD52</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>Ig1f1fy3</t>
-        </is>
-      </c>
-      <c r="H37" t="n">
-        <v>59</v>
-      </c>
-      <c r="I37" t="n">
-        <v>593</v>
-      </c>
-      <c r="J37" t="n">
-        <v>1</v>
-      </c>
-      <c r="K37" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>dfb pokal</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr"/>
-      <c r="O37" t="inlineStr">
-        <is>
-          <t>v9k3aY5F</t>
-        </is>
-      </c>
-      <c r="P37" t="inlineStr"/>
-      <c r="Q37" t="inlineStr"/>
-      <c r="R37" t="inlineStr"/>
-      <c r="S37" t="inlineStr"/>
-      <c r="T37" t="inlineStr"/>
-      <c r="U37" t="inlineStr"/>
-      <c r="V37" t="n">
-        <v>26.18181818181818</v>
-      </c>
-      <c r="W37" t="n">
-        <v>183.1272727272727</v>
-      </c>
-      <c r="X37" t="n">
-        <v>1.181818181818182</v>
-      </c>
-      <c r="Y37" t="n">
-        <v>73.16363636363636</v>
-      </c>
-      <c r="Z37" t="n">
-        <v>4815909.090909092</v>
-      </c>
-      <c r="AA37" t="n">
-        <v>75.94545454545455</v>
-      </c>
-      <c r="AB37" t="inlineStr"/>
-      <c r="AC37" t="inlineStr"/>
-      <c r="AD37" t="inlineStr"/>
-      <c r="AE37" t="inlineStr"/>
-      <c r="AF37" t="inlineStr"/>
-      <c r="AG37" t="inlineStr"/>
-      <c r="AH37" t="n">
-        <v>24.86158126293996</v>
-      </c>
-      <c r="AI37" t="n">
-        <v>184.8690601049726</v>
-      </c>
-      <c r="AJ37" t="n">
-        <v>1.111249364352911</v>
-      </c>
-      <c r="AK37" t="n">
-        <v>68.34426964149505</v>
-      </c>
-      <c r="AL37" t="n">
-        <v>2456707.041607642</v>
-      </c>
-      <c r="AM37" t="n">
-        <v>73.74422787040064</v>
-      </c>
-      <c r="AN37" t="inlineStr"/>
-      <c r="AO37" t="inlineStr">
-        <is>
-          <t>xzRzG0VI</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="1" t="inlineStr">
-        <is>
-          <t>Sff03OL7</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="n">
-        <v>45523.54166666666</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">heft f 
-  ger </t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">bieberer berg stadion
-  offenbach am main </t>
-        </is>
-      </c>
-      <c r="E38" t="n">
-        <v>20500</v>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>YJURlaIO</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>YFuz2RLm</t>
-        </is>
-      </c>
-      <c r="H38" t="n">
-        <v>59</v>
-      </c>
-      <c r="I38" t="n">
-        <v>593</v>
-      </c>
-      <c r="J38" t="n">
-        <v>1</v>
-      </c>
-      <c r="K38" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L38" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>dfb pokal</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr"/>
-      <c r="O38" t="inlineStr"/>
-      <c r="P38" t="inlineStr"/>
-      <c r="Q38" t="inlineStr"/>
-      <c r="R38" t="inlineStr"/>
-      <c r="S38" t="inlineStr"/>
-      <c r="T38" t="inlineStr"/>
-      <c r="U38" t="inlineStr"/>
-      <c r="V38" t="n">
-        <v>25.46666666666667</v>
-      </c>
-      <c r="W38" t="n">
-        <v>180.9833333333333</v>
-      </c>
-      <c r="X38" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y38" t="n">
-        <v>68.28333333333332</v>
-      </c>
-      <c r="Z38" t="n">
-        <v>1470833.333333333</v>
-      </c>
-      <c r="AA38" t="n">
-        <v>70.73333333333333</v>
-      </c>
-      <c r="AB38" t="inlineStr"/>
-      <c r="AC38" t="inlineStr"/>
-      <c r="AD38" t="inlineStr"/>
-      <c r="AE38" t="inlineStr"/>
-      <c r="AF38" t="inlineStr"/>
-      <c r="AG38" t="inlineStr"/>
-      <c r="AH38" t="n">
-        <v>23.22341269841269</v>
-      </c>
-      <c r="AI38" t="n">
-        <v>179.9242063492063</v>
-      </c>
-      <c r="AJ38" t="n">
-        <v>1</v>
-      </c>
-      <c r="AK38" t="n">
-        <v>65.57063492063493</v>
-      </c>
-      <c r="AL38" t="n">
-        <v>1241240.07936508</v>
-      </c>
-      <c r="AM38" t="n">
-        <v>70.34960317460317</v>
-      </c>
-      <c r="AN38" t="inlineStr"/>
-      <c r="AO38" t="inlineStr">
-        <is>
-          <t>8E8qmw3d</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="1" t="inlineStr">
-        <is>
-          <t>EkP2bxvB</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="n">
-        <v>45523.54166666666</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">willenborg f 
-  ger </t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stadion oberwerth
-  koblenz </t>
-        </is>
-      </c>
-      <c r="E39" t="n">
-        <v>9500</v>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>p8wBsqZt</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>nwkTahLL</t>
-        </is>
-      </c>
-      <c r="H39" t="n">
-        <v>59</v>
-      </c>
-      <c r="I39" t="n">
-        <v>593</v>
-      </c>
-      <c r="J39" t="n">
-        <v>1</v>
-      </c>
-      <c r="K39" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L39" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>dfb pokal</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr"/>
-      <c r="O39" t="inlineStr">
-        <is>
-          <t>dfNCCCzS</t>
-        </is>
-      </c>
-      <c r="P39" t="inlineStr"/>
-      <c r="Q39" t="inlineStr"/>
-      <c r="R39" t="inlineStr"/>
-      <c r="S39" t="inlineStr"/>
-      <c r="T39" t="inlineStr"/>
-      <c r="U39" t="inlineStr"/>
-      <c r="V39" t="n">
-        <v>25.22</v>
-      </c>
-      <c r="W39" t="n">
-        <v>186.74</v>
-      </c>
-      <c r="X39" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="Y39" t="n">
-        <v>75.81</v>
-      </c>
-      <c r="Z39" t="n">
-        <v>10860000</v>
-      </c>
-      <c r="AA39" t="n">
-        <v>79.66</v>
-      </c>
-      <c r="AB39" t="inlineStr"/>
-      <c r="AC39" t="inlineStr"/>
-      <c r="AD39" t="inlineStr"/>
-      <c r="AE39" t="inlineStr"/>
-      <c r="AF39" t="inlineStr"/>
-      <c r="AG39" t="inlineStr"/>
-      <c r="AH39" t="n">
-        <v>24.49049516908213</v>
-      </c>
-      <c r="AI39" t="n">
-        <v>183.5287318840579</v>
-      </c>
-      <c r="AJ39" t="n">
-        <v>1.273164251207729</v>
-      </c>
-      <c r="AK39" t="n">
-        <v>73.89692028985507</v>
-      </c>
-      <c r="AL39" t="n">
-        <v>8517461.956521738</v>
-      </c>
-      <c r="AM39" t="n">
-        <v>78.55956521739131</v>
-      </c>
-      <c r="AN39" t="inlineStr"/>
-      <c r="AO39" t="inlineStr">
-        <is>
-          <t>vZA6VYpf</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="1" t="inlineStr">
-        <is>
-          <t>pAXo2Kvn</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="n">
-        <v>45523.65625</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t xml:space="preserve">zwayer f 
-  ger </t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t xml:space="preserve">eintracht stadion
-  braunschweig </t>
-        </is>
-      </c>
-      <c r="E40" t="n">
-        <v>23325</v>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>QqLCC3il</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>8vndvXTk</t>
-        </is>
-      </c>
-      <c r="H40" t="n">
-        <v>59</v>
-      </c>
-      <c r="I40" t="n">
-        <v>593</v>
-      </c>
-      <c r="J40" t="n">
-        <v>1</v>
-      </c>
-      <c r="K40" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L40" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>dfb pokal</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr">
-        <is>
-          <t>dfNCCCzS</t>
-        </is>
-      </c>
-      <c r="O40" t="inlineStr">
-        <is>
-          <t>EuakNmc1</t>
-        </is>
-      </c>
-      <c r="P40" t="n">
-        <v>25.41720779220779</v>
-      </c>
-      <c r="Q40" t="n">
-        <v>184.2175324675325</v>
-      </c>
-      <c r="R40" t="n">
-        <v>1.082792207792208</v>
-      </c>
-      <c r="S40" t="n">
-        <v>67.33279220779221</v>
-      </c>
-      <c r="T40" t="n">
-        <v>1406980.519480519</v>
-      </c>
-      <c r="U40" t="n">
-        <v>71.29383116883118</v>
-      </c>
-      <c r="V40" t="n">
-        <v>24.25222222222222</v>
-      </c>
-      <c r="W40" t="n">
-        <v>183.0955555555556</v>
-      </c>
-      <c r="X40" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="Y40" t="n">
-        <v>76.98111111111112</v>
-      </c>
-      <c r="Z40" t="n">
-        <v>15614611.11111111</v>
-      </c>
-      <c r="AA40" t="n">
-        <v>81.18111111111111</v>
-      </c>
-      <c r="AB40" t="n">
-        <v>26.05385487528344</v>
-      </c>
-      <c r="AC40" t="n">
-        <v>182.6663832199546</v>
-      </c>
-      <c r="AD40" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE40" t="n">
-        <v>66.68679138321995</v>
-      </c>
-      <c r="AF40" t="n">
-        <v>1263927.154195011</v>
-      </c>
-      <c r="AG40" t="n">
-        <v>70.07199546485261</v>
-      </c>
-      <c r="AH40" t="n">
-        <v>24.30286226930964</v>
-      </c>
-      <c r="AI40" t="n">
-        <v>183.7797641831852</v>
-      </c>
-      <c r="AJ40" t="n">
-        <v>1.421828434723172</v>
-      </c>
-      <c r="AK40" t="n">
-        <v>71.9276110731374</v>
-      </c>
-      <c r="AL40" t="n">
-        <v>5697609.791524266</v>
-      </c>
-      <c r="AM40" t="n">
-        <v>78.33495215311004</v>
-      </c>
-      <c r="AN40" t="inlineStr">
-        <is>
-          <t>txZLBQVC</t>
-        </is>
-      </c>
-      <c r="AO40" t="inlineStr">
-        <is>
-          <t>pfoInmcq</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="1" t="inlineStr">
-        <is>
-          <t>W67CmLPh</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="n">
-        <v>45531.65625</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">schlager d 
-  ger </t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">preussenstadion
-  munster </t>
-        </is>
-      </c>
-      <c r="E41" t="n">
-        <v>12794</v>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>zedZaSL7</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>nJQmYp1B</t>
-        </is>
-      </c>
-      <c r="H41" t="n">
-        <v>59</v>
-      </c>
-      <c r="I41" t="n">
-        <v>593</v>
-      </c>
-      <c r="J41" t="n">
-        <v>1</v>
-      </c>
-      <c r="K41" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L41" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>dfb pokal</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr"/>
-      <c r="O41" t="inlineStr">
-        <is>
-          <t>fiEQZ7C7</t>
-        </is>
-      </c>
-      <c r="P41" t="inlineStr"/>
-      <c r="Q41" t="inlineStr"/>
-      <c r="R41" t="inlineStr"/>
-      <c r="S41" t="inlineStr"/>
-      <c r="T41" t="inlineStr"/>
-      <c r="U41" t="inlineStr"/>
-      <c r="V41" t="n">
-        <v>24.40909090909091</v>
-      </c>
-      <c r="W41" t="n">
-        <v>184.6454545454546</v>
-      </c>
-      <c r="X41" t="n">
-        <v>1.490909090909091</v>
-      </c>
-      <c r="Y41" t="n">
-        <v>76</v>
-      </c>
-      <c r="Z41" t="n">
-        <v>11738181.81818181</v>
-      </c>
-      <c r="AA41" t="n">
-        <v>79.16363636363636</v>
-      </c>
-      <c r="AB41" t="n">
-        <v>25.57142857142857</v>
-      </c>
-      <c r="AC41" t="n">
-        <v>181.8571428571429</v>
-      </c>
-      <c r="AD41" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE41" t="n">
-        <v>66.71428571428571</v>
-      </c>
-      <c r="AF41" t="n">
-        <v>1175000</v>
-      </c>
-      <c r="AG41" t="n">
-        <v>68.42857142857143</v>
-      </c>
-      <c r="AH41" t="n">
-        <v>24.40472222222222</v>
-      </c>
-      <c r="AI41" t="n">
-        <v>182.5288888888889</v>
-      </c>
-      <c r="AJ41" t="n">
-        <v>1.280753968253968</v>
-      </c>
-      <c r="AK41" t="n">
-        <v>71.27392857142857</v>
-      </c>
-      <c r="AL41" t="n">
-        <v>5835730.158730159</v>
-      </c>
-      <c r="AM41" t="n">
-        <v>75.7297619047619</v>
-      </c>
-      <c r="AN41" t="inlineStr">
-        <is>
-          <t>8E86CPuD</t>
-        </is>
-      </c>
-      <c r="AO41" t="inlineStr">
-        <is>
-          <t>M5BRZDsC</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="1" t="inlineStr">
-        <is>
-          <t>fcxqFy2l</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="n">
-        <v>45521.64583333334</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">schlager d 
-  ger </t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t xml:space="preserve">bayarena
-  leverkusen </t>
-        </is>
-      </c>
-      <c r="E42" t="n">
-        <v>30210</v>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>4jcj2zMd</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>nJQmYp1B</t>
-        </is>
-      </c>
-      <c r="H42" t="n">
-        <v>59</v>
-      </c>
-      <c r="I42" t="n">
-        <v>594</v>
-      </c>
-      <c r="J42" t="n">
-        <v>1</v>
-      </c>
-      <c r="K42" t="n">
-        <v>2024</v>
-      </c>
-      <c r="L42" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>super cup</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr">
-        <is>
-          <t>WG9pOTse</t>
-        </is>
-      </c>
-      <c r="O42" t="inlineStr">
-        <is>
-          <t>fiEQZ7C7</t>
-        </is>
-      </c>
-      <c r="P42" t="n">
-        <v>25.63939393939394</v>
-      </c>
-      <c r="Q42" t="n">
-        <v>185.3989898989899</v>
-      </c>
-      <c r="R42" t="n">
-        <v>2.018181818181818</v>
-      </c>
-      <c r="S42" t="n">
-        <v>81.13333333333334</v>
-      </c>
-      <c r="T42" t="n">
-        <v>31332828.28282828</v>
-      </c>
-      <c r="U42" t="n">
-        <v>84.04242424242423</v>
-      </c>
-      <c r="V42" t="n">
-        <v>24.40909090909091</v>
-      </c>
-      <c r="W42" t="n">
-        <v>184.6454545454546</v>
-      </c>
-      <c r="X42" t="n">
-        <v>1.490909090909091</v>
-      </c>
-      <c r="Y42" t="n">
-        <v>76</v>
-      </c>
-      <c r="Z42" t="n">
-        <v>11738181.81818181</v>
-      </c>
-      <c r="AA42" t="n">
-        <v>79.16363636363636</v>
-      </c>
-      <c r="AB42" t="n">
-        <v>22.87297666102014</v>
-      </c>
-      <c r="AC42" t="n">
-        <v>181.3535983779067</v>
-      </c>
-      <c r="AD42" t="n">
-        <v>1.797712300874356</v>
-      </c>
-      <c r="AE42" t="n">
-        <v>78.8402785620177</v>
-      </c>
-      <c r="AF42" t="n">
-        <v>36662927.46778912</v>
-      </c>
-      <c r="AG42" t="n">
-        <v>84.46393237855688</v>
-      </c>
-      <c r="AH42" t="n">
-        <v>24.40472222222222</v>
-      </c>
-      <c r="AI42" t="n">
-        <v>182.5288888888889</v>
-      </c>
-      <c r="AJ42" t="n">
-        <v>1.280753968253968</v>
-      </c>
-      <c r="AK42" t="n">
-        <v>71.27392857142857</v>
-      </c>
-      <c r="AL42" t="n">
-        <v>5835730.158730159</v>
-      </c>
-      <c r="AM42" t="n">
-        <v>75.7297619047619</v>
-      </c>
-      <c r="AN42" t="inlineStr">
-        <is>
-          <t>2BYSk4KO</t>
-        </is>
-      </c>
-      <c r="AO42" t="inlineStr">
         <is>
           <t>M5BRZDsC</t>
         </is>

--- a/data/germany/p6_deployment/data_preparation/df_filled.xlsx
+++ b/data/germany/p6_deployment/data_preparation/df_filled.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO33"/>
+  <dimension ref="A1:AO41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -701,76 +701,76 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>25.19424242424243</v>
+        <v>25.14640151515152</v>
       </c>
       <c r="Q2" t="n">
-        <v>184.7147474747474</v>
+        <v>184.4703282828283</v>
       </c>
       <c r="R2" t="n">
-        <v>1.488282828282828</v>
+        <v>1.505176767676768</v>
       </c>
       <c r="S2" t="n">
-        <v>74.99838383838383</v>
+        <v>75.26426767676767</v>
       </c>
       <c r="T2" t="n">
-        <v>7986070.707070706</v>
+        <v>8405877.525252525</v>
       </c>
       <c r="U2" t="n">
-        <v>78.09373737373737</v>
+        <v>78.13080808080808</v>
       </c>
       <c r="V2" t="n">
-        <v>25.63939393939394</v>
+        <v>25.54680134680135</v>
       </c>
       <c r="W2" t="n">
-        <v>185.3989898989899</v>
+        <v>184.8402918069585</v>
       </c>
       <c r="X2" t="n">
-        <v>2.018181818181818</v>
+        <v>2.118181818181818</v>
       </c>
       <c r="Y2" t="n">
-        <v>81.13333333333334</v>
+        <v>81.5117845117845</v>
       </c>
       <c r="Z2" t="n">
-        <v>31332828.28282828</v>
+        <v>35277132.43546578</v>
       </c>
       <c r="AA2" t="n">
-        <v>84.04242424242423</v>
+        <v>84.32390572390571</v>
       </c>
       <c r="AB2" t="n">
-        <v>22.90164596273292</v>
+        <v>23.2467367467582</v>
       </c>
       <c r="AC2" t="n">
-        <v>183.8122360248447</v>
+        <v>184.2953589816934</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.30304347826087</v>
+        <v>1.289895594965675</v>
       </c>
       <c r="AE2" t="n">
-        <v>72.49769409937889</v>
+        <v>73.01056539105917</v>
       </c>
       <c r="AF2" t="n">
-        <v>6790663.043478261</v>
+        <v>6783616.939767897</v>
       </c>
       <c r="AG2" t="n">
-        <v>78.79253105590062</v>
+        <v>78.64013924076495</v>
       </c>
       <c r="AH2" t="n">
-        <v>22.87297666102014</v>
+        <v>23.08555340646302</v>
       </c>
       <c r="AI2" t="n">
-        <v>181.3535983779067</v>
+        <v>181.9279143387124</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1.797712300874356</v>
+        <v>1.665550583199324</v>
       </c>
       <c r="AK2" t="n">
-        <v>78.8402785620177</v>
+        <v>78.42933481045608</v>
       </c>
       <c r="AL2" t="n">
-        <v>36662927.46778912</v>
+        <v>31689830.46590455</v>
       </c>
       <c r="AM2" t="n">
-        <v>84.46393237855688</v>
+        <v>84.08272580193346</v>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
@@ -786,45 +786,45 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>pWQQJq6l</t>
+          <t>YZZcMwBs</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45520.54166666666</v>
+        <v>45528.4375</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">aytekin d 
+          <t xml:space="preserve">petersen m 
   ger </t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">leuna chemie stadion
-  halle </t>
+          <t xml:space="preserve">wwk arena
+  augsburg </t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>15057</v>
+        <v>30660</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>boX3cIQa</t>
+          <t>fTVNku3I</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>ILyJuN3g</t>
+          <t>Ig1f1fy3</t>
         </is>
       </c>
       <c r="H3" t="n">
         <v>59</v>
       </c>
       <c r="I3" t="n">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="J3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
         <v>20242025</v>
@@ -836,7 +836,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>dfb pokal</t>
+          <t>bundesliga</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -845,103 +845,131 @@
           <t>v9k3aY5F</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr"/>
-      <c r="R3" t="inlineStr"/>
-      <c r="S3" t="inlineStr"/>
-      <c r="T3" t="inlineStr"/>
-      <c r="U3" t="inlineStr"/>
+      <c r="P3" t="n">
+        <v>25.52222222222222</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>185.9227272727273</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.443118686868687</v>
+      </c>
+      <c r="S3" t="n">
+        <v>74.47638888888889</v>
+      </c>
+      <c r="T3" t="n">
+        <v>6594744.318181818</v>
+      </c>
+      <c r="U3" t="n">
+        <v>77.25101010101011</v>
+      </c>
       <c r="V3" t="n">
-        <v>25.83181818181818</v>
+        <v>26.03295454545454</v>
       </c>
       <c r="W3" t="n">
-        <v>185.1212121212121</v>
+        <v>183.7102272727273</v>
       </c>
       <c r="X3" t="n">
-        <v>1</v>
+        <v>1.160227272727273</v>
       </c>
       <c r="Y3" t="n">
-        <v>70.01363636363637</v>
+        <v>73.18181818181819</v>
       </c>
       <c r="Z3" t="n">
-        <v>2280151.515151515</v>
+        <v>4846988.636363637</v>
       </c>
       <c r="AA3" t="n">
-        <v>72.97727272727273</v>
-      </c>
-      <c r="AB3" t="inlineStr"/>
-      <c r="AC3" t="inlineStr"/>
-      <c r="AD3" t="inlineStr"/>
-      <c r="AE3" t="inlineStr"/>
-      <c r="AF3" t="inlineStr"/>
-      <c r="AG3" t="inlineStr"/>
+        <v>76.05568181818182</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>23.98748973522822</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>183.9524915508468</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>1.126060475525936</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>71.1172962591137</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>3842467.299581815</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>76.40783059685197</v>
+      </c>
       <c r="AH3" t="n">
-        <v>25.85441729323308</v>
+        <v>24.93740564613527</v>
       </c>
       <c r="AI3" t="n">
-        <v>185.9193609022556</v>
+        <v>184.4495257902456</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1</v>
+        <v>1.198887305446587</v>
       </c>
       <c r="AK3" t="n">
-        <v>66.75798872180451</v>
+        <v>68.50645238549272</v>
       </c>
       <c r="AL3" t="n">
-        <v>1303942.669172932</v>
+        <v>2554425.22463314</v>
       </c>
       <c r="AM3" t="n">
-        <v>71.29758771929825</v>
-      </c>
-      <c r="AN3" t="inlineStr"/>
+        <v>74.0719348189314</v>
+      </c>
+      <c r="AN3" t="inlineStr">
+        <is>
+          <t>hAcTWKKN</t>
+        </is>
+      </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>QHesBmSQ</t>
+          <t>xzRzG0VI</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hIsO3XFj</t>
+          <t>GbeXvnR8</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45520.54166666666</v>
+        <v>45528.4375</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">willenborg f 
+          <t xml:space="preserve">schlager d 
   ger </t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">brita arena
-  wiesbaden </t>
+          <t xml:space="preserve">europa park stadion
+  freiburg </t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>12566</v>
+        <v>34700</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>ObxFt3lm</t>
+          <t>fiEQZ7C7</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>EuakNmc1</t>
+          <t>nJQmYp1B</t>
         </is>
       </c>
       <c r="H4" t="n">
         <v>59</v>
       </c>
       <c r="I4" t="n">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="J4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
         <v>20242025</v>
@@ -953,144 +981,144 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>dfb pokal</t>
+          <t>bundesliga</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>EuakNmc1</t>
+          <t>nJQmYp1B</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>8vndvXTk</t>
+          <t>fiEQZ7C7</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>26.10227272727273</v>
+        <v>27.22727272727273</v>
       </c>
       <c r="Q4" t="n">
-        <v>185.875</v>
+        <v>183.7443181818182</v>
       </c>
       <c r="R4" t="n">
-        <v>1</v>
+        <v>1.693181818181818</v>
       </c>
       <c r="S4" t="n">
-        <v>67.18181818181819</v>
+        <v>75.44318181818181</v>
       </c>
       <c r="T4" t="n">
-        <v>1195738.636363636</v>
+        <v>8740340.909090908</v>
       </c>
       <c r="U4" t="n">
-        <v>69.51136363636363</v>
+        <v>77.26704545454545</v>
       </c>
       <c r="V4" t="n">
-        <v>25.64545454545454</v>
+        <v>24.42613636363636</v>
       </c>
       <c r="W4" t="n">
-        <v>183.1363636363637</v>
+        <v>184.5852272727273</v>
       </c>
       <c r="X4" t="n">
-        <v>1.572727272727272</v>
+        <v>1.545454545454545</v>
       </c>
       <c r="Y4" t="n">
-        <v>74.40909090909091</v>
+        <v>76.29545454545455</v>
       </c>
       <c r="Z4" t="n">
-        <v>6797272.727272728</v>
+        <v>12134090.90909091</v>
       </c>
       <c r="AA4" t="n">
-        <v>78.53636363636363</v>
+        <v>79.20454545454545</v>
       </c>
       <c r="AB4" t="n">
-        <v>24.38020833333334</v>
+        <v>24.97832386673205</v>
       </c>
       <c r="AC4" t="n">
-        <v>183.2413194444445</v>
+        <v>184.924112931786</v>
       </c>
       <c r="AD4" t="n">
-        <v>1</v>
+        <v>1.461491534542879</v>
       </c>
       <c r="AE4" t="n">
-        <v>64.93229166666666</v>
+        <v>73.40985071374088</v>
       </c>
       <c r="AF4" t="n">
-        <v>1005946.180555556</v>
+        <v>6250986.629276996</v>
       </c>
       <c r="AG4" t="n">
-        <v>69.11458333333334</v>
+        <v>76.747364079356</v>
       </c>
       <c r="AH4" t="n">
-        <v>26.37440476190476</v>
+        <v>24.19603174603175</v>
       </c>
       <c r="AI4" t="n">
-        <v>185.5630952380952</v>
+        <v>182.6951388888889</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1.522420634920635</v>
+        <v>1.257316468253968</v>
       </c>
       <c r="AK4" t="n">
-        <v>72.53829365079365</v>
+        <v>71.08415178571428</v>
       </c>
       <c r="AL4" t="n">
-        <v>4587232.142857144</v>
+        <v>5528934.771825397</v>
       </c>
       <c r="AM4" t="n">
-        <v>76.54583333333332</v>
+        <v>75.84040178571428</v>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>QTAUlvUP</t>
+          <t>v9WoiHGP</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>vZA6VYpf</t>
+          <t>M5BRZDsC</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>EF8gXauC</t>
+          <t>O48oHrZ1</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45520.54166666666</v>
+        <v>45528.4375</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">fritz m 
+          <t xml:space="preserve">sather a 
   ger </t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">flyeralarm arena
-  wurzburger </t>
+          <t xml:space="preserve">prezero arena
+  sinsheim </t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>13090</v>
+        <v>30150</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>nVM1YUFj</t>
+          <t>hQAtP9Sl</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>hQAtP9Sl</t>
+          <t>63WsD2ei</t>
         </is>
       </c>
       <c r="H5" t="n">
         <v>59</v>
       </c>
       <c r="I5" t="n">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="J5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
         <v>20242025</v>
@@ -1102,112 +1130,144 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>dfb pokal</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>nJQmYp1B</t>
+        </is>
+      </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>nJQmYp1B</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="inlineStr"/>
-      <c r="S5" t="inlineStr"/>
-      <c r="T5" t="inlineStr"/>
-      <c r="U5" t="inlineStr"/>
+          <t>ILyJuN3g</t>
+        </is>
+      </c>
+      <c r="P5" t="n">
+        <v>26.34090909090909</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>185.7272727272727</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.784090909090909</v>
+      </c>
+      <c r="S5" t="n">
+        <v>75</v>
+      </c>
+      <c r="T5" t="n">
+        <v>8702272.727272727</v>
+      </c>
+      <c r="U5" t="n">
+        <v>78.84090909090909</v>
+      </c>
       <c r="V5" t="n">
-        <v>26.76363636363636</v>
+        <v>25.13131313131313</v>
       </c>
       <c r="W5" t="n">
-        <v>185.5272727272727</v>
+        <v>186.2424242424242</v>
       </c>
       <c r="X5" t="n">
-        <v>1.818181818181818</v>
+        <v>1.080808080808081</v>
       </c>
       <c r="Y5" t="n">
-        <v>75.38181818181819</v>
+        <v>68.62626262626263</v>
       </c>
       <c r="Z5" t="n">
-        <v>8930000</v>
+        <v>1785353.535353536</v>
       </c>
       <c r="AA5" t="n">
-        <v>78.72727272727272</v>
-      </c>
-      <c r="AB5" t="inlineStr"/>
-      <c r="AC5" t="inlineStr"/>
-      <c r="AD5" t="inlineStr"/>
-      <c r="AE5" t="inlineStr"/>
-      <c r="AF5" t="inlineStr"/>
-      <c r="AG5" t="inlineStr"/>
+        <v>72.65656565656566</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>24.77839781746032</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>184.8694196428571</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>1.387896825396825</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>71.80059523809524</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>5367630.828373016</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>77.50471230158729</v>
+      </c>
       <c r="AH5" t="n">
-        <v>24.22996031746032</v>
+        <v>25.36275017253278</v>
       </c>
       <c r="AI5" t="n">
-        <v>185.4827380952381</v>
+        <v>186.0456253354804</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1.367063492063492</v>
+        <v>1.010121923165401</v>
       </c>
       <c r="AK5" t="n">
-        <v>71.57718253968254</v>
+        <v>66.5227359865041</v>
       </c>
       <c r="AL5" t="n">
-        <v>5224836.30952381</v>
+        <v>1346571.869488536</v>
       </c>
       <c r="AM5" t="n">
-        <v>77.88630952380952</v>
-      </c>
-      <c r="AN5" t="inlineStr"/>
+        <v>70.92639559849705</v>
+      </c>
+      <c r="AN5" t="inlineStr">
+        <is>
+          <t>KUx4Q7x1</t>
+        </is>
+      </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>CQTUFgPk</t>
+          <t>A15eUM4C</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>lONsG15D</t>
+          <t>2FREIeA6</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45520.65625</v>
+        <v>45528.4375</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">fritz m 
+          <t xml:space="preserve">dingert c 
   ger </t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">donaustadion
-  ulm </t>
+          <t xml:space="preserve">mewa arena
+  mainz </t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>19500</v>
+        <v>34000</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>tbC3EcQn</t>
+          <t>EuakNmc1</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>nVp0wiqd</t>
+          <t>pzHW4oaE</t>
         </is>
       </c>
       <c r="H6" t="n">
         <v>59</v>
       </c>
       <c r="I6" t="n">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="J6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
         <v>20242025</v>
@@ -1219,112 +1279,140 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>dfb pokal</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>8vndvXTk</t>
+        </is>
+      </c>
       <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr"/>
-      <c r="R6" t="inlineStr"/>
-      <c r="S6" t="inlineStr"/>
-      <c r="T6" t="inlineStr"/>
-      <c r="U6" t="inlineStr"/>
+      <c r="P6" t="n">
+        <v>25.8125</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>183.3579545454546</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.585227272727272</v>
+      </c>
+      <c r="S6" t="n">
+        <v>74.52840909090909</v>
+      </c>
+      <c r="T6" t="n">
+        <v>6878977.272727272</v>
+      </c>
+      <c r="U6" t="n">
+        <v>78.36931818181819</v>
+      </c>
       <c r="V6" t="n">
-        <v>27.20909090909091</v>
+        <v>26.89772727272727</v>
       </c>
       <c r="W6" t="n">
-        <v>184.9909090909091</v>
+        <v>185.0965909090909</v>
       </c>
       <c r="X6" t="n">
-        <v>2.963636363636364</v>
+        <v>1.613636363636363</v>
       </c>
       <c r="Y6" t="n">
-        <v>81.31818181818183</v>
+        <v>75.78977272727272</v>
       </c>
       <c r="Z6" t="n">
-        <v>35758636.36363636</v>
+        <v>8422727.272727273</v>
       </c>
       <c r="AA6" t="n">
-        <v>84.24545454545454</v>
-      </c>
-      <c r="AB6" t="inlineStr"/>
-      <c r="AC6" t="inlineStr"/>
-      <c r="AD6" t="inlineStr"/>
-      <c r="AE6" t="inlineStr"/>
-      <c r="AF6" t="inlineStr"/>
-      <c r="AG6" t="inlineStr"/>
+        <v>78.27272727272728</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>26.28112599206349</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>185.0338541666667</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1.500372023809524</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>72.57080853174602</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>4647160.218253968</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>76.64918154761905</v>
+      </c>
       <c r="AH6" t="n">
-        <v>24.26583850931677</v>
+        <v>27.01653022955941</v>
       </c>
       <c r="AI6" t="n">
-        <v>182.2987005144614</v>
+        <v>183.9304934097018</v>
       </c>
       <c r="AJ6" t="n">
-        <v>2.199501223414267</v>
+        <v>1.489012102266536</v>
       </c>
       <c r="AK6" t="n">
-        <v>77.93849559257168</v>
+        <v>74.01422061721333</v>
       </c>
       <c r="AL6" t="n">
-        <v>28680910.13982998</v>
+        <v>5425408.999173659</v>
       </c>
       <c r="AM6" t="n">
-        <v>83.33003089905263</v>
+        <v>76.14322774781157</v>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>QevvB2nf</t>
+          <t>f3ddUIXs</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>CQTUFgPk</t>
+          <t>l0fHXMdE</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>0K2qBFNG</t>
+          <t>dfO6OQtS</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45521.33333333334</v>
+        <v>45528.4375</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">schlager d 
+          <t xml:space="preserve">aytekin d 
   ger </t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">erzgebirgsstadion
-  aue </t>
+          <t xml:space="preserve">red bull arena
+  leipzig </t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>16485</v>
+        <v>47069</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>vsXIDreP</t>
+          <t>KbS1suSm</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>88HSzjDr</t>
+          <t>8Y2m6ADe</t>
         </is>
       </c>
       <c r="H7" t="n">
         <v>59</v>
       </c>
       <c r="I7" t="n">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="J7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
         <v>20242025</v>
@@ -1336,112 +1424,144 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>dfb pokal</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>nP1i5US1</t>
+        </is>
+      </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>WG9pOTse</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr"/>
-      <c r="R7" t="inlineStr"/>
-      <c r="S7" t="inlineStr"/>
-      <c r="T7" t="inlineStr"/>
-      <c r="U7" t="inlineStr"/>
+          <t>0Ija0Ej9</t>
+        </is>
+      </c>
+      <c r="P7" t="n">
+        <v>24.79431818181818</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>182.5704545454545</v>
+      </c>
+      <c r="R7" t="n">
+        <v>2.106818181818181</v>
+      </c>
+      <c r="S7" t="n">
+        <v>80.32386363636364</v>
+      </c>
+      <c r="T7" t="n">
+        <v>29215340.90909091</v>
+      </c>
+      <c r="U7" t="n">
+        <v>83.81704545454545</v>
+      </c>
       <c r="V7" t="n">
-        <v>25.19424242424243</v>
+        <v>27.92345679012346</v>
       </c>
       <c r="W7" t="n">
-        <v>184.7147474747474</v>
+        <v>182.6172839506173</v>
       </c>
       <c r="X7" t="n">
-        <v>1.488282828282828</v>
+        <v>1.267283950617284</v>
       </c>
       <c r="Y7" t="n">
-        <v>74.99838383838383</v>
+        <v>73.31481481481482</v>
       </c>
       <c r="Z7" t="n">
-        <v>7986070.707070706</v>
+        <v>3698101.851851852</v>
       </c>
       <c r="AA7" t="n">
-        <v>78.09373737373737</v>
-      </c>
-      <c r="AB7" t="inlineStr"/>
-      <c r="AC7" t="inlineStr"/>
-      <c r="AD7" t="inlineStr"/>
-      <c r="AE7" t="inlineStr"/>
-      <c r="AF7" t="inlineStr"/>
-      <c r="AG7" t="inlineStr"/>
+        <v>75.24074074074075</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>24.96960188060732</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>185.2257052277433</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1.703976880607316</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>76.8670257505176</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>17711602.29037267</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>81.45813384230505</v>
+      </c>
       <c r="AH7" t="n">
-        <v>22.90164596273292</v>
+        <v>27.05132275132275</v>
       </c>
       <c r="AI7" t="n">
-        <v>183.8122360248447</v>
+        <v>182.6198217051192</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1.30304347826087</v>
+        <v>1.061030696709568</v>
       </c>
       <c r="AK7" t="n">
-        <v>72.49769409937889</v>
+        <v>70.56604844713158</v>
       </c>
       <c r="AL7" t="n">
-        <v>6790663.043478261</v>
+        <v>2347542.340700236</v>
       </c>
       <c r="AM7" t="n">
-        <v>78.79253105590062</v>
-      </c>
-      <c r="AN7" t="inlineStr"/>
+        <v>73.22149377341026</v>
+      </c>
+      <c r="AN7" t="inlineStr">
+        <is>
+          <t>UgdQz0fK</t>
+        </is>
+      </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>M5BRZDsC</t>
+          <t>xzRzG0VI</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Kj4sifWp</t>
+          <t>SxFxJ44k</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45521.33333333334</v>
+        <v>45528.5625</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">hempel r 
+          <t xml:space="preserve">zwayer f 
   ger </t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">bruchwegstadion
-  mainz </t>
+          <t xml:space="preserve">signal iduna park
+  dortmund </t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>7134</v>
+        <v>81365</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>WzEYqEyg</t>
+          <t>nP1i5US1</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>CCQGbik8</t>
+          <t>8vndvXTk</t>
         </is>
       </c>
       <c r="H8" t="n">
         <v>59</v>
       </c>
       <c r="I8" t="n">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="J8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
         <v>20242025</v>
@@ -1453,112 +1573,144 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>dfb pokal</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>0Ija0Ej9</t>
+        </is>
+      </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>6FDqshzF</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="inlineStr"/>
-      <c r="R8" t="inlineStr"/>
-      <c r="S8" t="inlineStr"/>
-      <c r="T8" t="inlineStr"/>
-      <c r="U8" t="inlineStr"/>
+          <t>EuakNmc1</t>
+        </is>
+      </c>
+      <c r="P8" t="n">
+        <v>25.68181818181818</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>184.7159090909091</v>
+      </c>
+      <c r="R8" t="n">
+        <v>2.278409090909091</v>
+      </c>
+      <c r="S8" t="n">
+        <v>79.99431818181819</v>
+      </c>
+      <c r="T8" t="n">
+        <v>28714204.54545454</v>
+      </c>
+      <c r="U8" t="n">
+        <v>83.10227272727272</v>
+      </c>
       <c r="V8" t="n">
-        <v>24.03636363636363</v>
+        <v>24.12986111111111</v>
       </c>
       <c r="W8" t="n">
-        <v>183.0597402597403</v>
+        <v>183.3236111111111</v>
       </c>
       <c r="X8" t="n">
-        <v>1</v>
+        <v>1.685416666666667</v>
       </c>
       <c r="Y8" t="n">
-        <v>68.67402597402598</v>
+        <v>76.91875</v>
       </c>
       <c r="Z8" t="n">
-        <v>2157987.012987013</v>
+        <v>15628576.38888889</v>
       </c>
       <c r="AA8" t="n">
-        <v>74.4974025974026</v>
-      </c>
-      <c r="AB8" t="inlineStr"/>
-      <c r="AC8" t="inlineStr"/>
-      <c r="AD8" t="inlineStr"/>
-      <c r="AE8" t="inlineStr"/>
-      <c r="AF8" t="inlineStr"/>
-      <c r="AG8" t="inlineStr"/>
+        <v>81.29375</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>24.79724702380953</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>183.9562251984127</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1.990823412698413</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>77.51909722222223</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>19649553.57142857</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>82.24913194444443</v>
+      </c>
       <c r="AH8" t="n">
-        <v>22.55202535559679</v>
+        <v>24.54544700655381</v>
       </c>
       <c r="AI8" t="n">
-        <v>183.5796227581941</v>
+        <v>183.7037129086084</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1</v>
+        <v>1.428440565819629</v>
       </c>
       <c r="AK8" t="n">
-        <v>63.46678519892806</v>
+        <v>71.82038192071087</v>
       </c>
       <c r="AL8" t="n">
-        <v>1206222.299525871</v>
+        <v>5729574.593967372</v>
       </c>
       <c r="AM8" t="n">
-        <v>72.42241290455577</v>
-      </c>
-      <c r="AN8" t="inlineStr"/>
+        <v>78.21237818392908</v>
+      </c>
+      <c r="AN8" t="inlineStr">
+        <is>
+          <t>Q1njn0Vm</t>
+        </is>
+      </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>pdPRS0me</t>
+          <t>pfoInmcq</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>bF2q76Mr</t>
+          <t>t0w6KHuf</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45521.4375</v>
+        <v>45529.4375</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">stieler t 
+          <t xml:space="preserve">fritz m 
   ger </t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">ostalb arena
-  aalen </t>
+          <t xml:space="preserve">volkswagen arena
+  wolfsburg </t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>14500</v>
+        <v>28917</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Oh2C15j0</t>
+          <t>nwkTahLL</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0Ija0Ej9</t>
+          <t>nVp0wiqd</t>
         </is>
       </c>
       <c r="H9" t="n">
         <v>59</v>
       </c>
       <c r="I9" t="n">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="J9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
         <v>20242025</v>
@@ -1570,112 +1722,140 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>dfb pokal</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>nP1i5US1</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr"/>
-      <c r="Q9" t="inlineStr"/>
-      <c r="R9" t="inlineStr"/>
-      <c r="S9" t="inlineStr"/>
-      <c r="T9" t="inlineStr"/>
-      <c r="U9" t="inlineStr"/>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>dfNCCCzS</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="n">
+        <v>25.4125</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>186.625</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="S9" t="n">
+        <v>75.70625</v>
+      </c>
+      <c r="T9" t="n">
+        <v>10658125</v>
+      </c>
+      <c r="U9" t="n">
+        <v>79.51249999999999</v>
+      </c>
       <c r="V9" t="n">
-        <v>25.75</v>
+        <v>27.21022727272727</v>
       </c>
       <c r="W9" t="n">
-        <v>186.5178571428571</v>
+        <v>185.0056818181818</v>
       </c>
       <c r="X9" t="n">
-        <v>1</v>
+        <v>3.090909090909091</v>
       </c>
       <c r="Y9" t="n">
-        <v>68.88571428571429</v>
+        <v>82.08522727272727</v>
       </c>
       <c r="Z9" t="n">
-        <v>1755446.428571429</v>
+        <v>42884943.18181818</v>
       </c>
       <c r="AA9" t="n">
-        <v>73.44285714285715</v>
-      </c>
-      <c r="AB9" t="inlineStr"/>
-      <c r="AC9" t="inlineStr"/>
-      <c r="AD9" t="inlineStr"/>
-      <c r="AE9" t="inlineStr"/>
-      <c r="AF9" t="inlineStr"/>
-      <c r="AG9" t="inlineStr"/>
+        <v>84.61931818181819</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>24.2524532004831</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>183.4932291666667</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1.250286835748792</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>73.52358846618358</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>8283535.250603864</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>78.12027475845412</v>
+      </c>
       <c r="AH9" t="n">
-        <v>25.18543956043956</v>
+        <v>24.74041024209073</v>
       </c>
       <c r="AI9" t="n">
-        <v>185.6027167277167</v>
+        <v>182.3741943482718</v>
       </c>
       <c r="AJ9" t="n">
-        <v>1.015873015873016</v>
+        <v>2.206357280924643</v>
       </c>
       <c r="AK9" t="n">
-        <v>66.876221001221</v>
+        <v>78.49309692163132</v>
       </c>
       <c r="AL9" t="n">
-        <v>1400815.018315018</v>
+        <v>28402571.72873668</v>
       </c>
       <c r="AM9" t="n">
-        <v>72.19536019536019</v>
-      </c>
-      <c r="AN9" t="inlineStr"/>
+        <v>83.3859176515069</v>
+      </c>
+      <c r="AN9" t="inlineStr">
+        <is>
+          <t>f3ddUIXs</t>
+        </is>
+      </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>SQrxFAMl</t>
+          <t>CQTUFgPk</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>vyk5gjdE</t>
+          <t>AuVMGZvJ</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45521.4375</v>
+        <v>45529.52083333334</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">dingert c 
+          <t xml:space="preserve">welz t 
   ger </t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">volksstadion greifswald
-  greifswald </t>
+          <t xml:space="preserve">millerntor stadion
+  hamburg </t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4990</v>
+        <v>29546</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Q1yNyI5t</t>
+          <t>ILyJuN3g</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>pzHW4oaE</t>
+          <t>KWixEVWi</t>
         </is>
       </c>
       <c r="H10" t="n">
         <v>59</v>
       </c>
       <c r="I10" t="n">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="J10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
         <v>20242025</v>
@@ -1687,98 +1867,130 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>dfb pokal</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>v9k3aY5F</t>
+        </is>
+      </c>
       <c r="O10" t="inlineStr"/>
-      <c r="P10" t="inlineStr"/>
-      <c r="Q10" t="inlineStr"/>
-      <c r="R10" t="inlineStr"/>
-      <c r="S10" t="inlineStr"/>
-      <c r="T10" t="inlineStr"/>
-      <c r="U10" t="inlineStr"/>
+      <c r="P10" t="n">
+        <v>25.8989898989899</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>185.0434343434343</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1</v>
+      </c>
+      <c r="S10" t="n">
+        <v>70</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2280606.060606061</v>
+      </c>
+      <c r="U10" t="n">
+        <v>72.98484848484848</v>
+      </c>
       <c r="V10" t="n">
-        <v>26.90909090909091</v>
+        <v>25.91477272727272</v>
       </c>
       <c r="W10" t="n">
-        <v>184.6090909090909</v>
+        <v>186.6818181818182</v>
       </c>
       <c r="X10" t="n">
-        <v>1.6</v>
+        <v>1</v>
       </c>
       <c r="Y10" t="n">
-        <v>75.7909090909091</v>
+        <v>72.89204545454545</v>
       </c>
       <c r="Z10" t="n">
-        <v>8480000</v>
+        <v>4421732.954545454</v>
       </c>
       <c r="AA10" t="n">
-        <v>78.2</v>
-      </c>
-      <c r="AB10" t="inlineStr"/>
-      <c r="AC10" t="inlineStr"/>
-      <c r="AD10" t="inlineStr"/>
-      <c r="AE10" t="inlineStr"/>
-      <c r="AF10" t="inlineStr"/>
-      <c r="AG10" t="inlineStr"/>
+        <v>75.20454545454544</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>25.97834168755221</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>185.9898913951546</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>66.54699248120301</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>1228074.874686717</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>71.10315371762741</v>
+      </c>
       <c r="AH10" t="n">
-        <v>27.1820039228506</v>
+        <v>27.07239906832298</v>
       </c>
       <c r="AI10" t="n">
-        <v>184.5026783444118</v>
+        <v>182.9631372929607</v>
       </c>
       <c r="AJ10" t="n">
-        <v>1.500474919182013</v>
+        <v>1</v>
       </c>
       <c r="AK10" t="n">
-        <v>73.97275298754133</v>
+        <v>69.32400038819875</v>
       </c>
       <c r="AL10" t="n">
-        <v>5185029.398677854</v>
+        <v>1934037.078373016</v>
       </c>
       <c r="AM10" t="n">
-        <v>76.06249772983183</v>
-      </c>
-      <c r="AN10" t="inlineStr"/>
+        <v>70.98749676501035</v>
+      </c>
+      <c r="AN10" t="inlineStr">
+        <is>
+          <t>QTAUlvUP</t>
+        </is>
+      </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>l0fHXMdE</t>
+          <t>lGJdeemM</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>tbKZHNz1</t>
+          <t>pWQQJq6l</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>45521.4375</v>
+        <v>45520.54166666666</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve">schroder r 
+          <t xml:space="preserve">aytekin d 
   ger </t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">audi sportpark
-  ingolstadt </t>
+          <t xml:space="preserve">leuna chemie stadion
+  halle </t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>15800</v>
+        <v>15057</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>ne5QkLtB</t>
+          <t>boX3cIQa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>naWckLmC</t>
+          <t>ILyJuN3g</t>
         </is>
       </c>
       <c r="H11" t="n">
@@ -1804,7 +2016,11 @@
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr"/>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>v9k3aY5F</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr"/>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr"/>
@@ -1812,22 +2028,22 @@
       <c r="T11" t="inlineStr"/>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>25.39886363636364</v>
+        <v>25.8989898989899</v>
       </c>
       <c r="W11" t="n">
-        <v>183.6647727272727</v>
+        <v>185.0434343434343</v>
       </c>
       <c r="X11" t="n">
         <v>1</v>
       </c>
       <c r="Y11" t="n">
-        <v>68.24431818181819</v>
+        <v>70</v>
       </c>
       <c r="Z11" t="n">
-        <v>1643323.863636364</v>
+        <v>2280606.060606061</v>
       </c>
       <c r="AA11" t="n">
-        <v>71.28181818181818</v>
+        <v>72.98484848484848</v>
       </c>
       <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="inlineStr"/>
@@ -1836,62 +2052,62 @@
       <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="inlineStr"/>
       <c r="AH11" t="n">
-        <v>26.36618725874304</v>
+        <v>25.97834168755221</v>
       </c>
       <c r="AI11" t="n">
-        <v>181.0833405565957</v>
+        <v>185.9898913951546</v>
       </c>
       <c r="AJ11" t="n">
         <v>1</v>
       </c>
       <c r="AK11" t="n">
-        <v>67.65210565321406</v>
+        <v>66.54699248120301</v>
       </c>
       <c r="AL11" t="n">
-        <v>1409553.920208955</v>
+        <v>1228074.874686717</v>
       </c>
       <c r="AM11" t="n">
-        <v>70.42419222256893</v>
+        <v>71.10315371762741</v>
       </c>
       <c r="AN11" t="inlineStr"/>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>4bJLk19p</t>
+          <t>QHesBmSQ</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>MZjh9ghT</t>
+          <t>hIsO3XFj</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>45521.4375</v>
+        <v>45520.54166666666</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t xml:space="preserve">zwayer f 
+          <t xml:space="preserve">willenborg f 
   ger </t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadion an der hafenstrasse
-  essen </t>
+          <t xml:space="preserve">brita arena
+  wiesbaden </t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>20352</v>
+        <v>12566</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>EB0xsr77</t>
+          <t>ObxFt3lm</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>KbS1suSm</t>
+          <t>EuakNmc1</t>
         </is>
       </c>
       <c r="H12" t="n">
@@ -1916,99 +2132,131 @@
           <t>dfb pokal</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr"/>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>EuakNmc1</t>
+        </is>
+      </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>nP1i5US1</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr"/>
-      <c r="Q12" t="inlineStr"/>
-      <c r="R12" t="inlineStr"/>
-      <c r="S12" t="inlineStr"/>
-      <c r="T12" t="inlineStr"/>
-      <c r="U12" t="inlineStr"/>
+          <t>8vndvXTk</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>26.11570247933884</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>185.7768595041322</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1</v>
+      </c>
+      <c r="S12" t="n">
+        <v>67.20661157024793</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1199793.388429752</v>
+      </c>
+      <c r="U12" t="n">
+        <v>69.57851239669421</v>
+      </c>
       <c r="V12" t="n">
-        <v>24.65090909090909</v>
+        <v>25.8125</v>
       </c>
       <c r="W12" t="n">
-        <v>182.9127272727273</v>
+        <v>183.3579545454546</v>
       </c>
       <c r="X12" t="n">
-        <v>2.070909090909091</v>
+        <v>1.585227272727272</v>
       </c>
       <c r="Y12" t="n">
-        <v>80.25818181818182</v>
+        <v>74.52840909090909</v>
       </c>
       <c r="Z12" t="n">
-        <v>29164545.45454546</v>
+        <v>6878977.272727272</v>
       </c>
       <c r="AA12" t="n">
-        <v>83.88727272727273</v>
-      </c>
-      <c r="AB12" t="inlineStr"/>
-      <c r="AC12" t="inlineStr"/>
-      <c r="AD12" t="inlineStr"/>
-      <c r="AE12" t="inlineStr"/>
-      <c r="AF12" t="inlineStr"/>
-      <c r="AG12" t="inlineStr"/>
+        <v>78.36931818181819</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>24.45833333333334</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>183.7209595959596</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>64.91035353535354</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>997506.3131313131</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>69.00252525252526</v>
+      </c>
       <c r="AH12" t="n">
-        <v>25.05359730848862</v>
+        <v>26.28112599206349</v>
       </c>
       <c r="AI12" t="n">
-        <v>184.9349206349206</v>
+        <v>185.0338541666667</v>
       </c>
       <c r="AJ12" t="n">
-        <v>1.724672187715666</v>
+        <v>1.500372023809524</v>
       </c>
       <c r="AK12" t="n">
-        <v>76.71725327812285</v>
+        <v>72.57080853174602</v>
       </c>
       <c r="AL12" t="n">
-        <v>17387078.1573499</v>
+        <v>4647160.218253968</v>
       </c>
       <c r="AM12" t="n">
-        <v>81.29726535541754</v>
-      </c>
-      <c r="AN12" t="inlineStr"/>
+        <v>76.64918154761905</v>
+      </c>
+      <c r="AN12" t="inlineStr">
+        <is>
+          <t>QTAUlvUP</t>
+        </is>
+      </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>pfoInmcq</t>
+          <t>vZA6VYpf</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>f1nnRRDE</t>
+          <t>EF8gXauC</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>45521.4375</v>
+        <v>45520.54166666666</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t xml:space="preserve">dingert c 
+          <t xml:space="preserve">fritz m 
   ger </t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadion an der bremer bruck
-  osnabruck </t>
+          <t xml:space="preserve">flyeralarm arena
+  wurzburger </t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>16667</v>
+        <v>13090</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>88Xgj1Y5</t>
+          <t>nVM1YUFj</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>fiEQZ7C7</t>
+          <t>hQAtP9Sl</t>
         </is>
       </c>
       <c r="H13" t="n">
@@ -2039,121 +2287,93 @@
           <t>nJQmYp1B</t>
         </is>
       </c>
-      <c r="P13" t="n">
-        <v>25.64848484848485</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>183.1606060606061</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1</v>
-      </c>
-      <c r="S13" t="n">
-        <v>67.04545454545455</v>
-      </c>
-      <c r="T13" t="n">
-        <v>1385075.757575758</v>
-      </c>
-      <c r="U13" t="n">
-        <v>70.99242424242424</v>
-      </c>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr"/>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>27.4</v>
+        <v>26.34090909090909</v>
       </c>
       <c r="W13" t="n">
-        <v>183.3909090909091</v>
+        <v>185.7272727272727</v>
       </c>
       <c r="X13" t="n">
-        <v>1.709090909090909</v>
+        <v>1.784090909090909</v>
       </c>
       <c r="Y13" t="n">
-        <v>75.58181818181818</v>
+        <v>75</v>
       </c>
       <c r="Z13" t="n">
-        <v>9104545.454545453</v>
+        <v>8702272.727272727</v>
       </c>
       <c r="AA13" t="n">
-        <v>77.26363636363635</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>25.70271164021164</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>184.5059523809524</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>66.62632275132275</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>1261367.394179894</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>69.8366402116402</v>
-      </c>
+        <v>78.84090909090909</v>
+      </c>
+      <c r="AB13" t="inlineStr"/>
+      <c r="AC13" t="inlineStr"/>
+      <c r="AD13" t="inlineStr"/>
+      <c r="AE13" t="inlineStr"/>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="inlineStr"/>
       <c r="AH13" t="n">
-        <v>24.61444862155389</v>
+        <v>24.77839781746032</v>
       </c>
       <c r="AI13" t="n">
-        <v>184.9235651629072</v>
+        <v>184.8694196428571</v>
       </c>
       <c r="AJ13" t="n">
-        <v>1.411942355889725</v>
+        <v>1.387896825396825</v>
       </c>
       <c r="AK13" t="n">
-        <v>72.99003132832081</v>
+        <v>71.80059523809524</v>
       </c>
       <c r="AL13" t="n">
-        <v>5321504.072681705</v>
+        <v>5367630.828373016</v>
       </c>
       <c r="AM13" t="n">
-        <v>76.56177631578949</v>
-      </c>
-      <c r="AN13" t="inlineStr">
-        <is>
-          <t>lxrr7DgN</t>
-        </is>
-      </c>
+        <v>77.50471230158729</v>
+      </c>
+      <c r="AN13" t="inlineStr"/>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>l0fHXMdE</t>
+          <t>CQTUFgPk</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>8QPARz8c</t>
+          <t>lONsG15D</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>45521.4375</v>
+        <v>45520.65625</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t xml:space="preserve">welz t 
+          <t xml:space="preserve">fritz m 
   ger </t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">ms technologie arena
-  villingen schwenningen </t>
+          <t xml:space="preserve">donaustadion
+  ulm </t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>8000</v>
+        <v>19500</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>lKLJUxeT</t>
+          <t>tbC3EcQn</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>KWixEVWi</t>
+          <t>nVp0wiqd</t>
         </is>
       </c>
       <c r="H14" t="n">
@@ -2187,86 +2407,102 @@
       <c r="T14" t="inlineStr"/>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>25.62727272727273</v>
+        <v>27.21022727272727</v>
       </c>
       <c r="W14" t="n">
-        <v>186.5272727272727</v>
+        <v>185.0056818181818</v>
       </c>
       <c r="X14" t="n">
-        <v>1</v>
+        <v>3.090909090909091</v>
       </c>
       <c r="Y14" t="n">
-        <v>72.90000000000001</v>
+        <v>82.08522727272727</v>
       </c>
       <c r="Z14" t="n">
-        <v>4462954.545454545</v>
+        <v>42884943.18181818</v>
       </c>
       <c r="AA14" t="n">
-        <v>75.34545454545454</v>
-      </c>
-      <c r="AB14" t="inlineStr"/>
-      <c r="AC14" t="inlineStr"/>
-      <c r="AD14" t="inlineStr"/>
-      <c r="AE14" t="inlineStr"/>
-      <c r="AF14" t="inlineStr"/>
-      <c r="AG14" t="inlineStr"/>
+        <v>84.61931818181819</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>183</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>62</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>887500</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>70.5</v>
+      </c>
       <c r="AH14" t="n">
-        <v>27.39107142857143</v>
+        <v>24.74041024209073</v>
       </c>
       <c r="AI14" t="n">
-        <v>183.0269841269841</v>
+        <v>182.3741943482718</v>
       </c>
       <c r="AJ14" t="n">
-        <v>1</v>
+        <v>2.206357280924643</v>
       </c>
       <c r="AK14" t="n">
-        <v>69.03234126984127</v>
+        <v>78.49309692163132</v>
       </c>
       <c r="AL14" t="n">
-        <v>1845550.595238096</v>
+        <v>28402571.72873668</v>
       </c>
       <c r="AM14" t="n">
-        <v>70.72083333333333</v>
-      </c>
-      <c r="AN14" t="inlineStr"/>
+        <v>83.3859176515069</v>
+      </c>
+      <c r="AN14" t="inlineStr">
+        <is>
+          <t>zyLSrbZQ</t>
+        </is>
+      </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>lGJdeemM</t>
+          <t>CQTUFgPk</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>hzyf0b9b</t>
+          <t>0K2qBFNG</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>45521.54166666666</v>
+        <v>45521.33333333334</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t xml:space="preserve">sather a 
+          <t xml:space="preserve">schlager d 
   ger </t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">new tivoli
-  aachen </t>
+          <t xml:space="preserve">erzgebirgsstadion
+  aue </t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>31026</v>
+        <v>16485</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>j3PKcB4E</t>
+          <t>vsXIDreP</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>63WsD2ei</t>
+          <t>88HSzjDr</t>
         </is>
       </c>
       <c r="H15" t="n">
@@ -2294,7 +2530,7 @@
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr">
         <is>
-          <t>ILyJuN3g</t>
+          <t>WG9pOTse</t>
         </is>
       </c>
       <c r="P15" t="inlineStr"/>
@@ -2304,22 +2540,22 @@
       <c r="T15" t="inlineStr"/>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>25.25757575757576</v>
+        <v>25.14640151515152</v>
       </c>
       <c r="W15" t="n">
-        <v>186.5454545454545</v>
+        <v>184.4703282828283</v>
       </c>
       <c r="X15" t="n">
-        <v>1.075757575757576</v>
+        <v>1.505176767676768</v>
       </c>
       <c r="Y15" t="n">
-        <v>68.48484848484848</v>
+        <v>75.26426767676767</v>
       </c>
       <c r="Z15" t="n">
-        <v>1749242.424242425</v>
+        <v>8405877.525252525</v>
       </c>
       <c r="AA15" t="n">
-        <v>72.46969696969698</v>
+        <v>78.13080808080808</v>
       </c>
       <c r="AB15" t="inlineStr"/>
       <c r="AC15" t="inlineStr"/>
@@ -2328,62 +2564,62 @@
       <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="inlineStr"/>
       <c r="AH15" t="n">
-        <v>25.07421785139177</v>
+        <v>23.2467367467582</v>
       </c>
       <c r="AI15" t="n">
-        <v>185.8624194847021</v>
+        <v>184.2953589816934</v>
       </c>
       <c r="AJ15" t="n">
-        <v>1.015182884748102</v>
+        <v>1.289895594965675</v>
       </c>
       <c r="AK15" t="n">
-        <v>66.6799373130895</v>
+        <v>73.01056539105917</v>
       </c>
       <c r="AL15" t="n">
-        <v>1411003.637566138</v>
+        <v>6783616.939767897</v>
       </c>
       <c r="AM15" t="n">
-        <v>71.2854267310789</v>
+        <v>78.64013924076495</v>
       </c>
       <c r="AN15" t="inlineStr"/>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>A15eUM4C</t>
+          <t>M5BRZDsC</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>CpiTEcOi</t>
+          <t>Kj4sifWp</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>45521.54166666666</v>
+        <v>45521.33333333334</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t xml:space="preserve">bacher m 
+          <t xml:space="preserve">lechner f 
   ger </t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">schuco arena
-  bielefeld </t>
+          <t xml:space="preserve">bruchwegstadion
+  mainz </t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>27332</v>
+        <v>7134</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>pp38UXK8</t>
+          <t>WzEYqEyg</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>dfNCCCzS</t>
+          <t>CCQGbik8</t>
         </is>
       </c>
       <c r="H16" t="n">
@@ -2411,7 +2647,7 @@
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr">
         <is>
-          <t>QqLCC3il</t>
+          <t>6FDqshzF</t>
         </is>
       </c>
       <c r="P16" t="inlineStr"/>
@@ -2421,22 +2657,22 @@
       <c r="T16" t="inlineStr"/>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>25.69350649350649</v>
+        <v>24.11157024793388</v>
       </c>
       <c r="W16" t="n">
-        <v>183.7831168831169</v>
+        <v>183.0305785123967</v>
       </c>
       <c r="X16" t="n">
-        <v>1.184415584415585</v>
+        <v>1</v>
       </c>
       <c r="Y16" t="n">
-        <v>69.68051948051948</v>
+        <v>68.71404958677687</v>
       </c>
       <c r="Z16" t="n">
-        <v>2022500</v>
+        <v>2150371.900826446</v>
       </c>
       <c r="AA16" t="n">
-        <v>73.85194805194806</v>
+        <v>74.48595041322314</v>
       </c>
       <c r="AB16" t="inlineStr"/>
       <c r="AC16" t="inlineStr"/>
@@ -2445,62 +2681,62 @@
       <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="inlineStr"/>
       <c r="AH16" t="n">
-        <v>24.29795403009689</v>
+        <v>22.60232192050374</v>
       </c>
       <c r="AI16" t="n">
-        <v>183.7678829107401</v>
+        <v>183.6703233635052</v>
       </c>
       <c r="AJ16" t="n">
         <v>1</v>
       </c>
       <c r="AK16" t="n">
-        <v>66.42261904761905</v>
+        <v>63.41615833661288</v>
       </c>
       <c r="AL16" t="n">
-        <v>1384835.600907029</v>
+        <v>1156622.638724911</v>
       </c>
       <c r="AM16" t="n">
-        <v>71.45305091733663</v>
+        <v>72.08353010625738</v>
       </c>
       <c r="AN16" t="inlineStr"/>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>zyLSrbZQ</t>
+          <t>8E86CPuD</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>8CpxDyg4</t>
+          <t>bF2q76Mr</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>45521.54166666666</v>
+        <v>45521.4375</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t xml:space="preserve">siebert d 
+          <t xml:space="preserve">winter n 
   ger </t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadion lohmuhle
-  lubeck </t>
+          <t xml:space="preserve">ostalb arena
+  aalen </t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>17849</v>
+        <v>14500</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>I1Vk6k3R</t>
+          <t>Oh2C15j0</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>nP1i5US1</t>
+          <t>0Ija0Ej9</t>
         </is>
       </c>
       <c r="H17" t="n">
@@ -2528,7 +2764,7 @@
       <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr">
         <is>
-          <t>0Ija0Ej9</t>
+          <t>nP1i5US1</t>
         </is>
       </c>
       <c r="P17" t="inlineStr"/>
@@ -2538,22 +2774,22 @@
       <c r="T17" t="inlineStr"/>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>25.14545454545455</v>
+        <v>26.00681818181818</v>
       </c>
       <c r="W17" t="n">
-        <v>184.7454545454545</v>
+        <v>186.7340909090909</v>
       </c>
       <c r="X17" t="n">
-        <v>2.245454545454546</v>
+        <v>1</v>
       </c>
       <c r="Y17" t="n">
-        <v>79.55454545454546</v>
+        <v>68.95681818181818</v>
       </c>
       <c r="Z17" t="n">
-        <v>28540909.09090909</v>
+        <v>1737386.363636364</v>
       </c>
       <c r="AA17" t="n">
-        <v>83.10909090909091</v>
+        <v>73.26363636363637</v>
       </c>
       <c r="AB17" t="inlineStr"/>
       <c r="AC17" t="inlineStr"/>
@@ -2562,62 +2798,62 @@
       <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="inlineStr"/>
       <c r="AH17" t="n">
-        <v>25.06309523809524</v>
+        <v>25.27980352980353</v>
       </c>
       <c r="AI17" t="n">
-        <v>183.609126984127</v>
+        <v>185.8285325785326</v>
       </c>
       <c r="AJ17" t="n">
-        <v>2.011706349206349</v>
+        <v>1.042929292929293</v>
       </c>
       <c r="AK17" t="n">
-        <v>77.71388888888889</v>
+        <v>67.04136141636141</v>
       </c>
       <c r="AL17" t="n">
-        <v>20714563.49206349</v>
+        <v>1389321.858696859</v>
       </c>
       <c r="AM17" t="n">
-        <v>82.11527777777778</v>
+        <v>72.32020757020756</v>
       </c>
       <c r="AN17" t="inlineStr"/>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>MDhPV0RQ</t>
+          <t>txZLBQVC</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>6q2yrHgU</t>
+          <t>vyk5gjdE</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
-        <v>45522.33333333334</v>
+        <v>45521.4375</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t xml:space="preserve">braun r 
+          <t xml:space="preserve">dingert c 
   ger </t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">ludwigspark stadion
-  saarbrucken </t>
+          <t xml:space="preserve">volksstadion greifswald
+  greifswald </t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>16003</v>
+        <v>4990</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>fLbhmJ5l</t>
+          <t>Q1yNyI5t</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>6FDqshzF</t>
+          <t>pzHW4oaE</t>
         </is>
       </c>
       <c r="H18" t="n">
@@ -2643,11 +2879,7 @@
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>CCQGbik8</t>
-        </is>
-      </c>
+      <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr"/>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr"/>
@@ -2655,22 +2887,22 @@
       <c r="T18" t="inlineStr"/>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>23.44877344877344</v>
+        <v>26.89772727272727</v>
       </c>
       <c r="W18" t="n">
-        <v>183.3506493506493</v>
+        <v>185.0965909090909</v>
       </c>
       <c r="X18" t="n">
-        <v>1.015873015873016</v>
+        <v>1.613636363636363</v>
       </c>
       <c r="Y18" t="n">
-        <v>66.96103896103897</v>
+        <v>75.78977272727272</v>
       </c>
       <c r="Z18" t="n">
-        <v>1622655.122655123</v>
+        <v>8422727.272727273</v>
       </c>
       <c r="AA18" t="n">
-        <v>72.92352092352093</v>
+        <v>78.27272727272728</v>
       </c>
       <c r="AB18" t="inlineStr"/>
       <c r="AC18" t="inlineStr"/>
@@ -2679,62 +2911,62 @@
       <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="inlineStr"/>
       <c r="AH18" t="n">
-        <v>27.19029581529582</v>
+        <v>27.01653022955941</v>
       </c>
       <c r="AI18" t="n">
-        <v>182.2007575757576</v>
+        <v>183.9304934097018</v>
       </c>
       <c r="AJ18" t="n">
-        <v>1.015873015873016</v>
+        <v>1.489012102266536</v>
       </c>
       <c r="AK18" t="n">
-        <v>67.24098124098124</v>
+        <v>74.01422061721333</v>
       </c>
       <c r="AL18" t="n">
-        <v>1184510.281385281</v>
+        <v>5425408.999173659</v>
       </c>
       <c r="AM18" t="n">
-        <v>69.51893939393939</v>
+        <v>76.14322774781157</v>
       </c>
       <c r="AN18" t="inlineStr"/>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>tO31cZrF</t>
+          <t>l0fHXMdE</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>AiJ3kset</t>
+          <t>tbKZHNz1</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
-        <v>45522.33333333334</v>
+        <v>45521.4375</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t xml:space="preserve">jollenbeck m 
+          <t xml:space="preserve">lechner f 
   ger </t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve">friedrich ludwig jahn sportpark
-  berlin </t>
+          <t xml:space="preserve">audi sportpark
+  ingolstadt </t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>19708</v>
+        <v>15800</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>UNr2EUfd</t>
+          <t>ne5QkLtB</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>fTVNku3I</t>
+          <t>naWckLmC</t>
         </is>
       </c>
       <c r="H19" t="n">
@@ -2768,22 +3000,22 @@
       <c r="T19" t="inlineStr"/>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>25.41333333333333</v>
+        <v>25.42027972027972</v>
       </c>
       <c r="W19" t="n">
-        <v>186.0030303030303</v>
+        <v>183.9895104895105</v>
       </c>
       <c r="X19" t="n">
-        <v>1.462323232323232</v>
+        <v>1</v>
       </c>
       <c r="Y19" t="n">
-        <v>74.33111111111111</v>
+        <v>68.18531468531469</v>
       </c>
       <c r="Z19" t="n">
-        <v>6657146.464646464</v>
+        <v>1616241.258741259</v>
       </c>
       <c r="AA19" t="n">
-        <v>77.32606060606061</v>
+        <v>71.23636363636363</v>
       </c>
       <c r="AB19" t="inlineStr"/>
       <c r="AC19" t="inlineStr"/>
@@ -2792,62 +3024,62 @@
       <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="inlineStr"/>
       <c r="AH19" t="n">
-        <v>23.899139420521</v>
+        <v>26.09921478366088</v>
       </c>
       <c r="AI19" t="n">
-        <v>184.2982721956406</v>
+        <v>181.5682548221585</v>
       </c>
       <c r="AJ19" t="n">
-        <v>1.139229228373965</v>
+        <v>1</v>
       </c>
       <c r="AK19" t="n">
-        <v>71.05004414445204</v>
+        <v>67.5308206734711</v>
       </c>
       <c r="AL19" t="n">
-        <v>3913032.094915318</v>
+        <v>1441450.602481529</v>
       </c>
       <c r="AM19" t="n">
-        <v>76.51723674717095</v>
+        <v>70.53366580212388</v>
       </c>
       <c r="AN19" t="inlineStr"/>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>2VSFgl3c</t>
+          <t>8E86CPuD</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>YV3TqwPH</t>
+          <t>MZjh9ghT</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
-        <v>45522.4375</v>
+        <v>45521.4375</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t xml:space="preserve">haslberger w 
+          <t xml:space="preserve">zwayer f 
   ger </t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadion am panzenberg
-  bremen </t>
+          <t xml:space="preserve">stadion an der hafenstrasse
+  essen </t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5000</v>
+        <v>20352</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>tW75B1ei</t>
+          <t>EB0xsr77</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>G2Op923t</t>
+          <t>KbS1suSm</t>
         </is>
       </c>
       <c r="H20" t="n">
@@ -2873,7 +3105,11 @@
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
-      <c r="O20" t="inlineStr"/>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>nP1i5US1</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr"/>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr"/>
@@ -2881,22 +3117,22 @@
       <c r="T20" t="inlineStr"/>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="n">
-        <v>24.10616883116883</v>
+        <v>24.79431818181818</v>
       </c>
       <c r="W20" t="n">
-        <v>185.4892857142857</v>
+        <v>182.5704545454545</v>
       </c>
       <c r="X20" t="n">
-        <v>1</v>
+        <v>2.106818181818181</v>
       </c>
       <c r="Y20" t="n">
-        <v>66.52467532467533</v>
+        <v>80.32386363636364</v>
       </c>
       <c r="Z20" t="n">
-        <v>1420081.168831169</v>
+        <v>29215340.90909091</v>
       </c>
       <c r="AA20" t="n">
-        <v>72.47792207792207</v>
+        <v>83.81704545454545</v>
       </c>
       <c r="AB20" t="inlineStr"/>
       <c r="AC20" t="inlineStr"/>
@@ -2905,62 +3141,62 @@
       <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="inlineStr"/>
       <c r="AH20" t="n">
-        <v>25.24755485198031</v>
+        <v>24.96960188060732</v>
       </c>
       <c r="AI20" t="n">
-        <v>186.3757108574655</v>
+        <v>185.2257052277433</v>
       </c>
       <c r="AJ20" t="n">
-        <v>1</v>
+        <v>1.703976880607316</v>
       </c>
       <c r="AK20" t="n">
-        <v>67.15276377349359</v>
+        <v>76.8670257505176</v>
       </c>
       <c r="AL20" t="n">
-        <v>1396154.689642655</v>
+        <v>17711602.29037267</v>
       </c>
       <c r="AM20" t="n">
-        <v>71.317123094297</v>
+        <v>81.45813384230505</v>
       </c>
       <c r="AN20" t="inlineStr"/>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>0AI1QUJH</t>
+          <t>pfoInmcq</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>l0ueP5rR</t>
+          <t>f1nnRRDE</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
-        <v>45522.4375</v>
+        <v>45521.4375</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t xml:space="preserve">haslberger w 
+          <t xml:space="preserve">dingert c 
   ger </t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t xml:space="preserve">ostseestadion
-  rostock </t>
+          <t xml:space="preserve">stadion an der bremer bruck
+  osnabruck </t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>29000</v>
+        <v>16667</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>KIHmtCkL</t>
+          <t>88Xgj1Y5</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2y0u8Wrq</t>
+          <t>fiEQZ7C7</t>
         </is>
       </c>
       <c r="H21" t="n">
@@ -2985,127 +3221,127 @@
           <t>dfb pokal</t>
         </is>
       </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>ILyJuN3g</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>nJQmYp1B</t>
+        </is>
+      </c>
       <c r="P21" t="n">
-        <v>26.5</v>
+        <v>25.68484848484849</v>
       </c>
       <c r="Q21" t="n">
-        <v>183.8030303030303</v>
+        <v>183.5727272727273</v>
       </c>
       <c r="R21" t="n">
         <v>1</v>
       </c>
       <c r="S21" t="n">
-        <v>67.83333333333333</v>
+        <v>67.07070707070709</v>
       </c>
       <c r="T21" t="n">
-        <v>1329545.454545455</v>
+        <v>1388535.353535353</v>
       </c>
       <c r="U21" t="n">
-        <v>70.51515151515152</v>
+        <v>71.0060606060606</v>
       </c>
       <c r="V21" t="n">
-        <v>23.96031746031746</v>
+        <v>27.22727272727273</v>
       </c>
       <c r="W21" t="n">
-        <v>184.3968253968254</v>
+        <v>183.7443181818182</v>
       </c>
       <c r="X21" t="n">
-        <v>1.073015873015873</v>
+        <v>1.693181818181818</v>
       </c>
       <c r="Y21" t="n">
-        <v>70.34920634920634</v>
+        <v>75.44318181818181</v>
       </c>
       <c r="Z21" t="n">
-        <v>2767460.317460318</v>
+        <v>8740340.909090908</v>
       </c>
       <c r="AA21" t="n">
-        <v>75.57301587301588</v>
+        <v>77.26704545454545</v>
       </c>
       <c r="AB21" t="n">
-        <v>25.27825224292616</v>
+        <v>25.75242504409171</v>
       </c>
       <c r="AC21" t="n">
-        <v>183.7509489302967</v>
+        <v>184.4576719576719</v>
       </c>
       <c r="AD21" t="n">
         <v>1</v>
       </c>
       <c r="AE21" t="n">
-        <v>66.6229583620888</v>
+        <v>66.6166225749559</v>
       </c>
       <c r="AF21" t="n">
-        <v>1184743.069933287</v>
+        <v>1239908.509700176</v>
       </c>
       <c r="AG21" t="n">
-        <v>70.17309351276742</v>
+        <v>69.8231922398589</v>
       </c>
       <c r="AH21" t="n">
-        <v>25.61522361805134</v>
+        <v>24.97832386673205</v>
       </c>
       <c r="AI21" t="n">
-        <v>183.4127876627386</v>
+        <v>184.924112931786</v>
       </c>
       <c r="AJ21" t="n">
-        <v>1.22867780216587</v>
+        <v>1.461491534542879</v>
       </c>
       <c r="AK21" t="n">
-        <v>68.87196121774416</v>
+        <v>73.40985071374088</v>
       </c>
       <c r="AL21" t="n">
-        <v>1815575.481145929</v>
+        <v>6250986.629276996</v>
       </c>
       <c r="AM21" t="n">
-        <v>73.76358209187563</v>
+        <v>76.747364079356</v>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>UyNNTYWE</t>
+          <t>lxrr7DgN</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>0AI1QUJH</t>
+          <t>l0fHXMdE</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>t2AoZLAa</t>
+          <t>8QPARz8c</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
-        <v>45522.4375</v>
+        <v>45521.4375</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t xml:space="preserve">heft f 
+          <t xml:space="preserve">welz t 
   ger </t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t xml:space="preserve">friedrich ebert stadium
-  hildesheim </t>
+          <t xml:space="preserve">ms technologie arena
+  villingen schwenningen </t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>10000</v>
+        <v>8000</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>E3xs5mIe</t>
+          <t>lKLJUxeT</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>6in2Eknb</t>
+          <t>KWixEVWi</t>
         </is>
       </c>
       <c r="H22" t="n">
@@ -3139,22 +3375,22 @@
       <c r="T22" t="inlineStr"/>
       <c r="U22" t="inlineStr"/>
       <c r="V22" t="n">
-        <v>25.27142857142857</v>
+        <v>25.91477272727272</v>
       </c>
       <c r="W22" t="n">
-        <v>182.0168831168831</v>
+        <v>186.6818181818182</v>
       </c>
       <c r="X22" t="n">
         <v>1</v>
       </c>
       <c r="Y22" t="n">
-        <v>67.14155844155843</v>
+        <v>72.89204545454545</v>
       </c>
       <c r="Z22" t="n">
-        <v>1294935.064935065</v>
+        <v>4421732.954545454</v>
       </c>
       <c r="AA22" t="n">
-        <v>70.81168831168831</v>
+        <v>75.20454545454544</v>
       </c>
       <c r="AB22" t="inlineStr"/>
       <c r="AC22" t="inlineStr"/>
@@ -3163,62 +3399,62 @@
       <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="inlineStr"/>
       <c r="AH22" t="n">
-        <v>27.46887755102041</v>
+        <v>27.07239906832298</v>
       </c>
       <c r="AI22" t="n">
-        <v>180.9216702470462</v>
+        <v>182.9631372929607</v>
       </c>
       <c r="AJ22" t="n">
         <v>1</v>
       </c>
       <c r="AK22" t="n">
-        <v>64.69414607948443</v>
+        <v>69.32400038819875</v>
       </c>
       <c r="AL22" t="n">
-        <v>798772.8696741855</v>
+        <v>1934037.078373016</v>
       </c>
       <c r="AM22" t="n">
-        <v>66.57149122807017</v>
+        <v>70.98749676501035</v>
       </c>
       <c r="AN22" t="inlineStr"/>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>8E8qmw3d</t>
+          <t>lGJdeemM</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>jFMCm08e</t>
+          <t>hzyf0b9b</t>
         </is>
       </c>
       <c r="B23" s="2" t="n">
-        <v>45522.4375</v>
+        <v>45521.54166666666</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t xml:space="preserve">aytekin d 
+          <t xml:space="preserve">sather a 
   ger </t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t xml:space="preserve">jahnstadion regensburg
-  regensburg </t>
+          <t xml:space="preserve">new tivoli
+  aachen </t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>15210</v>
+        <v>31026</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>UiCmEP56</t>
+          <t>j3PKcB4E</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>8Y2m6ADe</t>
+          <t>63WsD2ei</t>
         </is>
       </c>
       <c r="H23" t="n">
@@ -3246,7 +3482,7 @@
       <c r="N23" t="inlineStr"/>
       <c r="O23" t="inlineStr">
         <is>
-          <t>0Ija0Ej9</t>
+          <t>ILyJuN3g</t>
         </is>
       </c>
       <c r="P23" t="inlineStr"/>
@@ -3256,22 +3492,22 @@
       <c r="T23" t="inlineStr"/>
       <c r="U23" t="inlineStr"/>
       <c r="V23" t="n">
-        <v>27.97222222222222</v>
+        <v>25.13131313131313</v>
       </c>
       <c r="W23" t="n">
-        <v>182.4222222222222</v>
+        <v>186.2424242424242</v>
       </c>
       <c r="X23" t="n">
-        <v>1.258333333333333</v>
+        <v>1.080808080808081</v>
       </c>
       <c r="Y23" t="n">
-        <v>73.24259259259259</v>
+        <v>68.62626262626263</v>
       </c>
       <c r="Z23" t="n">
-        <v>3645069.444444445</v>
+        <v>1785353.535353536</v>
       </c>
       <c r="AA23" t="n">
-        <v>75.01111111111112</v>
+        <v>72.65656565656566</v>
       </c>
       <c r="AB23" t="inlineStr"/>
       <c r="AC23" t="inlineStr"/>
@@ -3280,66 +3516,62 @@
       <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="inlineStr"/>
       <c r="AH23" t="n">
-        <v>26.61693121693122</v>
+        <v>25.36275017253278</v>
       </c>
       <c r="AI23" t="n">
-        <v>182.9073032961191</v>
+        <v>186.0456253354804</v>
       </c>
       <c r="AJ23" t="n">
-        <v>1.064170843776107</v>
+        <v>1.010121923165401</v>
       </c>
       <c r="AK23" t="n">
-        <v>70.50391509075719</v>
+        <v>66.5227359865041</v>
       </c>
       <c r="AL23" t="n">
-        <v>2404898.16713501</v>
+        <v>1346571.869488536</v>
       </c>
       <c r="AM23" t="n">
-        <v>73.59740054049264</v>
-      </c>
-      <c r="AN23" t="inlineStr">
-        <is>
-          <t>t0ZPdkUl</t>
-        </is>
-      </c>
+        <v>70.92639559849705</v>
+      </c>
+      <c r="AN23" t="inlineStr"/>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>xzRzG0VI</t>
+          <t>A15eUM4C</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>tvOIPExA</t>
+          <t>CpiTEcOi</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
-        <v>45522.4375</v>
+        <v>45521.54166666666</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t xml:space="preserve">burda m 
+          <t xml:space="preserve">bacher m 
   ger </t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t xml:space="preserve">hardtwaldstadion
-  sandhausen </t>
+          <t xml:space="preserve">schuco arena
+  bielefeld </t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>15414</v>
+        <v>27332</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>UZxEj1R4</t>
+          <t>pp38UXK8</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>WG9pOTse</t>
+          <t>dfNCCCzS</t>
         </is>
       </c>
       <c r="H24" t="n">
@@ -3367,7 +3599,7 @@
       <c r="N24" t="inlineStr"/>
       <c r="O24" t="inlineStr">
         <is>
-          <t>88HSzjDr</t>
+          <t>QqLCC3il</t>
         </is>
       </c>
       <c r="P24" t="inlineStr"/>
@@ -3377,22 +3609,22 @@
       <c r="T24" t="inlineStr"/>
       <c r="U24" t="inlineStr"/>
       <c r="V24" t="n">
-        <v>24.17933884297521</v>
+        <v>25.86727272727273</v>
       </c>
       <c r="W24" t="n">
-        <v>185.0165289256199</v>
+        <v>183.7027272727273</v>
       </c>
       <c r="X24" t="n">
-        <v>1.340495867768595</v>
+        <v>1.183636363636364</v>
       </c>
       <c r="Y24" t="n">
-        <v>72.4404958677686</v>
+        <v>69.74909090909091</v>
       </c>
       <c r="Z24" t="n">
-        <v>5833719.008264463</v>
+        <v>2014159.090909091</v>
       </c>
       <c r="AA24" t="n">
-        <v>78.02479338842976</v>
+        <v>73.77818181818182</v>
       </c>
       <c r="AB24" t="inlineStr"/>
       <c r="AC24" t="inlineStr"/>
@@ -3401,62 +3633,62 @@
       <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="inlineStr"/>
       <c r="AH24" t="n">
-        <v>25.85333599149389</v>
+        <v>24.1863455988456</v>
       </c>
       <c r="AI24" t="n">
-        <v>184.8356592238171</v>
+        <v>184.1708513708514</v>
       </c>
       <c r="AJ24" t="n">
-        <v>1.308280170122275</v>
+        <v>1</v>
       </c>
       <c r="AK24" t="n">
-        <v>69.39958798511429</v>
+        <v>66.48472222222222</v>
       </c>
       <c r="AL24" t="n">
-        <v>2902165.071770335</v>
+        <v>1404107.142857143</v>
       </c>
       <c r="AM24" t="n">
-        <v>74.532562466773</v>
+        <v>71.70602453102454</v>
       </c>
       <c r="AN24" t="inlineStr"/>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>EDRZkDzS</t>
+          <t>zyLSrbZQ</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>KSwfVwAO</t>
+          <t>8CpxDyg4</t>
         </is>
       </c>
       <c r="B25" s="2" t="n">
-        <v>45522.4375</v>
+        <v>45521.54166666666</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t xml:space="preserve">kampka r 
+          <t xml:space="preserve">siebert d 
   ger </t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t xml:space="preserve">millerntor stadion
-  hamburg </t>
+          <t xml:space="preserve">stadion lohmuhle
+  lubeck </t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>29546</v>
+        <v>17849</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>WrbkcjCd</t>
+          <t>I1Vk6k3R</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>S0hPB9rA</t>
+          <t>nP1i5US1</t>
         </is>
       </c>
       <c r="H25" t="n">
@@ -3484,7 +3716,7 @@
       <c r="N25" t="inlineStr"/>
       <c r="O25" t="inlineStr">
         <is>
-          <t>8vndvXTk</t>
+          <t>0Ija0Ej9</t>
         </is>
       </c>
       <c r="P25" t="inlineStr"/>
@@ -3494,22 +3726,22 @@
       <c r="T25" t="inlineStr"/>
       <c r="U25" t="inlineStr"/>
       <c r="V25" t="n">
-        <v>25.86363636363636</v>
+        <v>25.68181818181818</v>
       </c>
       <c r="W25" t="n">
-        <v>187.1436363636363</v>
+        <v>184.7159090909091</v>
       </c>
       <c r="X25" t="n">
-        <v>1</v>
+        <v>2.278409090909091</v>
       </c>
       <c r="Y25" t="n">
-        <v>70.55818181818181</v>
+        <v>79.99431818181819</v>
       </c>
       <c r="Z25" t="n">
-        <v>2390886.363636363</v>
+        <v>28714204.54545454</v>
       </c>
       <c r="AA25" t="n">
-        <v>74.07090909090908</v>
+        <v>83.10227272727272</v>
       </c>
       <c r="AB25" t="inlineStr"/>
       <c r="AC25" t="inlineStr"/>
@@ -3518,62 +3750,62 @@
       <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="inlineStr"/>
       <c r="AH25" t="n">
-        <v>26.05142422581681</v>
+        <v>24.79724702380953</v>
       </c>
       <c r="AI25" t="n">
-        <v>186.2869533847795</v>
+        <v>183.9562251984127</v>
       </c>
       <c r="AJ25" t="n">
-        <v>1</v>
+        <v>1.990823412698413</v>
       </c>
       <c r="AK25" t="n">
-        <v>68.57811629263036</v>
+        <v>77.51909722222223</v>
       </c>
       <c r="AL25" t="n">
-        <v>1624988.634287707</v>
+        <v>19649553.57142857</v>
       </c>
       <c r="AM25" t="n">
-        <v>71.48562788092839</v>
+        <v>82.24913194444443</v>
       </c>
       <c r="AN25" t="inlineStr"/>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>AoL97rX8</t>
+          <t>MDhPV0RQ</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>pzHxyrtm</t>
+          <t>6q2yrHgU</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
-        <v>45522.54166666666</v>
+        <v>45522.33333333334</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t xml:space="preserve">braun r 
+          <t xml:space="preserve">winter n 
   ger </t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadion am lotter kreuz
-  lotte </t>
+          <t xml:space="preserve">ludwigspark stadion
+  saarbrucken </t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>10059</v>
+        <v>16003</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>hjNlCFPB</t>
+          <t>fLbhmJ5l</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>EB3q7jbk</t>
+          <t>6FDqshzF</t>
         </is>
       </c>
       <c r="H26" t="n">
@@ -3601,7 +3833,7 @@
       <c r="N26" t="inlineStr"/>
       <c r="O26" t="inlineStr">
         <is>
-          <t>naWckLmC</t>
+          <t>CCQGbik8</t>
         </is>
       </c>
       <c r="P26" t="inlineStr"/>
@@ -3611,22 +3843,22 @@
       <c r="T26" t="inlineStr"/>
       <c r="U26" t="inlineStr"/>
       <c r="V26" t="n">
-        <v>26.61038961038961</v>
+        <v>23.2653810835629</v>
       </c>
       <c r="W26" t="n">
-        <v>183.6103896103896</v>
+        <v>183.1652892561983</v>
       </c>
       <c r="X26" t="n">
-        <v>1.025974025974026</v>
+        <v>1.02020202020202</v>
       </c>
       <c r="Y26" t="n">
-        <v>68.55844155844156</v>
+        <v>67.02479338842976</v>
       </c>
       <c r="Z26" t="n">
-        <v>1629545.454545455</v>
+        <v>1666023.875114784</v>
       </c>
       <c r="AA26" t="n">
-        <v>72.8051948051948</v>
+        <v>73.16712580348944</v>
       </c>
       <c r="AB26" t="inlineStr"/>
       <c r="AC26" t="inlineStr"/>
@@ -3635,62 +3867,66 @@
       <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="inlineStr"/>
       <c r="AH26" t="n">
-        <v>26.45972073039743</v>
+        <v>27.24357208448118</v>
       </c>
       <c r="AI26" t="n">
-        <v>182.2928153717627</v>
+        <v>182.5620982552801</v>
       </c>
       <c r="AJ26" t="n">
-        <v>1.187641723356009</v>
+        <v>1.01010101010101</v>
       </c>
       <c r="AK26" t="n">
-        <v>66.75550483351235</v>
+        <v>67.31370523415977</v>
       </c>
       <c r="AL26" t="n">
-        <v>1201480.710705335</v>
+        <v>1166500.229568411</v>
       </c>
       <c r="AM26" t="n">
-        <v>71.62398555913595</v>
-      </c>
-      <c r="AN26" t="inlineStr"/>
+        <v>69.56255739210285</v>
+      </c>
+      <c r="AN26" t="inlineStr">
+        <is>
+          <t>trS1MB7T</t>
+        </is>
+      </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>tO31cZrF</t>
+          <t>txZLBQVC</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>dCPKovw8</t>
+          <t>AiJ3kset</t>
         </is>
       </c>
       <c r="B27" s="2" t="n">
-        <v>45522.54166666666</v>
+        <v>45522.33333333334</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t xml:space="preserve">burda m 
+          <t xml:space="preserve">jollenbeck m 
   ger </t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t xml:space="preserve">hansch arena
-  meppen </t>
+          <t xml:space="preserve">friedrich ludwig jahn sportpark
+  berlin </t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>13696</v>
+        <v>19708</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>rXqBh2xP</t>
+          <t>UNr2EUfd</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>v9k3aY5F</t>
+          <t>fTVNku3I</t>
         </is>
       </c>
       <c r="H27" t="n">
@@ -3716,11 +3952,7 @@
         </is>
       </c>
       <c r="N27" t="inlineStr"/>
-      <c r="O27" t="inlineStr">
-        <is>
-          <t>ILyJuN3g</t>
-        </is>
-      </c>
+      <c r="O27" t="inlineStr"/>
       <c r="P27" t="inlineStr"/>
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr"/>
@@ -3728,22 +3960,22 @@
       <c r="T27" t="inlineStr"/>
       <c r="U27" t="inlineStr"/>
       <c r="V27" t="n">
-        <v>24.9012987012987</v>
+        <v>25.52222222222222</v>
       </c>
       <c r="W27" t="n">
-        <v>183.1883116883117</v>
+        <v>185.9227272727273</v>
       </c>
       <c r="X27" t="n">
-        <v>1</v>
+        <v>1.443118686868687</v>
       </c>
       <c r="Y27" t="n">
-        <v>70.84155844155843</v>
+        <v>74.47638888888889</v>
       </c>
       <c r="Z27" t="n">
-        <v>2692337.662337662</v>
+        <v>6594744.318181818</v>
       </c>
       <c r="AA27" t="n">
-        <v>74.22597402597403</v>
+        <v>77.25101010101011</v>
       </c>
       <c r="AB27" t="inlineStr"/>
       <c r="AC27" t="inlineStr"/>
@@ -3752,62 +3984,62 @@
       <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="inlineStr"/>
       <c r="AH27" t="n">
-        <v>25.11075036075036</v>
+        <v>23.98748973522822</v>
       </c>
       <c r="AI27" t="n">
-        <v>181.7821067821068</v>
+        <v>183.9524915508468</v>
       </c>
       <c r="AJ27" t="n">
-        <v>1</v>
+        <v>1.126060475525936</v>
       </c>
       <c r="AK27" t="n">
-        <v>69.8781746031746</v>
+        <v>71.1172962591137</v>
       </c>
       <c r="AL27" t="n">
-        <v>2400109.668109668</v>
+        <v>3842467.299581815</v>
       </c>
       <c r="AM27" t="n">
-        <v>73.3320707070707</v>
+        <v>76.40783059685197</v>
       </c>
       <c r="AN27" t="inlineStr"/>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>EDRZkDzS</t>
+          <t>2VSFgl3c</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>vXAKoaf5</t>
+          <t>YV3TqwPH</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
-        <v>45522.54166666666</v>
+        <v>45522.4375</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t xml:space="preserve">kampka r 
+          <t xml:space="preserve">haslberger w 
   ger </t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t xml:space="preserve">rudolf harbig stadion
-  dresden </t>
+          <t xml:space="preserve">stadion am panzenberg
+  bremen </t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>32249</v>
+        <v>5000</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>zL1YsOi1</t>
+          <t>tW75B1ei</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>ne1oL3y7</t>
+          <t>G2Op923t</t>
         </is>
       </c>
       <c r="H28" t="n">
@@ -3833,11 +4065,7 @@
         </is>
       </c>
       <c r="N28" t="inlineStr"/>
-      <c r="O28" t="inlineStr">
-        <is>
-          <t>WG9pOTse</t>
-        </is>
-      </c>
+      <c r="O28" t="inlineStr"/>
       <c r="P28" t="inlineStr"/>
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr"/>
@@ -3845,22 +4073,22 @@
       <c r="T28" t="inlineStr"/>
       <c r="U28" t="inlineStr"/>
       <c r="V28" t="n">
-        <v>25.48787878787878</v>
+        <v>24.16522727272727</v>
       </c>
       <c r="W28" t="n">
-        <v>184.5181818181818</v>
+        <v>185.2697727272727</v>
       </c>
       <c r="X28" t="n">
         <v>1</v>
       </c>
       <c r="Y28" t="n">
-        <v>70.55454545454546</v>
+        <v>66.65818181818182</v>
       </c>
       <c r="Z28" t="n">
-        <v>2605202.02020202</v>
+        <v>1442465.909090909</v>
       </c>
       <c r="AA28" t="n">
-        <v>73.95959595959596</v>
+        <v>72.42545454545454</v>
       </c>
       <c r="AB28" t="inlineStr"/>
       <c r="AC28" t="inlineStr"/>
@@ -3869,62 +4097,62 @@
       <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="inlineStr"/>
       <c r="AH28" t="n">
-        <v>23.88383838383838</v>
+        <v>24.91971696781479</v>
       </c>
       <c r="AI28" t="n">
-        <v>185.8560606060606</v>
+        <v>186.4826404573687</v>
       </c>
       <c r="AJ28" t="n">
         <v>1</v>
       </c>
       <c r="AK28" t="n">
-        <v>66.90628507295173</v>
+        <v>66.83907749858835</v>
       </c>
       <c r="AL28" t="n">
-        <v>1690971.520763187</v>
+        <v>1358067.211321288</v>
       </c>
       <c r="AM28" t="n">
-        <v>72.77427048260382</v>
+        <v>71.49341473743648</v>
       </c>
       <c r="AN28" t="inlineStr"/>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>AoL97rX8</t>
+          <t>0AI1QUJH</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>06NAdG8N</t>
+          <t>l0ueP5rR</t>
         </is>
       </c>
       <c r="B29" s="2" t="n">
-        <v>45523.54166666666</v>
+        <v>45522.4375</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t xml:space="preserve">petersen m 
+          <t xml:space="preserve">haslberger w 
   ger </t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadion der freundschaft
-  cottbus </t>
+          <t xml:space="preserve">ostseestadion
+  rostock </t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>22450</v>
+        <v>29000</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>6g44VD52</t>
+          <t>KIHmtCkL</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Ig1f1fy3</t>
+          <t>2y0u8Wrq</t>
         </is>
       </c>
       <c r="H29" t="n">
@@ -3949,99 +4177,127 @@
           <t>dfb pokal</t>
         </is>
       </c>
-      <c r="N29" t="inlineStr"/>
-      <c r="O29" t="inlineStr">
-        <is>
-          <t>v9k3aY5F</t>
-        </is>
-      </c>
-      <c r="P29" t="inlineStr"/>
-      <c r="Q29" t="inlineStr"/>
-      <c r="R29" t="inlineStr"/>
-      <c r="S29" t="inlineStr"/>
-      <c r="T29" t="inlineStr"/>
-      <c r="U29" t="inlineStr"/>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>ILyJuN3g</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr"/>
+      <c r="P29" t="n">
+        <v>26.56565656565656</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>183.6969696969697</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1</v>
+      </c>
+      <c r="S29" t="n">
+        <v>67.84848484848484</v>
+      </c>
+      <c r="T29" t="n">
+        <v>1324747.474747475</v>
+      </c>
+      <c r="U29" t="n">
+        <v>70.47474747474747</v>
+      </c>
       <c r="V29" t="n">
-        <v>26.18181818181818</v>
+        <v>23.79494949494949</v>
       </c>
       <c r="W29" t="n">
-        <v>183.1272727272727</v>
+        <v>184.3386868686869</v>
       </c>
       <c r="X29" t="n">
-        <v>1.181818181818182</v>
+        <v>1.061111111111111</v>
       </c>
       <c r="Y29" t="n">
-        <v>73.16363636363636</v>
+        <v>70.34535353535352</v>
       </c>
       <c r="Z29" t="n">
-        <v>4815909.090909092</v>
+        <v>2794404.04040404</v>
       </c>
       <c r="AA29" t="n">
-        <v>75.94545454545455</v>
-      </c>
-      <c r="AB29" t="inlineStr"/>
-      <c r="AC29" t="inlineStr"/>
-      <c r="AD29" t="inlineStr"/>
-      <c r="AE29" t="inlineStr"/>
-      <c r="AF29" t="inlineStr"/>
-      <c r="AG29" t="inlineStr"/>
+        <v>75.62202020202021</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>24.94939038417299</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>183.7089659535312</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>66.42919446361475</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>1201634.268844414</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>70.40706234184495</v>
+      </c>
       <c r="AH29" t="n">
-        <v>24.86158126293996</v>
+        <v>25.98799780247721</v>
       </c>
       <c r="AI29" t="n">
-        <v>184.8690601049726</v>
+        <v>183.7798243797901</v>
       </c>
       <c r="AJ29" t="n">
-        <v>1.111249364352911</v>
+        <v>1.237257001198649</v>
       </c>
       <c r="AK29" t="n">
-        <v>68.34426964149505</v>
+        <v>69.01354745559551</v>
       </c>
       <c r="AL29" t="n">
-        <v>2456707.041607642</v>
+        <v>1786760.971722785</v>
       </c>
       <c r="AM29" t="n">
-        <v>73.74422787040064</v>
-      </c>
-      <c r="AN29" t="inlineStr"/>
+        <v>73.49799952780502</v>
+      </c>
+      <c r="AN29" t="inlineStr">
+        <is>
+          <t>UyNNTYWE</t>
+        </is>
+      </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>xzRzG0VI</t>
+          <t>0AI1QUJH</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>Sff03OL7</t>
+          <t>t2AoZLAa</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
-        <v>45523.54166666666</v>
+        <v>45522.4375</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t xml:space="preserve">heft f 
+          <t xml:space="preserve">bauer t 
   ger </t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t xml:space="preserve">bieberer berg stadion
-  offenbach am main </t>
+          <t xml:space="preserve">friedrich ebert stadium
+  hildesheim </t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>20500</v>
+        <v>10000</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>YJURlaIO</t>
+          <t>E3xs5mIe</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>YFuz2RLm</t>
+          <t>6in2Eknb</t>
         </is>
       </c>
       <c r="H30" t="n">
@@ -4075,22 +4331,22 @@
       <c r="T30" t="inlineStr"/>
       <c r="U30" t="inlineStr"/>
       <c r="V30" t="n">
-        <v>25.46666666666667</v>
+        <v>25.23801652892562</v>
       </c>
       <c r="W30" t="n">
-        <v>180.9833333333333</v>
+        <v>182.3520661157025</v>
       </c>
       <c r="X30" t="n">
         <v>1</v>
       </c>
       <c r="Y30" t="n">
-        <v>68.28333333333332</v>
+        <v>67.16363636363636</v>
       </c>
       <c r="Z30" t="n">
-        <v>1470833.333333333</v>
+        <v>1292231.404958678</v>
       </c>
       <c r="AA30" t="n">
-        <v>70.73333333333333</v>
+        <v>70.72727272727273</v>
       </c>
       <c r="AB30" t="inlineStr"/>
       <c r="AC30" t="inlineStr"/>
@@ -4099,62 +4355,62 @@
       <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="inlineStr"/>
       <c r="AH30" t="n">
-        <v>23.22341269841269</v>
+        <v>27.48165168165168</v>
       </c>
       <c r="AI30" t="n">
-        <v>179.9242063492063</v>
+        <v>181.1435298619509</v>
       </c>
       <c r="AJ30" t="n">
         <v>1</v>
       </c>
       <c r="AK30" t="n">
-        <v>65.57063492063493</v>
+        <v>64.49427400085295</v>
       </c>
       <c r="AL30" t="n">
-        <v>1241240.07936508</v>
+        <v>785399.6544391281</v>
       </c>
       <c r="AM30" t="n">
-        <v>70.34960317460317</v>
+        <v>66.55627530364373</v>
       </c>
       <c r="AN30" t="inlineStr"/>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>8E8qmw3d</t>
+          <t>4fX0k7gg</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>EkP2bxvB</t>
+          <t>jFMCm08e</t>
         </is>
       </c>
       <c r="B31" s="2" t="n">
-        <v>45523.54166666666</v>
+        <v>45522.4375</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t xml:space="preserve">willenborg f 
+          <t xml:space="preserve">aytekin d 
   ger </t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadion oberwerth
-  koblenz </t>
+          <t xml:space="preserve">jahnstadion regensburg
+  regensburg </t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>9500</v>
+        <v>15210</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>p8wBsqZt</t>
+          <t>UiCmEP56</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>nwkTahLL</t>
+          <t>8Y2m6ADe</t>
         </is>
       </c>
       <c r="H31" t="n">
@@ -4182,7 +4438,7 @@
       <c r="N31" t="inlineStr"/>
       <c r="O31" t="inlineStr">
         <is>
-          <t>dfNCCCzS</t>
+          <t>0Ija0Ej9</t>
         </is>
       </c>
       <c r="P31" t="inlineStr"/>
@@ -4192,22 +4448,22 @@
       <c r="T31" t="inlineStr"/>
       <c r="U31" t="inlineStr"/>
       <c r="V31" t="n">
-        <v>25.22</v>
+        <v>27.92345679012346</v>
       </c>
       <c r="W31" t="n">
-        <v>186.74</v>
+        <v>182.6172839506173</v>
       </c>
       <c r="X31" t="n">
-        <v>1.56</v>
+        <v>1.267283950617284</v>
       </c>
       <c r="Y31" t="n">
-        <v>75.81</v>
+        <v>73.31481481481482</v>
       </c>
       <c r="Z31" t="n">
-        <v>10860000</v>
+        <v>3698101.851851852</v>
       </c>
       <c r="AA31" t="n">
-        <v>79.66</v>
+        <v>75.24074074074075</v>
       </c>
       <c r="AB31" t="inlineStr"/>
       <c r="AC31" t="inlineStr"/>
@@ -4216,62 +4472,66 @@
       <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="inlineStr"/>
       <c r="AH31" t="n">
-        <v>24.49049516908213</v>
+        <v>27.05132275132275</v>
       </c>
       <c r="AI31" t="n">
-        <v>183.5287318840579</v>
+        <v>182.6198217051192</v>
       </c>
       <c r="AJ31" t="n">
-        <v>1.273164251207729</v>
+        <v>1.061030696709568</v>
       </c>
       <c r="AK31" t="n">
-        <v>73.89692028985507</v>
+        <v>70.56604844713158</v>
       </c>
       <c r="AL31" t="n">
-        <v>8517461.956521738</v>
+        <v>2347542.340700236</v>
       </c>
       <c r="AM31" t="n">
-        <v>78.55956521739131</v>
-      </c>
-      <c r="AN31" t="inlineStr"/>
+        <v>73.22149377341026</v>
+      </c>
+      <c r="AN31" t="inlineStr">
+        <is>
+          <t>zyLSrbZQ</t>
+        </is>
+      </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>vZA6VYpf</t>
+          <t>xzRzG0VI</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>pAXo2Kvn</t>
+          <t>tvOIPExA</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
-        <v>45523.65625</v>
+        <v>45522.4375</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t xml:space="preserve">zwayer f 
+          <t xml:space="preserve">bauer t 
   ger </t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t xml:space="preserve">eintracht stadion
-  braunschweig </t>
+          <t xml:space="preserve">hardtwaldstadion
+  sandhausen </t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>23325</v>
+        <v>15414</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>QqLCC3il</t>
+          <t>UZxEj1R4</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>8vndvXTk</t>
+          <t>WG9pOTse</t>
         </is>
       </c>
       <c r="H32" t="n">
@@ -4296,243 +4556,1175 @@
           <t>dfb pokal</t>
         </is>
       </c>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>dfNCCCzS</t>
-        </is>
-      </c>
+      <c r="N32" t="inlineStr"/>
       <c r="O32" t="inlineStr">
         <is>
-          <t>EuakNmc1</t>
-        </is>
-      </c>
-      <c r="P32" t="n">
-        <v>25.41720779220779</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>184.2175324675325</v>
-      </c>
-      <c r="R32" t="n">
-        <v>1.082792207792208</v>
-      </c>
-      <c r="S32" t="n">
-        <v>67.33279220779221</v>
-      </c>
-      <c r="T32" t="n">
-        <v>1406980.519480519</v>
-      </c>
-      <c r="U32" t="n">
-        <v>71.29383116883118</v>
-      </c>
+          <t>88HSzjDr</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr"/>
+      <c r="Q32" t="inlineStr"/>
+      <c r="R32" t="inlineStr"/>
+      <c r="S32" t="inlineStr"/>
+      <c r="T32" t="inlineStr"/>
+      <c r="U32" t="inlineStr"/>
       <c r="V32" t="n">
-        <v>24.25222222222222</v>
+        <v>24.41767676767677</v>
       </c>
       <c r="W32" t="n">
-        <v>183.0955555555556</v>
+        <v>185.3181818181818</v>
       </c>
       <c r="X32" t="n">
-        <v>1.63</v>
+        <v>1.298989898989899</v>
       </c>
       <c r="Y32" t="n">
-        <v>76.98111111111112</v>
+        <v>72.4510101010101</v>
       </c>
       <c r="Z32" t="n">
-        <v>15614611.11111111</v>
+        <v>5717575.757575758</v>
       </c>
       <c r="AA32" t="n">
-        <v>81.18111111111111</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>26.05385487528344</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>182.6663832199546</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE32" t="n">
-        <v>66.68679138321995</v>
-      </c>
-      <c r="AF32" t="n">
-        <v>1263927.154195011</v>
-      </c>
-      <c r="AG32" t="n">
-        <v>70.07199546485261</v>
-      </c>
+        <v>77.73737373737373</v>
+      </c>
+      <c r="AB32" t="inlineStr"/>
+      <c r="AC32" t="inlineStr"/>
+      <c r="AD32" t="inlineStr"/>
+      <c r="AE32" t="inlineStr"/>
+      <c r="AF32" t="inlineStr"/>
+      <c r="AG32" t="inlineStr"/>
       <c r="AH32" t="n">
-        <v>24.30286226930964</v>
+        <v>25.65728557504873</v>
       </c>
       <c r="AI32" t="n">
-        <v>183.7797641831852</v>
+        <v>185.3194328413627</v>
       </c>
       <c r="AJ32" t="n">
-        <v>1.421828434723172</v>
+        <v>1.300606841177016</v>
       </c>
       <c r="AK32" t="n">
-        <v>71.9276110731374</v>
+        <v>69.41030817785203</v>
       </c>
       <c r="AL32" t="n">
-        <v>5697609.791524266</v>
+        <v>2901885.268727374</v>
       </c>
       <c r="AM32" t="n">
-        <v>78.33495215311004</v>
-      </c>
-      <c r="AN32" t="inlineStr">
-        <is>
-          <t>txZLBQVC</t>
-        </is>
-      </c>
+        <v>74.59143808595564</v>
+      </c>
+      <c r="AN32" t="inlineStr"/>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>pfoInmcq</t>
+          <t>4fX0k7gg</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
+          <t>KSwfVwAO</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="n">
+        <v>45522.4375</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">kampka r 
+  ger </t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">millerntor stadion
+  hamburg </t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>29546</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>WrbkcjCd</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>S0hPB9rA</t>
+        </is>
+      </c>
+      <c r="H33" t="n">
+        <v>59</v>
+      </c>
+      <c r="I33" t="n">
+        <v>593</v>
+      </c>
+      <c r="J33" t="n">
+        <v>1</v>
+      </c>
+      <c r="K33" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>dfb pokal</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>8vndvXTk</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr"/>
+      <c r="Q33" t="inlineStr"/>
+      <c r="R33" t="inlineStr"/>
+      <c r="S33" t="inlineStr"/>
+      <c r="T33" t="inlineStr"/>
+      <c r="U33" t="inlineStr"/>
+      <c r="V33" t="n">
+        <v>25.94318181818182</v>
+      </c>
+      <c r="W33" t="n">
+        <v>186.2681818181818</v>
+      </c>
+      <c r="X33" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>70.66818181818182</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>2396065.340909091</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>73.91022727272727</v>
+      </c>
+      <c r="AB33" t="inlineStr"/>
+      <c r="AC33" t="inlineStr"/>
+      <c r="AD33" t="inlineStr"/>
+      <c r="AE33" t="inlineStr"/>
+      <c r="AF33" t="inlineStr"/>
+      <c r="AG33" t="inlineStr"/>
+      <c r="AH33" t="n">
+        <v>26.29174788841368</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>187.0984208176024</v>
+      </c>
+      <c r="AJ33" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK33" t="n">
+        <v>68.71287076637987</v>
+      </c>
+      <c r="AL33" t="n">
+        <v>1615761.786705304</v>
+      </c>
+      <c r="AM33" t="n">
+        <v>71.45998143929353</v>
+      </c>
+      <c r="AN33" t="inlineStr"/>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>AoL97rX8</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="inlineStr">
+        <is>
+          <t>pzHxyrtm</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="n">
+        <v>45522.54166666666</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hartmann r 
+  ger </t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadion am lotter kreuz
+  lotte </t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>10059</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>hjNlCFPB</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>EB3q7jbk</t>
+        </is>
+      </c>
+      <c r="H34" t="n">
+        <v>59</v>
+      </c>
+      <c r="I34" t="n">
+        <v>593</v>
+      </c>
+      <c r="J34" t="n">
+        <v>1</v>
+      </c>
+      <c r="K34" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>dfb pokal</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>naWckLmC</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr"/>
+      <c r="Q34" t="inlineStr"/>
+      <c r="R34" t="inlineStr"/>
+      <c r="S34" t="inlineStr"/>
+      <c r="T34" t="inlineStr"/>
+      <c r="U34" t="inlineStr"/>
+      <c r="V34" t="n">
+        <v>26.58677685950414</v>
+      </c>
+      <c r="W34" t="n">
+        <v>183.6611570247934</v>
+      </c>
+      <c r="X34" t="n">
+        <v>1.016528925619835</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>68.53719008264464</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>1616942.14876033</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>72.82644628099173</v>
+      </c>
+      <c r="AB34" t="inlineStr"/>
+      <c r="AC34" t="inlineStr"/>
+      <c r="AD34" t="inlineStr"/>
+      <c r="AE34" t="inlineStr"/>
+      <c r="AF34" t="inlineStr"/>
+      <c r="AG34" t="inlineStr"/>
+      <c r="AH34" t="n">
+        <v>26.26161521227311</v>
+      </c>
+      <c r="AI34" t="n">
+        <v>182.3870946305157</v>
+      </c>
+      <c r="AJ34" t="n">
+        <v>1.162337662337662</v>
+      </c>
+      <c r="AK34" t="n">
+        <v>66.63102832839674</v>
+      </c>
+      <c r="AL34" t="n">
+        <v>1178107.674489253</v>
+      </c>
+      <c r="AM34" t="n">
+        <v>71.65023828510671</v>
+      </c>
+      <c r="AN34" t="inlineStr"/>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>OzPMRhK3</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="inlineStr">
+        <is>
+          <t>dCPKovw8</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="n">
+        <v>45522.54166666666</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">burda m 
+  ger </t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hansch arena
+  meppen </t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>13696</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>rXqBh2xP</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>v9k3aY5F</t>
+        </is>
+      </c>
+      <c r="H35" t="n">
+        <v>59</v>
+      </c>
+      <c r="I35" t="n">
+        <v>593</v>
+      </c>
+      <c r="J35" t="n">
+        <v>1</v>
+      </c>
+      <c r="K35" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>dfb pokal</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>ILyJuN3g</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr"/>
+      <c r="Q35" t="inlineStr"/>
+      <c r="R35" t="inlineStr"/>
+      <c r="S35" t="inlineStr"/>
+      <c r="T35" t="inlineStr"/>
+      <c r="U35" t="inlineStr"/>
+      <c r="V35" t="n">
+        <v>24.75545454545455</v>
+      </c>
+      <c r="W35" t="n">
+        <v>183.2372727272727</v>
+      </c>
+      <c r="X35" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>70.73090909090908</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>2691545.454545455</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>74.36545454545455</v>
+      </c>
+      <c r="AB35" t="inlineStr"/>
+      <c r="AC35" t="inlineStr"/>
+      <c r="AD35" t="inlineStr"/>
+      <c r="AE35" t="inlineStr"/>
+      <c r="AF35" t="inlineStr"/>
+      <c r="AG35" t="inlineStr"/>
+      <c r="AH35" t="n">
+        <v>25.31502525252525</v>
+      </c>
+      <c r="AI35" t="n">
+        <v>181.8653318903319</v>
+      </c>
+      <c r="AJ35" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK35" t="n">
+        <v>69.77007936507937</v>
+      </c>
+      <c r="AL35" t="n">
+        <v>2341933.910533911</v>
+      </c>
+      <c r="AM35" t="n">
+        <v>73.05209235209236</v>
+      </c>
+      <c r="AN35" t="inlineStr"/>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>EDRZkDzS</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="inlineStr">
+        <is>
+          <t>vXAKoaf5</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="n">
+        <v>45522.54166666666</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hartmann r 
+  ger </t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">rudolf harbig stadion
+  dresden </t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>32249</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>zL1YsOi1</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>ne1oL3y7</t>
+        </is>
+      </c>
+      <c r="H36" t="n">
+        <v>59</v>
+      </c>
+      <c r="I36" t="n">
+        <v>593</v>
+      </c>
+      <c r="J36" t="n">
+        <v>1</v>
+      </c>
+      <c r="K36" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>dfb pokal</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>WG9pOTse</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr"/>
+      <c r="Q36" t="inlineStr"/>
+      <c r="R36" t="inlineStr"/>
+      <c r="S36" t="inlineStr"/>
+      <c r="T36" t="inlineStr"/>
+      <c r="U36" t="inlineStr"/>
+      <c r="V36" t="n">
+        <v>25.25519480519481</v>
+      </c>
+      <c r="W36" t="n">
+        <v>184.1707792207792</v>
+      </c>
+      <c r="X36" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>70.37597402597403</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>2605616.883116883</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>74.16883116883116</v>
+      </c>
+      <c r="AB36" t="inlineStr"/>
+      <c r="AC36" t="inlineStr"/>
+      <c r="AD36" t="inlineStr"/>
+      <c r="AE36" t="inlineStr"/>
+      <c r="AF36" t="inlineStr"/>
+      <c r="AG36" t="inlineStr"/>
+      <c r="AH36" t="n">
+        <v>23.85771173271173</v>
+      </c>
+      <c r="AI36" t="n">
+        <v>186.1571622821623</v>
+      </c>
+      <c r="AJ36" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK36" t="n">
+        <v>66.84550865800865</v>
+      </c>
+      <c r="AL36" t="n">
+        <v>1663146.298146298</v>
+      </c>
+      <c r="AM36" t="n">
+        <v>72.55505605505606</v>
+      </c>
+      <c r="AN36" t="inlineStr"/>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>OzPMRhK3</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="inlineStr">
+        <is>
+          <t>06NAdG8N</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="n">
+        <v>45523.54166666666</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">petersen m 
+  ger </t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadion der freundschaft
+  cottbus </t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>22450</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>6g44VD52</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Ig1f1fy3</t>
+        </is>
+      </c>
+      <c r="H37" t="n">
+        <v>59</v>
+      </c>
+      <c r="I37" t="n">
+        <v>593</v>
+      </c>
+      <c r="J37" t="n">
+        <v>1</v>
+      </c>
+      <c r="K37" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>dfb pokal</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>v9k3aY5F</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr"/>
+      <c r="Q37" t="inlineStr"/>
+      <c r="R37" t="inlineStr"/>
+      <c r="S37" t="inlineStr"/>
+      <c r="T37" t="inlineStr"/>
+      <c r="U37" t="inlineStr"/>
+      <c r="V37" t="n">
+        <v>26.03295454545454</v>
+      </c>
+      <c r="W37" t="n">
+        <v>183.7102272727273</v>
+      </c>
+      <c r="X37" t="n">
+        <v>1.160227272727273</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>73.18181818181819</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>4846988.636363637</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>76.05568181818182</v>
+      </c>
+      <c r="AB37" t="inlineStr"/>
+      <c r="AC37" t="inlineStr"/>
+      <c r="AD37" t="inlineStr"/>
+      <c r="AE37" t="inlineStr"/>
+      <c r="AF37" t="inlineStr"/>
+      <c r="AG37" t="inlineStr"/>
+      <c r="AH37" t="n">
+        <v>24.93740564613527</v>
+      </c>
+      <c r="AI37" t="n">
+        <v>184.4495257902456</v>
+      </c>
+      <c r="AJ37" t="n">
+        <v>1.198887305446587</v>
+      </c>
+      <c r="AK37" t="n">
+        <v>68.50645238549272</v>
+      </c>
+      <c r="AL37" t="n">
+        <v>2554425.22463314</v>
+      </c>
+      <c r="AM37" t="n">
+        <v>74.0719348189314</v>
+      </c>
+      <c r="AN37" t="inlineStr"/>
+      <c r="AO37" t="inlineStr">
+        <is>
+          <t>xzRzG0VI</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="inlineStr">
+        <is>
+          <t>Sff03OL7</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="n">
+        <v>45523.54166666666</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">heft f 
+  ger </t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bieberer berg stadion
+  offenbach am main </t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>20500</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>YJURlaIO</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>YFuz2RLm</t>
+        </is>
+      </c>
+      <c r="H38" t="n">
+        <v>59</v>
+      </c>
+      <c r="I38" t="n">
+        <v>593</v>
+      </c>
+      <c r="J38" t="n">
+        <v>1</v>
+      </c>
+      <c r="K38" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>dfb pokal</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr"/>
+      <c r="O38" t="inlineStr"/>
+      <c r="P38" t="inlineStr"/>
+      <c r="Q38" t="inlineStr"/>
+      <c r="R38" t="inlineStr"/>
+      <c r="S38" t="inlineStr"/>
+      <c r="T38" t="inlineStr"/>
+      <c r="U38" t="inlineStr"/>
+      <c r="V38" t="n">
+        <v>25.47777777777778</v>
+      </c>
+      <c r="W38" t="n">
+        <v>181.3777777777778</v>
+      </c>
+      <c r="X38" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>68.17777777777776</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>1441666.666666667</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>70.62222222222222</v>
+      </c>
+      <c r="AB38" t="inlineStr"/>
+      <c r="AC38" t="inlineStr"/>
+      <c r="AD38" t="inlineStr"/>
+      <c r="AE38" t="inlineStr"/>
+      <c r="AF38" t="inlineStr"/>
+      <c r="AG38" t="inlineStr"/>
+      <c r="AH38" t="n">
+        <v>23.11194444444444</v>
+      </c>
+      <c r="AI38" t="n">
+        <v>180.315</v>
+      </c>
+      <c r="AJ38" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK38" t="n">
+        <v>65.69805555555556</v>
+      </c>
+      <c r="AL38" t="n">
+        <v>1287097.222222222</v>
+      </c>
+      <c r="AM38" t="n">
+        <v>70.68916666666667</v>
+      </c>
+      <c r="AN38" t="inlineStr"/>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>8E8qmw3d</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="inlineStr">
+        <is>
+          <t>EkP2bxvB</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="n">
+        <v>45523.54166666666</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">willenborg f 
+  ger </t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadion oberwerth
+  koblenz </t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>9500</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>p8wBsqZt</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>nwkTahLL</t>
+        </is>
+      </c>
+      <c r="H39" t="n">
+        <v>59</v>
+      </c>
+      <c r="I39" t="n">
+        <v>593</v>
+      </c>
+      <c r="J39" t="n">
+        <v>1</v>
+      </c>
+      <c r="K39" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>dfb pokal</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>dfNCCCzS</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr"/>
+      <c r="Q39" t="inlineStr"/>
+      <c r="R39" t="inlineStr"/>
+      <c r="S39" t="inlineStr"/>
+      <c r="T39" t="inlineStr"/>
+      <c r="U39" t="inlineStr"/>
+      <c r="V39" t="n">
+        <v>25.4125</v>
+      </c>
+      <c r="W39" t="n">
+        <v>186.625</v>
+      </c>
+      <c r="X39" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>75.70625</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>10658125</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>79.51249999999999</v>
+      </c>
+      <c r="AB39" t="inlineStr"/>
+      <c r="AC39" t="inlineStr"/>
+      <c r="AD39" t="inlineStr"/>
+      <c r="AE39" t="inlineStr"/>
+      <c r="AF39" t="inlineStr"/>
+      <c r="AG39" t="inlineStr"/>
+      <c r="AH39" t="n">
+        <v>24.2524532004831</v>
+      </c>
+      <c r="AI39" t="n">
+        <v>183.4932291666667</v>
+      </c>
+      <c r="AJ39" t="n">
+        <v>1.250286835748792</v>
+      </c>
+      <c r="AK39" t="n">
+        <v>73.52358846618358</v>
+      </c>
+      <c r="AL39" t="n">
+        <v>8283535.250603864</v>
+      </c>
+      <c r="AM39" t="n">
+        <v>78.12027475845412</v>
+      </c>
+      <c r="AN39" t="inlineStr"/>
+      <c r="AO39" t="inlineStr">
+        <is>
+          <t>vZA6VYpf</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="inlineStr">
+        <is>
+          <t>pAXo2Kvn</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="n">
+        <v>45523.65625</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">zwayer f 
+  ger </t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">eintracht stadion
+  braunschweig </t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>23325</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>QqLCC3il</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>8vndvXTk</t>
+        </is>
+      </c>
+      <c r="H40" t="n">
+        <v>59</v>
+      </c>
+      <c r="I40" t="n">
+        <v>593</v>
+      </c>
+      <c r="J40" t="n">
+        <v>1</v>
+      </c>
+      <c r="K40" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>dfb pokal</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>dfNCCCzS</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>EuakNmc1</t>
+        </is>
+      </c>
+      <c r="P40" t="n">
+        <v>25.52840909090909</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>184.4431818181818</v>
+      </c>
+      <c r="R40" t="n">
+        <v>1.076136363636364</v>
+      </c>
+      <c r="S40" t="n">
+        <v>67.3875</v>
+      </c>
+      <c r="T40" t="n">
+        <v>1403750</v>
+      </c>
+      <c r="U40" t="n">
+        <v>71.15113636363637</v>
+      </c>
+      <c r="V40" t="n">
+        <v>24.12986111111111</v>
+      </c>
+      <c r="W40" t="n">
+        <v>183.3236111111111</v>
+      </c>
+      <c r="X40" t="n">
+        <v>1.685416666666667</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>76.91875</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>15628576.38888889</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>81.29375</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>25.95992063492063</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>182.7220238095238</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE40" t="n">
+        <v>66.7140873015873</v>
+      </c>
+      <c r="AF40" t="n">
+        <v>1283915.674603175</v>
+      </c>
+      <c r="AG40" t="n">
+        <v>70.22817460317461</v>
+      </c>
+      <c r="AH40" t="n">
+        <v>24.54544700655381</v>
+      </c>
+      <c r="AI40" t="n">
+        <v>183.7037129086084</v>
+      </c>
+      <c r="AJ40" t="n">
+        <v>1.428440565819629</v>
+      </c>
+      <c r="AK40" t="n">
+        <v>71.82038192071087</v>
+      </c>
+      <c r="AL40" t="n">
+        <v>5729574.593967372</v>
+      </c>
+      <c r="AM40" t="n">
+        <v>78.21237818392908</v>
+      </c>
+      <c r="AN40" t="inlineStr">
+        <is>
+          <t>txZLBQVC</t>
+        </is>
+      </c>
+      <c r="AO40" t="inlineStr">
+        <is>
+          <t>pfoInmcq</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="inlineStr">
+        <is>
           <t>fcxqFy2l</t>
         </is>
       </c>
-      <c r="B33" s="2" t="n">
+      <c r="B41" s="2" t="n">
         <v>45521.64583333334</v>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="C41" t="inlineStr">
         <is>
           <t xml:space="preserve">schlager d 
   ger </t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
+      <c r="D41" t="inlineStr">
         <is>
           <t xml:space="preserve">bayarena
   leverkusen </t>
         </is>
       </c>
-      <c r="E33" t="n">
+      <c r="E41" t="n">
         <v>30210</v>
       </c>
-      <c r="F33" t="inlineStr">
+      <c r="F41" t="inlineStr">
         <is>
           <t>4jcj2zMd</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
+      <c r="G41" t="inlineStr">
         <is>
           <t>nJQmYp1B</t>
         </is>
       </c>
-      <c r="H33" t="n">
+      <c r="H41" t="n">
         <v>59</v>
       </c>
-      <c r="I33" t="n">
+      <c r="I41" t="n">
         <v>594</v>
       </c>
-      <c r="J33" t="n">
-        <v>1</v>
-      </c>
-      <c r="K33" t="n">
+      <c r="J41" t="n">
+        <v>1</v>
+      </c>
+      <c r="K41" t="n">
         <v>2024</v>
       </c>
-      <c r="L33" t="inlineStr">
+      <c r="L41" t="inlineStr">
         <is>
           <t>germany</t>
         </is>
       </c>
-      <c r="M33" t="inlineStr">
+      <c r="M41" t="inlineStr">
         <is>
           <t>super cup</t>
         </is>
       </c>
-      <c r="N33" t="inlineStr">
+      <c r="N41" t="inlineStr">
         <is>
           <t>WG9pOTse</t>
         </is>
       </c>
-      <c r="O33" t="inlineStr">
+      <c r="O41" t="inlineStr">
         <is>
           <t>fiEQZ7C7</t>
         </is>
       </c>
-      <c r="P33" t="n">
-        <v>25.63939393939394</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>185.3989898989899</v>
-      </c>
-      <c r="R33" t="n">
-        <v>2.018181818181818</v>
-      </c>
-      <c r="S33" t="n">
-        <v>81.13333333333334</v>
-      </c>
-      <c r="T33" t="n">
-        <v>31332828.28282828</v>
-      </c>
-      <c r="U33" t="n">
-        <v>84.04242424242423</v>
-      </c>
-      <c r="V33" t="n">
-        <v>24.40909090909091</v>
-      </c>
-      <c r="W33" t="n">
-        <v>184.6454545454546</v>
-      </c>
-      <c r="X33" t="n">
-        <v>1.490909090909091</v>
-      </c>
-      <c r="Y33" t="n">
-        <v>76</v>
-      </c>
-      <c r="Z33" t="n">
-        <v>11738181.81818181</v>
-      </c>
-      <c r="AA33" t="n">
-        <v>79.16363636363636</v>
-      </c>
-      <c r="AB33" t="n">
-        <v>22.87297666102014</v>
-      </c>
-      <c r="AC33" t="n">
-        <v>181.3535983779067</v>
-      </c>
-      <c r="AD33" t="n">
-        <v>1.797712300874356</v>
-      </c>
-      <c r="AE33" t="n">
-        <v>78.8402785620177</v>
-      </c>
-      <c r="AF33" t="n">
-        <v>36662927.46778912</v>
-      </c>
-      <c r="AG33" t="n">
-        <v>84.46393237855688</v>
-      </c>
-      <c r="AH33" t="n">
-        <v>24.40472222222222</v>
-      </c>
-      <c r="AI33" t="n">
-        <v>182.5288888888889</v>
-      </c>
-      <c r="AJ33" t="n">
-        <v>1.280753968253968</v>
-      </c>
-      <c r="AK33" t="n">
-        <v>71.27392857142857</v>
-      </c>
-      <c r="AL33" t="n">
-        <v>5835730.158730159</v>
-      </c>
-      <c r="AM33" t="n">
-        <v>75.7297619047619</v>
-      </c>
-      <c r="AN33" t="inlineStr">
+      <c r="P41" t="n">
+        <v>25.54680134680135</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>184.8402918069585</v>
+      </c>
+      <c r="R41" t="n">
+        <v>2.118181818181818</v>
+      </c>
+      <c r="S41" t="n">
+        <v>81.5117845117845</v>
+      </c>
+      <c r="T41" t="n">
+        <v>35277132.43546578</v>
+      </c>
+      <c r="U41" t="n">
+        <v>84.32390572390571</v>
+      </c>
+      <c r="V41" t="n">
+        <v>24.42613636363636</v>
+      </c>
+      <c r="W41" t="n">
+        <v>184.5852272727273</v>
+      </c>
+      <c r="X41" t="n">
+        <v>1.545454545454545</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>76.29545454545455</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>12134090.90909091</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>79.20454545454545</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>23.08555340646302</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>181.9279143387124</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>1.665550583199324</v>
+      </c>
+      <c r="AE41" t="n">
+        <v>78.42933481045608</v>
+      </c>
+      <c r="AF41" t="n">
+        <v>31689830.46590455</v>
+      </c>
+      <c r="AG41" t="n">
+        <v>84.08272580193346</v>
+      </c>
+      <c r="AH41" t="n">
+        <v>24.19603174603175</v>
+      </c>
+      <c r="AI41" t="n">
+        <v>182.6951388888889</v>
+      </c>
+      <c r="AJ41" t="n">
+        <v>1.257316468253968</v>
+      </c>
+      <c r="AK41" t="n">
+        <v>71.08415178571428</v>
+      </c>
+      <c r="AL41" t="n">
+        <v>5528934.771825397</v>
+      </c>
+      <c r="AM41" t="n">
+        <v>75.84040178571428</v>
+      </c>
+      <c r="AN41" t="inlineStr">
         <is>
           <t>2BYSk4KO</t>
         </is>
       </c>
-      <c r="AO33" t="inlineStr">
+      <c r="AO41" t="inlineStr">
         <is>
           <t>M5BRZDsC</t>
         </is>

--- a/data/germany/p6_deployment/data_preparation/df_filled.xlsx
+++ b/data/germany/p6_deployment/data_preparation/df_filled.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO21"/>
+  <dimension ref="A1:AV19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -505,130 +505,165 @@
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
+          <t>mean_age_player_miss_home</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>mean_hei_player_miss_home</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>mean_int_rep_player_miss_home</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>n_player_miss_home</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>sum_rat_player_miss_home</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>sum_val_player_miss_home</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>sum_pot_player_miss_home</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
           <t>mean_age_player_start_home</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>mean_hei_player_start_home</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>mean_int_rep_player_start_home</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>mean_rat_player_start_home</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>mean_val_player_start_home</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>mean_pot_player_start_home</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>mean_age_player_start_away</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>mean_hei_player_start_away</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>mean_int_rep_player_start_away</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>mean_rat_player_start_away</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>mean_val_player_start_away</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>mean_pot_player_start_away</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>mean_age_player_sub_home</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>mean_hei_player_sub_home</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>mean_int_rep_player_sub_home</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>mean_rat_player_sub_home</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>mean_val_player_sub_home</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>mean_pot_player_sub_home</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>mean_age_player_sub_away</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>mean_hei_player_sub_away</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>mean_int_rep_player_sub_away</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>mean_rat_player_sub_away</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>mean_val_player_sub_away</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>mean_pot_player_sub_away</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>id_coach_home</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>id_coach_away</t>
         </is>
@@ -701,83 +736,104 @@
         </is>
       </c>
       <c r="P2" t="n">
+        <v>20.33333333333333</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>179.3333333333333</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1</v>
+      </c>
+      <c r="S2" t="n">
+        <v>3</v>
+      </c>
+      <c r="T2" t="n">
+        <v>199</v>
+      </c>
+      <c r="U2" t="n">
+        <v>8225000</v>
+      </c>
+      <c r="V2" t="n">
+        <v>231</v>
+      </c>
+      <c r="W2" t="n">
         <v>25.17367003367003</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="X2" t="n">
         <v>184.620202020202</v>
       </c>
-      <c r="R2" t="n">
+      <c r="Y2" t="n">
         <v>1.515959595959596</v>
       </c>
-      <c r="S2" t="n">
+      <c r="Z2" t="n">
         <v>75.27043771043772</v>
       </c>
-      <c r="T2" t="n">
+      <c r="AA2" t="n">
         <v>8491050.505050505</v>
       </c>
-      <c r="U2" t="n">
+      <c r="AB2" t="n">
         <v>78.22101010101009</v>
       </c>
-      <c r="V2" t="n">
+      <c r="AC2" t="n">
         <v>25.61907308377896</v>
       </c>
-      <c r="W2" t="n">
+      <c r="AD2" t="n">
         <v>184.9906565656566</v>
       </c>
-      <c r="X2" t="n">
+      <c r="AE2" t="n">
         <v>2.085695187165775</v>
       </c>
-      <c r="Y2" t="n">
+      <c r="AF2" t="n">
         <v>81.3868092691622</v>
       </c>
-      <c r="Z2" t="n">
+      <c r="AG2" t="n">
         <v>34021375.51990493</v>
       </c>
-      <c r="AA2" t="n">
+      <c r="AH2" t="n">
         <v>84.2319964349376</v>
       </c>
-      <c r="AB2" t="n">
+      <c r="AI2" t="n">
         <v>23.28772692601068</v>
       </c>
-      <c r="AC2" t="n">
+      <c r="AJ2" t="n">
         <v>184.160701754386</v>
       </c>
-      <c r="AD2" t="n">
+      <c r="AK2" t="n">
         <v>1.280188151538266</v>
       </c>
-      <c r="AE2" t="n">
+      <c r="AL2" t="n">
         <v>72.91982047510079</v>
       </c>
-      <c r="AF2" t="n">
+      <c r="AM2" t="n">
         <v>6706858.069085757</v>
       </c>
-      <c r="AG2" t="n">
+      <c r="AN2" t="n">
         <v>78.60991663942465</v>
       </c>
-      <c r="AH2" t="n">
+      <c r="AO2" t="n">
         <v>23.09709856482639</v>
       </c>
-      <c r="AI2" t="n">
+      <c r="AP2" t="n">
         <v>181.8285059384686</v>
       </c>
-      <c r="AJ2" t="n">
+      <c r="AQ2" t="n">
         <v>1.720316864003767</v>
       </c>
-      <c r="AK2" t="n">
+      <c r="AR2" t="n">
         <v>78.82048615784986</v>
       </c>
-      <c r="AL2" t="n">
+      <c r="AS2" t="n">
         <v>33966312.08994935</v>
       </c>
-      <c r="AM2" t="n">
+      <c r="AT2" t="n">
         <v>84.26231191353179</v>
       </c>
-      <c r="AN2" t="inlineStr">
+      <c r="AU2" t="inlineStr">
         <is>
           <t>rPfNaCdg</t>
         </is>
       </c>
-      <c r="AO2" t="inlineStr">
+      <c r="AV2" t="inlineStr">
         <is>
           <t>GzfvcwRj</t>
         </is>
@@ -845,84 +901,91 @@
           <t>v9k3aY5F</t>
         </is>
       </c>
-      <c r="P3" t="n">
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr"/>
+      <c r="W3" t="n">
         <v>25.3987037037037</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="X3" t="n">
         <v>185.8592424242424</v>
       </c>
-      <c r="R3" t="n">
+      <c r="Y3" t="n">
         <v>1.414326599326599</v>
       </c>
-      <c r="S3" t="n">
+      <c r="Z3" t="n">
         <v>74.34148148148148</v>
       </c>
-      <c r="T3" t="n">
+      <c r="AA3" t="n">
         <v>6432727.272727272</v>
       </c>
-      <c r="U3" t="n">
+      <c r="AB3" t="n">
         <v>77.28441077441077</v>
       </c>
-      <c r="V3" t="n">
+      <c r="AC3" t="n">
         <v>26.01212121212121</v>
       </c>
-      <c r="W3" t="n">
+      <c r="AD3" t="n">
         <v>183.3757575757576</v>
       </c>
-      <c r="X3" t="n">
+      <c r="AE3" t="n">
         <v>1.16969696969697</v>
       </c>
-      <c r="Y3" t="n">
+      <c r="AF3" t="n">
         <v>73.21212121212122</v>
       </c>
-      <c r="Z3" t="n">
+      <c r="AG3" t="n">
         <v>4874848.484848485</v>
       </c>
-      <c r="AA3" t="n">
+      <c r="AH3" t="n">
         <v>76.13333333333334</v>
       </c>
-      <c r="AB3" t="n">
+      <c r="AI3" t="n">
         <v>23.90786783878889</v>
       </c>
-      <c r="AC3" t="n">
+      <c r="AJ3" t="n">
         <v>184.0711136426926</v>
       </c>
-      <c r="AD3" t="n">
+      <c r="AK3" t="n">
         <v>1.151816599579758</v>
       </c>
-      <c r="AE3" t="n">
+      <c r="AL3" t="n">
         <v>71.11281442241969</v>
       </c>
-      <c r="AF3" t="n">
+      <c r="AM3" t="n">
         <v>3876240.913204729</v>
       </c>
-      <c r="AG3" t="n">
+      <c r="AN3" t="n">
         <v>76.49320833649782</v>
       </c>
-      <c r="AH3" t="n">
+      <c r="AO3" t="n">
         <v>24.83106351236146</v>
       </c>
-      <c r="AI3" t="n">
+      <c r="AP3" t="n">
         <v>184.539776453424</v>
       </c>
-      <c r="AJ3" t="n">
+      <c r="AQ3" t="n">
         <v>1.169217596776824</v>
       </c>
-      <c r="AK3" t="n">
+      <c r="AR3" t="n">
         <v>68.44581405916041</v>
       </c>
-      <c r="AL3" t="n">
+      <c r="AS3" t="n">
         <v>2549719.765989284</v>
       </c>
-      <c r="AM3" t="n">
+      <c r="AT3" t="n">
         <v>74.16400905645757</v>
       </c>
-      <c r="AN3" t="inlineStr">
+      <c r="AU3" t="inlineStr">
         <is>
           <t>CCww5Qfo</t>
         </is>
       </c>
-      <c r="AO3" t="inlineStr">
+      <c r="AV3" t="inlineStr">
         <is>
           <t>4fuCGs9P</t>
         </is>
@@ -994,84 +1057,91 @@
           <t>fiEQZ7C7</t>
         </is>
       </c>
-      <c r="P4" t="n">
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="n">
         <v>27.19259259259259</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="X4" t="n">
         <v>183.6707070707071</v>
       </c>
-      <c r="R4" t="n">
+      <c r="Y4" t="n">
         <v>1.694276094276094</v>
       </c>
-      <c r="S4" t="n">
+      <c r="Z4" t="n">
         <v>75.32255892255893</v>
       </c>
-      <c r="T4" t="n">
+      <c r="AA4" t="n">
         <v>8525252.525252525</v>
       </c>
-      <c r="U4" t="n">
+      <c r="AB4" t="n">
         <v>77.13265993265992</v>
       </c>
-      <c r="V4" t="n">
+      <c r="AC4" t="n">
         <v>24.38848484848485</v>
       </c>
-      <c r="W4" t="n">
+      <c r="AD4" t="n">
         <v>184.5909090909091</v>
       </c>
-      <c r="X4" t="n">
+      <c r="AE4" t="n">
         <v>1.516969696969697</v>
       </c>
-      <c r="Y4" t="n">
+      <c r="AF4" t="n">
         <v>76.14606060606062</v>
       </c>
-      <c r="Z4" t="n">
+      <c r="AG4" t="n">
         <v>11904909.09090909</v>
       </c>
-      <c r="AA4" t="n">
+      <c r="AH4" t="n">
         <v>79.19939393939394</v>
       </c>
-      <c r="AB4" t="n">
+      <c r="AI4" t="n">
         <v>24.970719370891</v>
       </c>
-      <c r="AC4" t="n">
+      <c r="AJ4" t="n">
         <v>184.6744885765137</v>
       </c>
-      <c r="AD4" t="n">
+      <c r="AK4" t="n">
         <v>1.444793868729796</v>
       </c>
-      <c r="AE4" t="n">
+      <c r="AL4" t="n">
         <v>73.33173931204824</v>
       </c>
-      <c r="AF4" t="n">
+      <c r="AM4" t="n">
         <v>6040617.621953433</v>
       </c>
-      <c r="AG4" t="n">
+      <c r="AN4" t="n">
         <v>76.71675356870438</v>
       </c>
-      <c r="AH4" t="n">
+      <c r="AO4" t="n">
         <v>24.20182539682539</v>
       </c>
-      <c r="AI4" t="n">
+      <c r="AP4" t="n">
         <v>182.7644973544974</v>
       </c>
-      <c r="AJ4" t="n">
+      <c r="AQ4" t="n">
         <v>1.250793650793651</v>
       </c>
-      <c r="AK4" t="n">
+      <c r="AR4" t="n">
         <v>71.08301587301588</v>
       </c>
-      <c r="AL4" t="n">
+      <c r="AS4" t="n">
         <v>5481326.719576719</v>
       </c>
-      <c r="AM4" t="n">
+      <c r="AT4" t="n">
         <v>75.89417989417989</v>
       </c>
-      <c r="AN4" t="inlineStr">
+      <c r="AU4" t="inlineStr">
         <is>
           <t>lxrr7DgN</t>
         </is>
       </c>
-      <c r="AO4" t="inlineStr">
+      <c r="AV4" t="inlineStr">
         <is>
           <t>GzfvcwRj</t>
         </is>
@@ -1143,84 +1213,91 @@
           <t>ILyJuN3g</t>
         </is>
       </c>
-      <c r="P5" t="n">
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="n">
         <v>26.48080808080808</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="X5" t="n">
         <v>185.6835016835017</v>
       </c>
-      <c r="R5" t="n">
+      <c r="Y5" t="n">
         <v>1.803367003367003</v>
       </c>
-      <c r="S5" t="n">
+      <c r="Z5" t="n">
         <v>75.05117845117846</v>
       </c>
-      <c r="T5" t="n">
+      <c r="AA5" t="n">
         <v>8855387.205387207</v>
       </c>
-      <c r="U5" t="n">
+      <c r="AB5" t="n">
         <v>78.73804713804712</v>
       </c>
-      <c r="V5" t="n">
+      <c r="AC5" t="n">
         <v>25.19191919191919</v>
       </c>
-      <c r="W5" t="n">
+      <c r="AD5" t="n">
         <v>186.149494949495</v>
       </c>
-      <c r="X5" t="n">
+      <c r="AE5" t="n">
         <v>1.081818181818182</v>
       </c>
-      <c r="Y5" t="n">
+      <c r="AF5" t="n">
         <v>68.6010101010101</v>
       </c>
-      <c r="Z5" t="n">
+      <c r="AG5" t="n">
         <v>1771818.181818182</v>
       </c>
-      <c r="AA5" t="n">
+      <c r="AH5" t="n">
         <v>72.58080808080808</v>
       </c>
-      <c r="AB5" t="n">
+      <c r="AI5" t="n">
         <v>24.60507314036726</v>
       </c>
-      <c r="AC5" t="n">
+      <c r="AJ5" t="n">
         <v>185.0131652661065</v>
       </c>
-      <c r="AD5" t="n">
+      <c r="AK5" t="n">
         <v>1.403680361033302</v>
       </c>
-      <c r="AE5" t="n">
+      <c r="AL5" t="n">
         <v>71.80881574852164</v>
       </c>
-      <c r="AF5" t="n">
+      <c r="AM5" t="n">
         <v>5458608.77684407</v>
       </c>
-      <c r="AG5" t="n">
+      <c r="AN5" t="n">
         <v>77.65164954870836</v>
       </c>
-      <c r="AH5" t="n">
+      <c r="AO5" t="n">
         <v>25.09037362932291</v>
       </c>
-      <c r="AI5" t="n">
+      <c r="AP5" t="n">
         <v>186.1050389157273</v>
       </c>
-      <c r="AJ5" t="n">
+      <c r="AQ5" t="n">
         <v>1.010121923165401</v>
       </c>
-      <c r="AK5" t="n">
+      <c r="AR5" t="n">
         <v>66.44403228280039</v>
       </c>
-      <c r="AL5" t="n">
+      <c r="AS5" t="n">
         <v>1363103.505291005</v>
       </c>
-      <c r="AM5" t="n">
+      <c r="AT5" t="n">
         <v>71.09151905528716</v>
       </c>
-      <c r="AN5" t="inlineStr">
+      <c r="AU5" t="inlineStr">
         <is>
           <t>lEwgk7go</t>
         </is>
       </c>
-      <c r="AO5" t="inlineStr">
+      <c r="AV5" t="inlineStr">
         <is>
           <t>A15eUM4C</t>
         </is>
@@ -1288,84 +1365,91 @@
         </is>
       </c>
       <c r="O6" t="inlineStr"/>
-      <c r="P6" t="n">
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="n">
         <v>25.77030303030303</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="X6" t="n">
         <v>183.2272727272727</v>
       </c>
-      <c r="R6" t="n">
+      <c r="Y6" t="n">
         <v>1.572727272727272</v>
       </c>
-      <c r="S6" t="n">
+      <c r="Z6" t="n">
         <v>74.43151515151516</v>
       </c>
-      <c r="T6" t="n">
+      <c r="AA6" t="n">
         <v>6764848.484848485</v>
       </c>
-      <c r="U6" t="n">
+      <c r="AB6" t="n">
         <v>78.35939393939394</v>
       </c>
-      <c r="V6" t="n">
+      <c r="AC6" t="n">
         <v>26.91515151515152</v>
       </c>
-      <c r="W6" t="n">
+      <c r="AD6" t="n">
         <v>184.9703703703704</v>
       </c>
-      <c r="X6" t="n">
+      <c r="AE6" t="n">
         <v>1.614141414141414</v>
       </c>
-      <c r="Y6" t="n">
+      <c r="AF6" t="n">
         <v>75.77508417508419</v>
       </c>
-      <c r="Z6" t="n">
+      <c r="AG6" t="n">
         <v>8399797.97979798</v>
       </c>
-      <c r="AA6" t="n">
+      <c r="AH6" t="n">
         <v>78.1905723905724</v>
       </c>
-      <c r="AB6" t="n">
+      <c r="AI6" t="n">
         <v>26.12653439153439</v>
       </c>
-      <c r="AC6" t="n">
+      <c r="AJ6" t="n">
         <v>185.0814814814815</v>
       </c>
-      <c r="AD6" t="n">
+      <c r="AK6" t="n">
         <v>1.494656084656085</v>
       </c>
-      <c r="AE6" t="n">
+      <c r="AL6" t="n">
         <v>72.38201058201057</v>
       </c>
-      <c r="AF6" t="n">
+      <c r="AM6" t="n">
         <v>4546836.64021164</v>
       </c>
-      <c r="AG6" t="n">
+      <c r="AN6" t="n">
         <v>76.68412698412698</v>
       </c>
-      <c r="AH6" t="n">
+      <c r="AO6" t="n">
         <v>26.9223423897909</v>
       </c>
-      <c r="AI6" t="n">
+      <c r="AP6" t="n">
         <v>184.1517050476433</v>
       </c>
-      <c r="AJ6" t="n">
+      <c r="AQ6" t="n">
         <v>1.471773939680118</v>
       </c>
-      <c r="AK6" t="n">
+      <c r="AR6" t="n">
         <v>73.81049877108229</v>
       </c>
-      <c r="AL6" t="n">
+      <c r="AS6" t="n">
         <v>5227253.898635478</v>
       </c>
-      <c r="AM6" t="n">
+      <c r="AT6" t="n">
         <v>76.12306611940478</v>
       </c>
-      <c r="AN6" t="inlineStr">
+      <c r="AU6" t="inlineStr">
         <is>
           <t>QTAUlvUP</t>
         </is>
       </c>
-      <c r="AO6" t="inlineStr">
+      <c r="AV6" t="inlineStr">
         <is>
           <t>hpYJ6izc</t>
         </is>
@@ -1437,84 +1521,91 @@
           <t>0Ija0Ej9</t>
         </is>
       </c>
-      <c r="P7" t="n">
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="n">
         <v>24.85090909090909</v>
       </c>
-      <c r="Q7" t="n">
+      <c r="X7" t="n">
         <v>182.64</v>
       </c>
-      <c r="R7" t="n">
+      <c r="Y7" t="n">
         <v>2.106666666666666</v>
       </c>
-      <c r="S7" t="n">
+      <c r="Z7" t="n">
         <v>80.28</v>
       </c>
-      <c r="T7" t="n">
+      <c r="AA7" t="n">
         <v>28992121.21212121</v>
       </c>
-      <c r="U7" t="n">
+      <c r="AB7" t="n">
         <v>83.77575757575758</v>
       </c>
-      <c r="V7" t="n">
+      <c r="AC7" t="n">
         <v>27.88888888888889</v>
       </c>
-      <c r="W7" t="n">
+      <c r="AD7" t="n">
         <v>182.4091503267974</v>
       </c>
-      <c r="X7" t="n">
+      <c r="AE7" t="n">
         <v>1.247712418300653</v>
       </c>
-      <c r="Y7" t="n">
+      <c r="AF7" t="n">
         <v>73.13856209150327</v>
       </c>
-      <c r="Z7" t="n">
+      <c r="AG7" t="n">
         <v>3579689.54248366</v>
       </c>
-      <c r="AA7" t="n">
+      <c r="AH7" t="n">
         <v>75.03398692810457</v>
       </c>
-      <c r="AB7" t="n">
+      <c r="AI7" t="n">
         <v>24.82412804586718</v>
       </c>
-      <c r="AC7" t="n">
+      <c r="AJ7" t="n">
         <v>185.1450257471997</v>
       </c>
-      <c r="AD7" t="n">
+      <c r="AK7" t="n">
         <v>1.702190723929854</v>
       </c>
-      <c r="AE7" t="n">
+      <c r="AL7" t="n">
         <v>76.87710666949798</v>
       </c>
-      <c r="AF7" t="n">
+      <c r="AM7" t="n">
         <v>18126442.72796446</v>
       </c>
-      <c r="AG7" t="n">
+      <c r="AN7" t="n">
         <v>81.50249376227637</v>
       </c>
-      <c r="AH7" t="n">
+      <c r="AO7" t="n">
         <v>26.78760504201681</v>
       </c>
-      <c r="AI7" t="n">
+      <c r="AP7" t="n">
         <v>182.8982285841318</v>
       </c>
-      <c r="AJ7" t="n">
+      <c r="AQ7" t="n">
         <v>1.064620737692483</v>
       </c>
-      <c r="AK7" t="n">
+      <c r="AR7" t="n">
         <v>70.48407930816735</v>
       </c>
-      <c r="AL7" t="n">
+      <c r="AS7" t="n">
         <v>2374219.376147588</v>
       </c>
-      <c r="AM7" t="n">
+      <c r="AT7" t="n">
         <v>73.50472590013746</v>
       </c>
-      <c r="AN7" t="inlineStr">
+      <c r="AU7" t="inlineStr">
         <is>
           <t>0KMe4S4D</t>
         </is>
       </c>
-      <c r="AO7" t="inlineStr">
+      <c r="AV7" t="inlineStr">
         <is>
           <t>8f6APkLc</t>
         </is>
@@ -1586,84 +1677,91 @@
           <t>EuakNmc1</t>
         </is>
       </c>
-      <c r="P8" t="n">
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" t="n">
         <v>25.38787878787879</v>
       </c>
-      <c r="Q8" t="n">
+      <c r="X8" t="n">
         <v>184.8551515151515</v>
       </c>
-      <c r="R8" t="n">
+      <c r="Y8" t="n">
         <v>2.293939393939394</v>
       </c>
-      <c r="S8" t="n">
+      <c r="Z8" t="n">
         <v>80</v>
       </c>
-      <c r="T8" t="n">
+      <c r="AA8" t="n">
         <v>29471515.15151515</v>
       </c>
-      <c r="U8" t="n">
+      <c r="AB8" t="n">
         <v>83.26060606060607</v>
       </c>
-      <c r="V8" t="n">
+      <c r="AC8" t="n">
         <v>24.13851851851852</v>
       </c>
-      <c r="W8" t="n">
+      <c r="AD8" t="n">
         <v>183.3451851851852</v>
       </c>
-      <c r="X8" t="n">
+      <c r="AE8" t="n">
         <v>1.671851851851852</v>
       </c>
-      <c r="Y8" t="n">
+      <c r="AF8" t="n">
         <v>76.8762962962963</v>
       </c>
-      <c r="Z8" t="n">
+      <c r="AG8" t="n">
         <v>15500111.11111111</v>
       </c>
-      <c r="AA8" t="n">
+      <c r="AH8" t="n">
         <v>81.26148148148148</v>
       </c>
-      <c r="AB8" t="n">
+      <c r="AI8" t="n">
         <v>25.00185185185186</v>
       </c>
-      <c r="AC8" t="n">
+      <c r="AJ8" t="n">
         <v>183.9712962962963</v>
       </c>
-      <c r="AD8" t="n">
+      <c r="AK8" t="n">
         <v>1.993518518518518</v>
       </c>
-      <c r="AE8" t="n">
+      <c r="AL8" t="n">
         <v>77.60859788359788</v>
       </c>
-      <c r="AF8" t="n">
+      <c r="AM8" t="n">
         <v>19937235.44973545</v>
       </c>
-      <c r="AG8" t="n">
+      <c r="AN8" t="n">
         <v>82.17949735449734</v>
       </c>
-      <c r="AH8" t="n">
+      <c r="AO8" t="n">
         <v>23.98952943856968</v>
       </c>
-      <c r="AI8" t="n">
+      <c r="AP8" t="n">
         <v>183.9351885060244</v>
       </c>
-      <c r="AJ8" t="n">
+      <c r="AQ8" t="n">
         <v>1.404722568453219</v>
       </c>
-      <c r="AK8" t="n">
+      <c r="AR8" t="n">
         <v>71.51946001367054</v>
       </c>
-      <c r="AL8" t="n">
+      <c r="AS8" t="n">
         <v>5542197.549354671</v>
       </c>
-      <c r="AM8" t="n">
+      <c r="AT8" t="n">
         <v>78.49802795759453</v>
       </c>
-      <c r="AN8" t="inlineStr">
+      <c r="AU8" t="inlineStr">
         <is>
           <t>AgnJojCs</t>
         </is>
       </c>
-      <c r="AO8" t="inlineStr">
+      <c r="AV8" t="inlineStr">
         <is>
           <t>UgdQz0fK</t>
         </is>
@@ -1731,84 +1829,91 @@
         </is>
       </c>
       <c r="O9" t="inlineStr"/>
-      <c r="P9" t="n">
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="n">
         <v>25.39407407407408</v>
       </c>
-      <c r="Q9" t="n">
+      <c r="X9" t="n">
         <v>186.6725925925926</v>
       </c>
-      <c r="R9" t="n">
+      <c r="Y9" t="n">
         <v>1.564444444444444</v>
       </c>
-      <c r="S9" t="n">
+      <c r="Z9" t="n">
         <v>75.71333333333332</v>
       </c>
-      <c r="T9" t="n">
+      <c r="AA9" t="n">
         <v>10651407.40740741</v>
       </c>
-      <c r="U9" t="n">
+      <c r="AB9" t="n">
         <v>79.47703703703704</v>
       </c>
-      <c r="V9" t="n">
+      <c r="AC9" t="n">
         <v>27.08484848484849</v>
       </c>
-      <c r="W9" t="n">
+      <c r="AD9" t="n">
         <v>184.9212121212121</v>
       </c>
-      <c r="X9" t="n">
+      <c r="AE9" t="n">
         <v>3.03030303030303</v>
       </c>
-      <c r="Y9" t="n">
+      <c r="AF9" t="n">
         <v>81.87878787878786</v>
       </c>
-      <c r="Z9" t="n">
+      <c r="AG9" t="n">
         <v>41254848.48484848</v>
       </c>
-      <c r="AA9" t="n">
+      <c r="AH9" t="n">
         <v>84.53333333333333</v>
       </c>
-      <c r="AB9" t="n">
+      <c r="AI9" t="n">
         <v>24.12706119162641</v>
       </c>
-      <c r="AC9" t="n">
+      <c r="AJ9" t="n">
         <v>183.7472222222222</v>
       </c>
-      <c r="AD9" t="n">
+      <c r="AK9" t="n">
         <v>1.246602254428341</v>
       </c>
-      <c r="AE9" t="n">
+      <c r="AL9" t="n">
         <v>73.50627214170693</v>
       </c>
-      <c r="AF9" t="n">
+      <c r="AM9" t="n">
         <v>8361891.304347825</v>
       </c>
-      <c r="AG9" t="n">
+      <c r="AN9" t="n">
         <v>78.35681159420291</v>
       </c>
-      <c r="AH9" t="n">
+      <c r="AO9" t="n">
         <v>24.6207077440689</v>
       </c>
-      <c r="AI9" t="n">
+      <c r="AP9" t="n">
         <v>182.3024630782438</v>
       </c>
-      <c r="AJ9" t="n">
+      <c r="AQ9" t="n">
         <v>2.250397657387158</v>
       </c>
-      <c r="AK9" t="n">
+      <c r="AR9" t="n">
         <v>78.52101362272482</v>
       </c>
-      <c r="AL9" t="n">
+      <c r="AS9" t="n">
         <v>29928093.12285289</v>
       </c>
-      <c r="AM9" t="n">
+      <c r="AT9" t="n">
         <v>83.50805072369886</v>
       </c>
-      <c r="AN9" t="inlineStr">
+      <c r="AU9" t="inlineStr">
         <is>
           <t>rFNN7oyi</t>
         </is>
       </c>
-      <c r="AO9" t="inlineStr">
+      <c r="AV9" t="inlineStr">
         <is>
           <t>K6A2elS9</t>
         </is>
@@ -1876,84 +1981,91 @@
         </is>
       </c>
       <c r="O10" t="inlineStr"/>
-      <c r="P10" t="n">
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="inlineStr"/>
+      <c r="W10" t="n">
         <v>25.85084175084175</v>
       </c>
-      <c r="Q10" t="n">
+      <c r="X10" t="n">
         <v>185.2088664421998</v>
       </c>
-      <c r="R10" t="n">
+      <c r="Y10" t="n">
         <v>1</v>
       </c>
-      <c r="S10" t="n">
+      <c r="Z10" t="n">
         <v>69.99135802469135</v>
       </c>
-      <c r="T10" t="n">
+      <c r="AA10" t="n">
         <v>2277025.81369248</v>
       </c>
-      <c r="U10" t="n">
+      <c r="AB10" t="n">
         <v>73.08237934904601</v>
       </c>
-      <c r="V10" t="n">
+      <c r="AC10" t="n">
         <v>25.81666666666667</v>
       </c>
-      <c r="W10" t="n">
+      <c r="AD10" t="n">
         <v>186.9015151515151</v>
       </c>
-      <c r="X10" t="n">
+      <c r="AE10" t="n">
         <v>1</v>
       </c>
-      <c r="Y10" t="n">
+      <c r="AF10" t="n">
         <v>72.875</v>
       </c>
-      <c r="Z10" t="n">
+      <c r="AG10" t="n">
         <v>4350833.333333333</v>
       </c>
-      <c r="AA10" t="n">
+      <c r="AH10" t="n">
         <v>75.22045454545453</v>
       </c>
-      <c r="AB10" t="n">
+      <c r="AI10" t="n">
         <v>25.74994662582382</v>
       </c>
-      <c r="AC10" t="n">
+      <c r="AJ10" t="n">
         <v>185.8726074445373</v>
       </c>
-      <c r="AD10" t="n">
+      <c r="AK10" t="n">
         <v>1</v>
       </c>
-      <c r="AE10" t="n">
+      <c r="AL10" t="n">
         <v>66.84020235774622</v>
       </c>
-      <c r="AF10" t="n">
+      <c r="AM10" t="n">
         <v>1325721.479624988</v>
       </c>
-      <c r="AG10" t="n">
+      <c r="AN10" t="n">
         <v>71.29296853244222</v>
       </c>
-      <c r="AH10" t="n">
+      <c r="AO10" t="n">
         <v>27.03253968253968</v>
       </c>
-      <c r="AI10" t="n">
+      <c r="AP10" t="n">
         <v>183.2093915343915</v>
       </c>
-      <c r="AJ10" t="n">
+      <c r="AQ10" t="n">
         <v>1</v>
       </c>
-      <c r="AK10" t="n">
+      <c r="AR10" t="n">
         <v>69.32208994708995</v>
       </c>
-      <c r="AL10" t="n">
+      <c r="AS10" t="n">
         <v>1942023.809523809</v>
       </c>
-      <c r="AM10" t="n">
+      <c r="AT10" t="n">
         <v>71.08320105820106</v>
       </c>
-      <c r="AN10" t="inlineStr">
+      <c r="AU10" t="inlineStr">
         <is>
           <t>02hM7hzd</t>
         </is>
       </c>
-      <c r="AO10" t="inlineStr">
+      <c r="AV10" t="inlineStr">
         <is>
           <t>4ljanukM</t>
         </is>
@@ -2021,84 +2133,91 @@
           <t>v9k3aY5F</t>
         </is>
       </c>
-      <c r="P11" t="n">
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="inlineStr"/>
+      <c r="W11" t="n">
         <v>26.91515151515152</v>
       </c>
-      <c r="Q11" t="n">
+      <c r="X11" t="n">
         <v>184.9703703703704</v>
       </c>
-      <c r="R11" t="n">
+      <c r="Y11" t="n">
         <v>1.614141414141414</v>
       </c>
-      <c r="S11" t="n">
+      <c r="Z11" t="n">
         <v>75.77508417508419</v>
       </c>
-      <c r="T11" t="n">
+      <c r="AA11" t="n">
         <v>8399797.97979798</v>
       </c>
-      <c r="U11" t="n">
+      <c r="AB11" t="n">
         <v>78.1905723905724</v>
       </c>
-      <c r="V11" t="n">
+      <c r="AC11" t="n">
         <v>25.85084175084175</v>
       </c>
-      <c r="W11" t="n">
+      <c r="AD11" t="n">
         <v>185.2088664421998</v>
       </c>
-      <c r="X11" t="n">
+      <c r="AE11" t="n">
         <v>1</v>
       </c>
-      <c r="Y11" t="n">
+      <c r="AF11" t="n">
         <v>69.99135802469135</v>
       </c>
-      <c r="Z11" t="n">
+      <c r="AG11" t="n">
         <v>2277025.81369248</v>
       </c>
-      <c r="AA11" t="n">
+      <c r="AH11" t="n">
         <v>73.08237934904601</v>
       </c>
-      <c r="AB11" t="n">
+      <c r="AI11" t="n">
         <v>26.9223423897909</v>
       </c>
-      <c r="AC11" t="n">
+      <c r="AJ11" t="n">
         <v>184.1517050476433</v>
       </c>
-      <c r="AD11" t="n">
+      <c r="AK11" t="n">
         <v>1.471773939680118</v>
       </c>
-      <c r="AE11" t="n">
+      <c r="AL11" t="n">
         <v>73.81049877108229</v>
       </c>
-      <c r="AF11" t="n">
+      <c r="AM11" t="n">
         <v>5227253.898635478</v>
       </c>
-      <c r="AG11" t="n">
+      <c r="AN11" t="n">
         <v>76.12306611940478</v>
       </c>
-      <c r="AH11" t="n">
+      <c r="AO11" t="n">
         <v>25.74994662582382</v>
       </c>
-      <c r="AI11" t="n">
+      <c r="AP11" t="n">
         <v>185.8726074445373</v>
       </c>
-      <c r="AJ11" t="n">
+      <c r="AQ11" t="n">
         <v>1</v>
       </c>
-      <c r="AK11" t="n">
+      <c r="AR11" t="n">
         <v>66.84020235774622</v>
       </c>
-      <c r="AL11" t="n">
+      <c r="AS11" t="n">
         <v>1325721.479624988</v>
       </c>
-      <c r="AM11" t="n">
+      <c r="AT11" t="n">
         <v>71.29296853244222</v>
       </c>
-      <c r="AN11" t="inlineStr">
+      <c r="AU11" t="inlineStr">
         <is>
           <t>Wbz1kusU</t>
         </is>
       </c>
-      <c r="AO11" t="inlineStr">
+      <c r="AV11" t="inlineStr">
         <is>
           <t>0jdIgO6t</t>
         </is>
@@ -2170,84 +2289,91 @@
           <t>WG9pOTse</t>
         </is>
       </c>
-      <c r="P12" t="n">
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr"/>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="inlineStr"/>
+      <c r="W12" t="n">
         <v>27.88888888888889</v>
       </c>
-      <c r="Q12" t="n">
+      <c r="X12" t="n">
         <v>182.4091503267974</v>
       </c>
-      <c r="R12" t="n">
+      <c r="Y12" t="n">
         <v>1.247712418300653</v>
       </c>
-      <c r="S12" t="n">
+      <c r="Z12" t="n">
         <v>73.13856209150327</v>
       </c>
-      <c r="T12" t="n">
+      <c r="AA12" t="n">
         <v>3579689.54248366</v>
       </c>
-      <c r="U12" t="n">
+      <c r="AB12" t="n">
         <v>75.03398692810457</v>
       </c>
-      <c r="V12" t="n">
+      <c r="AC12" t="n">
         <v>25.17367003367003</v>
       </c>
-      <c r="W12" t="n">
+      <c r="AD12" t="n">
         <v>184.620202020202</v>
       </c>
-      <c r="X12" t="n">
+      <c r="AE12" t="n">
         <v>1.515959595959596</v>
       </c>
-      <c r="Y12" t="n">
+      <c r="AF12" t="n">
         <v>75.27043771043772</v>
       </c>
-      <c r="Z12" t="n">
+      <c r="AG12" t="n">
         <v>8491050.505050505</v>
       </c>
-      <c r="AA12" t="n">
+      <c r="AH12" t="n">
         <v>78.22101010101009</v>
       </c>
-      <c r="AB12" t="n">
+      <c r="AI12" t="n">
         <v>26.78760504201681</v>
       </c>
-      <c r="AC12" t="n">
+      <c r="AJ12" t="n">
         <v>182.8982285841318</v>
       </c>
-      <c r="AD12" t="n">
+      <c r="AK12" t="n">
         <v>1.064620737692483</v>
       </c>
-      <c r="AE12" t="n">
+      <c r="AL12" t="n">
         <v>70.48407930816735</v>
       </c>
-      <c r="AF12" t="n">
+      <c r="AM12" t="n">
         <v>2374219.376147588</v>
       </c>
-      <c r="AG12" t="n">
+      <c r="AN12" t="n">
         <v>73.50472590013746</v>
       </c>
-      <c r="AH12" t="n">
+      <c r="AO12" t="n">
         <v>23.28772692601068</v>
       </c>
-      <c r="AI12" t="n">
+      <c r="AP12" t="n">
         <v>184.160701754386</v>
       </c>
-      <c r="AJ12" t="n">
+      <c r="AQ12" t="n">
         <v>1.280188151538266</v>
       </c>
-      <c r="AK12" t="n">
+      <c r="AR12" t="n">
         <v>72.91982047510079</v>
       </c>
-      <c r="AL12" t="n">
+      <c r="AS12" t="n">
         <v>6706858.069085757</v>
       </c>
-      <c r="AM12" t="n">
+      <c r="AT12" t="n">
         <v>78.60991663942465</v>
       </c>
-      <c r="AN12" t="inlineStr">
+      <c r="AU12" t="inlineStr">
         <is>
           <t>zyLSrbZQ</t>
         </is>
       </c>
-      <c r="AO12" t="inlineStr">
+      <c r="AV12" t="inlineStr">
         <is>
           <t>M5BRZDsC</t>
         </is>
@@ -2319,84 +2445,91 @@
           <t>nJQmYp1B</t>
         </is>
       </c>
-      <c r="P13" t="n">
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr"/>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="inlineStr"/>
+      <c r="W13" t="n">
         <v>24.13851851851852</v>
       </c>
-      <c r="Q13" t="n">
+      <c r="X13" t="n">
         <v>183.3451851851852</v>
       </c>
-      <c r="R13" t="n">
+      <c r="Y13" t="n">
         <v>1.671851851851852</v>
       </c>
-      <c r="S13" t="n">
+      <c r="Z13" t="n">
         <v>76.8762962962963</v>
       </c>
-      <c r="T13" t="n">
+      <c r="AA13" t="n">
         <v>15500111.11111111</v>
       </c>
-      <c r="U13" t="n">
+      <c r="AB13" t="n">
         <v>81.26148148148148</v>
       </c>
-      <c r="V13" t="n">
+      <c r="AC13" t="n">
         <v>26.48080808080808</v>
       </c>
-      <c r="W13" t="n">
+      <c r="AD13" t="n">
         <v>185.6835016835017</v>
       </c>
-      <c r="X13" t="n">
+      <c r="AE13" t="n">
         <v>1.803367003367003</v>
       </c>
-      <c r="Y13" t="n">
+      <c r="AF13" t="n">
         <v>75.05117845117846</v>
       </c>
-      <c r="Z13" t="n">
+      <c r="AG13" t="n">
         <v>8855387.205387207</v>
       </c>
-      <c r="AA13" t="n">
+      <c r="AH13" t="n">
         <v>78.73804713804712</v>
       </c>
-      <c r="AB13" t="n">
+      <c r="AI13" t="n">
         <v>23.98952943856968</v>
       </c>
-      <c r="AC13" t="n">
+      <c r="AJ13" t="n">
         <v>183.9351885060244</v>
       </c>
-      <c r="AD13" t="n">
+      <c r="AK13" t="n">
         <v>1.404722568453219</v>
       </c>
-      <c r="AE13" t="n">
+      <c r="AL13" t="n">
         <v>71.51946001367054</v>
       </c>
-      <c r="AF13" t="n">
+      <c r="AM13" t="n">
         <v>5542197.549354671</v>
       </c>
-      <c r="AG13" t="n">
+      <c r="AN13" t="n">
         <v>78.49802795759453</v>
       </c>
-      <c r="AH13" t="n">
+      <c r="AO13" t="n">
         <v>24.60507314036726</v>
       </c>
-      <c r="AI13" t="n">
+      <c r="AP13" t="n">
         <v>185.0131652661065</v>
       </c>
-      <c r="AJ13" t="n">
+      <c r="AQ13" t="n">
         <v>1.403680361033302</v>
       </c>
-      <c r="AK13" t="n">
+      <c r="AR13" t="n">
         <v>71.80881574852164</v>
       </c>
-      <c r="AL13" t="n">
+      <c r="AS13" t="n">
         <v>5458608.77684407</v>
       </c>
-      <c r="AM13" t="n">
+      <c r="AT13" t="n">
         <v>77.65164954870836</v>
       </c>
-      <c r="AN13" t="inlineStr">
+      <c r="AU13" t="inlineStr">
         <is>
           <t>SQrxFAMl</t>
         </is>
       </c>
-      <c r="AO13" t="inlineStr">
+      <c r="AV13" t="inlineStr">
         <is>
           <t>KUx4Q7x1</t>
         </is>
@@ -2468,84 +2601,91 @@
           <t>dfNCCCzS</t>
         </is>
       </c>
-      <c r="P14" t="n">
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr"/>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="inlineStr"/>
+      <c r="W14" t="n">
         <v>25.19191919191919</v>
       </c>
-      <c r="Q14" t="n">
+      <c r="X14" t="n">
         <v>186.149494949495</v>
       </c>
-      <c r="R14" t="n">
+      <c r="Y14" t="n">
         <v>1.081818181818182</v>
       </c>
-      <c r="S14" t="n">
+      <c r="Z14" t="n">
         <v>68.6010101010101</v>
       </c>
-      <c r="T14" t="n">
+      <c r="AA14" t="n">
         <v>1771818.181818182</v>
       </c>
-      <c r="U14" t="n">
+      <c r="AB14" t="n">
         <v>72.58080808080808</v>
       </c>
-      <c r="V14" t="n">
+      <c r="AC14" t="n">
         <v>25.39407407407408</v>
       </c>
-      <c r="W14" t="n">
+      <c r="AD14" t="n">
         <v>186.6725925925926</v>
       </c>
-      <c r="X14" t="n">
+      <c r="AE14" t="n">
         <v>1.564444444444444</v>
       </c>
-      <c r="Y14" t="n">
+      <c r="AF14" t="n">
         <v>75.71333333333332</v>
       </c>
-      <c r="Z14" t="n">
+      <c r="AG14" t="n">
         <v>10651407.40740741</v>
       </c>
-      <c r="AA14" t="n">
+      <c r="AH14" t="n">
         <v>79.47703703703704</v>
       </c>
-      <c r="AB14" t="n">
+      <c r="AI14" t="n">
         <v>25.09037362932291</v>
       </c>
-      <c r="AC14" t="n">
+      <c r="AJ14" t="n">
         <v>186.1050389157273</v>
       </c>
-      <c r="AD14" t="n">
+      <c r="AK14" t="n">
         <v>1.010121923165401</v>
       </c>
-      <c r="AE14" t="n">
+      <c r="AL14" t="n">
         <v>66.44403228280039</v>
       </c>
-      <c r="AF14" t="n">
+      <c r="AM14" t="n">
         <v>1363103.505291005</v>
       </c>
-      <c r="AG14" t="n">
+      <c r="AN14" t="n">
         <v>71.09151905528716</v>
       </c>
-      <c r="AH14" t="n">
+      <c r="AO14" t="n">
         <v>24.12706119162641</v>
       </c>
-      <c r="AI14" t="n">
+      <c r="AP14" t="n">
         <v>183.7472222222222</v>
       </c>
-      <c r="AJ14" t="n">
+      <c r="AQ14" t="n">
         <v>1.246602254428341</v>
       </c>
-      <c r="AK14" t="n">
+      <c r="AR14" t="n">
         <v>73.50627214170693</v>
       </c>
-      <c r="AL14" t="n">
+      <c r="AS14" t="n">
         <v>8361891.304347825</v>
       </c>
-      <c r="AM14" t="n">
+      <c r="AT14" t="n">
         <v>78.35681159420291</v>
       </c>
-      <c r="AN14" t="inlineStr">
+      <c r="AU14" t="inlineStr">
         <is>
           <t>SfKt2E6n</t>
         </is>
       </c>
-      <c r="AO14" t="inlineStr">
+      <c r="AV14" t="inlineStr">
         <is>
           <t>f3ddUIXs</t>
         </is>
@@ -2617,84 +2757,91 @@
           <t>8vndvXTk</t>
         </is>
       </c>
-      <c r="P15" t="n">
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr"/>
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="inlineStr"/>
+      <c r="W15" t="n">
         <v>24.38848484848485</v>
       </c>
-      <c r="Q15" t="n">
+      <c r="X15" t="n">
         <v>184.5909090909091</v>
       </c>
-      <c r="R15" t="n">
+      <c r="Y15" t="n">
         <v>1.516969696969697</v>
       </c>
-      <c r="S15" t="n">
+      <c r="Z15" t="n">
         <v>76.14606060606062</v>
       </c>
-      <c r="T15" t="n">
+      <c r="AA15" t="n">
         <v>11904909.09090909</v>
       </c>
-      <c r="U15" t="n">
+      <c r="AB15" t="n">
         <v>79.19939393939394</v>
       </c>
-      <c r="V15" t="n">
+      <c r="AC15" t="n">
         <v>25.77030303030303</v>
       </c>
-      <c r="W15" t="n">
+      <c r="AD15" t="n">
         <v>183.2272727272727</v>
       </c>
-      <c r="X15" t="n">
+      <c r="AE15" t="n">
         <v>1.572727272727272</v>
       </c>
-      <c r="Y15" t="n">
+      <c r="AF15" t="n">
         <v>74.43151515151516</v>
       </c>
-      <c r="Z15" t="n">
+      <c r="AG15" t="n">
         <v>6764848.484848485</v>
       </c>
-      <c r="AA15" t="n">
+      <c r="AH15" t="n">
         <v>78.35939393939394</v>
       </c>
-      <c r="AB15" t="n">
+      <c r="AI15" t="n">
         <v>24.20182539682539</v>
       </c>
-      <c r="AC15" t="n">
+      <c r="AJ15" t="n">
         <v>182.7644973544974</v>
       </c>
-      <c r="AD15" t="n">
+      <c r="AK15" t="n">
         <v>1.250793650793651</v>
       </c>
-      <c r="AE15" t="n">
+      <c r="AL15" t="n">
         <v>71.08301587301588</v>
       </c>
-      <c r="AF15" t="n">
+      <c r="AM15" t="n">
         <v>5481326.719576719</v>
       </c>
-      <c r="AG15" t="n">
+      <c r="AN15" t="n">
         <v>75.89417989417989</v>
       </c>
-      <c r="AH15" t="n">
+      <c r="AO15" t="n">
         <v>26.12653439153439</v>
       </c>
-      <c r="AI15" t="n">
+      <c r="AP15" t="n">
         <v>185.0814814814815</v>
       </c>
-      <c r="AJ15" t="n">
+      <c r="AQ15" t="n">
         <v>1.494656084656085</v>
       </c>
-      <c r="AK15" t="n">
+      <c r="AR15" t="n">
         <v>72.38201058201057</v>
       </c>
-      <c r="AL15" t="n">
+      <c r="AS15" t="n">
         <v>4546836.64021164</v>
       </c>
-      <c r="AM15" t="n">
+      <c r="AT15" t="n">
         <v>76.68412698412698</v>
       </c>
-      <c r="AN15" t="inlineStr">
+      <c r="AU15" t="inlineStr">
         <is>
           <t>hAcTWKKN</t>
         </is>
       </c>
-      <c r="AO15" t="inlineStr">
+      <c r="AV15" t="inlineStr">
         <is>
           <t>vZA6VYpf</t>
         </is>
@@ -2766,84 +2913,91 @@
           <t>0Ija0Ej9</t>
         </is>
       </c>
-      <c r="P16" t="n">
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="inlineStr"/>
+      <c r="T16" t="inlineStr"/>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="inlineStr"/>
+      <c r="W16" t="n">
         <v>26.01212121212121</v>
       </c>
-      <c r="Q16" t="n">
+      <c r="X16" t="n">
         <v>183.3757575757576</v>
       </c>
-      <c r="R16" t="n">
+      <c r="Y16" t="n">
         <v>1.16969696969697</v>
       </c>
-      <c r="S16" t="n">
+      <c r="Z16" t="n">
         <v>73.21212121212122</v>
       </c>
-      <c r="T16" t="n">
+      <c r="AA16" t="n">
         <v>4874848.484848485</v>
       </c>
-      <c r="U16" t="n">
+      <c r="AB16" t="n">
         <v>76.13333333333334</v>
       </c>
-      <c r="V16" t="n">
+      <c r="AC16" t="n">
         <v>25.38787878787879</v>
       </c>
-      <c r="W16" t="n">
+      <c r="AD16" t="n">
         <v>184.8551515151515</v>
       </c>
-      <c r="X16" t="n">
+      <c r="AE16" t="n">
         <v>2.293939393939394</v>
       </c>
-      <c r="Y16" t="n">
+      <c r="AF16" t="n">
         <v>80</v>
       </c>
-      <c r="Z16" t="n">
+      <c r="AG16" t="n">
         <v>29471515.15151515</v>
       </c>
-      <c r="AA16" t="n">
+      <c r="AH16" t="n">
         <v>83.26060606060607</v>
       </c>
-      <c r="AB16" t="n">
+      <c r="AI16" t="n">
         <v>24.83106351236146</v>
       </c>
-      <c r="AC16" t="n">
+      <c r="AJ16" t="n">
         <v>184.539776453424</v>
       </c>
-      <c r="AD16" t="n">
+      <c r="AK16" t="n">
         <v>1.169217596776824</v>
       </c>
-      <c r="AE16" t="n">
+      <c r="AL16" t="n">
         <v>68.44581405916041</v>
       </c>
-      <c r="AF16" t="n">
+      <c r="AM16" t="n">
         <v>2549719.765989284</v>
       </c>
-      <c r="AG16" t="n">
+      <c r="AN16" t="n">
         <v>74.16400905645757</v>
       </c>
-      <c r="AH16" t="n">
+      <c r="AO16" t="n">
         <v>25.00185185185186</v>
       </c>
-      <c r="AI16" t="n">
+      <c r="AP16" t="n">
         <v>183.9712962962963</v>
       </c>
-      <c r="AJ16" t="n">
+      <c r="AQ16" t="n">
         <v>1.993518518518518</v>
       </c>
-      <c r="AK16" t="n">
+      <c r="AR16" t="n">
         <v>77.60859788359788</v>
       </c>
-      <c r="AL16" t="n">
+      <c r="AS16" t="n">
         <v>19937235.44973545</v>
       </c>
-      <c r="AM16" t="n">
+      <c r="AT16" t="n">
         <v>82.17949735449734</v>
       </c>
-      <c r="AN16" t="inlineStr">
+      <c r="AU16" t="inlineStr">
         <is>
           <t>tnTvQd1l</t>
         </is>
       </c>
-      <c r="AO16" t="inlineStr">
+      <c r="AV16" t="inlineStr">
         <is>
           <t>IkCftsQm</t>
         </is>
@@ -2915,84 +3069,91 @@
           <t>nP1i5US1</t>
         </is>
       </c>
-      <c r="P17" t="n">
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="inlineStr"/>
+      <c r="T17" t="inlineStr"/>
+      <c r="U17" t="inlineStr"/>
+      <c r="V17" t="inlineStr"/>
+      <c r="W17" t="n">
         <v>25.61907308377896</v>
       </c>
-      <c r="Q17" t="n">
+      <c r="X17" t="n">
         <v>184.9906565656566</v>
       </c>
-      <c r="R17" t="n">
+      <c r="Y17" t="n">
         <v>2.085695187165775</v>
       </c>
-      <c r="S17" t="n">
+      <c r="Z17" t="n">
         <v>81.3868092691622</v>
       </c>
-      <c r="T17" t="n">
+      <c r="AA17" t="n">
         <v>34021375.51990493</v>
       </c>
-      <c r="U17" t="n">
+      <c r="AB17" t="n">
         <v>84.2319964349376</v>
       </c>
-      <c r="V17" t="n">
+      <c r="AC17" t="n">
         <v>24.85090909090909</v>
       </c>
-      <c r="W17" t="n">
+      <c r="AD17" t="n">
         <v>182.64</v>
       </c>
-      <c r="X17" t="n">
+      <c r="AE17" t="n">
         <v>2.106666666666666</v>
       </c>
-      <c r="Y17" t="n">
+      <c r="AF17" t="n">
         <v>80.28</v>
       </c>
-      <c r="Z17" t="n">
+      <c r="AG17" t="n">
         <v>28992121.21212121</v>
       </c>
-      <c r="AA17" t="n">
+      <c r="AH17" t="n">
         <v>83.77575757575758</v>
       </c>
-      <c r="AB17" t="n">
+      <c r="AI17" t="n">
         <v>23.09709856482639</v>
       </c>
-      <c r="AC17" t="n">
+      <c r="AJ17" t="n">
         <v>181.8285059384686</v>
       </c>
-      <c r="AD17" t="n">
+      <c r="AK17" t="n">
         <v>1.720316864003767</v>
       </c>
-      <c r="AE17" t="n">
+      <c r="AL17" t="n">
         <v>78.82048615784986</v>
       </c>
-      <c r="AF17" t="n">
+      <c r="AM17" t="n">
         <v>33966312.08994935</v>
       </c>
-      <c r="AG17" t="n">
+      <c r="AN17" t="n">
         <v>84.26231191353179</v>
       </c>
-      <c r="AH17" t="n">
+      <c r="AO17" t="n">
         <v>24.82412804586718</v>
       </c>
-      <c r="AI17" t="n">
+      <c r="AP17" t="n">
         <v>185.1450257471997</v>
       </c>
-      <c r="AJ17" t="n">
+      <c r="AQ17" t="n">
         <v>1.702190723929854</v>
       </c>
-      <c r="AK17" t="n">
+      <c r="AR17" t="n">
         <v>76.87710666949798</v>
       </c>
-      <c r="AL17" t="n">
+      <c r="AS17" t="n">
         <v>18126442.72796446</v>
       </c>
-      <c r="AM17" t="n">
+      <c r="AT17" t="n">
         <v>81.50249376227637</v>
       </c>
-      <c r="AN17" t="inlineStr">
+      <c r="AU17" t="inlineStr">
         <is>
           <t>hAcTWKKN</t>
         </is>
       </c>
-      <c r="AO17" t="inlineStr">
+      <c r="AV17" t="inlineStr">
         <is>
           <t>pfoInmcq</t>
         </is>
@@ -3056,84 +3217,91 @@
       </c>
       <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr"/>
-      <c r="P18" t="n">
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="inlineStr"/>
+      <c r="T18" t="inlineStr"/>
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="inlineStr"/>
+      <c r="W18" t="n">
         <v>25.81666666666667</v>
       </c>
-      <c r="Q18" t="n">
+      <c r="X18" t="n">
         <v>186.9015151515151</v>
       </c>
-      <c r="R18" t="n">
+      <c r="Y18" t="n">
         <v>1</v>
       </c>
-      <c r="S18" t="n">
+      <c r="Z18" t="n">
         <v>72.875</v>
       </c>
-      <c r="T18" t="n">
+      <c r="AA18" t="n">
         <v>4350833.333333333</v>
       </c>
-      <c r="U18" t="n">
+      <c r="AB18" t="n">
         <v>75.22045454545453</v>
       </c>
-      <c r="V18" t="n">
+      <c r="AC18" t="n">
         <v>25.3987037037037</v>
       </c>
-      <c r="W18" t="n">
+      <c r="AD18" t="n">
         <v>185.8592424242424</v>
       </c>
-      <c r="X18" t="n">
+      <c r="AE18" t="n">
         <v>1.414326599326599</v>
       </c>
-      <c r="Y18" t="n">
+      <c r="AF18" t="n">
         <v>74.34148148148148</v>
       </c>
-      <c r="Z18" t="n">
+      <c r="AG18" t="n">
         <v>6432727.272727272</v>
       </c>
-      <c r="AA18" t="n">
+      <c r="AH18" t="n">
         <v>77.28441077441077</v>
       </c>
-      <c r="AB18" t="n">
+      <c r="AI18" t="n">
         <v>27.03253968253968</v>
       </c>
-      <c r="AC18" t="n">
+      <c r="AJ18" t="n">
         <v>183.2093915343915</v>
       </c>
-      <c r="AD18" t="n">
+      <c r="AK18" t="n">
         <v>1</v>
       </c>
-      <c r="AE18" t="n">
+      <c r="AL18" t="n">
         <v>69.32208994708995</v>
       </c>
-      <c r="AF18" t="n">
+      <c r="AM18" t="n">
         <v>1942023.809523809</v>
       </c>
-      <c r="AG18" t="n">
+      <c r="AN18" t="n">
         <v>71.08320105820106</v>
       </c>
-      <c r="AH18" t="n">
+      <c r="AO18" t="n">
         <v>23.90786783878889</v>
       </c>
-      <c r="AI18" t="n">
+      <c r="AP18" t="n">
         <v>184.0711136426926</v>
       </c>
-      <c r="AJ18" t="n">
+      <c r="AQ18" t="n">
         <v>1.151816599579758</v>
       </c>
-      <c r="AK18" t="n">
+      <c r="AR18" t="n">
         <v>71.11281442241969</v>
       </c>
-      <c r="AL18" t="n">
+      <c r="AS18" t="n">
         <v>3876240.913204729</v>
       </c>
-      <c r="AM18" t="n">
+      <c r="AT18" t="n">
         <v>76.49320833649782</v>
       </c>
-      <c r="AN18" t="inlineStr">
+      <c r="AU18" t="inlineStr">
         <is>
           <t>lli2SfLl</t>
         </is>
       </c>
-      <c r="AO18" t="inlineStr">
+      <c r="AV18" t="inlineStr">
         <is>
           <t>2VSFgl3c</t>
         </is>
@@ -3201,336 +3369,93 @@
           <t>nJQmYp1B</t>
         </is>
       </c>
-      <c r="P19" t="n">
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr"/>
+      <c r="S19" t="inlineStr"/>
+      <c r="T19" t="inlineStr"/>
+      <c r="U19" t="inlineStr"/>
+      <c r="V19" t="inlineStr"/>
+      <c r="W19" t="n">
         <v>27.08484848484849</v>
       </c>
-      <c r="Q19" t="n">
+      <c r="X19" t="n">
         <v>184.9212121212121</v>
       </c>
-      <c r="R19" t="n">
+      <c r="Y19" t="n">
         <v>3.03030303030303</v>
       </c>
-      <c r="S19" t="n">
+      <c r="Z19" t="n">
         <v>81.87878787878786</v>
       </c>
-      <c r="T19" t="n">
+      <c r="AA19" t="n">
         <v>41254848.48484848</v>
       </c>
-      <c r="U19" t="n">
+      <c r="AB19" t="n">
         <v>84.53333333333333</v>
       </c>
-      <c r="V19" t="n">
+      <c r="AC19" t="n">
         <v>27.19259259259259</v>
       </c>
-      <c r="W19" t="n">
+      <c r="AD19" t="n">
         <v>183.6707070707071</v>
       </c>
-      <c r="X19" t="n">
+      <c r="AE19" t="n">
         <v>1.694276094276094</v>
       </c>
-      <c r="Y19" t="n">
+      <c r="AF19" t="n">
         <v>75.32255892255893</v>
       </c>
-      <c r="Z19" t="n">
+      <c r="AG19" t="n">
         <v>8525252.525252525</v>
       </c>
-      <c r="AA19" t="n">
+      <c r="AH19" t="n">
         <v>77.13265993265992</v>
       </c>
-      <c r="AB19" t="n">
+      <c r="AI19" t="n">
         <v>24.6207077440689</v>
       </c>
-      <c r="AC19" t="n">
+      <c r="AJ19" t="n">
         <v>182.3024630782438</v>
       </c>
-      <c r="AD19" t="n">
+      <c r="AK19" t="n">
         <v>2.250397657387158</v>
       </c>
-      <c r="AE19" t="n">
+      <c r="AL19" t="n">
         <v>78.52101362272482</v>
       </c>
-      <c r="AF19" t="n">
+      <c r="AM19" t="n">
         <v>29928093.12285289</v>
       </c>
-      <c r="AG19" t="n">
+      <c r="AN19" t="n">
         <v>83.50805072369886</v>
       </c>
-      <c r="AH19" t="n">
+      <c r="AO19" t="n">
         <v>24.970719370891</v>
       </c>
-      <c r="AI19" t="n">
+      <c r="AP19" t="n">
         <v>184.6744885765137</v>
       </c>
-      <c r="AJ19" t="n">
+      <c r="AQ19" t="n">
         <v>1.444793868729796</v>
       </c>
-      <c r="AK19" t="n">
+      <c r="AR19" t="n">
         <v>73.33173931204824</v>
       </c>
-      <c r="AL19" t="n">
+      <c r="AS19" t="n">
         <v>6040617.621953433</v>
       </c>
-      <c r="AM19" t="n">
+      <c r="AT19" t="n">
         <v>76.71675356870438</v>
       </c>
-      <c r="AN19" t="inlineStr">
+      <c r="AU19" t="inlineStr">
         <is>
           <t>QevvB2nf</t>
         </is>
       </c>
-      <c r="AO19" t="inlineStr">
+      <c r="AV19" t="inlineStr">
         <is>
           <t>YZPE6Sx7</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="inlineStr">
-        <is>
-          <t>W67CmLPh</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="n">
-        <v>45531.65625</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stieler t 
-  ger </t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">preussenstadion
-  munster </t>
-        </is>
-      </c>
-      <c r="E20" t="n">
-        <v>12794</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>zedZaSL7</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>nJQmYp1B</t>
-        </is>
-      </c>
-      <c r="H20" t="n">
-        <v>59</v>
-      </c>
-      <c r="I20" t="n">
-        <v>593</v>
-      </c>
-      <c r="J20" t="n">
-        <v>1</v>
-      </c>
-      <c r="K20" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>dfb pokal</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>fiEQZ7C7</t>
-        </is>
-      </c>
-      <c r="P20" t="inlineStr"/>
-      <c r="Q20" t="inlineStr"/>
-      <c r="R20" t="inlineStr"/>
-      <c r="S20" t="inlineStr"/>
-      <c r="T20" t="inlineStr"/>
-      <c r="U20" t="inlineStr"/>
-      <c r="V20" t="n">
-        <v>24.38848484848485</v>
-      </c>
-      <c r="W20" t="n">
-        <v>184.5909090909091</v>
-      </c>
-      <c r="X20" t="n">
-        <v>1.516969696969697</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>76.14606060606062</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>11904909.09090909</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>79.19939393939394</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>25.57142857142857</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>181.8571428571429</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>66.71428571428571</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>1175000</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>68.42857142857143</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>24.20182539682539</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>182.7644973544974</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>1.250793650793651</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>71.08301587301588</v>
-      </c>
-      <c r="AL20" t="n">
-        <v>5481326.719576719</v>
-      </c>
-      <c r="AM20" t="n">
-        <v>75.89417989417989</v>
-      </c>
-      <c r="AN20" t="inlineStr">
-        <is>
-          <t>pdPRS0me</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>GzfvcwRj</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="inlineStr">
-        <is>
-          <t>6u6i5pie</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="n">
-        <v>45532.54166666666</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stieler t 
-  ger </t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ernst abbe sportfeld
-  jena </t>
-        </is>
-      </c>
-      <c r="E21" t="n">
-        <v>10445</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>APNl8MIn</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>4jcj2zMd</t>
-        </is>
-      </c>
-      <c r="H21" t="n">
-        <v>59</v>
-      </c>
-      <c r="I21" t="n">
-        <v>593</v>
-      </c>
-      <c r="J21" t="n">
-        <v>1</v>
-      </c>
-      <c r="K21" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>dfb pokal</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>WG9pOTse</t>
-        </is>
-      </c>
-      <c r="P21" t="inlineStr"/>
-      <c r="Q21" t="inlineStr"/>
-      <c r="R21" t="inlineStr"/>
-      <c r="S21" t="inlineStr"/>
-      <c r="T21" t="inlineStr"/>
-      <c r="U21" t="inlineStr"/>
-      <c r="V21" t="n">
-        <v>25.61907308377896</v>
-      </c>
-      <c r="W21" t="n">
-        <v>184.9906565656566</v>
-      </c>
-      <c r="X21" t="n">
-        <v>2.085695187165775</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>81.3868092691622</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>34021375.51990493</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>84.2319964349376</v>
-      </c>
-      <c r="AB21" t="inlineStr"/>
-      <c r="AC21" t="inlineStr"/>
-      <c r="AD21" t="inlineStr"/>
-      <c r="AE21" t="inlineStr"/>
-      <c r="AF21" t="inlineStr"/>
-      <c r="AG21" t="inlineStr"/>
-      <c r="AH21" t="n">
-        <v>23.09709856482639</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>181.8285059384686</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>1.720316864003767</v>
-      </c>
-      <c r="AK21" t="n">
-        <v>78.82048615784986</v>
-      </c>
-      <c r="AL21" t="n">
-        <v>33966312.08994935</v>
-      </c>
-      <c r="AM21" t="n">
-        <v>84.26231191353179</v>
-      </c>
-      <c r="AN21" t="inlineStr"/>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>GzfvcwRj</t>
         </is>
       </c>
     </row>

--- a/data/germany/p6_deployment/data_preparation/df_filled.xlsx
+++ b/data/germany/p6_deployment/data_preparation/df_filled.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BC7"/>
+  <dimension ref="A1:BC12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -707,35 +707,35 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>YZZcMwBs</t>
+          <t>t0w6KHuf</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45528.4375</v>
+        <v>45529.4375</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">stegemann s 
+          <t xml:space="preserve">siebert d 
   ger </t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">wwk arena
-  augsburg </t>
+          <t xml:space="preserve">volkswagen arena
+  wolfsburg </t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>30660</v>
+        <v>28917</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>fTVNku3I</t>
+          <t>nwkTahLL</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Ig1f1fy3</t>
+          <t>nVp0wiqd</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -760,169 +760,169 @@
           <t>bundesliga</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>v9k3aY5F</t>
-        </is>
-      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>dfNCCCzS</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr"/>
       <c r="P2" t="n">
-        <v>25.66666666666667</v>
+        <v>22</v>
       </c>
       <c r="Q2" t="n">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="R2" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="S2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T2" t="n">
-        <v>214</v>
+        <v>149</v>
       </c>
       <c r="U2" t="n">
-        <v>9400000</v>
+        <v>21000000</v>
       </c>
       <c r="V2" t="n">
-        <v>220</v>
+        <v>164</v>
       </c>
       <c r="W2" t="n">
-        <v>26.5</v>
+        <v>21.83333333333333</v>
       </c>
       <c r="X2" t="n">
-        <v>182</v>
+        <v>184.8333333333333</v>
       </c>
       <c r="Y2" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="Z2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AA2" t="n">
-        <v>150</v>
+        <v>430</v>
       </c>
       <c r="AB2" t="n">
-        <v>13000000</v>
+        <v>98525000</v>
       </c>
       <c r="AC2" t="n">
-        <v>154</v>
+        <v>489</v>
       </c>
       <c r="AD2" t="n">
-        <v>25.3987037037037</v>
+        <v>25.39407407407408</v>
       </c>
       <c r="AE2" t="n">
-        <v>185.8592424242424</v>
+        <v>186.6725925925926</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.414326599326599</v>
+        <v>1.564444444444444</v>
       </c>
       <c r="AG2" t="n">
-        <v>74.34148148148148</v>
+        <v>75.71333333333332</v>
       </c>
       <c r="AH2" t="n">
-        <v>6432727.272727272</v>
+        <v>10651407.40740741</v>
       </c>
       <c r="AI2" t="n">
-        <v>77.28441077441077</v>
+        <v>79.47703703703704</v>
       </c>
       <c r="AJ2" t="n">
-        <v>26.01212121212121</v>
+        <v>27.08484848484849</v>
       </c>
       <c r="AK2" t="n">
-        <v>183.3757575757576</v>
+        <v>184.9212121212121</v>
       </c>
       <c r="AL2" t="n">
-        <v>1.16969696969697</v>
+        <v>3.03030303030303</v>
       </c>
       <c r="AM2" t="n">
-        <v>73.21212121212122</v>
+        <v>81.87878787878786</v>
       </c>
       <c r="AN2" t="n">
-        <v>4874848.484848485</v>
+        <v>41254848.48484848</v>
       </c>
       <c r="AO2" t="n">
-        <v>76.13333333333334</v>
+        <v>84.53333333333333</v>
       </c>
       <c r="AP2" t="n">
-        <v>23.90786783878889</v>
+        <v>24.12706119162641</v>
       </c>
       <c r="AQ2" t="n">
-        <v>184.0711136426926</v>
+        <v>183.7472222222222</v>
       </c>
       <c r="AR2" t="n">
-        <v>1.151816599579758</v>
+        <v>1.246602254428341</v>
       </c>
       <c r="AS2" t="n">
-        <v>71.11281442241969</v>
+        <v>73.50627214170692</v>
       </c>
       <c r="AT2" t="n">
-        <v>3876240.913204729</v>
+        <v>8361891.304347825</v>
       </c>
       <c r="AU2" t="n">
-        <v>76.49320833649782</v>
+        <v>78.35681159420288</v>
       </c>
       <c r="AV2" t="n">
-        <v>24.83106351236146</v>
+        <v>24.62070774406889</v>
       </c>
       <c r="AW2" t="n">
-        <v>184.539776453424</v>
+        <v>182.3024630782438</v>
       </c>
       <c r="AX2" t="n">
-        <v>1.169217596776824</v>
+        <v>2.250397657387158</v>
       </c>
       <c r="AY2" t="n">
-        <v>68.44581405916041</v>
+        <v>78.52101362272482</v>
       </c>
       <c r="AZ2" t="n">
-        <v>2549719.765989284</v>
+        <v>29928093.1228529</v>
       </c>
       <c r="BA2" t="n">
-        <v>74.16400905645757</v>
+        <v>83.50805072369886</v>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>CCww5Qfo</t>
+          <t>rFNN7oyi</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>4fuCGs9P</t>
+          <t>K6A2elS9</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>GbeXvnR8</t>
+          <t>AuVMGZvJ</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45528.4375</v>
+        <v>45529.52083333334</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">welz t 
+          <t xml:space="preserve">jablonski s 
   ger </t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">europa park stadion
-  freiburg </t>
+          <t xml:space="preserve">millerntor stadion
+  hamburg </t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>34700</v>
+        <v>29546</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>fiEQZ7C7</t>
+          <t>ILyJuN3g</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>nJQmYp1B</t>
+          <t>KWixEVWi</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -949,171 +949,153 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>nJQmYp1B</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>fiEQZ7C7</t>
-        </is>
-      </c>
-      <c r="P3" t="n">
-        <v>23.83333333333333</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>186.3333333333333</v>
-      </c>
-      <c r="R3" t="n">
+          <t>v9k3aY5F</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr"/>
+      <c r="W3" t="n">
+        <v>23</v>
+      </c>
+      <c r="X3" t="n">
+        <v>186</v>
+      </c>
+      <c r="Y3" t="n">
         <v>1</v>
       </c>
-      <c r="S3" t="n">
-        <v>6</v>
-      </c>
-      <c r="T3" t="n">
-        <v>428</v>
-      </c>
-      <c r="U3" t="n">
-        <v>24500000</v>
-      </c>
-      <c r="V3" t="n">
-        <v>457</v>
-      </c>
-      <c r="W3" t="n">
-        <v>22.28571428571428</v>
-      </c>
-      <c r="X3" t="n">
-        <v>188.7142857142857</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>1.285714285714286</v>
-      </c>
       <c r="Z3" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="AA3" t="n">
-        <v>495</v>
+        <v>66</v>
       </c>
       <c r="AB3" t="n">
-        <v>36825000</v>
+        <v>1100000</v>
       </c>
       <c r="AC3" t="n">
-        <v>541</v>
+        <v>70</v>
       </c>
       <c r="AD3" t="n">
-        <v>27.19259259259259</v>
+        <v>25.85084175084175</v>
       </c>
       <c r="AE3" t="n">
-        <v>183.6707070707071</v>
+        <v>185.2088664421998</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.694276094276094</v>
+        <v>1</v>
       </c>
       <c r="AG3" t="n">
-        <v>75.32255892255893</v>
+        <v>69.99135802469135</v>
       </c>
       <c r="AH3" t="n">
-        <v>8525252.525252525</v>
+        <v>2277025.81369248</v>
       </c>
       <c r="AI3" t="n">
-        <v>77.13265993265992</v>
+        <v>73.08237934904601</v>
       </c>
       <c r="AJ3" t="n">
-        <v>24.38848484848485</v>
+        <v>25.81666666666667</v>
       </c>
       <c r="AK3" t="n">
-        <v>184.5909090909091</v>
+        <v>186.9015151515151</v>
       </c>
       <c r="AL3" t="n">
-        <v>1.516969696969697</v>
+        <v>1</v>
       </c>
       <c r="AM3" t="n">
-        <v>76.14606060606062</v>
+        <v>72.875</v>
       </c>
       <c r="AN3" t="n">
-        <v>11904909.09090909</v>
+        <v>4350833.333333333</v>
       </c>
       <c r="AO3" t="n">
-        <v>79.19939393939394</v>
+        <v>75.22045454545453</v>
       </c>
       <c r="AP3" t="n">
-        <v>24.970719370891</v>
+        <v>25.74994662582382</v>
       </c>
       <c r="AQ3" t="n">
-        <v>184.6744885765137</v>
+        <v>185.8726074445373</v>
       </c>
       <c r="AR3" t="n">
-        <v>1.444793868729796</v>
+        <v>1</v>
       </c>
       <c r="AS3" t="n">
-        <v>73.33173931204824</v>
+        <v>66.84020235774622</v>
       </c>
       <c r="AT3" t="n">
-        <v>6040617.621953433</v>
+        <v>1325721.479624988</v>
       </c>
       <c r="AU3" t="n">
-        <v>76.71675356870438</v>
+        <v>71.29296853244222</v>
       </c>
       <c r="AV3" t="n">
-        <v>24.20182539682539</v>
+        <v>27.03253968253968</v>
       </c>
       <c r="AW3" t="n">
-        <v>182.7644973544974</v>
+        <v>183.2093915343915</v>
       </c>
       <c r="AX3" t="n">
-        <v>1.250793650793651</v>
+        <v>1</v>
       </c>
       <c r="AY3" t="n">
-        <v>71.08301587301588</v>
+        <v>69.32208994708995</v>
       </c>
       <c r="AZ3" t="n">
-        <v>5481326.719576719</v>
+        <v>1942023.809523809</v>
       </c>
       <c r="BA3" t="n">
-        <v>75.89417989417989</v>
+        <v>71.08320105820106</v>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>lxrr7DgN</t>
+          <t>02hM7hzd</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>GzfvcwRj</t>
+          <t>4ljanukM</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>O48oHrZ1</t>
+          <t>djSMofvg</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45528.4375</v>
+        <v>45534.64583333334</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">stieler t 
+          <t xml:space="preserve">siebert d 
   ger </t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">prezero arena
-  sinsheim </t>
+          <t xml:space="preserve">stadion an der alten forsterei
+  berlin </t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>30150</v>
+        <v>22012</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>hQAtP9Sl</t>
+          <t>pzHW4oaE</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>63WsD2ei</t>
+          <t>ILyJuN3g</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -1138,173 +1120,141 @@
           <t>bundesliga</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>nJQmYp1B</t>
-        </is>
-      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr">
         <is>
-          <t>ILyJuN3g</t>
-        </is>
-      </c>
-      <c r="P4" t="n">
-        <v>23.42857142857143</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>182.7142857142857</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1.428571428571429</v>
-      </c>
-      <c r="S4" t="n">
-        <v>7</v>
-      </c>
-      <c r="T4" t="n">
-        <v>512</v>
-      </c>
-      <c r="U4" t="n">
-        <v>48000000</v>
-      </c>
-      <c r="V4" t="n">
-        <v>558</v>
-      </c>
-      <c r="W4" t="n">
-        <v>26.33333333333333</v>
-      </c>
-      <c r="X4" t="n">
-        <v>184</v>
-      </c>
-      <c r="Y4" t="n">
+          <t>v9k3aY5F</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="inlineStr"/>
+      <c r="X4" t="inlineStr"/>
+      <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="inlineStr"/>
+      <c r="AA4" t="inlineStr"/>
+      <c r="AB4" t="inlineStr"/>
+      <c r="AC4" t="inlineStr"/>
+      <c r="AD4" t="n">
+        <v>26.95170454545455</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>185.0659722222222</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>1.619507575757576</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>75.7828914141414</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>8385435.606060605</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>78.17866161616162</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>25.85084175084175</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>185.2088664421998</v>
+      </c>
+      <c r="AL4" t="n">
         <v>1</v>
       </c>
-      <c r="Z4" t="n">
-        <v>3</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>207</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>5750000</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>217</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>26.48080808080808</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>185.6835016835017</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>1.803367003367003</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>75.05117845117846</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>8855387.205387207</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>78.73804713804712</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>25.19191919191919</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>186.149494949495</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>1.081818181818182</v>
-      </c>
       <c r="AM4" t="n">
-        <v>68.6010101010101</v>
+        <v>69.99135802469135</v>
       </c>
       <c r="AN4" t="n">
-        <v>1771818.181818182</v>
+        <v>2277025.81369248</v>
       </c>
       <c r="AO4" t="n">
-        <v>72.58080808080808</v>
+        <v>73.08237934904601</v>
       </c>
       <c r="AP4" t="n">
-        <v>24.60507314036726</v>
+        <v>26.83493408566707</v>
       </c>
       <c r="AQ4" t="n">
-        <v>185.0131652661065</v>
+        <v>184.1065091964513</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.403680361033302</v>
+        <v>1.463121401783444</v>
       </c>
       <c r="AS4" t="n">
-        <v>71.80881574852164</v>
+        <v>73.73900926455633</v>
       </c>
       <c r="AT4" t="n">
-        <v>5458608.77684407</v>
+        <v>5164687.434732665</v>
       </c>
       <c r="AU4" t="n">
-        <v>77.65164954870836</v>
+        <v>76.12727924884676</v>
       </c>
       <c r="AV4" t="n">
-        <v>25.09037362932291</v>
+        <v>25.74994662582382</v>
       </c>
       <c r="AW4" t="n">
-        <v>186.1050389157273</v>
+        <v>185.8726074445373</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.010121923165401</v>
+        <v>1</v>
       </c>
       <c r="AY4" t="n">
-        <v>66.44403228280039</v>
+        <v>66.84020235774622</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1363103.505291005</v>
+        <v>1325721.479624988</v>
       </c>
       <c r="BA4" t="n">
-        <v>71.09151905528716</v>
+        <v>71.29296853244222</v>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>lEwgk7go</t>
+          <t>vZA6VYpf</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>A15eUM4C</t>
+          <t>0jdIgO6t</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>2FREIeA6</t>
+          <t>U3QUqY85</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45528.4375</v>
+        <v>45535.4375</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">osmers h 
+          <t xml:space="preserve">schroder r 
   ger </t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">mewa arena
-  mainz </t>
+          <t xml:space="preserve">vonovia ruhrstadion
+  bochum </t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>34000</v>
+        <v>26000</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>EuakNmc1</t>
+          <t>8Y2m6ADe</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>pzHW4oaE</t>
+          <t>88HSzjDr</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -1331,10 +1281,14 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>8vndvXTk</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr"/>
+          <t>0Ija0Ej9</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>WG9pOTse</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr"/>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr"/>
@@ -1342,142 +1296,128 @@
       <c r="T5" t="inlineStr"/>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="inlineStr"/>
-      <c r="W5" t="n">
-        <v>29</v>
-      </c>
-      <c r="X5" t="n">
-        <v>175.6666666666667</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>1.666666666666667</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>3</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>229</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>25300000</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>229</v>
-      </c>
+      <c r="W5" t="inlineStr"/>
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="inlineStr"/>
+      <c r="AA5" t="inlineStr"/>
+      <c r="AB5" t="inlineStr"/>
+      <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="n">
-        <v>25.77030303030303</v>
+        <v>27.83950617283951</v>
       </c>
       <c r="AE5" t="n">
-        <v>183.2272727272727</v>
+        <v>182.4489197530864</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.572727272727272</v>
+        <v>1.233950617283951</v>
       </c>
       <c r="AG5" t="n">
-        <v>74.43151515151516</v>
+        <v>73.04058641975308</v>
       </c>
       <c r="AH5" t="n">
-        <v>6764848.484848485</v>
+        <v>3510852.62345679</v>
       </c>
       <c r="AI5" t="n">
-        <v>78.35939393939394</v>
+        <v>74.9695987654321</v>
       </c>
       <c r="AJ5" t="n">
-        <v>26.91515151515152</v>
+        <v>25.19690656565657</v>
       </c>
       <c r="AK5" t="n">
-        <v>184.9703703703704</v>
+        <v>184.5984848484849</v>
       </c>
       <c r="AL5" t="n">
-        <v>1.614141414141414</v>
+        <v>1.523484848484848</v>
       </c>
       <c r="AM5" t="n">
-        <v>75.77508417508419</v>
+        <v>75.34444444444443</v>
       </c>
       <c r="AN5" t="n">
-        <v>8399797.97979798</v>
+        <v>8616609.848484848</v>
       </c>
       <c r="AO5" t="n">
-        <v>78.1905723905724</v>
+        <v>78.24128787878787</v>
       </c>
       <c r="AP5" t="n">
-        <v>26.12653439153439</v>
+        <v>26.52903439153439</v>
       </c>
       <c r="AQ5" t="n">
-        <v>185.0814814814815</v>
+        <v>183.0409195887171</v>
       </c>
       <c r="AR5" t="n">
-        <v>1.494656084656085</v>
+        <v>1.061030696709568</v>
       </c>
       <c r="AS5" t="n">
-        <v>72.38201058201057</v>
+        <v>70.23866749475064</v>
       </c>
       <c r="AT5" t="n">
-        <v>4546836.64021164</v>
+        <v>2328151.633028278</v>
       </c>
       <c r="AU5" t="n">
-        <v>76.68412698412698</v>
+        <v>73.66187075753723</v>
       </c>
       <c r="AV5" t="n">
-        <v>26.9223423897909</v>
+        <v>23.34266065980168</v>
       </c>
       <c r="AW5" t="n">
-        <v>184.1517050476433</v>
+        <v>184.1793037280702</v>
       </c>
       <c r="AX5" t="n">
-        <v>1.471773939680118</v>
+        <v>1.278301392067124</v>
       </c>
       <c r="AY5" t="n">
-        <v>73.81049877108229</v>
+        <v>72.89358169540699</v>
       </c>
       <c r="AZ5" t="n">
-        <v>5227253.898635478</v>
+        <v>6622054.439767897</v>
       </c>
       <c r="BA5" t="n">
-        <v>76.12306611940478</v>
+        <v>78.54315101612727</v>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>QTAUlvUP</t>
+          <t>pfoInmcq</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>hpYJ6izc</t>
+          <t>hAcTWKKN</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>dfO6OQtS</t>
+          <t>AgAeVYgC</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45528.4375</v>
+        <v>45535.4375</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">brand b 
+          <t xml:space="preserve">stieler t 
   ger </t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">red bull arena
-  leipzig </t>
+          <t xml:space="preserve">deutsche bank park
+  frankfurt </t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>47069</v>
+        <v>58000</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>KbS1suSm</t>
+          <t>8vndvXTk</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>8Y2m6ADe</t>
+          <t>hQAtP9Sl</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -1504,327 +1444,1074 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>nP1i5US1</t>
+          <t>EuakNmc1</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>0Ija0Ej9</t>
-        </is>
-      </c>
-      <c r="P6" t="n">
-        <v>20.75</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>185.75</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S6" t="n">
-        <v>4</v>
-      </c>
-      <c r="T6" t="n">
-        <v>294</v>
-      </c>
-      <c r="U6" t="n">
-        <v>66900000</v>
-      </c>
-      <c r="V6" t="n">
-        <v>336</v>
-      </c>
-      <c r="W6" t="n">
-        <v>27.33333333333333</v>
-      </c>
-      <c r="X6" t="n">
-        <v>188.6666666666667</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>1.333333333333333</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>3</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>213</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>6550000</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>224</v>
-      </c>
+          <t>nJQmYp1B</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr"/>
+      <c r="X6" t="inlineStr"/>
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="inlineStr"/>
+      <c r="AA6" t="inlineStr"/>
+      <c r="AB6" t="inlineStr"/>
+      <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="n">
-        <v>24.85090909090909</v>
+        <v>24.12986111111111</v>
       </c>
       <c r="AE6" t="n">
-        <v>182.64</v>
+        <v>183.4407986111111</v>
       </c>
       <c r="AF6" t="n">
-        <v>2.106666666666666</v>
+        <v>1.676736111111111</v>
       </c>
       <c r="AG6" t="n">
-        <v>80.28</v>
+        <v>76.90746527777779</v>
       </c>
       <c r="AH6" t="n">
-        <v>28992121.21212121</v>
+        <v>15519635.41666666</v>
       </c>
       <c r="AI6" t="n">
-        <v>83.77575757575758</v>
+        <v>81.31545138888889</v>
       </c>
       <c r="AJ6" t="n">
-        <v>27.88888888888889</v>
+        <v>26.51950757575758</v>
       </c>
       <c r="AK6" t="n">
-        <v>182.4091503267974</v>
+        <v>185.7345328282828</v>
       </c>
       <c r="AL6" t="n">
-        <v>1.247712418300653</v>
+        <v>1.803156565656566</v>
       </c>
       <c r="AM6" t="n">
-        <v>73.13856209150327</v>
+        <v>75.0542297979798</v>
       </c>
       <c r="AN6" t="n">
-        <v>3579689.54248366</v>
+        <v>8872863.005050506</v>
       </c>
       <c r="AO6" t="n">
-        <v>75.03398692810457</v>
+        <v>78.69816919191919</v>
       </c>
       <c r="AP6" t="n">
-        <v>24.82412804586718</v>
+        <v>23.78294700655382</v>
       </c>
       <c r="AQ6" t="n">
-        <v>185.1450257471997</v>
+        <v>184.0116076454505</v>
       </c>
       <c r="AR6" t="n">
-        <v>1.702190723929854</v>
+        <v>1.399164250030156</v>
       </c>
       <c r="AS6" t="n">
-        <v>76.87710666949798</v>
+        <v>71.49686218386876</v>
       </c>
       <c r="AT6" t="n">
-        <v>18126442.72796446</v>
+        <v>5656665.465677898</v>
       </c>
       <c r="AU6" t="n">
-        <v>81.50249376227637</v>
+        <v>78.66426963129749</v>
       </c>
       <c r="AV6" t="n">
-        <v>26.78760504201681</v>
+        <v>24.55683940242763</v>
       </c>
       <c r="AW6" t="n">
-        <v>182.8982285841318</v>
+        <v>185.0505368814192</v>
       </c>
       <c r="AX6" t="n">
-        <v>1.064620737692483</v>
+        <v>1.409700338468721</v>
       </c>
       <c r="AY6" t="n">
-        <v>70.48407930816735</v>
+        <v>71.84159809757236</v>
       </c>
       <c r="AZ6" t="n">
-        <v>2374219.376147588</v>
+        <v>5627775.589402428</v>
       </c>
       <c r="BA6" t="n">
-        <v>73.50472590013746</v>
+        <v>77.73592145191409</v>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>0KMe4S4D</t>
+          <t>IkCftsQm</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>8f6APkLc</t>
+          <t>A15eUM4C</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>SxFxJ44k</t>
+          <t>QVJwrCwI</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45528.5625</v>
+        <v>45535.4375</v>
       </c>
       <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">storks s 
+  ger </t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">holstein stadion
+  kiel </t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>15034</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>63WsD2ei</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>nwkTahLL</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>59</v>
+      </c>
+      <c r="I7" t="n">
+        <v>591</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>ILyJuN3g</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>dfNCCCzS</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="inlineStr"/>
+      <c r="X7" t="inlineStr"/>
+      <c r="Y7" t="inlineStr"/>
+      <c r="Z7" t="inlineStr"/>
+      <c r="AA7" t="inlineStr"/>
+      <c r="AB7" t="inlineStr"/>
+      <c r="AC7" t="inlineStr"/>
+      <c r="AD7" t="n">
+        <v>25.1949494949495</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>186.1567676767677</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>1.084747474747475</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>68.59646464646464</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>1761303.030303031</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>72.54494949494951</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>25.39407407407408</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>186.6725925925926</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>1.564444444444444</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>75.71333333333332</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>10651407.40740741</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>79.47703703703704</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>25.12022515527951</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>185.9334239130435</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>1.014665286404417</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>66.5940734989648</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>1395265.376984127</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>71.16014492753622</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>24.12706119162641</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>183.7472222222222</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>1.246602254428341</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>73.50627214170692</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>8361891.304347825</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>78.35681159420288</v>
+      </c>
+      <c r="BB7" t="inlineStr">
+        <is>
+          <t>KUx4Q7x1</t>
+        </is>
+      </c>
+      <c r="BC7" t="inlineStr">
+        <is>
+          <t>f3ddUIXs</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>61DvZGfm</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>45535.4375</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">osmers h 
+  ger </t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mhparena
+  stuttgart </t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>60449</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>nJQmYp1B</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>EuakNmc1</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>59</v>
+      </c>
+      <c r="I8" t="n">
+        <v>591</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>fiEQZ7C7</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>8vndvXTk</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" t="inlineStr"/>
+      <c r="X8" t="inlineStr"/>
+      <c r="Y8" t="inlineStr"/>
+      <c r="Z8" t="inlineStr"/>
+      <c r="AA8" t="inlineStr"/>
+      <c r="AB8" t="inlineStr"/>
+      <c r="AC8" t="inlineStr"/>
+      <c r="AD8" t="n">
+        <v>24.38503787878788</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>184.6373106060606</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>1.49854797979798</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>76.09526515151515</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>11807380.05050505</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>79.15915404040403</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>25.85965909090909</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>183.2630681818182</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>1.574431818181818</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>74.44204545454545</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>6720170.454545455</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>78.25568181818181</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>24.09893353174603</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>182.931994047619</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>1.245535714285714</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>70.96324404761904</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>5420341.021825397</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>75.95982142857143</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>25.96584821428571</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>185.0104166666667</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>1.484573412698412</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>72.23660714285714</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>4440523.933531746</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>76.76636904761904</v>
+      </c>
+      <c r="BB8" t="inlineStr">
+        <is>
+          <t>YZPE6Sx7</t>
+        </is>
+      </c>
+      <c r="BC8" t="inlineStr">
+        <is>
+          <t>hpYJ6izc</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>0OYDmG9t</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>45535.4375</v>
+      </c>
+      <c r="C9" t="inlineStr">
         <is>
           <t xml:space="preserve">zwayer f 
   ger </t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">signal iduna park
-  dortmund </t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>81365</v>
-      </c>
-      <c r="F7" t="inlineStr">
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">weserstadion
+  bremen </t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>42100</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Ig1f1fy3</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
         <is>
           <t>nP1i5US1</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>8vndvXTk</t>
-        </is>
-      </c>
-      <c r="H7" t="n">
+      <c r="H9" t="n">
         <v>59</v>
       </c>
-      <c r="I7" t="n">
+      <c r="I9" t="n">
         <v>591</v>
       </c>
-      <c r="J7" t="n">
+      <c r="J9" t="n">
         <v>0</v>
       </c>
-      <c r="K7" t="n">
+      <c r="K9" t="n">
         <v>20242025</v>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>germany</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>bundesliga</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>v9k3aY5F</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
         <is>
           <t>0Ija0Ej9</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>EuakNmc1</t>
-        </is>
-      </c>
-      <c r="P7" t="n">
-        <v>22</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>182.5</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S7" t="n">
-        <v>2</v>
-      </c>
-      <c r="T7" t="n">
-        <v>143</v>
-      </c>
-      <c r="U7" t="n">
-        <v>29000000</v>
-      </c>
-      <c r="V7" t="n">
-        <v>161</v>
-      </c>
-      <c r="W7" t="n">
-        <v>19</v>
-      </c>
-      <c r="X7" t="n">
-        <v>180</v>
-      </c>
-      <c r="Y7" t="n">
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="inlineStr"/>
+      <c r="X9" t="inlineStr"/>
+      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="inlineStr"/>
+      <c r="AA9" t="inlineStr"/>
+      <c r="AB9" t="inlineStr"/>
+      <c r="AC9" t="inlineStr"/>
+      <c r="AD9" t="n">
+        <v>25.97727272727273</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>183.4318181818182</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>1.170454545454546</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>73.21590909090909</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>4900852.272727272</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>76.18181818181819</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>25.40113636363636</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>184.9142045454545</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>2.313068181818182</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>80.11875000000001</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>30029545.45454545</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>83.30056818181818</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>24.85632792519181</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>184.5575110133203</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>1.173347379331214</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>68.60912715105111</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>2601391.69237966</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>74.30081731395839</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>24.88488828502416</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>184.0247207125604</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>1.974901871980677</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>77.5977344289165</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>19987353.8863009</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>82.24436572636301</v>
+      </c>
+      <c r="BB9" t="inlineStr">
+        <is>
+          <t>2VSFgl3c</t>
+        </is>
+      </c>
+      <c r="BC9" t="inlineStr">
+        <is>
+          <t>UgdQz0fK</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>AVR8vwXP</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>45535.5625</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">brand b 
+  ger </t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bayarena
+  leverkusen </t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>30210</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>4jcj2zMd</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>KbS1suSm</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>59</v>
+      </c>
+      <c r="I10" t="n">
+        <v>591</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>WG9pOTse</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>nP1i5US1</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="inlineStr"/>
+      <c r="W10" t="inlineStr"/>
+      <c r="X10" t="inlineStr"/>
+      <c r="Y10" t="inlineStr"/>
+      <c r="Z10" t="inlineStr"/>
+      <c r="AA10" t="inlineStr"/>
+      <c r="AB10" t="inlineStr"/>
+      <c r="AC10" t="inlineStr"/>
+      <c r="AD10" t="n">
+        <v>25.60690235690236</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>184.957842312009</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>2.09760101010101</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>81.46531986531987</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>34631299.10213244</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>84.30244107744107</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>24.84886363636364</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>182.6511363636364</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>2.105681818181818</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>80.24545454545455</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>28893181.81818182</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>83.77840909090909</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>23.13491407665702</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>181.8688975838623</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>1.69881777896652</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>78.7255208774755</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>33311393.51705093</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>84.15514643685411</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>24.8385922652227</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>185.125544971333</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>1.713859359239794</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>77.0028430582099</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>18406734.50191113</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>81.53011567991187</v>
+      </c>
+      <c r="BB10" t="inlineStr">
+        <is>
+          <t>M5BRZDsC</t>
+        </is>
+      </c>
+      <c r="BC10" t="inlineStr">
+        <is>
+          <t>8f6APkLc</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>W8b4TCOO</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>45536.4375</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stegemann s 
+  ger </t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">voith arena
+  heidenheim </t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>15000</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>KWixEVWi</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>fTVNku3I</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>59</v>
+      </c>
+      <c r="I11" t="n">
+        <v>591</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="inlineStr"/>
+      <c r="W11" t="inlineStr"/>
+      <c r="X11" t="inlineStr"/>
+      <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="inlineStr"/>
+      <c r="AA11" t="inlineStr"/>
+      <c r="AB11" t="inlineStr"/>
+      <c r="AC11" t="inlineStr"/>
+      <c r="AD11" t="n">
+        <v>25.81666666666667</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>186.9015151515151</v>
+      </c>
+      <c r="AF11" t="n">
         <v>1</v>
       </c>
-      <c r="Z7" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>121</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>1575000</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>159</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>25.38787878787879</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>184.8551515151515</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>2.293939393939394</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>80</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>29471515.15151515</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>83.26060606060607</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>24.13851851851852</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>183.3451851851852</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>1.671851851851852</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>76.8762962962963</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>15500111.11111111</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>81.26148148148148</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>25.00185185185186</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>183.9712962962963</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>1.993518518518518</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>77.60859788359788</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>19937235.44973545</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>82.17949735449734</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>23.98952943856968</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>183.9351885060244</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>1.404722568453219</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>71.51946001367054</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>5542197.549354671</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>78.49802795759453</v>
-      </c>
-      <c r="BB7" t="inlineStr">
-        <is>
-          <t>AgnJojCs</t>
-        </is>
-      </c>
-      <c r="BC7" t="inlineStr">
-        <is>
-          <t>UgdQz0fK</t>
+      <c r="AG11" t="n">
+        <v>72.875</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>4350833.333333333</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>75.22045454545453</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>25.35034722222222</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>185.8133522727273</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>1.396243686868687</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>74.28888888888889</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>6341619.318181818</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>77.2822601010101</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>27.03253968253968</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>183.2093915343915</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>69.32208994708995</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>1942023.809523809</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>71.08320105820106</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>23.90971984886459</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>184.0197940400243</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>1.169671812106023</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>71.19951352101846</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>3934073.512379434</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>76.5209765654667</v>
+      </c>
+      <c r="BB11" t="inlineStr">
+        <is>
+          <t>lli2SfLl</t>
+        </is>
+      </c>
+      <c r="BC11" t="inlineStr">
+        <is>
+          <t>4fuCGs9P</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>2T6mXfPa</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>45536.52083333334</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">welz t 
+  ger </t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">allianz arena
+  munich </t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>75024</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>nVp0wiqd</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>fiEQZ7C7</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>59</v>
+      </c>
+      <c r="I12" t="n">
+        <v>591</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>nJQmYp1B</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr"/>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="inlineStr"/>
+      <c r="W12" t="inlineStr"/>
+      <c r="X12" t="inlineStr"/>
+      <c r="Y12" t="inlineStr"/>
+      <c r="Z12" t="inlineStr"/>
+      <c r="AA12" t="inlineStr"/>
+      <c r="AB12" t="inlineStr"/>
+      <c r="AC12" t="inlineStr"/>
+      <c r="AD12" t="n">
+        <v>27.08484848484849</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>184.9212121212121</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>3.03030303030303</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>81.87878787878786</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>41254848.48484848</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>84.53333333333333</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>27.08680555555556</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>183.6912878787879</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>1.694633838383838</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>75.30239898989899</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>8589299.242424242</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>77.16811868686868</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>24.62070774406889</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>182.3024630782438</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>2.250397657387158</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>78.52101362272482</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>29928093.1228529</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>83.50805072369886</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>25.06481131497221</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>184.5251901833388</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>1.467589490029422</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>73.46279131933093</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>6291650.449152773</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>76.73148028018414</v>
+      </c>
+      <c r="BB12" t="inlineStr">
+        <is>
+          <t>QevvB2nf</t>
+        </is>
+      </c>
+      <c r="BC12" t="inlineStr">
+        <is>
+          <t>GzfvcwRj</t>
         </is>
       </c>
     </row>

--- a/data/germany/p6_deployment/data_preparation/df_filled.xlsx
+++ b/data/germany/p6_deployment/data_preparation/df_filled.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BC12"/>
+  <dimension ref="A1:AO10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -505,200 +505,130 @@
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>mean_age_player_miss_home</t>
+          <t>mean_age_player_start_home</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>mean_hei_player_miss_home</t>
+          <t>mean_hei_player_start_home</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>mean_int_rep_player_miss_home</t>
+          <t>mean_int_rep_player_start_home</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>n_player_miss_home</t>
+          <t>mean_rat_player_start_home</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>sum_rat_player_miss_home</t>
+          <t>mean_val_player_start_home</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>sum_val_player_miss_home</t>
+          <t>mean_pot_player_start_home</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>sum_pot_player_miss_home</t>
+          <t>mean_age_player_start_away</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>mean_age_player_miss_away</t>
+          <t>mean_hei_player_start_away</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>mean_hei_player_miss_away</t>
+          <t>mean_int_rep_player_start_away</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>mean_int_rep_player_miss_away</t>
+          <t>mean_rat_player_start_away</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>n_player_miss_away</t>
+          <t>mean_val_player_start_away</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>sum_rat_player_miss_away</t>
+          <t>mean_pot_player_start_away</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>sum_val_player_miss_away</t>
+          <t>mean_age_player_sub_home</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>sum_pot_player_miss_away</t>
+          <t>mean_hei_player_sub_home</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>mean_age_player_start_home</t>
+          <t>mean_int_rep_player_sub_home</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>mean_hei_player_start_home</t>
+          <t>mean_rat_player_sub_home</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>mean_int_rep_player_start_home</t>
+          <t>mean_val_player_sub_home</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>mean_rat_player_start_home</t>
+          <t>mean_pot_player_sub_home</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>mean_val_player_start_home</t>
+          <t>mean_age_player_sub_away</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>mean_pot_player_start_home</t>
+          <t>mean_hei_player_sub_away</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>mean_age_player_start_away</t>
+          <t>mean_int_rep_player_sub_away</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
-          <t>mean_hei_player_start_away</t>
+          <t>mean_rat_player_sub_away</t>
         </is>
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
-          <t>mean_int_rep_player_start_away</t>
+          <t>mean_val_player_sub_away</t>
         </is>
       </c>
       <c r="AM1" s="1" t="inlineStr">
         <is>
-          <t>mean_rat_player_start_away</t>
+          <t>mean_pot_player_sub_away</t>
         </is>
       </c>
       <c r="AN1" s="1" t="inlineStr">
         <is>
-          <t>mean_val_player_start_away</t>
+          <t>id_coach_home</t>
         </is>
       </c>
       <c r="AO1" s="1" t="inlineStr">
-        <is>
-          <t>mean_pot_player_start_away</t>
-        </is>
-      </c>
-      <c r="AP1" s="1" t="inlineStr">
-        <is>
-          <t>mean_age_player_sub_home</t>
-        </is>
-      </c>
-      <c r="AQ1" s="1" t="inlineStr">
-        <is>
-          <t>mean_hei_player_sub_home</t>
-        </is>
-      </c>
-      <c r="AR1" s="1" t="inlineStr">
-        <is>
-          <t>mean_int_rep_player_sub_home</t>
-        </is>
-      </c>
-      <c r="AS1" s="1" t="inlineStr">
-        <is>
-          <t>mean_rat_player_sub_home</t>
-        </is>
-      </c>
-      <c r="AT1" s="1" t="inlineStr">
-        <is>
-          <t>mean_val_player_sub_home</t>
-        </is>
-      </c>
-      <c r="AU1" s="1" t="inlineStr">
-        <is>
-          <t>mean_pot_player_sub_home</t>
-        </is>
-      </c>
-      <c r="AV1" s="1" t="inlineStr">
-        <is>
-          <t>mean_age_player_sub_away</t>
-        </is>
-      </c>
-      <c r="AW1" s="1" t="inlineStr">
-        <is>
-          <t>mean_hei_player_sub_away</t>
-        </is>
-      </c>
-      <c r="AX1" s="1" t="inlineStr">
-        <is>
-          <t>mean_int_rep_player_sub_away</t>
-        </is>
-      </c>
-      <c r="AY1" s="1" t="inlineStr">
-        <is>
-          <t>mean_rat_player_sub_away</t>
-        </is>
-      </c>
-      <c r="AZ1" s="1" t="inlineStr">
-        <is>
-          <t>mean_val_player_sub_away</t>
-        </is>
-      </c>
-      <c r="BA1" s="1" t="inlineStr">
-        <is>
-          <t>mean_pot_player_sub_away</t>
-        </is>
-      </c>
-      <c r="BB1" s="1" t="inlineStr">
-        <is>
-          <t>id_coach_home</t>
-        </is>
-      </c>
-      <c r="BC1" s="1" t="inlineStr">
         <is>
           <t>id_coach_away</t>
         </is>
@@ -707,35 +637,35 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>t0w6KHuf</t>
+          <t>djSMofvg</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45529.4375</v>
+        <v>45534.64583333334</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">siebert d 
+          <t xml:space="preserve">jablonski s 
   ger </t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">volkswagen arena
-  wolfsburg </t>
+          <t xml:space="preserve">stadion an der alten forsterei
+  berlin </t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>28917</v>
+        <v>22012</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>nwkTahLL</t>
+          <t>pzHW4oaE</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>nVp0wiqd</t>
+          <t>ILyJuN3g</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -760,169 +690,127 @@
           <t>bundesliga</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>dfNCCCzS</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>v9k3aY5F</t>
+        </is>
+      </c>
       <c r="P2" t="n">
-        <v>22</v>
+        <v>26.95170454545455</v>
       </c>
       <c r="Q2" t="n">
-        <v>180</v>
+        <v>185.0659722222222</v>
       </c>
       <c r="R2" t="n">
-        <v>1.5</v>
+        <v>1.619507575757576</v>
       </c>
       <c r="S2" t="n">
-        <v>2</v>
+        <v>75.7828914141414</v>
       </c>
       <c r="T2" t="n">
-        <v>149</v>
+        <v>8385435.606060605</v>
       </c>
       <c r="U2" t="n">
-        <v>21000000</v>
+        <v>78.17866161616162</v>
       </c>
       <c r="V2" t="n">
-        <v>164</v>
+        <v>25.82575757575757</v>
       </c>
       <c r="W2" t="n">
-        <v>21.83333333333333</v>
+        <v>185.2379797979798</v>
       </c>
       <c r="X2" t="n">
-        <v>184.8333333333333</v>
+        <v>1</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.5</v>
+        <v>69.99222222222222</v>
       </c>
       <c r="Z2" t="n">
-        <v>6</v>
+        <v>2270323.232323232</v>
       </c>
       <c r="AA2" t="n">
-        <v>430</v>
+        <v>73.13414141414141</v>
       </c>
       <c r="AB2" t="n">
-        <v>98525000</v>
+        <v>26.83493408566707</v>
       </c>
       <c r="AC2" t="n">
-        <v>489</v>
+        <v>184.1065091964513</v>
       </c>
       <c r="AD2" t="n">
-        <v>25.39407407407408</v>
+        <v>1.463121401783444</v>
       </c>
       <c r="AE2" t="n">
-        <v>186.6725925925926</v>
+        <v>73.73900926455632</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.564444444444444</v>
+        <v>5164687.434732665</v>
       </c>
       <c r="AG2" t="n">
-        <v>75.71333333333332</v>
+        <v>76.12727924884675</v>
       </c>
       <c r="AH2" t="n">
-        <v>10651407.40740741</v>
+        <v>25.58083431618261</v>
       </c>
       <c r="AI2" t="n">
-        <v>79.47703703703704</v>
+        <v>185.5206408177306</v>
       </c>
       <c r="AJ2" t="n">
-        <v>27.08484848484849</v>
+        <v>1</v>
       </c>
       <c r="AK2" t="n">
-        <v>184.9212121212121</v>
+        <v>67.09735859255983</v>
       </c>
       <c r="AL2" t="n">
-        <v>3.03030303030303</v>
+        <v>1422561.096368372</v>
       </c>
       <c r="AM2" t="n">
-        <v>81.87878787878786</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>41254848.48484848</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>84.53333333333333</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>24.12706119162641</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>183.7472222222222</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>1.246602254428341</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>73.50627214170692</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>8361891.304347825</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>78.35681159420288</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>24.62070774406889</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>182.3024630782438</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>2.250397657387158</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>78.52101362272482</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>29928093.1228529</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>83.50805072369886</v>
-      </c>
-      <c r="BB2" t="inlineStr">
-        <is>
-          <t>rFNN7oyi</t>
-        </is>
-      </c>
-      <c r="BC2" t="inlineStr">
-        <is>
-          <t>K6A2elS9</t>
+        <v>71.5401422674333</v>
+      </c>
+      <c r="AN2" t="inlineStr">
+        <is>
+          <t>vZA6VYpf</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>4ljanukM</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>AuVMGZvJ</t>
+          <t>U3QUqY85</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45529.52083333334</v>
+        <v>45535.4375</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">jablonski s 
+          <t xml:space="preserve">schroder r 
   ger </t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">millerntor stadion
-  hamburg </t>
+          <t xml:space="preserve">vonovia ruhrstadion
+  bochum </t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>29546</v>
+        <v>26000</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>ILyJuN3g</t>
+          <t>8Y2m6ADe</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>KWixEVWi</t>
+          <t>88HSzjDr</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -949,153 +837,129 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>v9k3aY5F</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr"/>
-      <c r="R3" t="inlineStr"/>
-      <c r="S3" t="inlineStr"/>
-      <c r="T3" t="inlineStr"/>
-      <c r="U3" t="inlineStr"/>
-      <c r="V3" t="inlineStr"/>
+          <t>0Ija0Ej9</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>WG9pOTse</t>
+        </is>
+      </c>
+      <c r="P3" t="n">
+        <v>27.83950617283951</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>182.4489197530864</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.233950617283951</v>
+      </c>
+      <c r="S3" t="n">
+        <v>73.04058641975308</v>
+      </c>
+      <c r="T3" t="n">
+        <v>3510852.62345679</v>
+      </c>
+      <c r="U3" t="n">
+        <v>74.9695987654321</v>
+      </c>
+      <c r="V3" t="n">
+        <v>25.19690656565657</v>
+      </c>
       <c r="W3" t="n">
-        <v>23</v>
+        <v>184.5984848484849</v>
       </c>
       <c r="X3" t="n">
-        <v>186</v>
+        <v>1.523484848484848</v>
       </c>
       <c r="Y3" t="n">
-        <v>1</v>
+        <v>75.34444444444443</v>
       </c>
       <c r="Z3" t="n">
-        <v>1</v>
+        <v>8616609.848484848</v>
       </c>
       <c r="AA3" t="n">
-        <v>66</v>
+        <v>78.24128787878787</v>
       </c>
       <c r="AB3" t="n">
-        <v>1100000</v>
+        <v>26.52903439153439</v>
       </c>
       <c r="AC3" t="n">
-        <v>70</v>
+        <v>183.0409195887171</v>
       </c>
       <c r="AD3" t="n">
-        <v>25.85084175084175</v>
+        <v>1.061030696709568</v>
       </c>
       <c r="AE3" t="n">
-        <v>185.2088664421998</v>
+        <v>70.23866749475064</v>
       </c>
       <c r="AF3" t="n">
-        <v>1</v>
+        <v>2328151.633028278</v>
       </c>
       <c r="AG3" t="n">
-        <v>69.99135802469135</v>
+        <v>73.66187075753723</v>
       </c>
       <c r="AH3" t="n">
-        <v>2277025.81369248</v>
+        <v>23.34266065980168</v>
       </c>
       <c r="AI3" t="n">
-        <v>73.08237934904601</v>
+        <v>184.1793037280702</v>
       </c>
       <c r="AJ3" t="n">
-        <v>25.81666666666667</v>
+        <v>1.278301392067124</v>
       </c>
       <c r="AK3" t="n">
-        <v>186.9015151515151</v>
+        <v>72.89358169540699</v>
       </c>
       <c r="AL3" t="n">
-        <v>1</v>
+        <v>6622054.439767897</v>
       </c>
       <c r="AM3" t="n">
-        <v>72.875</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>4350833.333333333</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>75.22045454545453</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>25.74994662582382</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>185.8726074445373</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>66.84020235774622</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>1325721.479624988</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>71.29296853244222</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>27.03253968253968</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>183.2093915343915</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>69.32208994708995</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>1942023.809523809</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>71.08320105820106</v>
-      </c>
-      <c r="BB3" t="inlineStr">
-        <is>
-          <t>02hM7hzd</t>
-        </is>
-      </c>
-      <c r="BC3" t="inlineStr">
-        <is>
-          <t>4ljanukM</t>
+        <v>78.54315101612727</v>
+      </c>
+      <c r="AN3" t="inlineStr">
+        <is>
+          <t>pfoInmcq</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>hAcTWKKN</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>djSMofvg</t>
+          <t>AgAeVYgC</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45534.64583333334</v>
+        <v>45535.4375</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">siebert d 
+          <t xml:space="preserve">stieler t 
   ger </t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadion an der alten forsterei
-  berlin </t>
+          <t xml:space="preserve">deutsche bank park
+  frankfurt </t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>22012</v>
+        <v>58000</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>pzHW4oaE</t>
+          <t>8vndvXTk</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>ILyJuN3g</t>
+          <t>hQAtP9Sl</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -1120,113 +984,103 @@
           <t>bundesliga</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr"/>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>EuakNmc1</t>
+        </is>
+      </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>v9k3aY5F</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="inlineStr"/>
-      <c r="S4" t="inlineStr"/>
-      <c r="T4" t="inlineStr"/>
-      <c r="U4" t="inlineStr"/>
-      <c r="V4" t="inlineStr"/>
-      <c r="W4" t="inlineStr"/>
-      <c r="X4" t="inlineStr"/>
-      <c r="Y4" t="inlineStr"/>
-      <c r="Z4" t="inlineStr"/>
-      <c r="AA4" t="inlineStr"/>
-      <c r="AB4" t="inlineStr"/>
-      <c r="AC4" t="inlineStr"/>
+          <t>nJQmYp1B</t>
+        </is>
+      </c>
+      <c r="P4" t="n">
+        <v>24.12986111111111</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>183.4407986111111</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.676736111111111</v>
+      </c>
+      <c r="S4" t="n">
+        <v>76.90746527777779</v>
+      </c>
+      <c r="T4" t="n">
+        <v>15519635.41666666</v>
+      </c>
+      <c r="U4" t="n">
+        <v>81.31545138888889</v>
+      </c>
+      <c r="V4" t="n">
+        <v>26.51950757575758</v>
+      </c>
+      <c r="W4" t="n">
+        <v>185.7345328282828</v>
+      </c>
+      <c r="X4" t="n">
+        <v>1.803156565656566</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>75.0542297979798</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>8872863.005050506</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>78.69816919191919</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>23.78294700655382</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>184.0116076454505</v>
+      </c>
       <c r="AD4" t="n">
-        <v>26.95170454545455</v>
+        <v>1.399164250030156</v>
       </c>
       <c r="AE4" t="n">
-        <v>185.0659722222222</v>
+        <v>71.49686218386876</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.619507575757576</v>
+        <v>5656665.465677898</v>
       </c>
       <c r="AG4" t="n">
-        <v>75.7828914141414</v>
+        <v>78.66426963129749</v>
       </c>
       <c r="AH4" t="n">
-        <v>8385435.606060605</v>
+        <v>24.55683940242763</v>
       </c>
       <c r="AI4" t="n">
-        <v>78.17866161616162</v>
+        <v>185.0505368814192</v>
       </c>
       <c r="AJ4" t="n">
-        <v>25.85084175084175</v>
+        <v>1.409700338468721</v>
       </c>
       <c r="AK4" t="n">
-        <v>185.2088664421998</v>
+        <v>71.84159809757236</v>
       </c>
       <c r="AL4" t="n">
-        <v>1</v>
+        <v>5627775.589402428</v>
       </c>
       <c r="AM4" t="n">
-        <v>69.99135802469135</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>2277025.81369248</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>73.08237934904601</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>26.83493408566707</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>184.1065091964513</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>1.463121401783444</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>73.73900926455633</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>5164687.434732665</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>76.12727924884676</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>25.74994662582382</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>185.8726074445373</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>66.84020235774622</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>1325721.479624988</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>71.29296853244222</v>
-      </c>
-      <c r="BB4" t="inlineStr">
-        <is>
-          <t>vZA6VYpf</t>
-        </is>
-      </c>
-      <c r="BC4" t="inlineStr">
-        <is>
-          <t>0jdIgO6t</t>
+        <v>77.73592145191409</v>
+      </c>
+      <c r="AN4" t="inlineStr">
+        <is>
+          <t>IkCftsQm</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>A15eUM4C</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>U3QUqY85</t>
+          <t>QVJwrCwI</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
@@ -1234,27 +1088,27 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">schroder r 
+          <t xml:space="preserve">siebert d 
   ger </t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">vonovia ruhrstadion
-  bochum </t>
+          <t xml:space="preserve">holstein stadion
+  kiel </t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>26000</v>
+        <v>15034</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>8Y2m6ADe</t>
+          <t>63WsD2ei</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>88HSzjDr</t>
+          <t>nwkTahLL</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -1281,115 +1135,101 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>0Ija0Ej9</t>
+          <t>ILyJuN3g</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>WG9pOTse</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="inlineStr"/>
-      <c r="S5" t="inlineStr"/>
-      <c r="T5" t="inlineStr"/>
-      <c r="U5" t="inlineStr"/>
-      <c r="V5" t="inlineStr"/>
-      <c r="W5" t="inlineStr"/>
-      <c r="X5" t="inlineStr"/>
-      <c r="Y5" t="inlineStr"/>
-      <c r="Z5" t="inlineStr"/>
-      <c r="AA5" t="inlineStr"/>
-      <c r="AB5" t="inlineStr"/>
-      <c r="AC5" t="inlineStr"/>
+          <t>dfNCCCzS</t>
+        </is>
+      </c>
+      <c r="P5" t="n">
+        <v>25.1949494949495</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>186.1567676767677</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.084747474747475</v>
+      </c>
+      <c r="S5" t="n">
+        <v>68.59646464646464</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1761303.030303031</v>
+      </c>
+      <c r="U5" t="n">
+        <v>72.54494949494951</v>
+      </c>
+      <c r="V5" t="n">
+        <v>25.30694444444445</v>
+      </c>
+      <c r="W5" t="n">
+        <v>186.5289930555556</v>
+      </c>
+      <c r="X5" t="n">
+        <v>1.568229166666667</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>75.69999999999999</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>10678663.19444444</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>79.50190972222222</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>25.12022515527951</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>185.9334239130435</v>
+      </c>
       <c r="AD5" t="n">
-        <v>27.83950617283951</v>
+        <v>1.014665286404417</v>
       </c>
       <c r="AE5" t="n">
-        <v>182.4489197530864</v>
+        <v>66.5940734989648</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.233950617283951</v>
+        <v>1395265.376984127</v>
       </c>
       <c r="AG5" t="n">
-        <v>73.04058641975308</v>
+        <v>71.16014492753622</v>
       </c>
       <c r="AH5" t="n">
-        <v>3510852.62345679</v>
+        <v>24.26911986714976</v>
       </c>
       <c r="AI5" t="n">
-        <v>74.9695987654321</v>
+        <v>183.8380208333333</v>
       </c>
       <c r="AJ5" t="n">
-        <v>25.19690656565657</v>
+        <v>1.25618961352657</v>
       </c>
       <c r="AK5" t="n">
-        <v>184.5984848484849</v>
+        <v>73.62463013285024</v>
       </c>
       <c r="AL5" t="n">
-        <v>1.523484848484848</v>
+        <v>8505106.43115942</v>
       </c>
       <c r="AM5" t="n">
-        <v>75.34444444444443</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>8616609.848484848</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>78.24128787878787</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>26.52903439153439</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>183.0409195887171</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>1.061030696709568</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>70.23866749475064</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>2328151.633028278</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>73.66187075753723</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>23.34266065980168</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>184.1793037280702</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>1.278301392067124</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>72.89358169540699</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>6622054.439767897</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>78.54315101612727</v>
-      </c>
-      <c r="BB5" t="inlineStr">
-        <is>
-          <t>pfoInmcq</t>
-        </is>
-      </c>
-      <c r="BC5" t="inlineStr">
-        <is>
-          <t>hAcTWKKN</t>
+        <v>78.35117753623189</v>
+      </c>
+      <c r="AN5" t="inlineStr">
+        <is>
+          <t>KUx4Q7x1</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>K6A2elS9</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>AgAeVYgC</t>
+          <t>61DvZGfm</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -1397,27 +1237,27 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">stieler t 
+          <t xml:space="preserve">osmers h 
   ger </t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">deutsche bank park
-  frankfurt </t>
+          <t xml:space="preserve">mhparena
+  stuttgart </t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>58000</v>
+        <v>60449</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>8vndvXTk</t>
+          <t>nJQmYp1B</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>hQAtP9Sl</t>
+          <t>EuakNmc1</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -1444,115 +1284,101 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>EuakNmc1</t>
+          <t>fiEQZ7C7</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>nJQmYp1B</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr"/>
-      <c r="R6" t="inlineStr"/>
-      <c r="S6" t="inlineStr"/>
-      <c r="T6" t="inlineStr"/>
-      <c r="U6" t="inlineStr"/>
-      <c r="V6" t="inlineStr"/>
-      <c r="W6" t="inlineStr"/>
-      <c r="X6" t="inlineStr"/>
-      <c r="Y6" t="inlineStr"/>
-      <c r="Z6" t="inlineStr"/>
-      <c r="AA6" t="inlineStr"/>
-      <c r="AB6" t="inlineStr"/>
-      <c r="AC6" t="inlineStr"/>
+          <t>8vndvXTk</t>
+        </is>
+      </c>
+      <c r="P6" t="n">
+        <v>24.38503787878788</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>184.6373106060606</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.49854797979798</v>
+      </c>
+      <c r="S6" t="n">
+        <v>76.09526515151515</v>
+      </c>
+      <c r="T6" t="n">
+        <v>11807380.05050505</v>
+      </c>
+      <c r="U6" t="n">
+        <v>79.15915404040403</v>
+      </c>
+      <c r="V6" t="n">
+        <v>25.85965909090909</v>
+      </c>
+      <c r="W6" t="n">
+        <v>183.2630681818182</v>
+      </c>
+      <c r="X6" t="n">
+        <v>1.574431818181818</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>74.44204545454545</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>6720170.454545455</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>78.25568181818181</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>24.09893353174603</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>182.9319940476191</v>
+      </c>
       <c r="AD6" t="n">
-        <v>24.12986111111111</v>
+        <v>1.245535714285714</v>
       </c>
       <c r="AE6" t="n">
-        <v>183.4407986111111</v>
+        <v>70.96324404761904</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.676736111111111</v>
+        <v>5420341.021825396</v>
       </c>
       <c r="AG6" t="n">
-        <v>76.90746527777779</v>
+        <v>75.95982142857143</v>
       </c>
       <c r="AH6" t="n">
-        <v>15519635.41666666</v>
+        <v>25.96584821428571</v>
       </c>
       <c r="AI6" t="n">
-        <v>81.31545138888889</v>
+        <v>185.0104166666667</v>
       </c>
       <c r="AJ6" t="n">
-        <v>26.51950757575758</v>
+        <v>1.484573412698412</v>
       </c>
       <c r="AK6" t="n">
-        <v>185.7345328282828</v>
+        <v>72.23660714285714</v>
       </c>
       <c r="AL6" t="n">
-        <v>1.803156565656566</v>
+        <v>4440523.933531746</v>
       </c>
       <c r="AM6" t="n">
-        <v>75.0542297979798</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>8872863.005050506</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>78.69816919191919</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>23.78294700655382</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>184.0116076454505</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>1.399164250030156</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>71.49686218386876</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>5656665.465677898</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>78.66426963129749</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>24.55683940242763</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>185.0505368814192</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>1.409700338468721</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>71.84159809757236</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>5627775.589402428</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>77.73592145191409</v>
-      </c>
-      <c r="BB6" t="inlineStr">
-        <is>
-          <t>IkCftsQm</t>
-        </is>
-      </c>
-      <c r="BC6" t="inlineStr">
-        <is>
-          <t>A15eUM4C</t>
+        <v>76.76636904761904</v>
+      </c>
+      <c r="AN6" t="inlineStr">
+        <is>
+          <t>YZPE6Sx7</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>hpYJ6izc</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>QVJwrCwI</t>
+          <t>0OYDmG9t</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
@@ -1560,27 +1386,27 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">storks s 
+          <t xml:space="preserve">zwayer f 
   ger </t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">holstein stadion
-  kiel </t>
+          <t xml:space="preserve">weserstadion
+  bremen </t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>15034</v>
+        <v>42100</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>63WsD2ei</t>
+          <t>Ig1f1fy3</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>nwkTahLL</t>
+          <t>nP1i5US1</t>
         </is>
       </c>
       <c r="H7" t="n">
@@ -1607,143 +1433,129 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>ILyJuN3g</t>
+          <t>v9k3aY5F</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>dfNCCCzS</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr"/>
-      <c r="R7" t="inlineStr"/>
-      <c r="S7" t="inlineStr"/>
-      <c r="T7" t="inlineStr"/>
-      <c r="U7" t="inlineStr"/>
-      <c r="V7" t="inlineStr"/>
-      <c r="W7" t="inlineStr"/>
-      <c r="X7" t="inlineStr"/>
-      <c r="Y7" t="inlineStr"/>
-      <c r="Z7" t="inlineStr"/>
-      <c r="AA7" t="inlineStr"/>
-      <c r="AB7" t="inlineStr"/>
-      <c r="AC7" t="inlineStr"/>
+          <t>0Ija0Ej9</t>
+        </is>
+      </c>
+      <c r="P7" t="n">
+        <v>25.97727272727273</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>183.4318181818182</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.170454545454546</v>
+      </c>
+      <c r="S7" t="n">
+        <v>73.21590909090909</v>
+      </c>
+      <c r="T7" t="n">
+        <v>4900852.272727272</v>
+      </c>
+      <c r="U7" t="n">
+        <v>76.18181818181819</v>
+      </c>
+      <c r="V7" t="n">
+        <v>25.40113636363636</v>
+      </c>
+      <c r="W7" t="n">
+        <v>184.9142045454545</v>
+      </c>
+      <c r="X7" t="n">
+        <v>2.313068181818182</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>80.11875000000001</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>30029545.45454545</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>83.30056818181818</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>24.85632792519181</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>184.5575110133203</v>
+      </c>
       <c r="AD7" t="n">
-        <v>25.1949494949495</v>
+        <v>1.173347379331214</v>
       </c>
       <c r="AE7" t="n">
-        <v>186.1567676767677</v>
+        <v>68.60912715105111</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.084747474747475</v>
+        <v>2601391.69237966</v>
       </c>
       <c r="AG7" t="n">
-        <v>68.59646464646464</v>
+        <v>74.30081731395838</v>
       </c>
       <c r="AH7" t="n">
-        <v>1761303.030303031</v>
+        <v>24.88488828502416</v>
       </c>
       <c r="AI7" t="n">
-        <v>72.54494949494951</v>
+        <v>184.0247207125604</v>
       </c>
       <c r="AJ7" t="n">
-        <v>25.39407407407408</v>
+        <v>1.974901871980677</v>
       </c>
       <c r="AK7" t="n">
-        <v>186.6725925925926</v>
+        <v>77.5977344289165</v>
       </c>
       <c r="AL7" t="n">
-        <v>1.564444444444444</v>
+        <v>19987353.8863009</v>
       </c>
       <c r="AM7" t="n">
-        <v>75.71333333333332</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>10651407.40740741</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>79.47703703703704</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>25.12022515527951</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>185.9334239130435</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>1.014665286404417</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>66.5940734989648</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>1395265.376984127</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>71.16014492753622</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>24.12706119162641</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>183.7472222222222</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>1.246602254428341</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>73.50627214170692</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>8361891.304347825</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>78.35681159420288</v>
-      </c>
-      <c r="BB7" t="inlineStr">
-        <is>
-          <t>KUx4Q7x1</t>
-        </is>
-      </c>
-      <c r="BC7" t="inlineStr">
-        <is>
-          <t>f3ddUIXs</t>
+        <v>82.24436572636301</v>
+      </c>
+      <c r="AN7" t="inlineStr">
+        <is>
+          <t>2VSFgl3c</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>UgdQz0fK</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>61DvZGfm</t>
+          <t>AVR8vwXP</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45535.4375</v>
+        <v>45535.5625</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">osmers h 
+          <t xml:space="preserve">brand b 
   ger </t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">mhparena
-  stuttgart </t>
+          <t xml:space="preserve">bayarena
+  leverkusen </t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>60449</v>
+        <v>30210</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>nJQmYp1B</t>
+          <t>4jcj2zMd</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>EuakNmc1</t>
+          <t>KbS1suSm</t>
         </is>
       </c>
       <c r="H8" t="n">
@@ -1770,143 +1582,129 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>fiEQZ7C7</t>
+          <t>WG9pOTse</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>8vndvXTk</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="inlineStr"/>
-      <c r="R8" t="inlineStr"/>
-      <c r="S8" t="inlineStr"/>
-      <c r="T8" t="inlineStr"/>
-      <c r="U8" t="inlineStr"/>
-      <c r="V8" t="inlineStr"/>
-      <c r="W8" t="inlineStr"/>
-      <c r="X8" t="inlineStr"/>
-      <c r="Y8" t="inlineStr"/>
-      <c r="Z8" t="inlineStr"/>
-      <c r="AA8" t="inlineStr"/>
-      <c r="AB8" t="inlineStr"/>
-      <c r="AC8" t="inlineStr"/>
+          <t>nP1i5US1</t>
+        </is>
+      </c>
+      <c r="P8" t="n">
+        <v>25.60690235690236</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>184.957842312009</v>
+      </c>
+      <c r="R8" t="n">
+        <v>2.09760101010101</v>
+      </c>
+      <c r="S8" t="n">
+        <v>81.46531986531987</v>
+      </c>
+      <c r="T8" t="n">
+        <v>34631299.10213244</v>
+      </c>
+      <c r="U8" t="n">
+        <v>84.30244107744107</v>
+      </c>
+      <c r="V8" t="n">
+        <v>24.84886363636364</v>
+      </c>
+      <c r="W8" t="n">
+        <v>182.6511363636364</v>
+      </c>
+      <c r="X8" t="n">
+        <v>2.105681818181818</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>80.24545454545455</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>28893181.81818182</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>83.77840909090909</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>23.13491407665702</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>181.8688975838623</v>
+      </c>
       <c r="AD8" t="n">
-        <v>24.38503787878788</v>
+        <v>1.69881777896652</v>
       </c>
       <c r="AE8" t="n">
-        <v>184.6373106060606</v>
+        <v>78.7255208774755</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.49854797979798</v>
+        <v>33311393.51705093</v>
       </c>
       <c r="AG8" t="n">
-        <v>76.09526515151515</v>
+        <v>84.15514643685411</v>
       </c>
       <c r="AH8" t="n">
-        <v>11807380.05050505</v>
+        <v>24.8385922652227</v>
       </c>
       <c r="AI8" t="n">
-        <v>79.15915404040403</v>
+        <v>185.125544971333</v>
       </c>
       <c r="AJ8" t="n">
-        <v>25.85965909090909</v>
+        <v>1.713859359239794</v>
       </c>
       <c r="AK8" t="n">
-        <v>183.2630681818182</v>
+        <v>77.0028430582099</v>
       </c>
       <c r="AL8" t="n">
-        <v>1.574431818181818</v>
+        <v>18406734.50191113</v>
       </c>
       <c r="AM8" t="n">
-        <v>74.44204545454545</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>6720170.454545455</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>78.25568181818181</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>24.09893353174603</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>182.931994047619</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>1.245535714285714</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>70.96324404761904</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>5420341.021825397</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>75.95982142857143</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>25.96584821428571</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>185.0104166666667</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>1.484573412698412</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>72.23660714285714</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>4440523.933531746</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>76.76636904761904</v>
-      </c>
-      <c r="BB8" t="inlineStr">
-        <is>
-          <t>YZPE6Sx7</t>
-        </is>
-      </c>
-      <c r="BC8" t="inlineStr">
-        <is>
-          <t>hpYJ6izc</t>
+        <v>81.53011567991187</v>
+      </c>
+      <c r="AN8" t="inlineStr">
+        <is>
+          <t>M5BRZDsC</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>8f6APkLc</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>0OYDmG9t</t>
+          <t>W8b4TCOO</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45535.4375</v>
+        <v>45536.4375</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">zwayer f 
+          <t xml:space="preserve">stegemann s 
   ger </t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">weserstadion
-  bremen </t>
+          <t xml:space="preserve">voith arena
+  heidenheim </t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>42100</v>
+        <v>15000</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ig1f1fy3</t>
+          <t>KWixEVWi</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>nP1i5US1</t>
+          <t>fTVNku3I</t>
         </is>
       </c>
       <c r="H9" t="n">
@@ -1931,145 +1729,123 @@
           <t>bundesliga</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>v9k3aY5F</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>0Ija0Ej9</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr"/>
-      <c r="Q9" t="inlineStr"/>
-      <c r="R9" t="inlineStr"/>
-      <c r="S9" t="inlineStr"/>
-      <c r="T9" t="inlineStr"/>
-      <c r="U9" t="inlineStr"/>
-      <c r="V9" t="inlineStr"/>
-      <c r="W9" t="inlineStr"/>
-      <c r="X9" t="inlineStr"/>
-      <c r="Y9" t="inlineStr"/>
-      <c r="Z9" t="inlineStr"/>
-      <c r="AA9" t="inlineStr"/>
-      <c r="AB9" t="inlineStr"/>
-      <c r="AC9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="n">
+        <v>25.8515625</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>186.9779829545454</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1</v>
+      </c>
+      <c r="S9" t="n">
+        <v>72.828125</v>
+      </c>
+      <c r="T9" t="n">
+        <v>4253906.25</v>
+      </c>
+      <c r="U9" t="n">
+        <v>75.15198863636363</v>
+      </c>
+      <c r="V9" t="n">
+        <v>25.35034722222222</v>
+      </c>
+      <c r="W9" t="n">
+        <v>185.8133522727273</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1.396243686868687</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>74.28888888888889</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>6341619.318181818</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>77.2822601010101</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>26.94022817460317</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>183.3282490079365</v>
+      </c>
       <c r="AD9" t="n">
-        <v>25.97727272727273</v>
+        <v>1</v>
       </c>
       <c r="AE9" t="n">
-        <v>183.4318181818182</v>
+        <v>69.34015376984127</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.170454545454546</v>
+        <v>1937487.599206349</v>
       </c>
       <c r="AG9" t="n">
-        <v>73.21590909090909</v>
+        <v>71.13702876984127</v>
       </c>
       <c r="AH9" t="n">
-        <v>4900852.272727272</v>
+        <v>23.90971984886459</v>
       </c>
       <c r="AI9" t="n">
-        <v>76.18181818181819</v>
+        <v>184.0197940400243</v>
       </c>
       <c r="AJ9" t="n">
-        <v>25.40113636363636</v>
+        <v>1.169671812106023</v>
       </c>
       <c r="AK9" t="n">
-        <v>184.9142045454545</v>
+        <v>71.19951352101846</v>
       </c>
       <c r="AL9" t="n">
-        <v>2.313068181818182</v>
+        <v>3934073.512379434</v>
       </c>
       <c r="AM9" t="n">
-        <v>80.11875000000001</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>30029545.45454545</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>83.30056818181818</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>24.85632792519181</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>184.5575110133203</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>1.173347379331214</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>68.60912715105111</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>2601391.69237966</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>74.30081731395839</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>24.88488828502416</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>184.0247207125604</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>1.974901871980677</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>77.5977344289165</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>19987353.8863009</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>82.24436572636301</v>
-      </c>
-      <c r="BB9" t="inlineStr">
-        <is>
-          <t>2VSFgl3c</t>
-        </is>
-      </c>
-      <c r="BC9" t="inlineStr">
-        <is>
-          <t>UgdQz0fK</t>
+        <v>76.5209765654667</v>
+      </c>
+      <c r="AN9" t="inlineStr">
+        <is>
+          <t>0jdIgO6t</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>4fuCGs9P</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>AVR8vwXP</t>
+          <t>2T6mXfPa</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45535.5625</v>
+        <v>45536.52083333334</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">brand b 
+          <t xml:space="preserve">welz t 
   ger </t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">bayarena
-  leverkusen </t>
+          <t xml:space="preserve">allianz arena
+  munich </t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>30210</v>
+        <v>75024</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>4jcj2zMd</t>
+          <t>nVp0wiqd</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>KbS1suSm</t>
+          <t>fiEQZ7C7</t>
         </is>
       </c>
       <c r="H10" t="n">
@@ -2094,422 +1870,90 @@
           <t>bundesliga</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>WG9pOTse</t>
-        </is>
-      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr">
         <is>
-          <t>nP1i5US1</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr"/>
-      <c r="Q10" t="inlineStr"/>
-      <c r="R10" t="inlineStr"/>
-      <c r="S10" t="inlineStr"/>
-      <c r="T10" t="inlineStr"/>
-      <c r="U10" t="inlineStr"/>
-      <c r="V10" t="inlineStr"/>
-      <c r="W10" t="inlineStr"/>
-      <c r="X10" t="inlineStr"/>
-      <c r="Y10" t="inlineStr"/>
-      <c r="Z10" t="inlineStr"/>
-      <c r="AA10" t="inlineStr"/>
-      <c r="AB10" t="inlineStr"/>
-      <c r="AC10" t="inlineStr"/>
+          <t>nJQmYp1B</t>
+        </is>
+      </c>
+      <c r="P10" t="n">
+        <v>26.97954545454546</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>184.8948863636364</v>
+      </c>
+      <c r="R10" t="n">
+        <v>3.028409090909091</v>
+      </c>
+      <c r="S10" t="n">
+        <v>81.94886363636363</v>
+      </c>
+      <c r="T10" t="n">
+        <v>42040170.45454545</v>
+      </c>
+      <c r="U10" t="n">
+        <v>84.66249999999999</v>
+      </c>
+      <c r="V10" t="n">
+        <v>27.08680555555556</v>
+      </c>
+      <c r="W10" t="n">
+        <v>183.6912878787879</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1.694633838383838</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>75.30239898989899</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>8589299.242424242</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>77.16811868686868</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>24.83972601006459</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>182.4085591358535</v>
+      </c>
       <c r="AD10" t="n">
-        <v>25.60690235690236</v>
+        <v>2.28943530380046</v>
       </c>
       <c r="AE10" t="n">
-        <v>184.957842312009</v>
+        <v>78.68376277130452</v>
       </c>
       <c r="AF10" t="n">
-        <v>2.09760101010101</v>
+        <v>29910028.70892458</v>
       </c>
       <c r="AG10" t="n">
-        <v>81.46531986531987</v>
+        <v>83.44114130346767</v>
       </c>
       <c r="AH10" t="n">
-        <v>34631299.10213244</v>
+        <v>25.06481131497221</v>
       </c>
       <c r="AI10" t="n">
-        <v>84.30244107744107</v>
+        <v>184.5251901833388</v>
       </c>
       <c r="AJ10" t="n">
-        <v>24.84886363636364</v>
+        <v>1.467589490029422</v>
       </c>
       <c r="AK10" t="n">
-        <v>182.6511363636364</v>
+        <v>73.46279131933093</v>
       </c>
       <c r="AL10" t="n">
-        <v>2.105681818181818</v>
+        <v>6291650.449152773</v>
       </c>
       <c r="AM10" t="n">
-        <v>80.24545454545455</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>28893181.81818182</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>83.77840909090909</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>23.13491407665702</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>181.8688975838623</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>1.69881777896652</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>78.7255208774755</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>33311393.51705093</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>84.15514643685411</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>24.8385922652227</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>185.125544971333</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>1.713859359239794</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>77.0028430582099</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>18406734.50191113</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>81.53011567991187</v>
-      </c>
-      <c r="BB10" t="inlineStr">
-        <is>
-          <t>M5BRZDsC</t>
-        </is>
-      </c>
-      <c r="BC10" t="inlineStr">
-        <is>
-          <t>8f6APkLc</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>W8b4TCOO</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="n">
-        <v>45536.4375</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stegemann s 
-  ger </t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">voith arena
-  heidenheim </t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>15000</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>KWixEVWi</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>fTVNku3I</t>
-        </is>
-      </c>
-      <c r="H11" t="n">
-        <v>59</v>
-      </c>
-      <c r="I11" t="n">
-        <v>591</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>bundesliga</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr"/>
-      <c r="P11" t="inlineStr"/>
-      <c r="Q11" t="inlineStr"/>
-      <c r="R11" t="inlineStr"/>
-      <c r="S11" t="inlineStr"/>
-      <c r="T11" t="inlineStr"/>
-      <c r="U11" t="inlineStr"/>
-      <c r="V11" t="inlineStr"/>
-      <c r="W11" t="inlineStr"/>
-      <c r="X11" t="inlineStr"/>
-      <c r="Y11" t="inlineStr"/>
-      <c r="Z11" t="inlineStr"/>
-      <c r="AA11" t="inlineStr"/>
-      <c r="AB11" t="inlineStr"/>
-      <c r="AC11" t="inlineStr"/>
-      <c r="AD11" t="n">
-        <v>25.81666666666667</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>186.9015151515151</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>72.875</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>4350833.333333333</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>75.22045454545453</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>25.35034722222222</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>185.8133522727273</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>1.396243686868687</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>74.28888888888889</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>6341619.318181818</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>77.2822601010101</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>27.03253968253968</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>183.2093915343915</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>1</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>69.32208994708995</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>1942023.809523809</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>71.08320105820106</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>23.90971984886459</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>184.0197940400243</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>1.169671812106023</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>71.19951352101846</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>3934073.512379434</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>76.5209765654667</v>
-      </c>
-      <c r="BB11" t="inlineStr">
-        <is>
-          <t>lli2SfLl</t>
-        </is>
-      </c>
-      <c r="BC11" t="inlineStr">
-        <is>
-          <t>4fuCGs9P</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>2T6mXfPa</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="n">
-        <v>45536.52083333334</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">welz t 
-  ger </t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">allianz arena
-  munich </t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>75024</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>nVp0wiqd</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>fiEQZ7C7</t>
-        </is>
-      </c>
-      <c r="H12" t="n">
-        <v>59</v>
-      </c>
-      <c r="I12" t="n">
-        <v>591</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>bundesliga</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>nJQmYp1B</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr"/>
-      <c r="Q12" t="inlineStr"/>
-      <c r="R12" t="inlineStr"/>
-      <c r="S12" t="inlineStr"/>
-      <c r="T12" t="inlineStr"/>
-      <c r="U12" t="inlineStr"/>
-      <c r="V12" t="inlineStr"/>
-      <c r="W12" t="inlineStr"/>
-      <c r="X12" t="inlineStr"/>
-      <c r="Y12" t="inlineStr"/>
-      <c r="Z12" t="inlineStr"/>
-      <c r="AA12" t="inlineStr"/>
-      <c r="AB12" t="inlineStr"/>
-      <c r="AC12" t="inlineStr"/>
-      <c r="AD12" t="n">
-        <v>27.08484848484849</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>184.9212121212121</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>3.03030303030303</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>81.87878787878786</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>41254848.48484848</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>84.53333333333333</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>27.08680555555556</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>183.6912878787879</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>1.694633838383838</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>75.30239898989899</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>8589299.242424242</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>77.16811868686868</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>24.62070774406889</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>182.3024630782438</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>2.250397657387158</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>78.52101362272482</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>29928093.1228529</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>83.50805072369886</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>25.06481131497221</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>184.5251901833388</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>1.467589490029422</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>73.46279131933093</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>6291650.449152773</v>
-      </c>
-      <c r="BA12" t="n">
         <v>76.73148028018414</v>
       </c>
-      <c r="BB12" t="inlineStr">
-        <is>
-          <t>QevvB2nf</t>
-        </is>
-      </c>
-      <c r="BC12" t="inlineStr">
+      <c r="AN10" t="inlineStr">
+        <is>
+          <t>f3ddUIXs</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
         <is>
           <t>GzfvcwRj</t>
         </is>

--- a/data/germany/p6_deployment/data_preparation/df_filled.xlsx
+++ b/data/germany/p6_deployment/data_preparation/df_filled.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO10"/>
+  <dimension ref="A1:BC10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -505,130 +505,200 @@
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
+          <t>mean_age_player_miss_home</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>mean_hei_player_miss_home</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>mean_int_rep_player_miss_home</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>n_player_miss_home</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>sum_rat_player_miss_home</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>sum_val_player_miss_home</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>sum_pot_player_miss_home</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>mean_age_player_miss_away</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>mean_hei_player_miss_away</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>mean_int_rep_player_miss_away</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>n_player_miss_away</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>sum_rat_player_miss_away</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>sum_val_player_miss_away</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>sum_pot_player_miss_away</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
           <t>mean_age_player_start_home</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>mean_hei_player_start_home</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>mean_int_rep_player_start_home</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>mean_rat_player_start_home</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>mean_val_player_start_home</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>mean_pot_player_start_home</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>mean_age_player_start_away</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>mean_hei_player_start_away</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>mean_int_rep_player_start_away</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>mean_rat_player_start_away</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>mean_val_player_start_away</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>mean_pot_player_start_away</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>mean_age_player_sub_home</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>mean_hei_player_sub_home</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>mean_int_rep_player_sub_home</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>mean_rat_player_sub_home</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>mean_val_player_sub_home</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>mean_pot_player_sub_home</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>mean_age_player_sub_away</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AW1" s="1" t="inlineStr">
         <is>
           <t>mean_hei_player_sub_away</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AX1" s="1" t="inlineStr">
         <is>
           <t>mean_int_rep_player_sub_away</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AY1" s="1" t="inlineStr">
         <is>
           <t>mean_rat_player_sub_away</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AZ1" s="1" t="inlineStr">
         <is>
           <t>mean_val_player_sub_away</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="BA1" s="1" t="inlineStr">
         <is>
           <t>mean_pot_player_sub_away</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="BB1" s="1" t="inlineStr">
         <is>
           <t>id_coach_home</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="BC1" s="1" t="inlineStr">
         <is>
           <t>id_coach_away</t>
         </is>
@@ -697,83 +767,125 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>26.95170454545455</v>
+        <v>29</v>
       </c>
       <c r="Q2" t="n">
-        <v>185.0659722222222</v>
+        <v>175.6666666666667</v>
       </c>
       <c r="R2" t="n">
-        <v>1.619507575757576</v>
+        <v>1.666666666666667</v>
       </c>
       <c r="S2" t="n">
-        <v>75.7828914141414</v>
+        <v>3</v>
       </c>
       <c r="T2" t="n">
-        <v>8385435.606060605</v>
+        <v>229</v>
       </c>
       <c r="U2" t="n">
-        <v>78.17866161616162</v>
+        <v>25300000</v>
       </c>
       <c r="V2" t="n">
+        <v>229</v>
+      </c>
+      <c r="W2" t="n">
+        <v>30</v>
+      </c>
+      <c r="X2" t="n">
+        <v>186.6666666666667</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>199</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>2575000</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>204</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>26.97077922077922</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>184.8935786435787</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>1.617099567099567</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>75.79083694083694</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>8397640.692640692</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>78.15223665223665</v>
+      </c>
+      <c r="AJ2" t="n">
         <v>25.82575757575757</v>
       </c>
-      <c r="W2" t="n">
+      <c r="AK2" t="n">
         <v>185.2379797979798</v>
       </c>
-      <c r="X2" t="n">
+      <c r="AL2" t="n">
         <v>1</v>
       </c>
-      <c r="Y2" t="n">
+      <c r="AM2" t="n">
         <v>69.99222222222222</v>
       </c>
-      <c r="Z2" t="n">
+      <c r="AN2" t="n">
         <v>2270323.232323232</v>
       </c>
-      <c r="AA2" t="n">
+      <c r="AO2" t="n">
         <v>73.13414141414141</v>
       </c>
-      <c r="AB2" t="n">
-        <v>26.83493408566707</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>184.1065091964513</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>1.463121401783444</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>73.73900926455632</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>5164687.434732665</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>76.12727924884675</v>
-      </c>
-      <c r="AH2" t="n">
+      <c r="AP2" t="n">
+        <v>26.76075800266712</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>184.4074390816586</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>1.453884776641396</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>73.63823281028658</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>5021398.73493257</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>76.12165247487249</v>
+      </c>
+      <c r="AV2" t="n">
         <v>25.58083431618261</v>
       </c>
-      <c r="AI2" t="n">
+      <c r="AW2" t="n">
         <v>185.5206408177306</v>
       </c>
-      <c r="AJ2" t="n">
+      <c r="AX2" t="n">
         <v>1</v>
       </c>
-      <c r="AK2" t="n">
+      <c r="AY2" t="n">
         <v>67.09735859255983</v>
       </c>
-      <c r="AL2" t="n">
+      <c r="AZ2" t="n">
         <v>1422561.096368372</v>
       </c>
-      <c r="AM2" t="n">
+      <c r="BA2" t="n">
         <v>71.5401422674333</v>
       </c>
-      <c r="AN2" t="inlineStr">
+      <c r="BB2" t="inlineStr">
         <is>
           <t>vZA6VYpf</t>
         </is>
       </c>
-      <c r="AO2" t="inlineStr">
+      <c r="BC2" t="inlineStr">
         <is>
           <t>4ljanukM</t>
         </is>
@@ -845,84 +957,98 @@
           <t>WG9pOTse</t>
         </is>
       </c>
-      <c r="P3" t="n">
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr"/>
+      <c r="W3" t="inlineStr"/>
+      <c r="X3" t="inlineStr"/>
+      <c r="Y3" t="inlineStr"/>
+      <c r="Z3" t="inlineStr"/>
+      <c r="AA3" t="inlineStr"/>
+      <c r="AB3" t="inlineStr"/>
+      <c r="AC3" t="inlineStr"/>
+      <c r="AD3" t="n">
         <v>27.83950617283951</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="AE3" t="n">
         <v>182.4489197530864</v>
       </c>
-      <c r="R3" t="n">
+      <c r="AF3" t="n">
         <v>1.233950617283951</v>
       </c>
-      <c r="S3" t="n">
+      <c r="AG3" t="n">
         <v>73.04058641975308</v>
       </c>
-      <c r="T3" t="n">
+      <c r="AH3" t="n">
         <v>3510852.62345679</v>
       </c>
-      <c r="U3" t="n">
+      <c r="AI3" t="n">
         <v>74.9695987654321</v>
       </c>
-      <c r="V3" t="n">
-        <v>25.19690656565657</v>
-      </c>
-      <c r="W3" t="n">
-        <v>184.5984848484849</v>
-      </c>
-      <c r="X3" t="n">
-        <v>1.523484848484848</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>75.34444444444443</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>8616609.848484848</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>78.24128787878787</v>
-      </c>
-      <c r="AB3" t="n">
+      <c r="AJ3" t="n">
+        <v>25.33614718614719</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>184.7157287157287</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>1.518903318903319</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>75.25079365079364</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>8434855.6998557</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>78.14877344877345</v>
+      </c>
+      <c r="AP3" t="n">
         <v>26.52903439153439</v>
       </c>
-      <c r="AC3" t="n">
+      <c r="AQ3" t="n">
         <v>183.0409195887171</v>
       </c>
-      <c r="AD3" t="n">
+      <c r="AR3" t="n">
         <v>1.061030696709568</v>
       </c>
-      <c r="AE3" t="n">
+      <c r="AS3" t="n">
         <v>70.23866749475064</v>
       </c>
-      <c r="AF3" t="n">
+      <c r="AT3" t="n">
         <v>2328151.633028278</v>
       </c>
-      <c r="AG3" t="n">
+      <c r="AU3" t="n">
         <v>73.66187075753723</v>
       </c>
-      <c r="AH3" t="n">
-        <v>23.34266065980168</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>184.1793037280702</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>1.278301392067124</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>72.89358169540699</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>6622054.439767897</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>78.54315101612727</v>
-      </c>
-      <c r="AN3" t="inlineStr">
+      <c r="AV3" t="n">
+        <v>22.9902516384128</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>183.9804287504475</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>1.270439686171952</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>72.6402838423699</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>6597654.053612292</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>78.71258075312505</v>
+      </c>
+      <c r="BB3" t="inlineStr">
         <is>
           <t>pfoInmcq</t>
         </is>
       </c>
-      <c r="AO3" t="inlineStr">
+      <c r="BC3" t="inlineStr">
         <is>
           <t>hAcTWKKN</t>
         </is>
@@ -994,84 +1120,98 @@
           <t>nJQmYp1B</t>
         </is>
       </c>
-      <c r="P4" t="n">
-        <v>24.12986111111111</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>183.4407986111111</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1.676736111111111</v>
-      </c>
-      <c r="S4" t="n">
-        <v>76.90746527777779</v>
-      </c>
-      <c r="T4" t="n">
-        <v>15519635.41666666</v>
-      </c>
-      <c r="U4" t="n">
-        <v>81.31545138888889</v>
-      </c>
-      <c r="V4" t="n">
-        <v>26.51950757575758</v>
-      </c>
-      <c r="W4" t="n">
-        <v>185.7345328282828</v>
-      </c>
-      <c r="X4" t="n">
-        <v>1.803156565656566</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>75.0542297979798</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>8872863.005050506</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>78.69816919191919</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>23.78294700655382</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>184.0116076454505</v>
-      </c>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="inlineStr"/>
+      <c r="X4" t="inlineStr"/>
+      <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="inlineStr"/>
+      <c r="AA4" t="inlineStr"/>
+      <c r="AB4" t="inlineStr"/>
+      <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="n">
-        <v>1.399164250030156</v>
+        <v>24.13253968253968</v>
       </c>
       <c r="AE4" t="n">
-        <v>71.49686218386876</v>
+        <v>183.3767857142857</v>
       </c>
       <c r="AF4" t="n">
-        <v>5656665.465677898</v>
+        <v>1.662301587301588</v>
       </c>
       <c r="AG4" t="n">
-        <v>78.66426963129749</v>
+        <v>76.83075396825396</v>
       </c>
       <c r="AH4" t="n">
-        <v>24.55683940242763</v>
+        <v>15395456.34920635</v>
       </c>
       <c r="AI4" t="n">
-        <v>185.0505368814192</v>
+        <v>81.29702380952381</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1.409700338468721</v>
+        <v>26.69761904761905</v>
       </c>
       <c r="AK4" t="n">
-        <v>71.84159809757236</v>
+        <v>185.7875180375181</v>
       </c>
       <c r="AL4" t="n">
-        <v>5627775.589402428</v>
+        <v>1.813997113997114</v>
       </c>
       <c r="AM4" t="n">
-        <v>77.73592145191409</v>
-      </c>
-      <c r="AN4" t="inlineStr">
+        <v>75.16587301587302</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>8908596.681096682</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>78.57712842712843</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>23.63061590664974</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>184.1267112586661</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>1.39106166390001</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>71.51427106727859</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>5661307.275900791</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>78.78069890635679</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>24.30985727624383</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>185.2482326263839</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>1.392265239429105</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>71.63869714552489</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>5536278.678137922</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>77.87053154595172</v>
+      </c>
+      <c r="BB4" t="inlineStr">
         <is>
           <t>IkCftsQm</t>
         </is>
       </c>
-      <c r="AO4" t="inlineStr">
+      <c r="BC4" t="inlineStr">
         <is>
           <t>A15eUM4C</t>
         </is>
@@ -1143,84 +1283,98 @@
           <t>dfNCCCzS</t>
         </is>
       </c>
-      <c r="P5" t="n">
-        <v>25.1949494949495</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>186.1567676767677</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1.084747474747475</v>
-      </c>
-      <c r="S5" t="n">
-        <v>68.59646464646464</v>
-      </c>
-      <c r="T5" t="n">
-        <v>1761303.030303031</v>
-      </c>
-      <c r="U5" t="n">
-        <v>72.54494949494951</v>
-      </c>
-      <c r="V5" t="n">
-        <v>25.30694444444445</v>
-      </c>
-      <c r="W5" t="n">
-        <v>186.5289930555556</v>
-      </c>
-      <c r="X5" t="n">
-        <v>1.568229166666667</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>75.69999999999999</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>10678663.19444444</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>79.50190972222222</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>25.12022515527951</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>185.9334239130435</v>
-      </c>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="inlineStr"/>
+      <c r="AA5" t="inlineStr"/>
+      <c r="AB5" t="inlineStr"/>
+      <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="n">
-        <v>1.014665286404417</v>
+        <v>25.21661054994389</v>
       </c>
       <c r="AE5" t="n">
-        <v>66.5940734989648</v>
+        <v>186.3560044893378</v>
       </c>
       <c r="AF5" t="n">
-        <v>1395265.376984127</v>
+        <v>1.084062850729517</v>
       </c>
       <c r="AG5" t="n">
-        <v>71.16014492753622</v>
+        <v>68.55162738496071</v>
       </c>
       <c r="AH5" t="n">
-        <v>24.26911986714976</v>
+        <v>1749932.65993266</v>
       </c>
       <c r="AI5" t="n">
-        <v>183.8380208333333</v>
+        <v>72.49438832772167</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1.25618961352657</v>
+        <v>25.13650793650794</v>
       </c>
       <c r="AK5" t="n">
-        <v>73.62463013285024</v>
+        <v>186.4759920634921</v>
       </c>
       <c r="AL5" t="n">
-        <v>8505106.43115942</v>
+        <v>1.57797619047619</v>
       </c>
       <c r="AM5" t="n">
-        <v>78.35117753623189</v>
-      </c>
-      <c r="AN5" t="inlineStr">
+        <v>75.85714285714286</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>11076329.36507936</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>79.67361111111111</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>25.07185511080439</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>185.8889895330113</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>1.016294762671574</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>66.6971187025535</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>1422825.727513228</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>71.27670424047236</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>24.35002587991719</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>183.8105158730158</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>1.259057971014493</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>73.565450310559</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>8305568.064182194</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>78.39579020013801</v>
+      </c>
+      <c r="BB5" t="inlineStr">
         <is>
           <t>KUx4Q7x1</t>
         </is>
       </c>
-      <c r="AO5" t="inlineStr">
+      <c r="BC5" t="inlineStr">
         <is>
           <t>K6A2elS9</t>
         </is>
@@ -1292,84 +1446,98 @@
           <t>8vndvXTk</t>
         </is>
       </c>
-      <c r="P6" t="n">
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr"/>
+      <c r="X6" t="inlineStr"/>
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="inlineStr"/>
+      <c r="AA6" t="inlineStr"/>
+      <c r="AB6" t="inlineStr"/>
+      <c r="AC6" t="inlineStr"/>
+      <c r="AD6" t="n">
         <v>24.38503787878788</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="AE6" t="n">
         <v>184.6373106060606</v>
       </c>
-      <c r="R6" t="n">
+      <c r="AF6" t="n">
         <v>1.49854797979798</v>
       </c>
-      <c r="S6" t="n">
+      <c r="AG6" t="n">
         <v>76.09526515151515</v>
       </c>
-      <c r="T6" t="n">
+      <c r="AH6" t="n">
         <v>11807380.05050505</v>
       </c>
-      <c r="U6" t="n">
+      <c r="AI6" t="n">
         <v>79.15915404040403</v>
       </c>
-      <c r="V6" t="n">
-        <v>25.85965909090909</v>
-      </c>
-      <c r="W6" t="n">
-        <v>183.2630681818182</v>
-      </c>
-      <c r="X6" t="n">
-        <v>1.574431818181818</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>74.44204545454545</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>6720170.454545455</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>78.25568181818181</v>
-      </c>
-      <c r="AB6" t="n">
+      <c r="AJ6" t="n">
+        <v>25.7487012987013</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>183.0149350649351</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>1.565584415584415</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>74.4012987012987</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>6715259.740259741</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>78.35714285714286</v>
+      </c>
+      <c r="AP6" t="n">
         <v>24.09893353174603</v>
       </c>
-      <c r="AC6" t="n">
-        <v>182.9319940476191</v>
-      </c>
-      <c r="AD6" t="n">
+      <c r="AQ6" t="n">
+        <v>182.931994047619</v>
+      </c>
+      <c r="AR6" t="n">
         <v>1.245535714285714</v>
       </c>
-      <c r="AE6" t="n">
+      <c r="AS6" t="n">
         <v>70.96324404761904</v>
       </c>
-      <c r="AF6" t="n">
-        <v>5420341.021825396</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>75.95982142857143</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>25.96584821428571</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>185.0104166666667</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>1.484573412698412</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>72.23660714285714</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>4440523.933531746</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>76.76636904761904</v>
-      </c>
-      <c r="AN6" t="inlineStr">
+      <c r="AT6" t="n">
+        <v>5420341.021825397</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>75.95982142857142</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>26.1015589569161</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>185.3565759637188</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>1.495975056689342</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>72.27040816326532</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>4399317.602040815</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>76.67063492063492</v>
+      </c>
+      <c r="BB6" t="inlineStr">
         <is>
           <t>YZPE6Sx7</t>
         </is>
       </c>
-      <c r="AO6" t="inlineStr">
+      <c r="BC6" t="inlineStr">
         <is>
           <t>hpYJ6izc</t>
         </is>
@@ -1441,84 +1609,98 @@
           <t>0Ija0Ej9</t>
         </is>
       </c>
-      <c r="P7" t="n">
-        <v>25.97727272727273</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>183.4318181818182</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1.170454545454546</v>
-      </c>
-      <c r="S7" t="n">
-        <v>73.21590909090909</v>
-      </c>
-      <c r="T7" t="n">
-        <v>4900852.272727272</v>
-      </c>
-      <c r="U7" t="n">
-        <v>76.18181818181819</v>
-      </c>
-      <c r="V7" t="n">
-        <v>25.40113636363636</v>
-      </c>
-      <c r="W7" t="n">
-        <v>184.9142045454545</v>
-      </c>
-      <c r="X7" t="n">
-        <v>2.313068181818182</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>80.11875000000001</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>30029545.45454545</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>83.30056818181818</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>24.85632792519181</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>184.5575110133203</v>
-      </c>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="inlineStr"/>
+      <c r="X7" t="inlineStr"/>
+      <c r="Y7" t="inlineStr"/>
+      <c r="Z7" t="inlineStr"/>
+      <c r="AA7" t="inlineStr"/>
+      <c r="AB7" t="inlineStr"/>
+      <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="n">
-        <v>1.173347379331214</v>
+        <v>26.06493506493506</v>
       </c>
       <c r="AE7" t="n">
-        <v>68.60912715105111</v>
+        <v>183.2077922077922</v>
       </c>
       <c r="AF7" t="n">
-        <v>2601391.69237966</v>
+        <v>1.181818181818182</v>
       </c>
       <c r="AG7" t="n">
-        <v>74.30081731395838</v>
+        <v>73.3116883116883</v>
       </c>
       <c r="AH7" t="n">
-        <v>24.88488828502416</v>
+        <v>4990584.415584415</v>
       </c>
       <c r="AI7" t="n">
-        <v>184.0247207125604</v>
+        <v>76.15584415584416</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1.974901871980677</v>
+        <v>25.3025974025974</v>
       </c>
       <c r="AK7" t="n">
-        <v>77.5977344289165</v>
+        <v>184.824025974026</v>
       </c>
       <c r="AL7" t="n">
-        <v>19987353.8863009</v>
+        <v>2.331818181818182</v>
       </c>
       <c r="AM7" t="n">
-        <v>82.24436572636301</v>
-      </c>
-      <c r="AN7" t="inlineStr">
+        <v>80.10974025974026</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>30490909.09090909</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>83.35649350649351</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>24.93500969228271</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>184.7790205231597</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>1.150492243045197</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>68.8697564265981</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>2632865.307164056</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>74.30510073976197</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>24.89721359558316</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>184.0183316080056</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>1.962387853692201</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>77.71189490288869</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>20467194.12402643</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>82.26340209997042</v>
+      </c>
+      <c r="BB7" t="inlineStr">
         <is>
           <t>2VSFgl3c</t>
         </is>
       </c>
-      <c r="AO7" t="inlineStr">
+      <c r="BC7" t="inlineStr">
         <is>
           <t>UgdQz0fK</t>
         </is>
@@ -1590,84 +1772,98 @@
           <t>nP1i5US1</t>
         </is>
       </c>
-      <c r="P8" t="n">
-        <v>25.60690235690236</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>184.957842312009</v>
-      </c>
-      <c r="R8" t="n">
-        <v>2.09760101010101</v>
-      </c>
-      <c r="S8" t="n">
-        <v>81.46531986531987</v>
-      </c>
-      <c r="T8" t="n">
-        <v>34631299.10213244</v>
-      </c>
-      <c r="U8" t="n">
-        <v>84.30244107744107</v>
-      </c>
-      <c r="V8" t="n">
-        <v>24.84886363636364</v>
-      </c>
-      <c r="W8" t="n">
-        <v>182.6511363636364</v>
-      </c>
-      <c r="X8" t="n">
-        <v>2.105681818181818</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>80.24545454545455</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>28893181.81818182</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>83.77840909090909</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>23.13491407665702</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>181.8688975838623</v>
-      </c>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" t="inlineStr"/>
+      <c r="X8" t="inlineStr"/>
+      <c r="Y8" t="inlineStr"/>
+      <c r="Z8" t="inlineStr"/>
+      <c r="AA8" t="inlineStr"/>
+      <c r="AB8" t="inlineStr"/>
+      <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="n">
-        <v>1.69881777896652</v>
+        <v>25.57026515151515</v>
       </c>
       <c r="AE8" t="n">
-        <v>78.7255208774755</v>
+        <v>185.0150726010101</v>
       </c>
       <c r="AF8" t="n">
-        <v>33311393.51705093</v>
+        <v>2.047301136363636</v>
       </c>
       <c r="AG8" t="n">
-        <v>84.15514643685411</v>
+        <v>81.27348484848486</v>
       </c>
       <c r="AH8" t="n">
-        <v>24.8385922652227</v>
+        <v>33347711.48989899</v>
       </c>
       <c r="AI8" t="n">
-        <v>185.125544971333</v>
+        <v>84.20274621212121</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1.713859359239794</v>
+        <v>24.72727272727273</v>
       </c>
       <c r="AK8" t="n">
-        <v>77.0028430582099</v>
+        <v>182.8584415584416</v>
       </c>
       <c r="AL8" t="n">
-        <v>18406734.50191113</v>
+        <v>2.077922077922078</v>
       </c>
       <c r="AM8" t="n">
-        <v>81.53011567991187</v>
-      </c>
-      <c r="AN8" t="inlineStr">
+        <v>80.20909090909092</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>28920779.22077922</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>83.84675324675325</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>23.17891649413389</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>181.8475755713188</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>1.758620659232072</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>79.10732940821256</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>35266929.54878756</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>84.33736868882929</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>24.87208163644499</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>184.8121307608885</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>1.736474188337543</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>76.99233651097005</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>18437160.85932701</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>81.49275125323263</v>
+      </c>
+      <c r="BB8" t="inlineStr">
         <is>
           <t>M5BRZDsC</t>
         </is>
       </c>
-      <c r="AO8" t="inlineStr">
+      <c r="BC8" t="inlineStr">
         <is>
           <t>8f6APkLc</t>
         </is>
@@ -1731,84 +1927,98 @@
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
-      <c r="P9" t="n">
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="inlineStr"/>
+      <c r="X9" t="inlineStr"/>
+      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="inlineStr"/>
+      <c r="AA9" t="inlineStr"/>
+      <c r="AB9" t="inlineStr"/>
+      <c r="AC9" t="inlineStr"/>
+      <c r="AD9" t="n">
         <v>25.8515625</v>
       </c>
-      <c r="Q9" t="n">
+      <c r="AE9" t="n">
         <v>186.9779829545454</v>
       </c>
-      <c r="R9" t="n">
+      <c r="AF9" t="n">
         <v>1</v>
       </c>
-      <c r="S9" t="n">
+      <c r="AG9" t="n">
         <v>72.828125</v>
       </c>
-      <c r="T9" t="n">
+      <c r="AH9" t="n">
         <v>4253906.25</v>
       </c>
-      <c r="U9" t="n">
+      <c r="AI9" t="n">
         <v>75.15198863636363</v>
       </c>
-      <c r="V9" t="n">
+      <c r="AJ9" t="n">
         <v>25.35034722222222</v>
       </c>
-      <c r="W9" t="n">
+      <c r="AK9" t="n">
         <v>185.8133522727273</v>
       </c>
-      <c r="X9" t="n">
+      <c r="AL9" t="n">
         <v>1.396243686868687</v>
       </c>
-      <c r="Y9" t="n">
+      <c r="AM9" t="n">
         <v>74.28888888888889</v>
       </c>
-      <c r="Z9" t="n">
+      <c r="AN9" t="n">
         <v>6341619.318181818</v>
       </c>
-      <c r="AA9" t="n">
+      <c r="AO9" t="n">
         <v>77.2822601010101</v>
       </c>
-      <c r="AB9" t="n">
+      <c r="AP9" t="n">
         <v>26.94022817460317</v>
       </c>
-      <c r="AC9" t="n">
+      <c r="AQ9" t="n">
         <v>183.3282490079365</v>
       </c>
-      <c r="AD9" t="n">
+      <c r="AR9" t="n">
         <v>1</v>
       </c>
-      <c r="AE9" t="n">
+      <c r="AS9" t="n">
         <v>69.34015376984127</v>
       </c>
-      <c r="AF9" t="n">
+      <c r="AT9" t="n">
         <v>1937487.599206349</v>
       </c>
-      <c r="AG9" t="n">
+      <c r="AU9" t="n">
         <v>71.13702876984127</v>
       </c>
-      <c r="AH9" t="n">
+      <c r="AV9" t="n">
         <v>23.90971984886459</v>
       </c>
-      <c r="AI9" t="n">
+      <c r="AW9" t="n">
         <v>184.0197940400243</v>
       </c>
-      <c r="AJ9" t="n">
+      <c r="AX9" t="n">
         <v>1.169671812106023</v>
       </c>
-      <c r="AK9" t="n">
+      <c r="AY9" t="n">
         <v>71.19951352101846</v>
       </c>
-      <c r="AL9" t="n">
+      <c r="AZ9" t="n">
         <v>3934073.512379434</v>
       </c>
-      <c r="AM9" t="n">
+      <c r="BA9" t="n">
         <v>76.5209765654667</v>
       </c>
-      <c r="AN9" t="inlineStr">
+      <c r="BB9" t="inlineStr">
         <is>
           <t>0jdIgO6t</t>
         </is>
       </c>
-      <c r="AO9" t="inlineStr">
+      <c r="BC9" t="inlineStr">
         <is>
           <t>4fuCGs9P</t>
         </is>
@@ -1876,84 +2086,98 @@
           <t>nJQmYp1B</t>
         </is>
       </c>
-      <c r="P10" t="n">
-        <v>26.97954545454546</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>184.8948863636364</v>
-      </c>
-      <c r="R10" t="n">
-        <v>3.028409090909091</v>
-      </c>
-      <c r="S10" t="n">
-        <v>81.94886363636363</v>
-      </c>
-      <c r="T10" t="n">
-        <v>42040170.45454545</v>
-      </c>
-      <c r="U10" t="n">
-        <v>84.66249999999999</v>
-      </c>
-      <c r="V10" t="n">
-        <v>27.08680555555556</v>
-      </c>
-      <c r="W10" t="n">
-        <v>183.6912878787879</v>
-      </c>
-      <c r="X10" t="n">
-        <v>1.694633838383838</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>75.30239898989899</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>8589299.242424242</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>77.16811868686868</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>24.83972601006459</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>182.4085591358535</v>
-      </c>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="inlineStr"/>
+      <c r="W10" t="inlineStr"/>
+      <c r="X10" t="inlineStr"/>
+      <c r="Y10" t="inlineStr"/>
+      <c r="Z10" t="inlineStr"/>
+      <c r="AA10" t="inlineStr"/>
+      <c r="AB10" t="inlineStr"/>
+      <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="n">
-        <v>2.28943530380046</v>
+        <v>26.95064935064935</v>
       </c>
       <c r="AE10" t="n">
-        <v>78.68376277130452</v>
+        <v>184.8149350649351</v>
       </c>
       <c r="AF10" t="n">
-        <v>29910028.70892458</v>
+        <v>2.993506493506493</v>
       </c>
       <c r="AG10" t="n">
-        <v>83.44114130346767</v>
+        <v>81.74675324675324</v>
       </c>
       <c r="AH10" t="n">
-        <v>25.06481131497221</v>
+        <v>39978051.94805194</v>
       </c>
       <c r="AI10" t="n">
-        <v>184.5251901833388</v>
+        <v>84.61428571428571</v>
       </c>
       <c r="AJ10" t="n">
-        <v>1.467589490029422</v>
+        <v>27.09920634920635</v>
       </c>
       <c r="AK10" t="n">
-        <v>73.46279131933093</v>
+        <v>183.5822510822511</v>
       </c>
       <c r="AL10" t="n">
-        <v>6291650.449152773</v>
+        <v>1.702958152958153</v>
       </c>
       <c r="AM10" t="n">
-        <v>76.73148028018414</v>
-      </c>
-      <c r="AN10" t="inlineStr">
+        <v>75.38455988455988</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>8859199.134199133</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>77.23109668109667</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>24.78309956705795</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>182.3895437743088</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>2.29010860116878</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>78.49870507196707</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>29706104.23877095</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>83.38213768015353</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>25.00978435996824</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>184.517054087081</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>1.471632886564237</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>73.40237375270475</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>6103059.696990924</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>76.654855014088</v>
+      </c>
+      <c r="BB10" t="inlineStr">
         <is>
           <t>f3ddUIXs</t>
         </is>
       </c>
-      <c r="AO10" t="inlineStr">
+      <c r="BC10" t="inlineStr">
         <is>
           <t>GzfvcwRj</t>
         </is>

--- a/data/germany/p6_deployment/data_preparation/df_filled.xlsx
+++ b/data/germany/p6_deployment/data_preparation/df_filled.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BC10"/>
+  <dimension ref="A1:BC16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -707,35 +707,35 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>djSMofvg</t>
+          <t>U3QUqY85</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45534.64583333334</v>
+        <v>45535.4375</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">jablonski s 
+          <t xml:space="preserve">storks s 
   ger </t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadion an der alten forsterei
-  berlin </t>
+          <t xml:space="preserve">vonovia ruhrstadion
+  bochum </t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>22012</v>
+        <v>26000</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>pzHW4oaE</t>
+          <t>8Y2m6ADe</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>ILyJuN3g</t>
+          <t>88HSzjDr</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -760,38 +760,42 @@
           <t>bundesliga</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr"/>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0Ija0Ej9</t>
+        </is>
+      </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>v9k3aY5F</t>
+          <t>WG9pOTse</t>
         </is>
       </c>
       <c r="P2" t="n">
-        <v>29</v>
+        <v>27.33333333333333</v>
       </c>
       <c r="Q2" t="n">
-        <v>175.6666666666667</v>
+        <v>188.6666666666667</v>
       </c>
       <c r="R2" t="n">
-        <v>1.666666666666667</v>
+        <v>1.333333333333333</v>
       </c>
       <c r="S2" t="n">
         <v>3</v>
       </c>
       <c r="T2" t="n">
-        <v>229</v>
+        <v>213</v>
       </c>
       <c r="U2" t="n">
-        <v>25300000</v>
+        <v>6550000</v>
       </c>
       <c r="V2" t="n">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="W2" t="n">
-        <v>30</v>
+        <v>19.33333333333333</v>
       </c>
       <c r="X2" t="n">
-        <v>186.6666666666667</v>
+        <v>181.3333333333333</v>
       </c>
       <c r="Y2" t="n">
         <v>1</v>
@@ -800,101 +804,101 @@
         <v>3</v>
       </c>
       <c r="AA2" t="n">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="AB2" t="n">
-        <v>2575000</v>
+        <v>4625000</v>
       </c>
       <c r="AC2" t="n">
-        <v>204</v>
+        <v>230</v>
       </c>
       <c r="AD2" t="n">
-        <v>26.97077922077922</v>
+        <v>27.77777777777778</v>
       </c>
       <c r="AE2" t="n">
-        <v>184.8935786435787</v>
+        <v>182.6578125</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.617099567099567</v>
+        <v>1.221527777777778</v>
       </c>
       <c r="AG2" t="n">
-        <v>75.79083694083694</v>
+        <v>72.9484375</v>
       </c>
       <c r="AH2" t="n">
-        <v>8397640.692640692</v>
+        <v>3466028.645833334</v>
       </c>
       <c r="AI2" t="n">
-        <v>78.15223665223665</v>
+        <v>74.91024305555555</v>
       </c>
       <c r="AJ2" t="n">
-        <v>25.82575757575757</v>
+        <v>25.33614718614719</v>
       </c>
       <c r="AK2" t="n">
-        <v>185.2379797979798</v>
+        <v>184.7157287157287</v>
       </c>
       <c r="AL2" t="n">
-        <v>1</v>
+        <v>1.518903318903319</v>
       </c>
       <c r="AM2" t="n">
-        <v>69.99222222222222</v>
+        <v>75.25079365079364</v>
       </c>
       <c r="AN2" t="n">
-        <v>2270323.232323232</v>
+        <v>8434855.6998557</v>
       </c>
       <c r="AO2" t="n">
-        <v>73.13414141414141</v>
+        <v>78.14877344877345</v>
       </c>
       <c r="AP2" t="n">
-        <v>26.76075800266712</v>
+        <v>26.37626272429262</v>
       </c>
       <c r="AQ2" t="n">
-        <v>184.4074390816586</v>
+        <v>182.9074475807849</v>
       </c>
       <c r="AR2" t="n">
-        <v>1.453884776641396</v>
+        <v>1.065942142493916</v>
       </c>
       <c r="AS2" t="n">
-        <v>73.63823281028658</v>
+        <v>70.1685613180679</v>
       </c>
       <c r="AT2" t="n">
-        <v>5021398.73493257</v>
+        <v>2335882.543678551</v>
       </c>
       <c r="AU2" t="n">
-        <v>76.12165247487249</v>
+        <v>73.77268431237431</v>
       </c>
       <c r="AV2" t="n">
-        <v>25.58083431618261</v>
+        <v>22.9902516384128</v>
       </c>
       <c r="AW2" t="n">
-        <v>185.5206408177306</v>
+        <v>183.9804287504475</v>
       </c>
       <c r="AX2" t="n">
-        <v>1</v>
+        <v>1.270439686171952</v>
       </c>
       <c r="AY2" t="n">
-        <v>67.09735859255983</v>
+        <v>72.6402838423699</v>
       </c>
       <c r="AZ2" t="n">
-        <v>1422561.096368372</v>
+        <v>6597654.053612292</v>
       </c>
       <c r="BA2" t="n">
-        <v>71.5401422674333</v>
+        <v>78.71258075312505</v>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>vZA6VYpf</t>
+          <t>pfoInmcq</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>4ljanukM</t>
+          <t>hAcTWKKN</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>U3QUqY85</t>
+          <t>AgAeVYgC</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
@@ -902,27 +906,27 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">schroder r 
+          <t xml:space="preserve">badstubner f 
   ger </t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">vonovia ruhrstadion
-  bochum </t>
+          <t xml:space="preserve">deutsche bank park
+  frankfurt </t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>26000</v>
+        <v>58000</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>8Y2m6ADe</t>
+          <t>8vndvXTk</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>88HSzjDr</t>
+          <t>hQAtP9Sl</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -949,115 +953,143 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>0Ija0Ej9</t>
+          <t>EuakNmc1</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>WG9pOTse</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr"/>
-      <c r="R3" t="inlineStr"/>
-      <c r="S3" t="inlineStr"/>
-      <c r="T3" t="inlineStr"/>
-      <c r="U3" t="inlineStr"/>
-      <c r="V3" t="inlineStr"/>
-      <c r="W3" t="inlineStr"/>
-      <c r="X3" t="inlineStr"/>
-      <c r="Y3" t="inlineStr"/>
-      <c r="Z3" t="inlineStr"/>
-      <c r="AA3" t="inlineStr"/>
-      <c r="AB3" t="inlineStr"/>
-      <c r="AC3" t="inlineStr"/>
+          <t>nJQmYp1B</t>
+        </is>
+      </c>
+      <c r="P3" t="n">
+        <v>19</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>180</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1</v>
+      </c>
+      <c r="S3" t="n">
+        <v>2</v>
+      </c>
+      <c r="T3" t="n">
+        <v>121</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1575000</v>
+      </c>
+      <c r="V3" t="n">
+        <v>159</v>
+      </c>
+      <c r="W3" t="n">
+        <v>23</v>
+      </c>
+      <c r="X3" t="n">
+        <v>181.4</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>362</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>25600000</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>399</v>
+      </c>
       <c r="AD3" t="n">
-        <v>27.83950617283951</v>
+        <v>24.13253968253968</v>
       </c>
       <c r="AE3" t="n">
-        <v>182.4489197530864</v>
+        <v>183.3767857142857</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.233950617283951</v>
+        <v>1.662301587301588</v>
       </c>
       <c r="AG3" t="n">
-        <v>73.04058641975308</v>
+        <v>76.83075396825396</v>
       </c>
       <c r="AH3" t="n">
-        <v>3510852.62345679</v>
+        <v>15395456.34920635</v>
       </c>
       <c r="AI3" t="n">
-        <v>74.9695987654321</v>
+        <v>81.29702380952381</v>
       </c>
       <c r="AJ3" t="n">
-        <v>25.33614718614719</v>
+        <v>26.69761904761905</v>
       </c>
       <c r="AK3" t="n">
-        <v>184.7157287157287</v>
+        <v>185.7875180375181</v>
       </c>
       <c r="AL3" t="n">
-        <v>1.518903318903319</v>
+        <v>1.813997113997114</v>
       </c>
       <c r="AM3" t="n">
-        <v>75.25079365079364</v>
+        <v>75.16587301587302</v>
       </c>
       <c r="AN3" t="n">
-        <v>8434855.6998557</v>
+        <v>8908596.681096682</v>
       </c>
       <c r="AO3" t="n">
-        <v>78.14877344877345</v>
+        <v>78.57712842712843</v>
       </c>
       <c r="AP3" t="n">
-        <v>26.52903439153439</v>
+        <v>23.63061590664974</v>
       </c>
       <c r="AQ3" t="n">
-        <v>183.0409195887171</v>
+        <v>184.1267112586661</v>
       </c>
       <c r="AR3" t="n">
-        <v>1.061030696709568</v>
+        <v>1.39106166390001</v>
       </c>
       <c r="AS3" t="n">
-        <v>70.23866749475064</v>
+        <v>71.51427106727859</v>
       </c>
       <c r="AT3" t="n">
-        <v>2328151.633028278</v>
+        <v>5661307.275900791</v>
       </c>
       <c r="AU3" t="n">
-        <v>73.66187075753723</v>
+        <v>78.78069890635679</v>
       </c>
       <c r="AV3" t="n">
-        <v>22.9902516384128</v>
+        <v>24.30985727624383</v>
       </c>
       <c r="AW3" t="n">
-        <v>183.9804287504475</v>
+        <v>185.2482326263839</v>
       </c>
       <c r="AX3" t="n">
-        <v>1.270439686171952</v>
+        <v>1.392265239429105</v>
       </c>
       <c r="AY3" t="n">
-        <v>72.6402838423699</v>
+        <v>71.63869714552489</v>
       </c>
       <c r="AZ3" t="n">
-        <v>6597654.053612292</v>
+        <v>5536278.678137922</v>
       </c>
       <c r="BA3" t="n">
-        <v>78.71258075312505</v>
+        <v>77.87053154595172</v>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>pfoInmcq</t>
+          <t>IkCftsQm</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>hAcTWKKN</t>
+          <t>A15eUM4C</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>AgAeVYgC</t>
+          <t>QVJwrCwI</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -1065,27 +1097,27 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">stieler t 
+          <t xml:space="preserve">exner f 
   ger </t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">deutsche bank park
-  frankfurt </t>
+          <t xml:space="preserve">holstein stadion
+  kiel </t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>58000</v>
+        <v>15034</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>8vndvXTk</t>
+          <t>63WsD2ei</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>hQAtP9Sl</t>
+          <t>nwkTahLL</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -1112,115 +1144,143 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>EuakNmc1</t>
+          <t>ILyJuN3g</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>nJQmYp1B</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="inlineStr"/>
-      <c r="S4" t="inlineStr"/>
-      <c r="T4" t="inlineStr"/>
-      <c r="U4" t="inlineStr"/>
-      <c r="V4" t="inlineStr"/>
-      <c r="W4" t="inlineStr"/>
-      <c r="X4" t="inlineStr"/>
-      <c r="Y4" t="inlineStr"/>
-      <c r="Z4" t="inlineStr"/>
-      <c r="AA4" t="inlineStr"/>
-      <c r="AB4" t="inlineStr"/>
-      <c r="AC4" t="inlineStr"/>
+          <t>dfNCCCzS</t>
+        </is>
+      </c>
+      <c r="P4" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>182.5</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1</v>
+      </c>
+      <c r="S4" t="n">
+        <v>2</v>
+      </c>
+      <c r="T4" t="n">
+        <v>140</v>
+      </c>
+      <c r="U4" t="n">
+        <v>4800000</v>
+      </c>
+      <c r="V4" t="n">
+        <v>149</v>
+      </c>
+      <c r="W4" t="n">
+        <v>23.33333333333333</v>
+      </c>
+      <c r="X4" t="n">
+        <v>181.6666666666667</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1.666666666666667</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>226</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>33000000</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>243</v>
+      </c>
       <c r="AD4" t="n">
-        <v>24.13253968253968</v>
+        <v>25.21661054994389</v>
       </c>
       <c r="AE4" t="n">
-        <v>183.3767857142857</v>
+        <v>186.3560044893378</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.662301587301588</v>
+        <v>1.084062850729517</v>
       </c>
       <c r="AG4" t="n">
-        <v>76.83075396825396</v>
+        <v>68.55162738496071</v>
       </c>
       <c r="AH4" t="n">
-        <v>15395456.34920635</v>
+        <v>1749932.65993266</v>
       </c>
       <c r="AI4" t="n">
-        <v>81.29702380952381</v>
+        <v>72.49438832772167</v>
       </c>
       <c r="AJ4" t="n">
-        <v>26.69761904761905</v>
+        <v>25.13650793650794</v>
       </c>
       <c r="AK4" t="n">
-        <v>185.7875180375181</v>
+        <v>186.4759920634921</v>
       </c>
       <c r="AL4" t="n">
-        <v>1.813997113997114</v>
+        <v>1.57797619047619</v>
       </c>
       <c r="AM4" t="n">
-        <v>75.16587301587302</v>
+        <v>75.85714285714286</v>
       </c>
       <c r="AN4" t="n">
-        <v>8908596.681096682</v>
+        <v>11076329.36507936</v>
       </c>
       <c r="AO4" t="n">
-        <v>78.57712842712843</v>
+        <v>79.67361111111111</v>
       </c>
       <c r="AP4" t="n">
-        <v>23.63061590664974</v>
+        <v>25.07185511080439</v>
       </c>
       <c r="AQ4" t="n">
-        <v>184.1267112586661</v>
+        <v>185.8889895330113</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.39106166390001</v>
+        <v>1.016294762671574</v>
       </c>
       <c r="AS4" t="n">
-        <v>71.51427106727859</v>
+        <v>66.6971187025535</v>
       </c>
       <c r="AT4" t="n">
-        <v>5661307.275900791</v>
+        <v>1422825.727513228</v>
       </c>
       <c r="AU4" t="n">
-        <v>78.78069890635679</v>
+        <v>71.27670424047236</v>
       </c>
       <c r="AV4" t="n">
-        <v>24.30985727624383</v>
+        <v>24.35002587991719</v>
       </c>
       <c r="AW4" t="n">
-        <v>185.2482326263839</v>
+        <v>183.8105158730158</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.392265239429105</v>
+        <v>1.259057971014493</v>
       </c>
       <c r="AY4" t="n">
-        <v>71.63869714552489</v>
+        <v>73.565450310559</v>
       </c>
       <c r="AZ4" t="n">
-        <v>5536278.678137922</v>
+        <v>8305568.064182194</v>
       </c>
       <c r="BA4" t="n">
-        <v>77.87053154595172</v>
+        <v>78.39579020013801</v>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>IkCftsQm</t>
+          <t>KUx4Q7x1</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>A15eUM4C</t>
+          <t>K6A2elS9</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>QVJwrCwI</t>
+          <t>61DvZGfm</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
@@ -1228,27 +1288,27 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">siebert d 
+          <t xml:space="preserve">gerach t 
   ger </t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">holstein stadion
-  kiel </t>
+          <t xml:space="preserve">mhparena
+  stuttgart </t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>15034</v>
+        <v>60449</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>63WsD2ei</t>
+          <t>nJQmYp1B</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>nwkTahLL</t>
+          <t>EuakNmc1</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -1275,115 +1335,143 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>ILyJuN3g</t>
+          <t>fiEQZ7C7</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>dfNCCCzS</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="inlineStr"/>
-      <c r="S5" t="inlineStr"/>
-      <c r="T5" t="inlineStr"/>
-      <c r="U5" t="inlineStr"/>
-      <c r="V5" t="inlineStr"/>
-      <c r="W5" t="inlineStr"/>
-      <c r="X5" t="inlineStr"/>
-      <c r="Y5" t="inlineStr"/>
-      <c r="Z5" t="inlineStr"/>
-      <c r="AA5" t="inlineStr"/>
-      <c r="AB5" t="inlineStr"/>
-      <c r="AC5" t="inlineStr"/>
+          <t>8vndvXTk</t>
+        </is>
+      </c>
+      <c r="P5" t="n">
+        <v>21.6</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>187</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="n">
+        <v>351</v>
+      </c>
+      <c r="U5" t="n">
+        <v>27625000</v>
+      </c>
+      <c r="V5" t="n">
+        <v>392</v>
+      </c>
+      <c r="W5" t="n">
+        <v>24</v>
+      </c>
+      <c r="X5" t="n">
+        <v>190</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>75</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>7000000</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>79</v>
+      </c>
       <c r="AD5" t="n">
-        <v>25.21661054994389</v>
+        <v>24.33326599326599</v>
       </c>
       <c r="AE5" t="n">
-        <v>186.3560044893378</v>
+        <v>185.0003367003367</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.084062850729517</v>
+        <v>1.457037037037037</v>
       </c>
       <c r="AG5" t="n">
-        <v>68.55162738496071</v>
+        <v>75.73663299663301</v>
       </c>
       <c r="AH5" t="n">
-        <v>1749932.65993266</v>
+        <v>11309555.55555555</v>
       </c>
       <c r="AI5" t="n">
-        <v>72.49438832772167</v>
+        <v>78.97582491582492</v>
       </c>
       <c r="AJ5" t="n">
-        <v>25.13650793650794</v>
+        <v>25.7487012987013</v>
       </c>
       <c r="AK5" t="n">
-        <v>186.4759920634921</v>
+        <v>183.0149350649351</v>
       </c>
       <c r="AL5" t="n">
-        <v>1.57797619047619</v>
+        <v>1.565584415584415</v>
       </c>
       <c r="AM5" t="n">
-        <v>75.85714285714286</v>
+        <v>74.4012987012987</v>
       </c>
       <c r="AN5" t="n">
-        <v>11076329.36507936</v>
+        <v>6715259.740259741</v>
       </c>
       <c r="AO5" t="n">
-        <v>79.67361111111111</v>
+        <v>78.35714285714286</v>
       </c>
       <c r="AP5" t="n">
-        <v>25.07185511080439</v>
+        <v>24.10255291005291</v>
       </c>
       <c r="AQ5" t="n">
-        <v>185.8889895330113</v>
+        <v>182.6744841269841</v>
       </c>
       <c r="AR5" t="n">
-        <v>1.016294762671574</v>
+        <v>1.246031746031746</v>
       </c>
       <c r="AS5" t="n">
-        <v>66.6971187025535</v>
+        <v>71.18182539682539</v>
       </c>
       <c r="AT5" t="n">
-        <v>1422825.727513228</v>
+        <v>5778611.772486772</v>
       </c>
       <c r="AU5" t="n">
-        <v>71.27670424047236</v>
+        <v>76.13571428571429</v>
       </c>
       <c r="AV5" t="n">
-        <v>24.35002587991719</v>
+        <v>26.1015589569161</v>
       </c>
       <c r="AW5" t="n">
-        <v>183.8105158730158</v>
+        <v>185.3565759637188</v>
       </c>
       <c r="AX5" t="n">
-        <v>1.259057971014493</v>
+        <v>1.495975056689342</v>
       </c>
       <c r="AY5" t="n">
-        <v>73.565450310559</v>
+        <v>72.27040816326532</v>
       </c>
       <c r="AZ5" t="n">
-        <v>8305568.064182194</v>
+        <v>4399317.602040816</v>
       </c>
       <c r="BA5" t="n">
-        <v>78.39579020013801</v>
+        <v>76.67063492063492</v>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>KUx4Q7x1</t>
+          <t>pdPRS0me</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>K6A2elS9</t>
+          <t>hpYJ6izc</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>61DvZGfm</t>
+          <t>0OYDmG9t</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -1391,27 +1479,27 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">osmers h 
+          <t xml:space="preserve">hartmann r 
   ger </t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">mhparena
-  stuttgart </t>
+          <t xml:space="preserve">weserstadion
+  bremen </t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>60449</v>
+        <v>42100</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>nJQmYp1B</t>
+          <t>Ig1f1fy3</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>EuakNmc1</t>
+          <t>nP1i5US1</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -1438,21 +1526,35 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>fiEQZ7C7</t>
+          <t>v9k3aY5F</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>8vndvXTk</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr"/>
-      <c r="R6" t="inlineStr"/>
-      <c r="S6" t="inlineStr"/>
-      <c r="T6" t="inlineStr"/>
-      <c r="U6" t="inlineStr"/>
-      <c r="V6" t="inlineStr"/>
+          <t>0Ija0Ej9</t>
+        </is>
+      </c>
+      <c r="P6" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>182</v>
+      </c>
+      <c r="R6" t="n">
+        <v>2</v>
+      </c>
+      <c r="S6" t="n">
+        <v>2</v>
+      </c>
+      <c r="T6" t="n">
+        <v>150</v>
+      </c>
+      <c r="U6" t="n">
+        <v>13000000</v>
+      </c>
+      <c r="V6" t="n">
+        <v>154</v>
+      </c>
       <c r="W6" t="inlineStr"/>
       <c r="X6" t="inlineStr"/>
       <c r="Y6" t="inlineStr"/>
@@ -1461,120 +1563,120 @@
       <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="n">
-        <v>24.38503787878788</v>
+        <v>26.06493506493506</v>
       </c>
       <c r="AE6" t="n">
-        <v>184.6373106060606</v>
+        <v>183.2077922077922</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.49854797979798</v>
+        <v>1.181818181818182</v>
       </c>
       <c r="AG6" t="n">
-        <v>76.09526515151515</v>
+        <v>73.3116883116883</v>
       </c>
       <c r="AH6" t="n">
-        <v>11807380.05050505</v>
+        <v>4990584.415584415</v>
       </c>
       <c r="AI6" t="n">
-        <v>79.15915404040403</v>
+        <v>76.15584415584416</v>
       </c>
       <c r="AJ6" t="n">
-        <v>25.7487012987013</v>
+        <v>25.3025974025974</v>
       </c>
       <c r="AK6" t="n">
-        <v>183.0149350649351</v>
+        <v>184.824025974026</v>
       </c>
       <c r="AL6" t="n">
-        <v>1.565584415584415</v>
+        <v>2.331818181818182</v>
       </c>
       <c r="AM6" t="n">
-        <v>74.4012987012987</v>
+        <v>80.10974025974026</v>
       </c>
       <c r="AN6" t="n">
-        <v>6715259.740259741</v>
+        <v>30490909.09090909</v>
       </c>
       <c r="AO6" t="n">
-        <v>78.35714285714286</v>
+        <v>83.35649350649351</v>
       </c>
       <c r="AP6" t="n">
-        <v>24.09893353174603</v>
+        <v>24.93500969228271</v>
       </c>
       <c r="AQ6" t="n">
-        <v>182.931994047619</v>
+        <v>184.7790205231597</v>
       </c>
       <c r="AR6" t="n">
-        <v>1.245535714285714</v>
+        <v>1.150492243045197</v>
       </c>
       <c r="AS6" t="n">
-        <v>70.96324404761904</v>
+        <v>68.86975642659809</v>
       </c>
       <c r="AT6" t="n">
-        <v>5420341.021825397</v>
+        <v>2632865.307164055</v>
       </c>
       <c r="AU6" t="n">
-        <v>75.95982142857142</v>
+        <v>74.30510073976197</v>
       </c>
       <c r="AV6" t="n">
-        <v>26.1015589569161</v>
+        <v>24.89721359558316</v>
       </c>
       <c r="AW6" t="n">
-        <v>185.3565759637188</v>
+        <v>184.0183316080056</v>
       </c>
       <c r="AX6" t="n">
-        <v>1.495975056689342</v>
+        <v>1.962387853692201</v>
       </c>
       <c r="AY6" t="n">
-        <v>72.27040816326532</v>
+        <v>77.71189490288869</v>
       </c>
       <c r="AZ6" t="n">
-        <v>4399317.602040815</v>
+        <v>20467194.12402643</v>
       </c>
       <c r="BA6" t="n">
-        <v>76.67063492063492</v>
+        <v>82.26340209997042</v>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>YZPE6Sx7</t>
+          <t>2VSFgl3c</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>hpYJ6izc</t>
+          <t>UgdQz0fK</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>0OYDmG9t</t>
+          <t>AVR8vwXP</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45535.4375</v>
+        <v>45535.5625</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">zwayer f 
+          <t xml:space="preserve">jollenbeck m 
   ger </t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">weserstadion
-  bremen </t>
+          <t xml:space="preserve">bayarena
+  leverkusen </t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>42100</v>
+        <v>30210</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ig1f1fy3</t>
+          <t>4jcj2zMd</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>nP1i5US1</t>
+          <t>KbS1suSm</t>
         </is>
       </c>
       <c r="H7" t="n">
@@ -1601,143 +1703,171 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>v9k3aY5F</t>
+          <t>WG9pOTse</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>0Ija0Ej9</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr"/>
-      <c r="R7" t="inlineStr"/>
-      <c r="S7" t="inlineStr"/>
-      <c r="T7" t="inlineStr"/>
-      <c r="U7" t="inlineStr"/>
-      <c r="V7" t="inlineStr"/>
-      <c r="W7" t="inlineStr"/>
-      <c r="X7" t="inlineStr"/>
-      <c r="Y7" t="inlineStr"/>
-      <c r="Z7" t="inlineStr"/>
-      <c r="AA7" t="inlineStr"/>
-      <c r="AB7" t="inlineStr"/>
-      <c r="AC7" t="inlineStr"/>
+          <t>nP1i5US1</t>
+        </is>
+      </c>
+      <c r="P7" t="n">
+        <v>24</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>178</v>
+      </c>
+      <c r="R7" t="n">
+        <v>2</v>
+      </c>
+      <c r="S7" t="n">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>81</v>
+      </c>
+      <c r="U7" t="n">
+        <v>36500000</v>
+      </c>
+      <c r="V7" t="n">
+        <v>85</v>
+      </c>
+      <c r="W7" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="X7" t="n">
+        <v>186.75</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>297</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>63400000</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>333</v>
+      </c>
       <c r="AD7" t="n">
-        <v>26.06493506493506</v>
+        <v>25.57026515151515</v>
       </c>
       <c r="AE7" t="n">
-        <v>183.2077922077922</v>
+        <v>185.0150726010101</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.181818181818182</v>
+        <v>2.047301136363636</v>
       </c>
       <c r="AG7" t="n">
-        <v>73.3116883116883</v>
+        <v>81.27348484848486</v>
       </c>
       <c r="AH7" t="n">
-        <v>4990584.415584415</v>
+        <v>33347711.48989899</v>
       </c>
       <c r="AI7" t="n">
-        <v>76.15584415584416</v>
+        <v>84.20274621212121</v>
       </c>
       <c r="AJ7" t="n">
-        <v>25.3025974025974</v>
+        <v>24.72727272727273</v>
       </c>
       <c r="AK7" t="n">
-        <v>184.824025974026</v>
+        <v>182.8584415584416</v>
       </c>
       <c r="AL7" t="n">
-        <v>2.331818181818182</v>
+        <v>2.077922077922078</v>
       </c>
       <c r="AM7" t="n">
-        <v>80.10974025974026</v>
+        <v>80.20909090909092</v>
       </c>
       <c r="AN7" t="n">
-        <v>30490909.09090909</v>
+        <v>28920779.22077922</v>
       </c>
       <c r="AO7" t="n">
-        <v>83.35649350649351</v>
+        <v>83.84675324675325</v>
       </c>
       <c r="AP7" t="n">
-        <v>24.93500969228271</v>
+        <v>23.26643121016522</v>
       </c>
       <c r="AQ7" t="n">
-        <v>184.7790205231597</v>
+        <v>181.6212475965353</v>
       </c>
       <c r="AR7" t="n">
-        <v>1.150492243045197</v>
+        <v>1.789159313264173</v>
       </c>
       <c r="AS7" t="n">
-        <v>68.8697564265981</v>
+        <v>79.24480676328503</v>
       </c>
       <c r="AT7" t="n">
-        <v>2632865.307164056</v>
+        <v>36204414.0851334</v>
       </c>
       <c r="AU7" t="n">
-        <v>74.30510073976197</v>
+        <v>84.34693523654521</v>
       </c>
       <c r="AV7" t="n">
-        <v>24.89721359558316</v>
+        <v>24.87208163644499</v>
       </c>
       <c r="AW7" t="n">
-        <v>184.0183316080056</v>
+        <v>184.8121307608885</v>
       </c>
       <c r="AX7" t="n">
-        <v>1.962387853692201</v>
+        <v>1.736474188337543</v>
       </c>
       <c r="AY7" t="n">
-        <v>77.71189490288869</v>
+        <v>76.99233651097005</v>
       </c>
       <c r="AZ7" t="n">
-        <v>20467194.12402643</v>
+        <v>18437160.85932701</v>
       </c>
       <c r="BA7" t="n">
-        <v>82.26340209997042</v>
+        <v>81.49275125323263</v>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>2VSFgl3c</t>
+          <t>WzqXh8OL</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>UgdQz0fK</t>
+          <t>8f6APkLc</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>AVR8vwXP</t>
+          <t>W8b4TCOO</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45535.5625</v>
+        <v>45536.4375</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">brand b 
+          <t xml:space="preserve">stegemann s 
   ger </t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">bayarena
-  leverkusen </t>
+          <t xml:space="preserve">voith arena
+  heidenheim </t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>30210</v>
+        <v>15000</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>4jcj2zMd</t>
+          <t>KWixEVWi</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>KbS1suSm</t>
+          <t>fTVNku3I</t>
         </is>
       </c>
       <c r="H8" t="n">
@@ -1762,145 +1892,165 @@
           <t>bundesliga</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>WG9pOTse</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>nP1i5US1</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="inlineStr"/>
-      <c r="R8" t="inlineStr"/>
-      <c r="S8" t="inlineStr"/>
-      <c r="T8" t="inlineStr"/>
-      <c r="U8" t="inlineStr"/>
-      <c r="V8" t="inlineStr"/>
-      <c r="W8" t="inlineStr"/>
-      <c r="X8" t="inlineStr"/>
-      <c r="Y8" t="inlineStr"/>
-      <c r="Z8" t="inlineStr"/>
-      <c r="AA8" t="inlineStr"/>
-      <c r="AB8" t="inlineStr"/>
-      <c r="AC8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="n">
+        <v>23</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>186</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1</v>
+      </c>
+      <c r="S8" t="n">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>66</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1100000</v>
+      </c>
+      <c r="V8" t="n">
+        <v>70</v>
+      </c>
+      <c r="W8" t="n">
+        <v>25.75</v>
+      </c>
+      <c r="X8" t="n">
+        <v>182.5</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>287</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>12800000</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>295</v>
+      </c>
       <c r="AD8" t="n">
-        <v>25.57026515151515</v>
+        <v>25.73944805194805</v>
       </c>
       <c r="AE8" t="n">
-        <v>185.0150726010101</v>
+        <v>186.8969155844156</v>
       </c>
       <c r="AF8" t="n">
-        <v>2.047301136363636</v>
+        <v>1</v>
       </c>
       <c r="AG8" t="n">
-        <v>81.27348484848486</v>
+        <v>72.80357142857143</v>
       </c>
       <c r="AH8" t="n">
-        <v>33347711.48989899</v>
+        <v>4238555.194805195</v>
       </c>
       <c r="AI8" t="n">
-        <v>84.20274621212121</v>
+        <v>75.16071428571429</v>
       </c>
       <c r="AJ8" t="n">
-        <v>24.72727272727273</v>
+        <v>25.25753968253968</v>
       </c>
       <c r="AK8" t="n">
-        <v>182.8584415584416</v>
+        <v>185.8295454545455</v>
       </c>
       <c r="AL8" t="n">
-        <v>2.077922077922078</v>
+        <v>1.39570707070707</v>
       </c>
       <c r="AM8" t="n">
-        <v>80.20909090909092</v>
+        <v>74.24444444444444</v>
       </c>
       <c r="AN8" t="n">
-        <v>28920779.22077922</v>
+        <v>6440422.077922078</v>
       </c>
       <c r="AO8" t="n">
-        <v>83.84675324675325</v>
+        <v>77.37972582972581</v>
       </c>
       <c r="AP8" t="n">
-        <v>23.17891649413389</v>
+        <v>26.9906462585034</v>
       </c>
       <c r="AQ8" t="n">
-        <v>181.8475755713188</v>
+        <v>183.5202664399092</v>
       </c>
       <c r="AR8" t="n">
-        <v>1.758620659232072</v>
+        <v>1</v>
       </c>
       <c r="AS8" t="n">
-        <v>79.10732940821256</v>
+        <v>69.23341836734694</v>
       </c>
       <c r="AT8" t="n">
-        <v>35266929.54878756</v>
+        <v>1907610.544217687</v>
       </c>
       <c r="AU8" t="n">
-        <v>84.33736868882929</v>
+        <v>71.0625</v>
       </c>
       <c r="AV8" t="n">
-        <v>24.87208163644499</v>
+        <v>23.85461489220888</v>
       </c>
       <c r="AW8" t="n">
-        <v>184.8121307608885</v>
+        <v>184.2628815002875</v>
       </c>
       <c r="AX8" t="n">
-        <v>1.736474188337543</v>
+        <v>1.178488564484805</v>
       </c>
       <c r="AY8" t="n">
-        <v>76.99233651097005</v>
+        <v>71.15496350454058</v>
       </c>
       <c r="AZ8" t="n">
-        <v>18437160.85932701</v>
+        <v>3961201.708953119</v>
       </c>
       <c r="BA8" t="n">
-        <v>81.49275125323263</v>
+        <v>76.54832386702687</v>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>M5BRZDsC</t>
+          <t>0jdIgO6t</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>8f6APkLc</t>
+          <t>4fuCGs9P</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>W8b4TCOO</t>
+          <t>2T6mXfPa</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45536.4375</v>
+        <v>45536.52083333334</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">stegemann s 
+          <t xml:space="preserve">welz t 
   ger </t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">voith arena
-  heidenheim </t>
+          <t xml:space="preserve">allianz arena
+  munich </t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>15000</v>
+        <v>75024</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>KWixEVWi</t>
+          <t>nVp0wiqd</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>fTVNku3I</t>
+          <t>fiEQZ7C7</t>
         </is>
       </c>
       <c r="H9" t="n">
@@ -1926,136 +2076,168 @@
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr"/>
-      <c r="Q9" t="inlineStr"/>
-      <c r="R9" t="inlineStr"/>
-      <c r="S9" t="inlineStr"/>
-      <c r="T9" t="inlineStr"/>
-      <c r="U9" t="inlineStr"/>
-      <c r="V9" t="inlineStr"/>
-      <c r="W9" t="inlineStr"/>
-      <c r="X9" t="inlineStr"/>
-      <c r="Y9" t="inlineStr"/>
-      <c r="Z9" t="inlineStr"/>
-      <c r="AA9" t="inlineStr"/>
-      <c r="AB9" t="inlineStr"/>
-      <c r="AC9" t="inlineStr"/>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>nJQmYp1B</t>
+        </is>
+      </c>
+      <c r="P9" t="n">
+        <v>21.83333333333333</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>184.8333333333333</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S9" t="n">
+        <v>6</v>
+      </c>
+      <c r="T9" t="n">
+        <v>430</v>
+      </c>
+      <c r="U9" t="n">
+        <v>98525000</v>
+      </c>
+      <c r="V9" t="n">
+        <v>489</v>
+      </c>
+      <c r="W9" t="n">
+        <v>24.71428571428572</v>
+      </c>
+      <c r="X9" t="n">
+        <v>186.5714285714286</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.142857142857143</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>500</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>35900000</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>532</v>
+      </c>
       <c r="AD9" t="n">
-        <v>25.8515625</v>
+        <v>26.95064935064935</v>
       </c>
       <c r="AE9" t="n">
-        <v>186.9779829545454</v>
+        <v>184.8149350649351</v>
       </c>
       <c r="AF9" t="n">
-        <v>1</v>
+        <v>2.993506493506493</v>
       </c>
       <c r="AG9" t="n">
-        <v>72.828125</v>
+        <v>81.74675324675324</v>
       </c>
       <c r="AH9" t="n">
-        <v>4253906.25</v>
+        <v>39978051.94805194</v>
       </c>
       <c r="AI9" t="n">
-        <v>75.15198863636363</v>
+        <v>84.61428571428571</v>
       </c>
       <c r="AJ9" t="n">
-        <v>25.35034722222222</v>
+        <v>27.09920634920635</v>
       </c>
       <c r="AK9" t="n">
-        <v>185.8133522727273</v>
+        <v>183.5822510822511</v>
       </c>
       <c r="AL9" t="n">
-        <v>1.396243686868687</v>
+        <v>1.702958152958153</v>
       </c>
       <c r="AM9" t="n">
-        <v>74.28888888888889</v>
+        <v>75.38455988455988</v>
       </c>
       <c r="AN9" t="n">
-        <v>6341619.318181818</v>
+        <v>8859199.134199133</v>
       </c>
       <c r="AO9" t="n">
-        <v>77.2822601010101</v>
+        <v>77.23109668109667</v>
       </c>
       <c r="AP9" t="n">
-        <v>26.94022817460317</v>
+        <v>24.78309956705795</v>
       </c>
       <c r="AQ9" t="n">
-        <v>183.3282490079365</v>
+        <v>182.3895437743088</v>
       </c>
       <c r="AR9" t="n">
-        <v>1</v>
+        <v>2.29010860116878</v>
       </c>
       <c r="AS9" t="n">
-        <v>69.34015376984127</v>
+        <v>78.49870507196707</v>
       </c>
       <c r="AT9" t="n">
-        <v>1937487.599206349</v>
+        <v>29706104.23877095</v>
       </c>
       <c r="AU9" t="n">
-        <v>71.13702876984127</v>
+        <v>83.38213768015353</v>
       </c>
       <c r="AV9" t="n">
-        <v>23.90971984886459</v>
+        <v>25.00978435996824</v>
       </c>
       <c r="AW9" t="n">
-        <v>184.0197940400243</v>
+        <v>184.517054087081</v>
       </c>
       <c r="AX9" t="n">
-        <v>1.169671812106023</v>
+        <v>1.471632886564237</v>
       </c>
       <c r="AY9" t="n">
-        <v>71.19951352101846</v>
+        <v>73.40237375270475</v>
       </c>
       <c r="AZ9" t="n">
-        <v>3934073.512379434</v>
+        <v>6103059.696990924</v>
       </c>
       <c r="BA9" t="n">
-        <v>76.5209765654667</v>
+        <v>76.654855014088</v>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>0jdIgO6t</t>
+          <t>f3ddUIXs</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>4fuCGs9P</t>
+          <t>GzfvcwRj</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>2T6mXfPa</t>
+          <t>zsmd0ggn</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45536.52083333334</v>
+        <v>45548.64583333334</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">welz t 
+          <t xml:space="preserve">jablonski s 
   ger </t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">allianz arena
-  munich </t>
+          <t xml:space="preserve">signal iduna park
+  dortmund </t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>75024</v>
+        <v>81365</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>nVp0wiqd</t>
+          <t>nP1i5US1</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>fiEQZ7C7</t>
+          <t>KWixEVWi</t>
         </is>
       </c>
       <c r="H10" t="n">
@@ -2080,12 +2262,12 @@
           <t>bundesliga</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>nJQmYp1B</t>
-        </is>
-      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>0Ija0Ej9</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr"/>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr"/>
@@ -2101,85 +2283,1055 @@
       <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="n">
+        <v>25.3025974025974</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>184.824025974026</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>2.331818181818182</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>80.10974025974026</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>30490909.09090909</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>83.35649350649351</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>25.73944805194805</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>186.8969155844156</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>72.80357142857143</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>4238555.194805195</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>75.16071428571429</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>24.89721359558316</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>184.0183316080056</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>1.962387853692201</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>77.71189490288869</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>20467194.12402643</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>82.26340209997042</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>26.9906462585034</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>183.5202664399092</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>69.23341836734694</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>1907610.544217687</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>71.0625</v>
+      </c>
+      <c r="BB10" t="inlineStr">
+        <is>
+          <t>IkCftsQm</t>
+        </is>
+      </c>
+      <c r="BC10" t="inlineStr">
+        <is>
+          <t>4ljanukM</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>UwsvBA74</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>45549.4375</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">jollenbeck m 
+  ger </t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">borussia park
+  monchengladbach </t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>54042</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>88HSzjDr</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>nJQmYp1B</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>59</v>
+      </c>
+      <c r="I11" t="n">
+        <v>591</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>WG9pOTse</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>fiEQZ7C7</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="inlineStr"/>
+      <c r="W11" t="inlineStr"/>
+      <c r="X11" t="inlineStr"/>
+      <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="inlineStr"/>
+      <c r="AA11" t="inlineStr"/>
+      <c r="AB11" t="inlineStr"/>
+      <c r="AC11" t="inlineStr"/>
+      <c r="AD11" t="n">
+        <v>25.33614718614719</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>184.7157287157287</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>1.518903318903319</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>75.25079365079364</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>8434855.6998557</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>78.14877344877345</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>24.33326599326599</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>185.0003367003367</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>1.457037037037037</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>75.73663299663301</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>11309555.55555555</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>78.97582491582492</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>22.9902516384128</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>183.9804287504475</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>1.270439686171952</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>72.6402838423699</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>6597654.053612292</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>78.71258075312505</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>24.10255291005291</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>182.6744841269841</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>1.246031746031746</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>71.18182539682539</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>5778611.772486772</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>76.13571428571429</v>
+      </c>
+      <c r="BB11" t="inlineStr">
+        <is>
+          <t>M5BRZDsC</t>
+        </is>
+      </c>
+      <c r="BC11" t="inlineStr">
+        <is>
+          <t>GzfvcwRj</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>vZqDdBhB</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>45549.4375</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">brand b 
+  ger </t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">europa park stadion
+  freiburg </t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>34700</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>fiEQZ7C7</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>8Y2m6ADe</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>59</v>
+      </c>
+      <c r="I12" t="n">
+        <v>591</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>nJQmYp1B</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>0Ija0Ej9</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr"/>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="inlineStr"/>
+      <c r="W12" t="inlineStr"/>
+      <c r="X12" t="inlineStr"/>
+      <c r="Y12" t="inlineStr"/>
+      <c r="Z12" t="inlineStr"/>
+      <c r="AA12" t="inlineStr"/>
+      <c r="AB12" t="inlineStr"/>
+      <c r="AC12" t="inlineStr"/>
+      <c r="AD12" t="n">
+        <v>27.09920634920635</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>183.5822510822511</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>1.702958152958153</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>75.38455988455988</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>8859199.134199133</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>77.23109668109667</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>27.77777777777778</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>182.6578125</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>1.221527777777778</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>72.9484375</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>3466028.645833334</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>74.91024305555555</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>25.00978435996824</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>184.517054087081</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>1.471632886564237</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>73.40237375270475</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>6103059.696990924</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>76.654855014088</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>26.37626272429262</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>182.9074475807849</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>1.065942142493916</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>70.1685613180679</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>2335882.543678551</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>73.77268431237431</v>
+      </c>
+      <c r="BB12" t="inlineStr">
+        <is>
+          <t>YZPE6Sx7</t>
+        </is>
+      </c>
+      <c r="BC12" t="inlineStr">
+        <is>
+          <t>8f6APkLc</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>r7j4bXNb</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>45549.4375</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">welz t 
+  ger </t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">prezero arena
+  sinsheim </t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>30150</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>hQAtP9Sl</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>4jcj2zMd</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>59</v>
+      </c>
+      <c r="I13" t="n">
+        <v>591</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>nJQmYp1B</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>WG9pOTse</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr"/>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="inlineStr"/>
+      <c r="W13" t="inlineStr"/>
+      <c r="X13" t="inlineStr"/>
+      <c r="Y13" t="inlineStr"/>
+      <c r="Z13" t="inlineStr"/>
+      <c r="AA13" t="inlineStr"/>
+      <c r="AB13" t="inlineStr"/>
+      <c r="AC13" t="inlineStr"/>
+      <c r="AD13" t="n">
+        <v>26.69761904761905</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>185.7875180375181</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>1.813997113997114</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>75.16587301587302</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>8908596.681096682</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>78.57712842712843</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>25.57026515151515</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>185.0150726010101</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>2.047301136363636</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>81.27348484848486</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>33347711.48989899</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>84.20274621212121</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>24.30985727624383</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>185.2482326263839</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>1.392265239429105</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>71.63869714552489</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>5536278.678137922</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>77.87053154595172</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>23.26643121016522</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>181.6212475965353</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>1.789159313264173</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>79.24480676328503</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>36204414.0851334</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>84.34693523654521</v>
+      </c>
+      <c r="BB13" t="inlineStr">
+        <is>
+          <t>KUx4Q7x1</t>
+        </is>
+      </c>
+      <c r="BC13" t="inlineStr">
+        <is>
+          <t>hAcTWKKN</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>WSMotj8U</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>45549.4375</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dankert b 
+  ger </t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">red bull arena
+  leipzig </t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>47069</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>KbS1suSm</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>pzHW4oaE</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>59</v>
+      </c>
+      <c r="I14" t="n">
+        <v>591</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>nP1i5US1</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr"/>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="inlineStr"/>
+      <c r="W14" t="inlineStr"/>
+      <c r="X14" t="inlineStr"/>
+      <c r="Y14" t="inlineStr"/>
+      <c r="Z14" t="inlineStr"/>
+      <c r="AA14" t="inlineStr"/>
+      <c r="AB14" t="inlineStr"/>
+      <c r="AC14" t="inlineStr"/>
+      <c r="AD14" t="n">
+        <v>24.72727272727273</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>182.8584415584416</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>2.077922077922078</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>80.20909090909092</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>28920779.22077922</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>83.84675324675325</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>26.87939393939394</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>185.0273400673401</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>1.609292929292929</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>75.73811447811448</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>8341797.97979798</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>78.17542087542088</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>24.87208163644499</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>184.8121307608885</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>1.736474188337543</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>76.99233651097005</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>18437160.85932701</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>81.49275125323263</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>26.63337413582265</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>184.213609809548</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>1.436959124865303</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>73.52568395626749</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>4928472.152603731</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>76.12020897654766</v>
+      </c>
+      <c r="BB14" t="inlineStr">
+        <is>
+          <t>pfoInmcq</t>
+        </is>
+      </c>
+      <c r="BC14" t="inlineStr">
+        <is>
+          <t>0jdIgO6t</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>tI0qkTpo</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>45549.4375</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">zwayer f 
+  ger </t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">volkswagen arena
+  wolfsburg </t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>28917</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>nwkTahLL</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>8vndvXTk</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>59</v>
+      </c>
+      <c r="I15" t="n">
+        <v>591</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>dfNCCCzS</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>EuakNmc1</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr"/>
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="inlineStr"/>
+      <c r="W15" t="inlineStr"/>
+      <c r="X15" t="inlineStr"/>
+      <c r="Y15" t="inlineStr"/>
+      <c r="Z15" t="inlineStr"/>
+      <c r="AA15" t="inlineStr"/>
+      <c r="AB15" t="inlineStr"/>
+      <c r="AC15" t="inlineStr"/>
+      <c r="AD15" t="n">
+        <v>25.13650793650794</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>186.4759920634921</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>1.57797619047619</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>75.85714285714286</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>11076329.36507936</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>79.67361111111111</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>24.13253968253968</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>183.3767857142857</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>1.662301587301588</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>76.83075396825396</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>15395456.34920635</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>81.29702380952381</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>24.35002587991719</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>183.8105158730158</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>1.259057971014493</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>73.565450310559</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>8305568.064182194</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>78.39579020013801</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>23.63061590664974</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>184.1267112586661</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>1.39106166390001</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>71.51427106727859</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>5661307.275900791</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>78.78069890635679</v>
+      </c>
+      <c r="BB15" t="inlineStr">
+        <is>
+          <t>f3ddUIXs</t>
+        </is>
+      </c>
+      <c r="BC15" t="inlineStr">
+        <is>
+          <t>UgdQz0fK</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>x4pn9lxH</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>45549.5625</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">siebert d 
+  ger </t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">holstein stadion
+  kiel </t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>15034</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>63WsD2ei</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>nVp0wiqd</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>59</v>
+      </c>
+      <c r="I16" t="n">
+        <v>591</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>ILyJuN3g</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="inlineStr"/>
+      <c r="T16" t="inlineStr"/>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="inlineStr"/>
+      <c r="W16" t="inlineStr"/>
+      <c r="X16" t="inlineStr"/>
+      <c r="Y16" t="inlineStr"/>
+      <c r="Z16" t="inlineStr"/>
+      <c r="AA16" t="inlineStr"/>
+      <c r="AB16" t="inlineStr"/>
+      <c r="AC16" t="inlineStr"/>
+      <c r="AD16" t="n">
+        <v>25.21661054994389</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>186.3560044893378</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>1.084062850729517</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>68.55162738496071</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>1749932.65993266</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>72.49438832772167</v>
+      </c>
+      <c r="AJ16" t="n">
         <v>26.95064935064935</v>
       </c>
-      <c r="AE10" t="n">
+      <c r="AK16" t="n">
         <v>184.8149350649351</v>
       </c>
-      <c r="AF10" t="n">
+      <c r="AL16" t="n">
         <v>2.993506493506493</v>
       </c>
-      <c r="AG10" t="n">
+      <c r="AM16" t="n">
         <v>81.74675324675324</v>
       </c>
-      <c r="AH10" t="n">
+      <c r="AN16" t="n">
         <v>39978051.94805194</v>
       </c>
-      <c r="AI10" t="n">
+      <c r="AO16" t="n">
         <v>84.61428571428571</v>
       </c>
-      <c r="AJ10" t="n">
-        <v>27.09920634920635</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>183.5822510822511</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>1.702958152958153</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>75.38455988455988</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>8859199.134199133</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>77.23109668109667</v>
-      </c>
-      <c r="AP10" t="n">
+      <c r="AP16" t="n">
+        <v>25.07185511080439</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>185.8889895330113</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>1.016294762671574</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>66.6971187025535</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>1422825.727513228</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>71.27670424047236</v>
+      </c>
+      <c r="AV16" t="n">
         <v>24.78309956705795</v>
       </c>
-      <c r="AQ10" t="n">
+      <c r="AW16" t="n">
         <v>182.3895437743088</v>
       </c>
-      <c r="AR10" t="n">
+      <c r="AX16" t="n">
         <v>2.29010860116878</v>
       </c>
-      <c r="AS10" t="n">
+      <c r="AY16" t="n">
         <v>78.49870507196707</v>
       </c>
-      <c r="AT10" t="n">
+      <c r="AZ16" t="n">
         <v>29706104.23877095</v>
       </c>
-      <c r="AU10" t="n">
+      <c r="BA16" t="n">
         <v>83.38213768015353</v>
       </c>
-      <c r="AV10" t="n">
-        <v>25.00978435996824</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>184.517054087081</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>1.471632886564237</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>73.40237375270475</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>6103059.696990924</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>76.654855014088</v>
-      </c>
-      <c r="BB10" t="inlineStr">
-        <is>
-          <t>f3ddUIXs</t>
-        </is>
-      </c>
-      <c r="BC10" t="inlineStr">
-        <is>
-          <t>GzfvcwRj</t>
+      <c r="BB16" t="inlineStr">
+        <is>
+          <t>KUx4Q7x1</t>
+        </is>
+      </c>
+      <c r="BC16" t="inlineStr">
+        <is>
+          <t>K6A2elS9</t>
         </is>
       </c>
     </row>

--- a/data/germany/p6_deployment/data_preparation/df_filled.xlsx
+++ b/data/germany/p6_deployment/data_preparation/df_filled.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BB3"/>
+  <dimension ref="A1:AO10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -495,205 +495,140 @@
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
+          <t>id_team_home_rival_team</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
           <t>id_team_away_rival_team</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>mean_age_player_miss_home</t>
-        </is>
-      </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>mean_hei_player_miss_home</t>
+          <t>mean_age_player_start_home</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>mean_int_rep_player_miss_home</t>
+          <t>mean_hei_player_start_home</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>n_player_miss_home</t>
+          <t>mean_int_rep_player_start_home</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>sum_rat_player_miss_home</t>
+          <t>mean_rat_player_start_home</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>sum_val_player_miss_home</t>
+          <t>mean_val_player_start_home</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>sum_pot_player_miss_home</t>
+          <t>mean_pot_player_start_home</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>mean_age_player_miss_away</t>
+          <t>mean_age_player_start_away</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>mean_hei_player_miss_away</t>
+          <t>mean_hei_player_start_away</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>mean_int_rep_player_miss_away</t>
+          <t>mean_int_rep_player_start_away</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>n_player_miss_away</t>
+          <t>mean_rat_player_start_away</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>sum_rat_player_miss_away</t>
+          <t>mean_val_player_start_away</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>sum_val_player_miss_away</t>
+          <t>mean_pot_player_start_away</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>sum_pot_player_miss_away</t>
+          <t>mean_age_player_sub_home</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>mean_age_player_start_home</t>
+          <t>mean_hei_player_sub_home</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>mean_hei_player_start_home</t>
+          <t>mean_int_rep_player_sub_home</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>mean_int_rep_player_start_home</t>
+          <t>mean_rat_player_sub_home</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>mean_rat_player_start_home</t>
+          <t>mean_val_player_sub_home</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>mean_val_player_start_home</t>
+          <t>mean_pot_player_sub_home</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>mean_pot_player_start_home</t>
+          <t>mean_age_player_sub_away</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>mean_age_player_start_away</t>
+          <t>mean_hei_player_sub_away</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>mean_hei_player_start_away</t>
+          <t>mean_int_rep_player_sub_away</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
-          <t>mean_int_rep_player_start_away</t>
+          <t>mean_rat_player_sub_away</t>
         </is>
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
-          <t>mean_rat_player_start_away</t>
+          <t>mean_val_player_sub_away</t>
         </is>
       </c>
       <c r="AM1" s="1" t="inlineStr">
         <is>
-          <t>mean_val_player_start_away</t>
+          <t>mean_pot_player_sub_away</t>
         </is>
       </c>
       <c r="AN1" s="1" t="inlineStr">
         <is>
-          <t>mean_pot_player_start_away</t>
+          <t>id_coach_home</t>
         </is>
       </c>
       <c r="AO1" s="1" t="inlineStr">
-        <is>
-          <t>mean_age_player_sub_home</t>
-        </is>
-      </c>
-      <c r="AP1" s="1" t="inlineStr">
-        <is>
-          <t>mean_hei_player_sub_home</t>
-        </is>
-      </c>
-      <c r="AQ1" s="1" t="inlineStr">
-        <is>
-          <t>mean_int_rep_player_sub_home</t>
-        </is>
-      </c>
-      <c r="AR1" s="1" t="inlineStr">
-        <is>
-          <t>mean_rat_player_sub_home</t>
-        </is>
-      </c>
-      <c r="AS1" s="1" t="inlineStr">
-        <is>
-          <t>mean_val_player_sub_home</t>
-        </is>
-      </c>
-      <c r="AT1" s="1" t="inlineStr">
-        <is>
-          <t>mean_pot_player_sub_home</t>
-        </is>
-      </c>
-      <c r="AU1" s="1" t="inlineStr">
-        <is>
-          <t>mean_age_player_sub_away</t>
-        </is>
-      </c>
-      <c r="AV1" s="1" t="inlineStr">
-        <is>
-          <t>mean_hei_player_sub_away</t>
-        </is>
-      </c>
-      <c r="AW1" s="1" t="inlineStr">
-        <is>
-          <t>mean_int_rep_player_sub_away</t>
-        </is>
-      </c>
-      <c r="AX1" s="1" t="inlineStr">
-        <is>
-          <t>mean_rat_player_sub_away</t>
-        </is>
-      </c>
-      <c r="AY1" s="1" t="inlineStr">
-        <is>
-          <t>mean_val_player_sub_away</t>
-        </is>
-      </c>
-      <c r="AZ1" s="1" t="inlineStr">
-        <is>
-          <t>mean_pot_player_sub_away</t>
-        </is>
-      </c>
-      <c r="BA1" s="1" t="inlineStr">
-        <is>
-          <t>id_coach_home</t>
-        </is>
-      </c>
-      <c r="BB1" s="1" t="inlineStr">
         <is>
           <t>id_coach_away</t>
         </is>
@@ -702,35 +637,35 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>W8b4TCOO</t>
+          <t>zsmd0ggn</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45536.4375</v>
+        <v>45548.64583333334</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">stegemann s 
+          <t xml:space="preserve">petersen m 
   ger </t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">voith arena
-  heidenheim </t>
+          <t xml:space="preserve">signal iduna park
+  dortmund </t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>15000</v>
+        <v>81365</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
+          <t>nP1i5US1</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
           <t>KWixEVWi</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>fTVNku3I</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -755,164 +690,127 @@
           <t>bundesliga</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="n">
-        <v>23</v>
-      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0Ija0Ej9</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr"/>
       <c r="P2" t="n">
-        <v>186</v>
+        <v>25.16666666666667</v>
       </c>
       <c r="Q2" t="n">
-        <v>1</v>
+        <v>186.1666666666667</v>
       </c>
       <c r="R2" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="S2" t="n">
-        <v>66</v>
+        <v>81.13333333333334</v>
       </c>
       <c r="T2" t="n">
-        <v>1100000</v>
+        <v>34916666.66666666</v>
       </c>
       <c r="U2" t="n">
-        <v>70</v>
+        <v>83.86666666666666</v>
       </c>
       <c r="V2" t="n">
-        <v>25.66666666666667</v>
+        <v>26.20833333333333</v>
       </c>
       <c r="W2" t="n">
-        <v>183</v>
+        <v>188.2731481481482</v>
       </c>
       <c r="X2" t="n">
         <v>1</v>
       </c>
       <c r="Y2" t="n">
-        <v>3</v>
+        <v>72.08333333333333</v>
       </c>
       <c r="Z2" t="n">
-        <v>214</v>
+        <v>2808796.296296296</v>
       </c>
       <c r="AA2" t="n">
-        <v>9400000</v>
+        <v>74.1574074074074</v>
       </c>
       <c r="AB2" t="n">
-        <v>220</v>
+        <v>23.3831608005521</v>
       </c>
       <c r="AC2" t="n">
-        <v>25.73944805194805</v>
+        <v>184.4467908902692</v>
       </c>
       <c r="AD2" t="n">
-        <v>186.8969155844156</v>
+        <v>1.671566597653554</v>
       </c>
       <c r="AE2" t="n">
+        <v>77.41476880607316</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>22878360.93857833</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>83.22087646652864</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>25.71990740740741</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>185.9282407407407</v>
+      </c>
+      <c r="AJ2" t="n">
         <v>1</v>
       </c>
-      <c r="AF2" t="n">
-        <v>72.80357142857143</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>4238555.194805195</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>75.16071428571429</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>25.25753968253968</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>185.8295454545455</v>
-      </c>
       <c r="AK2" t="n">
-        <v>1.39570707070707</v>
+        <v>69.71296296296296</v>
       </c>
       <c r="AL2" t="n">
-        <v>74.24444444444444</v>
+        <v>1911111.111111111</v>
       </c>
       <c r="AM2" t="n">
-        <v>6440422.077922078</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>77.37972582972581</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>26.9906462585034</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>183.5202664399093</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>69.23341836734694</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>1907610.544217687</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>71.0625</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>23.85461489220888</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>184.2628815002875</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>1.178488564484805</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>71.15496350454058</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>3961201.708953119</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>76.54832386702687</v>
-      </c>
-      <c r="BA2" t="inlineStr">
-        <is>
-          <t>0jdIgO6t</t>
-        </is>
-      </c>
-      <c r="BB2" t="inlineStr">
+        <v>72.01851851851852</v>
+      </c>
+      <c r="AN2" t="inlineStr">
         <is>
           <t>4fuCGs9P</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>2VSFgl3c</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>2T6mXfPa</t>
+          <t>UwsvBA74</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45536.52083333334</v>
+        <v>45549.4375</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">welz t 
+          <t xml:space="preserve">gerach t 
   ger </t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">allianz arena
-  munich </t>
+          <t xml:space="preserve">borussia park
+  monchengladbach </t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>75024</v>
+        <v>54042</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>nVp0wiqd</t>
+          <t>88HSzjDr</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>fiEQZ7C7</t>
+          <t>nJQmYp1B</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -939,131 +837,1125 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
+          <t>WG9pOTse</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>fiEQZ7C7</t>
+        </is>
+      </c>
+      <c r="P3" t="n">
+        <v>25.42424242424243</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>184.4545454545455</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.606060606060606</v>
+      </c>
+      <c r="S3" t="n">
+        <v>75.96969696969695</v>
+      </c>
+      <c r="T3" t="n">
+        <v>10090909.09090909</v>
+      </c>
+      <c r="U3" t="n">
+        <v>78.48484848484848</v>
+      </c>
+      <c r="V3" t="n">
+        <v>24.11111111111111</v>
+      </c>
+      <c r="W3" t="n">
+        <v>186.0944444444445</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1.263888888888889</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>74.23055555555555</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>9213333.333333332</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>78.03888888888889</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>24.31159420289855</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>184.3115942028986</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>1.282608695652174</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>73.18719806763285</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>6169444.444444444</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>77.70772946859904</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>23.19751602564103</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>183.9873130341881</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>1.221420940170941</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>72.00160256410257</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>7025360.576923077</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>78.17788461538461</v>
+      </c>
+      <c r="AN3" t="inlineStr">
+        <is>
+          <t>8f6APkLc</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>vZA6VYpf</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>vZqDdBhB</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>45549.4375</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">storks s 
+  ger </t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">europa park stadion
+  freiburg </t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>34700</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>fiEQZ7C7</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>8Y2m6ADe</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>59</v>
+      </c>
+      <c r="I4" t="n">
+        <v>591</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
           <t>nJQmYp1B</t>
         </is>
       </c>
-      <c r="O3" t="n">
-        <v>21.83333333333333</v>
-      </c>
-      <c r="P3" t="n">
-        <v>184.8333333333333</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="R3" t="n">
-        <v>6</v>
-      </c>
-      <c r="S3" t="n">
-        <v>430</v>
-      </c>
-      <c r="T3" t="n">
-        <v>98525000</v>
-      </c>
-      <c r="U3" t="n">
-        <v>489</v>
-      </c>
-      <c r="V3" t="n">
-        <v>24.77777777777778</v>
-      </c>
-      <c r="W3" t="n">
-        <v>186.3333333333333</v>
-      </c>
-      <c r="X3" t="n">
-        <v>1.222222222222222</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>9</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>648</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>47100000</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>686</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>26.95064935064935</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>184.8149350649351</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>2.993506493506493</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>81.74675324675324</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>39978051.94805194</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>84.61428571428571</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>27.09920634920635</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>183.5822510822511</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>1.702958152958153</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>75.38455988455988</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>8859199.134199133</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>77.23109668109667</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>24.78309956705795</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>182.3895437743088</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>2.29010860116878</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>78.49870507196707</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>29706104.23877095</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>83.38213768015353</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>25.00978435996824</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>184.517054087081</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>1.471632886564237</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>73.40237375270475</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>6103059.696990924</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>76.654855014088</v>
-      </c>
-      <c r="BA3" t="inlineStr">
-        <is>
-          <t>f3ddUIXs</t>
-        </is>
-      </c>
-      <c r="BB3" t="inlineStr">
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>0Ija0Ej9</t>
+        </is>
+      </c>
+      <c r="P4" t="n">
+        <v>25.62962962962963</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>183.7777777777777</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.725925925925926</v>
+      </c>
+      <c r="S4" t="n">
+        <v>75.03703703703704</v>
+      </c>
+      <c r="T4" t="n">
+        <v>9711111.11111111</v>
+      </c>
+      <c r="U4" t="n">
+        <v>77.61481481481481</v>
+      </c>
+      <c r="V4" t="n">
+        <v>26.94444444444444</v>
+      </c>
+      <c r="W4" t="n">
+        <v>183.2847222222223</v>
+      </c>
+      <c r="X4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>71.13194444444444</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>2277256.944444444</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>73.65972222222223</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>26.19185645272601</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>183.2022084195997</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>1.663216011042098</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>74.63216011042097</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>8164182.194616978</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>76.85576259489302</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>22.6218253968254</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>185.1853174603175</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>66.77222222222223</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>1678616.071428572</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>75.97718253968253</v>
+      </c>
+      <c r="AN4" t="inlineStr">
+        <is>
+          <t>K6A2elS9</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>M5BRZDsC</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>r7j4bXNb</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>45549.4375</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">jollenbeck m 
+  ger </t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">prezero arena
+  sinsheim </t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>30150</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>hQAtP9Sl</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>4jcj2zMd</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>59</v>
+      </c>
+      <c r="I5" t="n">
+        <v>591</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>nJQmYp1B</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>WG9pOTse</t>
+        </is>
+      </c>
+      <c r="P5" t="n">
+        <v>26.88888888888889</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>186.162962962963</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.792592592592593</v>
+      </c>
+      <c r="S5" t="n">
+        <v>74.44074074074074</v>
+      </c>
+      <c r="T5" t="n">
+        <v>8654814.814814815</v>
+      </c>
+      <c r="U5" t="n">
+        <v>77.79629629629629</v>
+      </c>
+      <c r="V5" t="n">
+        <v>25.00833333333334</v>
+      </c>
+      <c r="W5" t="n">
+        <v>184.0916666666667</v>
+      </c>
+      <c r="X5" t="n">
+        <v>2.141666666666667</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>81.93333333333334</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>40666666.66666666</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>85.20833333333333</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>24.5402212166918</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>185.5973688620747</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>1.496983408748114</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>72.36148818501759</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>7682355.036031507</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>77.99095022624435</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>24.25606909430439</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>181.3531746031746</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>1.832749766573296</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>79.08916900093371</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>35985244.51447245</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>83.04096638655462</v>
+      </c>
+      <c r="AN5" t="inlineStr">
+        <is>
+          <t>UgdQz0fK</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>pfoInmcq</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>WSMotj8U</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>45549.4375</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dankert b 
+  ger </t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">red bull arena
+  leipzig </t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>47069</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>KbS1suSm</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>pzHW4oaE</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>59</v>
+      </c>
+      <c r="I6" t="n">
+        <v>591</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>nP1i5US1</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="n">
+        <v>24.90909090909091</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>183.4545454545455</v>
+      </c>
+      <c r="R6" t="n">
+        <v>2.060606060606061</v>
+      </c>
+      <c r="S6" t="n">
+        <v>79.39393939393939</v>
+      </c>
+      <c r="T6" t="n">
+        <v>26139393.93939394</v>
+      </c>
+      <c r="U6" t="n">
+        <v>83.42424242424242</v>
+      </c>
+      <c r="V6" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="W6" t="n">
+        <v>186.3185185185185</v>
+      </c>
+      <c r="X6" t="n">
+        <v>1.622222222222222</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>75.44814814814815</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>7854444.444444444</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>77.9074074074074</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>24.31424501424501</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>183.9769230769231</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1.819373219373219</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>78.0039886039886</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>22290242.16524216</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>82.01908831908833</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>25.35648723257419</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>183.0776397515528</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>1.308212560386473</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>72.08961352657006</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>3969346.100759144</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>76.19827467218771</v>
+      </c>
+      <c r="AN6" t="inlineStr">
+        <is>
+          <t>hAcTWKKN</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>0jdIgO6t</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>tI0qkTpo</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>45549.4375</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">badstubner f 
+  ger </t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">volkswagen arena
+  wolfsburg </t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>28917</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>nwkTahLL</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>8vndvXTk</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>59</v>
+      </c>
+      <c r="I7" t="n">
+        <v>591</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>dfNCCCzS</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>EuakNmc1</t>
+        </is>
+      </c>
+      <c r="P7" t="n">
+        <v>24.03703703703704</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>184.8796296296296</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.638888888888889</v>
+      </c>
+      <c r="S7" t="n">
+        <v>75.66666666666667</v>
+      </c>
+      <c r="T7" t="n">
+        <v>11595370.37037037</v>
+      </c>
+      <c r="U7" t="n">
+        <v>80.10185185185185</v>
+      </c>
+      <c r="V7" t="n">
+        <v>24.00925925925926</v>
+      </c>
+      <c r="W7" t="n">
+        <v>184.5694444444444</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1.722222222222222</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>77.08796296296296</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>15050925.92592593</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>81.875</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>24.39027777777777</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>185.7611111111111</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1.355555555555555</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>73.90416666666667</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>9255972.222222222</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>78.85277777777777</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>20.48484848484848</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>185.4936204146731</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>1.31658692185008</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>70.79425837320574</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>7149920.255183414</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>81.18660287081339</v>
+      </c>
+      <c r="AN7" t="inlineStr">
+        <is>
+          <t>A15eUM4C</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>KUx4Q7x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>x4pn9lxH</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>45549.5625</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dingert c 
+  ger </t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">holstein stadion
+  kiel </t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>15034</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>63WsD2ei</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>nVp0wiqd</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>59</v>
+      </c>
+      <c r="I8" t="n">
+        <v>591</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>ILyJuN3g</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="n">
+        <v>25.51851851851852</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>185.8962962962963</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.107407407407407</v>
+      </c>
+      <c r="S8" t="n">
+        <v>68.53703703703702</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1636666.666666667</v>
+      </c>
+      <c r="U8" t="n">
+        <v>71.83333333333333</v>
+      </c>
+      <c r="V8" t="n">
+        <v>25.63939393939394</v>
+      </c>
+      <c r="W8" t="n">
+        <v>183.8484848484848</v>
+      </c>
+      <c r="X8" t="n">
+        <v>2.909090909090909</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>82.22727272727273</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>47330000</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>86.06060606060606</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>24.66761982570806</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>185.4690904139434</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1.038126361655774</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>67.18981481481482</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>1611114.515250545</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>71.83523965141613</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>26.6593137254902</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>184.3656862745098</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>3.033823529411765</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>81.69558823529411</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>41524515.93137255</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>84.00563725490196</v>
+      </c>
+      <c r="AN8" t="inlineStr">
+        <is>
+          <t>A15eUM4C</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>YZPE6Sx7</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>CnrLfkNN</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>45550.4375</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dankert b 
+  ger </t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">wwk arena
+  augsburg </t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>30660</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>fTVNku3I</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>ILyJuN3g</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>59</v>
+      </c>
+      <c r="I9" t="n">
+        <v>591</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>v9k3aY5F</t>
+        </is>
+      </c>
+      <c r="P9" t="n">
+        <v>24.875</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>185.0416666666667</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.125</v>
+      </c>
+      <c r="S9" t="n">
+        <v>73.54166666666667</v>
+      </c>
+      <c r="T9" t="n">
+        <v>4916666.666666667</v>
+      </c>
+      <c r="U9" t="n">
+        <v>76.875</v>
+      </c>
+      <c r="V9" t="n">
+        <v>25.62222222222222</v>
+      </c>
+      <c r="W9" t="n">
+        <v>185.6296296296296</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>70.07407407407408</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>2232592.592592593</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>73.65925925925926</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>23.84953703703704</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>182.7949735449736</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1.415674603174603</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>71.87830687830687</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>4441459.986772487</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>76.6114417989418</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>24.40459809654856</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>183.8359706455682</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>68.86337575966058</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>2069432.97786951</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>73.40110079119366</v>
+      </c>
+      <c r="AN9" t="inlineStr">
+        <is>
+          <t>4ljanukM</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>0jdIgO6t</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>8OhVCWxh</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>45550.52083333334</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hartmann r 
+  ger </t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mewa arena
+  mainz </t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>34000</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>EuakNmc1</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Ig1f1fy3</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>59</v>
+      </c>
+      <c r="I10" t="n">
+        <v>591</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>8vndvXTk</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>v9k3aY5F</t>
+        </is>
+      </c>
+      <c r="P10" t="n">
+        <v>26.91481481481481</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>183.3222222222222</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.588888888888889</v>
+      </c>
+      <c r="S10" t="n">
+        <v>74.56296296296297</v>
+      </c>
+      <c r="T10" t="n">
+        <v>6157407.407407408</v>
+      </c>
+      <c r="U10" t="n">
+        <v>76.8888888888889</v>
+      </c>
+      <c r="V10" t="n">
+        <v>25.8030303030303</v>
+      </c>
+      <c r="W10" t="n">
+        <v>183.9151515151515</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1.187878787878788</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>73.58181818181818</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>5393939.393939394</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>76.77272727272727</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>24.80185185185185</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>184.1814814814815</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.394444444444444</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>71.03518518518518</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>3306111.111111111</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>77.16666666666667</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>24.44117647058824</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>184.9607843137255</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>1.190196078431373</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>70.15098039215687</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>3219215.68627451</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>76.71764705882354</v>
+      </c>
+      <c r="AN10" t="inlineStr">
         <is>
           <t>GzfvcwRj</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>IkCftsQm</t>
         </is>
       </c>
     </row>

--- a/data/germany/p6_deployment/data_preparation/df_filled.xlsx
+++ b/data/germany/p6_deployment/data_preparation/df_filled.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO10"/>
+  <dimension ref="A1:AO19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -697,22 +697,22 @@
       </c>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="n">
-        <v>25.16666666666667</v>
+        <v>25.78787878787879</v>
       </c>
       <c r="Q2" t="n">
-        <v>186.1666666666667</v>
+        <v>185.6363636363636</v>
       </c>
       <c r="R2" t="n">
-        <v>2.5</v>
+        <v>2.454545454545455</v>
       </c>
       <c r="S2" t="n">
-        <v>81.13333333333334</v>
+        <v>81.03030303030305</v>
       </c>
       <c r="T2" t="n">
-        <v>34916666.66666666</v>
+        <v>33242424.24242424</v>
       </c>
       <c r="U2" t="n">
-        <v>83.86666666666666</v>
+        <v>83.51515151515152</v>
       </c>
       <c r="V2" t="n">
         <v>26.20833333333333</v>
@@ -733,22 +733,22 @@
         <v>74.1574074074074</v>
       </c>
       <c r="AB2" t="n">
-        <v>23.3831608005521</v>
+        <v>23.24444444444445</v>
       </c>
       <c r="AC2" t="n">
-        <v>184.4467908902692</v>
+        <v>182.9472222222222</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.671566597653554</v>
+        <v>1.636111111111111</v>
       </c>
       <c r="AE2" t="n">
-        <v>77.41476880607316</v>
+        <v>77.47222222222221</v>
       </c>
       <c r="AF2" t="n">
-        <v>22878360.93857833</v>
+        <v>22828611.11111111</v>
       </c>
       <c r="AG2" t="n">
-        <v>83.22087646652864</v>
+        <v>83.25277777777778</v>
       </c>
       <c r="AH2" t="n">
         <v>25.71990740740741</v>
@@ -849,7 +849,7 @@
         <v>25.42424242424243</v>
       </c>
       <c r="Q3" t="n">
-        <v>184.4545454545455</v>
+        <v>184.1818181818182</v>
       </c>
       <c r="R3" t="n">
         <v>1.606060606060606</v>
@@ -864,28 +864,28 @@
         <v>78.48484848484848</v>
       </c>
       <c r="V3" t="n">
-        <v>24.11111111111111</v>
+        <v>24.03333333333333</v>
       </c>
       <c r="W3" t="n">
-        <v>186.0944444444445</v>
+        <v>185.8583333333333</v>
       </c>
       <c r="X3" t="n">
-        <v>1.263888888888889</v>
+        <v>1.255555555555556</v>
       </c>
       <c r="Y3" t="n">
-        <v>74.23055555555555</v>
+        <v>74.25833333333333</v>
       </c>
       <c r="Z3" t="n">
-        <v>9213333.333333332</v>
+        <v>9248611.11111111</v>
       </c>
       <c r="AA3" t="n">
-        <v>78.03888888888889</v>
+        <v>78.16388888888889</v>
       </c>
       <c r="AB3" t="n">
         <v>24.31159420289855</v>
       </c>
       <c r="AC3" t="n">
-        <v>184.3115942028986</v>
+        <v>183.713768115942</v>
       </c>
       <c r="AD3" t="n">
         <v>1.282608695652174</v>
@@ -900,22 +900,22 @@
         <v>77.70772946859904</v>
       </c>
       <c r="AH3" t="n">
-        <v>23.19751602564103</v>
+        <v>22.86119711042311</v>
       </c>
       <c r="AI3" t="n">
-        <v>183.9873130341881</v>
+        <v>183.3329647648533</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1.221420940170941</v>
+        <v>1.170389208314905</v>
       </c>
       <c r="AK3" t="n">
-        <v>72.00160256410257</v>
+        <v>72.10437859354268</v>
       </c>
       <c r="AL3" t="n">
-        <v>7025360.576923077</v>
+        <v>7074034.350582338</v>
       </c>
       <c r="AM3" t="n">
-        <v>78.17788461538461</v>
+        <v>78.65118679050566</v>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
@@ -1013,22 +1013,22 @@
         <v>77.61481481481481</v>
       </c>
       <c r="V4" t="n">
-        <v>26.94444444444444</v>
+        <v>27.18148148148148</v>
       </c>
       <c r="W4" t="n">
-        <v>183.2847222222223</v>
+        <v>185.1414141414141</v>
       </c>
       <c r="X4" t="n">
         <v>1</v>
       </c>
       <c r="Y4" t="n">
-        <v>71.13194444444444</v>
+        <v>71.72121212121212</v>
       </c>
       <c r="Z4" t="n">
-        <v>2277256.944444444</v>
+        <v>2688308.080808081</v>
       </c>
       <c r="AA4" t="n">
-        <v>73.65972222222223</v>
+        <v>73.94242424242424</v>
       </c>
       <c r="AB4" t="n">
         <v>26.19185645272601</v>
@@ -1049,22 +1049,22 @@
         <v>76.85576259489302</v>
       </c>
       <c r="AH4" t="n">
-        <v>22.6218253968254</v>
+        <v>22.56379585326954</v>
       </c>
       <c r="AI4" t="n">
-        <v>185.1853174603175</v>
+        <v>183.5039872408294</v>
       </c>
       <c r="AJ4" t="n">
         <v>1</v>
       </c>
       <c r="AK4" t="n">
-        <v>66.77222222222223</v>
+        <v>68.09808612440192</v>
       </c>
       <c r="AL4" t="n">
-        <v>1678616.071428572</v>
+        <v>2329984.051036683</v>
       </c>
       <c r="AM4" t="n">
-        <v>75.97718253968253</v>
+        <v>76.51435406698563</v>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
@@ -1144,76 +1144,76 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>26.88888888888889</v>
+        <v>26.8</v>
       </c>
       <c r="Q5" t="n">
-        <v>186.162962962963</v>
+        <v>186.3333333333333</v>
       </c>
       <c r="R5" t="n">
-        <v>1.792592592592593</v>
+        <v>1.766666666666667</v>
       </c>
       <c r="S5" t="n">
-        <v>74.44074074074074</v>
+        <v>74.43333333333332</v>
       </c>
       <c r="T5" t="n">
-        <v>8654814.814814815</v>
+        <v>8531666.666666666</v>
       </c>
       <c r="U5" t="n">
-        <v>77.79629629629629</v>
+        <v>77.73333333333333</v>
       </c>
       <c r="V5" t="n">
-        <v>25.00833333333334</v>
+        <v>24.78560606060606</v>
       </c>
       <c r="W5" t="n">
-        <v>184.0916666666667</v>
+        <v>183.6214646464646</v>
       </c>
       <c r="X5" t="n">
-        <v>2.141666666666667</v>
+        <v>1.996212121212121</v>
       </c>
       <c r="Y5" t="n">
-        <v>81.93333333333334</v>
+        <v>80.4760101010101</v>
       </c>
       <c r="Z5" t="n">
-        <v>40666666.66666666</v>
+        <v>35146590.90909091</v>
       </c>
       <c r="AA5" t="n">
-        <v>85.20833333333333</v>
+        <v>83.98712121212122</v>
       </c>
       <c r="AB5" t="n">
-        <v>24.5402212166918</v>
+        <v>24.3848428260193</v>
       </c>
       <c r="AC5" t="n">
-        <v>185.5973688620747</v>
+        <v>185.1204481792717</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.496983408748114</v>
+        <v>1.427170868347339</v>
       </c>
       <c r="AE5" t="n">
-        <v>72.36148818501759</v>
+        <v>72.4347961406785</v>
       </c>
       <c r="AF5" t="n">
-        <v>7682355.036031507</v>
+        <v>7185858.232181762</v>
       </c>
       <c r="AG5" t="n">
-        <v>77.99095022624435</v>
+        <v>77.72346716464364</v>
       </c>
       <c r="AH5" t="n">
-        <v>24.25606909430439</v>
+        <v>24.25416666666667</v>
       </c>
       <c r="AI5" t="n">
-        <v>181.3531746031746</v>
+        <v>181.029797979798</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1.832749766573296</v>
+        <v>1.881660353535354</v>
       </c>
       <c r="AK5" t="n">
-        <v>79.08916900093371</v>
+        <v>79.15773358585858</v>
       </c>
       <c r="AL5" t="n">
-        <v>35985244.51447245</v>
+        <v>35850836.48989899</v>
       </c>
       <c r="AM5" t="n">
-        <v>83.04096638655462</v>
+        <v>82.9270202020202</v>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
@@ -1292,16 +1292,16 @@
         <v>24.90909090909091</v>
       </c>
       <c r="Q6" t="n">
-        <v>183.4545454545455</v>
+        <v>182.4545454545455</v>
       </c>
       <c r="R6" t="n">
         <v>2.060606060606061</v>
       </c>
       <c r="S6" t="n">
-        <v>79.39393939393939</v>
+        <v>79.33333333333333</v>
       </c>
       <c r="T6" t="n">
-        <v>26139393.93939394</v>
+        <v>25866666.66666667</v>
       </c>
       <c r="U6" t="n">
         <v>83.42424242424242</v>
@@ -1325,22 +1325,22 @@
         <v>77.9074074074074</v>
       </c>
       <c r="AB6" t="n">
-        <v>24.31424501424501</v>
+        <v>24.27412280701755</v>
       </c>
       <c r="AC6" t="n">
-        <v>183.9769230769231</v>
+        <v>183.6853070175439</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.819373219373219</v>
+        <v>1.894736842105263</v>
       </c>
       <c r="AE6" t="n">
-        <v>78.0039886039886</v>
+        <v>78.06907894736842</v>
       </c>
       <c r="AF6" t="n">
-        <v>22290242.16524216</v>
+        <v>21713514.25438596</v>
       </c>
       <c r="AG6" t="n">
-        <v>82.01908831908833</v>
+        <v>82.07894736842105</v>
       </c>
       <c r="AH6" t="n">
         <v>25.35648723257419</v>
@@ -1447,31 +1447,31 @@
         <v>1.638888888888889</v>
       </c>
       <c r="S7" t="n">
-        <v>75.66666666666667</v>
+        <v>75.78703703703704</v>
       </c>
       <c r="T7" t="n">
-        <v>11595370.37037037</v>
+        <v>12317592.59259259</v>
       </c>
       <c r="U7" t="n">
-        <v>80.10185185185185</v>
+        <v>80.3425925925926</v>
       </c>
       <c r="V7" t="n">
-        <v>24.00925925925926</v>
+        <v>24.75757575757576</v>
       </c>
       <c r="W7" t="n">
-        <v>184.5694444444444</v>
+        <v>185.2121212121212</v>
       </c>
       <c r="X7" t="n">
-        <v>1.722222222222222</v>
+        <v>1.727272727272727</v>
       </c>
       <c r="Y7" t="n">
-        <v>77.08796296296296</v>
+        <v>77.2121212121212</v>
       </c>
       <c r="Z7" t="n">
-        <v>15050925.92592593</v>
+        <v>13818181.81818182</v>
       </c>
       <c r="AA7" t="n">
-        <v>81.875</v>
+        <v>81.3030303030303</v>
       </c>
       <c r="AB7" t="n">
         <v>24.39027777777777</v>
@@ -1483,31 +1483,31 @@
         <v>1.355555555555555</v>
       </c>
       <c r="AE7" t="n">
-        <v>73.90416666666667</v>
+        <v>73.89722222222223</v>
       </c>
       <c r="AF7" t="n">
-        <v>9255972.222222222</v>
+        <v>9444305.555555556</v>
       </c>
       <c r="AG7" t="n">
-        <v>78.85277777777777</v>
+        <v>78.88888888888887</v>
       </c>
       <c r="AH7" t="n">
-        <v>20.48484848484848</v>
+        <v>20.52344497607655</v>
       </c>
       <c r="AI7" t="n">
-        <v>185.4936204146731</v>
+        <v>185.4909888357257</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1.31658692185008</v>
+        <v>1.311323763955343</v>
       </c>
       <c r="AK7" t="n">
-        <v>70.79425837320574</v>
+        <v>70.45542264752793</v>
       </c>
       <c r="AL7" t="n">
-        <v>7149920.255183414</v>
+        <v>6239090.909090909</v>
       </c>
       <c r="AM7" t="n">
-        <v>81.18660287081339</v>
+        <v>80.87830940988836</v>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
@@ -1601,22 +1601,22 @@
         <v>71.83333333333333</v>
       </c>
       <c r="V8" t="n">
-        <v>25.63939393939394</v>
+        <v>25.36363636363636</v>
       </c>
       <c r="W8" t="n">
-        <v>183.8484848484848</v>
+        <v>183.5757575757576</v>
       </c>
       <c r="X8" t="n">
-        <v>2.909090909090909</v>
+        <v>2.787878787878788</v>
       </c>
       <c r="Y8" t="n">
-        <v>82.22727272727273</v>
+        <v>82.06060606060606</v>
       </c>
       <c r="Z8" t="n">
-        <v>47330000</v>
+        <v>47048484.84848485</v>
       </c>
       <c r="AA8" t="n">
-        <v>86.06060606060606</v>
+        <v>86.15151515151517</v>
       </c>
       <c r="AB8" t="n">
         <v>24.66761982570806</v>
@@ -1637,22 +1637,22 @@
         <v>71.83523965141613</v>
       </c>
       <c r="AH8" t="n">
-        <v>26.6593137254902</v>
+        <v>26.33333333333333</v>
       </c>
       <c r="AI8" t="n">
-        <v>184.3656862745098</v>
+        <v>184.4408212560386</v>
       </c>
       <c r="AJ8" t="n">
-        <v>3.033823529411765</v>
+        <v>2.764895330112721</v>
       </c>
       <c r="AK8" t="n">
-        <v>81.69558823529411</v>
+        <v>81.68880837359099</v>
       </c>
       <c r="AL8" t="n">
-        <v>41524515.93137255</v>
+        <v>41216611.31239935</v>
       </c>
       <c r="AM8" t="n">
-        <v>84.00563725490196</v>
+        <v>84.25100644122385</v>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
@@ -1728,76 +1728,76 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>24.875</v>
+        <v>25.11111111111111</v>
       </c>
       <c r="Q9" t="n">
-        <v>185.0416666666667</v>
+        <v>184.2592592592592</v>
       </c>
       <c r="R9" t="n">
-        <v>1.125</v>
+        <v>1.111111111111111</v>
       </c>
       <c r="S9" t="n">
-        <v>73.54166666666667</v>
+        <v>73.37037037037037</v>
       </c>
       <c r="T9" t="n">
-        <v>4916666.666666667</v>
+        <v>4625925.925925926</v>
       </c>
       <c r="U9" t="n">
-        <v>76.875</v>
+        <v>76.33333333333333</v>
       </c>
       <c r="V9" t="n">
-        <v>25.62222222222222</v>
+        <v>25.56363636363637</v>
       </c>
       <c r="W9" t="n">
-        <v>185.6296296296296</v>
+        <v>185.8515151515151</v>
       </c>
       <c r="X9" t="n">
         <v>1</v>
       </c>
       <c r="Y9" t="n">
-        <v>70.07407407407408</v>
+        <v>70.34848484848483</v>
       </c>
       <c r="Z9" t="n">
-        <v>2232592.592592593</v>
+        <v>2407878.787878788</v>
       </c>
       <c r="AA9" t="n">
-        <v>73.65925925925926</v>
+        <v>73.87878787878788</v>
       </c>
       <c r="AB9" t="n">
-        <v>23.84953703703704</v>
+        <v>24.31269841269841</v>
       </c>
       <c r="AC9" t="n">
-        <v>182.7949735449736</v>
+        <v>183.3809523809524</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.415674603174603</v>
+        <v>1.468253968253968</v>
       </c>
       <c r="AE9" t="n">
-        <v>71.87830687830687</v>
+        <v>72.09047619047618</v>
       </c>
       <c r="AF9" t="n">
-        <v>4441459.986772487</v>
+        <v>4394067.46031746</v>
       </c>
       <c r="AG9" t="n">
-        <v>76.6114417989418</v>
+        <v>76.28968253968254</v>
       </c>
       <c r="AH9" t="n">
-        <v>24.40459809654856</v>
+        <v>24.43703703703704</v>
       </c>
       <c r="AI9" t="n">
-        <v>183.8359706455682</v>
+        <v>184.1109161793372</v>
       </c>
       <c r="AJ9" t="n">
         <v>1</v>
       </c>
       <c r="AK9" t="n">
-        <v>68.86337575966058</v>
+        <v>69.08089668615985</v>
       </c>
       <c r="AL9" t="n">
-        <v>2069432.97786951</v>
+        <v>2176196.393762183</v>
       </c>
       <c r="AM9" t="n">
-        <v>73.40110079119366</v>
+        <v>73.53752436647173</v>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
@@ -1880,7 +1880,7 @@
         <v>26.91481481481481</v>
       </c>
       <c r="Q10" t="n">
-        <v>183.3222222222222</v>
+        <v>183.425925925926</v>
       </c>
       <c r="R10" t="n">
         <v>1.588888888888889</v>
@@ -1898,7 +1898,7 @@
         <v>25.8030303030303</v>
       </c>
       <c r="W10" t="n">
-        <v>183.9151515151515</v>
+        <v>183.6727272727273</v>
       </c>
       <c r="X10" t="n">
         <v>1.187878787878788</v>
@@ -1916,7 +1916,7 @@
         <v>24.80185185185185</v>
       </c>
       <c r="AC10" t="n">
-        <v>184.1814814814815</v>
+        <v>184.2833333333333</v>
       </c>
       <c r="AD10" t="n">
         <v>1.394444444444444</v>
@@ -1934,19 +1934,19 @@
         <v>24.44117647058824</v>
       </c>
       <c r="AI10" t="n">
-        <v>184.9607843137255</v>
+        <v>184.8882352941176</v>
       </c>
       <c r="AJ10" t="n">
         <v>1.190196078431373</v>
       </c>
       <c r="AK10" t="n">
-        <v>70.15098039215687</v>
+        <v>70.11764705882354</v>
       </c>
       <c r="AL10" t="n">
-        <v>3219215.68627451</v>
+        <v>3224901.960784314</v>
       </c>
       <c r="AM10" t="n">
-        <v>76.71764705882354</v>
+        <v>76.80784313725489</v>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
@@ -1956,6 +1956,1331 @@
       <c r="AO10" t="inlineStr">
         <is>
           <t>IkCftsQm</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>dCL13J5e</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>45555.64583333334</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gerach t 
+  ger </t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">wwk arena
+  augsburg </t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>30660</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>fTVNku3I</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>EuakNmc1</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>59</v>
+      </c>
+      <c r="I11" t="n">
+        <v>591</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>8vndvXTk</t>
+        </is>
+      </c>
+      <c r="P11" t="n">
+        <v>25.11111111111111</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>184.2592592592592</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.111111111111111</v>
+      </c>
+      <c r="S11" t="n">
+        <v>73.37037037037037</v>
+      </c>
+      <c r="T11" t="n">
+        <v>4625925.925925926</v>
+      </c>
+      <c r="U11" t="n">
+        <v>76.33333333333333</v>
+      </c>
+      <c r="V11" t="n">
+        <v>26.91481481481481</v>
+      </c>
+      <c r="W11" t="n">
+        <v>183.425925925926</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1.588888888888889</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>74.56296296296297</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>6157407.407407408</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>76.8888888888889</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>24.31269841269841</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>183.3809523809524</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.468253968253968</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>72.09047619047618</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>4394067.46031746</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>76.28968253968254</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>24.80185185185185</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>184.2833333333333</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>1.394444444444444</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>71.03518518518518</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>3306111.111111111</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>77.16666666666667</v>
+      </c>
+      <c r="AN11" t="inlineStr">
+        <is>
+          <t>4ljanukM</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>vZA6VYpf</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>pY1dP0SE</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>45556.4375</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">exner f 
+  ger </t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vonovia ruhrstadion
+  bochum </t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>26000</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>8Y2m6ADe</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>63WsD2ei</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>59</v>
+      </c>
+      <c r="I12" t="n">
+        <v>591</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>0Ija0Ej9</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>ILyJuN3g</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>27.18148148148148</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>185.1414141414141</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1</v>
+      </c>
+      <c r="S12" t="n">
+        <v>71.72121212121212</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2688308.080808081</v>
+      </c>
+      <c r="U12" t="n">
+        <v>73.94242424242424</v>
+      </c>
+      <c r="V12" t="n">
+        <v>25.51851851851852</v>
+      </c>
+      <c r="W12" t="n">
+        <v>185.8962962962963</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1.107407407407407</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>68.53703703703702</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>1636666.666666667</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>71.83333333333333</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>22.56379585326954</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>183.5039872408294</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>68.09808612440192</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>2329984.051036683</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>76.51435406698563</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>24.66761982570806</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>185.4690904139434</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>1.038126361655774</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>67.18981481481482</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>1611114.515250545</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>71.83523965141613</v>
+      </c>
+      <c r="AN12" t="inlineStr">
+        <is>
+          <t>8f6APkLc</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>f3ddUIXs</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>QNoNA1DL</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>45556.4375</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dingert c 
+  ger </t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">voith arena
+  heidenheim </t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>15000</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>KWixEVWi</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>fiEQZ7C7</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>59</v>
+      </c>
+      <c r="I13" t="n">
+        <v>591</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>nJQmYp1B</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
+        <v>26.20833333333333</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>188.2731481481482</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1</v>
+      </c>
+      <c r="S13" t="n">
+        <v>72.08333333333333</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2808796.296296296</v>
+      </c>
+      <c r="U13" t="n">
+        <v>74.1574074074074</v>
+      </c>
+      <c r="V13" t="n">
+        <v>25.62962962962963</v>
+      </c>
+      <c r="W13" t="n">
+        <v>183.7777777777777</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1.725925925925926</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>75.03703703703704</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>9711111.11111111</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>77.61481481481481</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>25.71990740740741</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>185.9282407407407</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>69.71296296296296</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>1911111.111111111</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>72.01851851851852</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>26.19185645272601</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>183.2022084195997</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>1.663216011042098</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>74.63216011042097</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>8164182.194616978</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>76.85576259489302</v>
+      </c>
+      <c r="AN13" t="inlineStr">
+        <is>
+          <t>4ljanukM</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>YZPE6Sx7</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>hvFA1cz8</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>45556.4375</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">badstubner f 
+  ger </t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadion an der alten forsterei
+  berlin </t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>22012</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>pzHW4oaE</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>hQAtP9Sl</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>59</v>
+      </c>
+      <c r="I14" t="n">
+        <v>591</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>nJQmYp1B</t>
+        </is>
+      </c>
+      <c r="P14" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>186.3185185185185</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.622222222222222</v>
+      </c>
+      <c r="S14" t="n">
+        <v>75.44814814814815</v>
+      </c>
+      <c r="T14" t="n">
+        <v>7854444.444444444</v>
+      </c>
+      <c r="U14" t="n">
+        <v>77.9074074074074</v>
+      </c>
+      <c r="V14" t="n">
+        <v>26.8</v>
+      </c>
+      <c r="W14" t="n">
+        <v>186.3333333333333</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1.766666666666667</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>74.43333333333332</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>8531666.666666666</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>77.73333333333333</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>25.35648723257419</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>183.0776397515528</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1.308212560386473</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>72.08961352657006</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>3969346.100759144</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>76.19827467218771</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>24.3848428260193</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>185.1204481792717</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>1.427170868347339</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>72.4347961406785</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>7185858.232181762</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>77.72346716464364</v>
+      </c>
+      <c r="AN14" t="inlineStr">
+        <is>
+          <t>hpYJ6izc</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>KUx4Q7x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>AeNg5uyq</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>45556.4375</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dingert c 
+  ger </t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">weserstadion
+  bremen </t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>42100</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Ig1f1fy3</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>nVp0wiqd</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>59</v>
+      </c>
+      <c r="I15" t="n">
+        <v>591</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>v9k3aY5F</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="n">
+        <v>25.8030303030303</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>183.6727272727273</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.187878787878788</v>
+      </c>
+      <c r="S15" t="n">
+        <v>73.58181818181818</v>
+      </c>
+      <c r="T15" t="n">
+        <v>5393939.393939394</v>
+      </c>
+      <c r="U15" t="n">
+        <v>76.77272727272727</v>
+      </c>
+      <c r="V15" t="n">
+        <v>25.36363636363636</v>
+      </c>
+      <c r="W15" t="n">
+        <v>183.5757575757576</v>
+      </c>
+      <c r="X15" t="n">
+        <v>2.787878787878788</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>82.06060606060606</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>47048484.84848485</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>86.15151515151517</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>24.44117647058824</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>184.8882352941176</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1.190196078431373</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>70.11764705882354</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>3224901.960784314</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>76.80784313725489</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>26.33333333333333</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>184.4408212560386</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>2.764895330112721</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>81.68880837359099</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>41216611.31239935</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>84.25100644122385</v>
+      </c>
+      <c r="AN15" t="inlineStr">
+        <is>
+          <t>4fuCGs9P</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>YZPE6Sx7</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>IcrFCNr9</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>45556.5625</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">storks s 
+  ger </t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">deutsche bank park
+  frankfurt </t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>58000</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>8vndvXTk</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>88HSzjDr</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>59</v>
+      </c>
+      <c r="I16" t="n">
+        <v>591</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>EuakNmc1</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>WG9pOTse</t>
+        </is>
+      </c>
+      <c r="P16" t="n">
+        <v>24.75757575757576</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>185.2121212121212</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.727272727272727</v>
+      </c>
+      <c r="S16" t="n">
+        <v>77.2121212121212</v>
+      </c>
+      <c r="T16" t="n">
+        <v>13818181.81818182</v>
+      </c>
+      <c r="U16" t="n">
+        <v>81.3030303030303</v>
+      </c>
+      <c r="V16" t="n">
+        <v>25.42424242424243</v>
+      </c>
+      <c r="W16" t="n">
+        <v>184.1818181818182</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1.606060606060606</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>75.96969696969695</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>10090909.09090909</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>78.48484848484848</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>20.52344497607655</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>185.4909888357257</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>1.311323763955343</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>70.45542264752793</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>6239090.909090909</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>80.87830940988836</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>24.31159420289855</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>183.713768115942</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>1.282608695652174</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>73.18719806763285</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>6169444.444444444</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>77.70772946859904</v>
+      </c>
+      <c r="AN16" t="inlineStr">
+        <is>
+          <t>UgdQz0fK</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>M5BRZDsC</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>Uy2KjtMk</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>45557.4375</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">exner f 
+  ger </t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bayarena
+  leverkusen </t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>30210</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>4jcj2zMd</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>nwkTahLL</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>59</v>
+      </c>
+      <c r="I17" t="n">
+        <v>591</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>WG9pOTse</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>dfNCCCzS</t>
+        </is>
+      </c>
+      <c r="P17" t="n">
+        <v>24.78560606060606</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>183.6214646464646</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.996212121212121</v>
+      </c>
+      <c r="S17" t="n">
+        <v>80.4760101010101</v>
+      </c>
+      <c r="T17" t="n">
+        <v>35146590.90909091</v>
+      </c>
+      <c r="U17" t="n">
+        <v>83.98712121212122</v>
+      </c>
+      <c r="V17" t="n">
+        <v>24.03703703703704</v>
+      </c>
+      <c r="W17" t="n">
+        <v>184.8796296296296</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1.638888888888889</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>75.78703703703704</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>12317592.59259259</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>80.3425925925926</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>24.25416666666667</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>181.029797979798</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1.881660353535354</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>79.15773358585858</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>35850836.48989899</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>82.9270202020202</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>24.39027777777777</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>185.7611111111111</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>1.355555555555555</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>73.89722222222223</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>9444305.555555556</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>78.88888888888887</v>
+      </c>
+      <c r="AN17" t="inlineStr">
+        <is>
+          <t>hAcTWKKN</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>f3ddUIXs</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>2k0SlKj2</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>45557.52083333334</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hartmann r 
+  ger </t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mhparena
+  stuttgart </t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>60449</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>nJQmYp1B</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>nP1i5US1</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>59</v>
+      </c>
+      <c r="I18" t="n">
+        <v>591</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>fiEQZ7C7</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>0Ija0Ej9</t>
+        </is>
+      </c>
+      <c r="P18" t="n">
+        <v>24.03333333333333</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>185.8583333333333</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.255555555555556</v>
+      </c>
+      <c r="S18" t="n">
+        <v>74.25833333333333</v>
+      </c>
+      <c r="T18" t="n">
+        <v>9248611.11111111</v>
+      </c>
+      <c r="U18" t="n">
+        <v>78.16388888888889</v>
+      </c>
+      <c r="V18" t="n">
+        <v>25.78787878787879</v>
+      </c>
+      <c r="W18" t="n">
+        <v>185.6363636363636</v>
+      </c>
+      <c r="X18" t="n">
+        <v>2.454545454545455</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>81.03030303030305</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>33242424.24242424</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>83.51515151515152</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>22.86119711042311</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>183.3329647648533</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>1.170389208314905</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>72.10437859354268</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>7074034.350582338</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>78.65118679050566</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>23.24444444444445</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>182.9472222222222</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>1.636111111111111</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>77.47222222222221</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>22828611.11111111</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>83.25277777777778</v>
+      </c>
+      <c r="AN18" t="inlineStr">
+        <is>
+          <t>GzfvcwRj</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>IkCftsQm</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>dQ0zIIKl</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>45557.60416666666</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">jollenbeck m 
+  ger </t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">millerntor stadion
+  hamburg </t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>29546</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>ILyJuN3g</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>KbS1suSm</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>59</v>
+      </c>
+      <c r="I19" t="n">
+        <v>591</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>v9k3aY5F</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>nP1i5US1</t>
+        </is>
+      </c>
+      <c r="P19" t="n">
+        <v>25.56363636363637</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>185.8515151515151</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1</v>
+      </c>
+      <c r="S19" t="n">
+        <v>70.34848484848483</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2407878.787878788</v>
+      </c>
+      <c r="U19" t="n">
+        <v>73.87878787878788</v>
+      </c>
+      <c r="V19" t="n">
+        <v>24.90909090909091</v>
+      </c>
+      <c r="W19" t="n">
+        <v>182.4545454545455</v>
+      </c>
+      <c r="X19" t="n">
+        <v>2.060606060606061</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>79.33333333333333</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>25866666.66666667</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>83.42424242424242</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>24.43703703703704</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>184.1109161793372</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>69.08089668615985</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>2176196.393762183</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>73.53752436647173</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>24.27412280701755</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>183.6853070175439</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>1.894736842105263</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>78.06907894736842</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>21713514.25438596</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>82.07894736842105</v>
+      </c>
+      <c r="AN19" t="inlineStr">
+        <is>
+          <t>hpYJ6izc</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>pfoInmcq</t>
         </is>
       </c>
     </row>

--- a/data/germany/p6_deployment/data_preparation/df_filled.xlsx
+++ b/data/germany/p6_deployment/data_preparation/df_filled.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BC3"/>
+  <dimension ref="A1:AO19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -505,200 +505,130 @@
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>mean_age_player_miss_home</t>
+          <t>mean_age_player_start_home</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>mean_hei_player_miss_home</t>
+          <t>mean_hei_player_start_home</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>mean_int_rep_player_miss_home</t>
+          <t>mean_int_rep_player_start_home</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>n_player_miss_home</t>
+          <t>mean_rat_player_start_home</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>sum_rat_player_miss_home</t>
+          <t>mean_val_player_start_home</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>sum_val_player_miss_home</t>
+          <t>mean_pot_player_start_home</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>sum_pot_player_miss_home</t>
+          <t>mean_age_player_start_away</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>mean_age_player_miss_away</t>
+          <t>mean_hei_player_start_away</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>mean_hei_player_miss_away</t>
+          <t>mean_int_rep_player_start_away</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>mean_int_rep_player_miss_away</t>
+          <t>mean_rat_player_start_away</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>n_player_miss_away</t>
+          <t>mean_val_player_start_away</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>sum_rat_player_miss_away</t>
+          <t>mean_pot_player_start_away</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>sum_val_player_miss_away</t>
+          <t>mean_age_player_sub_home</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>sum_pot_player_miss_away</t>
+          <t>mean_hei_player_sub_home</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>mean_age_player_start_home</t>
+          <t>mean_int_rep_player_sub_home</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>mean_hei_player_start_home</t>
+          <t>mean_rat_player_sub_home</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>mean_int_rep_player_start_home</t>
+          <t>mean_val_player_sub_home</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>mean_rat_player_start_home</t>
+          <t>mean_pot_player_sub_home</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>mean_val_player_start_home</t>
+          <t>mean_age_player_sub_away</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>mean_pot_player_start_home</t>
+          <t>mean_hei_player_sub_away</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>mean_age_player_start_away</t>
+          <t>mean_int_rep_player_sub_away</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
-          <t>mean_hei_player_start_away</t>
+          <t>mean_rat_player_sub_away</t>
         </is>
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
-          <t>mean_int_rep_player_start_away</t>
+          <t>mean_val_player_sub_away</t>
         </is>
       </c>
       <c r="AM1" s="1" t="inlineStr">
         <is>
-          <t>mean_rat_player_start_away</t>
+          <t>mean_pot_player_sub_away</t>
         </is>
       </c>
       <c r="AN1" s="1" t="inlineStr">
         <is>
-          <t>mean_val_player_start_away</t>
+          <t>id_coach_home</t>
         </is>
       </c>
       <c r="AO1" s="1" t="inlineStr">
-        <is>
-          <t>mean_pot_player_start_away</t>
-        </is>
-      </c>
-      <c r="AP1" s="1" t="inlineStr">
-        <is>
-          <t>mean_age_player_sub_home</t>
-        </is>
-      </c>
-      <c r="AQ1" s="1" t="inlineStr">
-        <is>
-          <t>mean_hei_player_sub_home</t>
-        </is>
-      </c>
-      <c r="AR1" s="1" t="inlineStr">
-        <is>
-          <t>mean_int_rep_player_sub_home</t>
-        </is>
-      </c>
-      <c r="AS1" s="1" t="inlineStr">
-        <is>
-          <t>mean_rat_player_sub_home</t>
-        </is>
-      </c>
-      <c r="AT1" s="1" t="inlineStr">
-        <is>
-          <t>mean_val_player_sub_home</t>
-        </is>
-      </c>
-      <c r="AU1" s="1" t="inlineStr">
-        <is>
-          <t>mean_pot_player_sub_home</t>
-        </is>
-      </c>
-      <c r="AV1" s="1" t="inlineStr">
-        <is>
-          <t>mean_age_player_sub_away</t>
-        </is>
-      </c>
-      <c r="AW1" s="1" t="inlineStr">
-        <is>
-          <t>mean_hei_player_sub_away</t>
-        </is>
-      </c>
-      <c r="AX1" s="1" t="inlineStr">
-        <is>
-          <t>mean_int_rep_player_sub_away</t>
-        </is>
-      </c>
-      <c r="AY1" s="1" t="inlineStr">
-        <is>
-          <t>mean_rat_player_sub_away</t>
-        </is>
-      </c>
-      <c r="AZ1" s="1" t="inlineStr">
-        <is>
-          <t>mean_val_player_sub_away</t>
-        </is>
-      </c>
-      <c r="BA1" s="1" t="inlineStr">
-        <is>
-          <t>mean_pot_player_sub_away</t>
-        </is>
-      </c>
-      <c r="BB1" s="1" t="inlineStr">
-        <is>
-          <t>id_coach_home</t>
-        </is>
-      </c>
-      <c r="BC1" s="1" t="inlineStr">
         <is>
           <t>id_coach_away</t>
         </is>
@@ -707,15 +637,15 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>CnrLfkNN</t>
+          <t>dCL13J5e</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45550.4375</v>
+        <v>45555.64583333334</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">zwayer f 
+          <t xml:space="preserve">brand b 
   ger </t>
         </is>
       </c>
@@ -735,7 +665,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>ILyJuN3g</t>
+          <t>EuakNmc1</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -763,322 +693,2594 @@
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr">
         <is>
-          <t>v9k3aY5F</t>
+          <t>8vndvXTk</t>
         </is>
       </c>
       <c r="P2" t="n">
-        <v>25.66666666666667</v>
+        <v>25.11111111111111</v>
       </c>
       <c r="Q2" t="n">
-        <v>183</v>
+        <v>184.2592592592592</v>
       </c>
       <c r="R2" t="n">
-        <v>1</v>
+        <v>1.111111111111111</v>
       </c>
       <c r="S2" t="n">
-        <v>3</v>
+        <v>73.37037037037037</v>
       </c>
       <c r="T2" t="n">
-        <v>214</v>
+        <v>4625925.925925926</v>
       </c>
       <c r="U2" t="n">
-        <v>9400000</v>
+        <v>76.33333333333333</v>
       </c>
       <c r="V2" t="n">
-        <v>220</v>
+        <v>26.825</v>
       </c>
       <c r="W2" t="n">
-        <v>27.8</v>
+        <v>183.5694444444445</v>
       </c>
       <c r="X2" t="n">
-        <v>187</v>
+        <v>1.580555555555556</v>
       </c>
       <c r="Y2" t="n">
-        <v>1</v>
+        <v>74.61666666666667</v>
       </c>
       <c r="Z2" t="n">
-        <v>5</v>
+        <v>6240277.777777778</v>
       </c>
       <c r="AA2" t="n">
-        <v>339</v>
+        <v>76.97222222222223</v>
       </c>
       <c r="AB2" t="n">
-        <v>7075000</v>
+        <v>24.19505012531328</v>
       </c>
       <c r="AC2" t="n">
-        <v>352</v>
+        <v>183.5357142857143</v>
       </c>
       <c r="AD2" t="n">
-        <v>25.11111111111111</v>
+        <v>1.390664160401003</v>
       </c>
       <c r="AE2" t="n">
-        <v>184.2592592592592</v>
+        <v>72.14680451127819</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.111111111111111</v>
+        <v>4420550.595238095</v>
       </c>
       <c r="AG2" t="n">
-        <v>73.37037037037037</v>
+        <v>76.33568295739349</v>
       </c>
       <c r="AH2" t="n">
-        <v>4625925.925925926</v>
+        <v>25.0656746031746</v>
       </c>
       <c r="AI2" t="n">
-        <v>76.33333333333333</v>
+        <v>183.7363095238095</v>
       </c>
       <c r="AJ2" t="n">
-        <v>25.56363636363637</v>
+        <v>1.414880952380952</v>
       </c>
       <c r="AK2" t="n">
-        <v>185.8515151515151</v>
+        <v>71.22876984126984</v>
       </c>
       <c r="AL2" t="n">
-        <v>1</v>
+        <v>3332261.904761905</v>
       </c>
       <c r="AM2" t="n">
-        <v>70.34848484848483</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>2407878.787878788</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>73.87878787878788</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>24.31269841269841</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>183.3809523809524</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>1.468253968253968</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>72.09047619047618</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>4394067.46031746</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>76.28968253968254</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>24.43703703703704</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>184.1109161793372</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>69.08089668615985</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>2176196.393762183</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>73.53752436647173</v>
-      </c>
-      <c r="BB2" t="inlineStr">
-        <is>
-          <t>4ljanukM</t>
-        </is>
-      </c>
-      <c r="BC2" t="inlineStr">
-        <is>
-          <t>0jdIgO6t</t>
+        <v>76.875</v>
+      </c>
+      <c r="AN2" t="inlineStr">
+        <is>
+          <t>2VSFgl3c</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>4fuCGs9P</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>8OhVCWxh</t>
+          <t>pY1dP0SE</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45550.52083333334</v>
+        <v>45556.4375</v>
       </c>
       <c r="C3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">reichel t 
+  ger </t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vonovia ruhrstadion
+  bochum </t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>26000</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>8Y2m6ADe</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>63WsD2ei</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>59</v>
+      </c>
+      <c r="I3" t="n">
+        <v>591</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0Ija0Ej9</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>ILyJuN3g</t>
+        </is>
+      </c>
+      <c r="P3" t="n">
+        <v>26.71944444444444</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>184.3282828282828</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1</v>
+      </c>
+      <c r="S3" t="n">
+        <v>71.6520202020202</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2777342.171717172</v>
+      </c>
+      <c r="U3" t="n">
+        <v>73.98459595959596</v>
+      </c>
+      <c r="V3" t="n">
+        <v>25.70138888888889</v>
+      </c>
+      <c r="W3" t="n">
+        <v>185.9534722222222</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1.111805555555555</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>68.55902777777777</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>1632187.5</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>71.75</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>22.88875598086124</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>182.9234449760766</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>68.30083732057416</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>2304874.401913876</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>76.20394736842104</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>24.61008986928104</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>185.4768178104575</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>1.04421977124183</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>67.23611111111111</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>1611851.511437909</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>71.92330473856209</v>
+      </c>
+      <c r="AN3" t="inlineStr">
+        <is>
+          <t>YZPE6Sx7</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>K6A2elS9</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>QNoNA1DL</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>45556.4375</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">siebert d 
+  ger </t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">voith arena
+  heidenheim </t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>15000</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>KWixEVWi</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>fiEQZ7C7</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>59</v>
+      </c>
+      <c r="I4" t="n">
+        <v>591</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>nJQmYp1B</t>
+        </is>
+      </c>
+      <c r="P4" t="n">
+        <v>26.15625</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>188.3159722222223</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1</v>
+      </c>
+      <c r="S4" t="n">
+        <v>72.0625</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2803819.444444444</v>
+      </c>
+      <c r="U4" t="n">
+        <v>74.17361111111111</v>
+      </c>
+      <c r="V4" t="n">
+        <v>25.49722222222222</v>
+      </c>
+      <c r="W4" t="n">
+        <v>183.8333333333333</v>
+      </c>
+      <c r="X4" t="n">
+        <v>1.694444444444444</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>75.05277777777778</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>9760833.333333332</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>77.78611111111111</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>25.56770833333334</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>185.515625</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>1.041666666666667</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>69.89583333333333</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>2125347.222222222</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>72.23611111111111</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>26.01889233954451</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>183.7312017692452</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>1.656502917372483</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>74.72412008281574</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>8411773.009599097</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>77.18727649162432</v>
+      </c>
+      <c r="AN4" t="inlineStr">
+        <is>
+          <t>IkCftsQm</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>8f6APkLc</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>hvFA1cz8</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>45556.4375</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">schlager d 
+  ger </t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadion an der alten forsterei
+  berlin </t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>22012</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>pzHW4oaE</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>hQAtP9Sl</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>59</v>
+      </c>
+      <c r="I5" t="n">
+        <v>591</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>nJQmYp1B</t>
+        </is>
+      </c>
+      <c r="P5" t="n">
+        <v>26.45681818181819</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>186.2843434343434</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.557575757575758</v>
+      </c>
+      <c r="S5" t="n">
+        <v>75.1770202020202</v>
+      </c>
+      <c r="T5" t="n">
+        <v>7490833.333333333</v>
+      </c>
+      <c r="U5" t="n">
+        <v>77.79419191919192</v>
+      </c>
+      <c r="V5" t="n">
+        <v>26.925</v>
+      </c>
+      <c r="W5" t="n">
+        <v>186.175</v>
+      </c>
+      <c r="X5" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>74.59999999999999</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>8707500</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>77.85000000000001</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>24.90625431331953</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>182.8915631469979</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>1.272826086956522</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>71.65054347826087</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>3873537.353347136</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>76.31537267080745</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>23.74317757405993</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>184.6698815889992</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>1.354469060351413</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>71.64427892369069</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>6545359.58322723</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>78.16760037348273</v>
+      </c>
+      <c r="AN5" t="inlineStr">
+        <is>
+          <t>IXf9Q08n</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>hAcTWKKN</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>AeNg5uyq</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>45556.4375</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">reichel t 
+  ger </t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">weserstadion
+  bremen </t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>42100</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Ig1f1fy3</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>nVp0wiqd</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>59</v>
+      </c>
+      <c r="I6" t="n">
+        <v>591</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>v9k3aY5F</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="n">
+        <v>25.97727272727273</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>183.5545454545455</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.190909090909091</v>
+      </c>
+      <c r="S6" t="n">
+        <v>73.73636363636363</v>
+      </c>
+      <c r="T6" t="n">
+        <v>5445454.545454545</v>
+      </c>
+      <c r="U6" t="n">
+        <v>76.70454545454545</v>
+      </c>
+      <c r="V6" t="n">
+        <v>25.75</v>
+      </c>
+      <c r="W6" t="n">
+        <v>183.2954545454546</v>
+      </c>
+      <c r="X6" t="n">
+        <v>2.886363636363636</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>82.70454545454545</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>49365909.09090909</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>86.18181818181819</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>24.03921568627451</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>185.7356209150327</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1.156535947712419</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>70.01879084967321</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>3286732.026143791</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>77.10588235294117</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>25.9375</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>184.0076992753623</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>2.677838164251208</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>81.3395229468599</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>39823135.56763285</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>84.37575483091788</v>
+      </c>
+      <c r="AN6" t="inlineStr">
+        <is>
+          <t>vZA6VYpf</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>K6A2elS9</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>IcrFCNr9</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>45556.5625</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">brych f 
+  ger </t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">deutsche bank park
+  frankfurt </t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>58000</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>8vndvXTk</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>88HSzjDr</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>59</v>
+      </c>
+      <c r="I7" t="n">
+        <v>591</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>EuakNmc1</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>WG9pOTse</t>
+        </is>
+      </c>
+      <c r="P7" t="n">
+        <v>24.79545454545455</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>185.2045454545455</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.727272727272727</v>
+      </c>
+      <c r="S7" t="n">
+        <v>77.22727272727272</v>
+      </c>
+      <c r="T7" t="n">
+        <v>13852272.72727273</v>
+      </c>
+      <c r="U7" t="n">
+        <v>81.25</v>
+      </c>
+      <c r="V7" t="n">
+        <v>25.54545454545455</v>
+      </c>
+      <c r="W7" t="n">
+        <v>184.3409090909091</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1.613636363636363</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>76.02272727272727</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>10104545.45454545</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>78.34090909090909</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>20.78008373205742</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>185.8057416267943</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1.345992822966507</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>70.57906698564594</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>6430568.181818182</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>80.80873205741626</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>24.32744565217391</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>183.4832427536232</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>1.295289855072464</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>73.41123188405797</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>6483333.333333333</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>77.79121376811594</v>
+      </c>
+      <c r="AN7" t="inlineStr">
+        <is>
+          <t>f3ddUIXs</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>GzfvcwRj</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>Uy2KjtMk</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>45557.4375</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">osmers h 
+  ger </t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bayarena
+  leverkusen </t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>30210</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>4jcj2zMd</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>nwkTahLL</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>59</v>
+      </c>
+      <c r="I8" t="n">
+        <v>591</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>WG9pOTse</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>dfNCCCzS</t>
+        </is>
+      </c>
+      <c r="P8" t="n">
+        <v>24.93757575757576</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>183.8244444444445</v>
+      </c>
+      <c r="R8" t="n">
+        <v>2.033333333333333</v>
+      </c>
+      <c r="S8" t="n">
+        <v>80.70808080808081</v>
+      </c>
+      <c r="T8" t="n">
+        <v>35799090.90909091</v>
+      </c>
+      <c r="U8" t="n">
+        <v>84.04424242424243</v>
+      </c>
+      <c r="V8" t="n">
+        <v>24.02777777777778</v>
+      </c>
+      <c r="W8" t="n">
+        <v>184.8784722222222</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1.635416666666667</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>75.68402777777777</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>11806944.44444444</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>80.16319444444444</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>24.22151515151516</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>180.9783838383838</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1.868964646464647</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>79.17164141414142</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>34640669.19191919</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>82.95070707070707</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>24.48020833333333</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>185.6802083333333</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>1.329166666666667</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>74.09479166666668</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>9505104.166666668</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>78.83854166666666</v>
+      </c>
+      <c r="AN8" t="inlineStr">
+        <is>
+          <t>KUx4Q7x1</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>UgdQz0fK</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>2k0SlKj2</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>45557.52083333334</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">schroder r 
+  ger </t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mhparena
+  stuttgart </t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>60449</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>nJQmYp1B</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>nP1i5US1</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>59</v>
+      </c>
+      <c r="I9" t="n">
+        <v>591</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>fiEQZ7C7</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>0Ija0Ej9</t>
+        </is>
+      </c>
+      <c r="P9" t="n">
+        <v>23.9539393939394</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>185.9048484848485</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.277171717171717</v>
+      </c>
+      <c r="S9" t="n">
+        <v>74.27939393939394</v>
+      </c>
+      <c r="T9" t="n">
+        <v>9364343.434343433</v>
+      </c>
+      <c r="U9" t="n">
+        <v>78.27656565656565</v>
+      </c>
+      <c r="V9" t="n">
+        <v>25.79545454545455</v>
+      </c>
+      <c r="W9" t="n">
+        <v>185.75</v>
+      </c>
+      <c r="X9" t="n">
+        <v>2.386363636363637</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>81</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>33295454.54545455</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>83.38636363636364</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>22.81895768833849</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>183.8063718118826</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1.186311366651924</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>72.46350287483415</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>7430227.480465871</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>78.83094943240454</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>23.3463768115942</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>182.2430253623189</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>1.672735507246377</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>77.44112318840578</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>22463849.63768116</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>83.22219202898552</v>
+      </c>
+      <c r="AN9" t="inlineStr">
+        <is>
+          <t>M5BRZDsC</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>4ljanukM</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>dQ0zIIKl</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>45557.60416666666</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">jablonski s 
+  ger </t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">millerntor stadion
+  hamburg </t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>29546</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>ILyJuN3g</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>KbS1suSm</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>59</v>
+      </c>
+      <c r="I10" t="n">
+        <v>591</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>v9k3aY5F</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>nP1i5US1</t>
+        </is>
+      </c>
+      <c r="P10" t="n">
+        <v>25.58181818181818</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>185.8886363636364</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1</v>
+      </c>
+      <c r="S10" t="n">
+        <v>70.28409090909091</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2399090.909090909</v>
+      </c>
+      <c r="U10" t="n">
+        <v>73.86363636363636</v>
+      </c>
+      <c r="V10" t="n">
+        <v>24.95681818181818</v>
+      </c>
+      <c r="W10" t="n">
+        <v>182.3409090909091</v>
+      </c>
+      <c r="X10" t="n">
+        <v>2.070454545454545</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>79.40000000000001</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>25925000</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>83.34318181818182</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>24.67777777777778</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>184.0706871345029</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>69.18567251461988</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>2173709.795321637</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>73.40314327485379</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>23.98190789473685</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>184.092927631579</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>1.842105263157895</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>77.63075657894737</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>20460135.69078947</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>82.21710526315789</v>
+      </c>
+      <c r="AN10" t="inlineStr">
+        <is>
+          <t>2VSFgl3c</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>6PecvuWE</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>rsNyMnwK</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>45562.64583333334</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">siebert d 
+  ger </t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">signal iduna park
+  dortmund </t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>81365</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>nP1i5US1</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>8Y2m6ADe</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>59</v>
+      </c>
+      <c r="I11" t="n">
+        <v>591</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>0Ija0Ej9</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>0Ija0Ej9</t>
+        </is>
+      </c>
+      <c r="P11" t="n">
+        <v>25.79545454545455</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>185.75</v>
+      </c>
+      <c r="R11" t="n">
+        <v>2.386363636363637</v>
+      </c>
+      <c r="S11" t="n">
+        <v>81</v>
+      </c>
+      <c r="T11" t="n">
+        <v>33295454.54545455</v>
+      </c>
+      <c r="U11" t="n">
+        <v>83.38636363636364</v>
+      </c>
+      <c r="V11" t="n">
+        <v>26.71944444444444</v>
+      </c>
+      <c r="W11" t="n">
+        <v>184.3282828282828</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>71.6520202020202</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>2777342.171717172</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>73.98459595959596</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>23.3463768115942</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>182.2430253623189</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.672735507246377</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>77.44112318840578</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>22463849.63768116</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>83.22219202898552</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>22.88875598086124</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>182.9234449760766</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>68.30083732057416</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>2304874.401913876</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>76.20394736842104</v>
+      </c>
+      <c r="AN11" t="inlineStr">
+        <is>
+          <t>IkCftsQm</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>8f6APkLc</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>CIlrT3pm</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>45563.4375</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">jablonski s 
+  ger </t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">borussia park
+  monchengladbach </t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>54042</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>88HSzjDr</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>pzHW4oaE</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>59</v>
+      </c>
+      <c r="I12" t="n">
+        <v>591</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>WG9pOTse</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="n">
+        <v>25.54545454545455</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>184.3409090909091</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.613636363636363</v>
+      </c>
+      <c r="S12" t="n">
+        <v>76.02272727272727</v>
+      </c>
+      <c r="T12" t="n">
+        <v>10104545.45454545</v>
+      </c>
+      <c r="U12" t="n">
+        <v>78.34090909090909</v>
+      </c>
+      <c r="V12" t="n">
+        <v>26.45681818181819</v>
+      </c>
+      <c r="W12" t="n">
+        <v>186.2843434343434</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1.557575757575758</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>75.1770202020202</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>7490833.333333333</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>77.79419191919192</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>24.32744565217391</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>183.4832427536232</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1.295289855072464</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>73.41123188405797</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>6483333.333333333</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>77.79121376811594</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>24.90625431331953</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>182.8915631469979</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>1.272826086956522</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>71.65054347826087</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>3873537.353347136</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>76.31537267080745</v>
+      </c>
+      <c r="AN12" t="inlineStr">
+        <is>
+          <t>M5BRZDsC</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>6PecvuWE</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>6uSGCr06</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>45563.4375</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">zwayer f 
+  ger </t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">europa park stadion
+  freiburg </t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>34700</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>fiEQZ7C7</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>ILyJuN3g</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>59</v>
+      </c>
+      <c r="I13" t="n">
+        <v>591</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>nJQmYp1B</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>v9k3aY5F</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
+        <v>25.49722222222222</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>183.8333333333333</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.694444444444444</v>
+      </c>
+      <c r="S13" t="n">
+        <v>75.05277777777778</v>
+      </c>
+      <c r="T13" t="n">
+        <v>9760833.333333332</v>
+      </c>
+      <c r="U13" t="n">
+        <v>77.78611111111111</v>
+      </c>
+      <c r="V13" t="n">
+        <v>25.58181818181818</v>
+      </c>
+      <c r="W13" t="n">
+        <v>185.8886363636364</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>70.28409090909091</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>2399090.909090909</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>73.86363636363636</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>26.01889233954451</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>183.7312017692452</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1.656502917372483</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>74.72412008281574</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>8411773.009599097</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>77.18727649162432</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>24.67777777777778</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>184.0706871345029</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>69.18567251461988</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>2173709.795321637</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>73.40314327485379</v>
+      </c>
+      <c r="AN13" t="inlineStr">
+        <is>
+          <t>YZPE6Sx7</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>0jdIgO6t</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>f18BYPMP</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>45563.4375</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">schroder r 
+  ger </t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mewa arena
+  mainz </t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>34000</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>EuakNmc1</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>KWixEVWi</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>59</v>
+      </c>
+      <c r="I14" t="n">
+        <v>591</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>8vndvXTk</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="n">
+        <v>26.825</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>183.5694444444445</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.580555555555556</v>
+      </c>
+      <c r="S14" t="n">
+        <v>74.61666666666667</v>
+      </c>
+      <c r="T14" t="n">
+        <v>6240277.777777778</v>
+      </c>
+      <c r="U14" t="n">
+        <v>76.97222222222223</v>
+      </c>
+      <c r="V14" t="n">
+        <v>26.15625</v>
+      </c>
+      <c r="W14" t="n">
+        <v>188.3159722222223</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>72.0625</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>2803819.444444444</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>74.17361111111111</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>25.0656746031746</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>183.7363095238095</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1.414880952380952</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>71.22876984126984</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>3332261.904761905</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>76.875</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>25.56770833333334</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>185.515625</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>1.041666666666667</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>69.89583333333333</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>2125347.222222222</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>72.23611111111111</v>
+      </c>
+      <c r="AN14" t="inlineStr">
+        <is>
+          <t>vZA6VYpf</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>4ljanukM</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>Q5hiEzKD</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>45563.4375</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">zwayer f 
+  ger </t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">red bull arena
+  leipzig </t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>47069</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>KbS1suSm</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>fTVNku3I</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>59</v>
+      </c>
+      <c r="I15" t="n">
+        <v>591</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>nP1i5US1</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="n">
+        <v>24.95681818181818</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>182.3409090909091</v>
+      </c>
+      <c r="R15" t="n">
+        <v>2.070454545454545</v>
+      </c>
+      <c r="S15" t="n">
+        <v>79.40000000000001</v>
+      </c>
+      <c r="T15" t="n">
+        <v>25925000</v>
+      </c>
+      <c r="U15" t="n">
+        <v>83.34318181818182</v>
+      </c>
+      <c r="V15" t="n">
+        <v>25.11111111111111</v>
+      </c>
+      <c r="W15" t="n">
+        <v>184.2592592592592</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.111111111111111</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>73.37037037037037</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>4625925.925925926</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>76.33333333333333</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>23.98190789473685</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>184.092927631579</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1.842105263157895</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>77.63075657894737</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>20460135.69078947</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>82.21710526315789</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>24.19505012531328</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>183.5357142857143</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>1.390664160401003</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>72.14680451127819</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>4420550.595238095</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>76.33568295739349</v>
+      </c>
+      <c r="AN15" t="inlineStr">
+        <is>
+          <t>IXf9Q08n</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>0jdIgO6t</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>SfGPAMUI</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>45563.4375</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">brych f 
+  ger </t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">volkswagen arena
+  wolfsburg </t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>28917</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>nwkTahLL</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>nJQmYp1B</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>59</v>
+      </c>
+      <c r="I16" t="n">
+        <v>591</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>dfNCCCzS</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>fiEQZ7C7</t>
+        </is>
+      </c>
+      <c r="P16" t="n">
+        <v>24.02777777777778</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>184.8784722222222</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.635416666666667</v>
+      </c>
+      <c r="S16" t="n">
+        <v>75.68402777777777</v>
+      </c>
+      <c r="T16" t="n">
+        <v>11806944.44444444</v>
+      </c>
+      <c r="U16" t="n">
+        <v>80.16319444444444</v>
+      </c>
+      <c r="V16" t="n">
+        <v>23.9539393939394</v>
+      </c>
+      <c r="W16" t="n">
+        <v>185.9048484848485</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1.277171717171717</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>74.27939393939394</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>9364343.434343433</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>78.27656565656565</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>24.48020833333333</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>185.6802083333333</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>1.329166666666667</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>74.09479166666668</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>9505104.166666668</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>78.83854166666666</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>22.81895768833849</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>183.8063718118826</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>1.186311366651924</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>72.46350287483415</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>7430227.480465871</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>78.83094943240454</v>
+      </c>
+      <c r="AN16" t="inlineStr">
+        <is>
+          <t>f3ddUIXs</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>GzfvcwRj</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>IukqGdk1</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>45563.5625</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">schlager d 
+  ger </t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">allianz arena
+  munich </t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>75024</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>nVp0wiqd</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>4jcj2zMd</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>59</v>
+      </c>
+      <c r="I17" t="n">
+        <v>591</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>WG9pOTse</t>
+        </is>
+      </c>
+      <c r="P17" t="n">
+        <v>25.75</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>183.2954545454546</v>
+      </c>
+      <c r="R17" t="n">
+        <v>2.886363636363636</v>
+      </c>
+      <c r="S17" t="n">
+        <v>82.70454545454545</v>
+      </c>
+      <c r="T17" t="n">
+        <v>49365909.09090909</v>
+      </c>
+      <c r="U17" t="n">
+        <v>86.18181818181819</v>
+      </c>
+      <c r="V17" t="n">
+        <v>24.93757575757576</v>
+      </c>
+      <c r="W17" t="n">
+        <v>183.8244444444445</v>
+      </c>
+      <c r="X17" t="n">
+        <v>2.033333333333333</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>80.70808080808081</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>35799090.90909091</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>84.04424242424243</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>25.9375</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>184.0076992753623</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>2.677838164251208</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>81.3395229468599</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>39823135.56763285</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>84.37575483091788</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>24.22151515151516</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>180.9783838383838</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>1.868964646464647</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>79.17164141414142</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>34640669.19191919</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>82.95070707070707</v>
+      </c>
+      <c r="AN17" t="inlineStr">
+        <is>
+          <t>8nuIt455</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>hAcTWKKN</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>pWnjRsFa</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>45564.4375</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">osmers h 
+  ger </t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">holstein stadion
+  kiel </t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>15034</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>63WsD2ei</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>8vndvXTk</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>59</v>
+      </c>
+      <c r="I18" t="n">
+        <v>591</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>ILyJuN3g</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>EuakNmc1</t>
+        </is>
+      </c>
+      <c r="P18" t="n">
+        <v>25.70138888888889</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>185.9534722222222</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.111805555555555</v>
+      </c>
+      <c r="S18" t="n">
+        <v>68.55902777777777</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1632187.5</v>
+      </c>
+      <c r="U18" t="n">
+        <v>71.75</v>
+      </c>
+      <c r="V18" t="n">
+        <v>24.79545454545455</v>
+      </c>
+      <c r="W18" t="n">
+        <v>185.2045454545455</v>
+      </c>
+      <c r="X18" t="n">
+        <v>1.727272727272727</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>77.22727272727272</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>13852272.72727273</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>81.25</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>24.61008986928104</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>185.4768178104575</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>1.04421977124183</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>67.23611111111111</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>1611851.511437909</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>71.92330473856209</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>20.78008373205742</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>185.8057416267943</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>1.345992822966507</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>70.57906698564594</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>6430568.181818182</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>80.80873205741626</v>
+      </c>
+      <c r="AN18" t="inlineStr">
+        <is>
+          <t>8nuIt455</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>UgdQz0fK</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>bFO8E4Vg</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>45564.52083333334</v>
+      </c>
+      <c r="C19" t="inlineStr">
         <is>
           <t xml:space="preserve">brand b 
   ger </t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mewa arena
-  mainz </t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>34000</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>EuakNmc1</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
+      <c r="D19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">prezero arena
+  sinsheim </t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>30150</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>hQAtP9Sl</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
         <is>
           <t>Ig1f1fy3</t>
         </is>
       </c>
-      <c r="H3" t="n">
+      <c r="H19" t="n">
         <v>59</v>
       </c>
-      <c r="I3" t="n">
+      <c r="I19" t="n">
         <v>591</v>
       </c>
-      <c r="J3" t="n">
+      <c r="J19" t="n">
         <v>0</v>
       </c>
-      <c r="K3" t="n">
+      <c r="K19" t="n">
         <v>20242025</v>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="L19" t="inlineStr">
         <is>
           <t>germany</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="M19" t="inlineStr">
         <is>
           <t>bundesliga</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>8vndvXTk</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>nJQmYp1B</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
         <is>
           <t>v9k3aY5F</t>
         </is>
       </c>
-      <c r="P3" t="n">
-        <v>26</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>185</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1</v>
-      </c>
-      <c r="S3" t="n">
-        <v>1</v>
-      </c>
-      <c r="T3" t="n">
-        <v>75</v>
-      </c>
-      <c r="U3" t="n">
-        <v>6500000</v>
-      </c>
-      <c r="V3" t="n">
-        <v>78</v>
-      </c>
-      <c r="W3" t="n">
-        <v>27</v>
-      </c>
-      <c r="X3" t="n">
-        <v>181.3333333333333</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>1.666666666666667</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>3</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>217</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>11600000</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>217</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>26.91481481481481</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>183.425925925926</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>1.588888888888889</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>74.56296296296297</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>6157407.407407408</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>76.8888888888889</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>25.8030303030303</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>183.6727272727273</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>1.187878787878788</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>73.58181818181818</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>5393939.393939394</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>76.77272727272727</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>24.80185185185185</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>184.2833333333333</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>1.394444444444444</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>71.03518518518518</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>3306111.111111111</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>77.16666666666667</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>24.44117647058824</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>184.8882352941176</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>1.190196078431373</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>70.11764705882354</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>3224901.960784314</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>76.80784313725489</v>
-      </c>
-      <c r="BB3" t="inlineStr">
-        <is>
-          <t>GzfvcwRj</t>
-        </is>
-      </c>
-      <c r="BC3" t="inlineStr">
-        <is>
-          <t>IkCftsQm</t>
+      <c r="P19" t="n">
+        <v>26.925</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>186.175</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="S19" t="n">
+        <v>74.59999999999999</v>
+      </c>
+      <c r="T19" t="n">
+        <v>8707500</v>
+      </c>
+      <c r="U19" t="n">
+        <v>77.85000000000001</v>
+      </c>
+      <c r="V19" t="n">
+        <v>25.97727272727273</v>
+      </c>
+      <c r="W19" t="n">
+        <v>183.5545454545455</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1.190909090909091</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>73.73636363636363</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>5445454.545454545</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>76.70454545454545</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>23.74317757405993</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>184.6698815889992</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>1.354469060351413</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>71.64427892369069</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>6545359.58322723</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>78.16760037348273</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>24.03921568627451</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>185.7356209150327</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>1.156535947712419</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>70.01879084967321</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>3286732.026143791</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>77.10588235294117</v>
+      </c>
+      <c r="AN19" t="inlineStr">
+        <is>
+          <t>KUx4Q7x1</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>4fuCGs9P</t>
         </is>
       </c>
     </row>

--- a/data/germany/p6_deployment/data_preparation/df_filled.xlsx
+++ b/data/germany/p6_deployment/data_preparation/df_filled.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BC3"/>
+  <dimension ref="A1:AG19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -505,200 +505,90 @@
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>mean_age_player_miss_home</t>
+          <t>mean_age_player_start_home</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>mean_hei_player_miss_home</t>
+          <t>mean_hei_player_start_home</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>mean_int_rep_player_miss_home</t>
+          <t>mean_rat_player_start_home</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>n_player_miss_home</t>
+          <t>mean_wage_player_start_home</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>sum_rat_player_miss_home</t>
+          <t>mean_age_player_start_away</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>sum_val_player_miss_home</t>
+          <t>mean_hei_player_start_away</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>sum_pot_player_miss_home</t>
+          <t>mean_rat_player_start_away</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>mean_age_player_miss_away</t>
+          <t>mean_wage_player_start_away</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>mean_hei_player_miss_away</t>
+          <t>mean_age_player_sub_home</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>mean_int_rep_player_miss_away</t>
+          <t>mean_hei_player_sub_home</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>n_player_miss_away</t>
+          <t>mean_rat_player_sub_home</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>sum_rat_player_miss_away</t>
+          <t>mean_wage_player_sub_home</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>sum_val_player_miss_away</t>
+          <t>mean_age_player_sub_away</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>sum_pot_player_miss_away</t>
+          <t>mean_hei_player_sub_away</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>mean_age_player_start_home</t>
+          <t>mean_rat_player_sub_away</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>mean_hei_player_start_home</t>
+          <t>mean_wage_player_sub_away</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>mean_int_rep_player_start_home</t>
+          <t>id_coach_home</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
-        <is>
-          <t>mean_rat_player_start_home</t>
-        </is>
-      </c>
-      <c r="AH1" s="1" t="inlineStr">
-        <is>
-          <t>mean_val_player_start_home</t>
-        </is>
-      </c>
-      <c r="AI1" s="1" t="inlineStr">
-        <is>
-          <t>mean_pot_player_start_home</t>
-        </is>
-      </c>
-      <c r="AJ1" s="1" t="inlineStr">
-        <is>
-          <t>mean_age_player_start_away</t>
-        </is>
-      </c>
-      <c r="AK1" s="1" t="inlineStr">
-        <is>
-          <t>mean_hei_player_start_away</t>
-        </is>
-      </c>
-      <c r="AL1" s="1" t="inlineStr">
-        <is>
-          <t>mean_int_rep_player_start_away</t>
-        </is>
-      </c>
-      <c r="AM1" s="1" t="inlineStr">
-        <is>
-          <t>mean_rat_player_start_away</t>
-        </is>
-      </c>
-      <c r="AN1" s="1" t="inlineStr">
-        <is>
-          <t>mean_val_player_start_away</t>
-        </is>
-      </c>
-      <c r="AO1" s="1" t="inlineStr">
-        <is>
-          <t>mean_pot_player_start_away</t>
-        </is>
-      </c>
-      <c r="AP1" s="1" t="inlineStr">
-        <is>
-          <t>mean_age_player_sub_home</t>
-        </is>
-      </c>
-      <c r="AQ1" s="1" t="inlineStr">
-        <is>
-          <t>mean_hei_player_sub_home</t>
-        </is>
-      </c>
-      <c r="AR1" s="1" t="inlineStr">
-        <is>
-          <t>mean_int_rep_player_sub_home</t>
-        </is>
-      </c>
-      <c r="AS1" s="1" t="inlineStr">
-        <is>
-          <t>mean_rat_player_sub_home</t>
-        </is>
-      </c>
-      <c r="AT1" s="1" t="inlineStr">
-        <is>
-          <t>mean_val_player_sub_home</t>
-        </is>
-      </c>
-      <c r="AU1" s="1" t="inlineStr">
-        <is>
-          <t>mean_pot_player_sub_home</t>
-        </is>
-      </c>
-      <c r="AV1" s="1" t="inlineStr">
-        <is>
-          <t>mean_age_player_sub_away</t>
-        </is>
-      </c>
-      <c r="AW1" s="1" t="inlineStr">
-        <is>
-          <t>mean_hei_player_sub_away</t>
-        </is>
-      </c>
-      <c r="AX1" s="1" t="inlineStr">
-        <is>
-          <t>mean_int_rep_player_sub_away</t>
-        </is>
-      </c>
-      <c r="AY1" s="1" t="inlineStr">
-        <is>
-          <t>mean_rat_player_sub_away</t>
-        </is>
-      </c>
-      <c r="AZ1" s="1" t="inlineStr">
-        <is>
-          <t>mean_val_player_sub_away</t>
-        </is>
-      </c>
-      <c r="BA1" s="1" t="inlineStr">
-        <is>
-          <t>mean_pot_player_sub_away</t>
-        </is>
-      </c>
-      <c r="BB1" s="1" t="inlineStr">
-        <is>
-          <t>id_coach_home</t>
-        </is>
-      </c>
-      <c r="BC1" s="1" t="inlineStr">
         <is>
           <t>id_coach_away</t>
         </is>
@@ -707,35 +597,35 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>CnrLfkNN</t>
+          <t>rsNyMnwK</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45550.4375</v>
+        <v>45562.64583333334</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">zwayer f 
+          <t xml:space="preserve">petersen m 
   ger </t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">wwk arena
-  augsburg </t>
+          <t xml:space="preserve">signal iduna park
+  dortmund </t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>30660</v>
+        <v>81365</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>fTVNku3I</t>
+          <t>nP1i5US1</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>ILyJuN3g</t>
+          <t>8Y2m6ADe</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -760,325 +650,2161 @@
           <t>bundesliga</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr"/>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0Ija0Ej9</t>
+        </is>
+      </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>v9k3aY5F</t>
+          <t>0Ija0Ej9</t>
         </is>
       </c>
       <c r="P2" t="n">
-        <v>25.66666666666667</v>
+        <v>25.8</v>
       </c>
       <c r="Q2" t="n">
-        <v>183</v>
+        <v>185.8727272727273</v>
       </c>
       <c r="R2" t="n">
-        <v>1</v>
+        <v>81.03636363636363</v>
       </c>
       <c r="S2" t="n">
-        <v>3</v>
+        <v>51963.63636363636</v>
       </c>
       <c r="T2" t="n">
-        <v>214</v>
+        <v>26.57555555555556</v>
       </c>
       <c r="U2" t="n">
-        <v>9400000</v>
+        <v>184.2626262626263</v>
       </c>
       <c r="V2" t="n">
-        <v>220</v>
+        <v>71.74383838383838</v>
       </c>
       <c r="W2" t="n">
-        <v>27.8</v>
+        <v>15590.10101010101</v>
       </c>
       <c r="X2" t="n">
-        <v>187</v>
+        <v>23.45210144927536</v>
       </c>
       <c r="Y2" t="n">
-        <v>1</v>
+        <v>181.9110869565217</v>
       </c>
       <c r="Z2" t="n">
-        <v>5</v>
+        <v>77.47789855072463</v>
       </c>
       <c r="AA2" t="n">
-        <v>339</v>
+        <v>38547.22222222222</v>
       </c>
       <c r="AB2" t="n">
-        <v>7075000</v>
+        <v>23.281004784689</v>
       </c>
       <c r="AC2" t="n">
-        <v>352</v>
+        <v>183.2587559808613</v>
       </c>
       <c r="AD2" t="n">
-        <v>25.11111111111111</v>
+        <v>68.37066985645933</v>
       </c>
       <c r="AE2" t="n">
-        <v>184.2592592592592</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>1.111111111111111</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>73.37037037037037</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>4625925.925925926</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>76.33333333333333</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>25.56363636363637</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>185.8515151515151</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>70.34848484848483</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>2407878.787878788</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>73.87878787878788</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>24.31269841269841</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>183.3809523809524</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>1.468253968253968</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>72.09047619047618</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>4394067.46031746</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>76.28968253968254</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>24.43703703703704</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>184.1109161793372</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>69.08089668615985</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>2176196.393762183</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>73.53752436647173</v>
-      </c>
-      <c r="BB2" t="inlineStr">
-        <is>
-          <t>4ljanukM</t>
-        </is>
-      </c>
-      <c r="BC2" t="inlineStr">
-        <is>
-          <t>0jdIgO6t</t>
+        <v>12168.94736842106</v>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>GzfvcwRj</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>A15eUM4C</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>8OhVCWxh</t>
+          <t>CIlrT3pm</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45550.52083333334</v>
+        <v>45563.4375</v>
       </c>
       <c r="C3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">jollenbeck m 
+  ger </t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">borussia park
+  monchengladbach </t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>54042</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>88HSzjDr</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>pzHW4oaE</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>59</v>
+      </c>
+      <c r="I3" t="n">
+        <v>591</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>WG9pOTse</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="n">
+        <v>25.30909090909091</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>184.3272727272727</v>
+      </c>
+      <c r="R3" t="n">
+        <v>75.81818181818181</v>
+      </c>
+      <c r="S3" t="n">
+        <v>23909.09090909091</v>
+      </c>
+      <c r="T3" t="n">
+        <v>26.26545454545455</v>
+      </c>
+      <c r="U3" t="n">
+        <v>186.3274747474747</v>
+      </c>
+      <c r="V3" t="n">
+        <v>75.02161616161615</v>
+      </c>
+      <c r="W3" t="n">
+        <v>26052.12121212121</v>
+      </c>
+      <c r="X3" t="n">
+        <v>24.60195652173913</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>183.6065942028985</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>73.47898550724638</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>20201.66666666667</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>25.13500345065562</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>182.9532505175983</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>71.8504347826087</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>20348.68184955141</v>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>UgdQz0fK</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>KUx4Q7x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>6uSGCr06</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>45563.4375</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hartmann r 
+  ger </t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">europa park stadion
+  freiburg </t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>34700</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>fiEQZ7C7</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>ILyJuN3g</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>59</v>
+      </c>
+      <c r="I4" t="n">
+        <v>591</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>nJQmYp1B</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>v9k3aY5F</t>
+        </is>
+      </c>
+      <c r="P4" t="n">
+        <v>25.61777777777778</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>183.8466666666666</v>
+      </c>
+      <c r="R4" t="n">
+        <v>75.42222222222222</v>
+      </c>
+      <c r="S4" t="n">
+        <v>23186.66666666666</v>
+      </c>
+      <c r="T4" t="n">
+        <v>25.68363636363637</v>
+      </c>
+      <c r="U4" t="n">
+        <v>185.6927272727273</v>
+      </c>
+      <c r="V4" t="n">
+        <v>70.31818181818183</v>
+      </c>
+      <c r="W4" t="n">
+        <v>11380</v>
+      </c>
+      <c r="X4" t="n">
+        <v>25.77300860847771</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>183.3849614153962</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>74.32666448730522</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>21868.25363804768</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>24.60104575163398</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>184.1977261781906</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>69.03089095287238</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>10354.92604059168</v>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>4ljanukM</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>pfoInmcq</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>f18BYPMP</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>45563.4375</v>
+      </c>
+      <c r="C5" t="inlineStr">
         <is>
           <t xml:space="preserve">brand b 
   ger </t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t xml:space="preserve">mewa arena
   mainz </t>
         </is>
       </c>
-      <c r="E3" t="n">
+      <c r="E5" t="n">
         <v>34000</v>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>EuakNmc1</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>KWixEVWi</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>59</v>
+      </c>
+      <c r="I5" t="n">
+        <v>591</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>8vndvXTk</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="n">
+        <v>26.57111111111111</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>183.4333333333333</v>
+      </c>
+      <c r="R5" t="n">
+        <v>74.55999999999999</v>
+      </c>
+      <c r="S5" t="n">
+        <v>22895.55555555555</v>
+      </c>
+      <c r="T5" t="n">
+        <v>26.21388888888889</v>
+      </c>
+      <c r="U5" t="n">
+        <v>188.2305555555556</v>
+      </c>
+      <c r="V5" t="n">
+        <v>72.07222222222222</v>
+      </c>
+      <c r="W5" t="n">
+        <v>18702.77777777777</v>
+      </c>
+      <c r="X5" t="n">
+        <v>25.09464494569758</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>184.0522055137845</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>71.24617376775271</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>15664.36090225564</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>25.6015350877193</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>185.0967105263158</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>69.89561403508772</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>14250.21929824561</v>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>2VSFgl3c</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>YZPE6Sx7</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>Q5hiEzKD</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>45563.4375</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">storks s 
+  ger </t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">red bull arena
+  leipzig </t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>47069</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>KbS1suSm</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>fTVNku3I</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>59</v>
+      </c>
+      <c r="I6" t="n">
+        <v>591</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>nP1i5US1</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="n">
+        <v>25.04545454545454</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>182.5727272727273</v>
+      </c>
+      <c r="R6" t="n">
+        <v>79.38</v>
+      </c>
+      <c r="S6" t="n">
+        <v>50536.36363636363</v>
+      </c>
+      <c r="T6" t="n">
+        <v>25.11111111111111</v>
+      </c>
+      <c r="U6" t="n">
+        <v>184.2592592592592</v>
+      </c>
+      <c r="V6" t="n">
+        <v>73.37037037037037</v>
+      </c>
+      <c r="W6" t="n">
+        <v>20370.37037037037</v>
+      </c>
+      <c r="X6" t="n">
+        <v>23.83552631578948</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>183.8643421052631</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>77.8346052631579</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>44449.34210526316</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>24.20149464570517</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>184.1285714285714</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>72.23562542720437</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>19814.59330143541</v>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>0jdIgO6t</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>vZA6VYpf</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>SfGPAMUI</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>45563.4375</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">badstubner f 
+  ger </t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">volkswagen arena
+  wolfsburg </t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>28917</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>nwkTahLL</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>nJQmYp1B</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>59</v>
+      </c>
+      <c r="I7" t="n">
+        <v>591</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>dfNCCCzS</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>fiEQZ7C7</t>
+        </is>
+      </c>
+      <c r="P7" t="n">
+        <v>24.02777777777778</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>184.8784722222222</v>
+      </c>
+      <c r="R7" t="n">
+        <v>75.68402777777777</v>
+      </c>
+      <c r="S7" t="n">
+        <v>34618.05555555555</v>
+      </c>
+      <c r="T7" t="n">
+        <v>23.93131313131313</v>
+      </c>
+      <c r="U7" t="n">
+        <v>185.8449494949495</v>
+      </c>
+      <c r="V7" t="n">
+        <v>74.53585858585858</v>
+      </c>
+      <c r="W7" t="n">
+        <v>26461.61616161616</v>
+      </c>
+      <c r="X7" t="n">
+        <v>24.5175</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>185.4641666666666</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>74.31583333333333</v>
+      </c>
+      <c r="AA7" t="inlineStr"/>
+      <c r="AB7" t="n">
+        <v>22.77413140694874</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>184.3969765099022</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>72.33625239569513</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>22564.41348469212</v>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>hAcTWKKN</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>IkCftsQm</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>IukqGdk1</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>45563.5625</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stegemann s 
+  ger </t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">allianz arena
+  munich </t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>75024</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>nVp0wiqd</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>4jcj2zMd</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>59</v>
+      </c>
+      <c r="I8" t="n">
+        <v>591</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>WG9pOTse</t>
+        </is>
+      </c>
+      <c r="P8" t="n">
+        <v>25.61818181818182</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>183.5818181818182</v>
+      </c>
+      <c r="R8" t="n">
+        <v>82.56363636363636</v>
+      </c>
+      <c r="S8" t="n">
+        <v>78109.09090909091</v>
+      </c>
+      <c r="T8" t="n">
+        <v>25.02373737373737</v>
+      </c>
+      <c r="U8" t="n">
+        <v>183.8082491582491</v>
+      </c>
+      <c r="V8" t="n">
+        <v>80.78703703703704</v>
+      </c>
+      <c r="W8" t="n">
+        <v>55135.35353535353</v>
+      </c>
+      <c r="X8" t="n">
+        <v>26.15</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>183.6061594202898</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>81.45495169082126</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>75471.37681159421</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>24.08611111111111</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>181.1259259259259</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>79.21879208754208</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>51963.02609427609</v>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>4fuCGs9P</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>f3ddUIXs</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>pWnjRsFa</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>45564.4375</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">welz t 
+  ger </t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">holstein stadion
+  kiel </t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>15034</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>63WsD2ei</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>8vndvXTk</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>59</v>
+      </c>
+      <c r="I9" t="n">
+        <v>591</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>ILyJuN3g</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>EuakNmc1</t>
+        </is>
+      </c>
+      <c r="P9" t="n">
+        <v>25.70138888888889</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>185.9534722222222</v>
+      </c>
+      <c r="R9" t="n">
+        <v>68.55902777777777</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10261.11111111111</v>
+      </c>
+      <c r="T9" t="n">
+        <v>24.38181818181818</v>
+      </c>
+      <c r="U9" t="n">
+        <v>185.4545454545455</v>
+      </c>
+      <c r="V9" t="n">
+        <v>76.78181818181818</v>
+      </c>
+      <c r="W9" t="n">
+        <v>34290.90909090909</v>
+      </c>
+      <c r="X9" t="n">
+        <v>24.62807189542483</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>185.241454248366</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>67.33888888888889</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>8659.346405228756</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>20.98406698564593</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>185.5145933014354</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>70.57325358851674</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>16901.31578947369</v>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>8f6APkLc</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>M5BRZDsC</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>bFO8E4Vg</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>45564.52083333334</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dankert b 
+  ger </t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">prezero arena
+  sinsheim </t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>30150</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>hQAtP9Sl</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
         <is>
           <t>Ig1f1fy3</t>
         </is>
       </c>
-      <c r="H3" t="n">
+      <c r="H10" t="n">
         <v>59</v>
       </c>
-      <c r="I3" t="n">
+      <c r="I10" t="n">
         <v>591</v>
       </c>
-      <c r="J3" t="n">
+      <c r="J10" t="n">
         <v>0</v>
       </c>
-      <c r="K3" t="n">
+      <c r="K10" t="n">
         <v>20242025</v>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>germany</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>bundesliga</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>nJQmYp1B</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>v9k3aY5F</t>
+        </is>
+      </c>
+      <c r="P10" t="n">
+        <v>26.85111111111111</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>186.1177777777778</v>
+      </c>
+      <c r="R10" t="n">
+        <v>74.50222222222223</v>
+      </c>
+      <c r="S10" t="n">
+        <v>28540</v>
+      </c>
+      <c r="T10" t="n">
+        <v>26.08181818181818</v>
+      </c>
+      <c r="U10" t="n">
+        <v>183.5836363636363</v>
+      </c>
+      <c r="V10" t="n">
+        <v>73.82909090909091</v>
+      </c>
+      <c r="W10" t="n">
+        <v>19249.0909090909</v>
+      </c>
+      <c r="X10" t="n">
+        <v>23.52787539258128</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>184.4787624140565</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>71.59161361514302</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>19751.72735760971</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>23.80409982174688</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>185.9703149138443</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>69.93321449792037</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>12631.44385026738</v>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>hpYJ6izc</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>K6A2elS9</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>UajsPCkT</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>45569.64583333334</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">welz t 
+  ger </t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">wwk arena
+  augsburg </t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>30660</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>fTVNku3I</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>88HSzjDr</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>59</v>
+      </c>
+      <c r="I11" t="n">
+        <v>591</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>WG9pOTse</t>
+        </is>
+      </c>
+      <c r="P11" t="n">
+        <v>25.11111111111111</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>184.2592592592592</v>
+      </c>
+      <c r="R11" t="n">
+        <v>73.37037037037037</v>
+      </c>
+      <c r="S11" t="n">
+        <v>20370.37037037037</v>
+      </c>
+      <c r="T11" t="n">
+        <v>25.30909090909091</v>
+      </c>
+      <c r="U11" t="n">
+        <v>184.3272727272727</v>
+      </c>
+      <c r="V11" t="n">
+        <v>75.81818181818181</v>
+      </c>
+      <c r="W11" t="n">
+        <v>23909.09090909091</v>
+      </c>
+      <c r="X11" t="n">
+        <v>24.20149464570517</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>184.1285714285714</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>72.23562542720437</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>19814.59330143541</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>24.60195652173913</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>183.6065942028985</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>73.47898550724638</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>20201.66666666667</v>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>2VSFgl3c</t>
+        </is>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>M5BRZDsC</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>tbtaPLqC</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>45570.4375</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">petersen m 
+  ger </t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bayarena
+  leverkusen </t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>30210</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>4jcj2zMd</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>63WsD2ei</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>59</v>
+      </c>
+      <c r="I12" t="n">
+        <v>591</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>WG9pOTse</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>ILyJuN3g</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>25.02373737373737</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>183.8082491582491</v>
+      </c>
+      <c r="R12" t="n">
+        <v>80.78703703703704</v>
+      </c>
+      <c r="S12" t="n">
+        <v>55135.35353535353</v>
+      </c>
+      <c r="T12" t="n">
+        <v>25.70138888888889</v>
+      </c>
+      <c r="U12" t="n">
+        <v>185.9534722222222</v>
+      </c>
+      <c r="V12" t="n">
+        <v>68.55902777777777</v>
+      </c>
+      <c r="W12" t="n">
+        <v>10261.11111111111</v>
+      </c>
+      <c r="X12" t="n">
+        <v>24.08611111111111</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>181.1259259259259</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>79.21879208754208</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>51963.02609427609</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>24.62807189542483</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>185.241454248366</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>67.33888888888889</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>8659.346405228756</v>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>hAcTWKKN</t>
+        </is>
+      </c>
+      <c r="AG12" t="inlineStr">
+        <is>
+          <t>A15eUM4C</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>ENOasf5c</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>45570.4375</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stegemann s 
+  ger </t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vonovia ruhrstadion
+  bochum </t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>26000</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>8Y2m6ADe</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>nwkTahLL</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>59</v>
+      </c>
+      <c r="I13" t="n">
+        <v>591</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>0Ija0Ej9</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>dfNCCCzS</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
+        <v>26.57555555555556</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>184.2626262626263</v>
+      </c>
+      <c r="R13" t="n">
+        <v>71.74383838383838</v>
+      </c>
+      <c r="S13" t="n">
+        <v>15590.10101010101</v>
+      </c>
+      <c r="T13" t="n">
+        <v>24.02777777777778</v>
+      </c>
+      <c r="U13" t="n">
+        <v>184.8784722222222</v>
+      </c>
+      <c r="V13" t="n">
+        <v>75.68402777777777</v>
+      </c>
+      <c r="W13" t="n">
+        <v>34618.05555555555</v>
+      </c>
+      <c r="X13" t="n">
+        <v>23.281004784689</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>183.2587559808613</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>68.37066985645933</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>12168.94736842106</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>24.5175</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>185.4641666666666</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>74.31583333333333</v>
+      </c>
+      <c r="AE13" t="inlineStr"/>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t>8f6APkLc</t>
+        </is>
+      </c>
+      <c r="AG13" t="inlineStr">
+        <is>
+          <t>f3ddUIXs</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>lpXDJjDj</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>45570.4375</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">badstubner f 
+  ger </t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadion an der alten forsterei
+  berlin </t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>22012</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>pzHW4oaE</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>nP1i5US1</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>59</v>
+      </c>
+      <c r="I14" t="n">
+        <v>591</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>0Ija0Ej9</t>
+        </is>
+      </c>
+      <c r="P14" t="n">
+        <v>26.26545454545455</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>186.3274747474747</v>
+      </c>
+      <c r="R14" t="n">
+        <v>75.02161616161615</v>
+      </c>
+      <c r="S14" t="n">
+        <v>26052.12121212121</v>
+      </c>
+      <c r="T14" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="U14" t="n">
+        <v>185.8727272727273</v>
+      </c>
+      <c r="V14" t="n">
+        <v>81.03636363636363</v>
+      </c>
+      <c r="W14" t="n">
+        <v>51963.63636363636</v>
+      </c>
+      <c r="X14" t="n">
+        <v>25.13500345065562</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>182.9532505175983</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>71.8504347826087</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>20348.68184955141</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>23.45210144927536</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>181.9110869565217</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>77.47789855072463</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>38547.22222222222</v>
+      </c>
+      <c r="AF14" t="inlineStr">
+        <is>
+          <t>hpYJ6izc</t>
+        </is>
+      </c>
+      <c r="AG14" t="inlineStr">
+        <is>
+          <t>IkCftsQm</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>dnhZQYKG</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>45570.4375</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">brand b 
+  ger </t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">weserstadion
+  bremen </t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>42100</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Ig1f1fy3</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>fiEQZ7C7</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>59</v>
+      </c>
+      <c r="I15" t="n">
+        <v>591</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>v9k3aY5F</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>nJQmYp1B</t>
+        </is>
+      </c>
+      <c r="P15" t="n">
+        <v>26.08181818181818</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>183.5836363636363</v>
+      </c>
+      <c r="R15" t="n">
+        <v>73.82909090909091</v>
+      </c>
+      <c r="S15" t="n">
+        <v>19249.0909090909</v>
+      </c>
+      <c r="T15" t="n">
+        <v>25.61777777777778</v>
+      </c>
+      <c r="U15" t="n">
+        <v>183.8466666666666</v>
+      </c>
+      <c r="V15" t="n">
+        <v>75.42222222222222</v>
+      </c>
+      <c r="W15" t="n">
+        <v>23186.66666666666</v>
+      </c>
+      <c r="X15" t="n">
+        <v>23.80409982174688</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>185.9703149138443</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>69.93321449792037</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>12631.44385026738</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>25.77300860847771</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>183.3849614153962</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>74.32666448730522</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>21868.25363804768</v>
+      </c>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>4fuCGs9P</t>
+        </is>
+      </c>
+      <c r="AG15" t="inlineStr">
+        <is>
+          <t>YZPE6Sx7</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>zwD8uYZ9</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>45570.5625</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">storks s 
+  ger </t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">millerntor stadion
+  hamburg </t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>29546</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>ILyJuN3g</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>EuakNmc1</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>59</v>
+      </c>
+      <c r="I16" t="n">
+        <v>591</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>v9k3aY5F</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
         <is>
           <t>8vndvXTk</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>v9k3aY5F</t>
-        </is>
-      </c>
-      <c r="P3" t="n">
-        <v>26</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>185</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1</v>
-      </c>
-      <c r="S3" t="n">
-        <v>1</v>
-      </c>
-      <c r="T3" t="n">
-        <v>75</v>
-      </c>
-      <c r="U3" t="n">
-        <v>6500000</v>
-      </c>
-      <c r="V3" t="n">
-        <v>78</v>
-      </c>
-      <c r="W3" t="n">
-        <v>27</v>
-      </c>
-      <c r="X3" t="n">
-        <v>181.3333333333333</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>1.666666666666667</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>3</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>217</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>11600000</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>217</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>26.91481481481481</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>183.425925925926</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>1.588888888888889</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>74.56296296296297</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>6157407.407407408</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>76.8888888888889</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>25.8030303030303</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>183.6727272727273</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>1.187878787878788</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>73.58181818181818</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>5393939.393939394</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>76.77272727272727</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>24.80185185185185</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>184.2833333333333</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>1.394444444444444</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>71.03518518518518</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>3306111.111111111</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>77.16666666666667</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>24.44117647058824</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>184.8882352941176</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>1.190196078431373</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>70.11764705882354</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>3224901.960784314</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>76.80784313725489</v>
-      </c>
-      <c r="BB3" t="inlineStr">
+      <c r="P16" t="n">
+        <v>25.68363636363637</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>185.6927272727273</v>
+      </c>
+      <c r="R16" t="n">
+        <v>70.31818181818183</v>
+      </c>
+      <c r="S16" t="n">
+        <v>11380</v>
+      </c>
+      <c r="T16" t="n">
+        <v>26.57111111111111</v>
+      </c>
+      <c r="U16" t="n">
+        <v>183.4333333333333</v>
+      </c>
+      <c r="V16" t="n">
+        <v>74.55999999999999</v>
+      </c>
+      <c r="W16" t="n">
+        <v>22895.55555555555</v>
+      </c>
+      <c r="X16" t="n">
+        <v>24.60104575163398</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>184.1977261781906</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>69.03089095287238</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>10354.92604059168</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>25.09464494569758</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>184.0522055137845</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>71.24617376775271</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>15664.36090225564</v>
+      </c>
+      <c r="AF16" t="inlineStr">
+        <is>
+          <t>0jdIgO6t</t>
+        </is>
+      </c>
+      <c r="AG16" t="inlineStr">
+        <is>
+          <t>vZA6VYpf</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>0KbQSfj4</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>45571.4375</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hartmann r 
+  ger </t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">voith arena
+  heidenheim </t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>15000</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>KWixEVWi</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>KbS1suSm</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>59</v>
+      </c>
+      <c r="I17" t="n">
+        <v>591</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>nP1i5US1</t>
+        </is>
+      </c>
+      <c r="P17" t="n">
+        <v>26.21388888888889</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>188.2305555555556</v>
+      </c>
+      <c r="R17" t="n">
+        <v>72.07222222222222</v>
+      </c>
+      <c r="S17" t="n">
+        <v>18702.77777777777</v>
+      </c>
+      <c r="T17" t="n">
+        <v>25.04545454545454</v>
+      </c>
+      <c r="U17" t="n">
+        <v>182.5727272727273</v>
+      </c>
+      <c r="V17" t="n">
+        <v>79.38</v>
+      </c>
+      <c r="W17" t="n">
+        <v>50536.36363636363</v>
+      </c>
+      <c r="X17" t="n">
+        <v>25.6015350877193</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>185.0967105263158</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>69.89561403508772</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>14250.21929824561</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>23.83552631578948</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>183.8643421052631</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>77.8346052631579</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>44449.34210526316</v>
+      </c>
+      <c r="AF17" t="inlineStr">
+        <is>
+          <t>4ljanukM</t>
+        </is>
+      </c>
+      <c r="AG17" t="inlineStr">
+        <is>
+          <t>pfoInmcq</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>ShoJUGLi</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>45571.52083333334</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dankert b 
+  ger </t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">deutsche bank park
+  frankfurt </t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>58000</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>8vndvXTk</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>nVp0wiqd</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>59</v>
+      </c>
+      <c r="I18" t="n">
+        <v>591</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>EuakNmc1</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="n">
+        <v>24.38181818181818</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>185.4545454545455</v>
+      </c>
+      <c r="R18" t="n">
+        <v>76.78181818181818</v>
+      </c>
+      <c r="S18" t="n">
+        <v>34290.90909090909</v>
+      </c>
+      <c r="T18" t="n">
+        <v>25.61818181818182</v>
+      </c>
+      <c r="U18" t="n">
+        <v>183.5818181818182</v>
+      </c>
+      <c r="V18" t="n">
+        <v>82.56363636363636</v>
+      </c>
+      <c r="W18" t="n">
+        <v>78109.09090909091</v>
+      </c>
+      <c r="X18" t="n">
+        <v>20.98406698564593</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>185.5145933014354</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>70.57325358851674</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>16901.31578947369</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>26.15</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>183.6061594202898</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>81.45495169082126</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>75471.37681159421</v>
+      </c>
+      <c r="AF18" t="inlineStr">
+        <is>
+          <t>UgdQz0fK</t>
+        </is>
+      </c>
+      <c r="AG18" t="inlineStr">
+        <is>
+          <t>K6A2elS9</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>nc8W6DTp</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>45571.60416666666</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">jollenbeck m 
+  ger </t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mhparena
+  stuttgart </t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>60449</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>nJQmYp1B</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>hQAtP9Sl</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>59</v>
+      </c>
+      <c r="I19" t="n">
+        <v>591</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>fiEQZ7C7</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>nJQmYp1B</t>
+        </is>
+      </c>
+      <c r="P19" t="n">
+        <v>23.93131313131313</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>185.8449494949495</v>
+      </c>
+      <c r="R19" t="n">
+        <v>74.53585858585858</v>
+      </c>
+      <c r="S19" t="n">
+        <v>26461.61616161616</v>
+      </c>
+      <c r="T19" t="n">
+        <v>26.85111111111111</v>
+      </c>
+      <c r="U19" t="n">
+        <v>186.1177777777778</v>
+      </c>
+      <c r="V19" t="n">
+        <v>74.50222222222223</v>
+      </c>
+      <c r="W19" t="n">
+        <v>28540</v>
+      </c>
+      <c r="X19" t="n">
+        <v>22.77413140694874</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>184.3969765099022</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>72.33625239569513</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>22564.41348469212</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>23.52787539258128</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>184.4787624140565</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>71.59161361514302</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>19751.72735760971</v>
+      </c>
+      <c r="AF19" t="inlineStr">
         <is>
           <t>GzfvcwRj</t>
         </is>
       </c>
-      <c r="BC3" t="inlineStr">
-        <is>
-          <t>IkCftsQm</t>
+      <c r="AG19" t="inlineStr">
+        <is>
+          <t>KUx4Q7x1</t>
         </is>
       </c>
     </row>

--- a/data/germany/p6_deployment/data_preparation/df_filled.xlsx
+++ b/data/germany/p6_deployment/data_preparation/df_filled.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG19"/>
+  <dimension ref="A1:AS10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -505,90 +505,150 @@
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
+          <t>mean_age_player_miss_home</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>mean_hei_player_miss_home</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>mean_rat_player_miss_home</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>mean_wage_player_miss_home</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>n_player_miss_home</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>sum_rat_player_miss_home</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>mean_age_player_miss_away</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>mean_hei_player_miss_away</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>mean_rat_player_miss_away</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>mean_wage_player_miss_away</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>n_player_miss_away</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>sum_rat_player_miss_away</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
           <t>mean_age_player_start_home</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>mean_hei_player_start_home</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>mean_rat_player_start_home</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>mean_wage_player_start_home</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>mean_age_player_start_away</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>mean_hei_player_start_away</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>mean_rat_player_start_away</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>mean_wage_player_start_away</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>mean_age_player_sub_home</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>mean_hei_player_sub_home</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>mean_rat_player_sub_home</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>mean_wage_player_sub_home</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>mean_age_player_sub_away</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>mean_hei_player_sub_away</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>mean_rat_player_sub_away</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>mean_wage_player_sub_away</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>id_coach_home</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>id_coach_away</t>
         </is>
@@ -605,7 +665,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">petersen m 
+          <t xml:space="preserve">brych f 
   ger </t>
         </is>
       </c>
@@ -661,59 +721,95 @@
         </is>
       </c>
       <c r="P2" t="n">
+        <v>21</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>185.5</v>
+      </c>
+      <c r="R2" t="n">
+        <v>78</v>
+      </c>
+      <c r="S2" t="n">
+        <v>36000</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2</v>
+      </c>
+      <c r="U2" t="n">
+        <v>156</v>
+      </c>
+      <c r="V2" t="n">
+        <v>23.33333333333333</v>
+      </c>
+      <c r="W2" t="n">
+        <v>186.6666666666667</v>
+      </c>
+      <c r="X2" t="n">
+        <v>69</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>12000</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>207</v>
+      </c>
+      <c r="AB2" t="n">
         <v>25.8</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="AC2" t="n">
         <v>185.8727272727273</v>
       </c>
-      <c r="R2" t="n">
+      <c r="AD2" t="n">
         <v>81.03636363636363</v>
       </c>
-      <c r="S2" t="n">
+      <c r="AE2" t="n">
         <v>51963.63636363636</v>
       </c>
-      <c r="T2" t="n">
+      <c r="AF2" t="n">
         <v>26.57555555555556</v>
       </c>
-      <c r="U2" t="n">
+      <c r="AG2" t="n">
         <v>184.2626262626263</v>
       </c>
-      <c r="V2" t="n">
+      <c r="AH2" t="n">
         <v>71.74383838383838</v>
       </c>
-      <c r="W2" t="n">
+      <c r="AI2" t="n">
         <v>15590.10101010101</v>
       </c>
-      <c r="X2" t="n">
+      <c r="AJ2" t="n">
         <v>23.45210144927536</v>
       </c>
-      <c r="Y2" t="n">
+      <c r="AK2" t="n">
         <v>181.9110869565217</v>
       </c>
-      <c r="Z2" t="n">
+      <c r="AL2" t="n">
         <v>77.47789855072463</v>
       </c>
-      <c r="AA2" t="n">
+      <c r="AM2" t="n">
         <v>38547.22222222222</v>
       </c>
-      <c r="AB2" t="n">
+      <c r="AN2" t="n">
         <v>23.281004784689</v>
       </c>
-      <c r="AC2" t="n">
+      <c r="AO2" t="n">
         <v>183.2587559808613</v>
       </c>
-      <c r="AD2" t="n">
+      <c r="AP2" t="n">
         <v>68.37066985645933</v>
       </c>
-      <c r="AE2" t="n">
+      <c r="AQ2" t="n">
         <v>12168.94736842106</v>
       </c>
-      <c r="AF2" t="inlineStr">
+      <c r="AR2" t="inlineStr">
         <is>
           <t>GzfvcwRj</t>
         </is>
       </c>
-      <c r="AG2" t="inlineStr">
+      <c r="AS2" t="inlineStr">
         <is>
           <t>A15eUM4C</t>
         </is>
@@ -730,7 +826,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">jollenbeck m 
+          <t xml:space="preserve">schlager d 
   ger </t>
         </is>
       </c>
@@ -782,59 +878,95 @@
       </c>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>182.6</v>
+      </c>
+      <c r="R3" t="n">
+        <v>70.40000000000001</v>
+      </c>
+      <c r="S3" t="n">
+        <v>13800</v>
+      </c>
+      <c r="T3" t="n">
+        <v>5</v>
+      </c>
+      <c r="U3" t="n">
+        <v>352</v>
+      </c>
+      <c r="V3" t="n">
+        <v>27</v>
+      </c>
+      <c r="W3" t="n">
+        <v>181</v>
+      </c>
+      <c r="X3" t="n">
+        <v>73</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>20500</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>146</v>
+      </c>
+      <c r="AB3" t="n">
         <v>25.30909090909091</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="AC3" t="n">
         <v>184.3272727272727</v>
       </c>
-      <c r="R3" t="n">
+      <c r="AD3" t="n">
         <v>75.81818181818181</v>
       </c>
-      <c r="S3" t="n">
+      <c r="AE3" t="n">
         <v>23909.09090909091</v>
       </c>
-      <c r="T3" t="n">
+      <c r="AF3" t="n">
         <v>26.26545454545455</v>
       </c>
-      <c r="U3" t="n">
+      <c r="AG3" t="n">
         <v>186.3274747474747</v>
       </c>
-      <c r="V3" t="n">
+      <c r="AH3" t="n">
         <v>75.02161616161615</v>
       </c>
-      <c r="W3" t="n">
+      <c r="AI3" t="n">
         <v>26052.12121212121</v>
       </c>
-      <c r="X3" t="n">
+      <c r="AJ3" t="n">
         <v>24.60195652173913</v>
       </c>
-      <c r="Y3" t="n">
+      <c r="AK3" t="n">
         <v>183.6065942028985</v>
       </c>
-      <c r="Z3" t="n">
+      <c r="AL3" t="n">
         <v>73.47898550724638</v>
       </c>
-      <c r="AA3" t="n">
+      <c r="AM3" t="n">
         <v>20201.66666666667</v>
       </c>
-      <c r="AB3" t="n">
+      <c r="AN3" t="n">
         <v>25.13500345065562</v>
       </c>
-      <c r="AC3" t="n">
+      <c r="AO3" t="n">
         <v>182.9532505175983</v>
       </c>
-      <c r="AD3" t="n">
+      <c r="AP3" t="n">
         <v>71.8504347826087</v>
       </c>
-      <c r="AE3" t="n">
+      <c r="AQ3" t="n">
         <v>20348.68184955141</v>
       </c>
-      <c r="AF3" t="inlineStr">
+      <c r="AR3" t="inlineStr">
         <is>
           <t>UgdQz0fK</t>
         </is>
       </c>
-      <c r="AG3" t="inlineStr">
+      <c r="AS3" t="inlineStr">
         <is>
           <t>KUx4Q7x1</t>
         </is>
@@ -851,7 +983,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">hartmann r 
+          <t xml:space="preserve">gerach t 
   ger </t>
         </is>
       </c>
@@ -907,59 +1039,95 @@
         </is>
       </c>
       <c r="P4" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>186</v>
+      </c>
+      <c r="R4" t="n">
+        <v>70.5</v>
+      </c>
+      <c r="S4" t="n">
+        <v>14500</v>
+      </c>
+      <c r="T4" t="n">
+        <v>4</v>
+      </c>
+      <c r="U4" t="n">
+        <v>282</v>
+      </c>
+      <c r="V4" t="n">
+        <v>28.8</v>
+      </c>
+      <c r="W4" t="n">
+        <v>187.6</v>
+      </c>
+      <c r="X4" t="n">
+        <v>67.40000000000001</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>12200</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>337</v>
+      </c>
+      <c r="AB4" t="n">
         <v>25.61777777777778</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="AC4" t="n">
         <v>183.8466666666666</v>
       </c>
-      <c r="R4" t="n">
+      <c r="AD4" t="n">
         <v>75.42222222222222</v>
       </c>
-      <c r="S4" t="n">
+      <c r="AE4" t="n">
         <v>23186.66666666666</v>
       </c>
-      <c r="T4" t="n">
+      <c r="AF4" t="n">
         <v>25.68363636363637</v>
       </c>
-      <c r="U4" t="n">
+      <c r="AG4" t="n">
         <v>185.6927272727273</v>
       </c>
-      <c r="V4" t="n">
+      <c r="AH4" t="n">
         <v>70.31818181818183</v>
       </c>
-      <c r="W4" t="n">
+      <c r="AI4" t="n">
         <v>11380</v>
       </c>
-      <c r="X4" t="n">
+      <c r="AJ4" t="n">
         <v>25.77300860847771</v>
       </c>
-      <c r="Y4" t="n">
+      <c r="AK4" t="n">
         <v>183.3849614153962</v>
       </c>
-      <c r="Z4" t="n">
+      <c r="AL4" t="n">
         <v>74.32666448730522</v>
       </c>
-      <c r="AA4" t="n">
+      <c r="AM4" t="n">
         <v>21868.25363804768</v>
       </c>
-      <c r="AB4" t="n">
+      <c r="AN4" t="n">
         <v>24.60104575163398</v>
       </c>
-      <c r="AC4" t="n">
+      <c r="AO4" t="n">
         <v>184.1977261781906</v>
       </c>
-      <c r="AD4" t="n">
+      <c r="AP4" t="n">
         <v>69.03089095287238</v>
       </c>
-      <c r="AE4" t="n">
+      <c r="AQ4" t="n">
         <v>10354.92604059168</v>
       </c>
-      <c r="AF4" t="inlineStr">
+      <c r="AR4" t="inlineStr">
         <is>
           <t>4ljanukM</t>
         </is>
       </c>
-      <c r="AG4" t="inlineStr">
+      <c r="AS4" t="inlineStr">
         <is>
           <t>pfoInmcq</t>
         </is>
@@ -976,7 +1144,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">brand b 
+          <t xml:space="preserve">exner f 
   ger </t>
         </is>
       </c>
@@ -1028,59 +1196,95 @@
       </c>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="n">
+        <v>26</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>180</v>
+      </c>
+      <c r="R5" t="n">
+        <v>77</v>
+      </c>
+      <c r="S5" t="n">
+        <v>29000</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1</v>
+      </c>
+      <c r="U5" t="n">
+        <v>77</v>
+      </c>
+      <c r="V5" t="n">
+        <v>23</v>
+      </c>
+      <c r="W5" t="n">
+        <v>186</v>
+      </c>
+      <c r="X5" t="n">
+        <v>66</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>7000</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>66</v>
+      </c>
+      <c r="AB5" t="n">
         <v>26.57111111111111</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="AC5" t="n">
         <v>183.4333333333333</v>
       </c>
-      <c r="R5" t="n">
+      <c r="AD5" t="n">
         <v>74.55999999999999</v>
       </c>
-      <c r="S5" t="n">
+      <c r="AE5" t="n">
         <v>22895.55555555555</v>
       </c>
-      <c r="T5" t="n">
+      <c r="AF5" t="n">
         <v>26.21388888888889</v>
       </c>
-      <c r="U5" t="n">
+      <c r="AG5" t="n">
         <v>188.2305555555556</v>
       </c>
-      <c r="V5" t="n">
+      <c r="AH5" t="n">
         <v>72.07222222222222</v>
       </c>
-      <c r="W5" t="n">
+      <c r="AI5" t="n">
         <v>18702.77777777777</v>
       </c>
-      <c r="X5" t="n">
+      <c r="AJ5" t="n">
         <v>25.09464494569758</v>
       </c>
-      <c r="Y5" t="n">
+      <c r="AK5" t="n">
         <v>184.0522055137845</v>
       </c>
-      <c r="Z5" t="n">
+      <c r="AL5" t="n">
         <v>71.24617376775271</v>
       </c>
-      <c r="AA5" t="n">
+      <c r="AM5" t="n">
         <v>15664.36090225564</v>
       </c>
-      <c r="AB5" t="n">
+      <c r="AN5" t="n">
         <v>25.6015350877193</v>
       </c>
-      <c r="AC5" t="n">
+      <c r="AO5" t="n">
         <v>185.0967105263158</v>
       </c>
-      <c r="AD5" t="n">
+      <c r="AP5" t="n">
         <v>69.89561403508772</v>
       </c>
-      <c r="AE5" t="n">
+      <c r="AQ5" t="n">
         <v>14250.21929824561</v>
       </c>
-      <c r="AF5" t="inlineStr">
+      <c r="AR5" t="inlineStr">
         <is>
           <t>2VSFgl3c</t>
         </is>
       </c>
-      <c r="AG5" t="inlineStr">
+      <c r="AS5" t="inlineStr">
         <is>
           <t>YZPE6Sx7</t>
         </is>
@@ -1097,7 +1301,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">storks s 
+          <t xml:space="preserve">siebert d 
   ger </t>
         </is>
       </c>
@@ -1149,59 +1353,93 @@
       </c>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="n">
+        <v>24.66666666666667</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>181</v>
+      </c>
+      <c r="R6" t="n">
+        <v>74.66666666666667</v>
+      </c>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="n">
+        <v>3</v>
+      </c>
+      <c r="U6" t="n">
+        <v>224</v>
+      </c>
+      <c r="V6" t="n">
+        <v>25.66666666666667</v>
+      </c>
+      <c r="W6" t="n">
+        <v>183</v>
+      </c>
+      <c r="X6" t="n">
+        <v>71.33333333333333</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>14333.33333333333</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>214</v>
+      </c>
+      <c r="AB6" t="n">
         <v>25.04545454545454</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="AC6" t="n">
         <v>182.5727272727273</v>
       </c>
-      <c r="R6" t="n">
+      <c r="AD6" t="n">
         <v>79.38</v>
       </c>
-      <c r="S6" t="n">
+      <c r="AE6" t="n">
         <v>50536.36363636363</v>
       </c>
-      <c r="T6" t="n">
+      <c r="AF6" t="n">
         <v>25.11111111111111</v>
       </c>
-      <c r="U6" t="n">
+      <c r="AG6" t="n">
         <v>184.2592592592592</v>
       </c>
-      <c r="V6" t="n">
+      <c r="AH6" t="n">
         <v>73.37037037037037</v>
       </c>
-      <c r="W6" t="n">
+      <c r="AI6" t="n">
         <v>20370.37037037037</v>
       </c>
-      <c r="X6" t="n">
+      <c r="AJ6" t="n">
         <v>23.83552631578948</v>
       </c>
-      <c r="Y6" t="n">
+      <c r="AK6" t="n">
         <v>183.8643421052631</v>
       </c>
-      <c r="Z6" t="n">
+      <c r="AL6" t="n">
         <v>77.8346052631579</v>
       </c>
-      <c r="AA6" t="n">
+      <c r="AM6" t="n">
         <v>44449.34210526316</v>
       </c>
-      <c r="AB6" t="n">
+      <c r="AN6" t="n">
         <v>24.20149464570517</v>
       </c>
-      <c r="AC6" t="n">
+      <c r="AO6" t="n">
         <v>184.1285714285714</v>
       </c>
-      <c r="AD6" t="n">
+      <c r="AP6" t="n">
         <v>72.23562542720437</v>
       </c>
-      <c r="AE6" t="n">
+      <c r="AQ6" t="n">
         <v>19814.59330143541</v>
       </c>
-      <c r="AF6" t="inlineStr">
+      <c r="AR6" t="inlineStr">
         <is>
           <t>0jdIgO6t</t>
         </is>
       </c>
-      <c r="AG6" t="inlineStr">
+      <c r="AS6" t="inlineStr">
         <is>
           <t>vZA6VYpf</t>
         </is>
@@ -1218,7 +1456,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">badstubner f 
+          <t xml:space="preserve">jablonski s 
   ger </t>
         </is>
       </c>
@@ -1274,57 +1512,93 @@
         </is>
       </c>
       <c r="P7" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>181.4</v>
+      </c>
+      <c r="R7" t="n">
+        <v>76.40000000000001</v>
+      </c>
+      <c r="S7" t="n">
+        <v>39000</v>
+      </c>
+      <c r="T7" t="n">
+        <v>5</v>
+      </c>
+      <c r="U7" t="n">
+        <v>382</v>
+      </c>
+      <c r="V7" t="n">
+        <v>21</v>
+      </c>
+      <c r="W7" t="n">
+        <v>185</v>
+      </c>
+      <c r="X7" t="n">
+        <v>71</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>12000</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>142</v>
+      </c>
+      <c r="AB7" t="n">
         <v>24.02777777777778</v>
       </c>
-      <c r="Q7" t="n">
+      <c r="AC7" t="n">
         <v>184.8784722222222</v>
       </c>
-      <c r="R7" t="n">
+      <c r="AD7" t="n">
         <v>75.68402777777777</v>
       </c>
-      <c r="S7" t="n">
+      <c r="AE7" t="n">
         <v>34618.05555555555</v>
       </c>
-      <c r="T7" t="n">
+      <c r="AF7" t="n">
         <v>23.93131313131313</v>
       </c>
-      <c r="U7" t="n">
+      <c r="AG7" t="n">
         <v>185.8449494949495</v>
       </c>
-      <c r="V7" t="n">
+      <c r="AH7" t="n">
         <v>74.53585858585858</v>
       </c>
-      <c r="W7" t="n">
+      <c r="AI7" t="n">
         <v>26461.61616161616</v>
       </c>
-      <c r="X7" t="n">
+      <c r="AJ7" t="n">
         <v>24.5175</v>
       </c>
-      <c r="Y7" t="n">
+      <c r="AK7" t="n">
         <v>185.4641666666666</v>
       </c>
-      <c r="Z7" t="n">
+      <c r="AL7" t="n">
         <v>74.31583333333333</v>
       </c>
-      <c r="AA7" t="inlineStr"/>
-      <c r="AB7" t="n">
+      <c r="AM7" t="inlineStr"/>
+      <c r="AN7" t="n">
         <v>22.77413140694874</v>
       </c>
-      <c r="AC7" t="n">
+      <c r="AO7" t="n">
         <v>184.3969765099022</v>
       </c>
-      <c r="AD7" t="n">
+      <c r="AP7" t="n">
         <v>72.33625239569513</v>
       </c>
-      <c r="AE7" t="n">
+      <c r="AQ7" t="n">
         <v>22564.41348469212</v>
       </c>
-      <c r="AF7" t="inlineStr">
+      <c r="AR7" t="inlineStr">
         <is>
           <t>hAcTWKKN</t>
         </is>
       </c>
-      <c r="AG7" t="inlineStr">
+      <c r="AS7" t="inlineStr">
         <is>
           <t>IkCftsQm</t>
         </is>
@@ -1341,7 +1615,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">stegemann s 
+          <t xml:space="preserve">zwayer f 
   ger </t>
         </is>
       </c>
@@ -1393,59 +1667,83 @@
         </is>
       </c>
       <c r="P8" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>183.4</v>
+      </c>
+      <c r="R8" t="n">
+        <v>70.40000000000001</v>
+      </c>
+      <c r="S8" t="n">
+        <v>22200</v>
+      </c>
+      <c r="T8" t="n">
+        <v>5</v>
+      </c>
+      <c r="U8" t="n">
+        <v>352</v>
+      </c>
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" t="inlineStr"/>
+      <c r="X8" t="inlineStr"/>
+      <c r="Y8" t="inlineStr"/>
+      <c r="Z8" t="inlineStr"/>
+      <c r="AA8" t="inlineStr"/>
+      <c r="AB8" t="n">
         <v>25.61818181818182</v>
       </c>
-      <c r="Q8" t="n">
+      <c r="AC8" t="n">
         <v>183.5818181818182</v>
       </c>
-      <c r="R8" t="n">
+      <c r="AD8" t="n">
         <v>82.56363636363636</v>
       </c>
-      <c r="S8" t="n">
+      <c r="AE8" t="n">
         <v>78109.09090909091</v>
       </c>
-      <c r="T8" t="n">
+      <c r="AF8" t="n">
         <v>25.02373737373737</v>
       </c>
-      <c r="U8" t="n">
+      <c r="AG8" t="n">
         <v>183.8082491582491</v>
       </c>
-      <c r="V8" t="n">
+      <c r="AH8" t="n">
         <v>80.78703703703704</v>
       </c>
-      <c r="W8" t="n">
+      <c r="AI8" t="n">
         <v>55135.35353535353</v>
       </c>
-      <c r="X8" t="n">
+      <c r="AJ8" t="n">
         <v>26.15</v>
       </c>
-      <c r="Y8" t="n">
+      <c r="AK8" t="n">
         <v>183.6061594202898</v>
       </c>
-      <c r="Z8" t="n">
+      <c r="AL8" t="n">
         <v>81.45495169082126</v>
       </c>
-      <c r="AA8" t="n">
+      <c r="AM8" t="n">
         <v>75471.37681159421</v>
       </c>
-      <c r="AB8" t="n">
+      <c r="AN8" t="n">
         <v>24.08611111111111</v>
       </c>
-      <c r="AC8" t="n">
+      <c r="AO8" t="n">
         <v>181.1259259259259</v>
       </c>
-      <c r="AD8" t="n">
+      <c r="AP8" t="n">
         <v>79.21879208754208</v>
       </c>
-      <c r="AE8" t="n">
+      <c r="AQ8" t="n">
         <v>51963.02609427609</v>
       </c>
-      <c r="AF8" t="inlineStr">
+      <c r="AR8" t="inlineStr">
         <is>
           <t>4fuCGs9P</t>
         </is>
       </c>
-      <c r="AG8" t="inlineStr">
+      <c r="AS8" t="inlineStr">
         <is>
           <t>f3ddUIXs</t>
         </is>
@@ -1518,59 +1816,95 @@
         </is>
       </c>
       <c r="P9" t="n">
+        <v>24</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>190.6666666666667</v>
+      </c>
+      <c r="R9" t="n">
+        <v>68</v>
+      </c>
+      <c r="S9" t="n">
+        <v>8000</v>
+      </c>
+      <c r="T9" t="n">
+        <v>3</v>
+      </c>
+      <c r="U9" t="n">
+        <v>204</v>
+      </c>
+      <c r="V9" t="n">
+        <v>25.5</v>
+      </c>
+      <c r="W9" t="n">
+        <v>180.5</v>
+      </c>
+      <c r="X9" t="n">
+        <v>71</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>22500</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>142</v>
+      </c>
+      <c r="AB9" t="n">
         <v>25.70138888888889</v>
       </c>
-      <c r="Q9" t="n">
+      <c r="AC9" t="n">
         <v>185.9534722222222</v>
       </c>
-      <c r="R9" t="n">
+      <c r="AD9" t="n">
         <v>68.55902777777777</v>
       </c>
-      <c r="S9" t="n">
+      <c r="AE9" t="n">
         <v>10261.11111111111</v>
       </c>
-      <c r="T9" t="n">
+      <c r="AF9" t="n">
         <v>24.38181818181818</v>
       </c>
-      <c r="U9" t="n">
+      <c r="AG9" t="n">
         <v>185.4545454545455</v>
       </c>
-      <c r="V9" t="n">
+      <c r="AH9" t="n">
         <v>76.78181818181818</v>
       </c>
-      <c r="W9" t="n">
+      <c r="AI9" t="n">
         <v>34290.90909090909</v>
       </c>
-      <c r="X9" t="n">
+      <c r="AJ9" t="n">
         <v>24.62807189542483</v>
       </c>
-      <c r="Y9" t="n">
+      <c r="AK9" t="n">
         <v>185.241454248366</v>
       </c>
-      <c r="Z9" t="n">
+      <c r="AL9" t="n">
         <v>67.33888888888889</v>
       </c>
-      <c r="AA9" t="n">
+      <c r="AM9" t="n">
         <v>8659.346405228756</v>
       </c>
-      <c r="AB9" t="n">
+      <c r="AN9" t="n">
         <v>20.98406698564593</v>
       </c>
-      <c r="AC9" t="n">
+      <c r="AO9" t="n">
         <v>185.5145933014354</v>
       </c>
-      <c r="AD9" t="n">
+      <c r="AP9" t="n">
         <v>70.57325358851674</v>
       </c>
-      <c r="AE9" t="n">
+      <c r="AQ9" t="n">
         <v>16901.31578947369</v>
       </c>
-      <c r="AF9" t="inlineStr">
+      <c r="AR9" t="inlineStr">
         <is>
           <t>8f6APkLc</t>
         </is>
       </c>
-      <c r="AG9" t="inlineStr">
+      <c r="AS9" t="inlineStr">
         <is>
           <t>M5BRZDsC</t>
         </is>
@@ -1643,1168 +1977,97 @@
         </is>
       </c>
       <c r="P10" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>181</v>
+      </c>
+      <c r="R10" t="n">
+        <v>74.8</v>
+      </c>
+      <c r="S10" t="n">
+        <v>28200</v>
+      </c>
+      <c r="T10" t="n">
+        <v>5</v>
+      </c>
+      <c r="U10" t="n">
+        <v>374</v>
+      </c>
+      <c r="V10" t="n">
+        <v>26</v>
+      </c>
+      <c r="W10" t="n">
+        <v>185.5</v>
+      </c>
+      <c r="X10" t="n">
+        <v>73.5</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>18500</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>147</v>
+      </c>
+      <c r="AB10" t="n">
         <v>26.85111111111111</v>
       </c>
-      <c r="Q10" t="n">
+      <c r="AC10" t="n">
         <v>186.1177777777778</v>
       </c>
-      <c r="R10" t="n">
+      <c r="AD10" t="n">
         <v>74.50222222222223</v>
       </c>
-      <c r="S10" t="n">
+      <c r="AE10" t="n">
         <v>28540</v>
       </c>
-      <c r="T10" t="n">
+      <c r="AF10" t="n">
         <v>26.08181818181818</v>
       </c>
-      <c r="U10" t="n">
+      <c r="AG10" t="n">
         <v>183.5836363636363</v>
       </c>
-      <c r="V10" t="n">
+      <c r="AH10" t="n">
         <v>73.82909090909091</v>
       </c>
-      <c r="W10" t="n">
+      <c r="AI10" t="n">
         <v>19249.0909090909</v>
       </c>
-      <c r="X10" t="n">
+      <c r="AJ10" t="n">
         <v>23.52787539258128</v>
       </c>
-      <c r="Y10" t="n">
+      <c r="AK10" t="n">
         <v>184.4787624140565</v>
       </c>
-      <c r="Z10" t="n">
+      <c r="AL10" t="n">
         <v>71.59161361514302</v>
       </c>
-      <c r="AA10" t="n">
+      <c r="AM10" t="n">
         <v>19751.72735760971</v>
       </c>
-      <c r="AB10" t="n">
+      <c r="AN10" t="n">
         <v>23.80409982174688</v>
       </c>
-      <c r="AC10" t="n">
+      <c r="AO10" t="n">
         <v>185.9703149138443</v>
       </c>
-      <c r="AD10" t="n">
+      <c r="AP10" t="n">
         <v>69.93321449792037</v>
       </c>
-      <c r="AE10" t="n">
+      <c r="AQ10" t="n">
         <v>12631.44385026738</v>
       </c>
-      <c r="AF10" t="inlineStr">
+      <c r="AR10" t="inlineStr">
         <is>
           <t>hpYJ6izc</t>
         </is>
       </c>
-      <c r="AG10" t="inlineStr">
+      <c r="AS10" t="inlineStr">
         <is>
           <t>K6A2elS9</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>UajsPCkT</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="n">
-        <v>45569.64583333334</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">welz t 
-  ger </t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">wwk arena
-  augsburg </t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>30660</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>fTVNku3I</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>88HSzjDr</t>
-        </is>
-      </c>
-      <c r="H11" t="n">
-        <v>59</v>
-      </c>
-      <c r="I11" t="n">
-        <v>591</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>bundesliga</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>WG9pOTse</t>
-        </is>
-      </c>
-      <c r="P11" t="n">
-        <v>25.11111111111111</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>184.2592592592592</v>
-      </c>
-      <c r="R11" t="n">
-        <v>73.37037037037037</v>
-      </c>
-      <c r="S11" t="n">
-        <v>20370.37037037037</v>
-      </c>
-      <c r="T11" t="n">
-        <v>25.30909090909091</v>
-      </c>
-      <c r="U11" t="n">
-        <v>184.3272727272727</v>
-      </c>
-      <c r="V11" t="n">
-        <v>75.81818181818181</v>
-      </c>
-      <c r="W11" t="n">
-        <v>23909.09090909091</v>
-      </c>
-      <c r="X11" t="n">
-        <v>24.20149464570517</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>184.1285714285714</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>72.23562542720437</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>19814.59330143541</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>24.60195652173913</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>183.6065942028985</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>73.47898550724638</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>20201.66666666667</v>
-      </c>
-      <c r="AF11" t="inlineStr">
-        <is>
-          <t>2VSFgl3c</t>
-        </is>
-      </c>
-      <c r="AG11" t="inlineStr">
-        <is>
-          <t>M5BRZDsC</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>tbtaPLqC</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="n">
-        <v>45570.4375</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">petersen m 
-  ger </t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">bayarena
-  leverkusen </t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>30210</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>4jcj2zMd</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>63WsD2ei</t>
-        </is>
-      </c>
-      <c r="H12" t="n">
-        <v>59</v>
-      </c>
-      <c r="I12" t="n">
-        <v>591</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>bundesliga</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>WG9pOTse</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>ILyJuN3g</t>
-        </is>
-      </c>
-      <c r="P12" t="n">
-        <v>25.02373737373737</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>183.8082491582491</v>
-      </c>
-      <c r="R12" t="n">
-        <v>80.78703703703704</v>
-      </c>
-      <c r="S12" t="n">
-        <v>55135.35353535353</v>
-      </c>
-      <c r="T12" t="n">
-        <v>25.70138888888889</v>
-      </c>
-      <c r="U12" t="n">
-        <v>185.9534722222222</v>
-      </c>
-      <c r="V12" t="n">
-        <v>68.55902777777777</v>
-      </c>
-      <c r="W12" t="n">
-        <v>10261.11111111111</v>
-      </c>
-      <c r="X12" t="n">
-        <v>24.08611111111111</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>181.1259259259259</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>79.21879208754208</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>51963.02609427609</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>24.62807189542483</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>185.241454248366</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>67.33888888888889</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>8659.346405228756</v>
-      </c>
-      <c r="AF12" t="inlineStr">
-        <is>
-          <t>hAcTWKKN</t>
-        </is>
-      </c>
-      <c r="AG12" t="inlineStr">
-        <is>
-          <t>A15eUM4C</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>ENOasf5c</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="n">
-        <v>45570.4375</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stegemann s 
-  ger </t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">vonovia ruhrstadion
-  bochum </t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>26000</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>8Y2m6ADe</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>nwkTahLL</t>
-        </is>
-      </c>
-      <c r="H13" t="n">
-        <v>59</v>
-      </c>
-      <c r="I13" t="n">
-        <v>591</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>bundesliga</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>0Ija0Ej9</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>dfNCCCzS</t>
-        </is>
-      </c>
-      <c r="P13" t="n">
-        <v>26.57555555555556</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>184.2626262626263</v>
-      </c>
-      <c r="R13" t="n">
-        <v>71.74383838383838</v>
-      </c>
-      <c r="S13" t="n">
-        <v>15590.10101010101</v>
-      </c>
-      <c r="T13" t="n">
-        <v>24.02777777777778</v>
-      </c>
-      <c r="U13" t="n">
-        <v>184.8784722222222</v>
-      </c>
-      <c r="V13" t="n">
-        <v>75.68402777777777</v>
-      </c>
-      <c r="W13" t="n">
-        <v>34618.05555555555</v>
-      </c>
-      <c r="X13" t="n">
-        <v>23.281004784689</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>183.2587559808613</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>68.37066985645933</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>12168.94736842106</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>24.5175</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>185.4641666666666</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>74.31583333333333</v>
-      </c>
-      <c r="AE13" t="inlineStr"/>
-      <c r="AF13" t="inlineStr">
-        <is>
-          <t>8f6APkLc</t>
-        </is>
-      </c>
-      <c r="AG13" t="inlineStr">
-        <is>
-          <t>f3ddUIXs</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>lpXDJjDj</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="n">
-        <v>45570.4375</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">badstubner f 
-  ger </t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">stadion an der alten forsterei
-  berlin </t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>22012</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>pzHW4oaE</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>nP1i5US1</t>
-        </is>
-      </c>
-      <c r="H14" t="n">
-        <v>59</v>
-      </c>
-      <c r="I14" t="n">
-        <v>591</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>bundesliga</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>0Ija0Ej9</t>
-        </is>
-      </c>
-      <c r="P14" t="n">
-        <v>26.26545454545455</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>186.3274747474747</v>
-      </c>
-      <c r="R14" t="n">
-        <v>75.02161616161615</v>
-      </c>
-      <c r="S14" t="n">
-        <v>26052.12121212121</v>
-      </c>
-      <c r="T14" t="n">
-        <v>25.8</v>
-      </c>
-      <c r="U14" t="n">
-        <v>185.8727272727273</v>
-      </c>
-      <c r="V14" t="n">
-        <v>81.03636363636363</v>
-      </c>
-      <c r="W14" t="n">
-        <v>51963.63636363636</v>
-      </c>
-      <c r="X14" t="n">
-        <v>25.13500345065562</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>182.9532505175983</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>71.8504347826087</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>20348.68184955141</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>23.45210144927536</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>181.9110869565217</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>77.47789855072463</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>38547.22222222222</v>
-      </c>
-      <c r="AF14" t="inlineStr">
-        <is>
-          <t>hpYJ6izc</t>
-        </is>
-      </c>
-      <c r="AG14" t="inlineStr">
-        <is>
-          <t>IkCftsQm</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>dnhZQYKG</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="n">
-        <v>45570.4375</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">brand b 
-  ger </t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">weserstadion
-  bremen </t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>42100</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Ig1f1fy3</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>fiEQZ7C7</t>
-        </is>
-      </c>
-      <c r="H15" t="n">
-        <v>59</v>
-      </c>
-      <c r="I15" t="n">
-        <v>591</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>bundesliga</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>v9k3aY5F</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>nJQmYp1B</t>
-        </is>
-      </c>
-      <c r="P15" t="n">
-        <v>26.08181818181818</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>183.5836363636363</v>
-      </c>
-      <c r="R15" t="n">
-        <v>73.82909090909091</v>
-      </c>
-      <c r="S15" t="n">
-        <v>19249.0909090909</v>
-      </c>
-      <c r="T15" t="n">
-        <v>25.61777777777778</v>
-      </c>
-      <c r="U15" t="n">
-        <v>183.8466666666666</v>
-      </c>
-      <c r="V15" t="n">
-        <v>75.42222222222222</v>
-      </c>
-      <c r="W15" t="n">
-        <v>23186.66666666666</v>
-      </c>
-      <c r="X15" t="n">
-        <v>23.80409982174688</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>185.9703149138443</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>69.93321449792037</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>12631.44385026738</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>25.77300860847771</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>183.3849614153962</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>74.32666448730522</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>21868.25363804768</v>
-      </c>
-      <c r="AF15" t="inlineStr">
-        <is>
-          <t>4fuCGs9P</t>
-        </is>
-      </c>
-      <c r="AG15" t="inlineStr">
-        <is>
-          <t>YZPE6Sx7</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>zwD8uYZ9</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="n">
-        <v>45570.5625</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">storks s 
-  ger </t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">millerntor stadion
-  hamburg </t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>29546</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>ILyJuN3g</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>EuakNmc1</t>
-        </is>
-      </c>
-      <c r="H16" t="n">
-        <v>59</v>
-      </c>
-      <c r="I16" t="n">
-        <v>591</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>bundesliga</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>v9k3aY5F</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>8vndvXTk</t>
-        </is>
-      </c>
-      <c r="P16" t="n">
-        <v>25.68363636363637</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>185.6927272727273</v>
-      </c>
-      <c r="R16" t="n">
-        <v>70.31818181818183</v>
-      </c>
-      <c r="S16" t="n">
-        <v>11380</v>
-      </c>
-      <c r="T16" t="n">
-        <v>26.57111111111111</v>
-      </c>
-      <c r="U16" t="n">
-        <v>183.4333333333333</v>
-      </c>
-      <c r="V16" t="n">
-        <v>74.55999999999999</v>
-      </c>
-      <c r="W16" t="n">
-        <v>22895.55555555555</v>
-      </c>
-      <c r="X16" t="n">
-        <v>24.60104575163398</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>184.1977261781906</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>69.03089095287238</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>10354.92604059168</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>25.09464494569758</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>184.0522055137845</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>71.24617376775271</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>15664.36090225564</v>
-      </c>
-      <c r="AF16" t="inlineStr">
-        <is>
-          <t>0jdIgO6t</t>
-        </is>
-      </c>
-      <c r="AG16" t="inlineStr">
-        <is>
-          <t>vZA6VYpf</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>0KbQSfj4</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="n">
-        <v>45571.4375</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">hartmann r 
-  ger </t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">voith arena
-  heidenheim </t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>15000</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>KWixEVWi</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>KbS1suSm</t>
-        </is>
-      </c>
-      <c r="H17" t="n">
-        <v>59</v>
-      </c>
-      <c r="I17" t="n">
-        <v>591</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>bundesliga</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>nP1i5US1</t>
-        </is>
-      </c>
-      <c r="P17" t="n">
-        <v>26.21388888888889</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>188.2305555555556</v>
-      </c>
-      <c r="R17" t="n">
-        <v>72.07222222222222</v>
-      </c>
-      <c r="S17" t="n">
-        <v>18702.77777777777</v>
-      </c>
-      <c r="T17" t="n">
-        <v>25.04545454545454</v>
-      </c>
-      <c r="U17" t="n">
-        <v>182.5727272727273</v>
-      </c>
-      <c r="V17" t="n">
-        <v>79.38</v>
-      </c>
-      <c r="W17" t="n">
-        <v>50536.36363636363</v>
-      </c>
-      <c r="X17" t="n">
-        <v>25.6015350877193</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>185.0967105263158</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>69.89561403508772</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>14250.21929824561</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>23.83552631578948</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>183.8643421052631</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>77.8346052631579</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>44449.34210526316</v>
-      </c>
-      <c r="AF17" t="inlineStr">
-        <is>
-          <t>4ljanukM</t>
-        </is>
-      </c>
-      <c r="AG17" t="inlineStr">
-        <is>
-          <t>pfoInmcq</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>ShoJUGLi</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="n">
-        <v>45571.52083333334</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">dankert b 
-  ger </t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">deutsche bank park
-  frankfurt </t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>58000</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>8vndvXTk</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>nVp0wiqd</t>
-        </is>
-      </c>
-      <c r="H18" t="n">
-        <v>59</v>
-      </c>
-      <c r="I18" t="n">
-        <v>591</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>bundesliga</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>EuakNmc1</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr"/>
-      <c r="P18" t="n">
-        <v>24.38181818181818</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>185.4545454545455</v>
-      </c>
-      <c r="R18" t="n">
-        <v>76.78181818181818</v>
-      </c>
-      <c r="S18" t="n">
-        <v>34290.90909090909</v>
-      </c>
-      <c r="T18" t="n">
-        <v>25.61818181818182</v>
-      </c>
-      <c r="U18" t="n">
-        <v>183.5818181818182</v>
-      </c>
-      <c r="V18" t="n">
-        <v>82.56363636363636</v>
-      </c>
-      <c r="W18" t="n">
-        <v>78109.09090909091</v>
-      </c>
-      <c r="X18" t="n">
-        <v>20.98406698564593</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>185.5145933014354</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>70.57325358851674</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>16901.31578947369</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>26.15</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>183.6061594202898</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>81.45495169082126</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>75471.37681159421</v>
-      </c>
-      <c r="AF18" t="inlineStr">
-        <is>
-          <t>UgdQz0fK</t>
-        </is>
-      </c>
-      <c r="AG18" t="inlineStr">
-        <is>
-          <t>K6A2elS9</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>nc8W6DTp</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="n">
-        <v>45571.60416666666</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">jollenbeck m 
-  ger </t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mhparena
-  stuttgart </t>
-        </is>
-      </c>
-      <c r="E19" t="n">
-        <v>60449</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>nJQmYp1B</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>hQAtP9Sl</t>
-        </is>
-      </c>
-      <c r="H19" t="n">
-        <v>59</v>
-      </c>
-      <c r="I19" t="n">
-        <v>591</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>bundesliga</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>fiEQZ7C7</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>nJQmYp1B</t>
-        </is>
-      </c>
-      <c r="P19" t="n">
-        <v>23.93131313131313</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>185.8449494949495</v>
-      </c>
-      <c r="R19" t="n">
-        <v>74.53585858585858</v>
-      </c>
-      <c r="S19" t="n">
-        <v>26461.61616161616</v>
-      </c>
-      <c r="T19" t="n">
-        <v>26.85111111111111</v>
-      </c>
-      <c r="U19" t="n">
-        <v>186.1177777777778</v>
-      </c>
-      <c r="V19" t="n">
-        <v>74.50222222222223</v>
-      </c>
-      <c r="W19" t="n">
-        <v>28540</v>
-      </c>
-      <c r="X19" t="n">
-        <v>22.77413140694874</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>184.3969765099022</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>72.33625239569513</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>22564.41348469212</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>23.52787539258128</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>184.4787624140565</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>71.59161361514302</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>19751.72735760971</v>
-      </c>
-      <c r="AF19" t="inlineStr">
-        <is>
-          <t>GzfvcwRj</t>
-        </is>
-      </c>
-      <c r="AG19" t="inlineStr">
-        <is>
-          <t>KUx4Q7x1</t>
         </is>
       </c>
     </row>

--- a/data/germany/p6_deployment/data_preparation/df_filled.xlsx
+++ b/data/germany/p6_deployment/data_preparation/df_filled.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AS3"/>
+  <dimension ref="A1:BG16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -495,42 +495,42 @@
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>id_team_home_rival_team</t>
+          <t>mean_age_player_miss_home</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>id_team_away_rival_team</t>
+          <t>mean_hei_player_miss_home</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>mean_age_player_miss_home</t>
+          <t>n_player_miss_home</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>mean_hei_player_miss_home</t>
+          <t>sum_rat_player_miss_home</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>mean_rat_player_miss_home</t>
+          <t>sum_wage_player_miss_home</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>mean_wage_player_miss_home</t>
+          <t>sum_value_player_miss_home</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>n_player_miss_home</t>
+          <t>sum_pot_player_miss_home</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>sum_rat_player_miss_home</t>
+          <t>sum_rep_player_miss_home</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
@@ -545,110 +545,180 @@
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>mean_rat_player_miss_away</t>
+          <t>n_player_miss_away</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>mean_wage_player_miss_away</t>
+          <t>sum_rat_player_miss_away</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>n_player_miss_away</t>
+          <t>sum_wage_player_miss_away</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>sum_rat_player_miss_away</t>
+          <t>sum_value_player_miss_away</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
+          <t>sum_pot_player_miss_away</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>sum_rep_player_miss_away</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
           <t>mean_age_player_start_home</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>mean_hei_player_start_home</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>mean_rat_player_start_home</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>mean_wage_player_start_home</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>mean_value_player_start_home</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>mean_pot_player_start_home</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>mean_rep_player_start_home</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>mean_age_player_start_away</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>mean_hei_player_start_away</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>mean_rat_player_start_away</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>mean_wage_player_start_away</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>mean_value_player_start_away</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>mean_pot_player_start_away</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>mean_rep_player_start_away</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>mean_age_player_sub_home</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>mean_hei_player_sub_home</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>mean_rat_player_sub_home</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>mean_wage_player_sub_home</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>mean_value_player_sub_home</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>mean_pot_player_sub_home</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>mean_rep_player_sub_home</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
         <is>
           <t>mean_age_player_sub_away</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AZ1" s="1" t="inlineStr">
         <is>
           <t>mean_hei_player_sub_away</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="BA1" s="1" t="inlineStr">
         <is>
           <t>mean_rat_player_sub_away</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="BB1" s="1" t="inlineStr">
         <is>
           <t>mean_wage_player_sub_away</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="BC1" s="1" t="inlineStr">
+        <is>
+          <t>mean_value_player_sub_away</t>
+        </is>
+      </c>
+      <c r="BD1" s="1" t="inlineStr">
+        <is>
+          <t>mean_pot_player_sub_away</t>
+        </is>
+      </c>
+      <c r="BE1" s="1" t="inlineStr">
+        <is>
+          <t>mean_rep_player_sub_away</t>
+        </is>
+      </c>
+      <c r="BF1" s="1" t="inlineStr">
         <is>
           <t>id_coach_home</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="BG1" s="1" t="inlineStr">
         <is>
           <t>id_coach_away</t>
         </is>
@@ -657,35 +727,35 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>pWnjRsFa</t>
+          <t>UajsPCkT</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45564.4375</v>
+        <v>45569.64583333334</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">stieler t 
+          <t xml:space="preserve">badstubner f 
   ger </t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">holstein stadion
-  kiel </t>
+          <t xml:space="preserve">wwk arena
+  augsburg </t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>15034</v>
+        <v>30660</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>63WsD2ei</t>
+          <t>fTVNku3I</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>8vndvXTk</t>
+          <t>88HSzjDr</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -710,269 +780,2724 @@
           <t>bundesliga</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>ILyJuN3g</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>EuakNmc1</t>
-        </is>
+      <c r="N2" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="O2" t="n">
+        <v>180.6</v>
       </c>
       <c r="P2" t="n">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="Q2" t="n">
-        <v>193.5</v>
+        <v>348</v>
       </c>
       <c r="R2" t="n">
-        <v>68.5</v>
+        <v>83000</v>
       </c>
       <c r="S2" t="n">
-        <v>8500</v>
+        <v>13325000</v>
       </c>
       <c r="T2" t="n">
-        <v>2</v>
+        <v>361</v>
       </c>
       <c r="U2" t="n">
-        <v>137</v>
+        <v>5</v>
       </c>
       <c r="V2" t="n">
-        <v>19</v>
+        <v>23.5</v>
       </c>
       <c r="W2" t="n">
-        <v>172</v>
+        <v>182.8333333333333</v>
       </c>
       <c r="X2" t="n">
-        <v>59</v>
+        <v>6</v>
       </c>
       <c r="Y2" t="n">
-        <v>3000</v>
+        <v>424</v>
       </c>
       <c r="Z2" t="n">
-        <v>1</v>
+        <v>96000</v>
       </c>
       <c r="AA2" t="n">
-        <v>59</v>
+        <v>39725000</v>
       </c>
       <c r="AB2" t="n">
-        <v>25.70138888888889</v>
+        <v>466</v>
       </c>
       <c r="AC2" t="n">
-        <v>185.9534722222222</v>
+        <v>8</v>
       </c>
       <c r="AD2" t="n">
-        <v>68.55902777777777</v>
+        <v>25.79166666666667</v>
       </c>
       <c r="AE2" t="n">
-        <v>10261.11111111111</v>
+        <v>185.0416666666667</v>
       </c>
       <c r="AF2" t="n">
-        <v>24.38181818181818</v>
+        <v>73.70833333333333</v>
       </c>
       <c r="AG2" t="n">
-        <v>185.4545454545455</v>
+        <v>22291.66666666667</v>
       </c>
       <c r="AH2" t="n">
-        <v>76.78181818181818</v>
+        <v>5350000</v>
       </c>
       <c r="AI2" t="n">
-        <v>34290.90909090909</v>
+        <v>76.91666666666667</v>
       </c>
       <c r="AJ2" t="n">
-        <v>24.62807189542483</v>
+        <v>1.125</v>
       </c>
       <c r="AK2" t="n">
-        <v>185.241454248366</v>
+        <v>26.13333333333334</v>
       </c>
       <c r="AL2" t="n">
-        <v>67.33888888888889</v>
+        <v>184.65</v>
       </c>
       <c r="AM2" t="n">
-        <v>8659.346405228756</v>
+        <v>75.55</v>
       </c>
       <c r="AN2" t="n">
-        <v>20.98406698564593</v>
+        <v>24516.66666666667</v>
       </c>
       <c r="AO2" t="n">
-        <v>185.5145933014354</v>
+        <v>8460000</v>
       </c>
       <c r="AP2" t="n">
-        <v>70.57325358851674</v>
+        <v>77.98333333333333</v>
       </c>
       <c r="AQ2" t="n">
-        <v>16901.31578947369</v>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>8f6APkLc</t>
-        </is>
-      </c>
-      <c r="AS2" t="inlineStr">
-        <is>
-          <t>M5BRZDsC</t>
+        <v>1.5</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>24.70897739744489</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>184.1469137229586</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>72.43944443141424</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>21145.91621470492</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>4947826.455808267</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>76.57492066470394</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>1.16975030974644</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>25.55264065962007</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>183.6602557117432</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>73.58824143692566</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>22408.07180995968</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>6264900.021793614</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>77.50048127565289</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>1.212310667974284</v>
+      </c>
+      <c r="BF2" t="inlineStr">
+        <is>
+          <t>pfoInmcq</t>
+        </is>
+      </c>
+      <c r="BG2" t="inlineStr">
+        <is>
+          <t>hpYJ6izc</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>bFO8E4Vg</t>
+          <t>tbtaPLqC</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45564.52083333334</v>
+        <v>45570.4375</v>
       </c>
       <c r="C3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stieler t 
+  ger </t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bayarena
+  leverkusen </t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>30210</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>4jcj2zMd</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>63WsD2ei</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>59</v>
+      </c>
+      <c r="I3" t="n">
+        <v>591</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="n">
+        <v>25</v>
+      </c>
+      <c r="W3" t="n">
+        <v>193.5</v>
+      </c>
+      <c r="X3" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>138</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>29000</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>3800000</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>147</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>26.35787037037037</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>184.4333333333333</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>83.63009259259259</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>98558.33333333333</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>49468750</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>85.83888888888889</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>3.025</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>26.66839225589226</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>185.7753367003367</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>69.92592592592592</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>16646.92760942761</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>1912622.053872054</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>72.23021885521887</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>24.53296406281811</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>180.5564682013156</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>80.85853288683894</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>82395.97593423336</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>40250463.78200404</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>84.65014075805762</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>2.317095259156293</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>25.47224310776943</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>185.0112364243943</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>68.16849067112224</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>15489.62684489</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>1845626.56641604</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>72.70550682261209</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF3" t="inlineStr">
+        <is>
+          <t>K6A2elS9</t>
+        </is>
+      </c>
+      <c r="BG3" t="inlineStr">
+        <is>
+          <t>UgdQz0fK</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>ENOasf5c</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>45570.4375</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">burda m 
+  ger </t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vonovia ruhrstadion
+  bochum </t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>26000</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>8Y2m6ADe</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>nwkTahLL</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>59</v>
+      </c>
+      <c r="I4" t="n">
+        <v>591</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="N4" t="n">
+        <v>24</v>
+      </c>
+      <c r="O4" t="n">
+        <v>185.5</v>
+      </c>
+      <c r="P4" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>136</v>
+      </c>
+      <c r="R4" t="n">
+        <v>32000</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5575000</v>
+      </c>
+      <c r="T4" t="n">
+        <v>147</v>
+      </c>
+      <c r="U4" t="n">
+        <v>2</v>
+      </c>
+      <c r="V4" t="n">
+        <v>23.57142857142857</v>
+      </c>
+      <c r="W4" t="n">
+        <v>182.5714285714286</v>
+      </c>
+      <c r="X4" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>520</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>244000</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>76100000</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>558</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>11</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>28.05666666666666</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>185.1505555555555</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>71.58555555555554</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>16957.77777777778</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>2249013.888888889</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>73.66055555555556</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>24.70833333333333</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>184.7083333333333</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>75.2986111111111</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>36312.5</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>10284953.7037037</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>79.89814814814814</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>1.418981481481481</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>25.24211011440113</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>185.612326127032</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>68.23141973838568</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>14886.9020842705</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>1770742.648161379</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>74.39888024485548</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>24.66797385620915</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>185.0577205882353</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>72.91958061002178</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>32168.57298474945</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>7789857.02614379</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>78.20927287581699</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>1.333428649237473</v>
+      </c>
+      <c r="BF4" t="inlineStr">
+        <is>
+          <t>IkCftsQm</t>
+        </is>
+      </c>
+      <c r="BG4" t="inlineStr">
+        <is>
+          <t>GzfvcwRj</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>lpXDJjDj</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>45570.4375</v>
+      </c>
+      <c r="C5" t="inlineStr">
         <is>
           <t xml:space="preserve">reichel t 
   ger </t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadion an der alten forsterei
+  berlin </t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>22012</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>pzHW4oaE</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>nP1i5US1</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>59</v>
+      </c>
+      <c r="I5" t="n">
+        <v>591</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="N5" t="n">
+        <v>28</v>
+      </c>
+      <c r="O5" t="n">
+        <v>181</v>
+      </c>
+      <c r="P5" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>146</v>
+      </c>
+      <c r="R5" t="n">
+        <v>58000</v>
+      </c>
+      <c r="S5" t="n">
+        <v>8600000</v>
+      </c>
+      <c r="T5" t="n">
+        <v>146</v>
+      </c>
+      <c r="U5" t="n">
+        <v>2</v>
+      </c>
+      <c r="V5" t="n">
+        <v>22.66666666666667</v>
+      </c>
+      <c r="W5" t="n">
+        <v>180.3333333333333</v>
+      </c>
+      <c r="X5" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>237</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>133000</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>92500000</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>253</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>7</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>27.1026936026936</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>186.356228956229</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>75.03198653198653</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>28156.39730639731</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>6726599.326599326</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>77.46144781144781</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>1.421380471380472</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>26.71666666666667</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>186.0545454545454</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>82.01363636363635</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>58143.93939393939</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>37515909.09090909</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>84.09696969696969</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>2.63030303030303</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>26.28750287554636</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>182.9943754313319</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>73.0883597883598</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>24678.21486082356</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>4189991.948470209</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>76.11999079825168</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>1.176386013342535</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>24.649016563147</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>183.9863103080494</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>77.62367620302403</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>42621.67325428195</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>22335895.13143861</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>83.02270060857018</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>1.854321161929858</v>
+      </c>
+      <c r="BF5" t="inlineStr">
+        <is>
+          <t>M5BRZDsC</t>
+        </is>
+      </c>
+      <c r="BG5" t="inlineStr">
+        <is>
+          <t>8f6APkLc</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>dnhZQYKG</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>45570.4375</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">welz t 
+  ger </t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">weserstadion
+  bremen </t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>42100</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Ig1f1fy3</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>fiEQZ7C7</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>59</v>
+      </c>
+      <c r="I6" t="n">
+        <v>591</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="N6" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="O6" t="n">
+        <v>189</v>
+      </c>
+      <c r="P6" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>147</v>
+      </c>
+      <c r="R6" t="n">
+        <v>46000</v>
+      </c>
+      <c r="S6" t="n">
+        <v>6500000</v>
+      </c>
+      <c r="T6" t="n">
+        <v>148</v>
+      </c>
+      <c r="U6" t="n">
+        <v>2</v>
+      </c>
+      <c r="V6" t="n">
+        <v>24.66666666666667</v>
+      </c>
+      <c r="W6" t="n">
+        <v>185.8333333333333</v>
+      </c>
+      <c r="X6" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>423</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>101000</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>26000000</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>454</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>6</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>27.06818181818182</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>183.6530303030303</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>74.53939393939395</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>23595.45454545454</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>6047121.212121212</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>76.77424242424242</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>1.095454545454545</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>26.73518518518519</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>183.7101851851852</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>76.02638888888889</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>26159.72222222222</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>10543888.88888889</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>78.63101851851852</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>1.606018518518519</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>24.44462991030497</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>186.7074735587322</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>70.49606751837872</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>19186.5910384217</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>3572388.013291903</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>76.78116404317778</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>26.86084050706476</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>183.3518257105214</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>74.39824643955079</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>24267.14051267827</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>7185075.060014992</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>76.81051649215264</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>1.408638443935927</v>
+      </c>
+      <c r="BF6" t="inlineStr">
+        <is>
+          <t>KUx4Q7x1</t>
+        </is>
+      </c>
+      <c r="BG6" t="inlineStr">
+        <is>
+          <t>0jdIgO6t</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>zwD8uYZ9</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>45570.5625</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dingert c 
+  ger </t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">millerntor stadion
+  hamburg </t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>29546</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>ILyJuN3g</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>EuakNmc1</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>59</v>
+      </c>
+      <c r="I7" t="n">
+        <v>591</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="N7" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="O7" t="n">
+        <v>187</v>
+      </c>
+      <c r="P7" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>326</v>
+      </c>
+      <c r="R7" t="n">
+        <v>71000</v>
+      </c>
+      <c r="S7" t="n">
+        <v>3310000</v>
+      </c>
+      <c r="T7" t="n">
+        <v>335</v>
+      </c>
+      <c r="U7" t="n">
+        <v>5</v>
+      </c>
+      <c r="V7" t="n">
+        <v>27</v>
+      </c>
+      <c r="W7" t="n">
+        <v>185</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>76</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>26000</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>8000000</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>78</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>26.79141414141414</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>185.4481481481481</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>70.55235690235691</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>17073.90572390573</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>2309494.94949495</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>73.50185185185185</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>27.66111111111111</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>183.4018518518519</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>74.87777777777778</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>25170.37037037037</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>6554629.62962963</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>76.90925925925926</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>1.411111111111111</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>25.52275828460039</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>184.5858674463937</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>68.49556530214424</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>16164.32748538012</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>1827714.424951267</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>72.08396686159844</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>25.99150527834739</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>183.8311460469355</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>71.37496392496392</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>21557.77322093112</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>3239910.334548492</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>76.42352851826536</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>1.130392268550163</v>
+      </c>
+      <c r="BF7" t="inlineStr">
+        <is>
+          <t>YZPE6Sx7</t>
+        </is>
+      </c>
+      <c r="BG7" t="inlineStr">
+        <is>
+          <t>4ljanukM</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>0KbQSfj4</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>45571.4375</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">siebert d 
+  ger </t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">voith arena
+  heidenheim </t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>15000</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>KWixEVWi</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>KbS1suSm</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>59</v>
+      </c>
+      <c r="I8" t="n">
+        <v>591</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="N8" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="O8" t="n">
+        <v>186.8</v>
+      </c>
+      <c r="P8" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>349</v>
+      </c>
+      <c r="R8" t="n">
+        <v>100000</v>
+      </c>
+      <c r="S8" t="n">
+        <v>14600000</v>
+      </c>
+      <c r="T8" t="n">
+        <v>370</v>
+      </c>
+      <c r="U8" t="n">
+        <v>6</v>
+      </c>
+      <c r="V8" t="n">
+        <v>25.25</v>
+      </c>
+      <c r="W8" t="n">
+        <v>180.75</v>
+      </c>
+      <c r="X8" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>308</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>184000</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>70500000</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>332</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>9</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>26.81666666666666</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>187.1166666666667</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>72.46666666666665</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>22100</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>3151666.666666667</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>74.21666666666665</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>1.016666666666667</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>25.87794612794613</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>183.3648148148148</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>80.43636363636362</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>56660.60606060606</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>30434343.43434344</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>84.00151515151515</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>2.224915824915825</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>25.67282608695652</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>185.1786231884058</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>69.60688405797102</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>19845.65217391304</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>2247119.565217391</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>72.58188405797101</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>1.043478260869565</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>25.33862229102168</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>184.7739042254329</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>78.53386581240683</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>52439.83058135535</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>24871615.74790735</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>82.27483946795093</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>1.980187908496732</v>
+      </c>
+      <c r="BF8" t="inlineStr">
+        <is>
+          <t>vZA6VYpf</t>
+        </is>
+      </c>
+      <c r="BG8" t="inlineStr">
+        <is>
+          <t>2VSFgl3c</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>ShoJUGLi</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>45571.52083333334</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">zwayer f 
+  ger </t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">deutsche bank park
+  frankfurt </t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>58000</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>8vndvXTk</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>nVp0wiqd</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>59</v>
+      </c>
+      <c r="I9" t="n">
+        <v>591</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="N9" t="n">
+        <v>19</v>
+      </c>
+      <c r="O9" t="n">
+        <v>172</v>
+      </c>
+      <c r="P9" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>59</v>
+      </c>
+      <c r="R9" t="n">
+        <v>3000</v>
+      </c>
+      <c r="S9" t="n">
+        <v>575000</v>
+      </c>
+      <c r="T9" t="n">
+        <v>76</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1</v>
+      </c>
+      <c r="V9" t="n">
+        <v>21.66666666666667</v>
+      </c>
+      <c r="W9" t="n">
+        <v>183.5</v>
+      </c>
+      <c r="X9" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>444</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>276000</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>189150000</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>498</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>24.74444444444444</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>185.0722222222223</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>76.98333333333333</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>35133.33333333334</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>15228055.55555556</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>81.71111111111111</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>1.694444444444445</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>26.78333333333333</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>183.75</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>82.85000000000001</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>76950</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>47282916.66666666</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>85.68333333333332</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>3.083333333333333</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>22.37575757575758</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>185.0691368572948</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>72.67647527910687</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>25312.00918964077</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>8847221.671603251</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>81.03199855699854</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>1.361995898838004</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>26.85416666666667</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>183.3313484581867</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>81.70669934640523</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>75162.88545332663</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>38261669.78276353</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>83.96209359812302</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>2.684724317077258</v>
+      </c>
+      <c r="BF9" t="inlineStr">
+        <is>
+          <t>A15eUM4C</t>
+        </is>
+      </c>
+      <c r="BG9" t="inlineStr">
+        <is>
+          <t>hAcTWKKN</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>nc8W6DTp</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>45571.60416666666</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">reichel t 
+  ger </t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mhparena
+  stuttgart </t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>60449</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>nJQmYp1B</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>hQAtP9Sl</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>59</v>
+      </c>
+      <c r="I10" t="n">
+        <v>591</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="N10" t="n">
+        <v>23.33333333333333</v>
+      </c>
+      <c r="O10" t="n">
+        <v>186</v>
+      </c>
+      <c r="P10" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>431</v>
+      </c>
+      <c r="R10" t="n">
+        <v>116000</v>
+      </c>
+      <c r="S10" t="n">
+        <v>32600000</v>
+      </c>
+      <c r="T10" t="n">
+        <v>471</v>
+      </c>
+      <c r="U10" t="n">
+        <v>8</v>
+      </c>
+      <c r="V10" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="W10" t="n">
+        <v>183.2</v>
+      </c>
+      <c r="X10" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>371</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>142000</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>30200000</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>386</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>24.95714285714286</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>185.7636363636364</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>76.23116883116883</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>27564.93506493506</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>13686363.63636363</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>79.42467532467533</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>1.45974025974026</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>27.68703703703704</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>186.0796296296296</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>74.88333333333334</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>30257.40740740741</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>7417592.592592592</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>78.01296296296296</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>1.655555555555556</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>24.18921166552746</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>184.4195906432749</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>73.40942507784612</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>24026.95374800638</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>10309174.54621402</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>78.25894281157441</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>1.483652312599681</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>24.35341130604289</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>186.3588693957115</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>71.36042884990253</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>24539.57115009746</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>5892831.384015595</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>77.62027290448343</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>1.239278752436647</v>
+      </c>
+      <c r="BF10" t="inlineStr">
+        <is>
+          <t>f3ddUIXs</t>
+        </is>
+      </c>
+      <c r="BG10" t="inlineStr">
+        <is>
+          <t>4fuCGs9P</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>z1eeWTdd</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>45583.64583333334</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gerach t 
+  ger </t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">signal iduna park
+  dortmund </t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>81365</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>nP1i5US1</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>ILyJuN3g</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>59</v>
+      </c>
+      <c r="I11" t="n">
+        <v>591</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="inlineStr"/>
+      <c r="W11" t="inlineStr"/>
+      <c r="X11" t="inlineStr"/>
+      <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="inlineStr"/>
+      <c r="AA11" t="inlineStr"/>
+      <c r="AB11" t="inlineStr"/>
+      <c r="AC11" t="inlineStr"/>
+      <c r="AD11" t="n">
+        <v>26.71666666666667</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>186.0545454545454</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>82.01363636363635</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>58143.93939393939</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>37515909.09090909</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>84.09696969696969</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>2.63030303030303</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>26.79141414141414</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>185.4481481481481</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>70.55235690235691</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>17073.90572390573</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>2309494.94949495</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>73.50185185185185</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>24.649016563147</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>183.9863103080494</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>77.62367620302403</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>42621.67325428195</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>22335895.13143861</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>83.02270060857018</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>1.854321161929858</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>25.52275828460039</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>184.5858674463937</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>68.49556530214424</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>16164.32748538012</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>1827714.424951267</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>72.08396686159844</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF11" t="inlineStr">
+        <is>
+          <t>IkCftsQm</t>
+        </is>
+      </c>
+      <c r="BG11" t="inlineStr">
+        <is>
+          <t>0jdIgO6t</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>fHjVr7t2</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>45584.4375</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">exner f 
+  ger </t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">borussia park
+  monchengladbach </t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>54042</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>88HSzjDr</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>KWixEVWi</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>59</v>
+      </c>
+      <c r="I12" t="n">
+        <v>591</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr"/>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="inlineStr"/>
+      <c r="W12" t="inlineStr"/>
+      <c r="X12" t="inlineStr"/>
+      <c r="Y12" t="inlineStr"/>
+      <c r="Z12" t="inlineStr"/>
+      <c r="AA12" t="inlineStr"/>
+      <c r="AB12" t="inlineStr"/>
+      <c r="AC12" t="inlineStr"/>
+      <c r="AD12" t="n">
+        <v>26.13333333333334</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>184.65</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>75.55</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>24516.66666666667</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>8460000</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>77.98333333333333</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>26.81666666666666</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>187.1166666666667</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>72.46666666666665</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>22100</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>3151666.666666667</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>74.21666666666665</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>1.016666666666667</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>25.55264065962007</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>183.6602557117432</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>73.58824143692566</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>22408.07180995968</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>6264900.021793614</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>77.50048127565289</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>1.212310667974284</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>25.67282608695652</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>185.1786231884058</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>69.60688405797102</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>19845.65217391304</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>2247119.565217391</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>72.58188405797101</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>1.043478260869565</v>
+      </c>
+      <c r="BF12" t="inlineStr">
+        <is>
+          <t>M5BRZDsC</t>
+        </is>
+      </c>
+      <c r="BG12" t="inlineStr">
+        <is>
+          <t>4ljanukM</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>r3GGwC4M</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>45584.4375</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stieler t 
+  ger </t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bayarena
+  leverkusen </t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>30210</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>4jcj2zMd</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>8vndvXTk</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>59</v>
+      </c>
+      <c r="I13" t="n">
+        <v>591</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr"/>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="inlineStr"/>
+      <c r="W13" t="inlineStr"/>
+      <c r="X13" t="inlineStr"/>
+      <c r="Y13" t="inlineStr"/>
+      <c r="Z13" t="inlineStr"/>
+      <c r="AA13" t="inlineStr"/>
+      <c r="AB13" t="inlineStr"/>
+      <c r="AC13" t="inlineStr"/>
+      <c r="AD13" t="n">
+        <v>26.35787037037037</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>184.4333333333333</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>83.63009259259259</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>98558.33333333333</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>49468750</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>85.83888888888889</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>3.025</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>24.74444444444444</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>185.0722222222223</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>76.98333333333333</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>35133.33333333334</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>15228055.55555556</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>81.71111111111111</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>1.694444444444445</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>24.53296406281811</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>180.5564682013156</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>80.85853288683894</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>82395.97593423336</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>40250463.78200404</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>84.65014075805762</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>2.317095259156293</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>22.37575757575758</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>185.0691368572948</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>72.67647527910687</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>25312.00918964077</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>8847221.671603251</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>81.03199855699854</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>1.361995898838004</v>
+      </c>
+      <c r="BF13" t="inlineStr">
+        <is>
+          <t>K6A2elS9</t>
+        </is>
+      </c>
+      <c r="BG13" t="inlineStr">
+        <is>
+          <t>UgdQz0fK</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>M93rhBJF</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>45584.4375</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">siebert d 
+  ger </t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">europa park stadion
+  freiburg </t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>34700</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>fiEQZ7C7</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>fTVNku3I</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>59</v>
+      </c>
+      <c r="I14" t="n">
+        <v>591</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr"/>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="inlineStr"/>
+      <c r="W14" t="inlineStr"/>
+      <c r="X14" t="inlineStr"/>
+      <c r="Y14" t="inlineStr"/>
+      <c r="Z14" t="inlineStr"/>
+      <c r="AA14" t="inlineStr"/>
+      <c r="AB14" t="inlineStr"/>
+      <c r="AC14" t="inlineStr"/>
+      <c r="AD14" t="n">
+        <v>26.73518518518519</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>183.7101851851852</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>76.02638888888889</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>26159.72222222222</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>10543888.88888889</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>78.63101851851852</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>1.606018518518519</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>25.79166666666667</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>185.0416666666667</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>73.70833333333333</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>22291.66666666667</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>5350000</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>76.91666666666667</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>1.125</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>26.86084050706476</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>183.3518257105214</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>74.39824643955079</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>24267.14051267827</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>7185075.060014992</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>76.81051649215264</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>1.408638443935927</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>24.70897739744489</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>184.1469137229586</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>72.43944443141424</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>21145.91621470492</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>4947826.455808267</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>76.57492066470394</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>1.16975030974644</v>
+      </c>
+      <c r="BF14" t="inlineStr">
+        <is>
+          <t>YZPE6Sx7</t>
+        </is>
+      </c>
+      <c r="BG14" t="inlineStr">
+        <is>
+          <t>2VSFgl3c</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>Eq0zfXl3</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>45584.4375</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">brych f 
+  ger </t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
         <is>
           <t xml:space="preserve">prezero arena
   sinsheim </t>
         </is>
       </c>
-      <c r="E3" t="n">
+      <c r="E15" t="n">
         <v>30150</v>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>hQAtP9Sl</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Ig1f1fy3</t>
-        </is>
-      </c>
-      <c r="H3" t="n">
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>8Y2m6ADe</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
         <v>59</v>
       </c>
-      <c r="I3" t="n">
+      <c r="I15" t="n">
         <v>591</v>
       </c>
-      <c r="J3" t="n">
+      <c r="J15" t="n">
         <v>0</v>
       </c>
-      <c r="K3" t="n">
+      <c r="K15" t="n">
         <v>20242025</v>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="L15" t="inlineStr">
         <is>
           <t>germany</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="M15" t="inlineStr">
         <is>
           <t>bundesliga</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>nJQmYp1B</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>v9k3aY5F</t>
-        </is>
-      </c>
-      <c r="P3" t="n">
-        <v>25.16666666666667</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>180.6666666666667</v>
-      </c>
-      <c r="R3" t="n">
-        <v>74.5</v>
-      </c>
-      <c r="S3" t="n">
-        <v>25333.33333333333</v>
-      </c>
-      <c r="T3" t="n">
-        <v>6</v>
-      </c>
-      <c r="U3" t="n">
-        <v>447</v>
-      </c>
-      <c r="V3" t="n">
-        <v>26</v>
-      </c>
-      <c r="W3" t="n">
-        <v>185.5</v>
-      </c>
-      <c r="X3" t="n">
-        <v>73.5</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>18500</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>147</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>26.85111111111111</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>186.1177777777778</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>74.50222222222223</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>28540</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>26.08181818181818</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>183.5836363636363</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>73.82909090909091</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>19249.0909090909</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>23.52787539258128</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>184.4787624140565</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>71.59161361514302</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>19751.72735760971</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>23.80409982174688</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>185.9703149138443</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>69.93321449792037</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>12631.44385026738</v>
-      </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>hpYJ6izc</t>
-        </is>
-      </c>
-      <c r="AS3" t="inlineStr">
-        <is>
-          <t>K6A2elS9</t>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr"/>
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="inlineStr"/>
+      <c r="W15" t="inlineStr"/>
+      <c r="X15" t="inlineStr"/>
+      <c r="Y15" t="inlineStr"/>
+      <c r="Z15" t="inlineStr"/>
+      <c r="AA15" t="inlineStr"/>
+      <c r="AB15" t="inlineStr"/>
+      <c r="AC15" t="inlineStr"/>
+      <c r="AD15" t="n">
+        <v>27.68703703703704</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>186.0796296296296</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>74.88333333333334</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>30257.40740740741</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>7417592.592592592</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>78.01296296296296</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>1.655555555555556</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>28.05666666666666</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>185.1505555555555</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>71.58555555555554</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>16957.77777777778</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>2249013.888888889</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>73.66055555555556</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>24.35341130604289</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>186.3588693957115</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>71.36042884990253</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>24539.57115009746</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>5892831.384015595</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>77.62027290448343</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>1.239278752436647</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>25.24211011440113</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>185.612326127032</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>68.23141973838568</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>14886.9020842705</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>1770742.648161379</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>74.39888024485548</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF15" t="inlineStr">
+        <is>
+          <t>KUx4Q7x1</t>
+        </is>
+      </c>
+      <c r="BG15" t="inlineStr">
+        <is>
+          <t>8f6APkLc</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>E7rNpTBk</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>45584.4375</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">siebert d 
+  ger </t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mewa arena
+  mainz </t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>34000</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>EuakNmc1</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>KbS1suSm</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>59</v>
+      </c>
+      <c r="I16" t="n">
+        <v>591</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="inlineStr"/>
+      <c r="T16" t="inlineStr"/>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="inlineStr"/>
+      <c r="W16" t="inlineStr"/>
+      <c r="X16" t="inlineStr"/>
+      <c r="Y16" t="inlineStr"/>
+      <c r="Z16" t="inlineStr"/>
+      <c r="AA16" t="inlineStr"/>
+      <c r="AB16" t="inlineStr"/>
+      <c r="AC16" t="inlineStr"/>
+      <c r="AD16" t="n">
+        <v>27.66111111111111</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>183.4018518518519</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>74.87777777777778</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>25170.37037037037</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>6554629.62962963</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>76.90925925925926</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>1.411111111111111</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>25.87794612794613</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>183.3648148148148</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>80.43636363636362</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>56660.60606060606</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>30434343.43434344</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>84.00151515151515</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>2.224915824915825</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>25.99150527834739</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>183.8311460469355</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>71.37496392496392</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>21557.77322093112</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>3239910.334548492</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>76.42352851826536</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>1.130392268550163</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>25.33862229102168</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>184.7739042254329</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>78.53386581240683</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>52439.83058135535</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>24871615.74790735</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>82.27483946795093</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>1.980187908496732</v>
+      </c>
+      <c r="BF16" t="inlineStr">
+        <is>
+          <t>vZA6VYpf</t>
+        </is>
+      </c>
+      <c r="BG16" t="inlineStr">
+        <is>
+          <t>2VSFgl3c</t>
         </is>
       </c>
     </row>

--- a/data/germany/p6_deployment/data_preparation/df_filled.xlsx
+++ b/data/germany/p6_deployment/data_preparation/df_filled.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BG16"/>
+  <dimension ref="A1:BG13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -727,35 +727,35 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>UajsPCkT</t>
+          <t>0KbQSfj4</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45569.64583333334</v>
+        <v>45571.4375</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">badstubner f 
+          <t xml:space="preserve">stegemann s 
   ger </t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">wwk arena
-  augsburg </t>
+          <t xml:space="preserve">voith arena
+  heidenheim </t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>30660</v>
+        <v>15000</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>fTVNku3I</t>
+          <t>KWixEVWi</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>88HSzjDr</t>
+          <t>KbS1suSm</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -781,180 +781,180 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>25.6</v>
+        <v>24.25</v>
       </c>
       <c r="O2" t="n">
-        <v>180.6</v>
+        <v>189.75</v>
       </c>
       <c r="P2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q2" t="n">
-        <v>348</v>
+        <v>274</v>
       </c>
       <c r="R2" t="n">
-        <v>83000</v>
+        <v>73000</v>
       </c>
       <c r="S2" t="n">
-        <v>13325000</v>
+        <v>7600000</v>
       </c>
       <c r="T2" t="n">
-        <v>361</v>
+        <v>291</v>
       </c>
       <c r="U2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="V2" t="n">
-        <v>23.5</v>
+        <v>25.25</v>
       </c>
       <c r="W2" t="n">
-        <v>182.8333333333333</v>
+        <v>180.75</v>
       </c>
       <c r="X2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Y2" t="n">
-        <v>424</v>
+        <v>308</v>
       </c>
       <c r="Z2" t="n">
-        <v>96000</v>
+        <v>184000</v>
       </c>
       <c r="AA2" t="n">
-        <v>39725000</v>
+        <v>70500000</v>
       </c>
       <c r="AB2" t="n">
-        <v>466</v>
+        <v>332</v>
       </c>
       <c r="AC2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AD2" t="n">
-        <v>25.79166666666667</v>
+        <v>26.81666666666666</v>
       </c>
       <c r="AE2" t="n">
-        <v>185.0416666666667</v>
+        <v>187.1166666666667</v>
       </c>
       <c r="AF2" t="n">
-        <v>73.70833333333333</v>
+        <v>72.46666666666665</v>
       </c>
       <c r="AG2" t="n">
-        <v>22291.66666666667</v>
+        <v>22100</v>
       </c>
       <c r="AH2" t="n">
-        <v>5350000</v>
+        <v>3151666.666666667</v>
       </c>
       <c r="AI2" t="n">
-        <v>76.91666666666667</v>
+        <v>74.21666666666665</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1.125</v>
+        <v>1.016666666666667</v>
       </c>
       <c r="AK2" t="n">
-        <v>26.13333333333334</v>
+        <v>25.87794612794613</v>
       </c>
       <c r="AL2" t="n">
-        <v>184.65</v>
+        <v>183.3648148148148</v>
       </c>
       <c r="AM2" t="n">
-        <v>75.55</v>
+        <v>80.43636363636362</v>
       </c>
       <c r="AN2" t="n">
-        <v>24516.66666666667</v>
+        <v>56660.60606060606</v>
       </c>
       <c r="AO2" t="n">
-        <v>8460000</v>
+        <v>30434343.43434344</v>
       </c>
       <c r="AP2" t="n">
-        <v>77.98333333333333</v>
+        <v>84.00151515151515</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.5</v>
+        <v>2.224915824915825</v>
       </c>
       <c r="AR2" t="n">
-        <v>24.70897739744489</v>
+        <v>25.67282608695652</v>
       </c>
       <c r="AS2" t="n">
-        <v>184.1469137229586</v>
+        <v>185.1786231884058</v>
       </c>
       <c r="AT2" t="n">
-        <v>72.43944443141424</v>
+        <v>69.60688405797102</v>
       </c>
       <c r="AU2" t="n">
-        <v>21145.91621470492</v>
+        <v>19845.65217391304</v>
       </c>
       <c r="AV2" t="n">
-        <v>4947826.455808267</v>
+        <v>2247119.565217391</v>
       </c>
       <c r="AW2" t="n">
-        <v>76.57492066470394</v>
+        <v>72.58188405797101</v>
       </c>
       <c r="AX2" t="n">
-        <v>1.16975030974644</v>
+        <v>1.043478260869565</v>
       </c>
       <c r="AY2" t="n">
-        <v>25.55264065962007</v>
+        <v>25.33862229102168</v>
       </c>
       <c r="AZ2" t="n">
-        <v>183.6602557117432</v>
+        <v>184.7739042254329</v>
       </c>
       <c r="BA2" t="n">
-        <v>73.58824143692566</v>
+        <v>78.53386581240683</v>
       </c>
       <c r="BB2" t="n">
-        <v>22408.07180995968</v>
+        <v>52439.83058135535</v>
       </c>
       <c r="BC2" t="n">
-        <v>6264900.021793614</v>
+        <v>24871615.74790735</v>
       </c>
       <c r="BD2" t="n">
-        <v>77.50048127565289</v>
+        <v>82.27483946795093</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.212310667974284</v>
+        <v>1.980187908496732</v>
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>pfoInmcq</t>
+          <t>vZA6VYpf</t>
         </is>
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>hpYJ6izc</t>
+          <t>2VSFgl3c</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>tbtaPLqC</t>
+          <t>ShoJUGLi</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45570.4375</v>
+        <v>45571.52083333334</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">stieler t 
+          <t xml:space="preserve">brand b 
   ger </t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">bayarena
-  leverkusen </t>
+          <t xml:space="preserve">deutsche bank park
+  frankfurt </t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>30210</v>
+        <v>58000</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>4jcj2zMd</t>
+          <t>8vndvXTk</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>63WsD2ei</t>
+          <t>nVp0wiqd</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -979,165 +979,181 @@
           <t>bundesliga</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr"/>
-      <c r="R3" t="inlineStr"/>
-      <c r="S3" t="inlineStr"/>
-      <c r="T3" t="inlineStr"/>
-      <c r="U3" t="inlineStr"/>
+      <c r="N3" t="n">
+        <v>19</v>
+      </c>
+      <c r="O3" t="n">
+        <v>172</v>
+      </c>
+      <c r="P3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>59</v>
+      </c>
+      <c r="R3" t="n">
+        <v>3000</v>
+      </c>
+      <c r="S3" t="n">
+        <v>575000</v>
+      </c>
+      <c r="T3" t="n">
+        <v>76</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1</v>
+      </c>
       <c r="V3" t="n">
-        <v>25</v>
+        <v>21.66666666666667</v>
       </c>
       <c r="W3" t="n">
-        <v>193.5</v>
+        <v>183.5</v>
       </c>
       <c r="X3" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="Y3" t="n">
-        <v>138</v>
+        <v>444</v>
       </c>
       <c r="Z3" t="n">
-        <v>29000</v>
+        <v>276000</v>
       </c>
       <c r="AA3" t="n">
-        <v>3800000</v>
+        <v>189150000</v>
       </c>
       <c r="AB3" t="n">
-        <v>147</v>
+        <v>498</v>
       </c>
       <c r="AC3" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="AD3" t="n">
-        <v>26.35787037037037</v>
+        <v>24.74444444444444</v>
       </c>
       <c r="AE3" t="n">
-        <v>184.4333333333333</v>
+        <v>185.0722222222223</v>
       </c>
       <c r="AF3" t="n">
-        <v>83.63009259259259</v>
+        <v>76.98333333333333</v>
       </c>
       <c r="AG3" t="n">
-        <v>98558.33333333333</v>
+        <v>35133.33333333334</v>
       </c>
       <c r="AH3" t="n">
-        <v>49468750</v>
+        <v>15228055.55555556</v>
       </c>
       <c r="AI3" t="n">
-        <v>85.83888888888889</v>
+        <v>81.71111111111111</v>
       </c>
       <c r="AJ3" t="n">
-        <v>3.025</v>
+        <v>1.694444444444445</v>
       </c>
       <c r="AK3" t="n">
-        <v>26.66839225589226</v>
+        <v>26.78333333333333</v>
       </c>
       <c r="AL3" t="n">
-        <v>185.7753367003367</v>
+        <v>183.75</v>
       </c>
       <c r="AM3" t="n">
-        <v>69.92592592592592</v>
+        <v>82.85000000000001</v>
       </c>
       <c r="AN3" t="n">
-        <v>16646.92760942761</v>
+        <v>76950</v>
       </c>
       <c r="AO3" t="n">
-        <v>1912622.053872054</v>
+        <v>47282916.66666666</v>
       </c>
       <c r="AP3" t="n">
-        <v>72.23021885521887</v>
+        <v>85.68333333333332</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1</v>
+        <v>3.083333333333333</v>
       </c>
       <c r="AR3" t="n">
-        <v>24.53296406281811</v>
+        <v>22.37575757575758</v>
       </c>
       <c r="AS3" t="n">
-        <v>180.5564682013156</v>
+        <v>185.0691368572948</v>
       </c>
       <c r="AT3" t="n">
-        <v>80.85853288683894</v>
+        <v>72.67647527910687</v>
       </c>
       <c r="AU3" t="n">
-        <v>82395.97593423336</v>
+        <v>25312.00918964077</v>
       </c>
       <c r="AV3" t="n">
-        <v>40250463.78200404</v>
+        <v>8847221.671603251</v>
       </c>
       <c r="AW3" t="n">
-        <v>84.65014075805762</v>
+        <v>81.03199855699854</v>
       </c>
       <c r="AX3" t="n">
-        <v>2.317095259156293</v>
+        <v>1.361995898838004</v>
       </c>
       <c r="AY3" t="n">
-        <v>25.47224310776943</v>
+        <v>26.85416666666667</v>
       </c>
       <c r="AZ3" t="n">
-        <v>185.0112364243943</v>
+        <v>183.3313484581867</v>
       </c>
       <c r="BA3" t="n">
-        <v>68.16849067112224</v>
+        <v>81.70669934640523</v>
       </c>
       <c r="BB3" t="n">
-        <v>15489.62684489</v>
+        <v>75162.88545332663</v>
       </c>
       <c r="BC3" t="n">
-        <v>1845626.56641604</v>
+        <v>38261669.78276353</v>
       </c>
       <c r="BD3" t="n">
-        <v>72.70550682261209</v>
+        <v>83.96209359812302</v>
       </c>
       <c r="BE3" t="n">
-        <v>1</v>
+        <v>2.684724317077258</v>
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>K6A2elS9</t>
+          <t>A15eUM4C</t>
         </is>
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>UgdQz0fK</t>
+          <t>hAcTWKKN</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>ENOasf5c</t>
+          <t>nc8W6DTp</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45570.4375</v>
+        <v>45571.60416666666</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">burda m 
+          <t xml:space="preserve">osmers h 
   ger </t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">vonovia ruhrstadion
-  bochum </t>
+          <t xml:space="preserve">mhparena
+  stuttgart </t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>26000</v>
+        <v>60449</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>8Y2m6ADe</t>
+          <t>nJQmYp1B</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>nwkTahLL</t>
+          <t>hQAtP9Sl</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -1163,180 +1179,180 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>24</v>
+        <v>23.33333333333333</v>
       </c>
       <c r="O4" t="n">
-        <v>185.5</v>
+        <v>186</v>
       </c>
       <c r="P4" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="Q4" t="n">
-        <v>136</v>
+        <v>431</v>
       </c>
       <c r="R4" t="n">
-        <v>32000</v>
+        <v>116000</v>
       </c>
       <c r="S4" t="n">
-        <v>5575000</v>
+        <v>32600000</v>
       </c>
       <c r="T4" t="n">
-        <v>147</v>
+        <v>471</v>
       </c>
       <c r="U4" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="V4" t="n">
-        <v>23.57142857142857</v>
+        <v>27.8</v>
       </c>
       <c r="W4" t="n">
-        <v>182.5714285714286</v>
+        <v>182.8</v>
       </c>
       <c r="X4" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Y4" t="n">
-        <v>520</v>
+        <v>375</v>
       </c>
       <c r="Z4" t="n">
-        <v>244000</v>
+        <v>151000</v>
       </c>
       <c r="AA4" t="n">
-        <v>76100000</v>
+        <v>31900000</v>
       </c>
       <c r="AB4" t="n">
-        <v>558</v>
+        <v>384</v>
       </c>
       <c r="AC4" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AD4" t="n">
-        <v>28.05666666666666</v>
+        <v>24.95714285714286</v>
       </c>
       <c r="AE4" t="n">
-        <v>185.1505555555555</v>
+        <v>185.7636363636364</v>
       </c>
       <c r="AF4" t="n">
-        <v>71.58555555555554</v>
+        <v>76.23116883116883</v>
       </c>
       <c r="AG4" t="n">
-        <v>16957.77777777778</v>
+        <v>27564.93506493506</v>
       </c>
       <c r="AH4" t="n">
-        <v>2249013.888888889</v>
+        <v>13686363.63636363</v>
       </c>
       <c r="AI4" t="n">
-        <v>73.66055555555556</v>
+        <v>79.42467532467533</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1</v>
+        <v>1.45974025974026</v>
       </c>
       <c r="AK4" t="n">
-        <v>24.70833333333333</v>
+        <v>27.68703703703704</v>
       </c>
       <c r="AL4" t="n">
-        <v>184.7083333333333</v>
+        <v>186.0796296296296</v>
       </c>
       <c r="AM4" t="n">
-        <v>75.2986111111111</v>
+        <v>74.88333333333334</v>
       </c>
       <c r="AN4" t="n">
-        <v>36312.5</v>
+        <v>30257.40740740741</v>
       </c>
       <c r="AO4" t="n">
-        <v>10284953.7037037</v>
+        <v>7417592.592592592</v>
       </c>
       <c r="AP4" t="n">
-        <v>79.89814814814814</v>
+        <v>78.01296296296296</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.418981481481481</v>
+        <v>1.655555555555556</v>
       </c>
       <c r="AR4" t="n">
-        <v>25.24211011440113</v>
+        <v>24.18921166552746</v>
       </c>
       <c r="AS4" t="n">
-        <v>185.612326127032</v>
+        <v>184.4195906432749</v>
       </c>
       <c r="AT4" t="n">
-        <v>68.23141973838568</v>
+        <v>73.40942507784612</v>
       </c>
       <c r="AU4" t="n">
-        <v>14886.9020842705</v>
+        <v>24026.95374800638</v>
       </c>
       <c r="AV4" t="n">
-        <v>1770742.648161379</v>
+        <v>10309174.54621402</v>
       </c>
       <c r="AW4" t="n">
-        <v>74.39888024485548</v>
+        <v>78.25894281157441</v>
       </c>
       <c r="AX4" t="n">
-        <v>1</v>
+        <v>1.483652312599681</v>
       </c>
       <c r="AY4" t="n">
-        <v>24.66797385620915</v>
+        <v>24.35341130604289</v>
       </c>
       <c r="AZ4" t="n">
-        <v>185.0577205882353</v>
+        <v>186.3588693957115</v>
       </c>
       <c r="BA4" t="n">
-        <v>72.91958061002178</v>
+        <v>71.36042884990253</v>
       </c>
       <c r="BB4" t="n">
-        <v>32168.57298474945</v>
+        <v>24539.57115009746</v>
       </c>
       <c r="BC4" t="n">
-        <v>7789857.02614379</v>
+        <v>5892831.384015595</v>
       </c>
       <c r="BD4" t="n">
-        <v>78.20927287581699</v>
+        <v>77.62027290448343</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.333428649237473</v>
+        <v>1.239278752436647</v>
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>IkCftsQm</t>
+          <t>f3ddUIXs</t>
         </is>
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>GzfvcwRj</t>
+          <t>4fuCGs9P</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>lpXDJjDj</t>
+          <t>z1eeWTdd</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45570.4375</v>
+        <v>45583.64583333334</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">reichel t 
+          <t xml:space="preserve">dingert c 
   ger </t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadion an der alten forsterei
-  berlin </t>
+          <t xml:space="preserve">signal iduna park
+  dortmund </t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>22012</v>
+        <v>81365</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>pzHW4oaE</t>
+          <t>nP1i5US1</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>nP1i5US1</t>
+          <t>ILyJuN3g</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -1361,181 +1377,149 @@
           <t>bundesliga</t>
         </is>
       </c>
-      <c r="N5" t="n">
-        <v>28</v>
-      </c>
-      <c r="O5" t="n">
-        <v>181</v>
-      </c>
-      <c r="P5" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>146</v>
-      </c>
-      <c r="R5" t="n">
-        <v>58000</v>
-      </c>
-      <c r="S5" t="n">
-        <v>8600000</v>
-      </c>
-      <c r="T5" t="n">
-        <v>146</v>
-      </c>
-      <c r="U5" t="n">
-        <v>2</v>
-      </c>
-      <c r="V5" t="n">
-        <v>22.66666666666667</v>
-      </c>
-      <c r="W5" t="n">
-        <v>180.3333333333333</v>
-      </c>
-      <c r="X5" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>237</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>133000</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>92500000</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>253</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>7</v>
-      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="inlineStr"/>
+      <c r="AA5" t="inlineStr"/>
+      <c r="AB5" t="inlineStr"/>
+      <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="n">
-        <v>27.1026936026936</v>
+        <v>26.64285714285714</v>
       </c>
       <c r="AE5" t="n">
-        <v>186.356228956229</v>
+        <v>186.061038961039</v>
       </c>
       <c r="AF5" t="n">
-        <v>75.03198653198653</v>
+        <v>81.98311688311686</v>
       </c>
       <c r="AG5" t="n">
-        <v>28156.39730639731</v>
+        <v>57966.23376623377</v>
       </c>
       <c r="AH5" t="n">
-        <v>6726599.326599326</v>
+        <v>37499350.64935065</v>
       </c>
       <c r="AI5" t="n">
-        <v>77.46144781144781</v>
+        <v>84.12597402597403</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1.421380471380472</v>
+        <v>2.611688311688312</v>
       </c>
       <c r="AK5" t="n">
-        <v>26.71666666666667</v>
+        <v>26.76926406926407</v>
       </c>
       <c r="AL5" t="n">
-        <v>186.0545454545454</v>
+        <v>185.3191919191919</v>
       </c>
       <c r="AM5" t="n">
-        <v>82.01363636363635</v>
+        <v>70.64227994227994</v>
       </c>
       <c r="AN5" t="n">
-        <v>58143.93939393939</v>
+        <v>17154.25685425686</v>
       </c>
       <c r="AO5" t="n">
-        <v>37515909.09090909</v>
+        <v>2338008.658008658</v>
       </c>
       <c r="AP5" t="n">
-        <v>84.09696969696969</v>
+        <v>73.57301587301588</v>
       </c>
       <c r="AQ5" t="n">
-        <v>2.63030303030303</v>
+        <v>1</v>
       </c>
       <c r="AR5" t="n">
-        <v>26.28750287554636</v>
+        <v>24.94727735487788</v>
       </c>
       <c r="AS5" t="n">
-        <v>182.9943754313319</v>
+        <v>184.0784915422379</v>
       </c>
       <c r="AT5" t="n">
-        <v>73.0883597883598</v>
+        <v>77.85036907627624</v>
       </c>
       <c r="AU5" t="n">
-        <v>24678.21486082356</v>
+        <v>43615.56955630182</v>
       </c>
       <c r="AV5" t="n">
-        <v>4189991.948470209</v>
+        <v>22506707.10514287</v>
       </c>
       <c r="AW5" t="n">
-        <v>76.11999079825168</v>
+        <v>82.89163811561654</v>
       </c>
       <c r="AX5" t="n">
-        <v>1.176386013342535</v>
+        <v>1.89768881548875</v>
       </c>
       <c r="AY5" t="n">
-        <v>24.649016563147</v>
+        <v>25.57589807852966</v>
       </c>
       <c r="AZ5" t="n">
-        <v>183.9863103080494</v>
+        <v>184.6525480367586</v>
       </c>
       <c r="BA5" t="n">
-        <v>77.62367620302403</v>
+        <v>68.33454469507102</v>
       </c>
       <c r="BB5" t="n">
-        <v>42621.67325428195</v>
+        <v>16058.14536340852</v>
       </c>
       <c r="BC5" t="n">
-        <v>22335895.13143861</v>
+        <v>1786161.236424394</v>
       </c>
       <c r="BD5" t="n">
-        <v>83.02270060857018</v>
+        <v>71.97422723475356</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.854321161929858</v>
+        <v>1</v>
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>M5BRZDsC</t>
+          <t>hpYJ6izc</t>
         </is>
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>8f6APkLc</t>
+          <t>vZA6VYpf</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>dnhZQYKG</t>
+          <t>fHjVr7t2</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45570.4375</v>
+        <v>45584.4375</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">welz t 
+          <t xml:space="preserve">exner f 
   ger </t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">weserstadion
-  bremen </t>
+          <t xml:space="preserve">borussia park
+  monchengladbach </t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>42100</v>
+        <v>54042</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ig1f1fy3</t>
+          <t>88HSzjDr</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>fiEQZ7C7</t>
+          <t>KWixEVWi</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -1560,181 +1544,149 @@
           <t>bundesliga</t>
         </is>
       </c>
-      <c r="N6" t="n">
-        <v>28.5</v>
-      </c>
-      <c r="O6" t="n">
-        <v>189</v>
-      </c>
-      <c r="P6" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>147</v>
-      </c>
-      <c r="R6" t="n">
-        <v>46000</v>
-      </c>
-      <c r="S6" t="n">
-        <v>6500000</v>
-      </c>
-      <c r="T6" t="n">
-        <v>148</v>
-      </c>
-      <c r="U6" t="n">
-        <v>2</v>
-      </c>
-      <c r="V6" t="n">
-        <v>24.66666666666667</v>
-      </c>
-      <c r="W6" t="n">
-        <v>185.8333333333333</v>
-      </c>
-      <c r="X6" t="n">
-        <v>6</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>423</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>101000</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>26000000</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>454</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>6</v>
-      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr"/>
+      <c r="X6" t="inlineStr"/>
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="inlineStr"/>
+      <c r="AA6" t="inlineStr"/>
+      <c r="AB6" t="inlineStr"/>
+      <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="n">
-        <v>27.06818181818182</v>
+        <v>26.11428571428572</v>
       </c>
       <c r="AE6" t="n">
-        <v>183.6530303030303</v>
+        <v>184.8857142857143</v>
       </c>
       <c r="AF6" t="n">
-        <v>74.53939393939395</v>
+        <v>75.48571428571428</v>
       </c>
       <c r="AG6" t="n">
-        <v>23595.45454545454</v>
+        <v>24414.28571428571</v>
       </c>
       <c r="AH6" t="n">
-        <v>6047121.212121212</v>
+        <v>8282857.142857143</v>
       </c>
       <c r="AI6" t="n">
-        <v>76.77424242424242</v>
+        <v>77.91428571428573</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1.095454545454545</v>
+        <v>1.485714285714286</v>
       </c>
       <c r="AK6" t="n">
-        <v>26.73518518518519</v>
+        <v>26.81666666666666</v>
       </c>
       <c r="AL6" t="n">
-        <v>183.7101851851852</v>
+        <v>187.1166666666667</v>
       </c>
       <c r="AM6" t="n">
-        <v>76.02638888888889</v>
+        <v>72.46666666666665</v>
       </c>
       <c r="AN6" t="n">
-        <v>26159.72222222222</v>
+        <v>22100</v>
       </c>
       <c r="AO6" t="n">
-        <v>10543888.88888889</v>
+        <v>3151666.666666667</v>
       </c>
       <c r="AP6" t="n">
-        <v>78.63101851851852</v>
+        <v>74.21666666666665</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.606018518518519</v>
+        <v>1.016666666666667</v>
       </c>
       <c r="AR6" t="n">
-        <v>24.44462991030497</v>
+        <v>25.63015457899407</v>
       </c>
       <c r="AS6" t="n">
-        <v>186.7074735587322</v>
+        <v>183.4706953719703</v>
       </c>
       <c r="AT6" t="n">
-        <v>70.49606751837872</v>
+        <v>73.49740422484784</v>
       </c>
       <c r="AU6" t="n">
-        <v>19186.5910384217</v>
+        <v>22261.34046295864</v>
       </c>
       <c r="AV6" t="n">
-        <v>3572388.013291903</v>
+        <v>6100050.358816296</v>
       </c>
       <c r="AW6" t="n">
-        <v>76.78116404317778</v>
+        <v>77.37456218185214</v>
       </c>
       <c r="AX6" t="n">
-        <v>1</v>
+        <v>1.202388735814692</v>
       </c>
       <c r="AY6" t="n">
-        <v>26.86084050706476</v>
+        <v>25.67282608695652</v>
       </c>
       <c r="AZ6" t="n">
-        <v>183.3518257105214</v>
+        <v>185.1786231884058</v>
       </c>
       <c r="BA6" t="n">
-        <v>74.39824643955079</v>
+        <v>69.60688405797102</v>
       </c>
       <c r="BB6" t="n">
-        <v>24267.14051267827</v>
+        <v>19845.65217391304</v>
       </c>
       <c r="BC6" t="n">
-        <v>7185075.060014992</v>
+        <v>2247119.565217391</v>
       </c>
       <c r="BD6" t="n">
-        <v>76.81051649215264</v>
+        <v>72.58188405797101</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.408638443935927</v>
+        <v>1.043478260869565</v>
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>KUx4Q7x1</t>
+          <t>2VSFgl3c</t>
         </is>
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>0jdIgO6t</t>
+          <t>4ljanukM</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>zwD8uYZ9</t>
+          <t>r3GGwC4M</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45570.5625</v>
+        <v>45584.4375</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">dingert c 
+          <t xml:space="preserve">stieler t 
   ger </t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">millerntor stadion
-  hamburg </t>
+          <t xml:space="preserve">bayarena
+  leverkusen </t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>29546</v>
+        <v>30210</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>ILyJuN3g</t>
+          <t>4jcj2zMd</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>EuakNmc1</t>
+          <t>8vndvXTk</t>
         </is>
       </c>
       <c r="H7" t="n">
@@ -1759,181 +1711,149 @@
           <t>bundesliga</t>
         </is>
       </c>
-      <c r="N7" t="n">
-        <v>29.6</v>
-      </c>
-      <c r="O7" t="n">
-        <v>187</v>
-      </c>
-      <c r="P7" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>326</v>
-      </c>
-      <c r="R7" t="n">
-        <v>71000</v>
-      </c>
-      <c r="S7" t="n">
-        <v>3310000</v>
-      </c>
-      <c r="T7" t="n">
-        <v>335</v>
-      </c>
-      <c r="U7" t="n">
-        <v>5</v>
-      </c>
-      <c r="V7" t="n">
-        <v>27</v>
-      </c>
-      <c r="W7" t="n">
-        <v>185</v>
-      </c>
-      <c r="X7" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>76</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>26000</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>8000000</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>78</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>1</v>
-      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="inlineStr"/>
+      <c r="X7" t="inlineStr"/>
+      <c r="Y7" t="inlineStr"/>
+      <c r="Z7" t="inlineStr"/>
+      <c r="AA7" t="inlineStr"/>
+      <c r="AB7" t="inlineStr"/>
+      <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="n">
-        <v>26.79141414141414</v>
+        <v>26.40674603174603</v>
       </c>
       <c r="AE7" t="n">
-        <v>185.4481481481481</v>
+        <v>184.3571428571429</v>
       </c>
       <c r="AF7" t="n">
-        <v>70.55235690235691</v>
+        <v>83.76865079365079</v>
       </c>
       <c r="AG7" t="n">
-        <v>17073.90572390573</v>
+        <v>99564.28571428571</v>
       </c>
       <c r="AH7" t="n">
-        <v>2309494.94949495</v>
+        <v>50273214.28571428</v>
       </c>
       <c r="AI7" t="n">
-        <v>73.50185185185185</v>
+        <v>85.91904761904763</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1</v>
+        <v>3.064285714285715</v>
       </c>
       <c r="AK7" t="n">
-        <v>27.66111111111111</v>
+        <v>24.74444444444444</v>
       </c>
       <c r="AL7" t="n">
-        <v>183.4018518518519</v>
+        <v>185.0722222222223</v>
       </c>
       <c r="AM7" t="n">
-        <v>74.87777777777778</v>
+        <v>76.98333333333333</v>
       </c>
       <c r="AN7" t="n">
-        <v>25170.37037037037</v>
+        <v>35133.33333333334</v>
       </c>
       <c r="AO7" t="n">
-        <v>6554629.62962963</v>
+        <v>15228055.55555556</v>
       </c>
       <c r="AP7" t="n">
-        <v>76.90925925925926</v>
+        <v>81.71111111111111</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.411111111111111</v>
+        <v>1.694444444444445</v>
       </c>
       <c r="AR7" t="n">
-        <v>25.52275828460039</v>
+        <v>24.56634355496585</v>
       </c>
       <c r="AS7" t="n">
-        <v>184.5858674463937</v>
+        <v>180.7619096761511</v>
       </c>
       <c r="AT7" t="n">
-        <v>68.49556530214424</v>
+        <v>80.84288294265075</v>
       </c>
       <c r="AU7" t="n">
-        <v>16164.32748538012</v>
+        <v>82188.14560912084</v>
       </c>
       <c r="AV7" t="n">
-        <v>1827714.424951267</v>
+        <v>39435822.47592019</v>
       </c>
       <c r="AW7" t="n">
-        <v>72.08396686159844</v>
+        <v>84.59387316330042</v>
       </c>
       <c r="AX7" t="n">
-        <v>1</v>
+        <v>2.302458351761757</v>
       </c>
       <c r="AY7" t="n">
-        <v>25.99150527834739</v>
+        <v>22.37575757575758</v>
       </c>
       <c r="AZ7" t="n">
-        <v>183.8311460469355</v>
+        <v>185.0691368572948</v>
       </c>
       <c r="BA7" t="n">
-        <v>71.37496392496392</v>
+        <v>72.67647527910687</v>
       </c>
       <c r="BB7" t="n">
-        <v>21557.77322093112</v>
+        <v>25312.00918964077</v>
       </c>
       <c r="BC7" t="n">
-        <v>3239910.334548492</v>
+        <v>8847221.671603251</v>
       </c>
       <c r="BD7" t="n">
-        <v>76.42352851826536</v>
+        <v>81.03199855699854</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.130392268550163</v>
+        <v>1.361995898838004</v>
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>YZPE6Sx7</t>
+          <t>hAcTWKKN</t>
         </is>
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>4ljanukM</t>
+          <t>UgdQz0fK</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>0KbQSfj4</t>
+          <t>M93rhBJF</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45571.4375</v>
+        <v>45584.4375</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">siebert d 
+          <t xml:space="preserve">badstubner f 
   ger </t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">voith arena
-  heidenheim </t>
+          <t xml:space="preserve">europa park stadion
+  freiburg </t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>15000</v>
+        <v>34700</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>KWixEVWi</t>
+          <t>fiEQZ7C7</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>KbS1suSm</t>
+          <t>fTVNku3I</t>
         </is>
       </c>
       <c r="H8" t="n">
@@ -1958,181 +1878,149 @@
           <t>bundesliga</t>
         </is>
       </c>
-      <c r="N8" t="n">
-        <v>24.6</v>
-      </c>
-      <c r="O8" t="n">
-        <v>186.8</v>
-      </c>
-      <c r="P8" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>349</v>
-      </c>
-      <c r="R8" t="n">
-        <v>100000</v>
-      </c>
-      <c r="S8" t="n">
-        <v>14600000</v>
-      </c>
-      <c r="T8" t="n">
-        <v>370</v>
-      </c>
-      <c r="U8" t="n">
-        <v>6</v>
-      </c>
-      <c r="V8" t="n">
-        <v>25.25</v>
-      </c>
-      <c r="W8" t="n">
-        <v>180.75</v>
-      </c>
-      <c r="X8" t="n">
-        <v>4</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>308</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>184000</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>70500000</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>332</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>9</v>
-      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" t="inlineStr"/>
+      <c r="X8" t="inlineStr"/>
+      <c r="Y8" t="inlineStr"/>
+      <c r="Z8" t="inlineStr"/>
+      <c r="AA8" t="inlineStr"/>
+      <c r="AB8" t="inlineStr"/>
+      <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="n">
-        <v>26.81666666666666</v>
+        <v>26.78730158730159</v>
       </c>
       <c r="AE8" t="n">
-        <v>187.1166666666667</v>
+        <v>183.765873015873</v>
       </c>
       <c r="AF8" t="n">
-        <v>72.46666666666665</v>
+        <v>76.15119047619048</v>
       </c>
       <c r="AG8" t="n">
-        <v>22100</v>
+        <v>26336.90476190476</v>
       </c>
       <c r="AH8" t="n">
-        <v>3151666.666666667</v>
+        <v>10731904.76190476</v>
       </c>
       <c r="AI8" t="n">
-        <v>74.21666666666665</v>
+        <v>78.68373015873014</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1.016666666666667</v>
+        <v>1.619444444444445</v>
       </c>
       <c r="AK8" t="n">
-        <v>25.87794612794613</v>
+        <v>25.79166666666667</v>
       </c>
       <c r="AL8" t="n">
-        <v>183.3648148148148</v>
+        <v>185.0416666666667</v>
       </c>
       <c r="AM8" t="n">
-        <v>80.43636363636362</v>
+        <v>73.70833333333333</v>
       </c>
       <c r="AN8" t="n">
-        <v>56660.60606060606</v>
+        <v>22291.66666666667</v>
       </c>
       <c r="AO8" t="n">
-        <v>30434343.43434344</v>
+        <v>5350000</v>
       </c>
       <c r="AP8" t="n">
-        <v>84.00151515151515</v>
+        <v>76.91666666666667</v>
       </c>
       <c r="AQ8" t="n">
-        <v>2.224915824915825</v>
+        <v>1.125</v>
       </c>
       <c r="AR8" t="n">
-        <v>25.67282608695652</v>
+        <v>26.78755273276358</v>
       </c>
       <c r="AS8" t="n">
-        <v>185.1786231884058</v>
+        <v>183.3636766959748</v>
       </c>
       <c r="AT8" t="n">
-        <v>69.60688405797102</v>
+        <v>74.21713048855905</v>
       </c>
       <c r="AU8" t="n">
-        <v>19845.65217391304</v>
+        <v>23961.89683695405</v>
       </c>
       <c r="AV8" t="n">
-        <v>2247119.565217391</v>
+        <v>6877269.306099807</v>
       </c>
       <c r="AW8" t="n">
-        <v>72.58188405797101</v>
+        <v>76.81895202432959</v>
       </c>
       <c r="AX8" t="n">
-        <v>1.043478260869565</v>
+        <v>1.387528604118993</v>
       </c>
       <c r="AY8" t="n">
-        <v>25.33862229102168</v>
+        <v>24.81548711988783</v>
       </c>
       <c r="AZ8" t="n">
-        <v>184.7739042254329</v>
+        <v>184.1908611131853</v>
       </c>
       <c r="BA8" t="n">
-        <v>78.53386581240683</v>
+        <v>72.5454978243291</v>
       </c>
       <c r="BB8" t="n">
-        <v>52439.83058135535</v>
+        <v>21177.0190931237</v>
       </c>
       <c r="BC8" t="n">
-        <v>24871615.74790735</v>
+        <v>4952682.416666826</v>
       </c>
       <c r="BD8" t="n">
-        <v>82.27483946795093</v>
+        <v>76.55772420610985</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.980187908496732</v>
+        <v>1.158487278483961</v>
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>vZA6VYpf</t>
+          <t>4fuCGs9P</t>
         </is>
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>2VSFgl3c</t>
+          <t>M5BRZDsC</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>ShoJUGLi</t>
+          <t>Eq0zfXl3</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45571.52083333334</v>
+        <v>45584.4375</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">zwayer f 
+          <t xml:space="preserve">burda m 
   ger </t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">deutsche bank park
-  frankfurt </t>
+          <t xml:space="preserve">prezero arena
+  sinsheim </t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>58000</v>
+        <v>30150</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>8vndvXTk</t>
+          <t>hQAtP9Sl</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>nVp0wiqd</t>
+          <t>8Y2m6ADe</t>
         </is>
       </c>
       <c r="H9" t="n">
@@ -2157,181 +2045,149 @@
           <t>bundesliga</t>
         </is>
       </c>
-      <c r="N9" t="n">
-        <v>19</v>
-      </c>
-      <c r="O9" t="n">
-        <v>172</v>
-      </c>
-      <c r="P9" t="n">
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="inlineStr"/>
+      <c r="X9" t="inlineStr"/>
+      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="inlineStr"/>
+      <c r="AA9" t="inlineStr"/>
+      <c r="AB9" t="inlineStr"/>
+      <c r="AC9" t="inlineStr"/>
+      <c r="AD9" t="n">
+        <v>27.68703703703704</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>186.0796296296296</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>74.88333333333334</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>30257.40740740741</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>7417592.592592592</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>78.01296296296296</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>1.655555555555556</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>28.33888888888889</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>185.2921296296296</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>71.6962962962963</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>17048.14814814815</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>2222615.740740741</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>73.5712962962963</v>
+      </c>
+      <c r="AQ9" t="n">
         <v>1</v>
       </c>
-      <c r="Q9" t="n">
-        <v>59</v>
-      </c>
-      <c r="R9" t="n">
-        <v>3000</v>
-      </c>
-      <c r="S9" t="n">
-        <v>575000</v>
-      </c>
-      <c r="T9" t="n">
-        <v>76</v>
-      </c>
-      <c r="U9" t="n">
+      <c r="AR9" t="n">
+        <v>24.35341130604289</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>186.3588693957115</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>71.36042884990253</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>24539.57115009746</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>5892831.384015595</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>77.62027290448343</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>1.239278752436647</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>25.40532515300317</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>185.6896861308626</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>68.42912900652838</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>15078.88310519889</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>1804867.324797665</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>74.38585339668931</v>
+      </c>
+      <c r="BE9" t="n">
         <v>1</v>
       </c>
-      <c r="V9" t="n">
-        <v>21.66666666666667</v>
-      </c>
-      <c r="W9" t="n">
-        <v>183.5</v>
-      </c>
-      <c r="X9" t="n">
-        <v>6</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>444</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>276000</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>189150000</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>498</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>10</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>24.74444444444444</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>185.0722222222223</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>76.98333333333333</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>35133.33333333334</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>15228055.55555556</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>81.71111111111111</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>1.694444444444445</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>26.78333333333333</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>183.75</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>82.85000000000001</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>76950</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>47282916.66666666</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>85.68333333333332</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>3.083333333333333</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>22.37575757575758</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>185.0691368572948</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>72.67647527910687</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>25312.00918964077</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>8847221.671603251</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>81.03199855699854</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>1.361995898838004</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>26.85416666666667</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>183.3313484581867</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>81.70669934640523</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>75162.88545332663</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>38261669.78276353</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>83.96209359812302</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>2.684724317077258</v>
-      </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>A15eUM4C</t>
+          <t>KUx4Q7x1</t>
         </is>
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>hAcTWKKN</t>
+          <t>f3ddUIXs</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>nc8W6DTp</t>
+          <t>E7rNpTBk</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45571.60416666666</v>
+        <v>45584.4375</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">reichel t 
+          <t xml:space="preserve">siebert d 
   ger </t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">mhparena
-  stuttgart </t>
+          <t xml:space="preserve">mewa arena
+  mainz </t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>60449</v>
+        <v>34000</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>nJQmYp1B</t>
+          <t>EuakNmc1</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>hQAtP9Sl</t>
+          <t>KbS1suSm</t>
         </is>
       </c>
       <c r="H10" t="n">
@@ -2356,181 +2212,149 @@
           <t>bundesliga</t>
         </is>
       </c>
-      <c r="N10" t="n">
-        <v>23.33333333333333</v>
-      </c>
-      <c r="O10" t="n">
-        <v>186</v>
-      </c>
-      <c r="P10" t="n">
-        <v>6</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>431</v>
-      </c>
-      <c r="R10" t="n">
-        <v>116000</v>
-      </c>
-      <c r="S10" t="n">
-        <v>32600000</v>
-      </c>
-      <c r="T10" t="n">
-        <v>471</v>
-      </c>
-      <c r="U10" t="n">
-        <v>8</v>
-      </c>
-      <c r="V10" t="n">
-        <v>26.4</v>
-      </c>
-      <c r="W10" t="n">
-        <v>183.2</v>
-      </c>
-      <c r="X10" t="n">
-        <v>5</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>371</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>142000</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>30200000</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>386</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>8</v>
-      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="inlineStr"/>
+      <c r="W10" t="inlineStr"/>
+      <c r="X10" t="inlineStr"/>
+      <c r="Y10" t="inlineStr"/>
+      <c r="Z10" t="inlineStr"/>
+      <c r="AA10" t="inlineStr"/>
+      <c r="AB10" t="inlineStr"/>
+      <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="n">
-        <v>24.95714285714286</v>
+        <v>27.55238095238095</v>
       </c>
       <c r="AE10" t="n">
-        <v>185.7636363636364</v>
+        <v>183.3444444444445</v>
       </c>
       <c r="AF10" t="n">
-        <v>76.23116883116883</v>
+        <v>74.82380952380952</v>
       </c>
       <c r="AG10" t="n">
-        <v>27564.93506493506</v>
+        <v>25260.31746031746</v>
       </c>
       <c r="AH10" t="n">
-        <v>13686363.63636363</v>
+        <v>6533968.253968254</v>
       </c>
       <c r="AI10" t="n">
-        <v>79.42467532467533</v>
+        <v>76.96507936507938</v>
       </c>
       <c r="AJ10" t="n">
-        <v>1.45974025974026</v>
+        <v>1.409523809523809</v>
       </c>
       <c r="AK10" t="n">
-        <v>27.68703703703704</v>
+        <v>25.87794612794613</v>
       </c>
       <c r="AL10" t="n">
-        <v>186.0796296296296</v>
+        <v>183.3648148148148</v>
       </c>
       <c r="AM10" t="n">
-        <v>74.88333333333334</v>
+        <v>80.43636363636362</v>
       </c>
       <c r="AN10" t="n">
-        <v>30257.40740740741</v>
+        <v>56660.60606060606</v>
       </c>
       <c r="AO10" t="n">
-        <v>7417592.592592592</v>
+        <v>30434343.43434344</v>
       </c>
       <c r="AP10" t="n">
-        <v>78.01296296296296</v>
+        <v>84.00151515151515</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1.655555555555556</v>
+        <v>2.224915824915825</v>
       </c>
       <c r="AR10" t="n">
-        <v>24.18921166552746</v>
+        <v>25.68795690525014</v>
       </c>
       <c r="AS10" t="n">
-        <v>184.4195906432749</v>
+        <v>183.6457442307066</v>
       </c>
       <c r="AT10" t="n">
-        <v>73.40942507784612</v>
+        <v>71.26425479282622</v>
       </c>
       <c r="AU10" t="n">
-        <v>24026.95374800638</v>
+        <v>21373.32942746477</v>
       </c>
       <c r="AV10" t="n">
-        <v>10309174.54621402</v>
+        <v>3395399.334374898</v>
       </c>
       <c r="AW10" t="n">
-        <v>78.25894281157441</v>
+        <v>76.77254825375128</v>
       </c>
       <c r="AX10" t="n">
-        <v>1.483652312599681</v>
+        <v>1.130812420662045</v>
       </c>
       <c r="AY10" t="n">
-        <v>24.35341130604289</v>
+        <v>25.33862229102168</v>
       </c>
       <c r="AZ10" t="n">
-        <v>186.3588693957115</v>
+        <v>184.7739042254329</v>
       </c>
       <c r="BA10" t="n">
-        <v>71.36042884990253</v>
+        <v>78.53386581240683</v>
       </c>
       <c r="BB10" t="n">
-        <v>24539.57115009746</v>
+        <v>52439.83058135535</v>
       </c>
       <c r="BC10" t="n">
-        <v>5892831.384015595</v>
+        <v>24871615.74790735</v>
       </c>
       <c r="BD10" t="n">
-        <v>77.62027290448343</v>
+        <v>82.27483946795093</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.239278752436647</v>
+        <v>1.980187908496732</v>
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>f3ddUIXs</t>
+          <t>0jdIgO6t</t>
         </is>
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>4fuCGs9P</t>
+          <t>2VSFgl3c</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>z1eeWTdd</t>
+          <t>2mcmYkSq</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>45583.64583333334</v>
+        <v>45584.5625</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve">gerach t 
+          <t xml:space="preserve">jablonski s 
   ger </t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">signal iduna park
-  dortmund </t>
+          <t xml:space="preserve">allianz arena
+  munich </t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>81365</v>
+        <v>75024</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>nP1i5US1</t>
+          <t>nVp0wiqd</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>ILyJuN3g</t>
+          <t>nJQmYp1B</t>
         </is>
       </c>
       <c r="H11" t="n">
@@ -2572,132 +2396,132 @@
       <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="n">
-        <v>26.71666666666667</v>
+        <v>26.78333333333333</v>
       </c>
       <c r="AE11" t="n">
-        <v>186.0545454545454</v>
+        <v>183.75</v>
       </c>
       <c r="AF11" t="n">
-        <v>82.01363636363635</v>
+        <v>82.85000000000001</v>
       </c>
       <c r="AG11" t="n">
-        <v>58143.93939393939</v>
+        <v>76950</v>
       </c>
       <c r="AH11" t="n">
-        <v>37515909.09090909</v>
+        <v>47282916.66666666</v>
       </c>
       <c r="AI11" t="n">
-        <v>84.09696969696969</v>
+        <v>85.68333333333332</v>
       </c>
       <c r="AJ11" t="n">
-        <v>2.63030303030303</v>
+        <v>3.083333333333333</v>
       </c>
       <c r="AK11" t="n">
-        <v>26.79141414141414</v>
+        <v>24.95714285714286</v>
       </c>
       <c r="AL11" t="n">
-        <v>185.4481481481481</v>
+        <v>185.7636363636364</v>
       </c>
       <c r="AM11" t="n">
-        <v>70.55235690235691</v>
+        <v>76.23116883116883</v>
       </c>
       <c r="AN11" t="n">
-        <v>17073.90572390573</v>
+        <v>27564.93506493506</v>
       </c>
       <c r="AO11" t="n">
-        <v>2309494.94949495</v>
+        <v>13686363.63636363</v>
       </c>
       <c r="AP11" t="n">
-        <v>73.50185185185185</v>
+        <v>79.42467532467533</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1</v>
+        <v>1.45974025974026</v>
       </c>
       <c r="AR11" t="n">
-        <v>24.649016563147</v>
+        <v>26.85416666666667</v>
       </c>
       <c r="AS11" t="n">
-        <v>183.9863103080494</v>
+        <v>183.3313484581867</v>
       </c>
       <c r="AT11" t="n">
-        <v>77.62367620302403</v>
+        <v>81.70669934640523</v>
       </c>
       <c r="AU11" t="n">
-        <v>42621.67325428195</v>
+        <v>75162.88545332663</v>
       </c>
       <c r="AV11" t="n">
-        <v>22335895.13143861</v>
+        <v>38261669.78276353</v>
       </c>
       <c r="AW11" t="n">
-        <v>83.02270060857018</v>
+        <v>83.96209359812302</v>
       </c>
       <c r="AX11" t="n">
-        <v>1.854321161929858</v>
+        <v>2.684724317077258</v>
       </c>
       <c r="AY11" t="n">
-        <v>25.52275828460039</v>
+        <v>24.18921166552746</v>
       </c>
       <c r="AZ11" t="n">
-        <v>184.5858674463937</v>
+        <v>184.4195906432749</v>
       </c>
       <c r="BA11" t="n">
-        <v>68.49556530214424</v>
+        <v>73.40942507784612</v>
       </c>
       <c r="BB11" t="n">
-        <v>16164.32748538012</v>
+        <v>24026.95374800638</v>
       </c>
       <c r="BC11" t="n">
-        <v>1827714.424951267</v>
+        <v>10309174.54621402</v>
       </c>
       <c r="BD11" t="n">
-        <v>72.08396686159844</v>
+        <v>78.25894281157441</v>
       </c>
       <c r="BE11" t="n">
-        <v>1</v>
+        <v>1.483652312599681</v>
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>IkCftsQm</t>
+          <t>K6A2elS9</t>
         </is>
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>0jdIgO6t</t>
+          <t>GzfvcwRj</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>fHjVr7t2</t>
+          <t>nBwH6AY8</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>45584.4375</v>
+        <v>45585.4375</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t xml:space="preserve">exner f 
+          <t xml:space="preserve">reichel t 
   ger </t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">borussia park
-  monchengladbach </t>
+          <t xml:space="preserve">holstein stadion
+  kiel </t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>54042</v>
+        <v>15034</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>88HSzjDr</t>
+          <t>63WsD2ei</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>KWixEVWi</t>
+          <t>pzHW4oaE</t>
         </is>
       </c>
       <c r="H12" t="n">
@@ -2739,132 +2563,132 @@
       <c r="AB12" t="inlineStr"/>
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="n">
-        <v>26.13333333333334</v>
+        <v>26.66814574314574</v>
       </c>
       <c r="AE12" t="n">
-        <v>184.65</v>
+        <v>185.6328282828283</v>
       </c>
       <c r="AF12" t="n">
-        <v>75.55</v>
+        <v>69.95238095238095</v>
       </c>
       <c r="AG12" t="n">
-        <v>24516.66666666667</v>
+        <v>16681.49350649351</v>
       </c>
       <c r="AH12" t="n">
-        <v>8460000</v>
+        <v>1926691.919191919</v>
       </c>
       <c r="AI12" t="n">
-        <v>77.98333333333333</v>
+        <v>72.3401875901876</v>
       </c>
       <c r="AJ12" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="AK12" t="n">
-        <v>26.81666666666666</v>
+        <v>26.98412698412698</v>
       </c>
       <c r="AL12" t="n">
-        <v>187.1166666666667</v>
+        <v>186.3702741702742</v>
       </c>
       <c r="AM12" t="n">
-        <v>72.46666666666665</v>
+        <v>74.8975468975469</v>
       </c>
       <c r="AN12" t="n">
-        <v>22100</v>
+        <v>27718.47041847042</v>
       </c>
       <c r="AO12" t="n">
-        <v>3151666.666666667</v>
+        <v>6582539.682539682</v>
       </c>
       <c r="AP12" t="n">
-        <v>74.21666666666665</v>
+        <v>77.52539682539683</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1.016666666666667</v>
+        <v>1.413131313131313</v>
       </c>
       <c r="AR12" t="n">
-        <v>25.55264065962007</v>
+        <v>25.60353757063466</v>
       </c>
       <c r="AS12" t="n">
-        <v>183.6602557117432</v>
+        <v>184.9785753202883</v>
       </c>
       <c r="AT12" t="n">
-        <v>73.58824143692566</v>
+        <v>68.25622181748368</v>
       </c>
       <c r="AU12" t="n">
-        <v>22408.07180995968</v>
+        <v>15618.43791673801</v>
       </c>
       <c r="AV12" t="n">
-        <v>6264900.021793614</v>
+        <v>1839729.603511885</v>
       </c>
       <c r="AW12" t="n">
-        <v>77.50048127565289</v>
+        <v>72.59229777341906</v>
       </c>
       <c r="AX12" t="n">
-        <v>1.212310667974284</v>
+        <v>1</v>
       </c>
       <c r="AY12" t="n">
-        <v>25.67282608695652</v>
+        <v>26.37341516316672</v>
       </c>
       <c r="AZ12" t="n">
-        <v>185.1786231884058</v>
+        <v>182.8920043379671</v>
       </c>
       <c r="BA12" t="n">
-        <v>69.60688405797102</v>
+        <v>73.10748299319728</v>
       </c>
       <c r="BB12" t="n">
-        <v>19845.65217391304</v>
+        <v>24930.5333727694</v>
       </c>
       <c r="BC12" t="n">
-        <v>2247119.565217391</v>
+        <v>4181897.860593513</v>
       </c>
       <c r="BD12" t="n">
-        <v>72.58188405797101</v>
+        <v>75.97586512866017</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.043478260869565</v>
+        <v>1.159124519372967</v>
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>M5BRZDsC</t>
+          <t>hAcTWKKN</t>
         </is>
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>4ljanukM</t>
+          <t>IkCftsQm</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>r3GGwC4M</t>
+          <t>rPiijklS</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>45584.4375</v>
+        <v>45585.52083333334</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t xml:space="preserve">stieler t 
+          <t xml:space="preserve">welz t 
   ger </t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">bayarena
-  leverkusen </t>
+          <t xml:space="preserve">volkswagen arena
+  wolfsburg </t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>30210</v>
+        <v>28917</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>4jcj2zMd</t>
+          <t>nwkTahLL</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>8vndvXTk</t>
+          <t>Ig1f1fy3</t>
         </is>
       </c>
       <c r="H13" t="n">
@@ -2906,598 +2730,97 @@
       <c r="AB13" t="inlineStr"/>
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="n">
-        <v>26.35787037037037</v>
+        <v>24.70833333333333</v>
       </c>
       <c r="AE13" t="n">
-        <v>184.4333333333333</v>
+        <v>184.7083333333333</v>
       </c>
       <c r="AF13" t="n">
-        <v>83.63009259259259</v>
+        <v>75.2986111111111</v>
       </c>
       <c r="AG13" t="n">
-        <v>98558.33333333333</v>
+        <v>36312.5</v>
       </c>
       <c r="AH13" t="n">
-        <v>49468750</v>
+        <v>10284953.7037037</v>
       </c>
       <c r="AI13" t="n">
-        <v>85.83888888888889</v>
+        <v>79.89814814814814</v>
       </c>
       <c r="AJ13" t="n">
-        <v>3.025</v>
+        <v>1.418981481481481</v>
       </c>
       <c r="AK13" t="n">
-        <v>24.74444444444444</v>
+        <v>26.98051948051948</v>
       </c>
       <c r="AL13" t="n">
-        <v>185.0722222222223</v>
+        <v>183.7805194805195</v>
       </c>
       <c r="AM13" t="n">
-        <v>76.98333333333333</v>
+        <v>74.43636363636365</v>
       </c>
       <c r="AN13" t="n">
-        <v>35133.33333333334</v>
+        <v>23588.31168831169</v>
       </c>
       <c r="AO13" t="n">
-        <v>15228055.55555556</v>
+        <v>6014415.584415585</v>
       </c>
       <c r="AP13" t="n">
-        <v>81.71111111111111</v>
+        <v>76.79350649350648</v>
       </c>
       <c r="AQ13" t="n">
-        <v>1.694444444444445</v>
+        <v>1.094805194805195</v>
       </c>
       <c r="AR13" t="n">
-        <v>24.53296406281811</v>
+        <v>24.70891265597148</v>
       </c>
       <c r="AS13" t="n">
-        <v>180.5564682013156</v>
+        <v>184.8741501145913</v>
       </c>
       <c r="AT13" t="n">
-        <v>80.85853288683894</v>
+        <v>73.08691325014854</v>
       </c>
       <c r="AU13" t="n">
-        <v>82395.97593423336</v>
+        <v>32352.28333757745</v>
       </c>
       <c r="AV13" t="n">
-        <v>40250463.78200404</v>
+        <v>7859812.515915456</v>
       </c>
       <c r="AW13" t="n">
-        <v>84.65014075805762</v>
+        <v>78.21184428316782</v>
       </c>
       <c r="AX13" t="n">
-        <v>2.317095259156293</v>
+        <v>1.363718062982769</v>
       </c>
       <c r="AY13" t="n">
-        <v>22.37575757575758</v>
+        <v>24.60253992311855</v>
       </c>
       <c r="AZ13" t="n">
-        <v>185.0691368572948</v>
+        <v>186.3206916217704</v>
       </c>
       <c r="BA13" t="n">
-        <v>72.67647527910687</v>
+        <v>70.48234358718177</v>
       </c>
       <c r="BB13" t="n">
-        <v>25312.00918964077</v>
+        <v>19202.79231864717</v>
       </c>
       <c r="BC13" t="n">
-        <v>8847221.671603251</v>
+        <v>3470618.297107345</v>
       </c>
       <c r="BD13" t="n">
-        <v>81.03199855699854</v>
+        <v>76.51956917986665</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.361995898838004</v>
+        <v>1</v>
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>K6A2elS9</t>
+          <t>8f6APkLc</t>
         </is>
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>UgdQz0fK</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>M93rhBJF</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="n">
-        <v>45584.4375</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">siebert d 
-  ger </t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">europa park stadion
-  freiburg </t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>34700</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>fiEQZ7C7</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>fTVNku3I</t>
-        </is>
-      </c>
-      <c r="H14" t="n">
-        <v>59</v>
-      </c>
-      <c r="I14" t="n">
-        <v>591</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>bundesliga</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr"/>
-      <c r="P14" t="inlineStr"/>
-      <c r="Q14" t="inlineStr"/>
-      <c r="R14" t="inlineStr"/>
-      <c r="S14" t="inlineStr"/>
-      <c r="T14" t="inlineStr"/>
-      <c r="U14" t="inlineStr"/>
-      <c r="V14" t="inlineStr"/>
-      <c r="W14" t="inlineStr"/>
-      <c r="X14" t="inlineStr"/>
-      <c r="Y14" t="inlineStr"/>
-      <c r="Z14" t="inlineStr"/>
-      <c r="AA14" t="inlineStr"/>
-      <c r="AB14" t="inlineStr"/>
-      <c r="AC14" t="inlineStr"/>
-      <c r="AD14" t="n">
-        <v>26.73518518518519</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>183.7101851851852</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>76.02638888888889</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>26159.72222222222</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>10543888.88888889</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>78.63101851851852</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>1.606018518518519</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>25.79166666666667</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>185.0416666666667</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>73.70833333333333</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>22291.66666666667</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>5350000</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>76.91666666666667</v>
-      </c>
-      <c r="AQ14" t="n">
-        <v>1.125</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>26.86084050706476</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>183.3518257105214</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>74.39824643955079</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>24267.14051267827</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>7185075.060014992</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>76.81051649215264</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>1.408638443935927</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>24.70897739744489</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>184.1469137229586</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>72.43944443141424</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>21145.91621470492</v>
-      </c>
-      <c r="BC14" t="n">
-        <v>4947826.455808267</v>
-      </c>
-      <c r="BD14" t="n">
-        <v>76.57492066470394</v>
-      </c>
-      <c r="BE14" t="n">
-        <v>1.16975030974644</v>
-      </c>
-      <c r="BF14" t="inlineStr">
-        <is>
           <t>YZPE6Sx7</t>
-        </is>
-      </c>
-      <c r="BG14" t="inlineStr">
-        <is>
-          <t>2VSFgl3c</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>Eq0zfXl3</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="n">
-        <v>45584.4375</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">brych f 
-  ger </t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">prezero arena
-  sinsheim </t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>30150</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>hQAtP9Sl</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>8Y2m6ADe</t>
-        </is>
-      </c>
-      <c r="H15" t="n">
-        <v>59</v>
-      </c>
-      <c r="I15" t="n">
-        <v>591</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>bundesliga</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
-      <c r="O15" t="inlineStr"/>
-      <c r="P15" t="inlineStr"/>
-      <c r="Q15" t="inlineStr"/>
-      <c r="R15" t="inlineStr"/>
-      <c r="S15" t="inlineStr"/>
-      <c r="T15" t="inlineStr"/>
-      <c r="U15" t="inlineStr"/>
-      <c r="V15" t="inlineStr"/>
-      <c r="W15" t="inlineStr"/>
-      <c r="X15" t="inlineStr"/>
-      <c r="Y15" t="inlineStr"/>
-      <c r="Z15" t="inlineStr"/>
-      <c r="AA15" t="inlineStr"/>
-      <c r="AB15" t="inlineStr"/>
-      <c r="AC15" t="inlineStr"/>
-      <c r="AD15" t="n">
-        <v>27.68703703703704</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>186.0796296296296</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>74.88333333333334</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>30257.40740740741</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>7417592.592592592</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>78.01296296296296</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>1.655555555555556</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>28.05666666666666</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>185.1505555555555</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>71.58555555555554</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>16957.77777777778</v>
-      </c>
-      <c r="AO15" t="n">
-        <v>2249013.888888889</v>
-      </c>
-      <c r="AP15" t="n">
-        <v>73.66055555555556</v>
-      </c>
-      <c r="AQ15" t="n">
-        <v>1</v>
-      </c>
-      <c r="AR15" t="n">
-        <v>24.35341130604289</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>186.3588693957115</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>71.36042884990253</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>24539.57115009746</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>5892831.384015595</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>77.62027290448343</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>1.239278752436647</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>25.24211011440113</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>185.612326127032</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>68.23141973838568</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>14886.9020842705</v>
-      </c>
-      <c r="BC15" t="n">
-        <v>1770742.648161379</v>
-      </c>
-      <c r="BD15" t="n">
-        <v>74.39888024485548</v>
-      </c>
-      <c r="BE15" t="n">
-        <v>1</v>
-      </c>
-      <c r="BF15" t="inlineStr">
-        <is>
-          <t>KUx4Q7x1</t>
-        </is>
-      </c>
-      <c r="BG15" t="inlineStr">
-        <is>
-          <t>8f6APkLc</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>E7rNpTBk</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="n">
-        <v>45584.4375</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">siebert d 
-  ger </t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">mewa arena
-  mainz </t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>34000</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>EuakNmc1</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>KbS1suSm</t>
-        </is>
-      </c>
-      <c r="H16" t="n">
-        <v>59</v>
-      </c>
-      <c r="I16" t="n">
-        <v>591</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="n">
-        <v>20242025</v>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>bundesliga</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
-      <c r="O16" t="inlineStr"/>
-      <c r="P16" t="inlineStr"/>
-      <c r="Q16" t="inlineStr"/>
-      <c r="R16" t="inlineStr"/>
-      <c r="S16" t="inlineStr"/>
-      <c r="T16" t="inlineStr"/>
-      <c r="U16" t="inlineStr"/>
-      <c r="V16" t="inlineStr"/>
-      <c r="W16" t="inlineStr"/>
-      <c r="X16" t="inlineStr"/>
-      <c r="Y16" t="inlineStr"/>
-      <c r="Z16" t="inlineStr"/>
-      <c r="AA16" t="inlineStr"/>
-      <c r="AB16" t="inlineStr"/>
-      <c r="AC16" t="inlineStr"/>
-      <c r="AD16" t="n">
-        <v>27.66111111111111</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>183.4018518518519</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>74.87777777777778</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>25170.37037037037</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>6554629.62962963</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>76.90925925925926</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>1.411111111111111</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>25.87794612794613</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>183.3648148148148</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>80.43636363636362</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>56660.60606060606</v>
-      </c>
-      <c r="AO16" t="n">
-        <v>30434343.43434344</v>
-      </c>
-      <c r="AP16" t="n">
-        <v>84.00151515151515</v>
-      </c>
-      <c r="AQ16" t="n">
-        <v>2.224915824915825</v>
-      </c>
-      <c r="AR16" t="n">
-        <v>25.99150527834739</v>
-      </c>
-      <c r="AS16" t="n">
-        <v>183.8311460469355</v>
-      </c>
-      <c r="AT16" t="n">
-        <v>71.37496392496392</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>21557.77322093112</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>3239910.334548492</v>
-      </c>
-      <c r="AW16" t="n">
-        <v>76.42352851826536</v>
-      </c>
-      <c r="AX16" t="n">
-        <v>1.130392268550163</v>
-      </c>
-      <c r="AY16" t="n">
-        <v>25.33862229102168</v>
-      </c>
-      <c r="AZ16" t="n">
-        <v>184.7739042254329</v>
-      </c>
-      <c r="BA16" t="n">
-        <v>78.53386581240683</v>
-      </c>
-      <c r="BB16" t="n">
-        <v>52439.83058135535</v>
-      </c>
-      <c r="BC16" t="n">
-        <v>24871615.74790735</v>
-      </c>
-      <c r="BD16" t="n">
-        <v>82.27483946795093</v>
-      </c>
-      <c r="BE16" t="n">
-        <v>1.980187908496732</v>
-      </c>
-      <c r="BF16" t="inlineStr">
-        <is>
-          <t>vZA6VYpf</t>
-        </is>
-      </c>
-      <c r="BG16" t="inlineStr">
-        <is>
-          <t>2VSFgl3c</t>
         </is>
       </c>
     </row>

--- a/data/germany/p6_deployment/data_preparation/df_filled.xlsx
+++ b/data/germany/p6_deployment/data_preparation/df_filled.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BG13"/>
+  <dimension ref="A1:AQ19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -495,230 +495,150 @@
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>mean_age_player_miss_home</t>
+          <t>mean_age_player_start_home</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>mean_hei_player_miss_home</t>
+          <t>mean_hei_player_start_home</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>n_player_miss_home</t>
+          <t>mean_rat_player_start_home</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>sum_rat_player_miss_home</t>
+          <t>mean_wage_player_start_home</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>sum_wage_player_miss_home</t>
+          <t>mean_value_player_start_home</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>sum_value_player_miss_home</t>
+          <t>mean_pot_player_start_home</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>sum_pot_player_miss_home</t>
+          <t>mean_rep_player_start_home</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>sum_rep_player_miss_home</t>
+          <t>mean_age_player_start_away</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>mean_age_player_miss_away</t>
+          <t>mean_hei_player_start_away</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>mean_hei_player_miss_away</t>
+          <t>mean_rat_player_start_away</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>n_player_miss_away</t>
+          <t>mean_wage_player_start_away</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>sum_rat_player_miss_away</t>
+          <t>mean_value_player_start_away</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>sum_wage_player_miss_away</t>
+          <t>mean_pot_player_start_away</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>sum_value_player_miss_away</t>
+          <t>mean_rep_player_start_away</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>sum_pot_player_miss_away</t>
+          <t>mean_age_player_sub_home</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>sum_rep_player_miss_away</t>
+          <t>mean_hei_player_sub_home</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>mean_age_player_start_home</t>
+          <t>mean_rat_player_sub_home</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>mean_hei_player_start_home</t>
+          <t>mean_wage_player_sub_home</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>mean_rat_player_start_home</t>
+          <t>mean_value_player_sub_home</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>mean_wage_player_start_home</t>
+          <t>mean_pot_player_sub_home</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>mean_value_player_start_home</t>
+          <t>mean_rep_player_sub_home</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>mean_pot_player_start_home</t>
+          <t>mean_age_player_sub_away</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>mean_rep_player_start_home</t>
+          <t>mean_hei_player_sub_away</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
-          <t>mean_age_player_start_away</t>
+          <t>mean_rat_player_sub_away</t>
         </is>
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
-          <t>mean_hei_player_start_away</t>
+          <t>mean_wage_player_sub_away</t>
         </is>
       </c>
       <c r="AM1" s="1" t="inlineStr">
         <is>
-          <t>mean_rat_player_start_away</t>
+          <t>mean_value_player_sub_away</t>
         </is>
       </c>
       <c r="AN1" s="1" t="inlineStr">
         <is>
-          <t>mean_wage_player_start_away</t>
+          <t>mean_pot_player_sub_away</t>
         </is>
       </c>
       <c r="AO1" s="1" t="inlineStr">
         <is>
-          <t>mean_value_player_start_away</t>
+          <t>mean_rep_player_sub_away</t>
         </is>
       </c>
       <c r="AP1" s="1" t="inlineStr">
         <is>
-          <t>mean_pot_player_start_away</t>
+          <t>id_coach_home</t>
         </is>
       </c>
       <c r="AQ1" s="1" t="inlineStr">
-        <is>
-          <t>mean_rep_player_start_away</t>
-        </is>
-      </c>
-      <c r="AR1" s="1" t="inlineStr">
-        <is>
-          <t>mean_age_player_sub_home</t>
-        </is>
-      </c>
-      <c r="AS1" s="1" t="inlineStr">
-        <is>
-          <t>mean_hei_player_sub_home</t>
-        </is>
-      </c>
-      <c r="AT1" s="1" t="inlineStr">
-        <is>
-          <t>mean_rat_player_sub_home</t>
-        </is>
-      </c>
-      <c r="AU1" s="1" t="inlineStr">
-        <is>
-          <t>mean_wage_player_sub_home</t>
-        </is>
-      </c>
-      <c r="AV1" s="1" t="inlineStr">
-        <is>
-          <t>mean_value_player_sub_home</t>
-        </is>
-      </c>
-      <c r="AW1" s="1" t="inlineStr">
-        <is>
-          <t>mean_pot_player_sub_home</t>
-        </is>
-      </c>
-      <c r="AX1" s="1" t="inlineStr">
-        <is>
-          <t>mean_rep_player_sub_home</t>
-        </is>
-      </c>
-      <c r="AY1" s="1" t="inlineStr">
-        <is>
-          <t>mean_age_player_sub_away</t>
-        </is>
-      </c>
-      <c r="AZ1" s="1" t="inlineStr">
-        <is>
-          <t>mean_hei_player_sub_away</t>
-        </is>
-      </c>
-      <c r="BA1" s="1" t="inlineStr">
-        <is>
-          <t>mean_rat_player_sub_away</t>
-        </is>
-      </c>
-      <c r="BB1" s="1" t="inlineStr">
-        <is>
-          <t>mean_wage_player_sub_away</t>
-        </is>
-      </c>
-      <c r="BC1" s="1" t="inlineStr">
-        <is>
-          <t>mean_value_player_sub_away</t>
-        </is>
-      </c>
-      <c r="BD1" s="1" t="inlineStr">
-        <is>
-          <t>mean_pot_player_sub_away</t>
-        </is>
-      </c>
-      <c r="BE1" s="1" t="inlineStr">
-        <is>
-          <t>mean_rep_player_sub_away</t>
-        </is>
-      </c>
-      <c r="BF1" s="1" t="inlineStr">
-        <is>
-          <t>id_coach_home</t>
-        </is>
-      </c>
-      <c r="BG1" s="1" t="inlineStr">
         <is>
           <t>id_coach_away</t>
         </is>
@@ -727,35 +647,35 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>0KbQSfj4</t>
+          <t>z1eeWTdd</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45571.4375</v>
+        <v>45583.64583333334</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">stegemann s 
+          <t xml:space="preserve">dingert c 
   ger </t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">voith arena
-  heidenheim </t>
+          <t xml:space="preserve">signal iduna park
+  dortmund </t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>15000</v>
+        <v>81365</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>KWixEVWi</t>
+          <t>nP1i5US1</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>KbS1suSm</t>
+          <t>ILyJuN3g</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -781,180 +701,132 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>24.25</v>
+        <v>26.64285714285714</v>
       </c>
       <c r="O2" t="n">
-        <v>189.75</v>
+        <v>186.061038961039</v>
       </c>
       <c r="P2" t="n">
-        <v>4</v>
+        <v>81.98311688311686</v>
       </c>
       <c r="Q2" t="n">
-        <v>274</v>
+        <v>57966.23376623377</v>
       </c>
       <c r="R2" t="n">
-        <v>73000</v>
+        <v>37499350.64935065</v>
       </c>
       <c r="S2" t="n">
-        <v>7600000</v>
+        <v>84.12597402597403</v>
       </c>
       <c r="T2" t="n">
-        <v>291</v>
+        <v>2.611688311688312</v>
       </c>
       <c r="U2" t="n">
-        <v>4</v>
+        <v>26.76926406926407</v>
       </c>
       <c r="V2" t="n">
-        <v>25.25</v>
+        <v>185.3191919191919</v>
       </c>
       <c r="W2" t="n">
-        <v>180.75</v>
+        <v>70.64227994227994</v>
       </c>
       <c r="X2" t="n">
-        <v>4</v>
+        <v>17154.25685425686</v>
       </c>
       <c r="Y2" t="n">
-        <v>308</v>
+        <v>2338008.658008658</v>
       </c>
       <c r="Z2" t="n">
-        <v>184000</v>
+        <v>73.57301587301588</v>
       </c>
       <c r="AA2" t="n">
-        <v>70500000</v>
+        <v>1</v>
       </c>
       <c r="AB2" t="n">
-        <v>332</v>
+        <v>24.94727735487788</v>
       </c>
       <c r="AC2" t="n">
-        <v>9</v>
+        <v>184.0784915422379</v>
       </c>
       <c r="AD2" t="n">
-        <v>26.81666666666666</v>
+        <v>77.85036907627624</v>
       </c>
       <c r="AE2" t="n">
-        <v>187.1166666666667</v>
+        <v>43615.56955630182</v>
       </c>
       <c r="AF2" t="n">
-        <v>72.46666666666665</v>
+        <v>22506707.10514287</v>
       </c>
       <c r="AG2" t="n">
-        <v>22100</v>
+        <v>82.89163811561654</v>
       </c>
       <c r="AH2" t="n">
-        <v>3151666.666666667</v>
+        <v>1.89768881548875</v>
       </c>
       <c r="AI2" t="n">
-        <v>74.21666666666665</v>
+        <v>25.57589807852966</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1.016666666666667</v>
+        <v>184.6525480367586</v>
       </c>
       <c r="AK2" t="n">
-        <v>25.87794612794613</v>
+        <v>68.33454469507102</v>
       </c>
       <c r="AL2" t="n">
-        <v>183.3648148148148</v>
+        <v>16058.14536340852</v>
       </c>
       <c r="AM2" t="n">
-        <v>80.43636363636362</v>
+        <v>1786161.236424394</v>
       </c>
       <c r="AN2" t="n">
-        <v>56660.60606060606</v>
+        <v>71.97422723475356</v>
       </c>
       <c r="AO2" t="n">
-        <v>30434343.43434344</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>84.00151515151515</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>2.224915824915825</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>25.67282608695652</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>185.1786231884058</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>69.60688405797102</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>19845.65217391304</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>2247119.565217391</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>72.58188405797101</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>1.043478260869565</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>25.33862229102168</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>184.7739042254329</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>78.53386581240683</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>52439.83058135535</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>24871615.74790735</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>82.27483946795093</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>1.980187908496732</v>
-      </c>
-      <c r="BF2" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>hpYJ6izc</t>
+        </is>
+      </c>
+      <c r="AQ2" t="inlineStr">
         <is>
           <t>vZA6VYpf</t>
-        </is>
-      </c>
-      <c r="BG2" t="inlineStr">
-        <is>
-          <t>2VSFgl3c</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>ShoJUGLi</t>
+          <t>fHjVr7t2</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45571.52083333334</v>
+        <v>45584.4375</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">brand b 
+          <t xml:space="preserve">stegemann s 
   ger </t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">deutsche bank park
-  frankfurt </t>
+          <t xml:space="preserve">borussia park
+  monchengladbach </t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>58000</v>
+        <v>54042</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>8vndvXTk</t>
+          <t>88HSzjDr</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>nVp0wiqd</t>
+          <t>KWixEVWi</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -980,180 +852,132 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>19</v>
+        <v>26.11428571428572</v>
       </c>
       <c r="O3" t="n">
-        <v>172</v>
+        <v>184.8857142857143</v>
       </c>
       <c r="P3" t="n">
-        <v>1</v>
+        <v>75.48571428571428</v>
       </c>
       <c r="Q3" t="n">
-        <v>59</v>
+        <v>24414.28571428571</v>
       </c>
       <c r="R3" t="n">
-        <v>3000</v>
+        <v>8282857.142857143</v>
       </c>
       <c r="S3" t="n">
-        <v>575000</v>
+        <v>77.91428571428573</v>
       </c>
       <c r="T3" t="n">
-        <v>76</v>
+        <v>1.485714285714286</v>
       </c>
       <c r="U3" t="n">
-        <v>1</v>
+        <v>26.81428571428571</v>
       </c>
       <c r="V3" t="n">
-        <v>21.66666666666667</v>
+        <v>187.2571428571428</v>
       </c>
       <c r="W3" t="n">
-        <v>183.5</v>
+        <v>72.52857142857142</v>
       </c>
       <c r="X3" t="n">
-        <v>6</v>
+        <v>22128.57142857143</v>
       </c>
       <c r="Y3" t="n">
-        <v>444</v>
+        <v>3170000</v>
       </c>
       <c r="Z3" t="n">
-        <v>276000</v>
+        <v>74.31428571428572</v>
       </c>
       <c r="AA3" t="n">
-        <v>189150000</v>
+        <v>1.014285714285714</v>
       </c>
       <c r="AB3" t="n">
-        <v>498</v>
+        <v>25.63015457899407</v>
       </c>
       <c r="AC3" t="n">
-        <v>10</v>
+        <v>183.4706953719703</v>
       </c>
       <c r="AD3" t="n">
-        <v>24.74444444444444</v>
+        <v>73.49740422484784</v>
       </c>
       <c r="AE3" t="n">
-        <v>185.0722222222223</v>
+        <v>22261.34046295864</v>
       </c>
       <c r="AF3" t="n">
-        <v>76.98333333333333</v>
+        <v>6100050.358816296</v>
       </c>
       <c r="AG3" t="n">
-        <v>35133.33333333334</v>
+        <v>77.37456218185214</v>
       </c>
       <c r="AH3" t="n">
-        <v>15228055.55555556</v>
+        <v>1.202388735814692</v>
       </c>
       <c r="AI3" t="n">
-        <v>81.71111111111111</v>
+        <v>25.78788819875777</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1.694444444444445</v>
+        <v>185.0847826086956</v>
       </c>
       <c r="AK3" t="n">
-        <v>26.78333333333333</v>
+        <v>69.52639751552795</v>
       </c>
       <c r="AL3" t="n">
-        <v>183.75</v>
+        <v>19842.85714285714</v>
       </c>
       <c r="AM3" t="n">
-        <v>82.85000000000001</v>
+        <v>2179208.074534161</v>
       </c>
       <c r="AN3" t="n">
-        <v>76950</v>
+        <v>72.36211180124224</v>
       </c>
       <c r="AO3" t="n">
-        <v>47282916.66666666</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>85.68333333333332</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>3.083333333333333</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>22.37575757575758</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>185.0691368572948</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>72.67647527910687</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>25312.00918964077</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>8847221.671603251</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>81.03199855699854</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>1.361995898838004</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>26.85416666666667</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>183.3313484581867</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>81.70669934640523</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>75162.88545332663</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>38261669.78276353</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>83.96209359812302</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>2.684724317077258</v>
-      </c>
-      <c r="BF3" t="inlineStr">
-        <is>
-          <t>A15eUM4C</t>
-        </is>
-      </c>
-      <c r="BG3" t="inlineStr">
-        <is>
-          <t>hAcTWKKN</t>
+        <v>1.037267080745342</v>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>2VSFgl3c</t>
+        </is>
+      </c>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>pfoInmcq</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>nc8W6DTp</t>
+          <t>r3GGwC4M</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45571.60416666666</v>
+        <v>45584.4375</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">osmers h 
+          <t xml:space="preserve">brand b 
   ger </t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">mhparena
-  stuttgart </t>
+          <t xml:space="preserve">bayarena
+  leverkusen </t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>60449</v>
+        <v>30210</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>nJQmYp1B</t>
+          <t>4jcj2zMd</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>hQAtP9Sl</t>
+          <t>8vndvXTk</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -1179,180 +1003,132 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>23.33333333333333</v>
+        <v>26.40674603174603</v>
       </c>
       <c r="O4" t="n">
-        <v>186</v>
+        <v>184.3571428571429</v>
       </c>
       <c r="P4" t="n">
-        <v>6</v>
+        <v>83.76865079365079</v>
       </c>
       <c r="Q4" t="n">
-        <v>431</v>
+        <v>99564.28571428571</v>
       </c>
       <c r="R4" t="n">
-        <v>116000</v>
+        <v>50273214.28571428</v>
       </c>
       <c r="S4" t="n">
-        <v>32600000</v>
+        <v>85.91904761904763</v>
       </c>
       <c r="T4" t="n">
-        <v>471</v>
+        <v>3.064285714285715</v>
       </c>
       <c r="U4" t="n">
-        <v>8</v>
+        <v>24.52777777777778</v>
       </c>
       <c r="V4" t="n">
-        <v>27.8</v>
+        <v>185.337962962963</v>
       </c>
       <c r="W4" t="n">
-        <v>182.8</v>
+        <v>76.72685185185185</v>
       </c>
       <c r="X4" t="n">
-        <v>5</v>
+        <v>34518.51851851852</v>
       </c>
       <c r="Y4" t="n">
-        <v>375</v>
+        <v>15101157.40740741</v>
       </c>
       <c r="Z4" t="n">
-        <v>151000</v>
+        <v>81.68518518518518</v>
       </c>
       <c r="AA4" t="n">
-        <v>31900000</v>
+        <v>1.671296296296297</v>
       </c>
       <c r="AB4" t="n">
-        <v>384</v>
+        <v>24.56634355496585</v>
       </c>
       <c r="AC4" t="n">
-        <v>9</v>
+        <v>180.7619096761511</v>
       </c>
       <c r="AD4" t="n">
-        <v>24.95714285714286</v>
+        <v>80.84288294265075</v>
       </c>
       <c r="AE4" t="n">
-        <v>185.7636363636364</v>
+        <v>82188.14560912084</v>
       </c>
       <c r="AF4" t="n">
-        <v>76.23116883116883</v>
+        <v>39435822.47592019</v>
       </c>
       <c r="AG4" t="n">
-        <v>27564.93506493506</v>
+        <v>84.59387316330042</v>
       </c>
       <c r="AH4" t="n">
-        <v>13686363.63636363</v>
+        <v>2.302458351761757</v>
       </c>
       <c r="AI4" t="n">
-        <v>79.42467532467533</v>
+        <v>22.60779220779221</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1.45974025974026</v>
+        <v>184.7599404355043</v>
       </c>
       <c r="AK4" t="n">
-        <v>27.68703703703704</v>
+        <v>72.78391758617323</v>
       </c>
       <c r="AL4" t="n">
-        <v>186.0796296296296</v>
+        <v>25675.59971356964</v>
       </c>
       <c r="AM4" t="n">
-        <v>74.88333333333334</v>
+        <v>8849931.500829998</v>
       </c>
       <c r="AN4" t="n">
-        <v>30257.40740740741</v>
+        <v>80.94579468150896</v>
       </c>
       <c r="AO4" t="n">
-        <v>7417592.592592592</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>78.01296296296296</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>1.655555555555556</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>24.18921166552746</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>184.4195906432749</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>73.40942507784612</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>24026.95374800638</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>10309174.54621402</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>78.25894281157441</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>1.483652312599681</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>24.35341130604289</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>186.3588693957115</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>71.36042884990253</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>24539.57115009746</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>5892831.384015595</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>77.62027290448343</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>1.239278752436647</v>
-      </c>
-      <c r="BF4" t="inlineStr">
-        <is>
-          <t>f3ddUIXs</t>
-        </is>
-      </c>
-      <c r="BG4" t="inlineStr">
-        <is>
-          <t>4fuCGs9P</t>
+        <v>1.391914852065228</v>
+      </c>
+      <c r="AP4" t="inlineStr">
+        <is>
+          <t>hAcTWKKN</t>
+        </is>
+      </c>
+      <c r="AQ4" t="inlineStr">
+        <is>
+          <t>K6A2elS9</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>z1eeWTdd</t>
+          <t>M93rhBJF</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45583.64583333334</v>
+        <v>45584.4375</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">dingert c 
+          <t xml:space="preserve">badstubner f 
   ger </t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">signal iduna park
-  dortmund </t>
+          <t xml:space="preserve">europa park stadion
+  freiburg </t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>81365</v>
+        <v>34700</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>nP1i5US1</t>
+          <t>fiEQZ7C7</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>ILyJuN3g</t>
+          <t>fTVNku3I</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -1377,121 +1153,105 @@
           <t>bundesliga</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="inlineStr"/>
-      <c r="S5" t="inlineStr"/>
-      <c r="T5" t="inlineStr"/>
-      <c r="U5" t="inlineStr"/>
-      <c r="V5" t="inlineStr"/>
-      <c r="W5" t="inlineStr"/>
-      <c r="X5" t="inlineStr"/>
-      <c r="Y5" t="inlineStr"/>
-      <c r="Z5" t="inlineStr"/>
-      <c r="AA5" t="inlineStr"/>
-      <c r="AB5" t="inlineStr"/>
-      <c r="AC5" t="inlineStr"/>
+      <c r="N5" t="n">
+        <v>26.78730158730159</v>
+      </c>
+      <c r="O5" t="n">
+        <v>183.765873015873</v>
+      </c>
+      <c r="P5" t="n">
+        <v>76.15119047619048</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>26336.90476190476</v>
+      </c>
+      <c r="R5" t="n">
+        <v>10731904.76190476</v>
+      </c>
+      <c r="S5" t="n">
+        <v>78.68373015873014</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1.619444444444445</v>
+      </c>
+      <c r="U5" t="n">
+        <v>25.79166666666667</v>
+      </c>
+      <c r="V5" t="n">
+        <v>185.0416666666667</v>
+      </c>
+      <c r="W5" t="n">
+        <v>73.70833333333333</v>
+      </c>
+      <c r="X5" t="n">
+        <v>22291.66666666667</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>5350000</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>76.91666666666667</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.125</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>26.78755273276358</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>183.3636766959748</v>
+      </c>
       <c r="AD5" t="n">
-        <v>26.64285714285714</v>
+        <v>74.21713048855905</v>
       </c>
       <c r="AE5" t="n">
-        <v>186.061038961039</v>
+        <v>23961.89683695405</v>
       </c>
       <c r="AF5" t="n">
-        <v>81.98311688311686</v>
+        <v>6877269.306099807</v>
       </c>
       <c r="AG5" t="n">
-        <v>57966.23376623377</v>
+        <v>76.81895202432959</v>
       </c>
       <c r="AH5" t="n">
-        <v>37499350.64935065</v>
+        <v>1.387528604118993</v>
       </c>
       <c r="AI5" t="n">
-        <v>84.12597402597403</v>
+        <v>24.81548711988782</v>
       </c>
       <c r="AJ5" t="n">
-        <v>2.611688311688312</v>
+        <v>184.1908611131853</v>
       </c>
       <c r="AK5" t="n">
-        <v>26.76926406926407</v>
+        <v>72.5454978243291</v>
       </c>
       <c r="AL5" t="n">
-        <v>185.3191919191919</v>
+        <v>21177.01909312369</v>
       </c>
       <c r="AM5" t="n">
-        <v>70.64227994227994</v>
+        <v>4952682.416666826</v>
       </c>
       <c r="AN5" t="n">
-        <v>17154.25685425686</v>
+        <v>76.55772420610985</v>
       </c>
       <c r="AO5" t="n">
-        <v>2338008.658008658</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>73.57301587301588</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>24.94727735487788</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>184.0784915422379</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>77.85036907627624</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>43615.56955630182</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>22506707.10514287</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>82.89163811561654</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>1.89768881548875</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>25.57589807852966</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>184.6525480367586</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>68.33454469507102</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>16058.14536340852</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>1786161.236424394</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>71.97422723475356</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>1</v>
-      </c>
-      <c r="BF5" t="inlineStr">
-        <is>
-          <t>hpYJ6izc</t>
-        </is>
-      </c>
-      <c r="BG5" t="inlineStr">
-        <is>
-          <t>vZA6VYpf</t>
+        <v>1.158487278483961</v>
+      </c>
+      <c r="AP5" t="inlineStr">
+        <is>
+          <t>4fuCGs9P</t>
+        </is>
+      </c>
+      <c r="AQ5" t="inlineStr">
+        <is>
+          <t>M5BRZDsC</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>fHjVr7t2</t>
+          <t>Eq0zfXl3</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -1499,27 +1259,27 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">exner f 
+          <t xml:space="preserve">burda m 
   ger </t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">borussia park
-  monchengladbach </t>
+          <t xml:space="preserve">prezero arena
+  sinsheim </t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>54042</v>
+        <v>30150</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>88HSzjDr</t>
+          <t>hQAtP9Sl</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>KWixEVWi</t>
+          <t>8Y2m6ADe</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -1544,121 +1304,105 @@
           <t>bundesliga</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr"/>
-      <c r="R6" t="inlineStr"/>
-      <c r="S6" t="inlineStr"/>
-      <c r="T6" t="inlineStr"/>
-      <c r="U6" t="inlineStr"/>
-      <c r="V6" t="inlineStr"/>
-      <c r="W6" t="inlineStr"/>
-      <c r="X6" t="inlineStr"/>
-      <c r="Y6" t="inlineStr"/>
-      <c r="Z6" t="inlineStr"/>
-      <c r="AA6" t="inlineStr"/>
-      <c r="AB6" t="inlineStr"/>
-      <c r="AC6" t="inlineStr"/>
+      <c r="N6" t="n">
+        <v>27.52539682539683</v>
+      </c>
+      <c r="O6" t="n">
+        <v>186.084126984127</v>
+      </c>
+      <c r="P6" t="n">
+        <v>74.82063492063492</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>30061.90476190476</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7427777.777777778</v>
+      </c>
+      <c r="S6" t="n">
+        <v>78.15396825396826</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1.641269841269841</v>
+      </c>
+      <c r="U6" t="n">
+        <v>28.33888888888889</v>
+      </c>
+      <c r="V6" t="n">
+        <v>185.2921296296296</v>
+      </c>
+      <c r="W6" t="n">
+        <v>71.6962962962963</v>
+      </c>
+      <c r="X6" t="n">
+        <v>17048.14814814815</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>2222615.740740741</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>73.5712962962963</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>24.26210765007758</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>186.1579424752357</v>
+      </c>
       <c r="AD6" t="n">
-        <v>26.11428571428572</v>
+        <v>71.20689819787563</v>
       </c>
       <c r="AE6" t="n">
-        <v>184.8857142857143</v>
+        <v>23972.69363885905</v>
       </c>
       <c r="AF6" t="n">
-        <v>75.48571428571428</v>
+        <v>5652869.077455544</v>
       </c>
       <c r="AG6" t="n">
-        <v>24414.28571428571</v>
+        <v>77.70173051676811</v>
       </c>
       <c r="AH6" t="n">
-        <v>8282857.142857143</v>
+        <v>1.218701515693997</v>
       </c>
       <c r="AI6" t="n">
-        <v>77.91428571428573</v>
+        <v>25.40532515300317</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1.485714285714286</v>
+        <v>185.6896861308626</v>
       </c>
       <c r="AK6" t="n">
-        <v>26.81666666666666</v>
+        <v>68.42912900652838</v>
       </c>
       <c r="AL6" t="n">
-        <v>187.1166666666667</v>
+        <v>15078.88310519889</v>
       </c>
       <c r="AM6" t="n">
-        <v>72.46666666666665</v>
+        <v>1804867.324797665</v>
       </c>
       <c r="AN6" t="n">
-        <v>22100</v>
+        <v>74.38585339668931</v>
       </c>
       <c r="AO6" t="n">
-        <v>3151666.666666667</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>74.21666666666665</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>1.016666666666667</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>25.63015457899407</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>183.4706953719703</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>73.49740422484784</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>22261.34046295864</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>6100050.358816296</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>77.37456218185214</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>1.202388735814692</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>25.67282608695652</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>185.1786231884058</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>69.60688405797102</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>19845.65217391304</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>2247119.565217391</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>72.58188405797101</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>1.043478260869565</v>
-      </c>
-      <c r="BF6" t="inlineStr">
-        <is>
-          <t>2VSFgl3c</t>
-        </is>
-      </c>
-      <c r="BG6" t="inlineStr">
-        <is>
-          <t>4ljanukM</t>
+        <v>1</v>
+      </c>
+      <c r="AP6" t="inlineStr">
+        <is>
+          <t>GzfvcwRj</t>
+        </is>
+      </c>
+      <c r="AQ6" t="inlineStr">
+        <is>
+          <t>f3ddUIXs</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>r3GGwC4M</t>
+          <t>E7rNpTBk</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
@@ -1666,27 +1410,27 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">stieler t 
+          <t xml:space="preserve">stegemann s 
   ger </t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">bayarena
-  leverkusen </t>
+          <t xml:space="preserve">mewa arena
+  mainz </t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>30210</v>
+        <v>34000</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>4jcj2zMd</t>
+          <t>EuakNmc1</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>8vndvXTk</t>
+          <t>KbS1suSm</t>
         </is>
       </c>
       <c r="H7" t="n">
@@ -1711,149 +1455,133 @@
           <t>bundesliga</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr"/>
-      <c r="R7" t="inlineStr"/>
-      <c r="S7" t="inlineStr"/>
-      <c r="T7" t="inlineStr"/>
-      <c r="U7" t="inlineStr"/>
-      <c r="V7" t="inlineStr"/>
-      <c r="W7" t="inlineStr"/>
-      <c r="X7" t="inlineStr"/>
-      <c r="Y7" t="inlineStr"/>
-      <c r="Z7" t="inlineStr"/>
-      <c r="AA7" t="inlineStr"/>
-      <c r="AB7" t="inlineStr"/>
-      <c r="AC7" t="inlineStr"/>
+      <c r="N7" t="n">
+        <v>27.55238095238095</v>
+      </c>
+      <c r="O7" t="n">
+        <v>183.3444444444445</v>
+      </c>
+      <c r="P7" t="n">
+        <v>74.82380952380952</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>25260.31746031746</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6533968.253968254</v>
+      </c>
+      <c r="S7" t="n">
+        <v>76.96507936507938</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1.409523809523809</v>
+      </c>
+      <c r="U7" t="n">
+        <v>25.86363636363637</v>
+      </c>
+      <c r="V7" t="n">
+        <v>183.4238095238095</v>
+      </c>
+      <c r="W7" t="n">
+        <v>80.54862914862915</v>
+      </c>
+      <c r="X7" t="n">
+        <v>57105.9163059163</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>30935786.43578643</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>84.0806637806638</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>2.24040404040404</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>25.68795690525014</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>183.6457442307066</v>
+      </c>
       <c r="AD7" t="n">
-        <v>26.40674603174603</v>
+        <v>71.26425479282622</v>
       </c>
       <c r="AE7" t="n">
-        <v>184.3571428571429</v>
+        <v>21373.32942746477</v>
       </c>
       <c r="AF7" t="n">
-        <v>83.76865079365079</v>
+        <v>3395399.334374898</v>
       </c>
       <c r="AG7" t="n">
-        <v>99564.28571428571</v>
+        <v>76.77254825375128</v>
       </c>
       <c r="AH7" t="n">
-        <v>50273214.28571428</v>
+        <v>1.130812420662045</v>
       </c>
       <c r="AI7" t="n">
-        <v>85.91904761904763</v>
+        <v>25.30528527200354</v>
       </c>
       <c r="AJ7" t="n">
-        <v>3.064285714285715</v>
+        <v>184.6633464789425</v>
       </c>
       <c r="AK7" t="n">
-        <v>24.74444444444444</v>
+        <v>78.55534362867954</v>
       </c>
       <c r="AL7" t="n">
-        <v>185.0722222222223</v>
+        <v>52375.29741428735</v>
       </c>
       <c r="AM7" t="n">
-        <v>76.98333333333333</v>
+        <v>24838828.53580029</v>
       </c>
       <c r="AN7" t="n">
-        <v>35133.33333333334</v>
+        <v>82.33332104771732</v>
       </c>
       <c r="AO7" t="n">
-        <v>15228055.55555556</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>81.71111111111111</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>1.694444444444445</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>24.56634355496585</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>180.7619096761511</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>80.84288294265075</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>82188.14560912084</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>39435822.47592019</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>84.59387316330042</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>2.302458351761757</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>22.37575757575758</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>185.0691368572948</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>72.67647527910687</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>25312.00918964077</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>8847221.671603251</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>81.03199855699854</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>1.361995898838004</v>
-      </c>
-      <c r="BF7" t="inlineStr">
-        <is>
-          <t>hAcTWKKN</t>
-        </is>
-      </c>
-      <c r="BG7" t="inlineStr">
-        <is>
-          <t>UgdQz0fK</t>
+        <v>1.96046181630547</v>
+      </c>
+      <c r="AP7" t="inlineStr">
+        <is>
+          <t>0jdIgO6t</t>
+        </is>
+      </c>
+      <c r="AQ7" t="inlineStr">
+        <is>
+          <t>pfoInmcq</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>M93rhBJF</t>
+          <t>2mcmYkSq</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45584.4375</v>
+        <v>45584.5625</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">badstubner f 
+          <t xml:space="preserve">osmers h 
   ger </t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">europa park stadion
-  freiburg </t>
+          <t xml:space="preserve">allianz arena
+  munich </t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>34700</v>
+        <v>75024</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>fiEQZ7C7</t>
+          <t>nVp0wiqd</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>fTVNku3I</t>
+          <t>nJQmYp1B</t>
         </is>
       </c>
       <c r="H8" t="n">
@@ -1878,149 +1606,133 @@
           <t>bundesliga</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="inlineStr"/>
-      <c r="R8" t="inlineStr"/>
-      <c r="S8" t="inlineStr"/>
-      <c r="T8" t="inlineStr"/>
-      <c r="U8" t="inlineStr"/>
-      <c r="V8" t="inlineStr"/>
-      <c r="W8" t="inlineStr"/>
-      <c r="X8" t="inlineStr"/>
-      <c r="Y8" t="inlineStr"/>
-      <c r="Z8" t="inlineStr"/>
-      <c r="AA8" t="inlineStr"/>
-      <c r="AB8" t="inlineStr"/>
-      <c r="AC8" t="inlineStr"/>
+      <c r="N8" t="n">
+        <v>26.92539682539682</v>
+      </c>
+      <c r="O8" t="n">
+        <v>183.7380952380952</v>
+      </c>
+      <c r="P8" t="n">
+        <v>82.85555555555557</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>77163.49206349207</v>
+      </c>
+      <c r="R8" t="n">
+        <v>46305992.06349206</v>
+      </c>
+      <c r="S8" t="n">
+        <v>85.61746031746031</v>
+      </c>
+      <c r="T8" t="n">
+        <v>3.103174603174603</v>
+      </c>
+      <c r="U8" t="n">
+        <v>24.8875</v>
+      </c>
+      <c r="V8" t="n">
+        <v>185.7181818181818</v>
+      </c>
+      <c r="W8" t="n">
+        <v>76.17727272727274</v>
+      </c>
+      <c r="X8" t="n">
+        <v>27419.31818181818</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>13679630.68181818</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>79.47159090909091</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.452272727272728</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>26.675</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>183.4268701070172</v>
+      </c>
       <c r="AD8" t="n">
-        <v>26.78730158730159</v>
+        <v>81.46288515406162</v>
       </c>
       <c r="AE8" t="n">
-        <v>183.765873015873</v>
+        <v>75162.88545332663</v>
       </c>
       <c r="AF8" t="n">
-        <v>76.15119047619048</v>
+        <v>37413574.0995116</v>
       </c>
       <c r="AG8" t="n">
-        <v>26336.90476190476</v>
+        <v>83.974651655534</v>
       </c>
       <c r="AH8" t="n">
-        <v>10731904.76190476</v>
+        <v>2.64404941463765</v>
       </c>
       <c r="AI8" t="n">
-        <v>78.68373015873014</v>
+        <v>24.23134968102073</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1.619444444444445</v>
+        <v>184.7684576023392</v>
       </c>
       <c r="AK8" t="n">
-        <v>25.79166666666667</v>
+        <v>73.57535220627327</v>
       </c>
       <c r="AL8" t="n">
-        <v>185.0416666666667</v>
+        <v>24095.95295055821</v>
       </c>
       <c r="AM8" t="n">
-        <v>73.70833333333333</v>
+        <v>10361317.20162148</v>
       </c>
       <c r="AN8" t="n">
-        <v>22291.66666666667</v>
+        <v>78.25289074960128</v>
       </c>
       <c r="AO8" t="n">
-        <v>5350000</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>76.91666666666667</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>1.125</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>26.78755273276358</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>183.3636766959748</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>74.21713048855905</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>23961.89683695405</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>6877269.306099807</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>76.81895202432959</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>1.387528604118993</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>24.81548711988783</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>184.1908611131853</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>72.5454978243291</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>21177.0190931237</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>4952682.416666826</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>76.55772420610985</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>1.158487278483961</v>
-      </c>
-      <c r="BF8" t="inlineStr">
-        <is>
-          <t>4fuCGs9P</t>
-        </is>
-      </c>
-      <c r="BG8" t="inlineStr">
-        <is>
-          <t>M5BRZDsC</t>
+        <v>1.482406299840511</v>
+      </c>
+      <c r="AP8" t="inlineStr">
+        <is>
+          <t>UgdQz0fK</t>
+        </is>
+      </c>
+      <c r="AQ8" t="inlineStr">
+        <is>
+          <t>KUx4Q7x1</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>Eq0zfXl3</t>
+          <t>nBwH6AY8</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45584.4375</v>
+        <v>45585.4375</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">burda m 
+          <t xml:space="preserve">reichel t 
   ger </t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">prezero arena
-  sinsheim </t>
+          <t xml:space="preserve">holstein stadion
+  kiel </t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>30150</v>
+        <v>15034</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>hQAtP9Sl</t>
+          <t>63WsD2ei</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>8Y2m6ADe</t>
+          <t>pzHW4oaE</t>
         </is>
       </c>
       <c r="H9" t="n">
@@ -2045,149 +1757,133 @@
           <t>bundesliga</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr"/>
-      <c r="Q9" t="inlineStr"/>
-      <c r="R9" t="inlineStr"/>
-      <c r="S9" t="inlineStr"/>
-      <c r="T9" t="inlineStr"/>
-      <c r="U9" t="inlineStr"/>
-      <c r="V9" t="inlineStr"/>
-      <c r="W9" t="inlineStr"/>
-      <c r="X9" t="inlineStr"/>
-      <c r="Y9" t="inlineStr"/>
-      <c r="Z9" t="inlineStr"/>
-      <c r="AA9" t="inlineStr"/>
-      <c r="AB9" t="inlineStr"/>
-      <c r="AC9" t="inlineStr"/>
+      <c r="N9" t="n">
+        <v>26.66814574314574</v>
+      </c>
+      <c r="O9" t="n">
+        <v>185.6328282828283</v>
+      </c>
+      <c r="P9" t="n">
+        <v>69.95238095238095</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>16681.49350649351</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1926691.919191919</v>
+      </c>
+      <c r="S9" t="n">
+        <v>72.3401875901876</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1</v>
+      </c>
+      <c r="U9" t="n">
+        <v>26.98412698412698</v>
+      </c>
+      <c r="V9" t="n">
+        <v>186.3702741702742</v>
+      </c>
+      <c r="W9" t="n">
+        <v>74.8975468975469</v>
+      </c>
+      <c r="X9" t="n">
+        <v>27718.47041847042</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>6582539.682539682</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>77.52539682539683</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.413131313131313</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>25.60353757063466</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>184.9785753202883</v>
+      </c>
       <c r="AD9" t="n">
-        <v>27.68703703703704</v>
+        <v>68.25622181748368</v>
       </c>
       <c r="AE9" t="n">
-        <v>186.0796296296296</v>
+        <v>15618.43791673801</v>
       </c>
       <c r="AF9" t="n">
-        <v>74.88333333333334</v>
+        <v>1839729.603511885</v>
       </c>
       <c r="AG9" t="n">
-        <v>30257.40740740741</v>
+        <v>72.59229777341906</v>
       </c>
       <c r="AH9" t="n">
-        <v>7417592.592592592</v>
+        <v>1</v>
       </c>
       <c r="AI9" t="n">
-        <v>78.01296296296296</v>
+        <v>26.37341516316672</v>
       </c>
       <c r="AJ9" t="n">
-        <v>1.655555555555556</v>
+        <v>182.8920043379671</v>
       </c>
       <c r="AK9" t="n">
-        <v>28.33888888888889</v>
+        <v>73.10748299319728</v>
       </c>
       <c r="AL9" t="n">
-        <v>185.2921296296296</v>
+        <v>24930.5333727694</v>
       </c>
       <c r="AM9" t="n">
-        <v>71.6962962962963</v>
+        <v>4181897.860593513</v>
       </c>
       <c r="AN9" t="n">
-        <v>17048.14814814815</v>
+        <v>75.97586512866017</v>
       </c>
       <c r="AO9" t="n">
-        <v>2222615.740740741</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>73.5712962962963</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>24.35341130604289</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>186.3588693957115</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>71.36042884990253</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>24539.57115009746</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>5892831.384015595</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>77.62027290448343</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>1.239278752436647</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>25.40532515300317</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>185.6896861308626</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>68.42912900652838</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>15078.88310519889</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>1804867.324797665</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>74.38585339668931</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>1</v>
-      </c>
-      <c r="BF9" t="inlineStr">
-        <is>
-          <t>KUx4Q7x1</t>
-        </is>
-      </c>
-      <c r="BG9" t="inlineStr">
-        <is>
-          <t>f3ddUIXs</t>
+        <v>1.159124519372967</v>
+      </c>
+      <c r="AP9" t="inlineStr">
+        <is>
+          <t>hAcTWKKN</t>
+        </is>
+      </c>
+      <c r="AQ9" t="inlineStr">
+        <is>
+          <t>IkCftsQm</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>E7rNpTBk</t>
+          <t>rPiijklS</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45584.4375</v>
+        <v>45585.52083333334</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">siebert d 
+          <t xml:space="preserve">welz t 
   ger </t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">mewa arena
-  mainz </t>
+          <t xml:space="preserve">volkswagen arena
+  wolfsburg </t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>34000</v>
+        <v>28917</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>EuakNmc1</t>
+          <t>nwkTahLL</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>KbS1suSm</t>
+          <t>Ig1f1fy3</t>
         </is>
       </c>
       <c r="H10" t="n">
@@ -2212,149 +1908,133 @@
           <t>bundesliga</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
-      <c r="P10" t="inlineStr"/>
-      <c r="Q10" t="inlineStr"/>
-      <c r="R10" t="inlineStr"/>
-      <c r="S10" t="inlineStr"/>
-      <c r="T10" t="inlineStr"/>
-      <c r="U10" t="inlineStr"/>
-      <c r="V10" t="inlineStr"/>
-      <c r="W10" t="inlineStr"/>
-      <c r="X10" t="inlineStr"/>
-      <c r="Y10" t="inlineStr"/>
-      <c r="Z10" t="inlineStr"/>
-      <c r="AA10" t="inlineStr"/>
-      <c r="AB10" t="inlineStr"/>
-      <c r="AC10" t="inlineStr"/>
+      <c r="N10" t="n">
+        <v>24.70833333333333</v>
+      </c>
+      <c r="O10" t="n">
+        <v>184.7083333333333</v>
+      </c>
+      <c r="P10" t="n">
+        <v>75.2986111111111</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>36312.5</v>
+      </c>
+      <c r="R10" t="n">
+        <v>10284953.7037037</v>
+      </c>
+      <c r="S10" t="n">
+        <v>79.89814814814814</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1.418981481481481</v>
+      </c>
+      <c r="U10" t="n">
+        <v>26.98051948051948</v>
+      </c>
+      <c r="V10" t="n">
+        <v>183.7805194805195</v>
+      </c>
+      <c r="W10" t="n">
+        <v>74.43636363636365</v>
+      </c>
+      <c r="X10" t="n">
+        <v>23588.31168831169</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>6014415.584415585</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>76.79350649350648</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.094805194805195</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>24.70891265597148</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>184.8741501145913</v>
+      </c>
       <c r="AD10" t="n">
-        <v>27.55238095238095</v>
+        <v>73.08691325014854</v>
       </c>
       <c r="AE10" t="n">
-        <v>183.3444444444445</v>
+        <v>32352.28333757745</v>
       </c>
       <c r="AF10" t="n">
-        <v>74.82380952380952</v>
+        <v>7859812.515915456</v>
       </c>
       <c r="AG10" t="n">
-        <v>25260.31746031746</v>
+        <v>78.21184428316782</v>
       </c>
       <c r="AH10" t="n">
-        <v>6533968.253968254</v>
+        <v>1.363718062982769</v>
       </c>
       <c r="AI10" t="n">
-        <v>76.96507936507938</v>
+        <v>24.60253992311855</v>
       </c>
       <c r="AJ10" t="n">
-        <v>1.409523809523809</v>
+        <v>186.3206916217704</v>
       </c>
       <c r="AK10" t="n">
-        <v>25.87794612794613</v>
+        <v>70.48234358718177</v>
       </c>
       <c r="AL10" t="n">
-        <v>183.3648148148148</v>
+        <v>19202.79231864717</v>
       </c>
       <c r="AM10" t="n">
-        <v>80.43636363636362</v>
+        <v>3470618.297107345</v>
       </c>
       <c r="AN10" t="n">
-        <v>56660.60606060606</v>
+        <v>76.51956917986665</v>
       </c>
       <c r="AO10" t="n">
-        <v>30434343.43434344</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>84.00151515151515</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>2.224915824915825</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>25.68795690525014</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>183.6457442307066</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>71.26425479282622</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>21373.32942746477</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>3395399.334374898</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>76.77254825375128</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>1.130812420662045</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>25.33862229102168</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>184.7739042254329</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>78.53386581240683</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>52439.83058135535</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>24871615.74790735</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>82.27483946795093</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>1.980187908496732</v>
-      </c>
-      <c r="BF10" t="inlineStr">
-        <is>
-          <t>0jdIgO6t</t>
-        </is>
-      </c>
-      <c r="BG10" t="inlineStr">
-        <is>
-          <t>2VSFgl3c</t>
+        <v>1</v>
+      </c>
+      <c r="AP10" t="inlineStr">
+        <is>
+          <t>8f6APkLc</t>
+        </is>
+      </c>
+      <c r="AQ10" t="inlineStr">
+        <is>
+          <t>YZPE6Sx7</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>2mcmYkSq</t>
+          <t>4E8uaJWa</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>45584.5625</v>
+        <v>45590.64583333334</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve">jablonski s 
+          <t xml:space="preserve">badstubner f 
   ger </t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">allianz arena
-  munich </t>
+          <t xml:space="preserve">mewa arena
+  mainz </t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>75024</v>
+        <v>34000</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>nVp0wiqd</t>
+          <t>EuakNmc1</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>nJQmYp1B</t>
+          <t>88HSzjDr</t>
         </is>
       </c>
       <c r="H11" t="n">
@@ -2379,125 +2059,109 @@
           <t>bundesliga</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr"/>
-      <c r="P11" t="inlineStr"/>
-      <c r="Q11" t="inlineStr"/>
-      <c r="R11" t="inlineStr"/>
-      <c r="S11" t="inlineStr"/>
-      <c r="T11" t="inlineStr"/>
-      <c r="U11" t="inlineStr"/>
-      <c r="V11" t="inlineStr"/>
-      <c r="W11" t="inlineStr"/>
-      <c r="X11" t="inlineStr"/>
-      <c r="Y11" t="inlineStr"/>
-      <c r="Z11" t="inlineStr"/>
-      <c r="AA11" t="inlineStr"/>
-      <c r="AB11" t="inlineStr"/>
-      <c r="AC11" t="inlineStr"/>
+      <c r="N11" t="n">
+        <v>27.55238095238095</v>
+      </c>
+      <c r="O11" t="n">
+        <v>183.3444444444445</v>
+      </c>
+      <c r="P11" t="n">
+        <v>74.82380952380952</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>25260.31746031746</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6533968.253968254</v>
+      </c>
+      <c r="S11" t="n">
+        <v>76.96507936507938</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1.409523809523809</v>
+      </c>
+      <c r="U11" t="n">
+        <v>26.11428571428572</v>
+      </c>
+      <c r="V11" t="n">
+        <v>184.8857142857143</v>
+      </c>
+      <c r="W11" t="n">
+        <v>75.48571428571428</v>
+      </c>
+      <c r="X11" t="n">
+        <v>24414.28571428571</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>8282857.142857143</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>77.91428571428573</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.485714285714286</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>25.68795690525014</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>183.6457442307066</v>
+      </c>
       <c r="AD11" t="n">
-        <v>26.78333333333333</v>
+        <v>71.26425479282622</v>
       </c>
       <c r="AE11" t="n">
-        <v>183.75</v>
+        <v>21373.32942746477</v>
       </c>
       <c r="AF11" t="n">
-        <v>82.85000000000001</v>
+        <v>3395399.334374898</v>
       </c>
       <c r="AG11" t="n">
-        <v>76950</v>
+        <v>76.77254825375128</v>
       </c>
       <c r="AH11" t="n">
-        <v>47282916.66666666</v>
+        <v>1.130812420662045</v>
       </c>
       <c r="AI11" t="n">
-        <v>85.68333333333332</v>
+        <v>25.63015457899407</v>
       </c>
       <c r="AJ11" t="n">
-        <v>3.083333333333333</v>
+        <v>183.4706953719703</v>
       </c>
       <c r="AK11" t="n">
-        <v>24.95714285714286</v>
+        <v>73.49740422484784</v>
       </c>
       <c r="AL11" t="n">
-        <v>185.7636363636364</v>
+        <v>22261.34046295864</v>
       </c>
       <c r="AM11" t="n">
-        <v>76.23116883116883</v>
+        <v>6100050.358816296</v>
       </c>
       <c r="AN11" t="n">
-        <v>27564.93506493506</v>
+        <v>77.37456218185214</v>
       </c>
       <c r="AO11" t="n">
-        <v>13686363.63636363</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>79.42467532467533</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>1.45974025974026</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>26.85416666666667</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>183.3313484581867</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>81.70669934640523</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>75162.88545332663</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>38261669.78276353</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>83.96209359812302</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>2.684724317077258</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>24.18921166552746</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>184.4195906432749</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>73.40942507784612</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>24026.95374800638</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>10309174.54621402</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>78.25894281157441</v>
-      </c>
-      <c r="BE11" t="n">
-        <v>1.483652312599681</v>
-      </c>
-      <c r="BF11" t="inlineStr">
-        <is>
-          <t>K6A2elS9</t>
-        </is>
-      </c>
-      <c r="BG11" t="inlineStr">
-        <is>
-          <t>GzfvcwRj</t>
+        <v>1.202388735814692</v>
+      </c>
+      <c r="AP11" t="inlineStr">
+        <is>
+          <t>0jdIgO6t</t>
+        </is>
+      </c>
+      <c r="AQ11" t="inlineStr">
+        <is>
+          <t>M5BRZDsC</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>nBwH6AY8</t>
+          <t>x0haJmIE</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>45585.4375</v>
+        <v>45591.4375</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2507,21 +2171,21 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">holstein stadion
-  kiel </t>
+          <t xml:space="preserve">wwk arena
+  augsburg </t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>15034</v>
+        <v>30660</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>63WsD2ei</t>
+          <t>fTVNku3I</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>pzHW4oaE</t>
+          <t>nP1i5US1</t>
         </is>
       </c>
       <c r="H12" t="n">
@@ -2546,112 +2210,96 @@
           <t>bundesliga</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr"/>
-      <c r="P12" t="inlineStr"/>
-      <c r="Q12" t="inlineStr"/>
-      <c r="R12" t="inlineStr"/>
-      <c r="S12" t="inlineStr"/>
-      <c r="T12" t="inlineStr"/>
-      <c r="U12" t="inlineStr"/>
-      <c r="V12" t="inlineStr"/>
-      <c r="W12" t="inlineStr"/>
-      <c r="X12" t="inlineStr"/>
-      <c r="Y12" t="inlineStr"/>
-      <c r="Z12" t="inlineStr"/>
-      <c r="AA12" t="inlineStr"/>
-      <c r="AB12" t="inlineStr"/>
-      <c r="AC12" t="inlineStr"/>
+      <c r="N12" t="n">
+        <v>25.79166666666667</v>
+      </c>
+      <c r="O12" t="n">
+        <v>185.0416666666667</v>
+      </c>
+      <c r="P12" t="n">
+        <v>73.70833333333333</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>22291.66666666667</v>
+      </c>
+      <c r="R12" t="n">
+        <v>5350000</v>
+      </c>
+      <c r="S12" t="n">
+        <v>76.91666666666667</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1.125</v>
+      </c>
+      <c r="U12" t="n">
+        <v>26.64285714285714</v>
+      </c>
+      <c r="V12" t="n">
+        <v>186.061038961039</v>
+      </c>
+      <c r="W12" t="n">
+        <v>81.98311688311686</v>
+      </c>
+      <c r="X12" t="n">
+        <v>57966.23376623377</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>37499350.64935065</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>84.12597402597403</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>2.611688311688312</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>24.81548711988782</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>184.1908611131853</v>
+      </c>
       <c r="AD12" t="n">
-        <v>26.66814574314574</v>
+        <v>72.5454978243291</v>
       </c>
       <c r="AE12" t="n">
-        <v>185.6328282828283</v>
+        <v>21177.01909312369</v>
       </c>
       <c r="AF12" t="n">
-        <v>69.95238095238095</v>
+        <v>4952682.416666826</v>
       </c>
       <c r="AG12" t="n">
-        <v>16681.49350649351</v>
+        <v>76.55772420610985</v>
       </c>
       <c r="AH12" t="n">
-        <v>1926691.919191919</v>
+        <v>1.158487278483961</v>
       </c>
       <c r="AI12" t="n">
-        <v>72.3401875901876</v>
+        <v>24.94727735487788</v>
       </c>
       <c r="AJ12" t="n">
-        <v>1</v>
+        <v>184.0784915422379</v>
       </c>
       <c r="AK12" t="n">
-        <v>26.98412698412698</v>
+        <v>77.85036907627624</v>
       </c>
       <c r="AL12" t="n">
-        <v>186.3702741702742</v>
+        <v>43615.56955630182</v>
       </c>
       <c r="AM12" t="n">
-        <v>74.8975468975469</v>
+        <v>22506707.10514287</v>
       </c>
       <c r="AN12" t="n">
-        <v>27718.47041847042</v>
+        <v>82.89163811561654</v>
       </c>
       <c r="AO12" t="n">
-        <v>6582539.682539682</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>77.52539682539683</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>1.413131313131313</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>25.60353757063466</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>184.9785753202883</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>68.25622181748368</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>15618.43791673801</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>1839729.603511885</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>72.59229777341906</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>1</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>26.37341516316672</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>182.8920043379671</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>73.10748299319728</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>24930.5333727694</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>4181897.860593513</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>75.97586512866017</v>
-      </c>
-      <c r="BE12" t="n">
-        <v>1.159124519372967</v>
-      </c>
-      <c r="BF12" t="inlineStr">
-        <is>
-          <t>hAcTWKKN</t>
-        </is>
-      </c>
-      <c r="BG12" t="inlineStr">
+        <v>1.89768881548875</v>
+      </c>
+      <c r="AP12" t="inlineStr">
+        <is>
+          <t>2VSFgl3c</t>
+        </is>
+      </c>
+      <c r="AQ12" t="inlineStr">
         <is>
           <t>IkCftsQm</t>
         </is>
@@ -2660,11 +2308,11 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>rPiijklS</t>
+          <t>ELNeaSQr</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>45585.52083333334</v>
+        <v>45591.4375</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2674,21 +2322,21 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">volkswagen arena
-  wolfsburg </t>
+          <t xml:space="preserve">red bull arena
+  leipzig </t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>28917</v>
+        <v>47069</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>nwkTahLL</t>
+          <t>KbS1suSm</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Ig1f1fy3</t>
+          <t>fiEQZ7C7</t>
         </is>
       </c>
       <c r="H13" t="n">
@@ -2713,114 +2361,1004 @@
           <t>bundesliga</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr"/>
-      <c r="P13" t="inlineStr"/>
-      <c r="Q13" t="inlineStr"/>
-      <c r="R13" t="inlineStr"/>
-      <c r="S13" t="inlineStr"/>
-      <c r="T13" t="inlineStr"/>
-      <c r="U13" t="inlineStr"/>
-      <c r="V13" t="inlineStr"/>
-      <c r="W13" t="inlineStr"/>
-      <c r="X13" t="inlineStr"/>
-      <c r="Y13" t="inlineStr"/>
-      <c r="Z13" t="inlineStr"/>
-      <c r="AA13" t="inlineStr"/>
-      <c r="AB13" t="inlineStr"/>
-      <c r="AC13" t="inlineStr"/>
+      <c r="N13" t="n">
+        <v>25.86363636363637</v>
+      </c>
+      <c r="O13" t="n">
+        <v>183.4238095238095</v>
+      </c>
+      <c r="P13" t="n">
+        <v>80.54862914862915</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>57105.9163059163</v>
+      </c>
+      <c r="R13" t="n">
+        <v>30935786.43578643</v>
+      </c>
+      <c r="S13" t="n">
+        <v>84.0806637806638</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2.24040404040404</v>
+      </c>
+      <c r="U13" t="n">
+        <v>26.78730158730159</v>
+      </c>
+      <c r="V13" t="n">
+        <v>183.765873015873</v>
+      </c>
+      <c r="W13" t="n">
+        <v>76.15119047619048</v>
+      </c>
+      <c r="X13" t="n">
+        <v>26336.90476190476</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>10731904.76190476</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>78.68373015873014</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.619444444444445</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>25.30528527200354</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>184.6633464789425</v>
+      </c>
       <c r="AD13" t="n">
+        <v>78.55534362867954</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>52375.29741428735</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>24838828.53580029</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>82.33332104771732</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>1.96046181630547</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>26.78755273276358</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>183.3636766959748</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>74.21713048855905</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>23961.89683695405</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>6877269.306099807</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>76.81895202432959</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>1.387528604118993</v>
+      </c>
+      <c r="AP13" t="inlineStr">
+        <is>
+          <t>4ljanukM</t>
+        </is>
+      </c>
+      <c r="AQ13" t="inlineStr">
+        <is>
+          <t>YZPE6Sx7</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>Mku6FvHt</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>45591.4375</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">burda m 
+  ger </t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">millerntor stadion
+  hamburg </t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>29546</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>ILyJuN3g</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>nwkTahLL</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>59</v>
+      </c>
+      <c r="I14" t="n">
+        <v>591</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="N14" t="n">
+        <v>26.76926406926407</v>
+      </c>
+      <c r="O14" t="n">
+        <v>185.3191919191919</v>
+      </c>
+      <c r="P14" t="n">
+        <v>70.64227994227994</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>17154.25685425686</v>
+      </c>
+      <c r="R14" t="n">
+        <v>2338008.658008658</v>
+      </c>
+      <c r="S14" t="n">
+        <v>73.57301587301588</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1</v>
+      </c>
+      <c r="U14" t="n">
         <v>24.70833333333333</v>
       </c>
-      <c r="AE13" t="n">
+      <c r="V14" t="n">
         <v>184.7083333333333</v>
       </c>
-      <c r="AF13" t="n">
+      <c r="W14" t="n">
         <v>75.2986111111111</v>
       </c>
-      <c r="AG13" t="n">
+      <c r="X14" t="n">
         <v>36312.5</v>
       </c>
-      <c r="AH13" t="n">
+      <c r="Y14" t="n">
         <v>10284953.7037037</v>
       </c>
-      <c r="AI13" t="n">
+      <c r="Z14" t="n">
         <v>79.89814814814814</v>
       </c>
-      <c r="AJ13" t="n">
+      <c r="AA14" t="n">
         <v>1.418981481481481</v>
       </c>
-      <c r="AK13" t="n">
+      <c r="AB14" t="n">
+        <v>25.57589807852966</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>184.6525480367586</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>68.33454469507102</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>16058.14536340852</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>1786161.236424394</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>71.97422723475356</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>24.70891265597148</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>184.8741501145913</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>73.08691325014854</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>32352.28333757745</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>7859812.515915456</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>78.21184428316782</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>1.363718062982769</v>
+      </c>
+      <c r="AP14" t="inlineStr">
+        <is>
+          <t>0jdIgO6t</t>
+        </is>
+      </c>
+      <c r="AQ14" t="inlineStr">
+        <is>
+          <t>f3ddUIXs</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>rwXP4l3L</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>45591.4375</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hartmann r 
+  ger </t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mhparena
+  stuttgart </t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>60449</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>nJQmYp1B</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>63WsD2ei</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>59</v>
+      </c>
+      <c r="I15" t="n">
+        <v>591</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="N15" t="n">
+        <v>24.8875</v>
+      </c>
+      <c r="O15" t="n">
+        <v>185.7181818181818</v>
+      </c>
+      <c r="P15" t="n">
+        <v>76.17727272727274</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>27419.31818181818</v>
+      </c>
+      <c r="R15" t="n">
+        <v>13679630.68181818</v>
+      </c>
+      <c r="S15" t="n">
+        <v>79.47159090909091</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1.452272727272728</v>
+      </c>
+      <c r="U15" t="n">
+        <v>26.66814574314574</v>
+      </c>
+      <c r="V15" t="n">
+        <v>185.6328282828283</v>
+      </c>
+      <c r="W15" t="n">
+        <v>69.95238095238095</v>
+      </c>
+      <c r="X15" t="n">
+        <v>16681.49350649351</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1926691.919191919</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>72.3401875901876</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>24.23134968102073</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>184.7684576023392</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>73.57535220627327</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>24095.95295055821</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>10361317.20162148</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>78.25289074960128</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>1.482406299840511</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>25.60353757063466</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>184.9785753202883</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>68.25622181748368</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>15618.43791673801</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>1839729.603511885</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>72.59229777341906</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP15" t="inlineStr">
+        <is>
+          <t>GzfvcwRj</t>
+        </is>
+      </c>
+      <c r="AQ15" t="inlineStr">
+        <is>
+          <t>A15eUM4C</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>MiACepQ7</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>45591.5625</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hartmann r 
+  ger </t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">weserstadion
+  bremen </t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>42100</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Ig1f1fy3</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>4jcj2zMd</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>59</v>
+      </c>
+      <c r="I16" t="n">
+        <v>591</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="N16" t="n">
         <v>26.98051948051948</v>
       </c>
-      <c r="AL13" t="n">
+      <c r="O16" t="n">
         <v>183.7805194805195</v>
       </c>
-      <c r="AM13" t="n">
+      <c r="P16" t="n">
         <v>74.43636363636365</v>
       </c>
-      <c r="AN13" t="n">
+      <c r="Q16" t="n">
         <v>23588.31168831169</v>
       </c>
-      <c r="AO13" t="n">
+      <c r="R16" t="n">
         <v>6014415.584415585</v>
       </c>
-      <c r="AP13" t="n">
+      <c r="S16" t="n">
         <v>76.79350649350648</v>
       </c>
-      <c r="AQ13" t="n">
+      <c r="T16" t="n">
         <v>1.094805194805195</v>
       </c>
-      <c r="AR13" t="n">
-        <v>24.70891265597148</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>184.8741501145913</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>73.08691325014854</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>32352.28333757745</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>7859812.515915456</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>78.21184428316782</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>1.363718062982769</v>
-      </c>
-      <c r="AY13" t="n">
+      <c r="U16" t="n">
+        <v>26.40674603174603</v>
+      </c>
+      <c r="V16" t="n">
+        <v>184.3571428571429</v>
+      </c>
+      <c r="W16" t="n">
+        <v>83.76865079365079</v>
+      </c>
+      <c r="X16" t="n">
+        <v>99564.28571428571</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>50273214.28571428</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>85.91904761904763</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>3.064285714285715</v>
+      </c>
+      <c r="AB16" t="n">
         <v>24.60253992311855</v>
       </c>
-      <c r="AZ13" t="n">
+      <c r="AC16" t="n">
         <v>186.3206916217704</v>
       </c>
-      <c r="BA13" t="n">
+      <c r="AD16" t="n">
         <v>70.48234358718177</v>
       </c>
-      <c r="BB13" t="n">
+      <c r="AE16" t="n">
         <v>19202.79231864717</v>
       </c>
-      <c r="BC13" t="n">
+      <c r="AF16" t="n">
         <v>3470618.297107345</v>
       </c>
-      <c r="BD13" t="n">
+      <c r="AG16" t="n">
         <v>76.51956917986665</v>
       </c>
-      <c r="BE13" t="n">
+      <c r="AH16" t="n">
         <v>1</v>
       </c>
-      <c r="BF13" t="inlineStr">
+      <c r="AI16" t="n">
+        <v>24.56634355496585</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>180.7619096761511</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>80.84288294265075</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>82188.14560912084</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>39435822.47592019</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>84.59387316330042</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>2.302458351761757</v>
+      </c>
+      <c r="AP16" t="inlineStr">
+        <is>
+          <t>4fuCGs9P</t>
+        </is>
+      </c>
+      <c r="AQ16" t="inlineStr">
+        <is>
+          <t>A15eUM4C</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>WQadeyWO</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>45592.47916666666</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">brand b 
+  ger </t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vonovia ruhrstadion
+  bochum </t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>26000</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>8Y2m6ADe</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>nVp0wiqd</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>59</v>
+      </c>
+      <c r="I17" t="n">
+        <v>591</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="N17" t="n">
+        <v>28.33888888888889</v>
+      </c>
+      <c r="O17" t="n">
+        <v>185.2921296296296</v>
+      </c>
+      <c r="P17" t="n">
+        <v>71.6962962962963</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>17048.14814814815</v>
+      </c>
+      <c r="R17" t="n">
+        <v>2222615.740740741</v>
+      </c>
+      <c r="S17" t="n">
+        <v>73.5712962962963</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1</v>
+      </c>
+      <c r="U17" t="n">
+        <v>26.92539682539682</v>
+      </c>
+      <c r="V17" t="n">
+        <v>183.7380952380952</v>
+      </c>
+      <c r="W17" t="n">
+        <v>82.85555555555557</v>
+      </c>
+      <c r="X17" t="n">
+        <v>77163.49206349207</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>46305992.06349206</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>85.61746031746031</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>3.103174603174603</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>25.40532515300317</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>185.6896861308626</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>68.42912900652838</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>15078.88310519889</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>1804867.324797665</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>74.38585339668931</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>26.675</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>183.4268701070172</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>81.46288515406162</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>75162.88545332663</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>37413574.0995116</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>83.974651655534</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>2.64404941463765</v>
+      </c>
+      <c r="AP17" t="inlineStr">
         <is>
           <t>8f6APkLc</t>
         </is>
       </c>
-      <c r="BG13" t="inlineStr">
-        <is>
-          <t>YZPE6Sx7</t>
+      <c r="AQ17" t="inlineStr">
+        <is>
+          <t>K6A2elS9</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>ABBmcc1C</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>45592.5625</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">brand b 
+  ger </t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadion an der alten forsterei
+  berlin </t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>22012</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>pzHW4oaE</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>8vndvXTk</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>59</v>
+      </c>
+      <c r="I18" t="n">
+        <v>591</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="N18" t="n">
+        <v>26.98412698412698</v>
+      </c>
+      <c r="O18" t="n">
+        <v>186.3702741702742</v>
+      </c>
+      <c r="P18" t="n">
+        <v>74.8975468975469</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>27718.47041847042</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6582539.682539682</v>
+      </c>
+      <c r="S18" t="n">
+        <v>77.52539682539683</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1.413131313131313</v>
+      </c>
+      <c r="U18" t="n">
+        <v>24.52777777777778</v>
+      </c>
+      <c r="V18" t="n">
+        <v>185.337962962963</v>
+      </c>
+      <c r="W18" t="n">
+        <v>76.72685185185185</v>
+      </c>
+      <c r="X18" t="n">
+        <v>34518.51851851852</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>15101157.40740741</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>81.68518518518518</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.671296296296297</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>26.37341516316672</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>182.8920043379671</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>73.10748299319728</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>24930.5333727694</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>4181897.860593513</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>75.97586512866017</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>1.159124519372967</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>22.60779220779221</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>184.7599404355043</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>72.78391758617323</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>25675.59971356964</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>8849931.500829998</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>80.94579468150896</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>1.391914852065228</v>
+      </c>
+      <c r="AP18" t="inlineStr">
+        <is>
+          <t>hpYJ6izc</t>
+        </is>
+      </c>
+      <c r="AQ18" t="inlineStr">
+        <is>
+          <t>K6A2elS9</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>zyC4c6ee</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>45592.64583333334</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">osmers h 
+  ger </t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">voith arena
+  heidenheim </t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>15000</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>KWixEVWi</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>hQAtP9Sl</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>59</v>
+      </c>
+      <c r="I19" t="n">
+        <v>591</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="N19" t="n">
+        <v>26.81428571428571</v>
+      </c>
+      <c r="O19" t="n">
+        <v>187.2571428571428</v>
+      </c>
+      <c r="P19" t="n">
+        <v>72.52857142857142</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>22128.57142857143</v>
+      </c>
+      <c r="R19" t="n">
+        <v>3170000</v>
+      </c>
+      <c r="S19" t="n">
+        <v>74.31428571428572</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1.014285714285714</v>
+      </c>
+      <c r="U19" t="n">
+        <v>27.52539682539683</v>
+      </c>
+      <c r="V19" t="n">
+        <v>186.084126984127</v>
+      </c>
+      <c r="W19" t="n">
+        <v>74.82063492063492</v>
+      </c>
+      <c r="X19" t="n">
+        <v>30061.90476190476</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>7427777.777777778</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>78.15396825396826</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1.641269841269841</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>25.78788819875777</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>185.0847826086956</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>69.52639751552795</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>19842.85714285714</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>2179208.074534161</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>72.36211180124224</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>1.037267080745342</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>24.26210765007758</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>186.1579424752357</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>71.20689819787563</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>23972.69363885905</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>5652869.077455544</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>77.70173051676811</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>1.218701515693997</v>
+      </c>
+      <c r="AP19" t="inlineStr">
+        <is>
+          <t>4ljanukM</t>
+        </is>
+      </c>
+      <c r="AQ19" t="inlineStr">
+        <is>
+          <t>KUx4Q7x1</t>
         </is>
       </c>
     </row>

--- a/data/germany/p6_deployment/data_preparation/df_filled.xlsx
+++ b/data/germany/p6_deployment/data_preparation/df_filled.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AQ19"/>
+  <dimension ref="A1:BG19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -495,150 +495,230 @@
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
+          <t>mean_age_player_miss_home</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>mean_hei_player_miss_home</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>n_player_miss_home</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>sum_rat_player_miss_home</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>sum_wage_player_miss_home</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>sum_value_player_miss_home</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>sum_pot_player_miss_home</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>sum_rep_player_miss_home</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>mean_age_player_miss_away</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>mean_hei_player_miss_away</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>n_player_miss_away</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>sum_rat_player_miss_away</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>sum_wage_player_miss_away</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>sum_value_player_miss_away</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>sum_pot_player_miss_away</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>sum_rep_player_miss_away</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
           <t>mean_age_player_start_home</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>mean_hei_player_start_home</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>mean_rat_player_start_home</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>mean_wage_player_start_home</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>mean_value_player_start_home</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>mean_pot_player_start_home</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>mean_rep_player_start_home</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>mean_age_player_start_away</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>mean_hei_player_start_away</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>mean_rat_player_start_away</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>mean_wage_player_start_away</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>mean_value_player_start_away</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>mean_pot_player_start_away</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>mean_rep_player_start_away</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>mean_age_player_sub_home</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>mean_hei_player_sub_home</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>mean_rat_player_sub_home</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>mean_wage_player_sub_home</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>mean_value_player_sub_home</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AW1" s="1" t="inlineStr">
         <is>
           <t>mean_pot_player_sub_home</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AX1" s="1" t="inlineStr">
         <is>
           <t>mean_rep_player_sub_home</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AY1" s="1" t="inlineStr">
         <is>
           <t>mean_age_player_sub_away</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AZ1" s="1" t="inlineStr">
         <is>
           <t>mean_hei_player_sub_away</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="BA1" s="1" t="inlineStr">
         <is>
           <t>mean_rat_player_sub_away</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="BB1" s="1" t="inlineStr">
         <is>
           <t>mean_wage_player_sub_away</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="BC1" s="1" t="inlineStr">
         <is>
           <t>mean_value_player_sub_away</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="BD1" s="1" t="inlineStr">
         <is>
           <t>mean_pot_player_sub_away</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="BE1" s="1" t="inlineStr">
         <is>
           <t>mean_rep_player_sub_away</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="BF1" s="1" t="inlineStr">
         <is>
           <t>id_coach_home</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="BG1" s="1" t="inlineStr">
         <is>
           <t>id_coach_away</t>
         </is>
@@ -701,95 +781,143 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>26.64285714285714</v>
+        <v>20.33333333333333</v>
       </c>
       <c r="O2" t="n">
-        <v>186.061038961039</v>
+        <v>178.3333333333333</v>
       </c>
       <c r="P2" t="n">
-        <v>81.98311688311686</v>
+        <v>3</v>
       </c>
       <c r="Q2" t="n">
-        <v>57966.23376623377</v>
+        <v>220</v>
       </c>
       <c r="R2" t="n">
-        <v>37499350.64935065</v>
+        <v>86000</v>
       </c>
       <c r="S2" t="n">
-        <v>84.12597402597403</v>
+        <v>49700000</v>
       </c>
       <c r="T2" t="n">
-        <v>2.611688311688312</v>
+        <v>255</v>
       </c>
       <c r="U2" t="n">
-        <v>26.76926406926407</v>
+        <v>5</v>
       </c>
       <c r="V2" t="n">
-        <v>185.3191919191919</v>
+        <v>27.33333333333333</v>
       </c>
       <c r="W2" t="n">
-        <v>70.64227994227994</v>
+        <v>187.1666666666667</v>
       </c>
       <c r="X2" t="n">
-        <v>17154.25685425686</v>
+        <v>6</v>
       </c>
       <c r="Y2" t="n">
-        <v>2338008.658008658</v>
+        <v>401</v>
       </c>
       <c r="Z2" t="n">
-        <v>73.57301587301588</v>
+        <v>80000</v>
       </c>
       <c r="AA2" t="n">
+        <v>7210000</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>420</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>6</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>26.64393939393939</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>186.1318181818182</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>81.99545454545454</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>58096.9696969697</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>37582575.75757576</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>84.10151515151516</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>2.607575757575757</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>26.78636363636364</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>185.2242424242424</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>70.61969696969697</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>17198.48484848485</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>2322121.212121212</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>73.48333333333333</v>
+      </c>
+      <c r="AQ2" t="n">
         <v>1</v>
       </c>
-      <c r="AB2" t="n">
-        <v>24.94727735487788</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>184.0784915422379</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>77.85036907627624</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>43615.56955630182</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>22506707.10514287</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>82.89163811561654</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>1.89768881548875</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>25.57589807852966</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>184.6525480367586</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>68.33454469507102</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>16058.14536340852</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>1786161.236424394</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>71.97422723475356</v>
-      </c>
-      <c r="AO2" t="n">
+      <c r="AR2" t="n">
+        <v>25.00991881878609</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>184.1391925135632</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>77.96828773184609</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>44313.40257759022</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>22440364.6385397</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>82.86564129361612</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>1.912382983149573</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>25.69819688109162</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>184.6735867446394</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>68.29381091617934</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>16059.06432748538</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>1761047.7582846</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>71.8646686159844</v>
+      </c>
+      <c r="BE2" t="n">
         <v>1</v>
       </c>
-      <c r="AP2" t="inlineStr">
+      <c r="BF2" t="inlineStr">
         <is>
           <t>hpYJ6izc</t>
         </is>
       </c>
-      <c r="AQ2" t="inlineStr">
+      <c r="BG2" t="inlineStr">
         <is>
           <t>vZA6VYpf</t>
         </is>
@@ -852,95 +980,143 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>26.11428571428572</v>
+        <v>23.5</v>
       </c>
       <c r="O3" t="n">
-        <v>184.8857142857143</v>
+        <v>182.8333333333333</v>
       </c>
       <c r="P3" t="n">
-        <v>75.48571428571428</v>
+        <v>6</v>
       </c>
       <c r="Q3" t="n">
-        <v>24414.28571428571</v>
+        <v>424</v>
       </c>
       <c r="R3" t="n">
-        <v>8282857.142857143</v>
+        <v>96000</v>
       </c>
       <c r="S3" t="n">
-        <v>77.91428571428573</v>
+        <v>39725000</v>
       </c>
       <c r="T3" t="n">
-        <v>1.485714285714286</v>
+        <v>466</v>
       </c>
       <c r="U3" t="n">
-        <v>26.81428571428571</v>
+        <v>8</v>
       </c>
       <c r="V3" t="n">
-        <v>187.2571428571428</v>
+        <v>24.66666666666667</v>
       </c>
       <c r="W3" t="n">
-        <v>72.52857142857142</v>
+        <v>189.6666666666667</v>
       </c>
       <c r="X3" t="n">
-        <v>22128.57142857143</v>
+        <v>3</v>
       </c>
       <c r="Y3" t="n">
-        <v>3170000</v>
+        <v>204</v>
       </c>
       <c r="Z3" t="n">
-        <v>74.31428571428572</v>
+        <v>53000</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.014285714285714</v>
+        <v>5100000</v>
       </c>
       <c r="AB3" t="n">
-        <v>25.63015457899407</v>
+        <v>215</v>
       </c>
       <c r="AC3" t="n">
-        <v>183.4706953719703</v>
+        <v>3</v>
       </c>
       <c r="AD3" t="n">
-        <v>73.49740422484784</v>
+        <v>26.2</v>
       </c>
       <c r="AE3" t="n">
-        <v>22261.34046295864</v>
+        <v>185.0666666666667</v>
       </c>
       <c r="AF3" t="n">
-        <v>6100050.358816296</v>
+        <v>75.55</v>
       </c>
       <c r="AG3" t="n">
-        <v>77.37456218185214</v>
+        <v>24450</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.202388735814692</v>
+        <v>8165000</v>
       </c>
       <c r="AI3" t="n">
-        <v>25.78788819875777</v>
+        <v>77.73333333333333</v>
       </c>
       <c r="AJ3" t="n">
-        <v>185.0847826086956</v>
+        <v>1.483333333333333</v>
       </c>
       <c r="AK3" t="n">
-        <v>69.52639751552795</v>
+        <v>26.85</v>
       </c>
       <c r="AL3" t="n">
-        <v>19842.85714285714</v>
+        <v>187.2833333333333</v>
       </c>
       <c r="AM3" t="n">
-        <v>2179208.074534161</v>
+        <v>72.61666666666667</v>
       </c>
       <c r="AN3" t="n">
-        <v>72.36211180124224</v>
+        <v>22200</v>
       </c>
       <c r="AO3" t="n">
-        <v>1.037267080745342</v>
-      </c>
-      <c r="AP3" t="inlineStr">
+        <v>3205000</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>74.39999999999999</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>1.016666666666667</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>25.68445570447859</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>183.1868257600523</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>73.44987014638045</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>22246.92619229232</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>5921073.244705968</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>77.25582979187097</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>1.185395554102648</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>25.78152173913044</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>184.888768115942</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>69.50543478260869</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>19889.13043478261</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>2174655.797101449</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>72.25579710144928</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>1.043478260869565</v>
+      </c>
+      <c r="BF3" t="inlineStr">
         <is>
           <t>2VSFgl3c</t>
         </is>
       </c>
-      <c r="AQ3" t="inlineStr">
+      <c r="BG3" t="inlineStr">
         <is>
           <t>pfoInmcq</t>
         </is>
@@ -1003,95 +1179,143 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>26.40674603174603</v>
+        <v>21</v>
       </c>
       <c r="O4" t="n">
-        <v>184.3571428571429</v>
+        <v>177</v>
       </c>
       <c r="P4" t="n">
-        <v>83.76865079365079</v>
+        <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>99564.28571428571</v>
+        <v>88</v>
       </c>
       <c r="R4" t="n">
-        <v>50273214.28571428</v>
+        <v>115000</v>
       </c>
       <c r="S4" t="n">
-        <v>85.91904761904763</v>
+        <v>133500000</v>
       </c>
       <c r="T4" t="n">
-        <v>3.064285714285715</v>
+        <v>92</v>
       </c>
       <c r="U4" t="n">
+        <v>4</v>
+      </c>
+      <c r="V4" t="n">
+        <v>19</v>
+      </c>
+      <c r="W4" t="n">
+        <v>172</v>
+      </c>
+      <c r="X4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>59</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>3000</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>575000</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>76</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>26.39120370370371</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>184.3125</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>84.12592592592593</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>102408.3333333333</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>53464583.33333334</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>86.15555555555557</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>3.158333333333334</v>
+      </c>
+      <c r="AK4" t="n">
         <v>24.52777777777778</v>
       </c>
-      <c r="V4" t="n">
+      <c r="AL4" t="n">
         <v>185.337962962963</v>
       </c>
-      <c r="W4" t="n">
+      <c r="AM4" t="n">
         <v>76.72685185185185</v>
       </c>
-      <c r="X4" t="n">
+      <c r="AN4" t="n">
         <v>34518.51851851852</v>
       </c>
-      <c r="Y4" t="n">
+      <c r="AO4" t="n">
         <v>15101157.40740741</v>
       </c>
-      <c r="Z4" t="n">
+      <c r="AP4" t="n">
         <v>81.68518518518518</v>
       </c>
-      <c r="AA4" t="n">
+      <c r="AQ4" t="n">
         <v>1.671296296296297</v>
       </c>
-      <c r="AB4" t="n">
-        <v>24.56634355496585</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>180.7619096761511</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>80.84288294265075</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>82188.14560912084</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>39435822.47592019</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>84.59387316330042</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>2.302458351761757</v>
-      </c>
-      <c r="AI4" t="n">
+      <c r="AR4" t="n">
+        <v>24.50439263424668</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>180.6530668407714</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>80.45989343105664</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>79589.1732131449</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>36725973.98608566</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>84.37939245873788</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>2.21641498704745</v>
+      </c>
+      <c r="AY4" t="n">
         <v>22.60779220779221</v>
       </c>
-      <c r="AJ4" t="n">
+      <c r="AZ4" t="n">
         <v>184.7599404355043</v>
       </c>
-      <c r="AK4" t="n">
+      <c r="BA4" t="n">
         <v>72.78391758617323</v>
       </c>
-      <c r="AL4" t="n">
+      <c r="BB4" t="n">
         <v>25675.59971356964</v>
       </c>
-      <c r="AM4" t="n">
+      <c r="BC4" t="n">
         <v>8849931.500829998</v>
       </c>
-      <c r="AN4" t="n">
+      <c r="BD4" t="n">
         <v>80.94579468150896</v>
       </c>
-      <c r="AO4" t="n">
+      <c r="BE4" t="n">
         <v>1.391914852065228</v>
       </c>
-      <c r="AP4" t="inlineStr">
+      <c r="BF4" t="inlineStr">
         <is>
           <t>hAcTWKKN</t>
         </is>
       </c>
-      <c r="AQ4" t="inlineStr">
+      <c r="BG4" t="inlineStr">
         <is>
           <t>K6A2elS9</t>
         </is>
@@ -1154,95 +1378,143 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>26.78730158730159</v>
+        <v>26</v>
       </c>
       <c r="O5" t="n">
-        <v>183.765873015873</v>
+        <v>185.5</v>
       </c>
       <c r="P5" t="n">
-        <v>76.15119047619048</v>
+        <v>4</v>
       </c>
       <c r="Q5" t="n">
-        <v>26336.90476190476</v>
+        <v>283</v>
       </c>
       <c r="R5" t="n">
-        <v>10731904.76190476</v>
+        <v>68000</v>
       </c>
       <c r="S5" t="n">
-        <v>78.68373015873014</v>
+        <v>17900000</v>
       </c>
       <c r="T5" t="n">
-        <v>1.619444444444445</v>
+        <v>298</v>
       </c>
       <c r="U5" t="n">
+        <v>4</v>
+      </c>
+      <c r="V5" t="n">
+        <v>25.83333333333333</v>
+      </c>
+      <c r="W5" t="n">
+        <v>182</v>
+      </c>
+      <c r="X5" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>423</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>107000</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>19825000</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>439</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>6</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>26.75185185185185</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>183.9351851851851</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>76.23888888888889</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>26288.88888888889</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>10895555.55555556</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>78.81851851851852</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>1.618518518518519</v>
+      </c>
+      <c r="AK5" t="n">
         <v>25.79166666666667</v>
       </c>
-      <c r="V5" t="n">
+      <c r="AL5" t="n">
         <v>185.0416666666667</v>
       </c>
-      <c r="W5" t="n">
+      <c r="AM5" t="n">
         <v>73.70833333333333</v>
       </c>
-      <c r="X5" t="n">
+      <c r="AN5" t="n">
         <v>22291.66666666667</v>
       </c>
-      <c r="Y5" t="n">
+      <c r="AO5" t="n">
         <v>5350000</v>
       </c>
-      <c r="Z5" t="n">
+      <c r="AP5" t="n">
         <v>76.91666666666667</v>
       </c>
-      <c r="AA5" t="n">
+      <c r="AQ5" t="n">
         <v>1.125</v>
       </c>
-      <c r="AB5" t="n">
-        <v>26.78755273276358</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>183.3636766959748</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>74.21713048855905</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>23961.89683695405</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>6877269.306099807</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>76.81895202432959</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>1.387528604118993</v>
-      </c>
-      <c r="AI5" t="n">
+      <c r="AR5" t="n">
+        <v>26.59272456503578</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>183.5692170148692</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>74.27505803375368</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>23933.80717934493</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>7083444.625232384</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>77.01341504287728</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>1.386899313501144</v>
+      </c>
+      <c r="AY5" t="n">
         <v>24.81548711988782</v>
       </c>
-      <c r="AJ5" t="n">
+      <c r="AZ5" t="n">
         <v>184.1908611131853</v>
       </c>
-      <c r="AK5" t="n">
+      <c r="BA5" t="n">
         <v>72.5454978243291</v>
       </c>
-      <c r="AL5" t="n">
+      <c r="BB5" t="n">
         <v>21177.01909312369</v>
       </c>
-      <c r="AM5" t="n">
+      <c r="BC5" t="n">
         <v>4952682.416666826</v>
       </c>
-      <c r="AN5" t="n">
+      <c r="BD5" t="n">
         <v>76.55772420610985</v>
       </c>
-      <c r="AO5" t="n">
+      <c r="BE5" t="n">
         <v>1.158487278483961</v>
       </c>
-      <c r="AP5" t="inlineStr">
+      <c r="BF5" t="inlineStr">
         <is>
           <t>4fuCGs9P</t>
         </is>
       </c>
-      <c r="AQ5" t="inlineStr">
+      <c r="BG5" t="inlineStr">
         <is>
           <t>M5BRZDsC</t>
         </is>
@@ -1305,95 +1577,143 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>27.52539682539683</v>
+        <v>27.8</v>
       </c>
       <c r="O6" t="n">
-        <v>186.084126984127</v>
+        <v>182.8</v>
       </c>
       <c r="P6" t="n">
-        <v>74.82063492063492</v>
+        <v>5</v>
       </c>
       <c r="Q6" t="n">
-        <v>30061.90476190476</v>
+        <v>375</v>
       </c>
       <c r="R6" t="n">
-        <v>7427777.777777778</v>
+        <v>151000</v>
       </c>
       <c r="S6" t="n">
-        <v>78.15396825396826</v>
+        <v>31900000</v>
       </c>
       <c r="T6" t="n">
-        <v>1.641269841269841</v>
+        <v>384</v>
       </c>
       <c r="U6" t="n">
+        <v>9</v>
+      </c>
+      <c r="V6" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="W6" t="n">
+        <v>183</v>
+      </c>
+      <c r="X6" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>133</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>29000</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>2975000</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>144</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>27.5462962962963</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>186.0148148148148</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>75.05740740740741</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>30288.88888888889</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>7644074.074074075</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>78.47962962962963</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>1.664814814814815</v>
+      </c>
+      <c r="AK6" t="n">
         <v>28.33888888888889</v>
       </c>
-      <c r="V6" t="n">
+      <c r="AL6" t="n">
         <v>185.2921296296296</v>
       </c>
-      <c r="W6" t="n">
+      <c r="AM6" t="n">
         <v>71.6962962962963</v>
       </c>
-      <c r="X6" t="n">
+      <c r="AN6" t="n">
         <v>17048.14814814815</v>
       </c>
-      <c r="Y6" t="n">
+      <c r="AO6" t="n">
         <v>2222615.740740741</v>
       </c>
-      <c r="Z6" t="n">
+      <c r="AP6" t="n">
         <v>73.5712962962963</v>
       </c>
-      <c r="AA6" t="n">
+      <c r="AQ6" t="n">
         <v>1</v>
       </c>
-      <c r="AB6" t="n">
-        <v>24.26210765007758</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>186.1579424752357</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>71.20689819787563</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>23972.69363885905</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>5652869.077455544</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>77.70173051676811</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>1.218701515693997</v>
-      </c>
-      <c r="AI6" t="n">
+      <c r="AR6" t="n">
+        <v>24.18357003620162</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>186.0842662211083</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>71.1302701197438</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>24001.47591200222</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>5547513.923698135</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>77.74090782511836</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>1.188485101642996</v>
+      </c>
+      <c r="AY6" t="n">
         <v>25.40532515300317</v>
       </c>
-      <c r="AJ6" t="n">
+      <c r="AZ6" t="n">
         <v>185.6896861308626</v>
       </c>
-      <c r="AK6" t="n">
+      <c r="BA6" t="n">
         <v>68.42912900652838</v>
       </c>
-      <c r="AL6" t="n">
+      <c r="BB6" t="n">
         <v>15078.88310519889</v>
       </c>
-      <c r="AM6" t="n">
+      <c r="BC6" t="n">
         <v>1804867.324797665</v>
       </c>
-      <c r="AN6" t="n">
+      <c r="BD6" t="n">
         <v>74.38585339668931</v>
       </c>
-      <c r="AO6" t="n">
+      <c r="BE6" t="n">
         <v>1</v>
       </c>
-      <c r="AP6" t="inlineStr">
+      <c r="BF6" t="inlineStr">
         <is>
           <t>GzfvcwRj</t>
         </is>
       </c>
-      <c r="AQ6" t="inlineStr">
+      <c r="BG6" t="inlineStr">
         <is>
           <t>f3ddUIXs</t>
         </is>
@@ -1456,95 +1776,143 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>27.55238095238095</v>
+        <v>30</v>
       </c>
       <c r="O7" t="n">
-        <v>183.3444444444445</v>
+        <v>183</v>
       </c>
       <c r="P7" t="n">
-        <v>74.82380952380952</v>
+        <v>1</v>
       </c>
       <c r="Q7" t="n">
-        <v>25260.31746031746</v>
+        <v>75</v>
       </c>
       <c r="R7" t="n">
-        <v>6533968.253968254</v>
+        <v>26000</v>
       </c>
       <c r="S7" t="n">
-        <v>76.96507936507938</v>
+        <v>4600000</v>
       </c>
       <c r="T7" t="n">
-        <v>1.409523809523809</v>
+        <v>75</v>
       </c>
       <c r="U7" t="n">
-        <v>25.86363636363637</v>
+        <v>2</v>
       </c>
       <c r="V7" t="n">
-        <v>183.4238095238095</v>
+        <v>25.75</v>
       </c>
       <c r="W7" t="n">
-        <v>80.54862914862915</v>
+        <v>180.75</v>
       </c>
       <c r="X7" t="n">
-        <v>57105.9163059163</v>
+        <v>4</v>
       </c>
       <c r="Y7" t="n">
-        <v>30935786.43578643</v>
+        <v>309</v>
       </c>
       <c r="Z7" t="n">
-        <v>84.0806637806638</v>
+        <v>192000</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.24040404040404</v>
+        <v>71500000</v>
       </c>
       <c r="AB7" t="n">
-        <v>25.68795690525014</v>
+        <v>332</v>
       </c>
       <c r="AC7" t="n">
-        <v>183.6457442307066</v>
+        <v>9</v>
       </c>
       <c r="AD7" t="n">
-        <v>71.26425479282622</v>
+        <v>27.62777777777778</v>
       </c>
       <c r="AE7" t="n">
-        <v>21373.32942746477</v>
+        <v>183.4851851851852</v>
       </c>
       <c r="AF7" t="n">
-        <v>3395399.334374898</v>
+        <v>74.84444444444445</v>
       </c>
       <c r="AG7" t="n">
-        <v>76.77254825375128</v>
+        <v>25270.37037037037</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.130812420662045</v>
+        <v>6512962.962962963</v>
       </c>
       <c r="AI7" t="n">
-        <v>25.30528527200354</v>
+        <v>76.90925925925926</v>
       </c>
       <c r="AJ7" t="n">
-        <v>184.6633464789425</v>
+        <v>1.411111111111111</v>
       </c>
       <c r="AK7" t="n">
-        <v>78.55534362867954</v>
+        <v>25.78030303030303</v>
       </c>
       <c r="AL7" t="n">
+        <v>183.4792929292929</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>80.53400673400672</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>56972.05387205387</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>31091750.84175084</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>84.12441077441078</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>2.235016835016835</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>25.62007670691881</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>183.5708285866181</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>71.28448773448773</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>21546.66210982001</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>3453957.953596111</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>76.79813169286854</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>1.144677982835877</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>25.3874161506708</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>184.7322375587662</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>78.60623423345946</v>
+      </c>
+      <c r="BB7" t="n">
         <v>52375.29741428735</v>
       </c>
-      <c r="AM7" t="n">
-        <v>24838828.53580029</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>82.33332104771732</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>1.96046181630547</v>
-      </c>
-      <c r="AP7" t="inlineStr">
+      <c r="BC7" t="n">
+        <v>24627070.791767</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>82.36804122233688</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>1.943455452356381</v>
+      </c>
+      <c r="BF7" t="inlineStr">
         <is>
           <t>0jdIgO6t</t>
         </is>
       </c>
-      <c r="AQ7" t="inlineStr">
+      <c r="BG7" t="inlineStr">
         <is>
           <t>pfoInmcq</t>
         </is>
@@ -1607,95 +1975,143 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>26.92539682539682</v>
+        <v>22.4</v>
       </c>
       <c r="O8" t="n">
-        <v>183.7380952380952</v>
+        <v>185</v>
       </c>
       <c r="P8" t="n">
-        <v>82.85555555555557</v>
+        <v>5</v>
       </c>
       <c r="Q8" t="n">
-        <v>77163.49206349207</v>
+        <v>382</v>
       </c>
       <c r="R8" t="n">
-        <v>46305992.06349206</v>
+        <v>255000</v>
       </c>
       <c r="S8" t="n">
-        <v>85.61746031746031</v>
+        <v>188150000</v>
       </c>
       <c r="T8" t="n">
-        <v>3.103174603174603</v>
+        <v>420</v>
       </c>
       <c r="U8" t="n">
-        <v>24.8875</v>
+        <v>9</v>
       </c>
       <c r="V8" t="n">
-        <v>185.7181818181818</v>
+        <v>22.57142857142857</v>
       </c>
       <c r="W8" t="n">
-        <v>76.17727272727274</v>
+        <v>184.8571428571429</v>
       </c>
       <c r="X8" t="n">
-        <v>27419.31818181818</v>
+        <v>7</v>
       </c>
       <c r="Y8" t="n">
-        <v>13679630.68181818</v>
+        <v>497</v>
       </c>
       <c r="Z8" t="n">
-        <v>79.47159090909091</v>
+        <v>138000</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.452272727272728</v>
+        <v>48550000</v>
       </c>
       <c r="AB8" t="n">
-        <v>26.675</v>
+        <v>552</v>
       </c>
       <c r="AC8" t="n">
-        <v>183.4268701070172</v>
+        <v>10</v>
       </c>
       <c r="AD8" t="n">
-        <v>81.46288515406162</v>
+        <v>27.06296296296297</v>
       </c>
       <c r="AE8" t="n">
-        <v>75162.88545332663</v>
+        <v>183.7944444444445</v>
       </c>
       <c r="AF8" t="n">
-        <v>37413574.0995116</v>
+        <v>83.08148148148149</v>
       </c>
       <c r="AG8" t="n">
-        <v>83.974651655534</v>
+        <v>79274.07407407407</v>
       </c>
       <c r="AH8" t="n">
-        <v>2.64404941463765</v>
+        <v>47881990.74074074</v>
       </c>
       <c r="AI8" t="n">
-        <v>24.23134968102073</v>
+        <v>85.68703703703704</v>
       </c>
       <c r="AJ8" t="n">
-        <v>184.7684576023392</v>
+        <v>3.170370370370371</v>
       </c>
       <c r="AK8" t="n">
-        <v>73.57535220627327</v>
+        <v>24.84545454545455</v>
       </c>
       <c r="AL8" t="n">
-        <v>24095.95295055821</v>
+        <v>185.8077922077922</v>
       </c>
       <c r="AM8" t="n">
-        <v>10361317.20162148</v>
+        <v>76.0987012987013</v>
       </c>
       <c r="AN8" t="n">
-        <v>78.25289074960128</v>
+        <v>27401.2987012987</v>
       </c>
       <c r="AO8" t="n">
-        <v>1.482406299840511</v>
-      </c>
-      <c r="AP8" t="inlineStr">
+        <v>13663733.76623377</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>79.44805194805194</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>1.464935064935065</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>26.72867647058824</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>183.1940935562259</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>81.25571895424837</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>73218.99195575666</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>34938630.56707726</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>83.71552497067204</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>2.584724317077258</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>24.2968671679198</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>185.0925229741019</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>73.74845446950711</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>24291.47869674185</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>10600596.2823726</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>78.23057644110277</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>1.49937343358396</v>
+      </c>
+      <c r="BF8" t="inlineStr">
         <is>
           <t>UgdQz0fK</t>
         </is>
       </c>
-      <c r="AQ8" t="inlineStr">
+      <c r="BG8" t="inlineStr">
         <is>
           <t>KUx4Q7x1</t>
         </is>
@@ -1758,95 +2174,143 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>26.66814574314574</v>
+        <v>24.97222222222222</v>
       </c>
       <c r="O9" t="n">
-        <v>185.6328282828283</v>
+        <v>189.1944444444445</v>
       </c>
       <c r="P9" t="n">
-        <v>69.95238095238095</v>
+        <v>2</v>
       </c>
       <c r="Q9" t="n">
-        <v>16681.49350649351</v>
+        <v>138</v>
       </c>
       <c r="R9" t="n">
-        <v>1926691.919191919</v>
+        <v>29666.66666666667</v>
       </c>
       <c r="S9" t="n">
-        <v>72.3401875901876</v>
+        <v>3933333.333333333</v>
       </c>
       <c r="T9" t="n">
+        <v>147</v>
+      </c>
+      <c r="U9" t="n">
+        <v>2</v>
+      </c>
+      <c r="V9" t="n">
+        <v>29.33333333333333</v>
+      </c>
+      <c r="W9" t="n">
+        <v>178.1111111111111</v>
+      </c>
+      <c r="X9" t="n">
+        <v>2.666666666666667</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>199.3333333333333</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>85666.66666666667</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>14816666.66666667</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>199.3333333333333</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>3.666666666666667</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>26.76435185185185</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>185.5564814814815</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>69.94444444444444</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>16704.16666666667</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>1906898.148148148</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>72.24537037037037</v>
+      </c>
+      <c r="AJ9" t="n">
         <v>1</v>
       </c>
-      <c r="U9" t="n">
-        <v>26.98412698412698</v>
-      </c>
-      <c r="V9" t="n">
-        <v>186.3702741702742</v>
-      </c>
-      <c r="W9" t="n">
-        <v>74.8975468975469</v>
-      </c>
-      <c r="X9" t="n">
-        <v>27718.47041847042</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>6582539.682539682</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>77.52539682539683</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>1.413131313131313</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>25.60353757063466</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>184.9785753202883</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>68.25622181748368</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>15618.43791673801</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>1839729.603511885</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>72.59229777341906</v>
-      </c>
-      <c r="AH9" t="n">
+      <c r="AK9" t="n">
+        <v>26.83333333333333</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>186.5060606060606</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>74.7878787878788</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>27319.69696969697</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>6433333.333333333</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>77.64999999999999</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>1.38939393939394</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>25.64857161018488</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>184.7527823181141</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>68.37299952780502</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>15767.80719915731</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>1865795.648541644</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>72.70027332824816</v>
+      </c>
+      <c r="AX9" t="n">
         <v>1</v>
       </c>
-      <c r="AI9" t="n">
-        <v>26.37341516316672</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>182.8920043379671</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>73.10748299319728</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>24930.5333727694</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>4181897.860593513</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>75.97586512866017</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>1.159124519372967</v>
-      </c>
-      <c r="AP9" t="inlineStr">
+      <c r="AY9" t="n">
+        <v>26.31970899470899</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>182.6566137566138</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>73.12539682539682</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>24962.43386243387</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>4186851.851851852</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>75.94285714285715</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>1.134920634920635</v>
+      </c>
+      <c r="BF9" t="inlineStr">
         <is>
           <t>hAcTWKKN</t>
         </is>
       </c>
-      <c r="AQ9" t="inlineStr">
+      <c r="BG9" t="inlineStr">
         <is>
           <t>IkCftsQm</t>
         </is>
@@ -1909,95 +2373,143 @@
         </is>
       </c>
       <c r="N10" t="n">
+        <v>23.78888888888889</v>
+      </c>
+      <c r="O10" t="n">
+        <v>183.475</v>
+      </c>
+      <c r="P10" t="n">
+        <v>5.333333333333333</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>393.1666666666667</v>
+      </c>
+      <c r="R10" t="n">
+        <v>185333.3333333333</v>
+      </c>
+      <c r="S10" t="n">
+        <v>54050000</v>
+      </c>
+      <c r="T10" t="n">
+        <v>423.1666666666667</v>
+      </c>
+      <c r="U10" t="n">
+        <v>8</v>
+      </c>
+      <c r="V10" t="n">
+        <v>27.12777777777778</v>
+      </c>
+      <c r="W10" t="n">
+        <v>185.1944444444445</v>
+      </c>
+      <c r="X10" t="n">
+        <v>2.666666666666667</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>192.3333333333333</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>56333.33333333334</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>9333333.333333334</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>199.1666666666667</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>2.666666666666667</v>
+      </c>
+      <c r="AD10" t="n">
         <v>24.70833333333333</v>
       </c>
-      <c r="O10" t="n">
+      <c r="AE10" t="n">
         <v>184.7083333333333</v>
       </c>
-      <c r="P10" t="n">
+      <c r="AF10" t="n">
         <v>75.2986111111111</v>
       </c>
-      <c r="Q10" t="n">
+      <c r="AG10" t="n">
         <v>36312.5</v>
       </c>
-      <c r="R10" t="n">
+      <c r="AH10" t="n">
         <v>10284953.7037037</v>
       </c>
-      <c r="S10" t="n">
+      <c r="AI10" t="n">
         <v>79.89814814814814</v>
       </c>
-      <c r="T10" t="n">
+      <c r="AJ10" t="n">
         <v>1.418981481481481</v>
       </c>
-      <c r="U10" t="n">
+      <c r="AK10" t="n">
         <v>26.98051948051948</v>
       </c>
-      <c r="V10" t="n">
+      <c r="AL10" t="n">
         <v>183.7805194805195</v>
       </c>
-      <c r="W10" t="n">
+      <c r="AM10" t="n">
         <v>74.43636363636365</v>
       </c>
-      <c r="X10" t="n">
+      <c r="AN10" t="n">
         <v>23588.31168831169</v>
       </c>
-      <c r="Y10" t="n">
+      <c r="AO10" t="n">
         <v>6014415.584415585</v>
       </c>
-      <c r="Z10" t="n">
+      <c r="AP10" t="n">
         <v>76.79350649350648</v>
       </c>
-      <c r="AA10" t="n">
+      <c r="AQ10" t="n">
         <v>1.094805194805195</v>
       </c>
-      <c r="AB10" t="n">
+      <c r="AR10" t="n">
         <v>24.70891265597148</v>
       </c>
-      <c r="AC10" t="n">
+      <c r="AS10" t="n">
         <v>184.8741501145913</v>
       </c>
-      <c r="AD10" t="n">
+      <c r="AT10" t="n">
         <v>73.08691325014854</v>
       </c>
-      <c r="AE10" t="n">
+      <c r="AU10" t="n">
         <v>32352.28333757745</v>
       </c>
-      <c r="AF10" t="n">
+      <c r="AV10" t="n">
         <v>7859812.515915456</v>
       </c>
-      <c r="AG10" t="n">
+      <c r="AW10" t="n">
         <v>78.21184428316782</v>
       </c>
-      <c r="AH10" t="n">
+      <c r="AX10" t="n">
         <v>1.363718062982769</v>
       </c>
-      <c r="AI10" t="n">
+      <c r="AY10" t="n">
         <v>24.60253992311855</v>
       </c>
-      <c r="AJ10" t="n">
+      <c r="AZ10" t="n">
         <v>186.3206916217704</v>
       </c>
-      <c r="AK10" t="n">
+      <c r="BA10" t="n">
         <v>70.48234358718177</v>
       </c>
-      <c r="AL10" t="n">
+      <c r="BB10" t="n">
         <v>19202.79231864717</v>
       </c>
-      <c r="AM10" t="n">
+      <c r="BC10" t="n">
         <v>3470618.297107345</v>
       </c>
-      <c r="AN10" t="n">
+      <c r="BD10" t="n">
         <v>76.51956917986665</v>
       </c>
-      <c r="AO10" t="n">
+      <c r="BE10" t="n">
         <v>1</v>
       </c>
-      <c r="AP10" t="inlineStr">
+      <c r="BF10" t="inlineStr">
         <is>
           <t>8f6APkLc</t>
         </is>
       </c>
-      <c r="AQ10" t="inlineStr">
+      <c r="BG10" t="inlineStr">
         <is>
           <t>YZPE6Sx7</t>
         </is>
@@ -2060,95 +2572,143 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>27.55238095238095</v>
+        <v>26.5</v>
       </c>
       <c r="O11" t="n">
-        <v>183.3444444444445</v>
+        <v>185</v>
       </c>
       <c r="P11" t="n">
-        <v>74.82380952380952</v>
+        <v>1</v>
       </c>
       <c r="Q11" t="n">
-        <v>25260.31746031746</v>
+        <v>76</v>
       </c>
       <c r="R11" t="n">
-        <v>6533968.253968254</v>
+        <v>28750</v>
       </c>
       <c r="S11" t="n">
-        <v>76.96507936507938</v>
+        <v>9375000</v>
       </c>
       <c r="T11" t="n">
-        <v>1.409523809523809</v>
+        <v>78.25</v>
       </c>
       <c r="U11" t="n">
-        <v>26.11428571428572</v>
+        <v>1.25</v>
       </c>
       <c r="V11" t="n">
-        <v>184.8857142857143</v>
+        <v>21.71666666666667</v>
       </c>
       <c r="W11" t="n">
-        <v>75.48571428571428</v>
+        <v>182.0722222222222</v>
       </c>
       <c r="X11" t="n">
-        <v>24414.28571428571</v>
+        <v>4.166666666666667</v>
       </c>
       <c r="Y11" t="n">
-        <v>8282857.142857143</v>
+        <v>285</v>
       </c>
       <c r="Z11" t="n">
-        <v>77.91428571428573</v>
+        <v>53000</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.485714285714286</v>
+        <v>20891666.66666667</v>
       </c>
       <c r="AB11" t="n">
-        <v>25.68795690525014</v>
+        <v>321.5</v>
       </c>
       <c r="AC11" t="n">
-        <v>183.6457442307066</v>
+        <v>5.166666666666667</v>
       </c>
       <c r="AD11" t="n">
-        <v>71.26425479282622</v>
+        <v>27.62777777777778</v>
       </c>
       <c r="AE11" t="n">
-        <v>21373.32942746477</v>
+        <v>183.4851851851852</v>
       </c>
       <c r="AF11" t="n">
-        <v>3395399.334374898</v>
+        <v>74.84444444444445</v>
       </c>
       <c r="AG11" t="n">
-        <v>76.77254825375128</v>
+        <v>25270.37037037037</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.130812420662045</v>
+        <v>6512962.962962963</v>
       </c>
       <c r="AI11" t="n">
-        <v>25.63015457899407</v>
+        <v>76.90925925925926</v>
       </c>
       <c r="AJ11" t="n">
-        <v>183.4706953719703</v>
+        <v>1.411111111111111</v>
       </c>
       <c r="AK11" t="n">
-        <v>73.49740422484784</v>
+        <v>26.2</v>
       </c>
       <c r="AL11" t="n">
-        <v>22261.34046295864</v>
+        <v>185.0666666666667</v>
       </c>
       <c r="AM11" t="n">
-        <v>6100050.358816296</v>
+        <v>75.55</v>
       </c>
       <c r="AN11" t="n">
-        <v>77.37456218185214</v>
+        <v>24450</v>
       </c>
       <c r="AO11" t="n">
-        <v>1.202388735814692</v>
-      </c>
-      <c r="AP11" t="inlineStr">
+        <v>8165000</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>77.73333333333333</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>1.483333333333333</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>25.62007670691881</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>183.5708285866181</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>71.28448773448773</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>21546.66210982001</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>3453957.953596111</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>76.79813169286854</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>1.144677982835877</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>25.68445570447859</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>183.1868257600523</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>73.44987014638045</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>22246.92619229232</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>5921073.244705968</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>77.25582979187097</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>1.185395554102648</v>
+      </c>
+      <c r="BF11" t="inlineStr">
         <is>
           <t>0jdIgO6t</t>
         </is>
       </c>
-      <c r="AQ11" t="inlineStr">
+      <c r="BG11" t="inlineStr">
         <is>
           <t>M5BRZDsC</t>
         </is>
@@ -2211,95 +2771,143 @@
         </is>
       </c>
       <c r="N12" t="n">
+        <v>25.91944444444445</v>
+      </c>
+      <c r="O12" t="n">
+        <v>184.3472222222223</v>
+      </c>
+      <c r="P12" t="n">
+        <v>4.666666666666667</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>327</v>
+      </c>
+      <c r="R12" t="n">
+        <v>77333.33333333333</v>
+      </c>
+      <c r="S12" t="n">
+        <v>11062500</v>
+      </c>
+      <c r="T12" t="n">
+        <v>338.5</v>
+      </c>
+      <c r="U12" t="n">
+        <v>4.666666666666667</v>
+      </c>
+      <c r="V12" t="n">
+        <v>22.63888888888889</v>
+      </c>
+      <c r="W12" t="n">
+        <v>184.8055555555555</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1.666666666666667</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>127.1666666666667</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>68333.33333333333</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>39666666.66666666</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>140</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AD12" t="n">
         <v>25.79166666666667</v>
       </c>
-      <c r="O12" t="n">
+      <c r="AE12" t="n">
         <v>185.0416666666667</v>
       </c>
-      <c r="P12" t="n">
+      <c r="AF12" t="n">
         <v>73.70833333333333</v>
       </c>
-      <c r="Q12" t="n">
+      <c r="AG12" t="n">
         <v>22291.66666666667</v>
       </c>
-      <c r="R12" t="n">
+      <c r="AH12" t="n">
         <v>5350000</v>
       </c>
-      <c r="S12" t="n">
+      <c r="AI12" t="n">
         <v>76.91666666666667</v>
       </c>
-      <c r="T12" t="n">
+      <c r="AJ12" t="n">
         <v>1.125</v>
       </c>
-      <c r="U12" t="n">
-        <v>26.64285714285714</v>
-      </c>
-      <c r="V12" t="n">
-        <v>186.061038961039</v>
-      </c>
-      <c r="W12" t="n">
-        <v>81.98311688311686</v>
-      </c>
-      <c r="X12" t="n">
-        <v>57966.23376623377</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>37499350.64935065</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>84.12597402597403</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>2.611688311688312</v>
-      </c>
-      <c r="AB12" t="n">
+      <c r="AK12" t="n">
+        <v>26.64393939393939</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>186.1318181818182</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>81.99545454545454</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>58096.9696969697</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>37582575.75757576</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>84.10151515151516</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>2.607575757575757</v>
+      </c>
+      <c r="AR12" t="n">
         <v>24.81548711988782</v>
       </c>
-      <c r="AC12" t="n">
+      <c r="AS12" t="n">
         <v>184.1908611131853</v>
       </c>
-      <c r="AD12" t="n">
+      <c r="AT12" t="n">
         <v>72.5454978243291</v>
       </c>
-      <c r="AE12" t="n">
+      <c r="AU12" t="n">
         <v>21177.01909312369</v>
       </c>
-      <c r="AF12" t="n">
+      <c r="AV12" t="n">
         <v>4952682.416666826</v>
       </c>
-      <c r="AG12" t="n">
+      <c r="AW12" t="n">
         <v>76.55772420610985</v>
       </c>
-      <c r="AH12" t="n">
+      <c r="AX12" t="n">
         <v>1.158487278483961</v>
       </c>
-      <c r="AI12" t="n">
-        <v>24.94727735487788</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>184.0784915422379</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>77.85036907627624</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>43615.56955630182</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>22506707.10514287</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>82.89163811561654</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>1.89768881548875</v>
-      </c>
-      <c r="AP12" t="inlineStr">
+      <c r="AY12" t="n">
+        <v>25.00991881878609</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>184.1391925135632</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>77.96828773184609</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>44313.40257759022</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>22440364.6385397</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>82.86564129361612</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>1.912382983149573</v>
+      </c>
+      <c r="BF12" t="inlineStr">
         <is>
           <t>2VSFgl3c</t>
         </is>
       </c>
-      <c r="AQ12" t="inlineStr">
+      <c r="BG12" t="inlineStr">
         <is>
           <t>IkCftsQm</t>
         </is>
@@ -2362,95 +2970,143 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>25.86363636363637</v>
+        <v>24.59722222222222</v>
       </c>
       <c r="O13" t="n">
-        <v>183.4238095238095</v>
+        <v>183.0138888888889</v>
       </c>
       <c r="P13" t="n">
-        <v>80.54862914862915</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="Q13" t="n">
-        <v>57105.9163059163</v>
+        <v>241.1666666666667</v>
       </c>
       <c r="R13" t="n">
-        <v>30935786.43578643</v>
+        <v>142000</v>
       </c>
       <c r="S13" t="n">
-        <v>84.0806637806638</v>
+        <v>49450000</v>
       </c>
       <c r="T13" t="n">
-        <v>2.24040404040404</v>
+        <v>264.5</v>
       </c>
       <c r="U13" t="n">
-        <v>26.78730158730159</v>
+        <v>7</v>
       </c>
       <c r="V13" t="n">
-        <v>183.765873015873</v>
+        <v>26.25515873015873</v>
       </c>
       <c r="W13" t="n">
-        <v>76.15119047619048</v>
+        <v>185.6285714285715</v>
       </c>
       <c r="X13" t="n">
-        <v>26336.90476190476</v>
+        <v>5.5</v>
       </c>
       <c r="Y13" t="n">
-        <v>10731904.76190476</v>
+        <v>392.1666666666667</v>
       </c>
       <c r="Z13" t="n">
-        <v>78.68373015873014</v>
+        <v>104833.3333333333</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.619444444444445</v>
+        <v>25950000</v>
       </c>
       <c r="AB13" t="n">
-        <v>25.30528527200354</v>
+        <v>410.5</v>
       </c>
       <c r="AC13" t="n">
-        <v>184.6633464789425</v>
+        <v>6</v>
       </c>
       <c r="AD13" t="n">
-        <v>78.55534362867954</v>
+        <v>25.78030303030303</v>
       </c>
       <c r="AE13" t="n">
+        <v>183.4792929292929</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>80.53400673400672</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>56972.05387205387</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>31091750.84175084</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>84.12441077441078</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>2.235016835016835</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>26.75185185185185</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>183.9351851851851</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>76.23888888888889</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>26288.88888888889</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>10895555.55555556</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>78.81851851851852</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>1.618518518518519</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>25.3874161506708</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>184.7322375587662</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>78.60623423345946</v>
+      </c>
+      <c r="AU13" t="n">
         <v>52375.29741428735</v>
       </c>
-      <c r="AF13" t="n">
-        <v>24838828.53580029</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>82.33332104771732</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>1.96046181630547</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>26.78755273276358</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>183.3636766959748</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>74.21713048855905</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>23961.89683695405</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>6877269.306099807</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>76.81895202432959</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>1.387528604118993</v>
-      </c>
-      <c r="AP13" t="inlineStr">
+      <c r="AV13" t="n">
+        <v>24627070.791767</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>82.36804122233688</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>1.943455452356381</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>26.59272456503578</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>183.5692170148692</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>74.27505803375368</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>23933.80717934493</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>7083444.625232384</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>77.01341504287728</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>1.386899313501144</v>
+      </c>
+      <c r="BF13" t="inlineStr">
         <is>
           <t>4ljanukM</t>
         </is>
       </c>
-      <c r="AQ13" t="inlineStr">
+      <c r="BG13" t="inlineStr">
         <is>
           <t>YZPE6Sx7</t>
         </is>
@@ -2513,95 +3169,143 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>26.76926406926407</v>
+        <v>29.675</v>
       </c>
       <c r="O14" t="n">
-        <v>185.3191919191919</v>
+        <v>186.3472222222223</v>
       </c>
       <c r="P14" t="n">
-        <v>70.64227994227994</v>
+        <v>4.166666666666667</v>
       </c>
       <c r="Q14" t="n">
-        <v>17154.25685425686</v>
+        <v>273.3333333333333</v>
       </c>
       <c r="R14" t="n">
-        <v>2338008.658008658</v>
+        <v>57166.66666666666</v>
       </c>
       <c r="S14" t="n">
-        <v>73.57301587301588</v>
+        <v>3476666.666666667</v>
       </c>
       <c r="T14" t="n">
+        <v>282.8333333333333</v>
+      </c>
+      <c r="U14" t="n">
+        <v>4.166666666666667</v>
+      </c>
+      <c r="V14" t="n">
+        <v>23.78888888888889</v>
+      </c>
+      <c r="W14" t="n">
+        <v>183.475</v>
+      </c>
+      <c r="X14" t="n">
+        <v>5.333333333333333</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>393.1666666666667</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>185333.3333333333</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>54050000</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>423.1666666666667</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>26.78636363636364</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>185.2242424242424</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>70.61969696969697</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>17198.48484848485</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>2322121.212121212</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>73.48333333333333</v>
+      </c>
+      <c r="AJ14" t="n">
         <v>1</v>
       </c>
-      <c r="U14" t="n">
+      <c r="AK14" t="n">
         <v>24.70833333333333</v>
       </c>
-      <c r="V14" t="n">
+      <c r="AL14" t="n">
         <v>184.7083333333333</v>
       </c>
-      <c r="W14" t="n">
+      <c r="AM14" t="n">
         <v>75.2986111111111</v>
       </c>
-      <c r="X14" t="n">
+      <c r="AN14" t="n">
         <v>36312.5</v>
       </c>
-      <c r="Y14" t="n">
+      <c r="AO14" t="n">
         <v>10284953.7037037</v>
       </c>
-      <c r="Z14" t="n">
+      <c r="AP14" t="n">
         <v>79.89814814814814</v>
       </c>
-      <c r="AA14" t="n">
+      <c r="AQ14" t="n">
         <v>1.418981481481481</v>
       </c>
-      <c r="AB14" t="n">
-        <v>25.57589807852966</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>184.6525480367586</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>68.33454469507102</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>16058.14536340852</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>1786161.236424394</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>71.97422723475356</v>
-      </c>
-      <c r="AH14" t="n">
+      <c r="AR14" t="n">
+        <v>25.69819688109162</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>184.6735867446394</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>68.29381091617934</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>16059.06432748538</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>1761047.7582846</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>71.8646686159844</v>
+      </c>
+      <c r="AX14" t="n">
         <v>1</v>
       </c>
-      <c r="AI14" t="n">
+      <c r="AY14" t="n">
         <v>24.70891265597148</v>
       </c>
-      <c r="AJ14" t="n">
+      <c r="AZ14" t="n">
         <v>184.8741501145913</v>
       </c>
-      <c r="AK14" t="n">
+      <c r="BA14" t="n">
         <v>73.08691325014854</v>
       </c>
-      <c r="AL14" t="n">
+      <c r="BB14" t="n">
         <v>32352.28333757745</v>
       </c>
-      <c r="AM14" t="n">
+      <c r="BC14" t="n">
         <v>7859812.515915456</v>
       </c>
-      <c r="AN14" t="n">
+      <c r="BD14" t="n">
         <v>78.21184428316782</v>
       </c>
-      <c r="AO14" t="n">
+      <c r="BE14" t="n">
         <v>1.363718062982769</v>
       </c>
-      <c r="AP14" t="inlineStr">
+      <c r="BF14" t="inlineStr">
         <is>
           <t>0jdIgO6t</t>
         </is>
       </c>
-      <c r="AQ14" t="inlineStr">
+      <c r="BG14" t="inlineStr">
         <is>
           <t>f3ddUIXs</t>
         </is>
@@ -2664,95 +3368,143 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>24.8875</v>
+        <v>22.48095238095238</v>
       </c>
       <c r="O15" t="n">
-        <v>185.7181818181818</v>
+        <v>183.9246031746032</v>
       </c>
       <c r="P15" t="n">
-        <v>76.17727272727274</v>
+        <v>4.333333333333333</v>
       </c>
       <c r="Q15" t="n">
-        <v>27419.31818181818</v>
+        <v>303.5</v>
       </c>
       <c r="R15" t="n">
-        <v>13679630.68181818</v>
+        <v>77833.33333333333</v>
       </c>
       <c r="S15" t="n">
-        <v>79.47159090909091</v>
+        <v>20516666.66666667</v>
       </c>
       <c r="T15" t="n">
-        <v>1.452272727272728</v>
+        <v>339.5</v>
       </c>
       <c r="U15" t="n">
-        <v>26.66814574314574</v>
+        <v>5.166666666666667</v>
       </c>
       <c r="V15" t="n">
-        <v>185.6328282828283</v>
+        <v>24.97222222222222</v>
       </c>
       <c r="W15" t="n">
-        <v>69.95238095238095</v>
+        <v>189.1944444444445</v>
       </c>
       <c r="X15" t="n">
-        <v>16681.49350649351</v>
+        <v>2</v>
       </c>
       <c r="Y15" t="n">
-        <v>1926691.919191919</v>
+        <v>138</v>
       </c>
       <c r="Z15" t="n">
-        <v>72.3401875901876</v>
+        <v>29666.66666666667</v>
       </c>
       <c r="AA15" t="n">
+        <v>3933333.333333333</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>147</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>24.84545454545455</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>185.8077922077922</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>76.0987012987013</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>27401.2987012987</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>13663733.76623377</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>79.44805194805194</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>1.464935064935065</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>26.76435185185185</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>185.5564814814815</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>69.94444444444444</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>16704.16666666667</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>1906898.148148148</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>72.24537037037037</v>
+      </c>
+      <c r="AQ15" t="n">
         <v>1</v>
       </c>
-      <c r="AB15" t="n">
-        <v>24.23134968102073</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>184.7684576023392</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>73.57535220627327</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>24095.95295055821</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>10361317.20162148</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>78.25289074960128</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>1.482406299840511</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>25.60353757063466</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>184.9785753202883</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>68.25622181748368</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>15618.43791673801</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>1839729.603511885</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>72.59229777341906</v>
-      </c>
-      <c r="AO15" t="n">
+      <c r="AR15" t="n">
+        <v>24.2968671679198</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>185.0925229741019</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>73.74845446950711</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>24291.47869674185</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>10600596.2823726</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>78.23057644110277</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>1.49937343358396</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>25.64857161018488</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>184.7527823181141</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>68.37299952780502</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>15767.80719915731</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>1865795.648541644</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>72.70027332824816</v>
+      </c>
+      <c r="BE15" t="n">
         <v>1</v>
       </c>
-      <c r="AP15" t="inlineStr">
+      <c r="BF15" t="inlineStr">
         <is>
           <t>GzfvcwRj</t>
         </is>
       </c>
-      <c r="AQ15" t="inlineStr">
+      <c r="BG15" t="inlineStr">
         <is>
           <t>A15eUM4C</t>
         </is>
@@ -2815,95 +3567,143 @@
         </is>
       </c>
       <c r="N16" t="n">
+        <v>27.12777777777778</v>
+      </c>
+      <c r="O16" t="n">
+        <v>185.1944444444445</v>
+      </c>
+      <c r="P16" t="n">
+        <v>2.666666666666667</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>192.3333333333333</v>
+      </c>
+      <c r="R16" t="n">
+        <v>56333.33333333334</v>
+      </c>
+      <c r="S16" t="n">
+        <v>9333333.333333334</v>
+      </c>
+      <c r="T16" t="n">
+        <v>199.1666666666667</v>
+      </c>
+      <c r="U16" t="n">
+        <v>2.666666666666667</v>
+      </c>
+      <c r="V16" t="n">
+        <v>27.25</v>
+      </c>
+      <c r="W16" t="n">
+        <v>181.5</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>126</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>140000</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>59000000</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>129</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AD16" t="n">
         <v>26.98051948051948</v>
       </c>
-      <c r="O16" t="n">
+      <c r="AE16" t="n">
         <v>183.7805194805195</v>
       </c>
-      <c r="P16" t="n">
+      <c r="AF16" t="n">
         <v>74.43636363636365</v>
       </c>
-      <c r="Q16" t="n">
+      <c r="AG16" t="n">
         <v>23588.31168831169</v>
       </c>
-      <c r="R16" t="n">
+      <c r="AH16" t="n">
         <v>6014415.584415585</v>
       </c>
-      <c r="S16" t="n">
+      <c r="AI16" t="n">
         <v>76.79350649350648</v>
       </c>
-      <c r="T16" t="n">
+      <c r="AJ16" t="n">
         <v>1.094805194805195</v>
       </c>
-      <c r="U16" t="n">
-        <v>26.40674603174603</v>
-      </c>
-      <c r="V16" t="n">
-        <v>184.3571428571429</v>
-      </c>
-      <c r="W16" t="n">
-        <v>83.76865079365079</v>
-      </c>
-      <c r="X16" t="n">
-        <v>99564.28571428571</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>50273214.28571428</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>85.91904761904763</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>3.064285714285715</v>
-      </c>
-      <c r="AB16" t="n">
+      <c r="AK16" t="n">
+        <v>26.39120370370371</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>184.3125</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>84.12592592592593</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>102408.3333333333</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>53464583.33333334</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>86.15555555555557</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>3.158333333333334</v>
+      </c>
+      <c r="AR16" t="n">
         <v>24.60253992311855</v>
       </c>
-      <c r="AC16" t="n">
+      <c r="AS16" t="n">
         <v>186.3206916217704</v>
       </c>
-      <c r="AD16" t="n">
+      <c r="AT16" t="n">
         <v>70.48234358718177</v>
       </c>
-      <c r="AE16" t="n">
+      <c r="AU16" t="n">
         <v>19202.79231864717</v>
       </c>
-      <c r="AF16" t="n">
+      <c r="AV16" t="n">
         <v>3470618.297107345</v>
       </c>
-      <c r="AG16" t="n">
+      <c r="AW16" t="n">
         <v>76.51956917986665</v>
       </c>
-      <c r="AH16" t="n">
+      <c r="AX16" t="n">
         <v>1</v>
       </c>
-      <c r="AI16" t="n">
-        <v>24.56634355496585</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>180.7619096761511</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>80.84288294265075</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>82188.14560912084</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>39435822.47592019</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>84.59387316330042</v>
-      </c>
-      <c r="AO16" t="n">
-        <v>2.302458351761757</v>
-      </c>
-      <c r="AP16" t="inlineStr">
+      <c r="AY16" t="n">
+        <v>24.50439263424668</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>180.6530668407714</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>80.45989343105664</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>79589.1732131449</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>36725973.98608566</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>84.37939245873788</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>2.21641498704745</v>
+      </c>
+      <c r="BF16" t="inlineStr">
         <is>
           <t>4fuCGs9P</t>
         </is>
       </c>
-      <c r="AQ16" t="inlineStr">
+      <c r="BG16" t="inlineStr">
         <is>
           <t>A15eUM4C</t>
         </is>
@@ -2966,95 +3766,143 @@
         </is>
       </c>
       <c r="N17" t="n">
+        <v>27.16666666666667</v>
+      </c>
+      <c r="O17" t="n">
+        <v>186.8416666666667</v>
+      </c>
+      <c r="P17" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>283.5</v>
+      </c>
+      <c r="R17" t="n">
+        <v>66000</v>
+      </c>
+      <c r="S17" t="n">
+        <v>9675000</v>
+      </c>
+      <c r="T17" t="n">
+        <v>295.1666666666667</v>
+      </c>
+      <c r="U17" t="n">
+        <v>4.666666666666667</v>
+      </c>
+      <c r="V17" t="n">
+        <v>22.15555555555556</v>
+      </c>
+      <c r="W17" t="n">
+        <v>184.6444444444444</v>
+      </c>
+      <c r="X17" t="n">
+        <v>5.666666666666667</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>408.3333333333333</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>223333.3333333333</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>91900000</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>460.6666666666667</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>8.166666666666666</v>
+      </c>
+      <c r="AD17" t="n">
         <v>28.33888888888889</v>
       </c>
-      <c r="O17" t="n">
+      <c r="AE17" t="n">
         <v>185.2921296296296</v>
       </c>
-      <c r="P17" t="n">
+      <c r="AF17" t="n">
         <v>71.6962962962963</v>
       </c>
-      <c r="Q17" t="n">
+      <c r="AG17" t="n">
         <v>17048.14814814815</v>
       </c>
-      <c r="R17" t="n">
+      <c r="AH17" t="n">
         <v>2222615.740740741</v>
       </c>
-      <c r="S17" t="n">
+      <c r="AI17" t="n">
         <v>73.5712962962963</v>
       </c>
-      <c r="T17" t="n">
+      <c r="AJ17" t="n">
         <v>1</v>
       </c>
-      <c r="U17" t="n">
-        <v>26.92539682539682</v>
-      </c>
-      <c r="V17" t="n">
-        <v>183.7380952380952</v>
-      </c>
-      <c r="W17" t="n">
-        <v>82.85555555555557</v>
-      </c>
-      <c r="X17" t="n">
-        <v>77163.49206349207</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>46305992.06349206</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>85.61746031746031</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>3.103174603174603</v>
-      </c>
-      <c r="AB17" t="n">
+      <c r="AK17" t="n">
+        <v>27.06296296296297</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>183.7944444444445</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>83.08148148148149</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>79274.07407407407</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>47881990.74074074</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>85.68703703703704</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>3.170370370370371</v>
+      </c>
+      <c r="AR17" t="n">
         <v>25.40532515300317</v>
       </c>
-      <c r="AC17" t="n">
+      <c r="AS17" t="n">
         <v>185.6896861308626</v>
       </c>
-      <c r="AD17" t="n">
+      <c r="AT17" t="n">
         <v>68.42912900652838</v>
       </c>
-      <c r="AE17" t="n">
+      <c r="AU17" t="n">
         <v>15078.88310519889</v>
       </c>
-      <c r="AF17" t="n">
+      <c r="AV17" t="n">
         <v>1804867.324797665</v>
       </c>
-      <c r="AG17" t="n">
+      <c r="AW17" t="n">
         <v>74.38585339668931</v>
       </c>
-      <c r="AH17" t="n">
+      <c r="AX17" t="n">
         <v>1</v>
       </c>
-      <c r="AI17" t="n">
-        <v>26.675</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>183.4268701070172</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>81.46288515406162</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>75162.88545332663</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>37413574.0995116</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>83.974651655534</v>
-      </c>
-      <c r="AO17" t="n">
-        <v>2.64404941463765</v>
-      </c>
-      <c r="AP17" t="inlineStr">
+      <c r="AY17" t="n">
+        <v>26.72867647058824</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>183.1940935562259</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>81.25571895424837</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>73218.99195575666</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>34938630.56707726</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>83.71552497067204</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>2.584724317077258</v>
+      </c>
+      <c r="BF17" t="inlineStr">
         <is>
           <t>8f6APkLc</t>
         </is>
       </c>
-      <c r="AQ17" t="inlineStr">
+      <c r="BG17" t="inlineStr">
         <is>
           <t>K6A2elS9</t>
         </is>
@@ -3117,95 +3965,143 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>26.98412698412698</v>
+        <v>29.33333333333333</v>
       </c>
       <c r="O18" t="n">
-        <v>186.3702741702742</v>
+        <v>178.1111111111111</v>
       </c>
       <c r="P18" t="n">
-        <v>74.8975468975469</v>
+        <v>2.666666666666667</v>
       </c>
       <c r="Q18" t="n">
-        <v>27718.47041847042</v>
+        <v>199.3333333333333</v>
       </c>
       <c r="R18" t="n">
-        <v>6582539.682539682</v>
+        <v>85666.66666666667</v>
       </c>
       <c r="S18" t="n">
-        <v>77.52539682539683</v>
+        <v>14816666.66666667</v>
       </c>
       <c r="T18" t="n">
-        <v>1.413131313131313</v>
+        <v>199.3333333333333</v>
       </c>
       <c r="U18" t="n">
+        <v>3.666666666666667</v>
+      </c>
+      <c r="V18" t="n">
+        <v>19.72222222222222</v>
+      </c>
+      <c r="W18" t="n">
+        <v>177.1111111111111</v>
+      </c>
+      <c r="X18" t="n">
+        <v>1.833333333333333</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>113.6666666666667</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>13666.66666666667</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>3991666.666666667</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>143.3333333333333</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>2.166666666666667</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>26.83333333333333</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>186.5060606060606</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>74.7878787878788</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>27319.69696969697</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>6433333.333333333</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>77.64999999999999</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>1.38939393939394</v>
+      </c>
+      <c r="AK18" t="n">
         <v>24.52777777777778</v>
       </c>
-      <c r="V18" t="n">
+      <c r="AL18" t="n">
         <v>185.337962962963</v>
       </c>
-      <c r="W18" t="n">
+      <c r="AM18" t="n">
         <v>76.72685185185185</v>
       </c>
-      <c r="X18" t="n">
+      <c r="AN18" t="n">
         <v>34518.51851851852</v>
       </c>
-      <c r="Y18" t="n">
+      <c r="AO18" t="n">
         <v>15101157.40740741</v>
       </c>
-      <c r="Z18" t="n">
+      <c r="AP18" t="n">
         <v>81.68518518518518</v>
       </c>
-      <c r="AA18" t="n">
+      <c r="AQ18" t="n">
         <v>1.671296296296297</v>
       </c>
-      <c r="AB18" t="n">
-        <v>26.37341516316672</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>182.8920043379671</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>73.10748299319728</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>24930.5333727694</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>4181897.860593513</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>75.97586512866017</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>1.159124519372967</v>
-      </c>
-      <c r="AI18" t="n">
+      <c r="AR18" t="n">
+        <v>26.31970899470899</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>182.6566137566138</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>73.12539682539682</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>24962.43386243387</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>4186851.851851852</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>75.94285714285715</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>1.134920634920635</v>
+      </c>
+      <c r="AY18" t="n">
         <v>22.60779220779221</v>
       </c>
-      <c r="AJ18" t="n">
+      <c r="AZ18" t="n">
         <v>184.7599404355043</v>
       </c>
-      <c r="AK18" t="n">
+      <c r="BA18" t="n">
         <v>72.78391758617323</v>
       </c>
-      <c r="AL18" t="n">
+      <c r="BB18" t="n">
         <v>25675.59971356964</v>
       </c>
-      <c r="AM18" t="n">
+      <c r="BC18" t="n">
         <v>8849931.500829998</v>
       </c>
-      <c r="AN18" t="n">
+      <c r="BD18" t="n">
         <v>80.94579468150896</v>
       </c>
-      <c r="AO18" t="n">
+      <c r="BE18" t="n">
         <v>1.391914852065228</v>
       </c>
-      <c r="AP18" t="inlineStr">
+      <c r="BF18" t="inlineStr">
         <is>
           <t>hpYJ6izc</t>
         </is>
       </c>
-      <c r="AQ18" t="inlineStr">
+      <c r="BG18" t="inlineStr">
         <is>
           <t>K6A2elS9</t>
         </is>
@@ -3268,95 +4164,143 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>26.81428571428571</v>
+        <v>24.63888888888889</v>
       </c>
       <c r="O19" t="n">
-        <v>187.2571428571428</v>
+        <v>187.6388888888889</v>
       </c>
       <c r="P19" t="n">
-        <v>72.52857142857142</v>
+        <v>3</v>
       </c>
       <c r="Q19" t="n">
-        <v>22128.57142857143</v>
+        <v>203</v>
       </c>
       <c r="R19" t="n">
-        <v>3170000</v>
+        <v>52166.66666666666</v>
       </c>
       <c r="S19" t="n">
-        <v>74.31428571428572</v>
+        <v>5545833.333333333</v>
       </c>
       <c r="T19" t="n">
-        <v>1.014285714285714</v>
+        <v>216</v>
       </c>
       <c r="U19" t="n">
-        <v>27.52539682539683</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="V19" t="n">
-        <v>186.084126984127</v>
+        <v>25.59920634920636</v>
       </c>
       <c r="W19" t="n">
-        <v>74.82063492063492</v>
+        <v>182.4007936507936</v>
       </c>
       <c r="X19" t="n">
-        <v>30061.90476190476</v>
+        <v>6.5</v>
       </c>
       <c r="Y19" t="n">
-        <v>7427777.777777778</v>
+        <v>479.6666666666667</v>
       </c>
       <c r="Z19" t="n">
-        <v>78.15396825396826</v>
+        <v>164833.3333333333</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.641269841269841</v>
+        <v>39233333.33333334</v>
       </c>
       <c r="AB19" t="n">
-        <v>25.78788819875777</v>
+        <v>506.6666666666667</v>
       </c>
       <c r="AC19" t="n">
-        <v>185.0847826086956</v>
+        <v>9.666666666666666</v>
       </c>
       <c r="AD19" t="n">
-        <v>69.52639751552795</v>
+        <v>26.85</v>
       </c>
       <c r="AE19" t="n">
-        <v>19842.85714285714</v>
+        <v>187.2833333333333</v>
       </c>
       <c r="AF19" t="n">
-        <v>2179208.074534161</v>
+        <v>72.61666666666667</v>
       </c>
       <c r="AG19" t="n">
-        <v>72.36211180124224</v>
+        <v>22200</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.037267080745342</v>
+        <v>3205000</v>
       </c>
       <c r="AI19" t="n">
-        <v>24.26210765007758</v>
+        <v>74.39999999999999</v>
       </c>
       <c r="AJ19" t="n">
-        <v>186.1579424752357</v>
+        <v>1.016666666666667</v>
       </c>
       <c r="AK19" t="n">
-        <v>71.20689819787563</v>
+        <v>27.5462962962963</v>
       </c>
       <c r="AL19" t="n">
-        <v>23972.69363885905</v>
+        <v>186.0148148148148</v>
       </c>
       <c r="AM19" t="n">
-        <v>5652869.077455544</v>
+        <v>75.05740740740741</v>
       </c>
       <c r="AN19" t="n">
-        <v>77.70173051676811</v>
+        <v>30288.88888888889</v>
       </c>
       <c r="AO19" t="n">
-        <v>1.218701515693997</v>
-      </c>
-      <c r="AP19" t="inlineStr">
+        <v>7644074.074074075</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>78.47962962962963</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>1.664814814814815</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>25.78152173913044</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>184.888768115942</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>69.50543478260869</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>19889.13043478261</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>2174655.797101449</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>72.25579710144928</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>1.043478260869565</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>24.18357003620162</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>186.0842662211083</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>71.1302701197438</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>24001.47591200222</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>5547513.923698135</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>77.74090782511836</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>1.188485101642996</v>
+      </c>
+      <c r="BF19" t="inlineStr">
         <is>
           <t>4ljanukM</t>
         </is>
       </c>
-      <c r="AQ19" t="inlineStr">
+      <c r="BG19" t="inlineStr">
         <is>
           <t>KUx4Q7x1</t>
         </is>

--- a/data/germany/p6_deployment/data_preparation/df_filled.xlsx
+++ b/data/germany/p6_deployment/data_preparation/df_filled.xlsx
@@ -735,7 +735,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">dingert c 
+          <t xml:space="preserve">jollenbeck m 
   ger </t>
         </is>
       </c>
@@ -805,28 +805,28 @@
         <v>5</v>
       </c>
       <c r="V2" t="n">
-        <v>27.33333333333333</v>
+        <v>27</v>
       </c>
       <c r="W2" t="n">
-        <v>187.1666666666667</v>
+        <v>186.75</v>
       </c>
       <c r="X2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Y2" t="n">
-        <v>401</v>
+        <v>535</v>
       </c>
       <c r="Z2" t="n">
-        <v>80000</v>
+        <v>111000</v>
       </c>
       <c r="AA2" t="n">
-        <v>7210000</v>
+        <v>9810000</v>
       </c>
       <c r="AB2" t="n">
-        <v>420</v>
+        <v>559</v>
       </c>
       <c r="AC2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AD2" t="n">
         <v>26.64393939393939</v>
@@ -980,52 +980,52 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>23.5</v>
+        <v>22.8</v>
       </c>
       <c r="O3" t="n">
-        <v>182.8333333333333</v>
+        <v>183.4</v>
       </c>
       <c r="P3" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>345</v>
+      </c>
+      <c r="R3" t="n">
+        <v>62000</v>
+      </c>
+      <c r="S3" t="n">
+        <v>21225000</v>
+      </c>
+      <c r="T3" t="n">
+        <v>387</v>
+      </c>
+      <c r="U3" t="n">
         <v>6</v>
       </c>
-      <c r="Q3" t="n">
-        <v>424</v>
-      </c>
-      <c r="R3" t="n">
-        <v>96000</v>
-      </c>
-      <c r="S3" t="n">
-        <v>39725000</v>
-      </c>
-      <c r="T3" t="n">
-        <v>466</v>
-      </c>
-      <c r="U3" t="n">
-        <v>8</v>
-      </c>
       <c r="V3" t="n">
-        <v>24.66666666666667</v>
+        <v>25</v>
       </c>
       <c r="W3" t="n">
-        <v>189.6666666666667</v>
+        <v>186</v>
       </c>
       <c r="X3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Y3" t="n">
-        <v>204</v>
+        <v>279</v>
       </c>
       <c r="Z3" t="n">
-        <v>53000</v>
+        <v>80000</v>
       </c>
       <c r="AA3" t="n">
-        <v>5100000</v>
+        <v>12100000</v>
       </c>
       <c r="AB3" t="n">
-        <v>215</v>
+        <v>294</v>
       </c>
       <c r="AC3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AD3" t="n">
         <v>26.2</v>
@@ -1378,28 +1378,28 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>26</v>
+        <v>23.66666666666667</v>
       </c>
       <c r="O5" t="n">
-        <v>185.5</v>
+        <v>186</v>
       </c>
       <c r="P5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q5" t="n">
-        <v>283</v>
+        <v>210</v>
       </c>
       <c r="R5" t="n">
-        <v>68000</v>
+        <v>46000</v>
       </c>
       <c r="S5" t="n">
-        <v>17900000</v>
+        <v>16400000</v>
       </c>
       <c r="T5" t="n">
-        <v>298</v>
+        <v>225</v>
       </c>
       <c r="U5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="V5" t="n">
         <v>25.83333333333333</v>
@@ -1447,22 +1447,22 @@
         <v>1.618518518518519</v>
       </c>
       <c r="AK5" t="n">
-        <v>25.79166666666667</v>
+        <v>25.9375</v>
       </c>
       <c r="AL5" t="n">
-        <v>185.0416666666667</v>
+        <v>185</v>
       </c>
       <c r="AM5" t="n">
-        <v>73.70833333333333</v>
+        <v>73.75</v>
       </c>
       <c r="AN5" t="n">
-        <v>22291.66666666667</v>
+        <v>22562.5</v>
       </c>
       <c r="AO5" t="n">
         <v>5350000</v>
       </c>
       <c r="AP5" t="n">
-        <v>76.91666666666667</v>
+        <v>76.75</v>
       </c>
       <c r="AQ5" t="n">
         <v>1.125</v>
@@ -1489,25 +1489,25 @@
         <v>1.386899313501144</v>
       </c>
       <c r="AY5" t="n">
-        <v>24.81548711988782</v>
+        <v>24.80746224592974</v>
       </c>
       <c r="AZ5" t="n">
-        <v>184.1908611131853</v>
+        <v>184.4575197835647</v>
       </c>
       <c r="BA5" t="n">
-        <v>72.5454978243291</v>
+        <v>72.56823231020213</v>
       </c>
       <c r="BB5" t="n">
-        <v>21177.01909312369</v>
+        <v>21153.49197228067</v>
       </c>
       <c r="BC5" t="n">
-        <v>4952682.416666826</v>
+        <v>4947637.061868872</v>
       </c>
       <c r="BD5" t="n">
-        <v>76.55772420610985</v>
+        <v>76.54461763440091</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.158487278483961</v>
+        <v>1.131871521867652</v>
       </c>
       <c r="BF5" t="inlineStr">
         <is>
@@ -1577,52 +1577,52 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>27.8</v>
+        <v>27.33333333333333</v>
       </c>
       <c r="O6" t="n">
-        <v>182.8</v>
+        <v>183</v>
       </c>
       <c r="P6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q6" t="n">
-        <v>375</v>
+        <v>447</v>
       </c>
       <c r="R6" t="n">
-        <v>151000</v>
+        <v>174000</v>
       </c>
       <c r="S6" t="n">
-        <v>31900000</v>
+        <v>35200000</v>
       </c>
       <c r="T6" t="n">
-        <v>384</v>
+        <v>462</v>
       </c>
       <c r="U6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V6" t="n">
-        <v>23.5</v>
+        <v>25.33333333333333</v>
       </c>
       <c r="W6" t="n">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="X6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y6" t="n">
-        <v>133</v>
+        <v>208</v>
       </c>
       <c r="Z6" t="n">
-        <v>29000</v>
+        <v>52000</v>
       </c>
       <c r="AA6" t="n">
-        <v>2975000</v>
+        <v>7875000</v>
       </c>
       <c r="AB6" t="n">
-        <v>144</v>
+        <v>219</v>
       </c>
       <c r="AC6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AD6" t="n">
         <v>27.5462962962963</v>
@@ -1646,22 +1646,22 @@
         <v>1.664814814814815</v>
       </c>
       <c r="AK6" t="n">
-        <v>28.33888888888889</v>
+        <v>28.36666666666666</v>
       </c>
       <c r="AL6" t="n">
-        <v>185.2921296296296</v>
+        <v>185.4105555555556</v>
       </c>
       <c r="AM6" t="n">
-        <v>71.6962962962963</v>
+        <v>71.77555555555554</v>
       </c>
       <c r="AN6" t="n">
-        <v>17048.14814814815</v>
+        <v>16977.77777777778</v>
       </c>
       <c r="AO6" t="n">
-        <v>2222615.740740741</v>
+        <v>2226638.888888889</v>
       </c>
       <c r="AP6" t="n">
-        <v>73.5712962962963</v>
+        <v>73.58555555555556</v>
       </c>
       <c r="AQ6" t="n">
         <v>1</v>
@@ -1688,22 +1688,22 @@
         <v>1.188485101642996</v>
       </c>
       <c r="AY6" t="n">
-        <v>25.40532515300317</v>
+        <v>25.59052640399389</v>
       </c>
       <c r="AZ6" t="n">
-        <v>185.6896861308626</v>
+        <v>185.9124769565946</v>
       </c>
       <c r="BA6" t="n">
-        <v>68.42912900652838</v>
+        <v>68.54967011545959</v>
       </c>
       <c r="BB6" t="n">
-        <v>15078.88310519889</v>
+        <v>15297.91264233989</v>
       </c>
       <c r="BC6" t="n">
-        <v>1804867.324797665</v>
+        <v>1801511.87893061</v>
       </c>
       <c r="BD6" t="n">
-        <v>74.38585339668931</v>
+        <v>74.26388778633361</v>
       </c>
       <c r="BE6" t="n">
         <v>1</v>
@@ -1776,52 +1776,52 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="O7" t="n">
-        <v>183</v>
+        <v>185.5</v>
       </c>
       <c r="P7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q7" t="n">
-        <v>75</v>
+        <v>148</v>
       </c>
       <c r="R7" t="n">
-        <v>26000</v>
+        <v>51000</v>
       </c>
       <c r="S7" t="n">
-        <v>4600000</v>
+        <v>7100000</v>
       </c>
       <c r="T7" t="n">
-        <v>75</v>
+        <v>148</v>
       </c>
       <c r="U7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V7" t="n">
-        <v>25.75</v>
+        <v>24.25</v>
       </c>
       <c r="W7" t="n">
-        <v>180.75</v>
+        <v>182</v>
       </c>
       <c r="X7" t="n">
         <v>4</v>
       </c>
       <c r="Y7" t="n">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="Z7" t="n">
-        <v>192000</v>
+        <v>200000</v>
       </c>
       <c r="AA7" t="n">
-        <v>71500000</v>
+        <v>90000000</v>
       </c>
       <c r="AB7" t="n">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="AC7" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AD7" t="n">
         <v>27.62777777777778</v>
@@ -1975,52 +1975,52 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>22.4</v>
+        <v>22.83333333333333</v>
       </c>
       <c r="O8" t="n">
-        <v>185</v>
+        <v>185.1666666666667</v>
       </c>
       <c r="P8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q8" t="n">
-        <v>382</v>
+        <v>464</v>
       </c>
       <c r="R8" t="n">
-        <v>255000</v>
+        <v>324000</v>
       </c>
       <c r="S8" t="n">
-        <v>188150000</v>
+        <v>224150000</v>
       </c>
       <c r="T8" t="n">
-        <v>420</v>
+        <v>505</v>
       </c>
       <c r="U8" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="V8" t="n">
-        <v>22.57142857142857</v>
+        <v>22.5</v>
       </c>
       <c r="W8" t="n">
-        <v>184.8571428571429</v>
+        <v>184</v>
       </c>
       <c r="X8" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y8" t="n">
-        <v>497</v>
+        <v>422</v>
       </c>
       <c r="Z8" t="n">
-        <v>138000</v>
+        <v>117000</v>
       </c>
       <c r="AA8" t="n">
-        <v>48550000</v>
+        <v>41050000</v>
       </c>
       <c r="AB8" t="n">
-        <v>552</v>
+        <v>473</v>
       </c>
       <c r="AC8" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AD8" t="n">
         <v>27.06296296296297</v>
@@ -2174,52 +2174,52 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>24.97222222222222</v>
+        <v>25.5</v>
       </c>
       <c r="O9" t="n">
-        <v>189.1944444444445</v>
+        <v>190</v>
       </c>
       <c r="P9" t="n">
         <v>2</v>
       </c>
       <c r="Q9" t="n">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="R9" t="n">
-        <v>29666.66666666667</v>
+        <v>27000</v>
       </c>
       <c r="S9" t="n">
-        <v>3933333.333333333</v>
+        <v>3500000</v>
       </c>
       <c r="T9" t="n">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="U9" t="n">
         <v>2</v>
       </c>
       <c r="V9" t="n">
-        <v>29.33333333333333</v>
+        <v>29</v>
       </c>
       <c r="W9" t="n">
-        <v>178.1111111111111</v>
+        <v>180.3333333333333</v>
       </c>
       <c r="X9" t="n">
-        <v>2.666666666666667</v>
+        <v>3</v>
       </c>
       <c r="Y9" t="n">
-        <v>199.3333333333333</v>
+        <v>222</v>
       </c>
       <c r="Z9" t="n">
-        <v>85666.66666666667</v>
+        <v>94000</v>
       </c>
       <c r="AA9" t="n">
-        <v>14816666.66666667</v>
+        <v>15100000</v>
       </c>
       <c r="AB9" t="n">
-        <v>199.3333333333333</v>
+        <v>222</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.666666666666667</v>
+        <v>4</v>
       </c>
       <c r="AD9" t="n">
         <v>26.76435185185185</v>
@@ -2819,22 +2819,22 @@
         <v>3.5</v>
       </c>
       <c r="AD12" t="n">
-        <v>25.79166666666667</v>
+        <v>25.9375</v>
       </c>
       <c r="AE12" t="n">
-        <v>185.0416666666667</v>
+        <v>185</v>
       </c>
       <c r="AF12" t="n">
-        <v>73.70833333333333</v>
+        <v>73.75</v>
       </c>
       <c r="AG12" t="n">
-        <v>22291.66666666667</v>
+        <v>22562.5</v>
       </c>
       <c r="AH12" t="n">
         <v>5350000</v>
       </c>
       <c r="AI12" t="n">
-        <v>76.91666666666667</v>
+        <v>76.75</v>
       </c>
       <c r="AJ12" t="n">
         <v>1.125</v>
@@ -2861,25 +2861,25 @@
         <v>2.607575757575757</v>
       </c>
       <c r="AR12" t="n">
-        <v>24.81548711988782</v>
+        <v>24.80746224592974</v>
       </c>
       <c r="AS12" t="n">
-        <v>184.1908611131853</v>
+        <v>184.4575197835647</v>
       </c>
       <c r="AT12" t="n">
-        <v>72.5454978243291</v>
+        <v>72.56823231020213</v>
       </c>
       <c r="AU12" t="n">
-        <v>21177.01909312369</v>
+        <v>21153.49197228067</v>
       </c>
       <c r="AV12" t="n">
-        <v>4952682.416666826</v>
+        <v>4947637.061868872</v>
       </c>
       <c r="AW12" t="n">
-        <v>76.55772420610985</v>
+        <v>76.54461763440091</v>
       </c>
       <c r="AX12" t="n">
-        <v>1.158487278483961</v>
+        <v>1.131871521867652</v>
       </c>
       <c r="AY12" t="n">
         <v>25.00991881878609</v>
@@ -3814,22 +3814,22 @@
         <v>8.166666666666666</v>
       </c>
       <c r="AD17" t="n">
-        <v>28.33888888888889</v>
+        <v>28.36666666666666</v>
       </c>
       <c r="AE17" t="n">
-        <v>185.2921296296296</v>
+        <v>185.4105555555556</v>
       </c>
       <c r="AF17" t="n">
-        <v>71.6962962962963</v>
+        <v>71.77555555555554</v>
       </c>
       <c r="AG17" t="n">
-        <v>17048.14814814815</v>
+        <v>16977.77777777778</v>
       </c>
       <c r="AH17" t="n">
-        <v>2222615.740740741</v>
+        <v>2226638.888888889</v>
       </c>
       <c r="AI17" t="n">
-        <v>73.5712962962963</v>
+        <v>73.58555555555556</v>
       </c>
       <c r="AJ17" t="n">
         <v>1</v>
@@ -3856,22 +3856,22 @@
         <v>3.170370370370371</v>
       </c>
       <c r="AR17" t="n">
-        <v>25.40532515300317</v>
+        <v>25.59052640399389</v>
       </c>
       <c r="AS17" t="n">
-        <v>185.6896861308626</v>
+        <v>185.9124769565946</v>
       </c>
       <c r="AT17" t="n">
-        <v>68.42912900652838</v>
+        <v>68.54967011545959</v>
       </c>
       <c r="AU17" t="n">
-        <v>15078.88310519889</v>
+        <v>15297.91264233989</v>
       </c>
       <c r="AV17" t="n">
-        <v>1804867.324797665</v>
+        <v>1801511.87893061</v>
       </c>
       <c r="AW17" t="n">
-        <v>74.38585339668931</v>
+        <v>74.26388778633361</v>
       </c>
       <c r="AX17" t="n">
         <v>1</v>

--- a/data/germany/p6_deployment/data_preparation/df_filled.xlsx
+++ b/data/germany/p6_deployment/data_preparation/df_filled.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BG3"/>
+  <dimension ref="A1:BG19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -495,222 +495,222 @@
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
+          <t>mean_age_player_start_home</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>mean_hei_player_start_home</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>mean_rat_player_start_home</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>mean_wage_player_start_home</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>mean_value_player_start_home</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>mean_pot_player_start_home</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>mean_rep_player_start_home</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>mean_age_player_start_away</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>mean_hei_player_start_away</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>mean_rat_player_start_away</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>mean_wage_player_start_away</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>mean_value_player_start_away</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>mean_pot_player_start_away</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>mean_rep_player_start_away</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>mean_age_player_sub_home</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>mean_hei_player_sub_home</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>mean_rat_player_sub_home</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>mean_wage_player_sub_home</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>mean_value_player_sub_home</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>mean_pot_player_sub_home</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>mean_rep_player_sub_home</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>mean_age_player_sub_away</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>mean_hei_player_sub_away</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>mean_rat_player_sub_away</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>mean_wage_player_sub_away</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>mean_value_player_sub_away</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>mean_pot_player_sub_away</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>mean_rep_player_sub_away</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
           <t>mean_age_player_miss_home</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>mean_hei_player_miss_home</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>n_player_miss_home</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>sum_rat_player_miss_home</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>sum_wage_player_miss_home</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>sum_value_player_miss_home</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>sum_pot_player_miss_home</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="AW1" s="1" t="inlineStr">
         <is>
           <t>sum_rep_player_miss_home</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="AX1" s="1" t="inlineStr">
         <is>
           <t>mean_age_player_miss_away</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="AY1" s="1" t="inlineStr">
         <is>
           <t>mean_hei_player_miss_away</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="AZ1" s="1" t="inlineStr">
         <is>
           <t>n_player_miss_away</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="BA1" s="1" t="inlineStr">
         <is>
           <t>sum_rat_player_miss_away</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="BB1" s="1" t="inlineStr">
         <is>
           <t>sum_wage_player_miss_away</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="BC1" s="1" t="inlineStr">
         <is>
           <t>sum_value_player_miss_away</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="BD1" s="1" t="inlineStr">
         <is>
           <t>sum_pot_player_miss_away</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="BE1" s="1" t="inlineStr">
         <is>
           <t>sum_rep_player_miss_away</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>mean_age_player_start_home</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>mean_hei_player_start_home</t>
-        </is>
-      </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>mean_rat_player_start_home</t>
-        </is>
-      </c>
-      <c r="AG1" s="1" t="inlineStr">
-        <is>
-          <t>mean_wage_player_start_home</t>
-        </is>
-      </c>
-      <c r="AH1" s="1" t="inlineStr">
-        <is>
-          <t>mean_value_player_start_home</t>
-        </is>
-      </c>
-      <c r="AI1" s="1" t="inlineStr">
-        <is>
-          <t>mean_pot_player_start_home</t>
-        </is>
-      </c>
-      <c r="AJ1" s="1" t="inlineStr">
-        <is>
-          <t>mean_rep_player_start_home</t>
-        </is>
-      </c>
-      <c r="AK1" s="1" t="inlineStr">
-        <is>
-          <t>mean_age_player_start_away</t>
-        </is>
-      </c>
-      <c r="AL1" s="1" t="inlineStr">
-        <is>
-          <t>mean_hei_player_start_away</t>
-        </is>
-      </c>
-      <c r="AM1" s="1" t="inlineStr">
-        <is>
-          <t>mean_rat_player_start_away</t>
-        </is>
-      </c>
-      <c r="AN1" s="1" t="inlineStr">
-        <is>
-          <t>mean_wage_player_start_away</t>
-        </is>
-      </c>
-      <c r="AO1" s="1" t="inlineStr">
-        <is>
-          <t>mean_value_player_start_away</t>
-        </is>
-      </c>
-      <c r="AP1" s="1" t="inlineStr">
-        <is>
-          <t>mean_pot_player_start_away</t>
-        </is>
-      </c>
-      <c r="AQ1" s="1" t="inlineStr">
-        <is>
-          <t>mean_rep_player_start_away</t>
-        </is>
-      </c>
-      <c r="AR1" s="1" t="inlineStr">
-        <is>
-          <t>mean_age_player_sub_home</t>
-        </is>
-      </c>
-      <c r="AS1" s="1" t="inlineStr">
-        <is>
-          <t>mean_hei_player_sub_home</t>
-        </is>
-      </c>
-      <c r="AT1" s="1" t="inlineStr">
-        <is>
-          <t>mean_rat_player_sub_home</t>
-        </is>
-      </c>
-      <c r="AU1" s="1" t="inlineStr">
-        <is>
-          <t>mean_wage_player_sub_home</t>
-        </is>
-      </c>
-      <c r="AV1" s="1" t="inlineStr">
-        <is>
-          <t>mean_value_player_sub_home</t>
-        </is>
-      </c>
-      <c r="AW1" s="1" t="inlineStr">
-        <is>
-          <t>mean_pot_player_sub_home</t>
-        </is>
-      </c>
-      <c r="AX1" s="1" t="inlineStr">
-        <is>
-          <t>mean_rep_player_sub_home</t>
-        </is>
-      </c>
-      <c r="AY1" s="1" t="inlineStr">
-        <is>
-          <t>mean_age_player_sub_away</t>
-        </is>
-      </c>
-      <c r="AZ1" s="1" t="inlineStr">
-        <is>
-          <t>mean_hei_player_sub_away</t>
-        </is>
-      </c>
-      <c r="BA1" s="1" t="inlineStr">
-        <is>
-          <t>mean_rat_player_sub_away</t>
-        </is>
-      </c>
-      <c r="BB1" s="1" t="inlineStr">
-        <is>
-          <t>mean_wage_player_sub_away</t>
-        </is>
-      </c>
-      <c r="BC1" s="1" t="inlineStr">
-        <is>
-          <t>mean_value_player_sub_away</t>
-        </is>
-      </c>
-      <c r="BD1" s="1" t="inlineStr">
-        <is>
-          <t>mean_pot_player_sub_away</t>
-        </is>
-      </c>
-      <c r="BE1" s="1" t="inlineStr">
-        <is>
-          <t>mean_rep_player_sub_away</t>
         </is>
       </c>
       <c r="BF1" s="1" t="inlineStr">
@@ -727,35 +727,35 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>nBwH6AY8</t>
+          <t>4E8uaJWa</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45585.4375</v>
+        <v>45590.64583333334</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">reichel t 
+          <t xml:space="preserve">siebert d 
   ger </t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">holstein stadion
-  kiel </t>
+          <t xml:space="preserve">mewa arena
+  mainz </t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>15034</v>
+        <v>34000</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>63WsD2ei</t>
+          <t>EuakNmc1</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>pzHW4oaE</t>
+          <t>88HSzjDr</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -781,344 +781,3528 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>25.5</v>
+        <v>27.52380952380953</v>
       </c>
       <c r="O2" t="n">
-        <v>190</v>
+        <v>183.4730158730159</v>
       </c>
       <c r="P2" t="n">
-        <v>2</v>
+        <v>74.76666666666667</v>
       </c>
       <c r="Q2" t="n">
-        <v>136</v>
+        <v>25288.88888888889</v>
       </c>
       <c r="R2" t="n">
-        <v>27000</v>
+        <v>6469682.539682539</v>
       </c>
       <c r="S2" t="n">
-        <v>3500000</v>
+        <v>76.93650793650795</v>
       </c>
       <c r="T2" t="n">
-        <v>145</v>
+        <v>1.395238095238095</v>
       </c>
       <c r="U2" t="n">
-        <v>2</v>
+        <v>26.25714285714286</v>
       </c>
       <c r="V2" t="n">
-        <v>28.5</v>
+        <v>184.9428571428571</v>
       </c>
       <c r="W2" t="n">
-        <v>181.5</v>
+        <v>75.5</v>
       </c>
       <c r="X2" t="n">
-        <v>4</v>
+        <v>24457.14285714286</v>
       </c>
       <c r="Y2" t="n">
-        <v>298</v>
+        <v>8100000</v>
       </c>
       <c r="Z2" t="n">
-        <v>125000</v>
+        <v>77.67142857142858</v>
       </c>
       <c r="AA2" t="n">
-        <v>23600000</v>
+        <v>1.457142857142857</v>
       </c>
       <c r="AB2" t="n">
-        <v>301</v>
+        <v>25.40367477134395</v>
       </c>
       <c r="AC2" t="n">
-        <v>6</v>
+        <v>183.4516876607102</v>
       </c>
       <c r="AD2" t="n">
-        <v>26.76435185185185</v>
+        <v>71.14610226865865</v>
       </c>
       <c r="AE2" t="n">
-        <v>185.5564814814815</v>
+        <v>21415.9359437555</v>
       </c>
       <c r="AF2" t="n">
-        <v>69.94444444444444</v>
+        <v>3409595.539172606</v>
       </c>
       <c r="AG2" t="n">
-        <v>16704.16666666667</v>
+        <v>77.02997754125575</v>
       </c>
       <c r="AH2" t="n">
-        <v>1906898.148148148</v>
+        <v>1.154084887543534</v>
       </c>
       <c r="AI2" t="n">
-        <v>72.24537037037037</v>
+        <v>25.59909867837295</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1</v>
+        <v>183.1228692850138</v>
       </c>
       <c r="AK2" t="n">
-        <v>26.83333333333333</v>
+        <v>73.29243528074845</v>
       </c>
       <c r="AL2" t="n">
-        <v>186.5060606060606</v>
+        <v>22174.38394121951</v>
       </c>
       <c r="AM2" t="n">
-        <v>74.7878787878788</v>
+        <v>5978963.402294556</v>
       </c>
       <c r="AN2" t="n">
-        <v>27319.69696969697</v>
+        <v>77.33729510110679</v>
       </c>
       <c r="AO2" t="n">
-        <v>6433333.333333333</v>
+        <v>1.208599915938916</v>
       </c>
       <c r="AP2" t="n">
-        <v>77.64999999999999</v>
+        <v>27.4</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.38939393939394</v>
+        <v>185.1</v>
       </c>
       <c r="AR2" t="n">
-        <v>25.64857161018488</v>
+        <v>1.2</v>
       </c>
       <c r="AS2" t="n">
-        <v>184.7527823181141</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="AT2" t="n">
-        <v>68.37299952780502</v>
+        <v>33200</v>
       </c>
       <c r="AU2" t="n">
-        <v>15767.80719915731</v>
+        <v>8920000</v>
       </c>
       <c r="AV2" t="n">
-        <v>1865795.648541644</v>
+        <v>92.2</v>
       </c>
       <c r="AW2" t="n">
-        <v>72.70027332824816</v>
+        <v>1.6</v>
       </c>
       <c r="AX2" t="n">
-        <v>1</v>
+        <v>21.87142857142857</v>
       </c>
       <c r="AY2" t="n">
-        <v>26.31970899470899</v>
+        <v>182.2619047619047</v>
       </c>
       <c r="AZ2" t="n">
-        <v>182.6566137566138</v>
+        <v>4.285714285714286</v>
       </c>
       <c r="BA2" t="n">
-        <v>73.12539682539682</v>
+        <v>293.5714285714286</v>
       </c>
       <c r="BB2" t="n">
-        <v>24962.43386243387</v>
+        <v>54285.71428571428</v>
       </c>
       <c r="BC2" t="n">
-        <v>4186851.851851852</v>
+        <v>20939285.71428571</v>
       </c>
       <c r="BD2" t="n">
-        <v>75.94285714285715</v>
+        <v>330.8571428571428</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.134920634920635</v>
+        <v>5.285714285714286</v>
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>hAcTWKKN</t>
+          <t>vZA6VYpf</t>
         </is>
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>IkCftsQm</t>
+          <t>4ljanukM</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>rPiijklS</t>
+          <t>x0haJmIE</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45585.52083333334</v>
+        <v>45591.4375</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">welz t 
+          <t xml:space="preserve">jollenbeck m 
   ger </t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">wwk arena
+  augsburg </t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>30660</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>fTVNku3I</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>nP1i5US1</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>59</v>
+      </c>
+      <c r="I3" t="n">
+        <v>591</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="N3" t="n">
+        <v>25.9375</v>
+      </c>
+      <c r="O3" t="n">
+        <v>185</v>
+      </c>
+      <c r="P3" t="n">
+        <v>73.75</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>22562.5</v>
+      </c>
+      <c r="R3" t="n">
+        <v>5350000</v>
+      </c>
+      <c r="S3" t="n">
+        <v>76.75</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1.125</v>
+      </c>
+      <c r="U3" t="n">
+        <v>26.81168831168831</v>
+      </c>
+      <c r="V3" t="n">
+        <v>186.0090909090909</v>
+      </c>
+      <c r="W3" t="n">
+        <v>82.10000000000001</v>
+      </c>
+      <c r="X3" t="n">
+        <v>58732.46753246753</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>37817532.46753247</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>84.02207792207794</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>2.637662337662337</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>24.58496763936835</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>184.5469217192459</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>72.36800864683993</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>20833.9455000501</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>4956307.957792367</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>76.70491035329601</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>1.124937494934178</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>24.69897803514998</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>184.3256570751177</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>77.55218313523315</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>42998.78951095034</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>21764360.16636736</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>82.87689888659159</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>1.845534620477412</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>25.93095238095238</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>184.2976190476191</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>4.714285714285714</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>332</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>80285.71428571429</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>12325000</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>343.1428571428572</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>4.714285714285714</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>22.58333333333333</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>184.4761904761905</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>152.1428571428571</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>79428.57142857143</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>45242857.14285714</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>168.2857142857143</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>4.142857142857143</v>
+      </c>
+      <c r="BF3" t="inlineStr">
+        <is>
+          <t>YZPE6Sx7</t>
+        </is>
+      </c>
+      <c r="BG3" t="inlineStr">
+        <is>
+          <t>0jdIgO6t</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>ELNeaSQr</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>45591.4375</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dankert b 
+  ger </t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">red bull arena
+  leipzig </t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>47069</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>KbS1suSm</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>fiEQZ7C7</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>59</v>
+      </c>
+      <c r="I4" t="n">
+        <v>591</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="N4" t="n">
+        <v>25.77597402597403</v>
+      </c>
+      <c r="O4" t="n">
+        <v>183.5893939393939</v>
+      </c>
+      <c r="P4" t="n">
+        <v>80.63629148629148</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>57368.90331890331</v>
+      </c>
+      <c r="R4" t="n">
+        <v>31551857.86435786</v>
+      </c>
+      <c r="S4" t="n">
+        <v>84.19592352092353</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2.25501443001443</v>
+      </c>
+      <c r="U4" t="n">
+        <v>26.80158730158731</v>
+      </c>
+      <c r="V4" t="n">
+        <v>183.9587301587301</v>
+      </c>
+      <c r="W4" t="n">
+        <v>76.33333333333334</v>
+      </c>
+      <c r="X4" t="n">
+        <v>26447.61904761905</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>11033333.33333333</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>78.84444444444443</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.63015873015873</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>25.58377166656136</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>184.6276321932282</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>78.57405111167274</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>52308.07805578371</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>24300244.35212681</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>82.19301492526836</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>1.965138687053769</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>26.55350417262807</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>183.5853028958619</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>74.19680298997069</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>23865.3412186593</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>7007238.250199185</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>77.06994016662209</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>1.390069541442539</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>24.40476190476191</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>182.7261904761905</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>3.285714285714286</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>250.7142857142857</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>147285.7142857143</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>54242857.14285714</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>275</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>26.10442176870748</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>185.6530612244898</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>5.428571428571429</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>386.1428571428572</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>101714.2857142857</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>25100000</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>405.2857142857143</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>5.857142857142857</v>
+      </c>
+      <c r="BF4" t="inlineStr">
+        <is>
+          <t>vZA6VYpf</t>
+        </is>
+      </c>
+      <c r="BG4" t="inlineStr">
+        <is>
+          <t>2VSFgl3c</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>Mku6FvHt</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>45591.4375</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">schlager d 
+  ger </t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">millerntor stadion
+  hamburg </t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>29546</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>ILyJuN3g</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>nwkTahLL</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>59</v>
+      </c>
+      <c r="I5" t="n">
+        <v>591</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="N5" t="n">
+        <v>26.8025974025974</v>
+      </c>
+      <c r="O5" t="n">
+        <v>185.1207792207792</v>
+      </c>
+      <c r="P5" t="n">
+        <v>70.70259740259739</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>17255.84415584416</v>
+      </c>
+      <c r="R5" t="n">
+        <v>2344675.324675325</v>
+      </c>
+      <c r="S5" t="n">
+        <v>73.52857142857144</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1</v>
+      </c>
+      <c r="U5" t="n">
+        <v>24.65</v>
+      </c>
+      <c r="V5" t="n">
+        <v>184.4722222222222</v>
+      </c>
+      <c r="W5" t="n">
+        <v>75.18055555555556</v>
+      </c>
+      <c r="X5" t="n">
+        <v>36041.66666666667</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>9941944.444444444</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>79.8111111111111</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.391666666666666</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>25.85559732664996</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>184.7678362573099</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>68.13755221386801</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>16069.67418546366</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>1699945.697577276</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>71.61733500417711</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>25.15803546298902</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>184.9212679090775</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>73.43227665866984</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>33404.91491652482</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>8240313.769048288</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>78.0910422781553</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>1.419858413859962</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>28.9</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>186.7619047619048</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>4.142857142857143</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>272.1428571428572</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>56142.85714285714</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>3857142.857142857</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>283</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>4.142857142857143</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>23.79047619047619</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>183.3785714285714</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>5.285714285714286</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>390</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>184714.2857142857</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>54371428.57142857</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>419.5714285714286</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF5" t="inlineStr">
+        <is>
+          <t>IkCftsQm</t>
+        </is>
+      </c>
+      <c r="BG5" t="inlineStr">
+        <is>
+          <t>4fuCGs9P</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>rwXP4l3L</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>45591.4375</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gerach t 
+  ger </t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mhparena
+  stuttgart </t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>60449</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>nJQmYp1B</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>63WsD2ei</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>59</v>
+      </c>
+      <c r="I6" t="n">
+        <v>591</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="N6" t="n">
+        <v>24.86477272727273</v>
+      </c>
+      <c r="O6" t="n">
+        <v>186.0123737373737</v>
+      </c>
+      <c r="P6" t="n">
+        <v>76.22525252525253</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>27545.58080808081</v>
+      </c>
+      <c r="R6" t="n">
+        <v>13754378.15656566</v>
+      </c>
+      <c r="S6" t="n">
+        <v>79.54482323232324</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1.476262626262626</v>
+      </c>
+      <c r="U6" t="n">
+        <v>26.6234126984127</v>
+      </c>
+      <c r="V6" t="n">
+        <v>185.8420634920635</v>
+      </c>
+      <c r="W6" t="n">
+        <v>69.87301587301587</v>
+      </c>
+      <c r="X6" t="n">
+        <v>16603.57142857143</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1902738.095238095</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>72.22619047619047</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>24.2202850877193</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>185.1006944444444</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>73.62858187134503</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>24011.62280701754</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>10507594.11549708</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>78.15570175438597</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>1.483004385964912</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>25.75319743458024</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>184.6112283815128</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>68.44896558165601</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>15875.80753125049</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>1854355.453852022</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>72.63424788679774</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>22.48367346938776</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>183.9353741496599</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>4.571428571428571</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>320.4285714285714</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>83428.57142857143</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>23450000</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>358.5714285714286</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>5.571428571428571</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>25.4047619047619</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>188.6428571428571</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>2.142857142857143</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>148.2857142857143</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>32428.57142857143</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>4242857.142857143</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>157.2857142857143</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>2.142857142857143</v>
+      </c>
+      <c r="BF6" t="inlineStr">
+        <is>
+          <t>K6A2elS9</t>
+        </is>
+      </c>
+      <c r="BG6" t="inlineStr">
+        <is>
+          <t>hpYJ6izc</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>MiACepQ7</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>45591.5625</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">brych f 
+  ger </t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">weserstadion
+  bremen </t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>42100</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Ig1f1fy3</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>4jcj2zMd</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>59</v>
+      </c>
+      <c r="I7" t="n">
+        <v>591</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="N7" t="n">
+        <v>27.08701298701299</v>
+      </c>
+      <c r="O7" t="n">
+        <v>183.4415584415584</v>
+      </c>
+      <c r="P7" t="n">
+        <v>74.42467532467533</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>23531.16883116883</v>
+      </c>
+      <c r="R7" t="n">
+        <v>5979220.779220779</v>
+      </c>
+      <c r="S7" t="n">
+        <v>76.70779220779221</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1.096103896103896</v>
+      </c>
+      <c r="U7" t="n">
+        <v>26.43531746031746</v>
+      </c>
+      <c r="V7" t="n">
+        <v>184.2964285714286</v>
+      </c>
+      <c r="W7" t="n">
+        <v>84.00793650793651</v>
+      </c>
+      <c r="X7" t="n">
+        <v>101621.4285714286</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>51919642.85714286</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>86.07619047619048</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>3.121428571428571</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>24.33053415111277</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>186.6280509291297</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>70.33227143710963</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>19356.47197232683</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>3512321.038810087</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>76.55925171954921</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>24.47705784068013</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>180.6071477713892</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>80.62562103788883</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>80560.16941864465</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>38657548.66639639</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>84.42125411568136</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>2.260791685095091</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>27.10952380952381</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>185.5095238095238</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>3</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>217</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>64285.71428571428</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>10871428.57142857</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>224.5714285714286</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>3</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>27.25</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>181.5</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>126</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>140000</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>59000000</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>129</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BF7" t="inlineStr">
+        <is>
+          <t>f3ddUIXs</t>
+        </is>
+      </c>
+      <c r="BG7" t="inlineStr">
+        <is>
+          <t>UgdQz0fK</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>WQadeyWO</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>45592.47916666666</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stieler t 
+  ger </t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vonovia ruhrstadion
+  bochum </t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>26000</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>8Y2m6ADe</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>nVp0wiqd</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>59</v>
+      </c>
+      <c r="I8" t="n">
+        <v>591</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="N8" t="n">
+        <v>28.30555555555555</v>
+      </c>
+      <c r="O8" t="n">
+        <v>185.7680555555555</v>
+      </c>
+      <c r="P8" t="n">
+        <v>71.62777777777778</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>16981.48148148148</v>
+      </c>
+      <c r="R8" t="n">
+        <v>2219421.296296296</v>
+      </c>
+      <c r="S8" t="n">
+        <v>73.71018518518518</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1</v>
+      </c>
+      <c r="U8" t="n">
+        <v>27.16507936507937</v>
+      </c>
+      <c r="V8" t="n">
+        <v>183.7761904761905</v>
+      </c>
+      <c r="W8" t="n">
+        <v>83.05396825396825</v>
+      </c>
+      <c r="X8" t="n">
+        <v>79155.55555555555</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>46819484.12698413</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>85.62063492063491</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>3.177777777777778</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>25.73924819590454</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>185.3610704740736</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>68.5839277681383</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>15383.17324230637</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>1771596.648105936</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>73.99310682437617</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>26.76743697478992</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>183.1663659053365</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>81.19061624649861</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>73218.99195575666</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>34593647.62892337</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>83.66330711771889</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>2.601192271780507</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>26.9047619047619</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>186.4357142857143</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>3.857142857142857</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>272.7142857142857</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>64000</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>9417857.142857144</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>284.2857142857143</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>4.428571428571429</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>22.19047619047619</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>184.6952380952381</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>5.571428571428571</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>404.5714285714286</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>227857.1428571429</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>105650000</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>454.8571428571428</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>8.285714285714286</v>
+      </c>
+      <c r="BF8" t="inlineStr">
+        <is>
+          <t>KUx4Q7x1</t>
+        </is>
+      </c>
+      <c r="BG8" t="inlineStr">
+        <is>
+          <t>GzfvcwRj</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>ABBmcc1C</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>45592.5625</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">brych f 
+  ger </t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadion an der alten forsterei
+  berlin </t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>22012</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>pzHW4oaE</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>8vndvXTk</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>59</v>
+      </c>
+      <c r="I9" t="n">
+        <v>591</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="N9" t="n">
+        <v>26.79220779220779</v>
+      </c>
+      <c r="O9" t="n">
+        <v>186.5246753246753</v>
+      </c>
+      <c r="P9" t="n">
+        <v>74.70129870129871</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>27118.18181818182</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6329870.129870131</v>
+      </c>
+      <c r="S9" t="n">
+        <v>77.64805194805194</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1.385714285714286</v>
+      </c>
+      <c r="U9" t="n">
+        <v>24.47777777777778</v>
+      </c>
+      <c r="V9" t="n">
+        <v>185.5166666666667</v>
+      </c>
+      <c r="W9" t="n">
+        <v>76.62777777777778</v>
+      </c>
+      <c r="X9" t="n">
+        <v>34377.77777777778</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>14999166.66666667</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>81.62222222222222</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.672222222222222</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>26.39433703305884</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>182.5778493853682</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>73.16763336913712</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>25200.88316028166</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>4233842.940685046</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>75.84575725026853</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>1.123165055495883</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>22.85488721804511</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>184.4735426227907</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>73.03716433941999</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>26354.00026039124</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>9288892.539791036</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>80.91401067604076</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>1.4322429450249</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>29.0952380952381</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>178.7142857142857</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>2.714285714285714</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>202.5714285714286</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>86142.85714285714</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>15142857.14285714</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>203</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>3.714285714285714</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>19.61904761904762</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>177.5238095238095</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>1.857142857142857</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>114.7142857142857</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>12714.28571428571</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>3646428.571428571</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>145.2857142857143</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>2.142857142857143</v>
+      </c>
+      <c r="BF9" t="inlineStr">
+        <is>
+          <t>A15eUM4C</t>
+        </is>
+      </c>
+      <c r="BG9" t="inlineStr">
+        <is>
+          <t>UgdQz0fK</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>zyC4c6ee</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>45592.64583333334</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">storks s 
+  ger </t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">voith arena
+  heidenheim </t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>15000</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>KWixEVWi</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>hQAtP9Sl</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>59</v>
+      </c>
+      <c r="I10" t="n">
+        <v>591</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="N10" t="n">
+        <v>26.88571428571428</v>
+      </c>
+      <c r="O10" t="n">
+        <v>187.1285714285714</v>
+      </c>
+      <c r="P10" t="n">
+        <v>72.61428571428571</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>22185.71428571429</v>
+      </c>
+      <c r="R10" t="n">
+        <v>3182857.142857143</v>
+      </c>
+      <c r="S10" t="n">
+        <v>74.34285714285714</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1.014285714285714</v>
+      </c>
+      <c r="U10" t="n">
+        <v>27.53968253968254</v>
+      </c>
+      <c r="V10" t="n">
+        <v>186.0305555555556</v>
+      </c>
+      <c r="W10" t="n">
+        <v>75.17420634920634</v>
+      </c>
+      <c r="X10" t="n">
+        <v>30372.61904761905</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>7735992.063492064</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>78.60753968253968</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.659126984126984</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>25.91832298136646</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>184.8549689440993</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>69.50155279503106</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>19911.1801242236</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>2133866.459627329</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>72.16335403726707</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>1.037267080745342</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>24.23217567728846</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>185.7456975772765</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>71.09125193937224</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>23906.02697219238</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>5350420.097863707</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>77.60105024465928</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>1.175164100728011</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>24.59523809523809</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>187.3095238095238</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>3</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>203.8571428571429</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>53142.85714285714</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>6239285.714285715</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>217.1428571428571</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>3.285714285714286</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>25.74574829931973</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>182.5756802721089</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>6.714285714285714</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>496.5714285714286</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>173142.8571428571</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>41942857.14285714</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>523.1428571428571</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>10.14285714285714</v>
+      </c>
+      <c r="BF10" t="inlineStr">
+        <is>
+          <t>M5BRZDsC</t>
+        </is>
+      </c>
+      <c r="BG10" t="inlineStr">
+        <is>
+          <t>8f6APkLc</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>IHYEDIog</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>45597.6875</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stieler t 
+  ger </t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bayarena
+  leverkusen </t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>30210</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>4jcj2zMd</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>nJQmYp1B</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>59</v>
+      </c>
+      <c r="I11" t="n">
+        <v>591</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="N11" t="n">
+        <v>26.43531746031746</v>
+      </c>
+      <c r="O11" t="n">
+        <v>184.2964285714286</v>
+      </c>
+      <c r="P11" t="n">
+        <v>84.00793650793651</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>101621.4285714286</v>
+      </c>
+      <c r="R11" t="n">
+        <v>51919642.85714286</v>
+      </c>
+      <c r="S11" t="n">
+        <v>86.07619047619048</v>
+      </c>
+      <c r="T11" t="n">
+        <v>3.121428571428571</v>
+      </c>
+      <c r="U11" t="n">
+        <v>24.86477272727273</v>
+      </c>
+      <c r="V11" t="n">
+        <v>186.0123737373737</v>
+      </c>
+      <c r="W11" t="n">
+        <v>76.22525252525253</v>
+      </c>
+      <c r="X11" t="n">
+        <v>27545.58080808081</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>13754378.15656566</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>79.54482323232324</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.476262626262626</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>24.47705784068013</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>180.6071477713892</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>80.62562103788883</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>80560.16941864465</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>38657548.66639639</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>84.42125411568136</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>2.260791685095091</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>24.2202850877193</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>185.1006944444444</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>73.62858187134503</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>24011.62280701754</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>10507594.11549708</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>78.15570175438597</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>1.483004385964912</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>27.25</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>181.5</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>126</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>140000</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>59000000</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>129</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>22.48367346938776</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>183.9353741496599</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>4.571428571428571</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>320.4285714285714</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>83428.57142857143</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>23450000</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>358.5714285714286</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>5.571428571428571</v>
+      </c>
+      <c r="BF11" t="inlineStr">
+        <is>
+          <t>hAcTWKKN</t>
+        </is>
+      </c>
+      <c r="BG11" t="inlineStr">
+        <is>
+          <t>GzfvcwRj</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>jVWMBdG5</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>45598.47916666666</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gerach t 
+  ger </t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">allianz arena
+  munich </t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>75024</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>nVp0wiqd</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>pzHW4oaE</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>59</v>
+      </c>
+      <c r="I12" t="n">
+        <v>591</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="N12" t="n">
+        <v>27.16507936507937</v>
+      </c>
+      <c r="O12" t="n">
+        <v>183.7761904761905</v>
+      </c>
+      <c r="P12" t="n">
+        <v>83.05396825396825</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>79155.55555555555</v>
+      </c>
+      <c r="R12" t="n">
+        <v>46819484.12698413</v>
+      </c>
+      <c r="S12" t="n">
+        <v>85.62063492063491</v>
+      </c>
+      <c r="T12" t="n">
+        <v>3.177777777777778</v>
+      </c>
+      <c r="U12" t="n">
+        <v>26.79220779220779</v>
+      </c>
+      <c r="V12" t="n">
+        <v>186.5246753246753</v>
+      </c>
+      <c r="W12" t="n">
+        <v>74.70129870129871</v>
+      </c>
+      <c r="X12" t="n">
+        <v>27118.18181818182</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>6329870.129870131</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>77.64805194805194</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.385714285714286</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>26.76743697478992</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>183.1663659053365</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>81.19061624649861</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>73218.99195575666</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>34593647.62892337</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>83.66330711771889</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>2.601192271780507</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>26.39433703305884</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>182.5778493853682</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>73.16763336913712</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>25200.88316028166</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>4233842.940685046</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>75.84575725026853</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>1.123165055495883</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>22.19047619047619</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>184.6952380952381</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>5.571428571428571</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>404.5714285714286</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>227857.1428571429</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>105650000</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>454.8571428571428</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>8.285714285714286</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>29.0952380952381</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>178.7142857142857</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>2.714285714285714</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>202.5714285714286</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>86142.85714285714</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>15142857.14285714</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>203</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>3.714285714285714</v>
+      </c>
+      <c r="BF12" t="inlineStr">
+        <is>
+          <t>K6A2elS9</t>
+        </is>
+      </c>
+      <c r="BG12" t="inlineStr">
+        <is>
+          <t>hpYJ6izc</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>485V7EFU</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>45598.47916666666</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">storks s 
+  ger </t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">deutsche bank park
+  frankfurt </t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>58000</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>8vndvXTk</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>8Y2m6ADe</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>59</v>
+      </c>
+      <c r="I13" t="n">
+        <v>591</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="N13" t="n">
+        <v>24.47777777777778</v>
+      </c>
+      <c r="O13" t="n">
+        <v>185.5166666666667</v>
+      </c>
+      <c r="P13" t="n">
+        <v>76.62777777777778</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>34377.77777777778</v>
+      </c>
+      <c r="R13" t="n">
+        <v>14999166.66666667</v>
+      </c>
+      <c r="S13" t="n">
+        <v>81.62222222222222</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1.672222222222222</v>
+      </c>
+      <c r="U13" t="n">
+        <v>28.30555555555555</v>
+      </c>
+      <c r="V13" t="n">
+        <v>185.7680555555555</v>
+      </c>
+      <c r="W13" t="n">
+        <v>71.62777777777778</v>
+      </c>
+      <c r="X13" t="n">
+        <v>16981.48148148148</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>2219421.296296296</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>73.71018518518518</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>22.85488721804511</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>184.4735426227907</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>73.03716433941999</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>26354.00026039124</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>9288892.539791036</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>80.91401067604076</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>1.4322429450249</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>25.73924819590454</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>185.3610704740736</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>68.5839277681383</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>15383.17324230637</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>1771596.648105936</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>73.99310682437617</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>19.61904761904762</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>177.5238095238095</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>1.857142857142857</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>114.7142857142857</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>12714.28571428571</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>3646428.571428571</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>145.2857142857143</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>2.142857142857143</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>26.9047619047619</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>186.4357142857143</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>3.857142857142857</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>272.7142857142857</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>64000</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>9417857.142857144</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>284.2857142857143</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>4.428571428571429</v>
+      </c>
+      <c r="BF13" t="inlineStr">
+        <is>
+          <t>hAcTWKKN</t>
+        </is>
+      </c>
+      <c r="BG13" t="inlineStr">
+        <is>
+          <t>8f6APkLc</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>8MVuSH0n</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>45598.47916666666</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">jollenbeck m 
+  ger </t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">prezero arena
+  sinsheim </t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>30150</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>hQAtP9Sl</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>ILyJuN3g</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>59</v>
+      </c>
+      <c r="I14" t="n">
+        <v>591</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="N14" t="n">
+        <v>27.53968253968254</v>
+      </c>
+      <c r="O14" t="n">
+        <v>186.0305555555556</v>
+      </c>
+      <c r="P14" t="n">
+        <v>75.17420634920634</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>30372.61904761905</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7735992.063492064</v>
+      </c>
+      <c r="S14" t="n">
+        <v>78.60753968253968</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1.659126984126984</v>
+      </c>
+      <c r="U14" t="n">
+        <v>26.8025974025974</v>
+      </c>
+      <c r="V14" t="n">
+        <v>185.1207792207792</v>
+      </c>
+      <c r="W14" t="n">
+        <v>70.70259740259739</v>
+      </c>
+      <c r="X14" t="n">
+        <v>17255.84415584416</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>2344675.324675325</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>73.52857142857144</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>24.23217567728846</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>185.7456975772765</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>71.09125193937224</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>23906.02697219238</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>5350420.097863707</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>77.60105024465928</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>1.175164100728011</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>25.85559732664996</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>184.7678362573099</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>68.13755221386801</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>16069.67418546366</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>1699945.697577276</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>71.61733500417711</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>25.74574829931973</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>182.5756802721089</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>6.714285714285714</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>496.5714285714286</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>173142.8571428571</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>41942857.14285714</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>523.1428571428571</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>10.14285714285714</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>28.9</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>186.7619047619048</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>4.142857142857143</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>272.1428571428572</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>56142.85714285714</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>3857142.857142857</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>283</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>4.142857142857143</v>
+      </c>
+      <c r="BF14" t="inlineStr">
+        <is>
+          <t>KUx4Q7x1</t>
+        </is>
+      </c>
+      <c r="BG14" t="inlineStr">
+        <is>
+          <t>0jdIgO6t</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>2q7yHiho</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>45598.47916666666</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">siebert d 
+  ger </t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">holstein stadion
+  kiel </t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>15034</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>63WsD2ei</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>KWixEVWi</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>59</v>
+      </c>
+      <c r="I15" t="n">
+        <v>591</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="N15" t="n">
+        <v>26.6234126984127</v>
+      </c>
+      <c r="O15" t="n">
+        <v>185.8420634920635</v>
+      </c>
+      <c r="P15" t="n">
+        <v>69.87301587301587</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>16603.57142857143</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1902738.095238095</v>
+      </c>
+      <c r="S15" t="n">
+        <v>72.22619047619047</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1</v>
+      </c>
+      <c r="U15" t="n">
+        <v>26.88571428571428</v>
+      </c>
+      <c r="V15" t="n">
+        <v>187.1285714285714</v>
+      </c>
+      <c r="W15" t="n">
+        <v>72.61428571428571</v>
+      </c>
+      <c r="X15" t="n">
+        <v>22185.71428571429</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>3182857.142857143</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>74.34285714285714</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.014285714285714</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>25.75319743458024</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>184.6112283815128</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>68.44896558165601</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>15875.80753125049</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>1854355.453852022</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>72.63424788679774</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>25.91832298136646</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>184.8549689440993</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>69.50155279503106</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>19911.1801242236</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>2133866.459627329</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>72.16335403726707</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>1.037267080745342</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>25.4047619047619</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>188.6428571428571</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>2.142857142857143</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>148.2857142857143</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>32428.57142857143</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>4242857.142857143</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>157.2857142857143</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>2.142857142857143</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>24.59523809523809</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>187.3095238095238</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>3</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>203.8571428571429</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>53142.85714285714</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>6239285.714285715</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>217.1428571428571</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>3.285714285714286</v>
+      </c>
+      <c r="BF15" t="inlineStr">
+        <is>
+          <t>A15eUM4C</t>
+        </is>
+      </c>
+      <c r="BG15" t="inlineStr">
+        <is>
+          <t>4ljanukM</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>AoSdOZaB</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>45598.47916666666</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dankert b 
+  ger </t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
         <is>
           <t xml:space="preserve">volkswagen arena
   wolfsburg </t>
         </is>
       </c>
-      <c r="E3" t="n">
+      <c r="E16" t="n">
         <v>28917</v>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>nwkTahLL</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>fTVNku3I</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>59</v>
+      </c>
+      <c r="I16" t="n">
+        <v>591</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="N16" t="n">
+        <v>24.65</v>
+      </c>
+      <c r="O16" t="n">
+        <v>184.4722222222222</v>
+      </c>
+      <c r="P16" t="n">
+        <v>75.18055555555556</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>36041.66666666667</v>
+      </c>
+      <c r="R16" t="n">
+        <v>9941944.444444444</v>
+      </c>
+      <c r="S16" t="n">
+        <v>79.8111111111111</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1.391666666666666</v>
+      </c>
+      <c r="U16" t="n">
+        <v>25.9375</v>
+      </c>
+      <c r="V16" t="n">
+        <v>185</v>
+      </c>
+      <c r="W16" t="n">
+        <v>73.75</v>
+      </c>
+      <c r="X16" t="n">
+        <v>22562.5</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>5350000</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>76.75</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.125</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>25.15803546298902</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>184.9212679090775</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>73.43227665866984</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>33404.91491652482</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>8240313.769048288</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>78.0910422781553</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>1.419858413859962</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>24.58496763936835</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>184.5469217192459</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>72.36800864683993</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>20833.9455000501</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>4956307.957792367</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>76.70491035329601</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>1.124937494934178</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>23.79047619047619</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>183.3785714285714</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>5.285714285714286</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>390</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>184714.2857142857</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>54371428.57142857</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>419.5714285714286</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>25.93095238095238</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>184.2976190476191</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>4.714285714285714</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>332</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>80285.71428571429</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>12325000</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>343.1428571428572</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>4.714285714285714</v>
+      </c>
+      <c r="BF16" t="inlineStr">
+        <is>
+          <t>f3ddUIXs</t>
+        </is>
+      </c>
+      <c r="BG16" t="inlineStr">
+        <is>
+          <t>2VSFgl3c</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>dr2N9zoI</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>45598.60416666666</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">zwayer f 
+  ger </t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">signal iduna park
+  dortmund </t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>81365</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>nP1i5US1</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>KbS1suSm</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>59</v>
+      </c>
+      <c r="I17" t="n">
+        <v>591</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="N17" t="n">
+        <v>26.81168831168831</v>
+      </c>
+      <c r="O17" t="n">
+        <v>186.0090909090909</v>
+      </c>
+      <c r="P17" t="n">
+        <v>82.10000000000001</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>58732.46753246753</v>
+      </c>
+      <c r="R17" t="n">
+        <v>37817532.46753247</v>
+      </c>
+      <c r="S17" t="n">
+        <v>84.02207792207794</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2.637662337662337</v>
+      </c>
+      <c r="U17" t="n">
+        <v>25.77597402597403</v>
+      </c>
+      <c r="V17" t="n">
+        <v>183.5893939393939</v>
+      </c>
+      <c r="W17" t="n">
+        <v>80.63629148629148</v>
+      </c>
+      <c r="X17" t="n">
+        <v>57368.90331890331</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>31551857.86435786</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>84.19592352092353</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>2.25501443001443</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>24.69897803514998</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>184.3256570751177</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>77.55218313523315</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>42998.78951095034</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>21764360.16636736</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>82.87689888659159</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>1.845534620477412</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>25.58377166656136</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>184.6276321932282</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>78.57405111167274</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>52308.07805578371</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>24300244.35212681</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>82.19301492526836</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>1.965138687053769</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>22.58333333333333</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>184.4761904761905</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>2</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>152.1428571428571</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>79428.57142857143</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>45242857.14285714</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>168.2857142857143</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>4.142857142857143</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>24.40476190476191</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>182.7261904761905</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>3.285714285714286</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>250.7142857142857</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>147285.7142857143</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>54242857.14285714</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>275</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>7</v>
+      </c>
+      <c r="BF17" t="inlineStr">
+        <is>
+          <t>IkCftsQm</t>
+        </is>
+      </c>
+      <c r="BG17" t="inlineStr">
+        <is>
+          <t>pfoInmcq</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>GnZmQeVb</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>45599.47916666666</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">zwayer f 
+  ger </t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">europa park stadion
+  freiburg </t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>34700</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>fiEQZ7C7</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>EuakNmc1</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>59</v>
+      </c>
+      <c r="I18" t="n">
+        <v>591</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="N18" t="n">
+        <v>26.80158730158731</v>
+      </c>
+      <c r="O18" t="n">
+        <v>183.9587301587301</v>
+      </c>
+      <c r="P18" t="n">
+        <v>76.33333333333334</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>26447.61904761905</v>
+      </c>
+      <c r="R18" t="n">
+        <v>11033333.33333333</v>
+      </c>
+      <c r="S18" t="n">
+        <v>78.84444444444443</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1.63015873015873</v>
+      </c>
+      <c r="U18" t="n">
+        <v>27.52380952380953</v>
+      </c>
+      <c r="V18" t="n">
+        <v>183.4730158730159</v>
+      </c>
+      <c r="W18" t="n">
+        <v>74.76666666666667</v>
+      </c>
+      <c r="X18" t="n">
+        <v>25288.88888888889</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>6469682.539682539</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>76.93650793650795</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.395238095238095</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>26.55350417262807</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>183.5853028958619</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>74.19680298997069</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>23865.3412186593</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>7007238.250199185</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>77.06994016662209</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>1.390069541442539</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>25.40367477134395</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>183.4516876607102</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>71.14610226865865</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>21415.9359437555</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>3409595.539172606</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>77.02997754125575</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>1.154084887543534</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>26.10442176870748</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>185.6530612244898</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>5.428571428571429</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>386.1428571428572</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>101714.2857142857</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>25100000</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>405.2857142857143</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>5.857142857142857</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>27.4</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>185.1</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>90.40000000000001</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>33200</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>8920000</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>92.2</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="BF18" t="inlineStr">
+        <is>
+          <t>YZPE6Sx7</t>
+        </is>
+      </c>
+      <c r="BG18" t="inlineStr">
+        <is>
+          <t>pfoInmcq</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>raQ4MDUN</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>45599.5625</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">schlager d 
+  ger </t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">borussia park
+  monchengladbach </t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>54042</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>88HSzjDr</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
         <is>
           <t>Ig1f1fy3</t>
         </is>
       </c>
-      <c r="H3" t="n">
+      <c r="H19" t="n">
         <v>59</v>
       </c>
-      <c r="I3" t="n">
+      <c r="I19" t="n">
         <v>591</v>
       </c>
-      <c r="J3" t="n">
+      <c r="J19" t="n">
         <v>0</v>
       </c>
-      <c r="K3" t="n">
+      <c r="K19" t="n">
         <v>20242025</v>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="L19" t="inlineStr">
         <is>
           <t>germany</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="M19" t="inlineStr">
         <is>
           <t>bundesliga</t>
         </is>
       </c>
-      <c r="N3" t="n">
-        <v>23.8</v>
-      </c>
-      <c r="O3" t="n">
-        <v>182.8</v>
-      </c>
-      <c r="P3" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>371</v>
-      </c>
-      <c r="R3" t="n">
-        <v>181000</v>
-      </c>
-      <c r="S3" t="n">
-        <v>56300000</v>
-      </c>
-      <c r="T3" t="n">
-        <v>398</v>
-      </c>
-      <c r="U3" t="n">
-        <v>8</v>
-      </c>
-      <c r="V3" t="n">
-        <v>26.66666666666667</v>
-      </c>
-      <c r="W3" t="n">
-        <v>187</v>
-      </c>
-      <c r="X3" t="n">
-        <v>6</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>440</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>135000</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>26600000</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>455</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>6</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>24.65</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>184.4722222222222</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>75.18055555555556</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>36041.66666666667</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>9941944.444444444</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>79.8111111111111</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>1.391666666666666</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>27.06818181818182</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>183.6984848484848</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>74.47878787878788</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>23686.36363636364</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>6027424.242424242</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>76.75909090909092</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>1.095454545454546</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>25.14928698752228</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>184.864286244801</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>73.39028768072886</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>33244.33056050703</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>8099225.713012476</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>78.03604055258468</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>1.402115517924341</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>24.33259287326793</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>186.7630291142877</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>70.34977122208244</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>19181.03548286615</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>3508313.93921783</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>76.65246033947408</v>
-      </c>
-      <c r="BE3" t="n">
+      <c r="N19" t="n">
+        <v>26.25714285714286</v>
+      </c>
+      <c r="O19" t="n">
+        <v>184.9428571428571</v>
+      </c>
+      <c r="P19" t="n">
+        <v>75.5</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>24457.14285714286</v>
+      </c>
+      <c r="R19" t="n">
+        <v>8100000</v>
+      </c>
+      <c r="S19" t="n">
+        <v>77.67142857142858</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1.457142857142857</v>
+      </c>
+      <c r="U19" t="n">
+        <v>27.08701298701299</v>
+      </c>
+      <c r="V19" t="n">
+        <v>183.4415584415584</v>
+      </c>
+      <c r="W19" t="n">
+        <v>74.42467532467533</v>
+      </c>
+      <c r="X19" t="n">
+        <v>23531.16883116883</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>5979220.779220779</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>76.70779220779221</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1.096103896103896</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>25.59909867837295</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>183.1228692850138</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>73.29243528074845</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>22174.38394121951</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>5978963.402294556</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>77.33729510110679</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>1.208599915938916</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>24.33053415111277</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>186.6280509291297</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>70.33227143710963</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>19356.47197232683</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>3512321.038810087</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>76.55925171954921</v>
+      </c>
+      <c r="AO19" t="n">
         <v>1</v>
       </c>
-      <c r="BF3" t="inlineStr">
-        <is>
-          <t>8f6APkLc</t>
-        </is>
-      </c>
-      <c r="BG3" t="inlineStr">
-        <is>
-          <t>YZPE6Sx7</t>
+      <c r="AP19" t="n">
+        <v>21.87142857142857</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>182.2619047619047</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>293.5714285714286</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>54285.71428571428</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>20939285.71428571</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>330.8571428571428</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>5.285714285714286</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>27.10952380952381</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>185.5095238095238</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>3</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>217</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>64285.71428571428</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>10871428.57142857</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>224.5714285714286</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>3</v>
+      </c>
+      <c r="BF19" t="inlineStr">
+        <is>
+          <t>M5BRZDsC</t>
+        </is>
+      </c>
+      <c r="BG19" t="inlineStr">
+        <is>
+          <t>4fuCGs9P</t>
         </is>
       </c>
     </row>

--- a/data/germany/p6_deployment/data_preparation/df_filled.xlsx
+++ b/data/germany/p6_deployment/data_preparation/df_filled.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BG10"/>
+  <dimension ref="A1:BG19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -495,222 +495,222 @@
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
+          <t>mean_age_player_start_home</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>mean_hei_player_start_home</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>mean_rat_player_start_home</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>mean_wage_player_start_home</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>mean_value_player_start_home</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>mean_pot_player_start_home</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>mean_rep_player_start_home</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>mean_age_player_start_away</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>mean_hei_player_start_away</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>mean_rat_player_start_away</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>mean_wage_player_start_away</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>mean_value_player_start_away</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>mean_pot_player_start_away</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>mean_rep_player_start_away</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>mean_age_player_sub_home</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>mean_hei_player_sub_home</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>mean_rat_player_sub_home</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>mean_wage_player_sub_home</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>mean_value_player_sub_home</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>mean_pot_player_sub_home</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>mean_rep_player_sub_home</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>mean_age_player_sub_away</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>mean_hei_player_sub_away</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>mean_rat_player_sub_away</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>mean_wage_player_sub_away</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>mean_value_player_sub_away</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>mean_pot_player_sub_away</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>mean_rep_player_sub_away</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
           <t>mean_age_player_miss_home</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>mean_hei_player_miss_home</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>n_player_miss_home</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>sum_rat_player_miss_home</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>sum_wage_player_miss_home</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>sum_value_player_miss_home</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>sum_pot_player_miss_home</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="AW1" s="1" t="inlineStr">
         <is>
           <t>sum_rep_player_miss_home</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="AX1" s="1" t="inlineStr">
         <is>
           <t>mean_age_player_miss_away</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="AY1" s="1" t="inlineStr">
         <is>
           <t>mean_hei_player_miss_away</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="AZ1" s="1" t="inlineStr">
         <is>
           <t>n_player_miss_away</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="BA1" s="1" t="inlineStr">
         <is>
           <t>sum_rat_player_miss_away</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="BB1" s="1" t="inlineStr">
         <is>
           <t>sum_wage_player_miss_away</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="BC1" s="1" t="inlineStr">
         <is>
           <t>sum_value_player_miss_away</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="BD1" s="1" t="inlineStr">
         <is>
           <t>sum_pot_player_miss_away</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="BE1" s="1" t="inlineStr">
         <is>
           <t>sum_rep_player_miss_away</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>mean_age_player_start_home</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>mean_hei_player_start_home</t>
-        </is>
-      </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>mean_rat_player_start_home</t>
-        </is>
-      </c>
-      <c r="AG1" s="1" t="inlineStr">
-        <is>
-          <t>mean_wage_player_start_home</t>
-        </is>
-      </c>
-      <c r="AH1" s="1" t="inlineStr">
-        <is>
-          <t>mean_value_player_start_home</t>
-        </is>
-      </c>
-      <c r="AI1" s="1" t="inlineStr">
-        <is>
-          <t>mean_pot_player_start_home</t>
-        </is>
-      </c>
-      <c r="AJ1" s="1" t="inlineStr">
-        <is>
-          <t>mean_rep_player_start_home</t>
-        </is>
-      </c>
-      <c r="AK1" s="1" t="inlineStr">
-        <is>
-          <t>mean_age_player_start_away</t>
-        </is>
-      </c>
-      <c r="AL1" s="1" t="inlineStr">
-        <is>
-          <t>mean_hei_player_start_away</t>
-        </is>
-      </c>
-      <c r="AM1" s="1" t="inlineStr">
-        <is>
-          <t>mean_rat_player_start_away</t>
-        </is>
-      </c>
-      <c r="AN1" s="1" t="inlineStr">
-        <is>
-          <t>mean_wage_player_start_away</t>
-        </is>
-      </c>
-      <c r="AO1" s="1" t="inlineStr">
-        <is>
-          <t>mean_value_player_start_away</t>
-        </is>
-      </c>
-      <c r="AP1" s="1" t="inlineStr">
-        <is>
-          <t>mean_pot_player_start_away</t>
-        </is>
-      </c>
-      <c r="AQ1" s="1" t="inlineStr">
-        <is>
-          <t>mean_rep_player_start_away</t>
-        </is>
-      </c>
-      <c r="AR1" s="1" t="inlineStr">
-        <is>
-          <t>mean_age_player_sub_home</t>
-        </is>
-      </c>
-      <c r="AS1" s="1" t="inlineStr">
-        <is>
-          <t>mean_hei_player_sub_home</t>
-        </is>
-      </c>
-      <c r="AT1" s="1" t="inlineStr">
-        <is>
-          <t>mean_rat_player_sub_home</t>
-        </is>
-      </c>
-      <c r="AU1" s="1" t="inlineStr">
-        <is>
-          <t>mean_wage_player_sub_home</t>
-        </is>
-      </c>
-      <c r="AV1" s="1" t="inlineStr">
-        <is>
-          <t>mean_value_player_sub_home</t>
-        </is>
-      </c>
-      <c r="AW1" s="1" t="inlineStr">
-        <is>
-          <t>mean_pot_player_sub_home</t>
-        </is>
-      </c>
-      <c r="AX1" s="1" t="inlineStr">
-        <is>
-          <t>mean_rep_player_sub_home</t>
-        </is>
-      </c>
-      <c r="AY1" s="1" t="inlineStr">
-        <is>
-          <t>mean_age_player_sub_away</t>
-        </is>
-      </c>
-      <c r="AZ1" s="1" t="inlineStr">
-        <is>
-          <t>mean_hei_player_sub_away</t>
-        </is>
-      </c>
-      <c r="BA1" s="1" t="inlineStr">
-        <is>
-          <t>mean_rat_player_sub_away</t>
-        </is>
-      </c>
-      <c r="BB1" s="1" t="inlineStr">
-        <is>
-          <t>mean_wage_player_sub_away</t>
-        </is>
-      </c>
-      <c r="BC1" s="1" t="inlineStr">
-        <is>
-          <t>mean_value_player_sub_away</t>
-        </is>
-      </c>
-      <c r="BD1" s="1" t="inlineStr">
-        <is>
-          <t>mean_pot_player_sub_away</t>
-        </is>
-      </c>
-      <c r="BE1" s="1" t="inlineStr">
-        <is>
-          <t>mean_rep_player_sub_away</t>
         </is>
       </c>
       <c r="BF1" s="1" t="inlineStr">
@@ -727,35 +727,35 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>4E8uaJWa</t>
+          <t>IHYEDIog</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45590.64583333334</v>
+        <v>45597.6875</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">petersen m 
+          <t xml:space="preserve">hartmann r 
   ger </t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">mewa arena
-  mainz </t>
+          <t xml:space="preserve">bayarena
+  leverkusen </t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>34000</v>
+        <v>30210</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>EuakNmc1</t>
+          <t>4jcj2zMd</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>88HSzjDr</t>
+          <t>nJQmYp1B</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -781,180 +781,180 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>29.5</v>
+        <v>26.43531746031746</v>
       </c>
       <c r="O2" t="n">
-        <v>186.5</v>
+        <v>184.2964285714286</v>
       </c>
       <c r="P2" t="n">
-        <v>2</v>
+        <v>84.00793650793651</v>
       </c>
       <c r="Q2" t="n">
-        <v>149</v>
+        <v>101621.4285714286</v>
       </c>
       <c r="R2" t="n">
-        <v>51000</v>
+        <v>51919642.85714286</v>
       </c>
       <c r="S2" t="n">
-        <v>10500000</v>
+        <v>86.07619047619048</v>
       </c>
       <c r="T2" t="n">
-        <v>151</v>
+        <v>3.121428571428571</v>
       </c>
       <c r="U2" t="n">
-        <v>2</v>
+        <v>24.68989898989899</v>
       </c>
       <c r="V2" t="n">
-        <v>23.14285714285714</v>
+        <v>185.9199134199134</v>
       </c>
       <c r="W2" t="n">
-        <v>184.2857142857143</v>
+        <v>76.38571428571429</v>
       </c>
       <c r="X2" t="n">
-        <v>7</v>
+        <v>27397.97979797979</v>
       </c>
       <c r="Y2" t="n">
-        <v>495</v>
+        <v>14030497.83549784</v>
       </c>
       <c r="Z2" t="n">
-        <v>105000</v>
+        <v>79.85642135642135</v>
       </c>
       <c r="AA2" t="n">
-        <v>34225000</v>
+        <v>1.501587301587302</v>
       </c>
       <c r="AB2" t="n">
-        <v>542</v>
+        <v>24.63209283713485</v>
       </c>
       <c r="AC2" t="n">
-        <v>9</v>
+        <v>181.4816860077364</v>
       </c>
       <c r="AD2" t="n">
-        <v>27.41111111111111</v>
+        <v>80.40254768574096</v>
       </c>
       <c r="AE2" t="n">
-        <v>183.4185185185186</v>
+        <v>79663.58543417367</v>
       </c>
       <c r="AF2" t="n">
-        <v>74.74444444444444</v>
+        <v>36154533.48005869</v>
       </c>
       <c r="AG2" t="n">
-        <v>25403.7037037037</v>
+        <v>83.88744831265841</v>
       </c>
       <c r="AH2" t="n">
-        <v>6466296.296296296</v>
+        <v>2.249593170601574</v>
       </c>
       <c r="AI2" t="n">
-        <v>76.9925925925926</v>
+        <v>24.53934837092732</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1.394444444444444</v>
+        <v>185.8327485380117</v>
       </c>
       <c r="AK2" t="n">
-        <v>26.23333333333333</v>
+        <v>74.44469507101086</v>
       </c>
       <c r="AL2" t="n">
-        <v>185.0833333333333</v>
+        <v>24816.29072681704</v>
       </c>
       <c r="AM2" t="n">
-        <v>75.36666666666666</v>
+        <v>11320962.82372598</v>
       </c>
       <c r="AN2" t="n">
-        <v>24250</v>
+        <v>78.18170426065164</v>
       </c>
       <c r="AO2" t="n">
-        <v>7858333.333333333</v>
+        <v>1.505012531328321</v>
       </c>
       <c r="AP2" t="n">
-        <v>77.56666666666668</v>
+        <v>26.75</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.433333333333334</v>
+        <v>179.5</v>
       </c>
       <c r="AR2" t="n">
-        <v>25.5323574086732</v>
+        <v>1.5</v>
       </c>
       <c r="AS2" t="n">
-        <v>183.4392496392497</v>
+        <v>123</v>
       </c>
       <c r="AT2" t="n">
-        <v>71.25817194501404</v>
+        <v>119500</v>
       </c>
       <c r="AU2" t="n">
-        <v>21590.52175894281</v>
+        <v>45500000</v>
       </c>
       <c r="AV2" t="n">
-        <v>3488168.479911901</v>
+        <v>128</v>
       </c>
       <c r="AW2" t="n">
-        <v>76.97357028935976</v>
+        <v>3.5</v>
       </c>
       <c r="AX2" t="n">
-        <v>1.179765702134123</v>
+        <v>22.27142857142857</v>
       </c>
       <c r="AY2" t="n">
-        <v>25.671170680324</v>
+        <v>183.347619047619</v>
       </c>
       <c r="AZ2" t="n">
-        <v>182.9419586102939</v>
+        <v>4.285714285714286</v>
       </c>
       <c r="BA2" t="n">
-        <v>73.37589671642876</v>
+        <v>298.4285714285714</v>
       </c>
       <c r="BB2" t="n">
-        <v>22314.55904253387</v>
+        <v>76285.71428571429</v>
       </c>
       <c r="BC2" t="n">
-        <v>6065735.080454759</v>
+        <v>20921428.57142857</v>
       </c>
       <c r="BD2" t="n">
-        <v>77.29628872906905</v>
+        <v>337.5714285714286</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.222533235262068</v>
+        <v>5.142857142857143</v>
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>vZA6VYpf</t>
+          <t>4fuCGs9P</t>
         </is>
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>4ljanukM</t>
+          <t>A15eUM4C</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>x0haJmIE</t>
+          <t>jVWMBdG5</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45591.4375</v>
+        <v>45598.47916666666</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">welz t 
+          <t xml:space="preserve">osmers h 
   ger </t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">wwk arena
-  augsburg </t>
+          <t xml:space="preserve">allianz arena
+  munich </t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>30660</v>
+        <v>75024</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>fTVNku3I</t>
+          <t>nVp0wiqd</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>nP1i5US1</t>
+          <t>pzHW4oaE</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -980,180 +980,180 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>26</v>
+        <v>27.33015873015873</v>
       </c>
       <c r="O3" t="n">
-        <v>184</v>
+        <v>183.8317460317461</v>
       </c>
       <c r="P3" t="n">
-        <v>5</v>
+        <v>83.3079365079365</v>
       </c>
       <c r="Q3" t="n">
-        <v>362</v>
+        <v>80646.03174603175</v>
       </c>
       <c r="R3" t="n">
-        <v>98000</v>
+        <v>47889325.3968254</v>
       </c>
       <c r="S3" t="n">
-        <v>19900000</v>
+        <v>85.68571428571428</v>
       </c>
       <c r="T3" t="n">
-        <v>371</v>
+        <v>3.242857142857142</v>
       </c>
       <c r="U3" t="n">
-        <v>5</v>
+        <v>26.48831168831169</v>
       </c>
       <c r="V3" t="n">
-        <v>23</v>
+        <v>186.5181818181818</v>
       </c>
       <c r="W3" t="n">
-        <v>182.6</v>
+        <v>74.45714285714287</v>
       </c>
       <c r="X3" t="n">
-        <v>5</v>
+        <v>26488.31168831169</v>
       </c>
       <c r="Y3" t="n">
-        <v>381</v>
+        <v>6066753.246753247</v>
       </c>
       <c r="Z3" t="n">
-        <v>193000</v>
+        <v>77.6922077922078</v>
       </c>
       <c r="AA3" t="n">
-        <v>97700000</v>
+        <v>1.337662337662338</v>
       </c>
       <c r="AB3" t="n">
-        <v>418</v>
+        <v>26.57194825298541</v>
       </c>
       <c r="AC3" t="n">
-        <v>10</v>
+        <v>183.2282513882746</v>
       </c>
       <c r="AD3" t="n">
-        <v>26.375</v>
+        <v>81.15302226153619</v>
       </c>
       <c r="AE3" t="n">
-        <v>184.875</v>
+        <v>74119.89379084967</v>
       </c>
       <c r="AF3" t="n">
-        <v>73.875</v>
+        <v>36113977.29925304</v>
       </c>
       <c r="AG3" t="n">
-        <v>23375</v>
+        <v>83.90506535947713</v>
       </c>
       <c r="AH3" t="n">
-        <v>5350000</v>
+        <v>2.647461791734237</v>
       </c>
       <c r="AI3" t="n">
-        <v>76.25</v>
+        <v>26.31236424394319</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1.125</v>
+        <v>182.3666248955722</v>
       </c>
       <c r="AK3" t="n">
-        <v>26.75</v>
+        <v>73.17681704260652</v>
       </c>
       <c r="AL3" t="n">
-        <v>186.1166666666666</v>
+        <v>25250.54302422724</v>
       </c>
       <c r="AM3" t="n">
-        <v>82.01060606060607</v>
+        <v>4284319.131161236</v>
       </c>
       <c r="AN3" t="n">
-        <v>58430.30303030303</v>
+        <v>75.82330827067669</v>
       </c>
       <c r="AO3" t="n">
-        <v>37446212.12121212</v>
+        <v>1.102756892230576</v>
       </c>
       <c r="AP3" t="n">
-        <v>83.99545454545455</v>
+        <v>22.1</v>
       </c>
       <c r="AQ3" t="n">
-        <v>2.607575757575757</v>
+        <v>184.7619047619048</v>
       </c>
       <c r="AR3" t="n">
-        <v>24.55501126553758</v>
+        <v>5.428571428571429</v>
       </c>
       <c r="AS3" t="n">
-        <v>184.6870949469634</v>
+        <v>395</v>
       </c>
       <c r="AT3" t="n">
-        <v>72.37051989190148</v>
+        <v>219142.8571428571</v>
       </c>
       <c r="AU3" t="n">
-        <v>20727.83837750943</v>
+        <v>101435714.2857143</v>
       </c>
       <c r="AV3" t="n">
-        <v>4951722.029189135</v>
+        <v>444.1428571428572</v>
       </c>
       <c r="AW3" t="n">
-        <v>76.69494443178654</v>
+        <v>7.714285714285714</v>
       </c>
       <c r="AX3" t="n">
-        <v>1.086936881344776</v>
+        <v>28.88095238095238</v>
       </c>
       <c r="AY3" t="n">
-        <v>24.80098162071846</v>
+        <v>179.547619047619</v>
       </c>
       <c r="AZ3" t="n">
-        <v>184.2422520948837</v>
+        <v>2.857142857142857</v>
       </c>
       <c r="BA3" t="n">
-        <v>77.55001075922128</v>
+        <v>212.8571428571429</v>
       </c>
       <c r="BB3" t="n">
-        <v>43375.39935697831</v>
+        <v>90285.71428571429</v>
       </c>
       <c r="BC3" t="n">
-        <v>21942478.16510974</v>
+        <v>16142857.14285714</v>
       </c>
       <c r="BD3" t="n">
-        <v>82.87087478798004</v>
+        <v>213.7142857142857</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.863268651426546</v>
+        <v>4</v>
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>YZPE6Sx7</t>
+          <t>8f6APkLc</t>
         </is>
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>0jdIgO6t</t>
+          <t>UgdQz0fK</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>ELNeaSQr</t>
+          <t>485V7EFU</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45591.4375</v>
+        <v>45598.47916666666</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">jablonski s 
+          <t xml:space="preserve">exner f 
   ger </t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">red bull arena
-  leipzig </t>
+          <t xml:space="preserve">deutsche bank park
+  frankfurt </t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>47069</v>
+        <v>58000</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>KbS1suSm</t>
+          <t>8vndvXTk</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>fiEQZ7C7</t>
+          <t>8Y2m6ADe</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -1179,156 +1179,156 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>23.66666666666667</v>
+        <v>24.50277777777778</v>
       </c>
       <c r="O4" t="n">
-        <v>181.6666666666667</v>
+        <v>185.4416666666667</v>
       </c>
       <c r="P4" t="n">
-        <v>6</v>
+        <v>76.60277777777779</v>
       </c>
       <c r="Q4" t="n">
-        <v>470</v>
+        <v>34427.77777777778</v>
       </c>
       <c r="R4" t="n">
-        <v>313000</v>
+        <v>14699166.66666667</v>
       </c>
       <c r="S4" t="n">
-        <v>158000000</v>
+        <v>81.47222222222221</v>
       </c>
       <c r="T4" t="n">
-        <v>507</v>
+        <v>1.697222222222222</v>
       </c>
       <c r="U4" t="n">
-        <v>12</v>
+        <v>28.21296296296296</v>
       </c>
       <c r="V4" t="n">
-        <v>25.2</v>
+        <v>185.9421296296296</v>
       </c>
       <c r="W4" t="n">
-        <v>185.8</v>
+        <v>71.62037037037037</v>
       </c>
       <c r="X4" t="n">
-        <v>5</v>
+        <v>16814.81481481481</v>
       </c>
       <c r="Y4" t="n">
-        <v>350</v>
+        <v>2233912.037037037</v>
       </c>
       <c r="Z4" t="n">
-        <v>83000</v>
+        <v>73.80092592592592</v>
       </c>
       <c r="AA4" t="n">
-        <v>20000000</v>
+        <v>1</v>
       </c>
       <c r="AB4" t="n">
-        <v>374</v>
+        <v>22.94464285714286</v>
       </c>
       <c r="AC4" t="n">
-        <v>5</v>
+        <v>184.4420576603847</v>
       </c>
       <c r="AD4" t="n">
-        <v>25.78409090909091</v>
+        <v>73.12410042964555</v>
       </c>
       <c r="AE4" t="n">
-        <v>183.7179292929293</v>
+        <v>26518.00401978973</v>
       </c>
       <c r="AF4" t="n">
-        <v>80.63627946127946</v>
+        <v>9585556.073625622</v>
       </c>
       <c r="AG4" t="n">
-        <v>57536.44781144781</v>
+        <v>80.91495052566481</v>
       </c>
       <c r="AH4" t="n">
-        <v>31560500.84175084</v>
+        <v>1.43036324577678</v>
       </c>
       <c r="AI4" t="n">
-        <v>84.16797138047139</v>
+        <v>26.12187142063303</v>
       </c>
       <c r="AJ4" t="n">
-        <v>2.25206228956229</v>
+        <v>185.2048465810076</v>
       </c>
       <c r="AK4" t="n">
-        <v>26.8425925925926</v>
+        <v>68.78568215410321</v>
       </c>
       <c r="AL4" t="n">
-        <v>184.0259259259259</v>
+        <v>15808.82069426961</v>
       </c>
       <c r="AM4" t="n">
-        <v>76.44444444444446</v>
+        <v>1769831.819367423</v>
       </c>
       <c r="AN4" t="n">
-        <v>26577.77777777778</v>
+        <v>73.6982028978933</v>
       </c>
       <c r="AO4" t="n">
-        <v>11194444.44444445</v>
+        <v>1</v>
       </c>
       <c r="AP4" t="n">
-        <v>78.89259259259259</v>
+        <v>19.61904761904762</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.642592592592593</v>
+        <v>176.3809523809524</v>
       </c>
       <c r="AR4" t="n">
-        <v>25.4968564180058</v>
+        <v>1.714285714285714</v>
       </c>
       <c r="AS4" t="n">
-        <v>184.6269744008715</v>
+        <v>105.8571428571429</v>
       </c>
       <c r="AT4" t="n">
-        <v>78.41534033203925</v>
+        <v>12142.85714285714</v>
       </c>
       <c r="AU4" t="n">
-        <v>51833.10860894065</v>
+        <v>3503571.428571429</v>
       </c>
       <c r="AV4" t="n">
-        <v>24091513.14765672</v>
+        <v>133.7142857142857</v>
       </c>
       <c r="AW4" t="n">
-        <v>82.21641214965518</v>
+        <v>2</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.959328468229397</v>
+        <v>26.52380952380952</v>
       </c>
       <c r="AY4" t="n">
-        <v>26.39972312203433</v>
+        <v>186.2357142857143</v>
       </c>
       <c r="AZ4" t="n">
-        <v>183.8019009975532</v>
+        <v>3.571428571428572</v>
       </c>
       <c r="BA4" t="n">
-        <v>73.9994447581404</v>
+        <v>251.7142857142857</v>
       </c>
       <c r="BB4" t="n">
-        <v>23438.13618367394</v>
+        <v>59714.28571428572</v>
       </c>
       <c r="BC4" t="n">
-        <v>6642373.196660954</v>
+        <v>9000000</v>
       </c>
       <c r="BD4" t="n">
-        <v>77.11334289280514</v>
+        <v>263.2857142857143</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.351906528508359</v>
+        <v>4</v>
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>vZA6VYpf</t>
+          <t>hpYJ6izc</t>
         </is>
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>2VSFgl3c</t>
+          <t>K6A2elS9</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>Mku6FvHt</t>
+          <t>8MVuSH0n</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45591.4375</v>
+        <v>45598.47916666666</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1338,21 +1338,21 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">millerntor stadion
-  hamburg </t>
+          <t xml:space="preserve">prezero arena
+  sinsheim </t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>29546</v>
+        <v>30150</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
+          <t>hQAtP9Sl</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
           <t>ILyJuN3g</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>nwkTahLL</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -1378,180 +1378,180 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>24.57142857142857</v>
+        <v>27.41428571428572</v>
       </c>
       <c r="O5" t="n">
-        <v>186.7142857142857</v>
+        <v>185.9432539682539</v>
       </c>
       <c r="P5" t="n">
-        <v>7</v>
+        <v>75.18055555555556</v>
       </c>
       <c r="Q5" t="n">
-        <v>473</v>
+        <v>30215.47619047619</v>
       </c>
       <c r="R5" t="n">
-        <v>98000</v>
+        <v>7743611.111111111</v>
       </c>
       <c r="S5" t="n">
-        <v>13640000</v>
+        <v>78.81071428571428</v>
       </c>
       <c r="T5" t="n">
-        <v>507</v>
+        <v>1.638492063492064</v>
       </c>
       <c r="U5" t="n">
-        <v>7</v>
+        <v>26.93116883116883</v>
       </c>
       <c r="V5" t="n">
-        <v>24.57142857142857</v>
+        <v>185.1207792207792</v>
       </c>
       <c r="W5" t="n">
-        <v>182.8571428571429</v>
+        <v>70.70259740259739</v>
       </c>
       <c r="X5" t="n">
-        <v>7</v>
+        <v>17327.27272727273</v>
       </c>
       <c r="Y5" t="n">
-        <v>528</v>
+        <v>2314675.324675325</v>
       </c>
       <c r="Z5" t="n">
-        <v>271000</v>
+        <v>73.32857142857142</v>
       </c>
       <c r="AA5" t="n">
-        <v>90300000</v>
+        <v>1</v>
       </c>
       <c r="AB5" t="n">
-        <v>561</v>
+        <v>24.38693758205036</v>
       </c>
       <c r="AC5" t="n">
-        <v>12</v>
+        <v>185.0631578947368</v>
       </c>
       <c r="AD5" t="n">
-        <v>26.83636363636363</v>
+        <v>71.22855352667383</v>
       </c>
       <c r="AE5" t="n">
-        <v>185.0575757575757</v>
+        <v>23816.34443250985</v>
       </c>
       <c r="AF5" t="n">
-        <v>70.7530303030303</v>
+        <v>5203475.653419263</v>
       </c>
       <c r="AG5" t="n">
-        <v>17348.48484848485</v>
+        <v>77.60978040338942</v>
       </c>
       <c r="AH5" t="n">
-        <v>2350454.545454545</v>
+        <v>1.178338703902614</v>
       </c>
       <c r="AI5" t="n">
-        <v>73.5</v>
+        <v>25.76829573934837</v>
       </c>
       <c r="AJ5" t="n">
+        <v>184.8265664160401</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>67.93120300751879</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>15998.24561403509</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>1688358.395989975</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>71.68082706766917</v>
+      </c>
+      <c r="AO5" t="n">
         <v>1</v>
       </c>
-      <c r="AK5" t="n">
-        <v>24.64583333333334</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>184.6180555555555</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>75.14236111111111</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>35940.97222222223</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>9807986.111111112</v>
-      </c>
       <c r="AP5" t="n">
-        <v>79.76388888888889</v>
+        <v>26.17431972789116</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.378472222222222</v>
+        <v>182.8818027210884</v>
       </c>
       <c r="AR5" t="n">
-        <v>26.00745614035087</v>
+        <v>6.428571428571429</v>
       </c>
       <c r="AS5" t="n">
-        <v>185.053216374269</v>
+        <v>477.7142857142857</v>
       </c>
       <c r="AT5" t="n">
-        <v>67.91973684210527</v>
+        <v>170857.1428571429</v>
       </c>
       <c r="AU5" t="n">
-        <v>15997.95321637427</v>
+        <v>41542857.14285714</v>
       </c>
       <c r="AV5" t="n">
-        <v>1628640.350877193</v>
+        <v>498.7142857142857</v>
       </c>
       <c r="AW5" t="n">
-        <v>71.40540935672514</v>
+        <v>10</v>
       </c>
       <c r="AX5" t="n">
-        <v>1</v>
+        <v>27.93571428571429</v>
       </c>
       <c r="AY5" t="n">
-        <v>24.99687470682052</v>
+        <v>187.1309523809524</v>
       </c>
       <c r="AZ5" t="n">
-        <v>184.8248125605904</v>
+        <v>4.285714285714286</v>
       </c>
       <c r="BA5" t="n">
-        <v>73.45223943511482</v>
+        <v>282.1428571428572</v>
       </c>
       <c r="BB5" t="n">
-        <v>33066.15073594562</v>
+        <v>57714.28571428572</v>
       </c>
       <c r="BC5" t="n">
-        <v>8144428.56388967</v>
+        <v>4547142.857142857</v>
       </c>
       <c r="BD5" t="n">
-        <v>78.14788265784783</v>
+        <v>295.1428571428572</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.427334816169956</v>
+        <v>4.285714285714286</v>
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>IkCftsQm</t>
+          <t>4ljanukM</t>
         </is>
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>4fuCGs9P</t>
+          <t>f3ddUIXs</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>rwXP4l3L</t>
+          <t>2q7yHiho</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45591.4375</v>
+        <v>45598.47916666666</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">hartmann r 
+          <t xml:space="preserve">dingert c 
   ger </t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">mhparena
-  stuttgart </t>
+          <t xml:space="preserve">holstein stadion
+  kiel </t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>60449</v>
+        <v>15034</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>nJQmYp1B</t>
+          <t>63WsD2ei</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>63WsD2ei</t>
+          <t>KWixEVWi</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -1577,180 +1577,180 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>22.5</v>
+        <v>26.53293650793651</v>
       </c>
       <c r="O6" t="n">
-        <v>184</v>
+        <v>186.0357142857143</v>
       </c>
       <c r="P6" t="n">
-        <v>6</v>
+        <v>69.74603174603175</v>
       </c>
       <c r="Q6" t="n">
-        <v>422</v>
+        <v>16501.98412698413</v>
       </c>
       <c r="R6" t="n">
-        <v>117000</v>
+        <v>1887976.19047619</v>
       </c>
       <c r="S6" t="n">
-        <v>41050000</v>
+        <v>72.18968253968254</v>
       </c>
       <c r="T6" t="n">
-        <v>473</v>
+        <v>1</v>
       </c>
       <c r="U6" t="n">
-        <v>8</v>
+        <v>26.88571428571428</v>
       </c>
       <c r="V6" t="n">
-        <v>28</v>
+        <v>186.9428571428571</v>
       </c>
       <c r="W6" t="n">
-        <v>185.3333333333333</v>
+        <v>72.77142857142857</v>
       </c>
       <c r="X6" t="n">
+        <v>22328.57142857143</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>3284285.714285714</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>74.51428571428572</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.028571428571428</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>25.65921247217423</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>184.5859378825381</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>68.39975163770522</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>15890.84512523545</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>1848853.061507524</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>72.72310639670887</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>25.90516989404457</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>184.9050237486299</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>69.37879064669345</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>19860.39459261965</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>2123343.989769821</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>72.11987577639752</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>1.045670442089879</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>25.39285714285714</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>188.7261904761905</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>2.285714285714286</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>158.2857142857143</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>34714.28571428572</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>4528571.428571428</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>167.4285714285714</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>2.285714285714286</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>24.38095238095238</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>186.4523809523809</v>
+      </c>
+      <c r="AZ6" t="n">
         <v>3</v>
       </c>
-      <c r="Y6" t="n">
-        <v>210</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>49000</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>6100000</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>219</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>3</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>24.84545454545455</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>186.2738816738817</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>76.24444444444445</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>27402.7417027417</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>13736172.43867244</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>79.57070707070706</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>1.479365079365079</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>26.67731481481482</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>185.7824074074074</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>69.85185185185185</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>16604.16666666667</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>1891527.777777778</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>72.14722222222223</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>24.32318295739348</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>185.1436507936508</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>74.05409356725147</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>24520.4260651629</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>11011000.41771094</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>78.28508771929826</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>1.509147869674186</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>25.68574788420326</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>184.6078366205369</v>
-      </c>
       <c r="BA6" t="n">
-        <v>68.43607388035306</v>
+        <v>202.5714285714286</v>
       </c>
       <c r="BB6" t="n">
-        <v>15872.65264610802</v>
+        <v>52571.42857142857</v>
       </c>
       <c r="BC6" t="n">
-        <v>1860783.117213323</v>
+        <v>5978571.428571428</v>
       </c>
       <c r="BD6" t="n">
-        <v>72.72241200828157</v>
+        <v>216.4285714285714</v>
       </c>
       <c r="BE6" t="n">
-        <v>1</v>
+        <v>3.285714285714286</v>
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>K6A2elS9</t>
+          <t>GzfvcwRj</t>
         </is>
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>hpYJ6izc</t>
+          <t>KUx4Q7x1</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>MiACepQ7</t>
+          <t>AoSdOZaB</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45591.5625</v>
+        <v>45598.47916666666</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">badstubner f 
+          <t xml:space="preserve">welz t 
   ger </t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">weserstadion
-  bremen </t>
+          <t xml:space="preserve">volkswagen arena
+  wolfsburg </t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>42100</v>
+        <v>28917</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ig1f1fy3</t>
+          <t>nwkTahLL</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>4jcj2zMd</t>
+          <t>fTVNku3I</t>
         </is>
       </c>
       <c r="H7" t="n">
@@ -1776,180 +1776,180 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>26.4</v>
+        <v>24.64583333333334</v>
       </c>
       <c r="O7" t="n">
-        <v>186.8</v>
+        <v>184.6180555555555</v>
       </c>
       <c r="P7" t="n">
-        <v>5</v>
+        <v>75.14236111111111</v>
       </c>
       <c r="Q7" t="n">
-        <v>367</v>
+        <v>35940.97222222223</v>
       </c>
       <c r="R7" t="n">
-        <v>113000</v>
+        <v>9807986.111111112</v>
       </c>
       <c r="S7" t="n">
-        <v>24000000</v>
+        <v>79.76388888888889</v>
       </c>
       <c r="T7" t="n">
-        <v>382</v>
+        <v>1.378472222222222</v>
       </c>
       <c r="U7" t="n">
-        <v>5</v>
+        <v>26.375</v>
       </c>
       <c r="V7" t="n">
-        <v>23.5</v>
+        <v>184.875</v>
       </c>
       <c r="W7" t="n">
-        <v>182</v>
+        <v>73.875</v>
       </c>
       <c r="X7" t="n">
-        <v>2</v>
+        <v>23375</v>
       </c>
       <c r="Y7" t="n">
-        <v>160</v>
+        <v>5350000</v>
       </c>
       <c r="Z7" t="n">
-        <v>150000</v>
+        <v>76.25</v>
       </c>
       <c r="AA7" t="n">
-        <v>77000000</v>
+        <v>1.125</v>
       </c>
       <c r="AB7" t="n">
-        <v>173</v>
+        <v>24.97827355822712</v>
       </c>
       <c r="AC7" t="n">
-        <v>4</v>
+        <v>184.7069821947918</v>
       </c>
       <c r="AD7" t="n">
-        <v>27.19242424242424</v>
+        <v>73.26382427771748</v>
       </c>
       <c r="AE7" t="n">
-        <v>183.3030303030303</v>
+        <v>32866.22444033434</v>
       </c>
       <c r="AF7" t="n">
-        <v>74.46515151515152</v>
+        <v>8046176.864286385</v>
       </c>
       <c r="AG7" t="n">
-        <v>23619.69696969697</v>
+        <v>78.16485180196482</v>
       </c>
       <c r="AH7" t="n">
-        <v>5986363.636363637</v>
+        <v>1.394858413859962</v>
       </c>
       <c r="AI7" t="n">
-        <v>76.65909090909091</v>
+        <v>24.37182783799325</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1.096969696969697</v>
+        <v>184.978548915579</v>
       </c>
       <c r="AK7" t="n">
-        <v>26.4412037037037</v>
+        <v>72.2266793878636</v>
       </c>
       <c r="AL7" t="n">
-        <v>184.2625</v>
+        <v>20481.00432357951</v>
       </c>
       <c r="AM7" t="n">
-        <v>83.95925925925926</v>
+        <v>4975501.999045232</v>
       </c>
       <c r="AN7" t="n">
-        <v>101558.3333333333</v>
+        <v>76.86839392854429</v>
       </c>
       <c r="AO7" t="n">
-        <v>51714583.33333334</v>
+        <v>1.087504339853964</v>
       </c>
       <c r="AP7" t="n">
-        <v>86.03888888888889</v>
+        <v>23.84149659863946</v>
       </c>
       <c r="AQ7" t="n">
-        <v>3.108333333333333</v>
+        <v>183.1982993197279</v>
       </c>
       <c r="AR7" t="n">
-        <v>24.07080836148342</v>
+        <v>5.428571428571429</v>
       </c>
       <c r="AS7" t="n">
-        <v>186.8438371950957</v>
+        <v>401.7142857142857</v>
       </c>
       <c r="AT7" t="n">
-        <v>70.20246482477604</v>
+        <v>192571.4285714286</v>
       </c>
       <c r="AU7" t="n">
-        <v>19369.58767141834</v>
+        <v>58300000</v>
       </c>
       <c r="AV7" t="n">
-        <v>3515300.471204361</v>
+        <v>431.8571428571428</v>
       </c>
       <c r="AW7" t="n">
-        <v>76.60616404317777</v>
+        <v>8.428571428571429</v>
       </c>
       <c r="AX7" t="n">
-        <v>1</v>
+        <v>25.87380952380952</v>
       </c>
       <c r="AY7" t="n">
-        <v>24.52933594490428</v>
+        <v>183.9452380952381</v>
       </c>
       <c r="AZ7" t="n">
-        <v>180.4875339609528</v>
+        <v>4.857142857142857</v>
       </c>
       <c r="BA7" t="n">
-        <v>80.81023356711106</v>
+        <v>343</v>
       </c>
       <c r="BB7" t="n">
-        <v>82370.35235146689</v>
+        <v>85000</v>
       </c>
       <c r="BC7" t="n">
-        <v>40076881.01556413</v>
+        <v>13467857.14285714</v>
       </c>
       <c r="BD7" t="n">
-        <v>84.40206819569934</v>
+        <v>353.8571428571428</v>
       </c>
       <c r="BE7" t="n">
-        <v>2.345666687727722</v>
+        <v>4.857142857142857</v>
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>f3ddUIXs</t>
+          <t>0jdIgO6t</t>
         </is>
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>UgdQz0fK</t>
+          <t>IkCftsQm</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>WQadeyWO</t>
+          <t>dr2N9zoI</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45592.47916666666</v>
+        <v>45598.60416666666</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">stieler t 
+          <t xml:space="preserve">jablonski s 
   ger </t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">vonovia ruhrstadion
-  bochum </t>
+          <t xml:space="preserve">signal iduna park
+  dortmund </t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>26000</v>
+        <v>81365</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>8Y2m6ADe</t>
+          <t>nP1i5US1</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>nVp0wiqd</t>
+          <t>KbS1suSm</t>
         </is>
       </c>
       <c r="H8" t="n">
@@ -1975,180 +1975,180 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>25.5</v>
+        <v>26.62987012987013</v>
       </c>
       <c r="O8" t="n">
-        <v>181.75</v>
+        <v>186.074025974026</v>
       </c>
       <c r="P8" t="n">
-        <v>4</v>
+        <v>81.97012987012987</v>
       </c>
       <c r="Q8" t="n">
-        <v>277</v>
+        <v>58329.87012987013</v>
       </c>
       <c r="R8" t="n">
-        <v>70000</v>
+        <v>37570779.22077922</v>
       </c>
       <c r="S8" t="n">
-        <v>9375000</v>
+        <v>84.0090909090909</v>
       </c>
       <c r="T8" t="n">
-        <v>288</v>
+        <v>2.585714285714286</v>
       </c>
       <c r="U8" t="n">
-        <v>4</v>
+        <v>25.92604617604617</v>
       </c>
       <c r="V8" t="n">
-        <v>22.2</v>
+        <v>183.647113997114</v>
       </c>
       <c r="W8" t="n">
-        <v>185.8</v>
+        <v>80.65649350649349</v>
       </c>
       <c r="X8" t="n">
-        <v>5</v>
+        <v>57380.44733044733</v>
       </c>
       <c r="Y8" t="n">
-        <v>368</v>
+        <v>31258207.07070708</v>
       </c>
       <c r="Z8" t="n">
-        <v>195000</v>
+        <v>84.08048340548341</v>
       </c>
       <c r="AA8" t="n">
-        <v>67150000</v>
+        <v>2.263672438672439</v>
       </c>
       <c r="AB8" t="n">
-        <v>412</v>
+        <v>25.06470693540574</v>
       </c>
       <c r="AC8" t="n">
-        <v>6</v>
+        <v>184.34209843427</v>
       </c>
       <c r="AD8" t="n">
-        <v>28.36666666666666</v>
+        <v>77.62269829781992</v>
       </c>
       <c r="AE8" t="n">
-        <v>185.8416666666666</v>
+        <v>43666.30869253603</v>
       </c>
       <c r="AF8" t="n">
-        <v>71.63333333333333</v>
+        <v>21783888.84740499</v>
       </c>
       <c r="AG8" t="n">
-        <v>16977.77777777778</v>
+        <v>82.71285065860476</v>
       </c>
       <c r="AH8" t="n">
-        <v>2206805.555555555</v>
+        <v>1.891205062567291</v>
       </c>
       <c r="AI8" t="n">
-        <v>73.67222222222222</v>
+        <v>25.52409121543354</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1</v>
+        <v>185.1266923436041</v>
       </c>
       <c r="AK8" t="n">
-        <v>27.29259259259259</v>
+        <v>78.15957742746221</v>
       </c>
       <c r="AL8" t="n">
-        <v>183.6555555555556</v>
+        <v>50919.45023623485</v>
       </c>
       <c r="AM8" t="n">
-        <v>83.06296296296296</v>
+        <v>23002770.19799148</v>
       </c>
       <c r="AN8" t="n">
-        <v>79531.48148148147</v>
+        <v>82.0515675568473</v>
       </c>
       <c r="AO8" t="n">
-        <v>46472731.48148149</v>
+        <v>1.956210115625197</v>
       </c>
       <c r="AP8" t="n">
-        <v>85.54074074074073</v>
+        <v>21.76190476190476</v>
       </c>
       <c r="AQ8" t="n">
-        <v>3.190740740740741</v>
+        <v>183.8333333333333</v>
       </c>
       <c r="AR8" t="n">
-        <v>26.01060437670344</v>
+        <v>2.428571428571428</v>
       </c>
       <c r="AS8" t="n">
-        <v>185.1249525901229</v>
+        <v>183.2857142857143</v>
       </c>
       <c r="AT8" t="n">
-        <v>68.8201379517169</v>
+        <v>88714.28571428571</v>
       </c>
       <c r="AU8" t="n">
-        <v>15715.55396787595</v>
+        <v>50342857.14285714</v>
       </c>
       <c r="AV8" t="n">
-        <v>1790242.385753222</v>
+        <v>204.5714285714286</v>
       </c>
       <c r="AW8" t="n">
-        <v>73.78825425806851</v>
+        <v>4.857142857142857</v>
       </c>
       <c r="AX8" t="n">
-        <v>1</v>
+        <v>24.66190476190476</v>
       </c>
       <c r="AY8" t="n">
-        <v>26.56200980392157</v>
+        <v>181.8119047619048</v>
       </c>
       <c r="AZ8" t="n">
-        <v>182.9505038126362</v>
+        <v>3.571428571428572</v>
       </c>
       <c r="BA8" t="n">
-        <v>81.22238562091503</v>
+        <v>275.4285714285714</v>
       </c>
       <c r="BB8" t="n">
-        <v>74119.89379084967</v>
+        <v>170000</v>
       </c>
       <c r="BC8" t="n">
-        <v>35712140.18246188</v>
+        <v>69500000</v>
       </c>
       <c r="BD8" t="n">
-        <v>83.88924291938997</v>
+        <v>299.8571428571428</v>
       </c>
       <c r="BE8" t="n">
-        <v>2.650108932461874</v>
+        <v>7.714285714285714</v>
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>KUx4Q7x1</t>
+          <t>2VSFgl3c</t>
         </is>
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>GzfvcwRj</t>
+          <t>YZPE6Sx7</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>ABBmcc1C</t>
+          <t>GnZmQeVb</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45592.5625</v>
+        <v>45599.47916666666</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">brych f 
+          <t xml:space="preserve">petersen m 
   ger </t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">stadion an der alten forsterei
-  berlin </t>
+          <t xml:space="preserve">europa park stadion
+  freiburg </t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>22012</v>
+        <v>34700</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>pzHW4oaE</t>
+          <t>fiEQZ7C7</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>8vndvXTk</t>
+          <t>EuakNmc1</t>
         </is>
       </c>
       <c r="H9" t="n">
@@ -2174,344 +2174,2135 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>28.5</v>
+        <v>26.85079365079365</v>
       </c>
       <c r="O9" t="n">
-        <v>181.5</v>
+        <v>183.9936507936507</v>
       </c>
       <c r="P9" t="n">
-        <v>4</v>
+        <v>76.30952380952382</v>
       </c>
       <c r="Q9" t="n">
-        <v>298</v>
+        <v>26323.80952380953</v>
       </c>
       <c r="R9" t="n">
-        <v>125000</v>
+        <v>10909523.80952381</v>
       </c>
       <c r="S9" t="n">
-        <v>23600000</v>
+        <v>78.85079365079365</v>
       </c>
       <c r="T9" t="n">
-        <v>301</v>
+        <v>1.622222222222222</v>
       </c>
       <c r="U9" t="n">
-        <v>6</v>
+        <v>27.33809523809524</v>
       </c>
       <c r="V9" t="n">
-        <v>20</v>
+        <v>183.2730158730159</v>
       </c>
       <c r="W9" t="n">
-        <v>180</v>
+        <v>74.70952380952382</v>
       </c>
       <c r="X9" t="n">
-        <v>3</v>
+        <v>25246.03174603175</v>
       </c>
       <c r="Y9" t="n">
-        <v>197</v>
+        <v>6458253.968253968</v>
       </c>
       <c r="Z9" t="n">
-        <v>37000</v>
+        <v>77.03650793650793</v>
       </c>
       <c r="AA9" t="n">
-        <v>13075000</v>
+        <v>1.395238095238095</v>
       </c>
       <c r="AB9" t="n">
-        <v>238</v>
+        <v>26.57391233589338</v>
       </c>
       <c r="AC9" t="n">
-        <v>4</v>
+        <v>183.8710171815762</v>
       </c>
       <c r="AD9" t="n">
-        <v>26.52424242424243</v>
+        <v>74.25122475867818</v>
       </c>
       <c r="AE9" t="n">
-        <v>186.5287878787879</v>
+        <v>24049.01468804705</v>
       </c>
       <c r="AF9" t="n">
-        <v>74.51818181818182</v>
+        <v>7097544.372648165</v>
       </c>
       <c r="AG9" t="n">
-        <v>26721.21212121212</v>
+        <v>77.17198098294863</v>
       </c>
       <c r="AH9" t="n">
-        <v>6124848.484848485</v>
+        <v>1.383266820354104</v>
       </c>
       <c r="AI9" t="n">
-        <v>77.65606060606061</v>
+        <v>25.45630635029132</v>
       </c>
       <c r="AJ9" t="n">
-        <v>1.333333333333334</v>
+        <v>183.5277601949871</v>
       </c>
       <c r="AK9" t="n">
-        <v>24.34722222222222</v>
+        <v>71.23809696127255</v>
       </c>
       <c r="AL9" t="n">
-        <v>185.6458333333334</v>
+        <v>21758.26234800141</v>
       </c>
       <c r="AM9" t="n">
-        <v>76.34722222222223</v>
+        <v>3515278.86513457</v>
       </c>
       <c r="AN9" t="n">
-        <v>33784.72222222223</v>
+        <v>77.08658965978735</v>
       </c>
       <c r="AO9" t="n">
-        <v>14545833.33333334</v>
+        <v>1.187698332921685</v>
       </c>
       <c r="AP9" t="n">
-        <v>81.46527777777777</v>
+        <v>26.15680272108844</v>
       </c>
       <c r="AQ9" t="n">
-        <v>1.652777777777778</v>
+        <v>185.6721088435374</v>
       </c>
       <c r="AR9" t="n">
-        <v>26.37275828460039</v>
+        <v>5.285714285714286</v>
       </c>
       <c r="AS9" t="n">
-        <v>182.4360623781676</v>
+        <v>374.7142857142857</v>
       </c>
       <c r="AT9" t="n">
-        <v>73.14795321637428</v>
+        <v>99142.85714285714</v>
       </c>
       <c r="AU9" t="n">
-        <v>25075.63352826511</v>
+        <v>23757142.85714286</v>
       </c>
       <c r="AV9" t="n">
-        <v>4228372.319688109</v>
+        <v>393.2857142857143</v>
       </c>
       <c r="AW9" t="n">
-        <v>75.84385964912281</v>
+        <v>5.714285714285714</v>
       </c>
       <c r="AX9" t="n">
-        <v>1.119883040935673</v>
+        <v>27.75</v>
       </c>
       <c r="AY9" t="n">
-        <v>23.05</v>
+        <v>185.3333333333333</v>
       </c>
       <c r="AZ9" t="n">
-        <v>184.3594839371155</v>
+        <v>1.333333333333333</v>
       </c>
       <c r="BA9" t="n">
-        <v>73.11353383458646</v>
+        <v>100.1666666666667</v>
       </c>
       <c r="BB9" t="n">
-        <v>26614.75468975469</v>
+        <v>36166.66666666666</v>
       </c>
       <c r="BC9" t="n">
-        <v>9430023.752563225</v>
+        <v>9183333.333333334</v>
       </c>
       <c r="BD9" t="n">
-        <v>80.8382756132756</v>
+        <v>102</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.460423786739576</v>
+        <v>1.666666666666667</v>
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>A15eUM4C</t>
+          <t>pfoInmcq</t>
         </is>
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>UgdQz0fK</t>
+          <t>M5BRZDsC</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>zyC4c6ee</t>
+          <t>raQ4MDUN</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45592.64583333334</v>
+        <v>45599.5625</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">storks s 
+          <t xml:space="preserve">badstubner f 
   ger </t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">borussia park
+  monchengladbach </t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>54042</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>88HSzjDr</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Ig1f1fy3</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>59</v>
+      </c>
+      <c r="I10" t="n">
+        <v>591</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="N10" t="n">
+        <v>26.28571428571428</v>
+      </c>
+      <c r="O10" t="n">
+        <v>184.9571428571428</v>
+      </c>
+      <c r="P10" t="n">
+        <v>75.34285714285714</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>24285.71428571429</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7837142.857142857</v>
+      </c>
+      <c r="S10" t="n">
+        <v>77.52857142857144</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1.414285714285714</v>
+      </c>
+      <c r="U10" t="n">
+        <v>27.10779220779221</v>
+      </c>
+      <c r="V10" t="n">
+        <v>183.2025974025974</v>
+      </c>
+      <c r="W10" t="n">
+        <v>74.42727272727272</v>
+      </c>
+      <c r="X10" t="n">
+        <v>23488.31168831169</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>5986883.116883117</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>76.69350649350648</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.097402597402598</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>25.58957486884914</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>182.8716788088233</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>73.1650543283675</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>22191.05060788617</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>6070665.783246936</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>77.36824748205918</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>1.233599915938915</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>24.24640716698579</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>186.6161461672249</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>70.20925556409375</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>19559.64657550143</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>3437400.403889453</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>76.40528346558095</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>22.32040816326531</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>182.6836734693877</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>4.857142857142857</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>336.5714285714286</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>66142.85714285714</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>25182142.85714286</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>375.5714285714286</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>6.142857142857143</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>27.00238095238095</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>186.2595238095238</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>3.285714285714286</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>237.5714285714286</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>70285.71428571429</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>12071428.57142857</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>246.2857142857143</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>3.285714285714286</v>
+      </c>
+      <c r="BF10" t="inlineStr">
+        <is>
+          <t>vZA6VYpf</t>
+        </is>
+      </c>
+      <c r="BG10" t="inlineStr">
+        <is>
+          <t>hAcTWKKN</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>v3DAZKP9</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>45604.6875</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">jablonski s 
+  ger </t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stadion an der alten forsterei
+  berlin </t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>22012</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>pzHW4oaE</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>fiEQZ7C7</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>59</v>
+      </c>
+      <c r="I11" t="n">
+        <v>591</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="N11" t="n">
+        <v>26.48831168831169</v>
+      </c>
+      <c r="O11" t="n">
+        <v>186.5181818181818</v>
+      </c>
+      <c r="P11" t="n">
+        <v>74.45714285714287</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>26488.31168831169</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6066753.246753247</v>
+      </c>
+      <c r="S11" t="n">
+        <v>77.6922077922078</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1.337662337662338</v>
+      </c>
+      <c r="U11" t="n">
+        <v>26.85079365079365</v>
+      </c>
+      <c r="V11" t="n">
+        <v>183.9936507936507</v>
+      </c>
+      <c r="W11" t="n">
+        <v>76.30952380952382</v>
+      </c>
+      <c r="X11" t="n">
+        <v>26323.80952380953</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>10909523.80952381</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>78.85079365079365</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.622222222222222</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>26.31236424394319</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>182.3666248955722</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>73.17681704260652</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>25250.54302422724</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>4284319.131161236</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>75.82330827067669</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>1.102756892230576</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>26.57391233589338</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>183.8710171815762</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>74.25122475867818</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>24049.01468804705</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>7097544.372648165</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>77.17198098294863</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>1.383266820354104</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>28.88095238095238</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>179.547619047619</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>212.8571428571429</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>90285.71428571429</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>16142857.14285714</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>213.7142857142857</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>26.15680272108844</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>185.6721088435374</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>5.285714285714286</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>374.7142857142857</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>99142.85714285714</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>23757142.85714286</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>393.2857142857143</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="BF11" t="inlineStr">
+        <is>
+          <t>hpYJ6izc</t>
+        </is>
+      </c>
+      <c r="BG11" t="inlineStr">
+        <is>
+          <t>YZPE6Sx7</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>biQrHC9r</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>45605.47916666666</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">badstubner f 
+  ger </t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vonovia ruhrstadion
+  bochum </t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>26000</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>8Y2m6ADe</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>4jcj2zMd</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>59</v>
+      </c>
+      <c r="I12" t="n">
+        <v>591</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="N12" t="n">
+        <v>28.21296296296296</v>
+      </c>
+      <c r="O12" t="n">
+        <v>185.9421296296296</v>
+      </c>
+      <c r="P12" t="n">
+        <v>71.62037037037037</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>16814.81481481481</v>
+      </c>
+      <c r="R12" t="n">
+        <v>2233912.037037037</v>
+      </c>
+      <c r="S12" t="n">
+        <v>73.80092592592592</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1</v>
+      </c>
+      <c r="U12" t="n">
+        <v>26.43531746031746</v>
+      </c>
+      <c r="V12" t="n">
+        <v>184.2964285714286</v>
+      </c>
+      <c r="W12" t="n">
+        <v>84.00793650793651</v>
+      </c>
+      <c r="X12" t="n">
+        <v>101621.4285714286</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>51919642.85714286</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>86.07619047619048</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>3.121428571428571</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>26.12187142063303</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>185.2048465810076</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>68.78568215410321</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>15808.82069426961</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>1769831.819367423</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>73.6982028978933</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>24.63209283713485</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>181.4816860077364</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>80.40254768574096</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>79663.58543417367</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>36154533.48005869</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>83.88744831265841</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>2.249593170601574</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>26.52380952380952</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>186.2357142857143</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>3.571428571428572</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>251.7142857142857</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>59714.28571428572</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>9000000</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>263.2857142857143</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>26.75</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>179.5</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>123</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>119500</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>45500000</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>128</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BF12" t="inlineStr">
+        <is>
+          <t>8f6APkLc</t>
+        </is>
+      </c>
+      <c r="BG12" t="inlineStr">
+        <is>
+          <t>hAcTWKKN</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>nee3ysec</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>45605.47916666666</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">welz t 
+  ger </t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mewa arena
+  mainz </t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>34000</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>EuakNmc1</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>nP1i5US1</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>59</v>
+      </c>
+      <c r="I13" t="n">
+        <v>591</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="N13" t="n">
+        <v>27.33809523809524</v>
+      </c>
+      <c r="O13" t="n">
+        <v>183.2730158730159</v>
+      </c>
+      <c r="P13" t="n">
+        <v>74.70952380952382</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>25246.03174603175</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6458253.968253968</v>
+      </c>
+      <c r="S13" t="n">
+        <v>77.03650793650793</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1.395238095238095</v>
+      </c>
+      <c r="U13" t="n">
+        <v>26.62987012987013</v>
+      </c>
+      <c r="V13" t="n">
+        <v>186.074025974026</v>
+      </c>
+      <c r="W13" t="n">
+        <v>81.97012987012987</v>
+      </c>
+      <c r="X13" t="n">
+        <v>58329.87012987013</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>37570779.22077922</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>84.0090909090909</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>2.585714285714286</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>25.45630635029132</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>183.5277601949871</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>71.23809696127255</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>21758.26234800141</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>3515278.86513457</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>77.08658965978735</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>1.187698332921685</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>25.06470693540574</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>184.34209843427</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>77.62269829781992</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>43666.30869253603</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>21783888.84740499</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>82.71285065860476</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>1.891205062567291</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>27.75</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>185.3333333333333</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>100.1666666666667</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>36166.66666666666</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>9183333.333333334</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>102</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>1.666666666666667</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>21.76190476190476</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>183.8333333333333</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>2.428571428571428</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>183.2857142857143</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>88714.28571428571</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>50342857.14285714</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>204.5714285714286</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>4.857142857142857</v>
+      </c>
+      <c r="BF13" t="inlineStr">
+        <is>
+          <t>vZA6VYpf</t>
+        </is>
+      </c>
+      <c r="BG13" t="inlineStr">
+        <is>
+          <t>IkCftsQm</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>6HTjFjve</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>45605.47916666666</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">exner f 
+  ger </t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">millerntor stadion
+  hamburg </t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>29546</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>ILyJuN3g</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>nVp0wiqd</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>59</v>
+      </c>
+      <c r="I14" t="n">
+        <v>591</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="N14" t="n">
+        <v>26.93116883116883</v>
+      </c>
+      <c r="O14" t="n">
+        <v>185.1207792207792</v>
+      </c>
+      <c r="P14" t="n">
+        <v>70.70259740259739</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>17327.27272727273</v>
+      </c>
+      <c r="R14" t="n">
+        <v>2314675.324675325</v>
+      </c>
+      <c r="S14" t="n">
+        <v>73.32857142857142</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1</v>
+      </c>
+      <c r="U14" t="n">
+        <v>27.33015873015873</v>
+      </c>
+      <c r="V14" t="n">
+        <v>183.8317460317461</v>
+      </c>
+      <c r="W14" t="n">
+        <v>83.3079365079365</v>
+      </c>
+      <c r="X14" t="n">
+        <v>80646.03174603175</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>47889325.3968254</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>85.68571428571428</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>3.242857142857142</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>25.76829573934837</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>184.8265664160401</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>67.93120300751879</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>15998.24561403509</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>1688358.395989975</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>71.68082706766917</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>26.57194825298541</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>183.2282513882746</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>81.15302226153619</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>74119.89379084967</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>36113977.29925304</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>83.90506535947713</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>2.647461791734237</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>27.93571428571429</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>187.1309523809524</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>282.1428571428572</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>57714.28571428572</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>4547142.857142857</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>295.1428571428572</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>184.7619047619048</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>5.428571428571429</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>395</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>219142.8571428571</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>101435714.2857143</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>444.1428571428572</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>7.714285714285714</v>
+      </c>
+      <c r="BF14" t="inlineStr">
+        <is>
+          <t>0jdIgO6t</t>
+        </is>
+      </c>
+      <c r="BG14" t="inlineStr">
+        <is>
+          <t>K6A2elS9</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>YmumZjET</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>45605.47916666666</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">hartmann r 
+  ger </t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">weserstadion
+  bremen </t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>42100</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Ig1f1fy3</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>63WsD2ei</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>59</v>
+      </c>
+      <c r="I15" t="n">
+        <v>591</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="N15" t="n">
+        <v>27.10779220779221</v>
+      </c>
+      <c r="O15" t="n">
+        <v>183.2025974025974</v>
+      </c>
+      <c r="P15" t="n">
+        <v>74.42727272727272</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>23488.31168831169</v>
+      </c>
+      <c r="R15" t="n">
+        <v>5986883.116883117</v>
+      </c>
+      <c r="S15" t="n">
+        <v>76.69350649350648</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1.097402597402598</v>
+      </c>
+      <c r="U15" t="n">
+        <v>26.53293650793651</v>
+      </c>
+      <c r="V15" t="n">
+        <v>186.0357142857143</v>
+      </c>
+      <c r="W15" t="n">
+        <v>69.74603174603175</v>
+      </c>
+      <c r="X15" t="n">
+        <v>16501.98412698413</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1887976.19047619</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>72.18968253968254</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>24.24640716698579</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>186.6161461672249</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>70.20925556409375</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>19559.64657550143</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>3437400.403889453</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>76.40528346558095</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>25.65921247217423</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>184.5859378825381</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>68.39975163770522</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>15890.84512523545</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>1848853.061507524</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>72.72310639670887</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>27.00238095238095</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>186.2595238095238</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>3.285714285714286</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>237.5714285714286</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>70285.71428571429</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>12071428.57142857</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>246.2857142857143</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>3.285714285714286</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>25.39285714285714</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>188.7261904761905</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>2.285714285714286</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>158.2857142857143</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>34714.28571428572</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>4528571.428571428</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>167.4285714285714</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>2.285714285714286</v>
+      </c>
+      <c r="BF15" t="inlineStr">
+        <is>
+          <t>4fuCGs9P</t>
+        </is>
+      </c>
+      <c r="BG15" t="inlineStr">
+        <is>
+          <t>A15eUM4C</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>j5mWxZE4</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>45605.60416666666</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">petersen m 
+  ger </t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">red bull arena
+  leipzig </t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>47069</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>KbS1suSm</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>88HSzjDr</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>59</v>
+      </c>
+      <c r="I16" t="n">
+        <v>591</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="N16" t="n">
+        <v>25.92604617604617</v>
+      </c>
+      <c r="O16" t="n">
+        <v>183.647113997114</v>
+      </c>
+      <c r="P16" t="n">
+        <v>80.65649350649349</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>57380.44733044733</v>
+      </c>
+      <c r="R16" t="n">
+        <v>31258207.07070708</v>
+      </c>
+      <c r="S16" t="n">
+        <v>84.08048340548341</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2.263672438672439</v>
+      </c>
+      <c r="U16" t="n">
+        <v>26.28571428571428</v>
+      </c>
+      <c r="V16" t="n">
+        <v>184.9571428571428</v>
+      </c>
+      <c r="W16" t="n">
+        <v>75.34285714285714</v>
+      </c>
+      <c r="X16" t="n">
+        <v>24285.71428571429</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>7837142.857142857</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>77.52857142857144</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.414285714285714</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>25.52409121543354</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>185.1266923436041</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>78.15957742746221</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>50919.45023623485</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>23002770.19799148</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>82.0515675568473</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>1.956210115625197</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>25.58957486884914</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>182.8716788088233</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>73.1650543283675</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>22191.05060788617</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>6070665.783246936</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>77.36824748205918</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>1.233599915938915</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>24.66190476190476</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>181.8119047619048</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>3.571428571428572</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>275.4285714285714</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>170000</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>69500000</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>299.8571428571428</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>7.714285714285714</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>22.32040816326531</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>182.6836734693877</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>4.857142857142857</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>336.5714285714286</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>66142.85714285714</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>25182142.85714286</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>375.5714285714286</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>6.142857142857143</v>
+      </c>
+      <c r="BF16" t="inlineStr">
+        <is>
+          <t>pfoInmcq</t>
+        </is>
+      </c>
+      <c r="BG16" t="inlineStr">
+        <is>
+          <t>M5BRZDsC</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>UJQITUyi</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>45606.47916666666</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dingert c 
+  ger </t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">wwk arena
+  augsburg </t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>30660</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>fTVNku3I</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>hQAtP9Sl</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>59</v>
+      </c>
+      <c r="I17" t="n">
+        <v>591</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="N17" t="n">
+        <v>26.375</v>
+      </c>
+      <c r="O17" t="n">
+        <v>184.875</v>
+      </c>
+      <c r="P17" t="n">
+        <v>73.875</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>23375</v>
+      </c>
+      <c r="R17" t="n">
+        <v>5350000</v>
+      </c>
+      <c r="S17" t="n">
+        <v>76.25</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1.125</v>
+      </c>
+      <c r="U17" t="n">
+        <v>27.41428571428572</v>
+      </c>
+      <c r="V17" t="n">
+        <v>185.9432539682539</v>
+      </c>
+      <c r="W17" t="n">
+        <v>75.18055555555556</v>
+      </c>
+      <c r="X17" t="n">
+        <v>30215.47619047619</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>7743611.111111111</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>78.81071428571428</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.638492063492064</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>24.37182783799325</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>184.978548915579</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>72.2266793878636</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>20481.00432357951</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>4975501.999045232</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>76.86839392854429</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>1.087504339853964</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>24.38693758205036</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>185.0631578947368</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>71.22855352667383</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>23816.34443250985</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>5203475.653419263</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>77.60978040338942</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>1.178338703902614</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>25.87380952380952</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>183.9452380952381</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>4.857142857142857</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>343</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>85000</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>13467857.14285714</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>353.8571428571428</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>4.857142857142857</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>26.17431972789116</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>182.8818027210884</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>6.428571428571429</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>477.7142857142857</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>170857.1428571429</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>41542857.14285714</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>498.7142857142857</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>10</v>
+      </c>
+      <c r="BF17" t="inlineStr">
+        <is>
+          <t>2VSFgl3c</t>
+        </is>
+      </c>
+      <c r="BG17" t="inlineStr">
+        <is>
+          <t>KUx4Q7x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>UkaNveph</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>45606.5625</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">osmers h 
+  ger </t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mhparena
+  stuttgart </t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>60449</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>nJQmYp1B</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>8vndvXTk</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>59</v>
+      </c>
+      <c r="I18" t="n">
+        <v>591</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="N18" t="n">
+        <v>24.68989898989899</v>
+      </c>
+      <c r="O18" t="n">
+        <v>185.9199134199134</v>
+      </c>
+      <c r="P18" t="n">
+        <v>76.38571428571429</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>27397.97979797979</v>
+      </c>
+      <c r="R18" t="n">
+        <v>14030497.83549784</v>
+      </c>
+      <c r="S18" t="n">
+        <v>79.85642135642135</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1.501587301587302</v>
+      </c>
+      <c r="U18" t="n">
+        <v>24.50277777777778</v>
+      </c>
+      <c r="V18" t="n">
+        <v>185.4416666666667</v>
+      </c>
+      <c r="W18" t="n">
+        <v>76.60277777777779</v>
+      </c>
+      <c r="X18" t="n">
+        <v>34427.77777777778</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>14699166.66666667</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>81.47222222222221</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.697222222222222</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>24.53934837092732</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>185.8327485380117</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>74.44469507101086</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>24816.29072681704</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>11320962.82372598</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>78.18170426065164</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>1.505012531328321</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>22.94464285714286</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>184.4420576603847</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>73.12410042964555</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>26518.00401978973</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>9585556.073625622</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>80.91495052566481</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>1.43036324577678</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>22.27142857142857</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>183.347619047619</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>298.4285714285714</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>76285.71428571429</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>20921428.57142857</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>337.5714285714286</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>5.142857142857143</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>19.61904761904762</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>176.3809523809524</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>1.714285714285714</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>105.8571428571429</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>12142.85714285714</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>3503571.428571429</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>133.7142857142857</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>2</v>
+      </c>
+      <c r="BF18" t="inlineStr">
+        <is>
+          <t>GzfvcwRj</t>
+        </is>
+      </c>
+      <c r="BG18" t="inlineStr">
+        <is>
+          <t>UgdQz0fK</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>xMovyDqH</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>45606.64583333334</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">reichel t 
+  ger </t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
         <is>
           <t xml:space="preserve">voith arena
   heidenheim </t>
         </is>
       </c>
-      <c r="E10" t="n">
+      <c r="E19" t="n">
         <v>15000</v>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>KWixEVWi</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>hQAtP9Sl</t>
-        </is>
-      </c>
-      <c r="H10" t="n">
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>nwkTahLL</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
         <v>59</v>
       </c>
-      <c r="I10" t="n">
+      <c r="I19" t="n">
         <v>591</v>
       </c>
-      <c r="J10" t="n">
+      <c r="J19" t="n">
         <v>0</v>
       </c>
-      <c r="K10" t="n">
+      <c r="K19" t="n">
         <v>20242025</v>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="L19" t="inlineStr">
         <is>
           <t>germany</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="M19" t="inlineStr">
         <is>
           <t>bundesliga</t>
         </is>
       </c>
-      <c r="N10" t="n">
-        <v>24</v>
-      </c>
-      <c r="O10" t="n">
-        <v>186</v>
-      </c>
-      <c r="P10" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>66</v>
-      </c>
-      <c r="R10" t="n">
-        <v>16000</v>
-      </c>
-      <c r="S10" t="n">
-        <v>1100000</v>
-      </c>
-      <c r="T10" t="n">
-        <v>70</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1</v>
-      </c>
-      <c r="V10" t="n">
-        <v>27</v>
-      </c>
-      <c r="W10" t="n">
-        <v>184</v>
-      </c>
-      <c r="X10" t="n">
-        <v>8</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>600</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>228000</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>58900000</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>619</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>13</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>26.91666666666667</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>187.15</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>72.7</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>22266.66666666667</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>3213333.333333333</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>74.41666666666667</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>1.016666666666667</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>27.4462962962963</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>185.9523148148148</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>75.13657407407406</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>30251.38888888889</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>7745324.074074075</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>78.74212962962963</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>1.652314814814815</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>25.9481884057971</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>184.8597826086956</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>69.4909420289855</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>19925.36231884058</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>2149293.47826087</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>72.13985507246377</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>1.043478260869565</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>24.15976051239209</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>185.490350877193</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>70.95831244778613</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>23427.40183792815</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>5084054.928989139</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>77.55307713728767</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>1.158061821219716</v>
-      </c>
-      <c r="BF10" t="inlineStr">
-        <is>
-          <t>M5BRZDsC</t>
-        </is>
-      </c>
-      <c r="BG10" t="inlineStr">
-        <is>
-          <t>8f6APkLc</t>
+      <c r="N19" t="n">
+        <v>26.88571428571428</v>
+      </c>
+      <c r="O19" t="n">
+        <v>186.9428571428571</v>
+      </c>
+      <c r="P19" t="n">
+        <v>72.77142857142857</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>22328.57142857143</v>
+      </c>
+      <c r="R19" t="n">
+        <v>3284285.714285714</v>
+      </c>
+      <c r="S19" t="n">
+        <v>74.51428571428572</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1.028571428571428</v>
+      </c>
+      <c r="U19" t="n">
+        <v>24.64583333333334</v>
+      </c>
+      <c r="V19" t="n">
+        <v>184.6180555555555</v>
+      </c>
+      <c r="W19" t="n">
+        <v>75.14236111111111</v>
+      </c>
+      <c r="X19" t="n">
+        <v>35940.97222222223</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>9807986.111111112</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>79.76388888888889</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1.378472222222222</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>25.90516989404457</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>184.9050237486299</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>69.37879064669345</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>19860.39459261965</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>2123343.989769821</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>72.11987577639752</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>1.045670442089879</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>24.97827355822712</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>184.7069821947918</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>73.26382427771748</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>32866.22444033434</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>8046176.864286385</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>78.16485180196482</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>1.394858413859962</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>24.38095238095238</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>186.4523809523809</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>3</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>202.5714285714286</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>52571.42857142857</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>5978571.428571428</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>216.4285714285714</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>3.285714285714286</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>23.84149659863946</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>183.1982993197279</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>5.428571428571429</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>401.7142857142857</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>192571.4285714286</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>58300000</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>431.8571428571428</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>8.428571428571429</v>
+      </c>
+      <c r="BF19" t="inlineStr">
+        <is>
+          <t>4ljanukM</t>
+        </is>
+      </c>
+      <c r="BG19" t="inlineStr">
+        <is>
+          <t>f3ddUIXs</t>
         </is>
       </c>
     </row>

--- a/data/germany/p6_deployment/data_preparation/df_filled.xlsx
+++ b/data/germany/p6_deployment/data_preparation/df_filled.xlsx
@@ -495,222 +495,222 @@
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
+          <t>mean_age_player_start_home</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>mean_hei_player_start_home</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>mean_rat_player_start_home</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>mean_wage_player_start_home</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>mean_value_player_start_home</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>mean_pot_player_start_home</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>mean_rep_player_start_home</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>mean_age_player_start_away</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>mean_hei_player_start_away</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>mean_rat_player_start_away</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>mean_wage_player_start_away</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>mean_value_player_start_away</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>mean_pot_player_start_away</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>mean_rep_player_start_away</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>mean_age_player_sub_home</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>mean_hei_player_sub_home</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>mean_rat_player_sub_home</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>mean_wage_player_sub_home</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>mean_value_player_sub_home</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>mean_pot_player_sub_home</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>mean_rep_player_sub_home</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>mean_age_player_sub_away</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>mean_hei_player_sub_away</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>mean_rat_player_sub_away</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>mean_wage_player_sub_away</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>mean_value_player_sub_away</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>mean_pot_player_sub_away</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>mean_rep_player_sub_away</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
           <t>mean_age_player_miss_home</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>mean_hei_player_miss_home</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>n_player_miss_home</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>sum_rat_player_miss_home</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>sum_wage_player_miss_home</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>sum_value_player_miss_home</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>sum_pot_player_miss_home</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="AW1" s="1" t="inlineStr">
         <is>
           <t>sum_rep_player_miss_home</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="AX1" s="1" t="inlineStr">
         <is>
           <t>mean_age_player_miss_away</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="AY1" s="1" t="inlineStr">
         <is>
           <t>mean_hei_player_miss_away</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="AZ1" s="1" t="inlineStr">
         <is>
           <t>n_player_miss_away</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="BA1" s="1" t="inlineStr">
         <is>
           <t>sum_rat_player_miss_away</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="BB1" s="1" t="inlineStr">
         <is>
           <t>sum_wage_player_miss_away</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="BC1" s="1" t="inlineStr">
         <is>
           <t>sum_value_player_miss_away</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="BD1" s="1" t="inlineStr">
         <is>
           <t>sum_pot_player_miss_away</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="BE1" s="1" t="inlineStr">
         <is>
           <t>sum_rep_player_miss_away</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>mean_age_player_start_home</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>mean_hei_player_start_home</t>
-        </is>
-      </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>mean_rat_player_start_home</t>
-        </is>
-      </c>
-      <c r="AG1" s="1" t="inlineStr">
-        <is>
-          <t>mean_wage_player_start_home</t>
-        </is>
-      </c>
-      <c r="AH1" s="1" t="inlineStr">
-        <is>
-          <t>mean_value_player_start_home</t>
-        </is>
-      </c>
-      <c r="AI1" s="1" t="inlineStr">
-        <is>
-          <t>mean_pot_player_start_home</t>
-        </is>
-      </c>
-      <c r="AJ1" s="1" t="inlineStr">
-        <is>
-          <t>mean_rep_player_start_home</t>
-        </is>
-      </c>
-      <c r="AK1" s="1" t="inlineStr">
-        <is>
-          <t>mean_age_player_start_away</t>
-        </is>
-      </c>
-      <c r="AL1" s="1" t="inlineStr">
-        <is>
-          <t>mean_hei_player_start_away</t>
-        </is>
-      </c>
-      <c r="AM1" s="1" t="inlineStr">
-        <is>
-          <t>mean_rat_player_start_away</t>
-        </is>
-      </c>
-      <c r="AN1" s="1" t="inlineStr">
-        <is>
-          <t>mean_wage_player_start_away</t>
-        </is>
-      </c>
-      <c r="AO1" s="1" t="inlineStr">
-        <is>
-          <t>mean_value_player_start_away</t>
-        </is>
-      </c>
-      <c r="AP1" s="1" t="inlineStr">
-        <is>
-          <t>mean_pot_player_start_away</t>
-        </is>
-      </c>
-      <c r="AQ1" s="1" t="inlineStr">
-        <is>
-          <t>mean_rep_player_start_away</t>
-        </is>
-      </c>
-      <c r="AR1" s="1" t="inlineStr">
-        <is>
-          <t>mean_age_player_sub_home</t>
-        </is>
-      </c>
-      <c r="AS1" s="1" t="inlineStr">
-        <is>
-          <t>mean_hei_player_sub_home</t>
-        </is>
-      </c>
-      <c r="AT1" s="1" t="inlineStr">
-        <is>
-          <t>mean_rat_player_sub_home</t>
-        </is>
-      </c>
-      <c r="AU1" s="1" t="inlineStr">
-        <is>
-          <t>mean_wage_player_sub_home</t>
-        </is>
-      </c>
-      <c r="AV1" s="1" t="inlineStr">
-        <is>
-          <t>mean_value_player_sub_home</t>
-        </is>
-      </c>
-      <c r="AW1" s="1" t="inlineStr">
-        <is>
-          <t>mean_pot_player_sub_home</t>
-        </is>
-      </c>
-      <c r="AX1" s="1" t="inlineStr">
-        <is>
-          <t>mean_rep_player_sub_home</t>
-        </is>
-      </c>
-      <c r="AY1" s="1" t="inlineStr">
-        <is>
-          <t>mean_age_player_sub_away</t>
-        </is>
-      </c>
-      <c r="AZ1" s="1" t="inlineStr">
-        <is>
-          <t>mean_hei_player_sub_away</t>
-        </is>
-      </c>
-      <c r="BA1" s="1" t="inlineStr">
-        <is>
-          <t>mean_rat_player_sub_away</t>
-        </is>
-      </c>
-      <c r="BB1" s="1" t="inlineStr">
-        <is>
-          <t>mean_wage_player_sub_away</t>
-        </is>
-      </c>
-      <c r="BC1" s="1" t="inlineStr">
-        <is>
-          <t>mean_value_player_sub_away</t>
-        </is>
-      </c>
-      <c r="BD1" s="1" t="inlineStr">
-        <is>
-          <t>mean_pot_player_sub_away</t>
-        </is>
-      </c>
-      <c r="BE1" s="1" t="inlineStr">
-        <is>
-          <t>mean_rep_player_sub_away</t>
         </is>
       </c>
       <c r="BF1" s="1" t="inlineStr">
@@ -727,35 +727,35 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>IHYEDIog</t>
+          <t>v3DAZKP9</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45597.6875</v>
+        <v>45604.6875</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">schlager d 
+          <t xml:space="preserve">brand b 
   ger </t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">bayarena
-  leverkusen </t>
+          <t xml:space="preserve">stadion an der alten forsterei
+  berlin </t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>30210</v>
+        <v>22012</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>4jcj2zMd</t>
+          <t>pzHW4oaE</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>nJQmYp1B</t>
+          <t>fiEQZ7C7</t>
         </is>
       </c>
       <c r="H2" t="n">
@@ -781,180 +781,180 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>24</v>
+        <v>26.73282828282828</v>
       </c>
       <c r="O2" t="n">
-        <v>174</v>
+        <v>186.4034090909091</v>
       </c>
       <c r="P2" t="n">
-        <v>1</v>
+        <v>74.49166666666666</v>
       </c>
       <c r="Q2" t="n">
-        <v>78</v>
+        <v>26611.99494949495</v>
       </c>
       <c r="R2" t="n">
-        <v>64000</v>
+        <v>6037575.757575758</v>
       </c>
       <c r="S2" t="n">
-        <v>28500000</v>
+        <v>77.49595959595959</v>
       </c>
       <c r="T2" t="n">
-        <v>85</v>
+        <v>1.338510101010101</v>
       </c>
       <c r="U2" t="n">
-        <v>1</v>
+        <v>27.1</v>
       </c>
       <c r="V2" t="n">
-        <v>22.5</v>
+        <v>184.25</v>
       </c>
       <c r="W2" t="n">
-        <v>186.3333333333333</v>
+        <v>76.51250000000002</v>
       </c>
       <c r="X2" t="n">
-        <v>6</v>
+        <v>26875</v>
       </c>
       <c r="Y2" t="n">
-        <v>420</v>
+        <v>11181250</v>
       </c>
       <c r="Z2" t="n">
-        <v>110000</v>
+        <v>78.8</v>
       </c>
       <c r="AA2" t="n">
-        <v>33550000</v>
+        <v>1.65</v>
       </c>
       <c r="AB2" t="n">
-        <v>474</v>
+        <v>26.32467740910247</v>
       </c>
       <c r="AC2" t="n">
-        <v>7</v>
+        <v>182.5191663488431</v>
       </c>
       <c r="AD2" t="n">
-        <v>26.52460317460318</v>
+        <v>73.17101926010679</v>
       </c>
       <c r="AE2" t="n">
-        <v>184.5642857142857</v>
+        <v>25448.02949402492</v>
       </c>
       <c r="AF2" t="n">
-        <v>83.57936507936508</v>
+        <v>4287583.587592169</v>
       </c>
       <c r="AG2" t="n">
-        <v>99192.85714285714</v>
+        <v>75.89593821510297</v>
       </c>
       <c r="AH2" t="n">
-        <v>48178571.42857143</v>
+        <v>1.110020976353928</v>
       </c>
       <c r="AI2" t="n">
-        <v>85.68333333333332</v>
+        <v>26.65878139169127</v>
       </c>
       <c r="AJ2" t="n">
-        <v>3.014285714285715</v>
+        <v>183.677628956721</v>
       </c>
       <c r="AK2" t="n">
-        <v>24.64227994227994</v>
+        <v>73.94523228263637</v>
       </c>
       <c r="AL2" t="n">
-        <v>186.1810966810967</v>
+        <v>23646.48156225253</v>
       </c>
       <c r="AM2" t="n">
-        <v>75.83737373737374</v>
+        <v>6517540.338035568</v>
       </c>
       <c r="AN2" t="n">
-        <v>26718.32611832611</v>
+        <v>76.99487793609227</v>
       </c>
       <c r="AO2" t="n">
-        <v>13175158.73015873</v>
+        <v>1.373969366714857</v>
       </c>
       <c r="AP2" t="n">
-        <v>79.50144300144299</v>
+        <v>28.69047619047619</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.468398268398268</v>
+        <v>179.8333333333333</v>
       </c>
       <c r="AR2" t="n">
-        <v>24.60611881116083</v>
+        <v>2.857142857142857</v>
       </c>
       <c r="AS2" t="n">
-        <v>181.579088605139</v>
+        <v>212.8571428571429</v>
       </c>
       <c r="AT2" t="n">
-        <v>80.63631391950719</v>
+        <v>89571.42857142857</v>
       </c>
       <c r="AU2" t="n">
-        <v>82423.32569391394</v>
+        <v>16428571.42857143</v>
       </c>
       <c r="AV2" t="n">
-        <v>39397011.83503705</v>
+        <v>214.1428571428571</v>
       </c>
       <c r="AW2" t="n">
-        <v>84.3051972304073</v>
+        <v>4</v>
       </c>
       <c r="AX2" t="n">
-        <v>2.390285811294215</v>
+        <v>25.86428571428572</v>
       </c>
       <c r="AY2" t="n">
-        <v>24.44002864303616</v>
+        <v>185.8047619047619</v>
       </c>
       <c r="AZ2" t="n">
-        <v>185.5892111230457</v>
+        <v>5.142857142857143</v>
       </c>
       <c r="BA2" t="n">
-        <v>74.68415085332379</v>
+        <v>363.7142857142857</v>
       </c>
       <c r="BB2" t="n">
-        <v>24907.44718940208</v>
+        <v>93285.71428571429</v>
       </c>
       <c r="BC2" t="n">
-        <v>11700010.4427736</v>
+        <v>22871428.57142857</v>
       </c>
       <c r="BD2" t="n">
-        <v>78.37898317221627</v>
+        <v>383.4285714285714</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.49140708915145</v>
+        <v>5.428571428571429</v>
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>hAcTWKKN</t>
+          <t>K6A2elS9</t>
         </is>
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>4bJLk19p</t>
+          <t>vZA6VYpf</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>jVWMBdG5</t>
+          <t>biQrHC9r</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45598.47916666666</v>
+        <v>45605.47916666666</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">haslberger w 
+          <t xml:space="preserve">siebert d 
   ger </t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">allianz arena
-  munich </t>
+          <t xml:space="preserve">vonovia ruhrstadion
+  bochum </t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>75024</v>
+        <v>26000</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>nVp0wiqd</t>
+          <t>8Y2m6ADe</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>pzHW4oaE</t>
+          <t>4jcj2zMd</t>
         </is>
       </c>
       <c r="H3" t="n">
@@ -980,180 +980,180 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>22.66666666666667</v>
+        <v>28.34490740740741</v>
       </c>
       <c r="O3" t="n">
-        <v>185.8333333333333</v>
+        <v>186.0833333333333</v>
       </c>
       <c r="P3" t="n">
-        <v>6</v>
+        <v>71.69907407407408</v>
       </c>
       <c r="Q3" t="n">
-        <v>450</v>
+        <v>16979.16666666667</v>
       </c>
       <c r="R3" t="n">
-        <v>264000</v>
+        <v>2252025.462962963</v>
       </c>
       <c r="S3" t="n">
-        <v>103150000</v>
+        <v>73.83796296296296</v>
       </c>
       <c r="T3" t="n">
-        <v>497</v>
+        <v>1</v>
       </c>
       <c r="U3" t="n">
-        <v>9</v>
+        <v>26.50448232323232</v>
       </c>
       <c r="V3" t="n">
-        <v>27.66666666666667</v>
+        <v>184.5846590909091</v>
       </c>
       <c r="W3" t="n">
-        <v>182.3333333333333</v>
+        <v>83.60921717171718</v>
       </c>
       <c r="X3" t="n">
-        <v>3</v>
+        <v>99236.93181818182</v>
       </c>
       <c r="Y3" t="n">
-        <v>222</v>
+        <v>48423295.45454545</v>
       </c>
       <c r="Z3" t="n">
-        <v>89000</v>
+        <v>85.70018939393938</v>
       </c>
       <c r="AA3" t="n">
-        <v>17100000</v>
+        <v>3.023863636363636</v>
       </c>
       <c r="AB3" t="n">
-        <v>225</v>
+        <v>26.41635443122857</v>
       </c>
       <c r="AC3" t="n">
-        <v>4</v>
+        <v>184.6034581995681</v>
       </c>
       <c r="AD3" t="n">
-        <v>27.53015873015873</v>
+        <v>69.04034053919638</v>
       </c>
       <c r="AE3" t="n">
-        <v>184.0031746031746</v>
+        <v>16141.66687622065</v>
       </c>
       <c r="AF3" t="n">
-        <v>83.53650793650795</v>
+        <v>1787561.084986714</v>
       </c>
       <c r="AG3" t="n">
-        <v>81974.60317460318</v>
+        <v>73.39604725302665</v>
       </c>
       <c r="AH3" t="n">
-        <v>48739325.3968254</v>
+        <v>1</v>
       </c>
       <c r="AI3" t="n">
-        <v>85.62857142857142</v>
+        <v>24.63972895976573</v>
       </c>
       <c r="AJ3" t="n">
-        <v>3.3</v>
+        <v>181.6395150294966</v>
       </c>
       <c r="AK3" t="n">
-        <v>26.63116883116883</v>
+        <v>80.36146217956879</v>
       </c>
       <c r="AL3" t="n">
-        <v>186.3181818181818</v>
+        <v>81495.40998217469</v>
       </c>
       <c r="AM3" t="n">
-        <v>74.51428571428572</v>
+        <v>38064377.54315741</v>
       </c>
       <c r="AN3" t="n">
-        <v>26731.16883116883</v>
+        <v>84.05611007660639</v>
       </c>
       <c r="AO3" t="n">
-        <v>6081038.961038962</v>
+        <v>2.364937584882438</v>
       </c>
       <c r="AP3" t="n">
-        <v>77.53506493506494</v>
+        <v>25.95238095238095</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.323376623376624</v>
+        <v>186.25</v>
       </c>
       <c r="AR3" t="n">
-        <v>26.37152808491818</v>
+        <v>3.142857142857143</v>
       </c>
       <c r="AS3" t="n">
-        <v>182.8669068504595</v>
+        <v>220.4285714285714</v>
       </c>
       <c r="AT3" t="n">
-        <v>80.615627303553</v>
+        <v>52571.42857142857</v>
       </c>
       <c r="AU3" t="n">
-        <v>75434.36819172114</v>
+        <v>8253571.428571428</v>
       </c>
       <c r="AV3" t="n">
-        <v>35476477.29925304</v>
+        <v>232</v>
       </c>
       <c r="AW3" t="n">
-        <v>83.79077964519141</v>
+        <v>3.428571428571428</v>
       </c>
       <c r="AX3" t="n">
-        <v>2.61468868249054</v>
+        <v>24</v>
       </c>
       <c r="AY3" t="n">
-        <v>26.2903145545022</v>
+        <v>174</v>
       </c>
       <c r="AZ3" t="n">
-        <v>182.6616559514728</v>
+        <v>1</v>
       </c>
       <c r="BA3" t="n">
-        <v>73.15197232210961</v>
+        <v>78</v>
       </c>
       <c r="BB3" t="n">
-        <v>25338.12066397879</v>
+        <v>64000</v>
       </c>
       <c r="BC3" t="n">
-        <v>4288915.404453161</v>
+        <v>28500000</v>
       </c>
       <c r="BD3" t="n">
-        <v>75.92455050670154</v>
+        <v>85</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.11952707856598</v>
+        <v>1</v>
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>vZA6VYpf</t>
+          <t>UgdQz0fK</t>
         </is>
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>hpYJ6izc</t>
+          <t>GzfvcwRj</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>485V7EFU</t>
+          <t>nee3ysec</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45598.47916666666</v>
+        <v>45605.47916666666</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">exner f 
+          <t xml:space="preserve">stieler t 
   ger </t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">deutsche bank park
-  frankfurt </t>
+          <t xml:space="preserve">mewa arena
+  mainz </t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>58000</v>
+        <v>34000</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>8vndvXTk</t>
+          <t>EuakNmc1</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>8Y2m6ADe</t>
+          <t>nP1i5US1</t>
         </is>
       </c>
       <c r="H4" t="n">
@@ -1179,180 +1179,180 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>19</v>
+        <v>27.01527777777778</v>
       </c>
       <c r="O4" t="n">
-        <v>180</v>
+        <v>182.9430555555556</v>
       </c>
       <c r="P4" t="n">
-        <v>2</v>
+        <v>74.41944444444445</v>
       </c>
       <c r="Q4" t="n">
-        <v>121</v>
+        <v>24981.94444444445</v>
       </c>
       <c r="R4" t="n">
-        <v>7000</v>
+        <v>6222777.777777778</v>
       </c>
       <c r="S4" t="n">
-        <v>1575000</v>
+        <v>77.15138888888889</v>
       </c>
       <c r="T4" t="n">
-        <v>157</v>
+        <v>1.377777777777778</v>
       </c>
       <c r="U4" t="n">
-        <v>2</v>
+        <v>26.61931818181818</v>
       </c>
       <c r="V4" t="n">
-        <v>25.33333333333333</v>
+        <v>186.0761363636364</v>
       </c>
       <c r="W4" t="n">
-        <v>184</v>
+        <v>81.72386363636363</v>
       </c>
       <c r="X4" t="n">
-        <v>3</v>
+        <v>57572.72727272727</v>
       </c>
       <c r="Y4" t="n">
-        <v>208</v>
+        <v>36480113.63636364</v>
       </c>
       <c r="Z4" t="n">
-        <v>52000</v>
+        <v>83.87159090909091</v>
       </c>
       <c r="AA4" t="n">
-        <v>7875000</v>
+        <v>2.523863636363636</v>
       </c>
       <c r="AB4" t="n">
-        <v>219</v>
+        <v>25.5305180565049</v>
       </c>
       <c r="AC4" t="n">
-        <v>3</v>
+        <v>183.6403615991851</v>
       </c>
       <c r="AD4" t="n">
-        <v>24.35277777777778</v>
+        <v>71.26726341254205</v>
       </c>
       <c r="AE4" t="n">
-        <v>185.7166666666667</v>
+        <v>21928.6581259298</v>
       </c>
       <c r="AF4" t="n">
-        <v>76.30277777777778</v>
+        <v>3633502.935564177</v>
       </c>
       <c r="AG4" t="n">
-        <v>33677.77777777778</v>
+        <v>77.18648023802822</v>
       </c>
       <c r="AH4" t="n">
-        <v>14166666.66666667</v>
+        <v>1.199950327020761</v>
       </c>
       <c r="AI4" t="n">
-        <v>81.44722222222222</v>
+        <v>24.86772967959113</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1.697222222222222</v>
+        <v>183.6715583522085</v>
       </c>
       <c r="AK4" t="n">
-        <v>28.18888888888889</v>
+        <v>77.07611101059243</v>
       </c>
       <c r="AL4" t="n">
-        <v>185.975</v>
+        <v>43169.13121708013</v>
       </c>
       <c r="AM4" t="n">
-        <v>71.58888888888889</v>
+        <v>22125694.40814603</v>
       </c>
       <c r="AN4" t="n">
-        <v>16800</v>
+        <v>82.51749432627915</v>
       </c>
       <c r="AO4" t="n">
-        <v>2226805.555555555</v>
+        <v>1.895776651968602</v>
       </c>
       <c r="AP4" t="n">
-        <v>73.80555555555556</v>
+        <v>27.91666666666667</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1</v>
+        <v>184.9166666666667</v>
       </c>
       <c r="AR4" t="n">
-        <v>23.13534688995216</v>
+        <v>1.5</v>
       </c>
       <c r="AS4" t="n">
-        <v>184.2004308661264</v>
+        <v>112.8333333333333</v>
       </c>
       <c r="AT4" t="n">
-        <v>73.16682086710283</v>
+        <v>40500</v>
       </c>
       <c r="AU4" t="n">
-        <v>26920.25965888748</v>
+        <v>10516666.66666667</v>
       </c>
       <c r="AV4" t="n">
-        <v>9540204.057220975</v>
+        <v>115</v>
       </c>
       <c r="AW4" t="n">
-        <v>80.69280425088695</v>
+        <v>1.833333333333333</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.436514988770628</v>
+        <v>21.79761904761904</v>
       </c>
       <c r="AY4" t="n">
-        <v>26.34806567701304</v>
+        <v>183.7797619047619</v>
       </c>
       <c r="AZ4" t="n">
-        <v>184.8272229719598</v>
+        <v>3.285714285714286</v>
       </c>
       <c r="BA4" t="n">
-        <v>68.91662917978708</v>
+        <v>249.8571428571429</v>
       </c>
       <c r="BB4" t="n">
-        <v>16071.0751237067</v>
+        <v>121142.8571428571</v>
       </c>
       <c r="BC4" t="n">
-        <v>1767009.671614935</v>
+        <v>74157142.85714285</v>
       </c>
       <c r="BD4" t="n">
-        <v>73.49104063577748</v>
+        <v>276.8571428571428</v>
       </c>
       <c r="BE4" t="n">
-        <v>1</v>
+        <v>6.714285714285714</v>
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>UgdQz0fK</t>
+          <t>YZPE6Sx7</t>
         </is>
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>K6A2elS9</t>
+          <t>pfoInmcq</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>8MVuSH0n</t>
+          <t>6HTjFjve</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45598.47916666666</v>
+        <v>45605.47916666666</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">zwayer f 
+          <t xml:space="preserve">jollenbeck m 
   ger </t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">prezero arena
-  sinsheim </t>
+          <t xml:space="preserve">millerntor stadion
+  hamburg </t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>30150</v>
+        <v>29546</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>hQAtP9Sl</t>
+          <t>ILyJuN3g</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>ILyJuN3g</t>
+          <t>nVp0wiqd</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -1378,136 +1378,136 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>26.75</v>
+        <v>27.02727272727272</v>
       </c>
       <c r="O5" t="n">
-        <v>183</v>
+        <v>184.9806818181818</v>
       </c>
       <c r="P5" t="n">
-        <v>4</v>
+        <v>70.81477272727273</v>
       </c>
       <c r="Q5" t="n">
-        <v>299</v>
+        <v>17486.36363636364</v>
       </c>
       <c r="R5" t="n">
-        <v>119000</v>
+        <v>2325340.909090909</v>
       </c>
       <c r="S5" t="n">
-        <v>26900000</v>
+        <v>73.2625</v>
       </c>
       <c r="T5" t="n">
-        <v>308</v>
+        <v>1</v>
       </c>
       <c r="U5" t="n">
-        <v>7</v>
+        <v>27.575</v>
       </c>
       <c r="V5" t="n">
-        <v>24.25</v>
+        <v>183.975</v>
       </c>
       <c r="W5" t="n">
-        <v>189.25</v>
+        <v>83.67777777777778</v>
       </c>
       <c r="X5" t="n">
-        <v>4</v>
+        <v>82602.77777777778</v>
       </c>
       <c r="Y5" t="n">
-        <v>265</v>
+        <v>49549687.5</v>
       </c>
       <c r="Z5" t="n">
-        <v>50000</v>
+        <v>85.71666666666667</v>
       </c>
       <c r="AA5" t="n">
-        <v>6140000</v>
+        <v>3.331944444444444</v>
       </c>
       <c r="AB5" t="n">
-        <v>284</v>
+        <v>25.80038377192982</v>
       </c>
       <c r="AC5" t="n">
-        <v>4</v>
+        <v>184.5357456140351</v>
       </c>
       <c r="AD5" t="n">
-        <v>27.28412698412698</v>
+        <v>67.83199013157893</v>
       </c>
       <c r="AE5" t="n">
-        <v>186.022619047619</v>
+        <v>15898.4649122807</v>
       </c>
       <c r="AF5" t="n">
-        <v>75.10119047619047</v>
+        <v>1667469.846491228</v>
       </c>
       <c r="AG5" t="n">
-        <v>29523.4126984127</v>
+        <v>71.65978618421052</v>
       </c>
       <c r="AH5" t="n">
-        <v>7488055.555555555</v>
+        <v>1</v>
       </c>
       <c r="AI5" t="n">
-        <v>78.80912698412699</v>
+        <v>26.31192917956656</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1.58452380952381</v>
+        <v>183.0611750730994</v>
       </c>
       <c r="AK5" t="n">
-        <v>26.97402597402597</v>
+        <v>80.37420020639834</v>
       </c>
       <c r="AL5" t="n">
-        <v>184.9779220779221</v>
+        <v>75434.36819172114</v>
       </c>
       <c r="AM5" t="n">
-        <v>70.81688311688312</v>
+        <v>35147016.32105693</v>
       </c>
       <c r="AN5" t="n">
-        <v>17455.84415584416</v>
+        <v>83.74456376848985</v>
       </c>
       <c r="AO5" t="n">
-        <v>2338961.038961039</v>
+        <v>2.603642070863433</v>
       </c>
       <c r="AP5" t="n">
-        <v>73.34285714285716</v>
+        <v>26.90714285714286</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1</v>
+        <v>187.3214285714286</v>
       </c>
       <c r="AR5" t="n">
-        <v>24.14646139157418</v>
+        <v>4.571428571428571</v>
       </c>
       <c r="AS5" t="n">
-        <v>184.5869674185464</v>
+        <v>301.1428571428572</v>
       </c>
       <c r="AT5" t="n">
-        <v>71.18093447905478</v>
+        <v>61142.85714285714</v>
       </c>
       <c r="AU5" t="n">
-        <v>23840.15395631937</v>
+        <v>5394285.714285715</v>
       </c>
       <c r="AV5" t="n">
-        <v>5477285.177228787</v>
+        <v>317.5714285714286</v>
       </c>
       <c r="AW5" t="n">
-        <v>78.07644707005609</v>
+        <v>4.571428571428571</v>
       </c>
       <c r="AX5" t="n">
-        <v>1.211672037235947</v>
+        <v>22.00952380952381</v>
       </c>
       <c r="AY5" t="n">
-        <v>25.78972431077694</v>
+        <v>184.8285714285714</v>
       </c>
       <c r="AZ5" t="n">
-        <v>184.683709273183</v>
+        <v>5.285714285714286</v>
       </c>
       <c r="BA5" t="n">
-        <v>67.74548872180451</v>
+        <v>385.4285714285714</v>
       </c>
       <c r="BB5" t="n">
-        <v>15883.95989974937</v>
+        <v>210428.5714285714</v>
       </c>
       <c r="BC5" t="n">
-        <v>1629786.967418546</v>
+        <v>97221428.57142857</v>
       </c>
       <c r="BD5" t="n">
-        <v>71.49511278195487</v>
+        <v>433.4285714285714</v>
       </c>
       <c r="BE5" t="n">
-        <v>1</v>
+        <v>7.142857142857143</v>
       </c>
       <c r="BF5" t="inlineStr">
         <is>
@@ -1516,42 +1516,42 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>0jdIgO6t</t>
+          <t>hpYJ6izc</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>2q7yHiho</t>
+          <t>YmumZjET</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45598.47916666666</v>
+        <v>45605.47916666666</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">kampka r 
+          <t xml:space="preserve">willenborg f 
   ger </t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">holstein stadion
-  kiel </t>
+          <t xml:space="preserve">weserstadion
+  bremen </t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>15034</v>
+        <v>42100</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
+          <t>Ig1f1fy3</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
           <t>63WsD2ei</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>KWixEVWi</t>
         </is>
       </c>
       <c r="H6" t="n">
@@ -1577,140 +1577,140 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>26.6</v>
+        <v>27.01931818181819</v>
       </c>
       <c r="O6" t="n">
-        <v>185.4</v>
+        <v>182.9647727272727</v>
       </c>
       <c r="P6" t="n">
-        <v>5</v>
+        <v>74.33636363636364</v>
       </c>
       <c r="Q6" t="n">
-        <v>346</v>
+        <v>23502.27272727273</v>
       </c>
       <c r="R6" t="n">
-        <v>81000</v>
+        <v>5967272.727272728</v>
       </c>
       <c r="S6" t="n">
-        <v>9900000</v>
+        <v>76.69431818181818</v>
       </c>
       <c r="T6" t="n">
-        <v>363</v>
+        <v>1.097727272727273</v>
       </c>
       <c r="U6" t="n">
-        <v>5</v>
+        <v>26.18159722222222</v>
       </c>
       <c r="V6" t="n">
-        <v>22</v>
+        <v>186.2173611111111</v>
       </c>
       <c r="W6" t="n">
-        <v>184.5</v>
+        <v>69.47499999999999</v>
       </c>
       <c r="X6" t="n">
-        <v>2</v>
+        <v>16258.68055555555</v>
       </c>
       <c r="Y6" t="n">
-        <v>125</v>
+        <v>1893645.833333333</v>
       </c>
       <c r="Z6" t="n">
-        <v>28000</v>
+        <v>72.51041666666667</v>
       </c>
       <c r="AA6" t="n">
-        <v>1575000</v>
+        <v>1</v>
       </c>
       <c r="AB6" t="n">
-        <v>140</v>
+        <v>24.68268878099399</v>
       </c>
       <c r="AC6" t="n">
-        <v>2</v>
+        <v>186.1664438548199</v>
       </c>
       <c r="AD6" t="n">
-        <v>26.31865079365079</v>
+        <v>70.46240321344368</v>
       </c>
       <c r="AE6" t="n">
-        <v>186.1214285714286</v>
+        <v>20019.85997293134</v>
       </c>
       <c r="AF6" t="n">
-        <v>69.57460317460318</v>
+        <v>3344203.243719476</v>
       </c>
       <c r="AG6" t="n">
-        <v>16359.12698412698</v>
+        <v>75.91573345728452</v>
       </c>
       <c r="AH6" t="n">
-        <v>1887976.19047619</v>
+        <v>1</v>
       </c>
       <c r="AI6" t="n">
-        <v>72.36111111111111</v>
+        <v>25.89556091315245</v>
       </c>
       <c r="AJ6" t="n">
+        <v>184.7922411017663</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>68.52194177390115</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>16085.17130276284</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>1807007.792455447</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>72.39919536984755</v>
+      </c>
+      <c r="AO6" t="n">
         <v>1</v>
       </c>
-      <c r="AK6" t="n">
-        <v>26.86233766233767</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>186.5961038961039</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>72.38571428571429</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>21963.63636363636</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>3179870.12987013</v>
-      </c>
       <c r="AP6" t="n">
-        <v>74.41948051948053</v>
+        <v>26.69285714285714</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.041558441558442</v>
+        <v>186.6880952380952</v>
       </c>
       <c r="AR6" t="n">
-        <v>25.80921247217423</v>
+        <v>3.142857142857143</v>
       </c>
       <c r="AS6" t="n">
-        <v>184.6716521682524</v>
+        <v>226.4285714285714</v>
       </c>
       <c r="AT6" t="n">
-        <v>68.56403735199093</v>
+        <v>66000</v>
       </c>
       <c r="AU6" t="n">
-        <v>16090.84512523545</v>
+        <v>11414285.71428571</v>
       </c>
       <c r="AV6" t="n">
-        <v>1849567.347221809</v>
+        <v>236</v>
       </c>
       <c r="AW6" t="n">
-        <v>72.64453496813745</v>
+        <v>3.142857142857143</v>
       </c>
       <c r="AX6" t="n">
-        <v>1</v>
+        <v>25.47857142857143</v>
       </c>
       <c r="AY6" t="n">
-        <v>25.95545087600258</v>
+        <v>189.1404761904762</v>
       </c>
       <c r="AZ6" t="n">
-        <v>184.9576708944448</v>
+        <v>2.714285714285714</v>
       </c>
       <c r="BA6" t="n">
-        <v>69.59322424622022</v>
+        <v>187.7142857142857</v>
       </c>
       <c r="BB6" t="n">
-        <v>20095.23635541173</v>
+        <v>41571.42857142857</v>
       </c>
       <c r="BC6" t="n">
-        <v>2205405.510030099</v>
+        <v>5300000</v>
       </c>
       <c r="BD6" t="n">
-        <v>72.24853593611358</v>
+        <v>198</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.045670442089879</v>
+        <v>2.714285714285714</v>
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>4fX0k7gg</t>
+          <t>M5BRZDsC</t>
         </is>
       </c>
       <c r="BG6" t="inlineStr">
@@ -1722,35 +1722,35 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>AoSdOZaB</t>
+          <t>j5mWxZE4</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45598.47916666666</v>
+        <v>45605.60416666666</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">willenborg f 
+          <t xml:space="preserve">dankert b 
   ger </t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">volkswagen arena
-  wolfsburg </t>
+          <t xml:space="preserve">red bull arena
+  leipzig </t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>28917</v>
+        <v>47069</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>nwkTahLL</t>
+          <t>KbS1suSm</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>fTVNku3I</t>
+          <t>88HSzjDr</t>
         </is>
       </c>
       <c r="H7" t="n">
@@ -1776,166 +1776,180 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>23.14285714285714</v>
+        <v>26.30034722222222</v>
       </c>
       <c r="O7" t="n">
-        <v>184.5714285714286</v>
+        <v>183.9454861111111</v>
       </c>
       <c r="P7" t="n">
-        <v>7</v>
+        <v>80.55312499999999</v>
       </c>
       <c r="Q7" t="n">
-        <v>519</v>
+        <v>57571.52777777778</v>
       </c>
       <c r="R7" t="n">
-        <v>232000</v>
+        <v>29693402.77777778</v>
       </c>
       <c r="S7" t="n">
-        <v>69300000</v>
+        <v>83.65138888888889</v>
       </c>
       <c r="T7" t="n">
-        <v>559</v>
+        <v>2.270486111111111</v>
       </c>
       <c r="U7" t="n">
-        <v>10</v>
+        <v>26.0875</v>
       </c>
       <c r="V7" t="n">
-        <v>26</v>
+        <v>185.0125</v>
       </c>
       <c r="W7" t="n">
-        <v>181.3333333333333</v>
+        <v>74.91250000000001</v>
       </c>
       <c r="X7" t="n">
-        <v>6</v>
+        <v>23875</v>
       </c>
       <c r="Y7" t="n">
-        <v>434</v>
+        <v>7567500</v>
       </c>
       <c r="Z7" t="n">
-        <v>119000</v>
+        <v>77.52500000000001</v>
       </c>
       <c r="AA7" t="n">
-        <v>21300000</v>
+        <v>1.375</v>
       </c>
       <c r="AB7" t="n">
-        <v>441</v>
+        <v>25.37051163168617</v>
       </c>
       <c r="AC7" t="n">
-        <v>6</v>
+        <v>185.3800319370172</v>
       </c>
       <c r="AD7" t="n">
-        <v>24.63888888888889</v>
+        <v>77.7063916126658</v>
       </c>
       <c r="AE7" t="n">
-        <v>184.8611111111111</v>
+        <v>48885.4848657964</v>
       </c>
       <c r="AF7" t="n">
-        <v>75.07870370370371</v>
+        <v>21657661.84937891</v>
       </c>
       <c r="AG7" t="n">
-        <v>35773.14814814815</v>
+        <v>82.03091706678684</v>
       </c>
       <c r="AH7" t="n">
-        <v>9584722.222222222</v>
+        <v>1.941087260262957</v>
       </c>
       <c r="AI7" t="n">
-        <v>79.68518518518518</v>
+        <v>25.69703743053286</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1.356481481481481</v>
-      </c>
-      <c r="AK7" t="inlineStr"/>
-      <c r="AL7" t="inlineStr"/>
-      <c r="AM7" t="inlineStr"/>
-      <c r="AN7" t="inlineStr"/>
-      <c r="AO7" t="inlineStr"/>
-      <c r="AP7" t="inlineStr"/>
-      <c r="AQ7" t="inlineStr"/>
+        <v>182.788760624387</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>72.99202217500272</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>22148.60044132069</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>6073390.531355562</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>77.35256074970033</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>1.259427100359595</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>24.56666666666667</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>180.9547619047619</v>
+      </c>
       <c r="AR7" t="n">
-        <v>24.97827355822712</v>
+        <v>3.571428571428572</v>
       </c>
       <c r="AS7" t="n">
-        <v>184.4948609826706</v>
+        <v>277.1428571428572</v>
       </c>
       <c r="AT7" t="n">
-        <v>73.3843148982081</v>
+        <v>176428.5714285714</v>
       </c>
       <c r="AU7" t="n">
-        <v>32916.7294908394</v>
+        <v>78214285.71428572</v>
       </c>
       <c r="AV7" t="n">
-        <v>8085787.253896774</v>
+        <v>300.2857142857143</v>
       </c>
       <c r="AW7" t="n">
-        <v>78.22329336040636</v>
+        <v>7.857142857142857</v>
       </c>
       <c r="AX7" t="n">
-        <v>1.38331440231595</v>
+        <v>22.74897959183673</v>
       </c>
       <c r="AY7" t="n">
-        <v>24.14079571222428</v>
+        <v>183.1360544217687</v>
       </c>
       <c r="AZ7" t="n">
-        <v>185.302540713255</v>
+        <v>5.285714285714286</v>
       </c>
       <c r="BA7" t="n">
-        <v>72.11047979797981</v>
+        <v>369.2857142857143</v>
       </c>
       <c r="BB7" t="n">
-        <v>20355.9188827046</v>
+        <v>75428.57142857143</v>
       </c>
       <c r="BC7" t="n">
-        <v>5060071.377035663</v>
+        <v>28896428.57142857</v>
       </c>
       <c r="BD7" t="n">
-        <v>77.12471655328798</v>
+        <v>409.1428571428572</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.077934961863533</v>
+        <v>6.857142857142857</v>
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>f3ddUIXs</t>
+          <t>IkCftsQm</t>
         </is>
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>SMaB5LKo</t>
+          <t>4fuCGs9P</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>dr2N9zoI</t>
+          <t>UJQITUyi</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45598.60416666666</v>
+        <v>45606.47916666666</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">zwayer f 
+          <t xml:space="preserve">stegemann s 
   ger </t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">signal iduna park
-  dortmund </t>
+          <t xml:space="preserve">wwk arena
+  augsburg </t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>81365</v>
+        <v>30660</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>nP1i5US1</t>
+          <t>fTVNku3I</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>KbS1suSm</t>
+          <t>hQAtP9Sl</t>
         </is>
       </c>
       <c r="H8" t="n">
@@ -1960,137 +1974,123 @@
           <t>bundesliga</t>
         </is>
       </c>
-      <c r="N8" t="n">
-        <v>23.25</v>
-      </c>
-      <c r="O8" t="n">
-        <v>185.125</v>
-      </c>
-      <c r="P8" t="n">
-        <v>8</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>615</v>
-      </c>
-      <c r="R8" t="n">
-        <v>324000</v>
-      </c>
-      <c r="S8" t="n">
-        <v>211500000</v>
-      </c>
-      <c r="T8" t="n">
-        <v>673</v>
-      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="inlineStr"/>
       <c r="U8" t="n">
-        <v>17</v>
+        <v>27.24861111111111</v>
       </c>
       <c r="V8" t="n">
-        <v>23</v>
+        <v>185.9104166666667</v>
       </c>
       <c r="W8" t="n">
-        <v>180</v>
+        <v>75.16666666666666</v>
       </c>
       <c r="X8" t="n">
-        <v>6</v>
+        <v>29614.23611111111</v>
       </c>
       <c r="Y8" t="n">
-        <v>476</v>
+        <v>7584861.111111112</v>
       </c>
       <c r="Z8" t="n">
-        <v>342000</v>
+        <v>78.94236111111111</v>
       </c>
       <c r="AA8" t="n">
-        <v>212500000</v>
+        <v>1.589583333333334</v>
       </c>
       <c r="AB8" t="n">
-        <v>514</v>
+        <v>24.06069624819624</v>
       </c>
       <c r="AC8" t="n">
-        <v>13</v>
+        <v>185.4313897907647</v>
       </c>
       <c r="AD8" t="n">
-        <v>26.55194805194805</v>
+        <v>72.04458648989899</v>
       </c>
       <c r="AE8" t="n">
-        <v>186.061038961039</v>
+        <v>20238.51235569986</v>
       </c>
       <c r="AF8" t="n">
-        <v>81.91818181818182</v>
+        <v>5071312.454906205</v>
       </c>
       <c r="AG8" t="n">
-        <v>58187.01298701298</v>
+        <v>77.21329365079364</v>
       </c>
       <c r="AH8" t="n">
-        <v>37609740.25974026</v>
+        <v>1.078609758297258</v>
       </c>
       <c r="AI8" t="n">
-        <v>84.02207792207794</v>
+        <v>24.40196324143693</v>
       </c>
       <c r="AJ8" t="n">
-        <v>2.572727272727273</v>
+        <v>184.79335839599</v>
       </c>
       <c r="AK8" t="n">
-        <v>26.21825396825397</v>
+        <v>71.46188909774436</v>
       </c>
       <c r="AL8" t="n">
-        <v>183.9019841269841</v>
+        <v>24020.84899749373</v>
       </c>
       <c r="AM8" t="n">
-        <v>80.47142857142856</v>
+        <v>5589053.10150376</v>
       </c>
       <c r="AN8" t="n">
-        <v>57349.60317460318</v>
+        <v>77.93593880534669</v>
       </c>
       <c r="AO8" t="n">
-        <v>29649603.17460318</v>
+        <v>1.220927318295739</v>
       </c>
       <c r="AP8" t="n">
-        <v>83.67301587301587</v>
+        <v>25.81666666666667</v>
       </c>
       <c r="AQ8" t="n">
-        <v>2.273412698412698</v>
+        <v>183.5928571428572</v>
       </c>
       <c r="AR8" t="n">
-        <v>25.15042122112002</v>
+        <v>5</v>
       </c>
       <c r="AS8" t="n">
-        <v>184.0055904977621</v>
+        <v>354</v>
       </c>
       <c r="AT8" t="n">
-        <v>77.436190361312</v>
+        <v>89714.28571428571</v>
       </c>
       <c r="AU8" t="n">
-        <v>43875.83250205983</v>
+        <v>14610714.28571429</v>
       </c>
       <c r="AV8" t="n">
-        <v>21774206.30772245</v>
+        <v>364.5714285714286</v>
       </c>
       <c r="AW8" t="n">
-        <v>82.62316811892221</v>
+        <v>5</v>
       </c>
       <c r="AX8" t="n">
-        <v>1.896760618122847</v>
+        <v>26.61479591836735</v>
       </c>
       <c r="AY8" t="n">
-        <v>25.41694835829069</v>
+        <v>183.0484693877551</v>
       </c>
       <c r="AZ8" t="n">
-        <v>185.2070494864613</v>
+        <v>6.142857142857143</v>
       </c>
       <c r="BA8" t="n">
-        <v>78.03457742746221</v>
+        <v>458.4285714285714</v>
       </c>
       <c r="BB8" t="n">
-        <v>49901.59309337771</v>
+        <v>169571.4285714286</v>
       </c>
       <c r="BC8" t="n">
-        <v>22673529.1265629</v>
+        <v>41042857.14285714</v>
       </c>
       <c r="BD8" t="n">
-        <v>82.08728184256158</v>
+        <v>475</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.965138687053769</v>
+        <v>9.857142857142858</v>
       </c>
       <c r="BF8" t="inlineStr">
         <is>
@@ -2106,35 +2106,35 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>GnZmQeVb</t>
+          <t>UkaNveph</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45599.47916666666</v>
+        <v>45606.5625</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">stegemann s 
+          <t xml:space="preserve">schlager d 
   ger </t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">europa park stadion
-  freiburg </t>
+          <t xml:space="preserve">mhparena
+  stuttgart </t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>34700</v>
+        <v>60449</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>fiEQZ7C7</t>
+          <t>nJQmYp1B</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>EuakNmc1</t>
+          <t>8vndvXTk</t>
         </is>
       </c>
       <c r="H9" t="n">
@@ -2160,180 +2160,180 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>25.2</v>
+        <v>24.57449494949495</v>
       </c>
       <c r="O9" t="n">
-        <v>185.8</v>
+        <v>186.0209595959596</v>
       </c>
       <c r="P9" t="n">
-        <v>5</v>
+        <v>75.80770202020202</v>
       </c>
       <c r="Q9" t="n">
-        <v>350</v>
+        <v>26603.53535353535</v>
       </c>
       <c r="R9" t="n">
-        <v>83000</v>
+        <v>13163576.38888889</v>
       </c>
       <c r="S9" t="n">
-        <v>20000000</v>
+        <v>79.51376262626263</v>
       </c>
       <c r="T9" t="n">
-        <v>374</v>
+        <v>1.472348484848485</v>
       </c>
       <c r="U9" t="n">
-        <v>5</v>
+        <v>24.24398148148148</v>
       </c>
       <c r="V9" t="n">
-        <v>25</v>
+        <v>185.4805555555556</v>
       </c>
       <c r="W9" t="n">
-        <v>185.3333333333333</v>
+        <v>75.95231481481481</v>
       </c>
       <c r="X9" t="n">
-        <v>3</v>
+        <v>33214.81481481482</v>
       </c>
       <c r="Y9" t="n">
-        <v>226</v>
+        <v>13640555.55555556</v>
       </c>
       <c r="Z9" t="n">
-        <v>84000</v>
+        <v>81.23935185185185</v>
       </c>
       <c r="AA9" t="n">
-        <v>25500000</v>
+        <v>1.681018518518519</v>
       </c>
       <c r="AB9" t="n">
-        <v>238</v>
+        <v>24.52925583188741</v>
       </c>
       <c r="AC9" t="n">
-        <v>3</v>
+        <v>185.3232520403573</v>
       </c>
       <c r="AD9" t="n">
-        <v>27.1</v>
+        <v>74.78132430435062</v>
       </c>
       <c r="AE9" t="n">
-        <v>184.2714285714286</v>
+        <v>25274.78552149605</v>
       </c>
       <c r="AF9" t="n">
-        <v>76.45714285714287</v>
+        <v>11943278.36819613</v>
       </c>
       <c r="AG9" t="n">
-        <v>26800</v>
+        <v>78.4085333526123</v>
       </c>
       <c r="AH9" t="n">
-        <v>11084285.71428571</v>
+        <v>1.497288895315211</v>
       </c>
       <c r="AI9" t="n">
-        <v>78.77142857142857</v>
+        <v>23.01548735223755</v>
       </c>
       <c r="AJ9" t="n">
-        <v>1.642857142857143</v>
+        <v>184.5430240666841</v>
       </c>
       <c r="AK9" t="n">
-        <v>26.93174603174603</v>
+        <v>73.1900859057738</v>
       </c>
       <c r="AL9" t="n">
-        <v>182.9920634920635</v>
+        <v>26812.58014270301</v>
       </c>
       <c r="AM9" t="n">
-        <v>74.43650793650795</v>
+        <v>9503560.903009528</v>
       </c>
       <c r="AN9" t="n">
-        <v>25236.50793650794</v>
+        <v>80.85620371952608</v>
       </c>
       <c r="AO9" t="n">
-        <v>6253174.603174604</v>
+        <v>1.426068262233123</v>
       </c>
       <c r="AP9" t="n">
-        <v>77.21587301587303</v>
+        <v>22.35714285714286</v>
       </c>
       <c r="AQ9" t="n">
-        <v>1.374603174603174</v>
+        <v>183.6047619047619</v>
       </c>
       <c r="AR9" t="n">
-        <v>26.68795795414067</v>
+        <v>4.285714285714286</v>
       </c>
       <c r="AS9" t="n">
-        <v>183.6705369894994</v>
+        <v>298.7142857142857</v>
       </c>
       <c r="AT9" t="n">
-        <v>73.94390182950652</v>
+        <v>77142.85714285714</v>
       </c>
       <c r="AU9" t="n">
-        <v>23628.44646075613</v>
+        <v>21278571.42857143</v>
       </c>
       <c r="AV9" t="n">
-        <v>6479137.009702987</v>
+        <v>337.4285714285714</v>
       </c>
       <c r="AW9" t="n">
-        <v>76.94869166722232</v>
+        <v>5.142857142857143</v>
       </c>
       <c r="AX9" t="n">
-        <v>1.362458497024772</v>
+        <v>19.61904761904762</v>
       </c>
       <c r="AY9" t="n">
-        <v>25.53487777886275</v>
+        <v>177.5238095238095</v>
       </c>
       <c r="AZ9" t="n">
-        <v>183.8849030521299</v>
+        <v>1.571428571428571</v>
       </c>
       <c r="BA9" t="n">
-        <v>71.15238267555826</v>
+        <v>97.42857142857143</v>
       </c>
       <c r="BB9" t="n">
-        <v>21693.97663371569</v>
+        <v>11714.28571428571</v>
       </c>
       <c r="BC9" t="n">
-        <v>3471707.436563142</v>
+        <v>3421428.571428571</v>
       </c>
       <c r="BD9" t="n">
-        <v>77.17230394550165</v>
+        <v>122.8571428571429</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.187698332921685</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>YZPE6Sx7</t>
+          <t>hAcTWKKN</t>
         </is>
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>K6A2elS9</t>
+          <t>UkPWzhq8</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>raQ4MDUN</t>
+          <t>xMovyDqH</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45599.5625</v>
+        <v>45606.64583333334</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">burda m 
+          <t xml:space="preserve">brych f 
   ger </t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">borussia park
-  monchengladbach </t>
+          <t xml:space="preserve">voith arena
+  heidenheim </t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>54042</v>
+        <v>15000</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>88HSzjDr</t>
+          <t>KWixEVWi</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Ig1f1fy3</t>
+          <t>nwkTahLL</t>
         </is>
       </c>
       <c r="H10" t="n">
@@ -2359,145 +2359,145 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>23.14285714285714</v>
+        <v>26.84204545454546</v>
       </c>
       <c r="O10" t="n">
-        <v>184.2857142857143</v>
+        <v>186.4840909090909</v>
       </c>
       <c r="P10" t="n">
-        <v>7</v>
+        <v>72.46250000000001</v>
       </c>
       <c r="Q10" t="n">
-        <v>495</v>
+        <v>22043.18181818182</v>
       </c>
       <c r="R10" t="n">
-        <v>105000</v>
+        <v>3228636.363636364</v>
       </c>
       <c r="S10" t="n">
-        <v>34225000</v>
+        <v>74.49204545454546</v>
       </c>
       <c r="T10" t="n">
-        <v>542</v>
+        <v>1.048863636363636</v>
       </c>
       <c r="U10" t="n">
-        <v>9</v>
+        <v>24.63888888888889</v>
       </c>
       <c r="V10" t="n">
-        <v>26.75</v>
+        <v>184.8611111111111</v>
       </c>
       <c r="W10" t="n">
-        <v>187.25</v>
+        <v>75.07870370370371</v>
       </c>
       <c r="X10" t="n">
-        <v>4</v>
+        <v>35773.14814814815</v>
       </c>
       <c r="Y10" t="n">
-        <v>292</v>
+        <v>9584722.222222222</v>
       </c>
       <c r="Z10" t="n">
-        <v>90000</v>
+        <v>79.68518518518518</v>
       </c>
       <c r="AA10" t="n">
-        <v>17500000</v>
+        <v>1.356481481481481</v>
       </c>
       <c r="AB10" t="n">
-        <v>304</v>
+        <v>25.99362821215443</v>
       </c>
       <c r="AC10" t="n">
-        <v>4</v>
+        <v>185.1477446413348</v>
       </c>
       <c r="AD10" t="n">
-        <v>26.17142857142857</v>
+        <v>69.55711469370357</v>
       </c>
       <c r="AE10" t="n">
-        <v>185.0571428571429</v>
+        <v>20094.20137620265</v>
       </c>
       <c r="AF10" t="n">
-        <v>75.02857142857144</v>
+        <v>2177827.647363293</v>
       </c>
       <c r="AG10" t="n">
-        <v>23942.85714285714</v>
+        <v>72.18486024844721</v>
       </c>
       <c r="AH10" t="n">
-        <v>7564285.714285715</v>
+        <v>1.04539641943734</v>
       </c>
       <c r="AI10" t="n">
-        <v>77.47142857142856</v>
+        <v>25.08425023301394</v>
       </c>
       <c r="AJ10" t="n">
-        <v>1.385714285714286</v>
+        <v>184.356916403315</v>
       </c>
       <c r="AK10" t="n">
-        <v>27.07922077922078</v>
+        <v>73.46671031854078</v>
       </c>
       <c r="AL10" t="n">
-        <v>183.0168831168831</v>
+        <v>33329.31221752795</v>
       </c>
       <c r="AM10" t="n">
-        <v>74.35584415584415</v>
+        <v>8219357.325420547</v>
       </c>
       <c r="AN10" t="n">
-        <v>23616.88311688312</v>
+        <v>78.25516429905122</v>
       </c>
       <c r="AO10" t="n">
-        <v>5964025.974025974</v>
+        <v>1.395182710722109</v>
       </c>
       <c r="AP10" t="n">
-        <v>76.66493506493507</v>
+        <v>24.16666666666666</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1.097402597402597</v>
+        <v>185.5952380952381</v>
       </c>
       <c r="AR10" t="n">
-        <v>25.68481296408724</v>
+        <v>3</v>
       </c>
       <c r="AS10" t="n">
-        <v>182.7337388502312</v>
+        <v>201.2857142857143</v>
       </c>
       <c r="AT10" t="n">
-        <v>73.00951602609007</v>
+        <v>52000</v>
       </c>
       <c r="AU10" t="n">
-        <v>22113.92845467707</v>
+        <v>5717857.142857143</v>
       </c>
       <c r="AV10" t="n">
-        <v>6009154.396083376</v>
+        <v>215.7142857142857</v>
       </c>
       <c r="AW10" t="n">
-        <v>77.29112532885007</v>
+        <v>3.285714285714286</v>
       </c>
       <c r="AX10" t="n">
-        <v>1.246798673702891</v>
+        <v>23.7891156462585</v>
       </c>
       <c r="AY10" t="n">
-        <v>24.48829028386891</v>
+        <v>183.2982993197279</v>
       </c>
       <c r="AZ10" t="n">
-        <v>186.1591656477444</v>
+        <v>5.571428571428571</v>
       </c>
       <c r="BA10" t="n">
-        <v>70.35454777188596</v>
+        <v>412.1428571428572</v>
       </c>
       <c r="BB10" t="n">
-        <v>19799.09462744948</v>
+        <v>195571.4285714286</v>
       </c>
       <c r="BC10" t="n">
-        <v>3362319.235058284</v>
+        <v>59085714.28571428</v>
       </c>
       <c r="BD10" t="n">
-        <v>76.06518606298354</v>
+        <v>443.2857142857143</v>
       </c>
       <c r="BE10" t="n">
-        <v>1</v>
+        <v>8.571428571428571</v>
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>UgdQz0fK</t>
+          <t>A15eUM4C</t>
         </is>
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>4fuCGs9P</t>
+          <t>2VSFgl3c</t>
         </is>
       </c>
     </row>

--- a/data/germany/p6_deployment/data_preparation/df_filled.xlsx
+++ b/data/germany/p6_deployment/data_preparation/df_filled.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BG10"/>
+  <dimension ref="A1:BG17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -465,262 +465,262 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t>id_country</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>id_competition</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>is_cup</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>season</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>country</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>competition</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>mean_age_player_start_home</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>mean_hei_player_start_home</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>mean_rat_player_start_home</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>mean_wage_player_start_home</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>mean_value_player_start_home</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>mean_pot_player_start_home</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>mean_rep_player_start_home</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>mean_age_player_start_away</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>mean_hei_player_start_away</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>mean_rat_player_start_away</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>mean_wage_player_start_away</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>mean_value_player_start_away</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>mean_pot_player_start_away</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>mean_rep_player_start_away</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>mean_age_player_sub_home</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>mean_hei_player_sub_home</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>mean_rat_player_sub_home</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>mean_wage_player_sub_home</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>mean_value_player_sub_home</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>mean_pot_player_sub_home</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>mean_rep_player_sub_home</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>mean_age_player_sub_away</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>mean_hei_player_sub_away</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>mean_rat_player_sub_away</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>mean_wage_player_sub_away</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>mean_value_player_sub_away</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>mean_pot_player_sub_away</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>mean_rep_player_sub_away</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>mean_age_player_miss_home</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>mean_hei_player_miss_home</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>n_player_miss_home</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>sum_rat_player_miss_home</t>
         </is>
       </c>
-      <c r="AT1" s="1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>sum_wage_player_miss_home</t>
         </is>
       </c>
-      <c r="AU1" s="1" t="inlineStr">
+      <c r="AW1" s="1" t="inlineStr">
         <is>
           <t>sum_value_player_miss_home</t>
         </is>
       </c>
-      <c r="AV1" s="1" t="inlineStr">
+      <c r="AX1" s="1" t="inlineStr">
         <is>
           <t>sum_pot_player_miss_home</t>
         </is>
       </c>
-      <c r="AW1" s="1" t="inlineStr">
+      <c r="AY1" s="1" t="inlineStr">
         <is>
           <t>sum_rep_player_miss_home</t>
         </is>
       </c>
-      <c r="AX1" s="1" t="inlineStr">
+      <c r="AZ1" s="1" t="inlineStr">
         <is>
           <t>mean_age_player_miss_away</t>
         </is>
       </c>
-      <c r="AY1" s="1" t="inlineStr">
+      <c r="BA1" s="1" t="inlineStr">
         <is>
           <t>mean_hei_player_miss_away</t>
         </is>
       </c>
-      <c r="AZ1" s="1" t="inlineStr">
+      <c r="BB1" s="1" t="inlineStr">
         <is>
           <t>n_player_miss_away</t>
         </is>
       </c>
-      <c r="BA1" s="1" t="inlineStr">
+      <c r="BC1" s="1" t="inlineStr">
         <is>
           <t>sum_rat_player_miss_away</t>
         </is>
       </c>
-      <c r="BB1" s="1" t="inlineStr">
+      <c r="BD1" s="1" t="inlineStr">
         <is>
           <t>sum_wage_player_miss_away</t>
         </is>
       </c>
-      <c r="BC1" s="1" t="inlineStr">
+      <c r="BE1" s="1" t="inlineStr">
         <is>
           <t>sum_value_player_miss_away</t>
         </is>
       </c>
-      <c r="BD1" s="1" t="inlineStr">
+      <c r="BF1" s="1" t="inlineStr">
         <is>
           <t>sum_pot_player_miss_away</t>
         </is>
       </c>
-      <c r="BE1" s="1" t="inlineStr">
+      <c r="BG1" s="1" t="inlineStr">
         <is>
           <t>sum_rep_player_miss_away</t>
-        </is>
-      </c>
-      <c r="BF1" s="1" t="inlineStr">
-        <is>
-          <t>id_coach_home</t>
-        </is>
-      </c>
-      <c r="BG1" s="1" t="inlineStr">
-        <is>
-          <t>id_coach_away</t>
         </is>
       </c>
     </row>
@@ -735,7 +735,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">brand b 
+          <t xml:space="preserve">reichel t 
   ger </t>
         </is>
       </c>
@@ -758,169 +758,169 @@
           <t>fiEQZ7C7</t>
         </is>
       </c>
-      <c r="H2" t="n">
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>hpYJ6izc</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>YZPE6Sx7</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
         <v>59</v>
       </c>
-      <c r="I2" t="n">
+      <c r="K2" t="n">
         <v>591</v>
       </c>
-      <c r="J2" t="n">
+      <c r="L2" t="n">
         <v>0</v>
       </c>
-      <c r="K2" t="n">
+      <c r="M2" t="n">
         <v>20242025</v>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>germany</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>bundesliga</t>
         </is>
       </c>
-      <c r="N2" t="n">
-        <v>26.73282828282828</v>
-      </c>
-      <c r="O2" t="n">
-        <v>186.4034090909091</v>
-      </c>
       <c r="P2" t="n">
-        <v>74.49166666666666</v>
+        <v>27.09090909090909</v>
       </c>
       <c r="Q2" t="n">
-        <v>26611.99494949495</v>
+        <v>185.8181818181818</v>
       </c>
       <c r="R2" t="n">
-        <v>6037575.757575758</v>
+        <v>74.45454545454545</v>
       </c>
       <c r="S2" t="n">
-        <v>77.49595959595959</v>
+        <v>26636.36363636364</v>
       </c>
       <c r="T2" t="n">
-        <v>1.338510101010101</v>
+        <v>5963636.363636363</v>
       </c>
       <c r="U2" t="n">
+        <v>77.27272727272727</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1.363636363636364</v>
+      </c>
+      <c r="W2" t="n">
         <v>27.1</v>
       </c>
-      <c r="V2" t="n">
-        <v>184.25</v>
-      </c>
-      <c r="W2" t="n">
-        <v>76.51250000000002</v>
-      </c>
       <c r="X2" t="n">
-        <v>26875</v>
+        <v>184.1</v>
       </c>
       <c r="Y2" t="n">
-        <v>11181250</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="Z2" t="n">
-        <v>78.8</v>
+        <v>27400</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.65</v>
+        <v>11860000</v>
       </c>
       <c r="AB2" t="n">
-        <v>26.32467740910247</v>
+        <v>79</v>
       </c>
       <c r="AC2" t="n">
-        <v>182.5191663488431</v>
+        <v>1.7</v>
       </c>
       <c r="AD2" t="n">
-        <v>73.17101926010679</v>
+        <v>28.85714285714286</v>
       </c>
       <c r="AE2" t="n">
-        <v>25448.02949402492</v>
+        <v>180.7142857142857</v>
       </c>
       <c r="AF2" t="n">
-        <v>4287583.587592169</v>
+        <v>73.57142857142857</v>
       </c>
       <c r="AG2" t="n">
-        <v>75.89593821510297</v>
+        <v>27428.57142857143</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.110020976353928</v>
+        <v>4014285.714285714</v>
       </c>
       <c r="AI2" t="n">
-        <v>26.65878139169127</v>
+        <v>74.14285714285714</v>
       </c>
       <c r="AJ2" t="n">
-        <v>183.677628956721</v>
+        <v>1.142857142857143</v>
       </c>
       <c r="AK2" t="n">
-        <v>73.94523228263637</v>
+        <v>26.625</v>
       </c>
       <c r="AL2" t="n">
-        <v>23646.48156225253</v>
+        <v>183.25</v>
       </c>
       <c r="AM2" t="n">
-        <v>6517540.338035568</v>
+        <v>72.875</v>
       </c>
       <c r="AN2" t="n">
-        <v>76.99487793609227</v>
+        <v>22375</v>
       </c>
       <c r="AO2" t="n">
-        <v>1.373969366714857</v>
+        <v>4600000</v>
       </c>
       <c r="AP2" t="n">
-        <v>28.69047619047619</v>
+        <v>76.125</v>
       </c>
       <c r="AQ2" t="n">
-        <v>179.8333333333333</v>
+        <v>1.25</v>
       </c>
       <c r="AR2" t="n">
-        <v>2.857142857142857</v>
+        <v>27.66666666666667</v>
       </c>
       <c r="AS2" t="n">
-        <v>212.8571428571429</v>
+        <v>182.3333333333333</v>
       </c>
       <c r="AT2" t="n">
-        <v>89571.42857142857</v>
+        <v>3</v>
       </c>
       <c r="AU2" t="n">
-        <v>16428571.42857143</v>
+        <v>222</v>
       </c>
       <c r="AV2" t="n">
-        <v>214.1428571428571</v>
+        <v>89000</v>
       </c>
       <c r="AW2" t="n">
+        <v>17100000</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>225</v>
+      </c>
+      <c r="AY2" t="n">
         <v>4</v>
       </c>
-      <c r="AX2" t="n">
-        <v>25.86428571428572</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>185.8047619047619</v>
-      </c>
       <c r="AZ2" t="n">
-        <v>5.142857142857143</v>
+        <v>24.66666666666667</v>
       </c>
       <c r="BA2" t="n">
-        <v>363.7142857142857</v>
+        <v>186.5</v>
       </c>
       <c r="BB2" t="n">
-        <v>93285.71428571429</v>
+        <v>6</v>
       </c>
       <c r="BC2" t="n">
-        <v>22871428.57142857</v>
+        <v>420</v>
       </c>
       <c r="BD2" t="n">
-        <v>383.4285714285714</v>
+        <v>99000</v>
       </c>
       <c r="BE2" t="n">
-        <v>5.428571428571429</v>
-      </c>
-      <c r="BF2" t="inlineStr">
-        <is>
-          <t>K6A2elS9</t>
-        </is>
-      </c>
-      <c r="BG2" t="inlineStr">
-        <is>
-          <t>vZA6VYpf</t>
-        </is>
+        <v>23100000</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>451</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="3">
@@ -934,7 +934,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">siebert d 
+          <t xml:space="preserve">hartmann r 
   ger </t>
         </is>
       </c>
@@ -957,169 +957,169 @@
           <t>4jcj2zMd</t>
         </is>
       </c>
-      <c r="H3" t="n">
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>UgdQz0fK</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>GzfvcwRj</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
         <v>59</v>
       </c>
-      <c r="I3" t="n">
+      <c r="K3" t="n">
         <v>591</v>
       </c>
-      <c r="J3" t="n">
+      <c r="L3" t="n">
         <v>0</v>
       </c>
-      <c r="K3" t="n">
+      <c r="M3" t="n">
         <v>20242025</v>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>germany</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>bundesliga</t>
         </is>
       </c>
-      <c r="N3" t="n">
+      <c r="P3" t="n">
         <v>28.34490740740741</v>
       </c>
-      <c r="O3" t="n">
+      <c r="Q3" t="n">
         <v>186.0833333333333</v>
       </c>
-      <c r="P3" t="n">
+      <c r="R3" t="n">
         <v>71.69907407407408</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="S3" t="n">
         <v>16979.16666666667</v>
       </c>
-      <c r="R3" t="n">
+      <c r="T3" t="n">
         <v>2252025.462962963</v>
       </c>
-      <c r="S3" t="n">
+      <c r="U3" t="n">
         <v>73.83796296296296</v>
       </c>
-      <c r="T3" t="n">
+      <c r="V3" t="n">
         <v>1</v>
       </c>
-      <c r="U3" t="n">
+      <c r="W3" t="n">
         <v>26.50448232323232</v>
       </c>
-      <c r="V3" t="n">
+      <c r="X3" t="n">
         <v>184.5846590909091</v>
       </c>
-      <c r="W3" t="n">
+      <c r="Y3" t="n">
         <v>83.60921717171718</v>
       </c>
-      <c r="X3" t="n">
+      <c r="Z3" t="n">
         <v>99236.93181818182</v>
       </c>
-      <c r="Y3" t="n">
+      <c r="AA3" t="n">
         <v>48423295.45454545</v>
       </c>
-      <c r="Z3" t="n">
+      <c r="AB3" t="n">
         <v>85.70018939393938</v>
       </c>
-      <c r="AA3" t="n">
+      <c r="AC3" t="n">
         <v>3.023863636363636</v>
       </c>
-      <c r="AB3" t="n">
+      <c r="AD3" t="n">
         <v>26.41635443122857</v>
       </c>
-      <c r="AC3" t="n">
+      <c r="AE3" t="n">
         <v>184.6034581995681</v>
       </c>
-      <c r="AD3" t="n">
+      <c r="AF3" t="n">
         <v>69.04034053919638</v>
       </c>
-      <c r="AE3" t="n">
+      <c r="AG3" t="n">
         <v>16141.66687622065</v>
       </c>
-      <c r="AF3" t="n">
+      <c r="AH3" t="n">
         <v>1787561.084986714</v>
       </c>
-      <c r="AG3" t="n">
+      <c r="AI3" t="n">
         <v>73.39604725302665</v>
       </c>
-      <c r="AH3" t="n">
+      <c r="AJ3" t="n">
         <v>1</v>
       </c>
-      <c r="AI3" t="n">
+      <c r="AK3" t="n">
         <v>24.63972895976573</v>
       </c>
-      <c r="AJ3" t="n">
+      <c r="AL3" t="n">
         <v>181.6395150294966</v>
       </c>
-      <c r="AK3" t="n">
+      <c r="AM3" t="n">
         <v>80.36146217956879</v>
       </c>
-      <c r="AL3" t="n">
+      <c r="AN3" t="n">
         <v>81495.40998217469</v>
       </c>
-      <c r="AM3" t="n">
+      <c r="AO3" t="n">
         <v>38064377.54315741</v>
       </c>
-      <c r="AN3" t="n">
+      <c r="AP3" t="n">
         <v>84.05611007660639</v>
       </c>
-      <c r="AO3" t="n">
+      <c r="AQ3" t="n">
         <v>2.364937584882438</v>
       </c>
-      <c r="AP3" t="n">
-        <v>25.95238095238095</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>186.25</v>
-      </c>
       <c r="AR3" t="n">
-        <v>3.142857142857143</v>
+        <v>23.5</v>
       </c>
       <c r="AS3" t="n">
-        <v>220.4285714285714</v>
+        <v>182.5</v>
       </c>
       <c r="AT3" t="n">
-        <v>52571.42857142857</v>
+        <v>4</v>
       </c>
       <c r="AU3" t="n">
-        <v>8253571.428571428</v>
+        <v>274</v>
       </c>
       <c r="AV3" t="n">
-        <v>232</v>
+        <v>73000</v>
       </c>
       <c r="AW3" t="n">
-        <v>3.428571428571428</v>
+        <v>9675000</v>
       </c>
       <c r="AX3" t="n">
+        <v>301</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>4</v>
+      </c>
+      <c r="AZ3" t="n">
         <v>24</v>
       </c>
-      <c r="AY3" t="n">
-        <v>174</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>1</v>
-      </c>
       <c r="BA3" t="n">
-        <v>78</v>
+        <v>181.75</v>
       </c>
       <c r="BB3" t="n">
-        <v>64000</v>
+        <v>4</v>
       </c>
       <c r="BC3" t="n">
-        <v>28500000</v>
+        <v>306</v>
       </c>
       <c r="BD3" t="n">
-        <v>85</v>
+        <v>246000</v>
       </c>
       <c r="BE3" t="n">
-        <v>1</v>
-      </c>
-      <c r="BF3" t="inlineStr">
-        <is>
-          <t>UgdQz0fK</t>
-        </is>
-      </c>
-      <c r="BG3" t="inlineStr">
-        <is>
-          <t>GzfvcwRj</t>
-        </is>
+        <v>71000000</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>327</v>
+      </c>
+      <c r="BG3" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="4">
@@ -1133,7 +1133,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">stieler t 
+          <t xml:space="preserve">badstubner f 
   ger </t>
         </is>
       </c>
@@ -1156,169 +1156,169 @@
           <t>nP1i5US1</t>
         </is>
       </c>
-      <c r="H4" t="n">
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>YZPE6Sx7</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>pfoInmcq</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
         <v>59</v>
       </c>
-      <c r="I4" t="n">
+      <c r="K4" t="n">
         <v>591</v>
       </c>
-      <c r="J4" t="n">
+      <c r="L4" t="n">
         <v>0</v>
       </c>
-      <c r="K4" t="n">
+      <c r="M4" t="n">
         <v>20242025</v>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>germany</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>bundesliga</t>
         </is>
       </c>
-      <c r="N4" t="n">
+      <c r="P4" t="n">
         <v>27.01527777777778</v>
       </c>
-      <c r="O4" t="n">
+      <c r="Q4" t="n">
         <v>182.9430555555556</v>
       </c>
-      <c r="P4" t="n">
+      <c r="R4" t="n">
         <v>74.41944444444445</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="S4" t="n">
         <v>24981.94444444445</v>
       </c>
-      <c r="R4" t="n">
+      <c r="T4" t="n">
         <v>6222777.777777778</v>
       </c>
-      <c r="S4" t="n">
+      <c r="U4" t="n">
         <v>77.15138888888889</v>
       </c>
-      <c r="T4" t="n">
+      <c r="V4" t="n">
         <v>1.377777777777778</v>
       </c>
-      <c r="U4" t="n">
+      <c r="W4" t="n">
         <v>26.61931818181818</v>
       </c>
-      <c r="V4" t="n">
+      <c r="X4" t="n">
         <v>186.0761363636364</v>
       </c>
-      <c r="W4" t="n">
+      <c r="Y4" t="n">
         <v>81.72386363636363</v>
       </c>
-      <c r="X4" t="n">
+      <c r="Z4" t="n">
         <v>57572.72727272727</v>
       </c>
-      <c r="Y4" t="n">
+      <c r="AA4" t="n">
         <v>36480113.63636364</v>
       </c>
-      <c r="Z4" t="n">
+      <c r="AB4" t="n">
         <v>83.87159090909091</v>
       </c>
-      <c r="AA4" t="n">
+      <c r="AC4" t="n">
         <v>2.523863636363636</v>
       </c>
-      <c r="AB4" t="n">
+      <c r="AD4" t="n">
         <v>25.5305180565049</v>
       </c>
-      <c r="AC4" t="n">
+      <c r="AE4" t="n">
         <v>183.6403615991851</v>
       </c>
-      <c r="AD4" t="n">
+      <c r="AF4" t="n">
         <v>71.26726341254205</v>
       </c>
-      <c r="AE4" t="n">
+      <c r="AG4" t="n">
         <v>21928.6581259298</v>
       </c>
-      <c r="AF4" t="n">
+      <c r="AH4" t="n">
         <v>3633502.935564177</v>
       </c>
-      <c r="AG4" t="n">
+      <c r="AI4" t="n">
         <v>77.18648023802822</v>
       </c>
-      <c r="AH4" t="n">
+      <c r="AJ4" t="n">
         <v>1.199950327020761</v>
       </c>
-      <c r="AI4" t="n">
+      <c r="AK4" t="n">
         <v>24.86772967959113</v>
       </c>
-      <c r="AJ4" t="n">
+      <c r="AL4" t="n">
         <v>183.6715583522085</v>
       </c>
-      <c r="AK4" t="n">
+      <c r="AM4" t="n">
         <v>77.07611101059243</v>
       </c>
-      <c r="AL4" t="n">
+      <c r="AN4" t="n">
         <v>43169.13121708013</v>
       </c>
-      <c r="AM4" t="n">
+      <c r="AO4" t="n">
         <v>22125694.40814603</v>
       </c>
-      <c r="AN4" t="n">
+      <c r="AP4" t="n">
         <v>82.51749432627915</v>
       </c>
-      <c r="AO4" t="n">
+      <c r="AQ4" t="n">
         <v>1.895776651968602</v>
       </c>
-      <c r="AP4" t="n">
-        <v>27.91666666666667</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>184.9166666666667</v>
-      </c>
       <c r="AR4" t="n">
-        <v>1.5</v>
+        <v>26</v>
       </c>
       <c r="AS4" t="n">
-        <v>112.8333333333333</v>
+        <v>187.5</v>
       </c>
       <c r="AT4" t="n">
-        <v>40500</v>
+        <v>2</v>
       </c>
       <c r="AU4" t="n">
-        <v>10516666.66666667</v>
+        <v>150</v>
       </c>
       <c r="AV4" t="n">
-        <v>115</v>
+        <v>58000</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.833333333333333</v>
+        <v>13500000</v>
       </c>
       <c r="AX4" t="n">
-        <v>21.79761904761904</v>
+        <v>156</v>
       </c>
       <c r="AY4" t="n">
-        <v>183.7797619047619</v>
+        <v>2</v>
       </c>
       <c r="AZ4" t="n">
-        <v>3.285714285714286</v>
+        <v>24.625</v>
       </c>
       <c r="BA4" t="n">
-        <v>249.8571428571429</v>
+        <v>185.375</v>
       </c>
       <c r="BB4" t="n">
-        <v>121142.8571428571</v>
+        <v>8</v>
       </c>
       <c r="BC4" t="n">
-        <v>74157142.85714285</v>
+        <v>628</v>
       </c>
       <c r="BD4" t="n">
-        <v>276.8571428571428</v>
+        <v>352000</v>
       </c>
       <c r="BE4" t="n">
-        <v>6.714285714285714</v>
-      </c>
-      <c r="BF4" t="inlineStr">
-        <is>
-          <t>YZPE6Sx7</t>
-        </is>
-      </c>
-      <c r="BG4" t="inlineStr">
-        <is>
-          <t>pfoInmcq</t>
-        </is>
+        <v>222200000</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>668</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>18</v>
       </c>
     </row>
     <row r="5">
@@ -1332,7 +1332,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">jollenbeck m 
+          <t xml:space="preserve">gerach t 
   ger </t>
         </is>
       </c>
@@ -1355,169 +1355,169 @@
           <t>nVp0wiqd</t>
         </is>
       </c>
-      <c r="H5" t="n">
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>KUx4Q7x1</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>hpYJ6izc</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
         <v>59</v>
       </c>
-      <c r="I5" t="n">
+      <c r="K5" t="n">
         <v>591</v>
       </c>
-      <c r="J5" t="n">
+      <c r="L5" t="n">
         <v>0</v>
       </c>
-      <c r="K5" t="n">
+      <c r="M5" t="n">
         <v>20242025</v>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>germany</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>bundesliga</t>
         </is>
       </c>
-      <c r="N5" t="n">
+      <c r="P5" t="n">
         <v>27.02727272727272</v>
       </c>
-      <c r="O5" t="n">
+      <c r="Q5" t="n">
         <v>184.9806818181818</v>
       </c>
-      <c r="P5" t="n">
+      <c r="R5" t="n">
         <v>70.81477272727273</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="S5" t="n">
         <v>17486.36363636364</v>
       </c>
-      <c r="R5" t="n">
+      <c r="T5" t="n">
         <v>2325340.909090909</v>
       </c>
-      <c r="S5" t="n">
+      <c r="U5" t="n">
         <v>73.2625</v>
       </c>
-      <c r="T5" t="n">
+      <c r="V5" t="n">
         <v>1</v>
       </c>
-      <c r="U5" t="n">
+      <c r="W5" t="n">
         <v>27.575</v>
       </c>
-      <c r="V5" t="n">
+      <c r="X5" t="n">
         <v>183.975</v>
       </c>
-      <c r="W5" t="n">
+      <c r="Y5" t="n">
         <v>83.67777777777778</v>
       </c>
-      <c r="X5" t="n">
+      <c r="Z5" t="n">
         <v>82602.77777777778</v>
       </c>
-      <c r="Y5" t="n">
+      <c r="AA5" t="n">
         <v>49549687.5</v>
       </c>
-      <c r="Z5" t="n">
+      <c r="AB5" t="n">
         <v>85.71666666666667</v>
       </c>
-      <c r="AA5" t="n">
+      <c r="AC5" t="n">
         <v>3.331944444444444</v>
       </c>
-      <c r="AB5" t="n">
+      <c r="AD5" t="n">
         <v>25.80038377192982</v>
       </c>
-      <c r="AC5" t="n">
+      <c r="AE5" t="n">
         <v>184.5357456140351</v>
       </c>
-      <c r="AD5" t="n">
+      <c r="AF5" t="n">
         <v>67.83199013157893</v>
       </c>
-      <c r="AE5" t="n">
+      <c r="AG5" t="n">
         <v>15898.4649122807</v>
       </c>
-      <c r="AF5" t="n">
+      <c r="AH5" t="n">
         <v>1667469.846491228</v>
       </c>
-      <c r="AG5" t="n">
+      <c r="AI5" t="n">
         <v>71.65978618421052</v>
       </c>
-      <c r="AH5" t="n">
+      <c r="AJ5" t="n">
         <v>1</v>
       </c>
-      <c r="AI5" t="n">
+      <c r="AK5" t="n">
         <v>26.31192917956656</v>
       </c>
-      <c r="AJ5" t="n">
+      <c r="AL5" t="n">
         <v>183.0611750730994</v>
       </c>
-      <c r="AK5" t="n">
+      <c r="AM5" t="n">
         <v>80.37420020639834</v>
       </c>
-      <c r="AL5" t="n">
+      <c r="AN5" t="n">
         <v>75434.36819172114</v>
       </c>
-      <c r="AM5" t="n">
+      <c r="AO5" t="n">
         <v>35147016.32105693</v>
       </c>
-      <c r="AN5" t="n">
+      <c r="AP5" t="n">
         <v>83.74456376848985</v>
       </c>
-      <c r="AO5" t="n">
+      <c r="AQ5" t="n">
         <v>2.603642070863433</v>
       </c>
-      <c r="AP5" t="n">
-        <v>26.90714285714286</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>187.3214285714286</v>
-      </c>
       <c r="AR5" t="n">
-        <v>4.571428571428571</v>
+        <v>23.66666666666667</v>
       </c>
       <c r="AS5" t="n">
-        <v>301.1428571428572</v>
+        <v>185.3333333333333</v>
       </c>
       <c r="AT5" t="n">
-        <v>61142.85714285714</v>
+        <v>6</v>
       </c>
       <c r="AU5" t="n">
-        <v>5394285.714285715</v>
+        <v>397</v>
       </c>
       <c r="AV5" t="n">
-        <v>317.5714285714286</v>
+        <v>77000</v>
       </c>
       <c r="AW5" t="n">
-        <v>4.571428571428571</v>
+        <v>9940000</v>
       </c>
       <c r="AX5" t="n">
-        <v>22.00952380952381</v>
+        <v>432</v>
       </c>
       <c r="AY5" t="n">
-        <v>184.8285714285714</v>
+        <v>6</v>
       </c>
       <c r="AZ5" t="n">
-        <v>5.285714285714286</v>
+        <v>22.2</v>
       </c>
       <c r="BA5" t="n">
-        <v>385.4285714285714</v>
+        <v>185.8</v>
       </c>
       <c r="BB5" t="n">
-        <v>210428.5714285714</v>
+        <v>5</v>
       </c>
       <c r="BC5" t="n">
-        <v>97221428.57142857</v>
+        <v>368</v>
       </c>
       <c r="BD5" t="n">
-        <v>433.4285714285714</v>
+        <v>195000</v>
       </c>
       <c r="BE5" t="n">
-        <v>7.142857142857143</v>
-      </c>
-      <c r="BF5" t="inlineStr">
-        <is>
-          <t>KUx4Q7x1</t>
-        </is>
-      </c>
-      <c r="BG5" t="inlineStr">
-        <is>
-          <t>hpYJ6izc</t>
-        </is>
+        <v>67150000</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>412</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="6">
@@ -1531,7 +1531,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">willenborg f 
+          <t xml:space="preserve">storks s 
   ger </t>
         </is>
       </c>
@@ -1554,169 +1554,169 @@
           <t>63WsD2ei</t>
         </is>
       </c>
-      <c r="H6" t="n">
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>M5BRZDsC</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>4ljanukM</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
         <v>59</v>
       </c>
-      <c r="I6" t="n">
+      <c r="K6" t="n">
         <v>591</v>
       </c>
-      <c r="J6" t="n">
+      <c r="L6" t="n">
         <v>0</v>
       </c>
-      <c r="K6" t="n">
+      <c r="M6" t="n">
         <v>20242025</v>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>germany</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>bundesliga</t>
         </is>
       </c>
-      <c r="N6" t="n">
+      <c r="P6" t="n">
         <v>27.01931818181819</v>
       </c>
-      <c r="O6" t="n">
+      <c r="Q6" t="n">
         <v>182.9647727272727</v>
       </c>
-      <c r="P6" t="n">
+      <c r="R6" t="n">
         <v>74.33636363636364</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="S6" t="n">
         <v>23502.27272727273</v>
       </c>
-      <c r="R6" t="n">
+      <c r="T6" t="n">
         <v>5967272.727272728</v>
       </c>
-      <c r="S6" t="n">
+      <c r="U6" t="n">
         <v>76.69431818181818</v>
       </c>
-      <c r="T6" t="n">
+      <c r="V6" t="n">
         <v>1.097727272727273</v>
       </c>
-      <c r="U6" t="n">
+      <c r="W6" t="n">
         <v>26.18159722222222</v>
       </c>
-      <c r="V6" t="n">
+      <c r="X6" t="n">
         <v>186.2173611111111</v>
       </c>
-      <c r="W6" t="n">
+      <c r="Y6" t="n">
         <v>69.47499999999999</v>
       </c>
-      <c r="X6" t="n">
+      <c r="Z6" t="n">
         <v>16258.68055555555</v>
       </c>
-      <c r="Y6" t="n">
+      <c r="AA6" t="n">
         <v>1893645.833333333</v>
       </c>
-      <c r="Z6" t="n">
+      <c r="AB6" t="n">
         <v>72.51041666666667</v>
       </c>
-      <c r="AA6" t="n">
+      <c r="AC6" t="n">
         <v>1</v>
       </c>
-      <c r="AB6" t="n">
+      <c r="AD6" t="n">
         <v>24.68268878099399</v>
       </c>
-      <c r="AC6" t="n">
+      <c r="AE6" t="n">
         <v>186.1664438548199</v>
       </c>
-      <c r="AD6" t="n">
+      <c r="AF6" t="n">
         <v>70.46240321344368</v>
       </c>
-      <c r="AE6" t="n">
+      <c r="AG6" t="n">
         <v>20019.85997293134</v>
       </c>
-      <c r="AF6" t="n">
+      <c r="AH6" t="n">
         <v>3344203.243719476</v>
       </c>
-      <c r="AG6" t="n">
+      <c r="AI6" t="n">
         <v>75.91573345728452</v>
       </c>
-      <c r="AH6" t="n">
+      <c r="AJ6" t="n">
         <v>1</v>
       </c>
-      <c r="AI6" t="n">
+      <c r="AK6" t="n">
         <v>25.89556091315245</v>
       </c>
-      <c r="AJ6" t="n">
+      <c r="AL6" t="n">
         <v>184.7922411017663</v>
       </c>
-      <c r="AK6" t="n">
+      <c r="AM6" t="n">
         <v>68.52194177390115</v>
       </c>
-      <c r="AL6" t="n">
+      <c r="AN6" t="n">
         <v>16085.17130276284</v>
       </c>
-      <c r="AM6" t="n">
+      <c r="AO6" t="n">
         <v>1807007.792455447</v>
       </c>
-      <c r="AN6" t="n">
+      <c r="AP6" t="n">
         <v>72.39919536984755</v>
       </c>
-      <c r="AO6" t="n">
+      <c r="AQ6" t="n">
         <v>1</v>
       </c>
-      <c r="AP6" t="n">
-        <v>26.69285714285714</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>186.6880952380952</v>
-      </c>
       <c r="AR6" t="n">
-        <v>3.142857142857143</v>
+        <v>27.5</v>
       </c>
       <c r="AS6" t="n">
-        <v>226.4285714285714</v>
+        <v>185.25</v>
       </c>
       <c r="AT6" t="n">
-        <v>66000</v>
+        <v>4</v>
       </c>
       <c r="AU6" t="n">
-        <v>11414285.71428571</v>
+        <v>294</v>
       </c>
       <c r="AV6" t="n">
-        <v>236</v>
+        <v>93000</v>
       </c>
       <c r="AW6" t="n">
-        <v>3.142857142857143</v>
+        <v>20000000</v>
       </c>
       <c r="AX6" t="n">
-        <v>25.47857142857143</v>
+        <v>305</v>
       </c>
       <c r="AY6" t="n">
-        <v>189.1404761904762</v>
+        <v>5</v>
       </c>
       <c r="AZ6" t="n">
-        <v>2.714285714285714</v>
+        <v>27.25</v>
       </c>
       <c r="BA6" t="n">
-        <v>187.7142857142857</v>
+        <v>185.25</v>
       </c>
       <c r="BB6" t="n">
-        <v>41571.42857142857</v>
+        <v>4</v>
       </c>
       <c r="BC6" t="n">
-        <v>5300000</v>
+        <v>278</v>
       </c>
       <c r="BD6" t="n">
-        <v>198</v>
+        <v>65000</v>
       </c>
       <c r="BE6" t="n">
-        <v>2.714285714285714</v>
-      </c>
-      <c r="BF6" t="inlineStr">
-        <is>
-          <t>M5BRZDsC</t>
-        </is>
-      </c>
-      <c r="BG6" t="inlineStr">
-        <is>
-          <t>4ljanukM</t>
-        </is>
+        <v>7500000</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>288</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="7">
@@ -1730,7 +1730,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">dankert b 
+          <t xml:space="preserve">dingert c 
   ger </t>
         </is>
       </c>
@@ -1753,169 +1753,169 @@
           <t>88HSzjDr</t>
         </is>
       </c>
-      <c r="H7" t="n">
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>IkCftsQm</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>4fuCGs9P</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
         <v>59</v>
       </c>
-      <c r="I7" t="n">
+      <c r="K7" t="n">
         <v>591</v>
       </c>
-      <c r="J7" t="n">
+      <c r="L7" t="n">
         <v>0</v>
       </c>
-      <c r="K7" t="n">
+      <c r="M7" t="n">
         <v>20242025</v>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>germany</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>bundesliga</t>
         </is>
       </c>
-      <c r="N7" t="n">
+      <c r="P7" t="n">
         <v>26.30034722222222</v>
       </c>
-      <c r="O7" t="n">
+      <c r="Q7" t="n">
         <v>183.9454861111111</v>
       </c>
-      <c r="P7" t="n">
+      <c r="R7" t="n">
         <v>80.55312499999999</v>
       </c>
-      <c r="Q7" t="n">
+      <c r="S7" t="n">
         <v>57571.52777777778</v>
       </c>
-      <c r="R7" t="n">
+      <c r="T7" t="n">
         <v>29693402.77777778</v>
       </c>
-      <c r="S7" t="n">
+      <c r="U7" t="n">
         <v>83.65138888888889</v>
       </c>
-      <c r="T7" t="n">
+      <c r="V7" t="n">
         <v>2.270486111111111</v>
       </c>
-      <c r="U7" t="n">
+      <c r="W7" t="n">
         <v>26.0875</v>
       </c>
-      <c r="V7" t="n">
+      <c r="X7" t="n">
         <v>185.0125</v>
       </c>
-      <c r="W7" t="n">
+      <c r="Y7" t="n">
         <v>74.91250000000001</v>
       </c>
-      <c r="X7" t="n">
+      <c r="Z7" t="n">
         <v>23875</v>
       </c>
-      <c r="Y7" t="n">
+      <c r="AA7" t="n">
         <v>7567500</v>
       </c>
-      <c r="Z7" t="n">
+      <c r="AB7" t="n">
         <v>77.52500000000001</v>
       </c>
-      <c r="AA7" t="n">
+      <c r="AC7" t="n">
         <v>1.375</v>
       </c>
-      <c r="AB7" t="n">
+      <c r="AD7" t="n">
         <v>25.37051163168617</v>
       </c>
-      <c r="AC7" t="n">
+      <c r="AE7" t="n">
         <v>185.3800319370172</v>
       </c>
-      <c r="AD7" t="n">
+      <c r="AF7" t="n">
         <v>77.7063916126658</v>
       </c>
-      <c r="AE7" t="n">
+      <c r="AG7" t="n">
         <v>48885.4848657964</v>
       </c>
-      <c r="AF7" t="n">
+      <c r="AH7" t="n">
         <v>21657661.84937891</v>
       </c>
-      <c r="AG7" t="n">
+      <c r="AI7" t="n">
         <v>82.03091706678684</v>
       </c>
-      <c r="AH7" t="n">
+      <c r="AJ7" t="n">
         <v>1.941087260262957</v>
       </c>
-      <c r="AI7" t="n">
+      <c r="AK7" t="n">
         <v>25.69703743053286</v>
       </c>
-      <c r="AJ7" t="n">
+      <c r="AL7" t="n">
         <v>182.788760624387</v>
       </c>
-      <c r="AK7" t="n">
+      <c r="AM7" t="n">
         <v>72.99202217500272</v>
       </c>
-      <c r="AL7" t="n">
+      <c r="AN7" t="n">
         <v>22148.60044132069</v>
       </c>
-      <c r="AM7" t="n">
+      <c r="AO7" t="n">
         <v>6073390.531355562</v>
       </c>
-      <c r="AN7" t="n">
+      <c r="AP7" t="n">
         <v>77.35256074970033</v>
       </c>
-      <c r="AO7" t="n">
+      <c r="AQ7" t="n">
         <v>1.259427100359595</v>
       </c>
-      <c r="AP7" t="n">
-        <v>24.56666666666667</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>180.9547619047619</v>
-      </c>
       <c r="AR7" t="n">
-        <v>3.571428571428572</v>
+        <v>23.5</v>
       </c>
       <c r="AS7" t="n">
-        <v>277.1428571428572</v>
+        <v>176.5</v>
       </c>
       <c r="AT7" t="n">
-        <v>176428.5714285714</v>
+        <v>4</v>
       </c>
       <c r="AU7" t="n">
-        <v>78214285.71428572</v>
+        <v>324</v>
       </c>
       <c r="AV7" t="n">
-        <v>300.2857142857143</v>
+        <v>237000</v>
       </c>
       <c r="AW7" t="n">
-        <v>7.857142857142857</v>
+        <v>151000000</v>
       </c>
       <c r="AX7" t="n">
-        <v>22.74897959183673</v>
+        <v>342</v>
       </c>
       <c r="AY7" t="n">
-        <v>183.1360544217687</v>
+        <v>10</v>
       </c>
       <c r="AZ7" t="n">
-        <v>5.285714285714286</v>
+        <v>24.125</v>
       </c>
       <c r="BA7" t="n">
-        <v>369.2857142857143</v>
+        <v>183.625</v>
       </c>
       <c r="BB7" t="n">
-        <v>75428.57142857143</v>
+        <v>8</v>
       </c>
       <c r="BC7" t="n">
-        <v>28896428.57142857</v>
+        <v>572</v>
       </c>
       <c r="BD7" t="n">
-        <v>409.1428571428572</v>
+        <v>137000</v>
       </c>
       <c r="BE7" t="n">
-        <v>6.857142857142857</v>
-      </c>
-      <c r="BF7" t="inlineStr">
-        <is>
-          <t>IkCftsQm</t>
-        </is>
-      </c>
-      <c r="BG7" t="inlineStr">
-        <is>
-          <t>4fuCGs9P</t>
-        </is>
+        <v>43225000</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>619</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="8">
@@ -1952,155 +1952,155 @@
           <t>hQAtP9Sl</t>
         </is>
       </c>
-      <c r="H8" t="n">
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>f3ddUIXs</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>0jdIgO6t</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
         <v>59</v>
       </c>
-      <c r="I8" t="n">
+      <c r="K8" t="n">
         <v>591</v>
       </c>
-      <c r="J8" t="n">
+      <c r="L8" t="n">
         <v>0</v>
       </c>
-      <c r="K8" t="n">
+      <c r="M8" t="n">
         <v>20242025</v>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>germany</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>bundesliga</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr"/>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="inlineStr"/>
       <c r="T8" t="inlineStr"/>
-      <c r="U8" t="n">
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" t="n">
         <v>27.24861111111111</v>
       </c>
-      <c r="V8" t="n">
+      <c r="X8" t="n">
         <v>185.9104166666667</v>
       </c>
-      <c r="W8" t="n">
+      <c r="Y8" t="n">
         <v>75.16666666666666</v>
       </c>
-      <c r="X8" t="n">
+      <c r="Z8" t="n">
         <v>29614.23611111111</v>
       </c>
-      <c r="Y8" t="n">
+      <c r="AA8" t="n">
         <v>7584861.111111112</v>
       </c>
-      <c r="Z8" t="n">
+      <c r="AB8" t="n">
         <v>78.94236111111111</v>
       </c>
-      <c r="AA8" t="n">
+      <c r="AC8" t="n">
         <v>1.589583333333334</v>
       </c>
-      <c r="AB8" t="n">
+      <c r="AD8" t="n">
         <v>24.06069624819624</v>
       </c>
-      <c r="AC8" t="n">
+      <c r="AE8" t="n">
         <v>185.4313897907647</v>
       </c>
-      <c r="AD8" t="n">
+      <c r="AF8" t="n">
         <v>72.04458648989899</v>
       </c>
-      <c r="AE8" t="n">
+      <c r="AG8" t="n">
         <v>20238.51235569986</v>
       </c>
-      <c r="AF8" t="n">
+      <c r="AH8" t="n">
         <v>5071312.454906205</v>
       </c>
-      <c r="AG8" t="n">
+      <c r="AI8" t="n">
         <v>77.21329365079364</v>
       </c>
-      <c r="AH8" t="n">
+      <c r="AJ8" t="n">
         <v>1.078609758297258</v>
       </c>
-      <c r="AI8" t="n">
+      <c r="AK8" t="n">
         <v>24.40196324143693</v>
       </c>
-      <c r="AJ8" t="n">
+      <c r="AL8" t="n">
         <v>184.79335839599</v>
       </c>
-      <c r="AK8" t="n">
+      <c r="AM8" t="n">
         <v>71.46188909774436</v>
       </c>
-      <c r="AL8" t="n">
+      <c r="AN8" t="n">
         <v>24020.84899749373</v>
       </c>
-      <c r="AM8" t="n">
+      <c r="AO8" t="n">
         <v>5589053.10150376</v>
       </c>
-      <c r="AN8" t="n">
+      <c r="AP8" t="n">
         <v>77.93593880534669</v>
       </c>
-      <c r="AO8" t="n">
+      <c r="AQ8" t="n">
         <v>1.220927318295739</v>
       </c>
-      <c r="AP8" t="n">
-        <v>25.81666666666667</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>183.5928571428572</v>
-      </c>
       <c r="AR8" t="n">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="AS8" t="n">
-        <v>354</v>
+        <v>181.1428571428571</v>
       </c>
       <c r="AT8" t="n">
-        <v>89714.28571428571</v>
+        <v>7</v>
       </c>
       <c r="AU8" t="n">
-        <v>14610714.28571429</v>
+        <v>508</v>
       </c>
       <c r="AV8" t="n">
-        <v>364.5714285714286</v>
+        <v>143000</v>
       </c>
       <c r="AW8" t="n">
-        <v>5</v>
+        <v>26800000</v>
       </c>
       <c r="AX8" t="n">
-        <v>26.61479591836735</v>
+        <v>518</v>
       </c>
       <c r="AY8" t="n">
-        <v>183.0484693877551</v>
+        <v>7</v>
       </c>
       <c r="AZ8" t="n">
-        <v>6.142857142857143</v>
+        <v>26.75</v>
       </c>
       <c r="BA8" t="n">
-        <v>458.4285714285714</v>
+        <v>183</v>
       </c>
       <c r="BB8" t="n">
-        <v>169571.4285714286</v>
+        <v>4</v>
       </c>
       <c r="BC8" t="n">
-        <v>41042857.14285714</v>
+        <v>299</v>
       </c>
       <c r="BD8" t="n">
-        <v>475</v>
+        <v>119000</v>
       </c>
       <c r="BE8" t="n">
-        <v>9.857142857142858</v>
-      </c>
-      <c r="BF8" t="inlineStr">
-        <is>
-          <t>f3ddUIXs</t>
-        </is>
-      </c>
-      <c r="BG8" t="inlineStr">
-        <is>
-          <t>0jdIgO6t</t>
-        </is>
+        <v>26900000</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>308</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="9">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">schlager d 
+          <t xml:space="preserve">zwayer f 
   ger </t>
         </is>
       </c>
@@ -2137,169 +2137,169 @@
           <t>8vndvXTk</t>
         </is>
       </c>
-      <c r="H9" t="n">
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>hAcTWKKN</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>UkPWzhq8</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
         <v>59</v>
       </c>
-      <c r="I9" t="n">
+      <c r="K9" t="n">
         <v>591</v>
       </c>
-      <c r="J9" t="n">
+      <c r="L9" t="n">
         <v>0</v>
       </c>
-      <c r="K9" t="n">
+      <c r="M9" t="n">
         <v>20242025</v>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>germany</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>bundesliga</t>
         </is>
       </c>
-      <c r="N9" t="n">
+      <c r="P9" t="n">
         <v>24.57449494949495</v>
       </c>
-      <c r="O9" t="n">
+      <c r="Q9" t="n">
         <v>186.0209595959596</v>
       </c>
-      <c r="P9" t="n">
+      <c r="R9" t="n">
         <v>75.80770202020202</v>
       </c>
-      <c r="Q9" t="n">
+      <c r="S9" t="n">
         <v>26603.53535353535</v>
       </c>
-      <c r="R9" t="n">
+      <c r="T9" t="n">
         <v>13163576.38888889</v>
       </c>
-      <c r="S9" t="n">
+      <c r="U9" t="n">
         <v>79.51376262626263</v>
       </c>
-      <c r="T9" t="n">
+      <c r="V9" t="n">
         <v>1.472348484848485</v>
       </c>
-      <c r="U9" t="n">
+      <c r="W9" t="n">
         <v>24.24398148148148</v>
       </c>
-      <c r="V9" t="n">
+      <c r="X9" t="n">
         <v>185.4805555555556</v>
       </c>
-      <c r="W9" t="n">
+      <c r="Y9" t="n">
         <v>75.95231481481481</v>
       </c>
-      <c r="X9" t="n">
+      <c r="Z9" t="n">
         <v>33214.81481481482</v>
       </c>
-      <c r="Y9" t="n">
+      <c r="AA9" t="n">
         <v>13640555.55555556</v>
       </c>
-      <c r="Z9" t="n">
+      <c r="AB9" t="n">
         <v>81.23935185185185</v>
       </c>
-      <c r="AA9" t="n">
+      <c r="AC9" t="n">
         <v>1.681018518518519</v>
       </c>
-      <c r="AB9" t="n">
+      <c r="AD9" t="n">
         <v>24.52925583188741</v>
       </c>
-      <c r="AC9" t="n">
+      <c r="AE9" t="n">
         <v>185.3232520403573</v>
       </c>
-      <c r="AD9" t="n">
+      <c r="AF9" t="n">
         <v>74.78132430435062</v>
       </c>
-      <c r="AE9" t="n">
+      <c r="AG9" t="n">
         <v>25274.78552149605</v>
       </c>
-      <c r="AF9" t="n">
+      <c r="AH9" t="n">
         <v>11943278.36819613</v>
       </c>
-      <c r="AG9" t="n">
+      <c r="AI9" t="n">
         <v>78.4085333526123</v>
       </c>
-      <c r="AH9" t="n">
+      <c r="AJ9" t="n">
         <v>1.497288895315211</v>
       </c>
-      <c r="AI9" t="n">
+      <c r="AK9" t="n">
         <v>23.01548735223755</v>
       </c>
-      <c r="AJ9" t="n">
+      <c r="AL9" t="n">
         <v>184.5430240666841</v>
       </c>
-      <c r="AK9" t="n">
+      <c r="AM9" t="n">
         <v>73.1900859057738</v>
       </c>
-      <c r="AL9" t="n">
+      <c r="AN9" t="n">
         <v>26812.58014270301</v>
       </c>
-      <c r="AM9" t="n">
+      <c r="AO9" t="n">
         <v>9503560.903009528</v>
       </c>
-      <c r="AN9" t="n">
+      <c r="AP9" t="n">
         <v>80.85620371952608</v>
       </c>
-      <c r="AO9" t="n">
+      <c r="AQ9" t="n">
         <v>1.426068262233123</v>
       </c>
-      <c r="AP9" t="n">
-        <v>22.35714285714286</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>183.6047619047619</v>
-      </c>
       <c r="AR9" t="n">
-        <v>4.285714285714286</v>
+        <v>22.71428571428572</v>
       </c>
       <c r="AS9" t="n">
-        <v>298.7142857142857</v>
+        <v>183.8571428571429</v>
       </c>
       <c r="AT9" t="n">
-        <v>77142.85714285714</v>
+        <v>7</v>
       </c>
       <c r="AU9" t="n">
-        <v>21278571.42857143</v>
+        <v>498</v>
       </c>
       <c r="AV9" t="n">
-        <v>337.4285714285714</v>
+        <v>146000</v>
       </c>
       <c r="AW9" t="n">
-        <v>5.142857142857143</v>
+        <v>55050000</v>
       </c>
       <c r="AX9" t="n">
-        <v>19.61904761904762</v>
+        <v>554</v>
       </c>
       <c r="AY9" t="n">
-        <v>177.5238095238095</v>
+        <v>10</v>
       </c>
       <c r="AZ9" t="n">
-        <v>1.571428571428571</v>
+        <v>21.33333333333333</v>
       </c>
       <c r="BA9" t="n">
-        <v>97.42857142857143</v>
+        <v>182.3333333333333</v>
       </c>
       <c r="BB9" t="n">
-        <v>11714.28571428571</v>
+        <v>3</v>
       </c>
       <c r="BC9" t="n">
-        <v>3421428.571428571</v>
+        <v>197</v>
       </c>
       <c r="BD9" t="n">
-        <v>122.8571428571429</v>
+        <v>56000</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.857142857142857</v>
-      </c>
-      <c r="BF9" t="inlineStr">
-        <is>
-          <t>hAcTWKKN</t>
-        </is>
-      </c>
-      <c r="BG9" t="inlineStr">
-        <is>
-          <t>UkPWzhq8</t>
-        </is>
+        <v>9575000</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>234</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="10">
@@ -2313,192 +2313,1571 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
+          <t xml:space="preserve">osmers h 
+  ger </t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">voith arena
+  heidenheim </t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>15000</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>KWixEVWi</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>nwkTahLL</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>A15eUM4C</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2VSFgl3c</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>59</v>
+      </c>
+      <c r="K10" t="n">
+        <v>591</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="P10" t="n">
+        <v>26.84204545454546</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>186.4840909090909</v>
+      </c>
+      <c r="R10" t="n">
+        <v>72.46250000000001</v>
+      </c>
+      <c r="S10" t="n">
+        <v>22043.18181818182</v>
+      </c>
+      <c r="T10" t="n">
+        <v>3228636.363636364</v>
+      </c>
+      <c r="U10" t="n">
+        <v>74.49204545454546</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.048863636363636</v>
+      </c>
+      <c r="W10" t="n">
+        <v>24.63888888888889</v>
+      </c>
+      <c r="X10" t="n">
+        <v>184.8611111111111</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>75.07870370370371</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>35773.14814814815</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>9584722.222222222</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>79.68518518518518</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>1.356481481481481</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>25.99362821215443</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>185.1477446413348</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>69.55711469370357</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>20094.20137620265</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>2177827.647363293</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>72.18486024844721</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>1.04539641943734</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>25.08425023301394</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>184.356916403315</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>73.46671031854078</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>33329.31221752795</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>8219357.325420547</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>78.25516429905122</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>1.395182710722109</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>22.33333333333333</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>188</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>193</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>44000</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>3875000</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>215</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>3</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>23.57142857142857</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>184</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>7</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>520</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>241000</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>70800000</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>557</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>EuQnZBVQ</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>45618.6875</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
           <t xml:space="preserve">brych f 
   ger </t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">voith arena
-  heidenheim </t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>15000</v>
-      </c>
-      <c r="F10" t="inlineStr">
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">allianz arena
+  munich </t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>75024</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>nVp0wiqd</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>fTVNku3I</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>K6A2elS9</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2VSFgl3c</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>59</v>
+      </c>
+      <c r="K11" t="n">
+        <v>591</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="P11" t="n">
+        <v>27.575</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>183.975</v>
+      </c>
+      <c r="R11" t="n">
+        <v>83.67777777777778</v>
+      </c>
+      <c r="S11" t="n">
+        <v>82602.77777777778</v>
+      </c>
+      <c r="T11" t="n">
+        <v>49549687.5</v>
+      </c>
+      <c r="U11" t="n">
+        <v>85.71666666666667</v>
+      </c>
+      <c r="V11" t="n">
+        <v>3.331944444444444</v>
+      </c>
+      <c r="W11" t="inlineStr"/>
+      <c r="X11" t="inlineStr"/>
+      <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="inlineStr"/>
+      <c r="AA11" t="inlineStr"/>
+      <c r="AB11" t="inlineStr"/>
+      <c r="AC11" t="inlineStr"/>
+      <c r="AD11" t="n">
+        <v>26.31192917956656</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>183.0611750730994</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>80.37420020639834</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>75434.36819172114</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>35147016.32105693</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>83.74456376848985</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>2.603642070863433</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>24.06069624819624</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>185.4313897907647</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>72.04458648989899</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>20238.51235569986</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>5071312.454906205</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>77.21329365079364</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>1.078609758297258</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>22.00952380952381</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>184.8285714285714</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>5.285714285714286</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>385.4285714285714</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>210428.5714285714</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>97221428.57142857</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>433.4285714285714</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>25.81666666666667</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>183.5928571428572</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>354</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>89714.28571428571</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>14610714.28571429</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>364.5714285714286</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>2qNaDU87</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>45619.47916666666</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">willenborg f 
+  ger </t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bayarena
+  leverkusen </t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>30210</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>4jcj2zMd</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
         <is>
           <t>KWixEVWi</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>hAcTWKKN</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>4ljanukM</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>59</v>
+      </c>
+      <c r="K12" t="n">
+        <v>591</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>26.50448232323232</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>184.5846590909091</v>
+      </c>
+      <c r="R12" t="n">
+        <v>83.60921717171718</v>
+      </c>
+      <c r="S12" t="n">
+        <v>99236.93181818182</v>
+      </c>
+      <c r="T12" t="n">
+        <v>48423295.45454545</v>
+      </c>
+      <c r="U12" t="n">
+        <v>85.70018939393938</v>
+      </c>
+      <c r="V12" t="n">
+        <v>3.023863636363636</v>
+      </c>
+      <c r="W12" t="n">
+        <v>26.84204545454546</v>
+      </c>
+      <c r="X12" t="n">
+        <v>186.4840909090909</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>72.46250000000001</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>22043.18181818182</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>3228636.363636364</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>74.49204545454546</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>1.048863636363636</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>24.63972895976573</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>181.6395150294966</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>80.36146217956879</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>81495.40998217469</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>38064377.54315741</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>84.05611007660639</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>2.364937584882438</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>25.99362821215443</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>185.1477446413348</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>69.55711469370357</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>20094.20137620265</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>2177827.647363293</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>72.18486024844721</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>1.04539641943734</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>24</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>174</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>78</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>64000</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>28500000</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>85</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>24.16666666666666</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>185.5952380952381</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>201.2857142857143</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>52000</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>5717857.142857143</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>215.7142857142857</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>3.285714285714286</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>pOGITkgl</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>45619.47916666666</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">brand b 
+  ger </t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">signal iduna park
+  dortmund </t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>81365</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>nP1i5US1</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>fiEQZ7C7</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>IkCftsQm</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>vZA6VYpf</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>59</v>
+      </c>
+      <c r="K13" t="n">
+        <v>591</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
+        <v>26.61931818181818</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>186.0761363636364</v>
+      </c>
+      <c r="R13" t="n">
+        <v>81.72386363636363</v>
+      </c>
+      <c r="S13" t="n">
+        <v>57572.72727272727</v>
+      </c>
+      <c r="T13" t="n">
+        <v>36480113.63636364</v>
+      </c>
+      <c r="U13" t="n">
+        <v>83.87159090909091</v>
+      </c>
+      <c r="V13" t="n">
+        <v>2.523863636363636</v>
+      </c>
+      <c r="W13" t="n">
+        <v>27.1</v>
+      </c>
+      <c r="X13" t="n">
+        <v>184.25</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>76.51250000000002</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>26875</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>11181250</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>78.8</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>24.86772967959113</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>183.6715583522085</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>77.07611101059243</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>43169.13121708013</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>22125694.40814603</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>82.51749432627915</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>1.895776651968602</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>26.65878139169127</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>183.677628956721</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>73.94523228263637</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>23646.48156225253</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>6517540.338035568</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>76.99487793609227</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>1.373969366714857</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>21.79761904761904</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>183.7797619047619</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>3.285714285714286</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>249.8571428571429</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>121142.8571428571</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>74157142.85714285</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>276.8571428571428</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>6.714285714285714</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>25.86428571428572</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>185.8047619047619</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>5.142857142857143</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>363.7142857142857</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>93285.71428571429</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>22871428.57142857</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>383.4285714285714</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>5.428571428571429</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>E38ZP7hD</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>45619.47916666666</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">stieler t 
+  ger </t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">prezero arena
+  sinsheim </t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>30150</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>hQAtP9Sl</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>KbS1suSm</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>KUx4Q7x1</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>pfoInmcq</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>59</v>
+      </c>
+      <c r="K14" t="n">
+        <v>591</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="P14" t="n">
+        <v>27.24861111111111</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>185.9104166666667</v>
+      </c>
+      <c r="R14" t="n">
+        <v>75.16666666666666</v>
+      </c>
+      <c r="S14" t="n">
+        <v>29614.23611111111</v>
+      </c>
+      <c r="T14" t="n">
+        <v>7584861.111111112</v>
+      </c>
+      <c r="U14" t="n">
+        <v>78.94236111111111</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.589583333333334</v>
+      </c>
+      <c r="W14" t="n">
+        <v>26.30034722222222</v>
+      </c>
+      <c r="X14" t="n">
+        <v>183.9454861111111</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>80.55312499999999</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>57571.52777777778</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>29693402.77777778</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>83.65138888888889</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>2.270486111111111</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>24.40196324143693</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>184.79335839599</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>71.46188909774436</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>24020.84899749373</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>5589053.10150376</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>77.93593880534669</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>1.220927318295739</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>25.37051163168617</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>185.3800319370172</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>77.7063916126658</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>48885.4848657964</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>21657661.84937891</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>82.03091706678684</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>1.941087260262957</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>26.61479591836735</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>183.0484693877551</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>6.142857142857143</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>458.4285714285714</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>169571.4285714286</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>41042857.14285714</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>475</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>9.857142857142858</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>24.56666666666667</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>180.9547619047619</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>3.571428571428572</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>277.1428571428572</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>176428.5714285714</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>78214285.71428572</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>300.2857142857143</v>
+      </c>
+      <c r="BG14" t="n">
+        <v>7.857142857142857</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>fwAoyY0E</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>45619.47916666666</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">schlager d 
+  ger </t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mhparena
+  stuttgart </t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>60449</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>nJQmYp1B</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>8Y2m6ADe</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>hAcTWKKN</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>UkPWzhq8</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>59</v>
+      </c>
+      <c r="K15" t="n">
+        <v>591</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="P15" t="n">
+        <v>24.57449494949495</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>186.0209595959596</v>
+      </c>
+      <c r="R15" t="n">
+        <v>75.80770202020202</v>
+      </c>
+      <c r="S15" t="n">
+        <v>26603.53535353535</v>
+      </c>
+      <c r="T15" t="n">
+        <v>13163576.38888889</v>
+      </c>
+      <c r="U15" t="n">
+        <v>79.51376262626263</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.472348484848485</v>
+      </c>
+      <c r="W15" t="n">
+        <v>28.34490740740741</v>
+      </c>
+      <c r="X15" t="n">
+        <v>186.0833333333333</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>71.69907407407408</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>16979.16666666667</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>2252025.462962963</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>73.83796296296296</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>24.52925583188741</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>185.3232520403573</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>74.78132430435062</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>25274.78552149605</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>11943278.36819613</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>78.4085333526123</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>1.497288895315211</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>26.41635443122857</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>184.6034581995681</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>69.04034053919638</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>16141.66687622065</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>1787561.084986714</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>73.39604725302665</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>22.35714285714286</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>183.6047619047619</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>298.7142857142857</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>77142.85714285714</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>21278571.42857143</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>337.4285714285714</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>5.142857142857143</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>25.95238095238095</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>186.25</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>3.142857142857143</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>220.4285714285714</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>52571.42857142857</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>8253571.428571428</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>232</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>3.428571428571428</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>SrjMmBpK</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>45619.47916666666</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">jollenbeck m 
+  ger </t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">volkswagen arena
+  wolfsburg </t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>28917</v>
+      </c>
+      <c r="F16" t="inlineStr">
         <is>
           <t>nwkTahLL</t>
         </is>
       </c>
-      <c r="H10" t="n">
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>pzHW4oaE</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>f3ddUIXs</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>hpYJ6izc</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
         <v>59</v>
       </c>
-      <c r="I10" t="n">
+      <c r="K16" t="n">
         <v>591</v>
       </c>
-      <c r="J10" t="n">
+      <c r="L16" t="n">
         <v>0</v>
       </c>
-      <c r="K10" t="n">
+      <c r="M16" t="n">
         <v>20242025</v>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="N16" t="inlineStr">
         <is>
           <t>germany</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="O16" t="inlineStr">
         <is>
           <t>bundesliga</t>
         </is>
       </c>
-      <c r="N10" t="n">
-        <v>26.84204545454546</v>
-      </c>
-      <c r="O10" t="n">
-        <v>186.4840909090909</v>
-      </c>
-      <c r="P10" t="n">
-        <v>72.46250000000001</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>22043.18181818182</v>
-      </c>
-      <c r="R10" t="n">
-        <v>3228636.363636364</v>
-      </c>
-      <c r="S10" t="n">
-        <v>74.49204545454546</v>
-      </c>
-      <c r="T10" t="n">
-        <v>1.048863636363636</v>
-      </c>
-      <c r="U10" t="n">
+      <c r="P16" t="n">
         <v>24.63888888888889</v>
       </c>
-      <c r="V10" t="n">
+      <c r="Q16" t="n">
         <v>184.8611111111111</v>
       </c>
-      <c r="W10" t="n">
+      <c r="R16" t="n">
         <v>75.07870370370371</v>
       </c>
-      <c r="X10" t="n">
+      <c r="S16" t="n">
         <v>35773.14814814815</v>
       </c>
-      <c r="Y10" t="n">
+      <c r="T16" t="n">
         <v>9584722.222222222</v>
       </c>
-      <c r="Z10" t="n">
+      <c r="U16" t="n">
         <v>79.68518518518518</v>
       </c>
-      <c r="AA10" t="n">
+      <c r="V16" t="n">
         <v>1.356481481481481</v>
       </c>
-      <c r="AB10" t="n">
-        <v>25.99362821215443</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>185.1477446413348</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>69.55711469370357</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>20094.20137620265</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>2177827.647363293</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>72.18486024844721</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>1.04539641943734</v>
-      </c>
-      <c r="AI10" t="n">
+      <c r="W16" t="n">
+        <v>26.73282828282828</v>
+      </c>
+      <c r="X16" t="n">
+        <v>186.4034090909091</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>74.49166666666666</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>26611.99494949495</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>6037575.757575758</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>77.49595959595959</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1.338510101010101</v>
+      </c>
+      <c r="AD16" t="n">
         <v>25.08425023301394</v>
       </c>
-      <c r="AJ10" t="n">
+      <c r="AE16" t="n">
         <v>184.356916403315</v>
       </c>
-      <c r="AK10" t="n">
+      <c r="AF16" t="n">
         <v>73.46671031854078</v>
       </c>
-      <c r="AL10" t="n">
+      <c r="AG16" t="n">
         <v>33329.31221752795</v>
       </c>
-      <c r="AM10" t="n">
+      <c r="AH16" t="n">
         <v>8219357.325420547</v>
       </c>
-      <c r="AN10" t="n">
+      <c r="AI16" t="n">
         <v>78.25516429905122</v>
       </c>
-      <c r="AO10" t="n">
+      <c r="AJ16" t="n">
         <v>1.395182710722109</v>
       </c>
-      <c r="AP10" t="n">
-        <v>24.16666666666666</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>185.5952380952381</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>3</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>201.2857142857143</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>52000</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>5717857.142857143</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>215.7142857142857</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>3.285714285714286</v>
-      </c>
-      <c r="AX10" t="n">
+      <c r="AK16" t="n">
+        <v>26.32467740910247</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>182.5191663488431</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>73.17101926010679</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>25448.02949402492</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>4287583.587592169</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>75.89593821510297</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>1.110020976353928</v>
+      </c>
+      <c r="AR16" t="n">
         <v>23.7891156462585</v>
       </c>
-      <c r="AY10" t="n">
+      <c r="AS16" t="n">
         <v>183.2982993197279</v>
       </c>
-      <c r="AZ10" t="n">
+      <c r="AT16" t="n">
         <v>5.571428571428571</v>
       </c>
-      <c r="BA10" t="n">
+      <c r="AU16" t="n">
         <v>412.1428571428572</v>
       </c>
-      <c r="BB10" t="n">
+      <c r="AV16" t="n">
         <v>195571.4285714286</v>
       </c>
-      <c r="BC10" t="n">
+      <c r="AW16" t="n">
         <v>59085714.28571428</v>
       </c>
-      <c r="BD10" t="n">
+      <c r="AX16" t="n">
         <v>443.2857142857143</v>
       </c>
-      <c r="BE10" t="n">
+      <c r="AY16" t="n">
         <v>8.571428571428571</v>
       </c>
-      <c r="BF10" t="inlineStr">
-        <is>
-          <t>A15eUM4C</t>
-        </is>
-      </c>
-      <c r="BG10" t="inlineStr">
-        <is>
-          <t>2VSFgl3c</t>
-        </is>
+      <c r="AZ16" t="n">
+        <v>28.69047619047619</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>179.8333333333333</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>212.8571428571429</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>89571.42857142857</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>16428571.42857143</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>214.1428571428571</v>
+      </c>
+      <c r="BG16" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>6w5RRTN0</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>45619.60416666666</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dankert b 
+  ger </t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">deutsche bank park
+  frankfurt </t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>58000</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>8vndvXTk</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Ig1f1fy3</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>UgdQz0fK</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>4fuCGs9P</t>
+        </is>
+      </c>
+      <c r="J17" t="n">
+        <v>59</v>
+      </c>
+      <c r="K17" t="n">
+        <v>591</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>20242025</v>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>bundesliga</t>
+        </is>
+      </c>
+      <c r="P17" t="n">
+        <v>24.24398148148148</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>185.4805555555556</v>
+      </c>
+      <c r="R17" t="n">
+        <v>75.95231481481481</v>
+      </c>
+      <c r="S17" t="n">
+        <v>33214.81481481482</v>
+      </c>
+      <c r="T17" t="n">
+        <v>13640555.55555556</v>
+      </c>
+      <c r="U17" t="n">
+        <v>81.23935185185185</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.681018518518519</v>
+      </c>
+      <c r="W17" t="n">
+        <v>27.01931818181819</v>
+      </c>
+      <c r="X17" t="n">
+        <v>182.9647727272727</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>74.33636363636364</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>23502.27272727273</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>5967272.727272728</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>76.69431818181818</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1.097727272727273</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>23.01548735223755</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>184.5430240666841</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>73.1900859057738</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>26812.58014270301</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>9503560.903009528</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>80.85620371952608</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>1.426068262233123</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>24.68268878099399</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>186.1664438548199</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>70.46240321344368</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>20019.85997293134</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>3344203.243719476</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>75.91573345728452</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>19.61904761904762</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>177.5238095238095</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>1.571428571428571</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>97.42857142857143</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>11714.28571428571</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>3421428.571428571</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>122.8571428571429</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>1.857142857142857</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>26.69285714285714</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>186.6880952380952</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>3.142857142857143</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>226.4285714285714</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>66000</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>11414285.71428571</v>
+      </c>
+      <c r="BF17" t="n">
+        <v>236</v>
+      </c>
+      <c r="BG17" t="n">
+        <v>3.142857142857143</v>
       </c>
     </row>
   </sheetData>
